--- a/data/MOL.MI.xlsx
+++ b/data/MOL.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">6.850661277771</t>
+    <t xml:space="preserve">6.85066175460815</t>
   </si>
   <si>
     <t xml:space="preserve">MOL.MI</t>
@@ -47,13 +47,13 @@
     <t xml:space="preserve">6.75772619247437</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66036510467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77100229263306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63823843002319</t>
+    <t xml:space="preserve">6.66036558151245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77100276947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63823795318604</t>
   </si>
   <si>
     <t xml:space="preserve">6.7267484664917</t>
@@ -62,34 +62,34 @@
     <t xml:space="preserve">6.81525754928589</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54972887039185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31960248947144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09832763671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35058116912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23994445800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55857849121094</t>
+    <t xml:space="preserve">6.54972839355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31960296630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09832811355591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35058164596558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23994398117065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5585789680481</t>
   </si>
   <si>
     <t xml:space="preserve">6.46121835708618</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89475536346436</t>
+    <t xml:space="preserve">5.8947548866272</t>
   </si>
   <si>
     <t xml:space="preserve">6.52317571640015</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65594005584717</t>
+    <t xml:space="preserve">6.65594053268433</t>
   </si>
   <si>
     <t xml:space="preserve">6.76215171813965</t>
@@ -98,85 +98,85 @@
     <t xml:space="preserve">6.66479158401489</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69134426116943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68249273300171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01867008209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89918041229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28419876098633</t>
+    <t xml:space="preserve">6.69134378433228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68249416351318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01866912841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89917993545532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28419923782349</t>
   </si>
   <si>
     <t xml:space="preserve">6.06292343139648</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2532205581665</t>
+    <t xml:space="preserve">6.25322008132935</t>
   </si>
   <si>
     <t xml:space="preserve">6.39926147460938</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34173059463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50989818572998</t>
+    <t xml:space="preserve">6.34172964096069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50989866256714</t>
   </si>
   <si>
     <t xml:space="preserve">6.33287954330444</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42581415176392</t>
+    <t xml:space="preserve">6.42581510543823</t>
   </si>
   <si>
     <t xml:space="preserve">6.39040994644165</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3063268661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40811252593994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35500621795654</t>
+    <t xml:space="preserve">6.30632638931274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40811204910278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3550066947937</t>
   </si>
   <si>
     <t xml:space="preserve">6.63381242752075</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43466567993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22666692733765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24436902999878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27534818649292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26649618148804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62938690185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43909025192261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41253805160522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45236730575562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45679330825806</t>
+    <t xml:space="preserve">6.43466520309448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2266674041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24436950683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27534770965576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2664966583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62938642501831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43909072875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41253757476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45236682891846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4567928314209</t>
   </si>
   <si>
     <t xml:space="preserve">6.36828231811523</t>
@@ -188,19 +188,19 @@
     <t xml:space="preserve">6.06734991073608</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28862380981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20454072952271</t>
+    <t xml:space="preserve">6.28862428665161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20453977584839</t>
   </si>
   <si>
     <t xml:space="preserve">6.29304981231689</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24879503250122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22224235534668</t>
+    <t xml:space="preserve">6.24879455566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22224140167236</t>
   </si>
   <si>
     <t xml:space="preserve">6.25764608383179</t>
@@ -209,7 +209,7 @@
     <t xml:space="preserve">6.15585899353027</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1912636756897</t>
+    <t xml:space="preserve">6.19126272201538</t>
   </si>
   <si>
     <t xml:space="preserve">6.58955764770508</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">6.49662256240845</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42138957977295</t>
+    <t xml:space="preserve">6.42138910293579</t>
   </si>
   <si>
     <t xml:space="preserve">6.63348960876465</t>
@@ -230,64 +230,64 @@
     <t xml:space="preserve">6.45274019241333</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54311513900757</t>
+    <t xml:space="preserve">6.54311418533325</t>
   </si>
   <si>
     <t xml:space="preserve">6.44370317459106</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50696468353271</t>
+    <t xml:space="preserve">6.50696516036987</t>
   </si>
   <si>
     <t xml:space="preserve">6.55667161941528</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36688423156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61993360519409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69223356246948</t>
+    <t xml:space="preserve">6.36688470840454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61993265151978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69223308563232</t>
   </si>
   <si>
     <t xml:space="preserve">6.59733963012695</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6831955909729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70578861236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75097513198853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85038805007935</t>
+    <t xml:space="preserve">6.68319606781006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70578908920288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75097560882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85038900375366</t>
   </si>
   <si>
     <t xml:space="preserve">6.94528102874756</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98594951629639</t>
+    <t xml:space="preserve">6.98594999313354</t>
   </si>
   <si>
     <t xml:space="preserve">7.1034369468689</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25255393981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32033634185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45589780807495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30226039886475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37907934188843</t>
+    <t xml:space="preserve">7.25255441665649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32033586502075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45589733123779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30226135253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37907838821411</t>
   </si>
   <si>
     <t xml:space="preserve">7.25707340240479</t>
@@ -296,22 +296,22 @@
     <t xml:space="preserve">7.22996091842651</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22544193267822</t>
+    <t xml:space="preserve">7.22544240951538</t>
   </si>
   <si>
     <t xml:space="preserve">7.19832992553711</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09439945220947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13958597183228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00402545928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08084344863892</t>
+    <t xml:space="preserve">7.09439897537231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13958644866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00402498245239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08084297180176</t>
   </si>
   <si>
     <t xml:space="preserve">6.95883750915527</t>
@@ -320,10 +320,10 @@
     <t xml:space="preserve">6.84135055541992</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11699390411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16669893264771</t>
+    <t xml:space="preserve">7.11699295043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16669845581055</t>
   </si>
   <si>
     <t xml:space="preserve">7.31129837036133</t>
@@ -332,7 +332,7 @@
     <t xml:space="preserve">7.32485342025757</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99950647354126</t>
+    <t xml:space="preserve">6.99950695037842</t>
   </si>
   <si>
     <t xml:space="preserve">6.73290157318115</t>
@@ -341,22 +341,22 @@
     <t xml:space="preserve">7.08987998962402</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18477296829224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85942602157593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67867660522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49792766571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57022762298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57926559448242</t>
+    <t xml:space="preserve">7.18477344512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85942554473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67867612838745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49792814254761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57022714614868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57926464080811</t>
   </si>
   <si>
     <t xml:space="preserve">6.41659069061279</t>
@@ -368,25 +368,25 @@
     <t xml:space="preserve">6.65156412124634</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55215120315552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4617772102356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43466520309448</t>
+    <t xml:space="preserve">6.55215263366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46177768707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43466472625732</t>
   </si>
   <si>
     <t xml:space="preserve">6.75549459457397</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56570816040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77808904647827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71030807495117</t>
+    <t xml:space="preserve">6.56570863723755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77808856964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71030759811401</t>
   </si>
   <si>
     <t xml:space="preserve">6.48889017105103</t>
@@ -395,19 +395,19 @@
     <t xml:space="preserve">6.53859615325928</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66060209274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68771457672119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76001405715942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87750053405762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70126962661743</t>
+    <t xml:space="preserve">6.66060161590576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68771409988403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76001358032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87750101089478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70127010345459</t>
   </si>
   <si>
     <t xml:space="preserve">6.78712606430054</t>
@@ -419,49 +419,49 @@
     <t xml:space="preserve">6.81423807144165</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8187575340271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82327556610107</t>
+    <t xml:space="preserve">6.81875705718994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82327604293823</t>
   </si>
   <si>
     <t xml:space="preserve">6.80520153045654</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92268800735474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90461301803589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86846351623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98143148422241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17573642730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01306295394897</t>
+    <t xml:space="preserve">6.92268753051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90461254119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86846303939819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98143100738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17573690414429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01306247711182</t>
   </si>
   <si>
     <t xml:space="preserve">6.97691249847412</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64252710342407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6967511177063</t>
+    <t xml:space="preserve">6.64252662658691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69675064086914</t>
   </si>
   <si>
     <t xml:space="preserve">6.88653802871704</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93172550201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02209901809692</t>
+    <t xml:space="preserve">6.93172454833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02209949493408</t>
   </si>
   <si>
     <t xml:space="preserve">6.99046802520752</t>
@@ -470,13 +470,13 @@
     <t xml:space="preserve">7.19381141662598</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05824995040894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04921245574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06728744506836</t>
+    <t xml:space="preserve">7.05825042724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04921197891235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0672869682312</t>
   </si>
   <si>
     <t xml:space="preserve">7.14862394332886</t>
@@ -488,19 +488,19 @@
     <t xml:space="preserve">7.06276845932007</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15766191482544</t>
+    <t xml:space="preserve">7.15766096115112</t>
   </si>
   <si>
     <t xml:space="preserve">7.21188640594482</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3835973739624</t>
+    <t xml:space="preserve">7.38359642028809</t>
   </si>
   <si>
     <t xml:space="preserve">7.22092342376709</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24803638458252</t>
+    <t xml:space="preserve">7.24803590774536</t>
   </si>
   <si>
     <t xml:space="preserve">7.18929243087769</t>
@@ -509,58 +509,58 @@
     <t xml:space="preserve">7.35648584365845</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37004137039185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88201951980591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03565549850464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18025541305542</t>
+    <t xml:space="preserve">7.370041847229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88201904296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03565502166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18025588989258</t>
   </si>
   <si>
     <t xml:space="preserve">6.91365003585815</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51915836334229</t>
+    <t xml:space="preserve">7.51915884017944</t>
   </si>
   <si>
     <t xml:space="preserve">7.47849035263062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50108432769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41071033477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27514839172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60953521728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66375780105591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72702074050903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68183326721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67731428146362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63664674758911</t>
+    <t xml:space="preserve">7.50108480453491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41070985794067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27514791488647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60953330993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66375923156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72702121734619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68183374404907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67731475830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63664531707764</t>
   </si>
   <si>
     <t xml:space="preserve">7.77220869064331</t>
   </si>
   <si>
-    <t xml:space="preserve">7.971031665802</t>
+    <t xml:space="preserve">7.97103214263916</t>
   </si>
   <si>
     <t xml:space="preserve">8.34156799316406</t>
@@ -569,64 +569,64 @@
     <t xml:space="preserve">8.41386699676514</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45001697540283</t>
+    <t xml:space="preserve">8.45001792907715</t>
   </si>
   <si>
     <t xml:space="preserve">8.57654094696045</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37771701812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.409348487854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35964298248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22408008575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24215602874756</t>
+    <t xml:space="preserve">8.37771797180176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40934944152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35964107513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22408199310303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24215507507324</t>
   </si>
   <si>
     <t xml:space="preserve">8.33704853057861</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32800960540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32349395751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36416149139404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37320041656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46809005737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30541706085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30090045928955</t>
+    <t xml:space="preserve">8.32801151275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32349109649658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36416244506836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37319850921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46809196472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30541801452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30089950561523</t>
   </si>
   <si>
     <t xml:space="preserve">8.09755611419678</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26926708221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20600509643555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07496356964111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11111259460449</t>
+    <t xml:space="preserve">8.26926612854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20600414276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0749626159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11111354827881</t>
   </si>
   <si>
     <t xml:space="preserve">8.28282451629639</t>
@@ -635,64 +635,64 @@
     <t xml:space="preserve">8.2963809967041</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40482902526855</t>
+    <t xml:space="preserve">8.40483093261719</t>
   </si>
   <si>
     <t xml:space="preserve">8.48164939880371</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42290496826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22859859466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27378749847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02977561950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13370704650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27830410003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43194103240967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6940279006958</t>
+    <t xml:space="preserve">8.42290306091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22859954833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2737865447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02977657318115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13370800018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27830600738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4319429397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69402694702148</t>
   </si>
   <si>
     <t xml:space="preserve">9.57969856262207</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25434970855713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21819972991943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01937770843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16397666931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2001256942749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2091646194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22723865509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94707679748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03745079040527</t>
+    <t xml:space="preserve">9.25434875488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21820068359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01937580108643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16397476196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20012474060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20916366577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22723770141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94707584381104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03745174407959</t>
   </si>
   <si>
     <t xml:space="preserve">9.12782669067383</t>
@@ -701,70 +701,70 @@
     <t xml:space="preserve">9.35376262664795</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55258464813232</t>
+    <t xml:space="preserve">9.55258655548096</t>
   </si>
   <si>
     <t xml:space="preserve">9.47124862670898</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80563545227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89600849151611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2123203277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94119644165039</t>
+    <t xml:space="preserve">9.80563640594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89600944519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2123212814331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94119739532471</t>
   </si>
   <si>
     <t xml:space="preserve">10.4472951889038</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8449430465698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8087921142578</t>
+    <t xml:space="preserve">10.8449420928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8087911605835</t>
   </si>
   <si>
     <t xml:space="preserve">10.908203125</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9353160858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7364931106567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7093811035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.754566192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4764308929443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2261095046997</t>
+    <t xml:space="preserve">10.9353170394897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7364912033081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.709379196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7545680999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.476432800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.226110458374</t>
   </si>
   <si>
     <t xml:space="preserve">10.0128736495972</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3837203979492</t>
+    <t xml:space="preserve">10.3837194442749</t>
   </si>
   <si>
     <t xml:space="preserve">10.4300756454468</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2817392349243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4022626876831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5135173797607</t>
+    <t xml:space="preserve">10.2817373275757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4022617340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5135164260864</t>
   </si>
   <si>
     <t xml:space="preserve">10.4949731826782</t>
@@ -779,103 +779,100 @@
     <t xml:space="preserve">11.0790586471558</t>
   </si>
   <si>
-    <t xml:space="preserve">11.774395942688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5889739990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2181262969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3015661239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0976009368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1439571380615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0327014923096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8287372589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7545671463013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7360258102417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9863481521606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8658199310303</t>
+    <t xml:space="preserve">11.7743968963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5889720916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2181272506714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3015670776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.097601890564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1439580917358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0327033996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8287363052368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7360248565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.986346244812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8658218383789</t>
   </si>
   <si>
     <t xml:space="preserve">10.5691432952881</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1254138946533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0605154037476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4869899749756</t>
+    <t xml:space="preserve">11.1254148483276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0605173110962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4869909286499</t>
   </si>
   <si>
     <t xml:space="preserve">11.0697860717773</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9399909973145</t>
+    <t xml:space="preserve">10.9399900436401</t>
   </si>
   <si>
     <t xml:space="preserve">11.4499063491821</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4035491943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7094974517822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0988883972168</t>
+    <t xml:space="preserve">11.4035511016846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7094993591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0988874435425</t>
   </si>
   <si>
     <t xml:space="preserve">12.3213968276978</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8949222564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5160913467407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5253639221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6737012863159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7478694915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5346355438232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7942276000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7293291091919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5439033508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5809898376465</t>
+    <t xml:space="preserve">11.894923210144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5160903930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5253620147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6736993789673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7478713989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5346336364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7942266464233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7293281555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5439052581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5809888839722</t>
   </si>
   <si>
     <t xml:space="preserve">12.5624475479126</t>
@@ -884,7 +881,7 @@
     <t xml:space="preserve">12.4697360992432</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4975490570068</t>
+    <t xml:space="preserve">12.4975481033325</t>
   </si>
   <si>
     <t xml:space="preserve">12.4882774353027</t>
@@ -896,19 +893,19 @@
     <t xml:space="preserve">12.6273460388184</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5531768798828</t>
+    <t xml:space="preserve">12.5531749725342</t>
   </si>
   <si>
     <t xml:space="preserve">12.1823282241821</t>
   </si>
   <si>
-    <t xml:space="preserve">12.395565032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4233798980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2935819625854</t>
+    <t xml:space="preserve">12.3955640792847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.423378944397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2935838699341</t>
   </si>
   <si>
     <t xml:space="preserve">12.3677520751953</t>
@@ -917,7 +914,7 @@
     <t xml:space="preserve">11.8856515884399</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2843112945557</t>
+    <t xml:space="preserve">12.2843103408813</t>
   </si>
   <si>
     <t xml:space="preserve">12.1730575561523</t>
@@ -926,10 +923,10 @@
     <t xml:space="preserve">12.0525321960449</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9505491256714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3121242523193</t>
+    <t xml:space="preserve">11.95055103302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3121252059937</t>
   </si>
   <si>
     <t xml:space="preserve">12.2657690048218</t>
@@ -938,115 +935,115 @@
     <t xml:space="preserve">11.9412775039673</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9598197937012</t>
+    <t xml:space="preserve">11.9598217010498</t>
   </si>
   <si>
     <t xml:space="preserve">12.3306684494019</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4419221878052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3492088317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3770217895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1545152664185</t>
+    <t xml:space="preserve">12.4419212341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3492097854614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3770246505737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1545143127441</t>
   </si>
   <si>
     <t xml:space="preserve">12.2472267150879</t>
   </si>
   <si>
-    <t xml:space="preserve">12.339940071106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4511938095093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.200870513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4326505661011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3028554916382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2564992904663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.061803817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0247192382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.440634727478</t>
+    <t xml:space="preserve">12.339937210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.451192855835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2008724212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4326496124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3028545379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.256498336792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0618047714233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0247173309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4406328201294</t>
   </si>
   <si>
     <t xml:space="preserve">11.635329246521</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7929391860962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6631422042847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6816854476929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7465829849243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9227342605591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8207530975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8671083450317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7373113632202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.228684425354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1916007995605</t>
+    <t xml:space="preserve">11.7929401397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.663143157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6816864013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.74658203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9227352142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8207521438599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8671092987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7373123168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2286853790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1915979385376</t>
   </si>
   <si>
     <t xml:space="preserve">11.7651252746582</t>
   </si>
   <si>
-    <t xml:space="preserve">11.718770980835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1903133392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2922964096069</t>
+    <t xml:space="preserve">11.7187700271606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1903114318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2922954559326</t>
   </si>
   <si>
     <t xml:space="preserve">11.1624994277954</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5426168441772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4684467315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5982437133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.579701423645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4962606430054</t>
+    <t xml:space="preserve">11.5426177978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4684476852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5982446670532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5797023773193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4962615966797</t>
   </si>
   <si>
     <t xml:space="preserve">11.6724138259888</t>
@@ -1055,16 +1052,16 @@
     <t xml:space="preserve">11.8578367233276</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1452436447144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0061750411987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9134654998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9240236282349</t>
+    <t xml:space="preserve">12.1452445983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0061769485474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9134645462036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9240226745605</t>
   </si>
   <si>
     <t xml:space="preserve">13.9253101348877</t>
@@ -1073,22 +1070,22 @@
     <t xml:space="preserve">14.1107349395752</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0921907424927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9438533782959</t>
+    <t xml:space="preserve">14.092191696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9438524246216</t>
   </si>
   <si>
     <t xml:space="preserve">13.9994802474976</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6299200057983</t>
+    <t xml:space="preserve">14.629919052124</t>
   </si>
   <si>
     <t xml:space="preserve">13.9067678451538</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6286306381226</t>
+    <t xml:space="preserve">13.6286325454712</t>
   </si>
   <si>
     <t xml:space="preserve">14.2034454345703</t>
@@ -1097,25 +1094,25 @@
     <t xml:space="preserve">14.0180225372314</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7028026580811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3888702392578</t>
+    <t xml:space="preserve">13.7028007507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3888692855835</t>
   </si>
   <si>
     <t xml:space="preserve">14.518666267395</t>
   </si>
   <si>
-    <t xml:space="preserve">14.574294090271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4815797805786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1849031448364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8325996398926</t>
+    <t xml:space="preserve">14.5742931365967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4815826416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1849021911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8325986862183</t>
   </si>
   <si>
     <t xml:space="preserve">12.9981918334961</t>
@@ -1124,25 +1121,25 @@
     <t xml:space="preserve">12.7756834030151</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3690395355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0352783203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7385988235474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9796504974365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5173788070679</t>
+    <t xml:space="preserve">13.3690385818481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0352773666382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.738597869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9796514511108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5173778533936</t>
   </si>
   <si>
     <t xml:space="preserve">13.3134126663208</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6644306182861</t>
+    <t xml:space="preserve">12.6644296646118</t>
   </si>
   <si>
     <t xml:space="preserve">12.1081600189209</t>
@@ -1157,7 +1154,7 @@
     <t xml:space="preserve">12.5902605056763</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7200565338135</t>
+    <t xml:space="preserve">12.7200574874878</t>
   </si>
   <si>
     <t xml:space="preserve">12.6088027954102</t>
@@ -1172,94 +1169,94 @@
     <t xml:space="preserve">12.0710744857788</t>
   </si>
   <si>
-    <t xml:space="preserve">11.607515335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4604625701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8114814758301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8485660552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2379560470581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3862953186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3504962921143</t>
+    <t xml:space="preserve">11.6075162887573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4604644775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8114805221558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8485670089722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2379550933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3862943649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3504972457886</t>
   </si>
   <si>
     <t xml:space="preserve">13.5359210968018</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7213449478149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2590732574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9080543518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7782602310181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.741174697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7968006134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0235719680786</t>
+    <t xml:space="preserve">13.7213439941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2590742111206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.908055305481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7782583236694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7411727905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7968015670776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.02357006073</t>
   </si>
   <si>
     <t xml:space="preserve">15.6849880218506</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4015245437622</t>
+    <t xml:space="preserve">15.4015216827393</t>
   </si>
   <si>
     <t xml:space="preserve">15.2314462661743</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0802659988403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1180601119995</t>
+    <t xml:space="preserve">15.080265045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1180591583252</t>
   </si>
   <si>
     <t xml:space="preserve">15.1747522354126</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3070363998413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.13538646698</t>
+    <t xml:space="preserve">15.307035446167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1353855133057</t>
   </si>
   <si>
     <t xml:space="preserve">13.8141269683838</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2660980224609</t>
+    <t xml:space="preserve">13.2660970687866</t>
   </si>
   <si>
     <t xml:space="preserve">13.6062536239624</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6818437576294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0771217346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9448394775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.114917755127</t>
+    <t xml:space="preserve">13.6818428039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0771207809448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9448385238647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1149168014526</t>
   </si>
   <si>
     <t xml:space="preserve">12.8881464004517</t>
@@ -1268,19 +1265,19 @@
     <t xml:space="preserve">12.0944480895996</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5479888916016</t>
+    <t xml:space="preserve">12.5479898452759</t>
   </si>
   <si>
     <t xml:space="preserve">13.0015316009521</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6235790252686</t>
+    <t xml:space="preserve">12.6235799789429</t>
   </si>
   <si>
     <t xml:space="preserve">12.6991701126099</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7558622360229</t>
+    <t xml:space="preserve">12.7558631896973</t>
   </si>
   <si>
     <t xml:space="preserve">12.8692493438721</t>
@@ -1289,13 +1286,13 @@
     <t xml:space="preserve">12.3401165008545</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7369661331177</t>
+    <t xml:space="preserve">12.7369651794434</t>
   </si>
   <si>
     <t xml:space="preserve">12.7180681228638</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7747621536255</t>
+    <t xml:space="preserve">12.7747611999512</t>
   </si>
   <si>
     <t xml:space="preserve">12.2645254135132</t>
@@ -1304,19 +1301,19 @@
     <t xml:space="preserve">13.7385368347168</t>
   </si>
   <si>
-    <t xml:space="preserve">13.776330947876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9653081893921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8708181381226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0786924362183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6251516342163</t>
+    <t xml:space="preserve">13.7763319015503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9653062820435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8708200454712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0786933898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.625150680542</t>
   </si>
   <si>
     <t xml:space="preserve">13.5873565673828</t>
@@ -1328,64 +1325,64 @@
     <t xml:space="preserve">13.4550724029541</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4361763000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.247200012207</t>
+    <t xml:space="preserve">13.4361753463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2471990585327</t>
   </si>
   <si>
     <t xml:space="preserve">13.1338138580322</t>
   </si>
   <si>
-    <t xml:space="preserve">13.322790145874</t>
+    <t xml:space="preserve">13.3227910995483</t>
   </si>
   <si>
     <t xml:space="preserve">13.4739713668823</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2094039916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3605852127075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5668869018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5101938247681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2834234237671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6802730560303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0393257141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9826335906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8125562667847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9637355804443</t>
+    <t xml:space="preserve">13.2094058990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3605861663818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5668878555298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5101928710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2834243774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.680272102356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.03932762146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9826326370239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8125553131104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9637365341187</t>
   </si>
   <si>
     <t xml:space="preserve">13.7952299118042</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1164875030518</t>
+    <t xml:space="preserve">14.1164865493774</t>
   </si>
   <si>
     <t xml:space="preserve">14.2676687240601</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3054637908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.059796333313</t>
+    <t xml:space="preserve">14.3054628372192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0597953796387</t>
   </si>
   <si>
     <t xml:space="preserve">13.7007417678833</t>
@@ -1394,13 +1391,13 @@
     <t xml:space="preserve">13.4928684234619</t>
   </si>
   <si>
-    <t xml:space="preserve">13.757435798645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.549560546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1731824874878</t>
+    <t xml:space="preserve">13.7574348449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5495615005493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1731805801392</t>
   </si>
   <si>
     <t xml:space="preserve">14.9290838241577</t>
@@ -1409,10 +1406,10 @@
     <t xml:space="preserve">15.4960098266602</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2692422866821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1558561325073</t>
+    <t xml:space="preserve">15.2692413330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1558542251587</t>
   </si>
   <si>
     <t xml:space="preserve">16.5353775024414</t>
@@ -1421,55 +1418,55 @@
     <t xml:space="preserve">16.7054576873779</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9133319854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6298675537109</t>
+    <t xml:space="preserve">16.913330078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6298656463623</t>
   </si>
   <si>
     <t xml:space="preserve">16.2330169677734</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9117555618286</t>
+    <t xml:space="preserve">15.9117565155029</t>
   </si>
   <si>
     <t xml:space="preserve">15.5904979705811</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5149097442627</t>
+    <t xml:space="preserve">15.514910697937</t>
   </si>
   <si>
     <t xml:space="preserve">15.0046739578247</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2125482559204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3810548782349</t>
+    <t xml:space="preserve">15.2125473022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3810558319092</t>
   </si>
   <si>
     <t xml:space="preserve">14.6078252792358</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4377470016479</t>
+    <t xml:space="preserve">14.4377460479736</t>
   </si>
   <si>
     <t xml:space="preserve">14.6456203460693</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2487707138062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1920776367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8897180557251</t>
+    <t xml:space="preserve">14.2487716674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1920785903931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8897171020508</t>
   </si>
   <si>
     <t xml:space="preserve">13.5306625366211</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8519229888916</t>
+    <t xml:space="preserve">13.851921081543</t>
   </si>
   <si>
     <t xml:space="preserve">14.0220003128052</t>
@@ -1481,7 +1478,7 @@
     <t xml:space="preserve">14.4755420684814</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4188480377197</t>
+    <t xml:space="preserve">14.4188499450684</t>
   </si>
   <si>
     <t xml:space="preserve">15.5527038574219</t>
@@ -1490,55 +1487,55 @@
     <t xml:space="preserve">14.9668788909912</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0818367004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0629367828369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2519130706787</t>
+    <t xml:space="preserve">16.0818347930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0629386901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2519149780273</t>
   </si>
   <si>
     <t xml:space="preserve">16.0440406799316</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8739614486694</t>
+    <t xml:space="preserve">15.8739624023438</t>
   </si>
   <si>
     <t xml:space="preserve">15.458215713501</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0251426696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3464031219482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1007328033447</t>
+    <t xml:space="preserve">16.0251445770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3464012145996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1007347106934</t>
   </si>
   <si>
     <t xml:space="preserve">16.327507019043</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6471910476685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7983722686768</t>
+    <t xml:space="preserve">15.6471929550171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7983703613281</t>
   </si>
   <si>
     <t xml:space="preserve">15.9306564331055</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0613670349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8550662994385</t>
+    <t xml:space="preserve">15.0613660812378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8550672531128</t>
   </si>
   <si>
     <t xml:space="preserve">15.4771137237549</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7401075363159</t>
+    <t xml:space="preserve">14.7401084899902</t>
   </si>
   <si>
     <t xml:space="preserve">14.9101858139038</t>
@@ -1553,37 +1550,37 @@
     <t xml:space="preserve">14.9857759475708</t>
   </si>
   <si>
-    <t xml:space="preserve">15.533805847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7416791915894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0424690246582</t>
+    <t xml:space="preserve">15.5338068008423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.741678237915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0424699783325</t>
   </si>
   <si>
     <t xml:space="preserve">15.4204216003418</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7605781555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6282968521118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8928623199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.968451499939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0062465667725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9873456954956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6093969345093</t>
+    <t xml:space="preserve">15.7605772018433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6282939910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8928594589233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.968448638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0062484741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9873504638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6093950271606</t>
   </si>
   <si>
     <t xml:space="preserve">14.6834154129028</t>
@@ -1595,7 +1592,7 @@
     <t xml:space="preserve">14.8534936904907</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1936511993408</t>
+    <t xml:space="preserve">15.1936502456665</t>
   </si>
   <si>
     <t xml:space="preserve">15.0991621017456</t>
@@ -1604,64 +1601,64 @@
     <t xml:space="preserve">15.2881383895874</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1952209472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0078144073486</t>
+    <t xml:space="preserve">16.1952228546143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0078201293945</t>
   </si>
   <si>
     <t xml:space="preserve">17.2345886230469</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2534847259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2912788391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1023063659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.064510345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0471820831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4046669006348</t>
+    <t xml:space="preserve">17.2534885406494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2912769317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1023025512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0645084381104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0471839904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4046630859375</t>
   </si>
   <si>
     <t xml:space="preserve">17.347972869873</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3668689727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4991550445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0456161499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3857707977295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4424591064453</t>
+    <t xml:space="preserve">17.366870880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.499153137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0456123352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3857688903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4424610137939</t>
   </si>
   <si>
     <t xml:space="preserve">17.8582077026367</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8204116821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5558452606201</t>
+    <t xml:space="preserve">17.8204154968262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5558490753174</t>
   </si>
   <si>
     <t xml:space="preserve">17.3290767669678</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1400985717773</t>
+    <t xml:space="preserve">17.1401023864746</t>
   </si>
   <si>
     <t xml:space="preserve">16.5731754302979</t>
@@ -1670,34 +1667,34 @@
     <t xml:space="preserve">16.5920696258545</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2897090911865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8566379547119</t>
+    <t xml:space="preserve">16.2897071838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8566360473633</t>
   </si>
   <si>
     <t xml:space="preserve">16.1574268341064</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5805950164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5421257019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3882484436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.445951461792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2343673706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0035457611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9843111038208</t>
+    <t xml:space="preserve">16.5805931091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5421276092529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3882465362549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4459533691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2343635559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0035438537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9843120574951</t>
   </si>
   <si>
     <t xml:space="preserve">16.6767730712891</t>
@@ -1712,28 +1709,28 @@
     <t xml:space="preserve">16.7537117004395</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6383018493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4267139434814</t>
+    <t xml:space="preserve">16.6382999420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4267158508301</t>
   </si>
   <si>
     <t xml:space="preserve">16.522891998291</t>
   </si>
   <si>
-    <t xml:space="preserve">15.945839881897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4651889801025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9650774002075</t>
+    <t xml:space="preserve">15.9458417892456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4651870727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9650754928589</t>
   </si>
   <si>
     <t xml:space="preserve">16.0227813720703</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8688993453979</t>
+    <t xml:space="preserve">15.8689022064209</t>
   </si>
   <si>
     <t xml:space="preserve">15.7342557907104</t>
@@ -1742,7 +1739,7 @@
     <t xml:space="preserve">15.6573171615601</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4264965057373</t>
+    <t xml:space="preserve">15.426495552063</t>
   </si>
   <si>
     <t xml:space="preserve">15.3687896728516</t>
@@ -1751,28 +1748,28 @@
     <t xml:space="preserve">15.3110857009888</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9840898513794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1956748962402</t>
+    <t xml:space="preserve">14.9840888977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1956739425659</t>
   </si>
   <si>
     <t xml:space="preserve">15.2341442108154</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1379699707031</t>
+    <t xml:space="preserve">15.1379690170288</t>
   </si>
   <si>
     <t xml:space="preserve">15.0994987487793</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0033235549927</t>
+    <t xml:space="preserve">15.003324508667</t>
   </si>
   <si>
     <t xml:space="preserve">15.1187343597412</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2533798217773</t>
+    <t xml:space="preserve">15.253378868103</t>
   </si>
   <si>
     <t xml:space="preserve">15.0610284805298</t>
@@ -1781,49 +1778,49 @@
     <t xml:space="preserve">14.8686800003052</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8494434356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7147979736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4457292556763</t>
+    <t xml:space="preserve">14.8494443893433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7147989273071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4457302093506</t>
   </si>
   <si>
     <t xml:space="preserve">15.1764392852783</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8302097320557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.080265045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9648542404175</t>
+    <t xml:space="preserve">14.8302087783813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0802640914917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9648551940918</t>
   </si>
   <si>
     <t xml:space="preserve">15.1572046279907</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7917404174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.753270149231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9071502685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0225601196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8109741210938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8879127502441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5416831970215</t>
+    <t xml:space="preserve">14.7917394638062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7532691955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9071483612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0225591659546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8109750747681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8879137039185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5416841506958</t>
   </si>
   <si>
     <t xml:space="preserve">14.580153465271</t>
@@ -1835,7 +1832,7 @@
     <t xml:space="preserve">14.5032138824463</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6378583908081</t>
+    <t xml:space="preserve">14.6378593444824</t>
   </si>
   <si>
     <t xml:space="preserve">14.6186237335205</t>
@@ -1847,49 +1844,52 @@
     <t xml:space="preserve">14.4455080032349</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6570930480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9263849258423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5609188079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3495559692383</t>
+    <t xml:space="preserve">14.65709400177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.926383972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5609178543091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.349555015564</t>
   </si>
   <si>
     <t xml:space="preserve">15.3880252838135</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6765508651733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5226678848267</t>
+    <t xml:space="preserve">15.6765480041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5226697921753</t>
   </si>
   <si>
     <t xml:space="preserve">15.7150192260742</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7919607162476</t>
+    <t xml:space="preserve">15.7919626235962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1574249267578</t>
   </si>
   <si>
     <t xml:space="preserve">15.7727251052856</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8111953735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9073734283447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6380786895752</t>
+    <t xml:space="preserve">15.8111972808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9073705673218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6380796432495</t>
   </si>
   <si>
     <t xml:space="preserve">15.6188459396362</t>
   </si>
   <si>
-    <t xml:space="preserve">15.849666595459</t>
+    <t xml:space="preserve">15.8496646881104</t>
   </si>
   <si>
     <t xml:space="preserve">15.5803756713867</t>
@@ -1901,52 +1901,52 @@
     <t xml:space="preserve">15.8304300308228</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9266052246094</t>
+    <t xml:space="preserve">15.9266080856323</t>
   </si>
   <si>
     <t xml:space="preserve">16.1189575195312</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1576499938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0037670135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9460639953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.888355255127</t>
+    <t xml:space="preserve">17.1576480865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0037689208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9460620880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8883571624756</t>
   </si>
   <si>
     <t xml:space="preserve">16.9845314025879</t>
   </si>
   <si>
-    <t xml:space="preserve">17.119176864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2730598449707</t>
+    <t xml:space="preserve">17.1191749572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2730560302734</t>
   </si>
   <si>
     <t xml:space="preserve">18.2732772827148</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1771068572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6000537872314</t>
+    <t xml:space="preserve">18.1771030426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6000518798828</t>
   </si>
   <si>
     <t xml:space="preserve">17.6577587127686</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1001644134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9847564697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1194000244141</t>
+    <t xml:space="preserve">18.1001625061035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9847545623779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1193981170654</t>
   </si>
   <si>
     <t xml:space="preserve">17.965518951416</t>
@@ -1955,10 +1955,10 @@
     <t xml:space="preserve">17.9462833404541</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0616970062256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9270496368408</t>
+    <t xml:space="preserve">18.061695098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9270477294922</t>
   </si>
   <si>
     <t xml:space="preserve">18.3117504119873</t>
@@ -1967,19 +1967,19 @@
     <t xml:space="preserve">18.7541542053223</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1003875732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0234470367432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5425720214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9657402038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9080352783203</t>
+    <t xml:space="preserve">19.1003856658936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0234451293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5425682067871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9657382965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9080371856689</t>
   </si>
   <si>
     <t xml:space="preserve">19.4273815155029</t>
@@ -1991,10 +1991,10 @@
     <t xml:space="preserve">19.5235557556152</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6678218841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2831172943115</t>
+    <t xml:space="preserve">19.6678199768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2831192016602</t>
   </si>
   <si>
     <t xml:space="preserve">18.8503303527832</t>
@@ -2006,13 +2006,13 @@
     <t xml:space="preserve">19.7159061431885</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7639923095703</t>
+    <t xml:space="preserve">19.7639942169189</t>
   </si>
   <si>
     <t xml:space="preserve">19.331205368042</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5716457366943</t>
+    <t xml:space="preserve">19.5716438293457</t>
   </si>
   <si>
     <t xml:space="preserve">20.1967830657959</t>
@@ -2024,13 +2024,13 @@
     <t xml:space="preserve">22.2164611816406</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1585330963135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1104488372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8219223022461</t>
+    <t xml:space="preserve">21.1585350036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.110445022583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8219203948975</t>
   </si>
   <si>
     <t xml:space="preserve">20.6295719146729</t>
@@ -2039,28 +2039,28 @@
     <t xml:space="preserve">21.0142726898193</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7257423400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6776580810547</t>
+    <t xml:space="preserve">20.7257442474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6776599884033</t>
   </si>
   <si>
     <t xml:space="preserve">19.9563446044922</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2929573059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.004430770874</t>
+    <t xml:space="preserve">20.2929592132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0044326782227</t>
   </si>
   <si>
     <t xml:space="preserve">19.8601703643799</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0811500549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.773832321167</t>
+    <t xml:space="preserve">19.0811538696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7738342285156</t>
   </si>
   <si>
     <t xml:space="preserve">20.9180965423584</t>
@@ -2069,7 +2069,7 @@
     <t xml:space="preserve">20.5814819335938</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2547092437744</t>
+    <t xml:space="preserve">21.2547130584717</t>
   </si>
   <si>
     <t xml:space="preserve">21.3989715576172</t>
@@ -2081,7 +2081,7 @@
     <t xml:space="preserve">21.6394100189209</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4470615386963</t>
+    <t xml:space="preserve">21.4470596313477</t>
   </si>
   <si>
     <t xml:space="preserve">21.8317604064941</t>
@@ -2090,16 +2090,16 @@
     <t xml:space="preserve">20.0525207519531</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1006050109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7349185943604</t>
+    <t xml:space="preserve">20.1006088256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.734920501709</t>
   </si>
   <si>
     <t xml:space="preserve">18.1963405609131</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6192874908447</t>
+    <t xml:space="preserve">17.6192893981934</t>
   </si>
   <si>
     <t xml:space="preserve">16.3113059997559</t>
@@ -2108,34 +2108,34 @@
     <t xml:space="preserve">16.195894241333</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4839782714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4262742996216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4643001556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0218954086304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1373043060303</t>
+    <t xml:space="preserve">14.4839792251587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4262733459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.464301109314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0218944549561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1373052597046</t>
   </si>
   <si>
     <t xml:space="preserve">12.6951198577881</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9067068099976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9834241867065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3106412887573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.560697555542</t>
+    <t xml:space="preserve">12.9067058563232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9834251403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3106422424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5606966018677</t>
   </si>
   <si>
     <t xml:space="preserve">14.0223369598389</t>
@@ -2144,16 +2144,16 @@
     <t xml:space="preserve">14.1954526901245</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2916269302368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1185121536255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.734034538269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0992784500122</t>
+    <t xml:space="preserve">14.2916278839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1185131072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7340335845947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0992774963379</t>
   </si>
   <si>
     <t xml:space="preserve">15.4072599411011</t>
@@ -2168,31 +2168,31 @@
     <t xml:space="preserve">16.2151317596436</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4649658203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0612487792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1381912231445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0420169830322</t>
+    <t xml:space="preserve">15.4649639129639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0612525939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1381931304932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0420150756836</t>
   </si>
   <si>
     <t xml:space="preserve">16.59983253479</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2153549194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7152404785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9268283843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0614738464355</t>
+    <t xml:space="preserve">17.2153511047363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.715238571167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9268264770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0614700317383</t>
   </si>
   <si>
     <t xml:space="preserve">18.2540454864502</t>
@@ -2201,13 +2201,13 @@
     <t xml:space="preserve">18.638744354248</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0774536132812</t>
+    <t xml:space="preserve">18.0774574279785</t>
   </si>
   <si>
     <t xml:space="preserve">17.7677764892578</t>
   </si>
   <si>
-    <t xml:space="preserve">17.458101272583</t>
+    <t xml:space="preserve">17.4580993652344</t>
   </si>
   <si>
     <t xml:space="preserve">17.4387435913086</t>
@@ -2219,25 +2219,25 @@
     <t xml:space="preserve">16.954870223999</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4193859100342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6129379272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1677761077881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.651647567749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4968070983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7290649414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2903594970703</t>
+    <t xml:space="preserve">17.4193897247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6129398345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1677742004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6516456604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4968090057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7290668487549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.290355682373</t>
   </si>
   <si>
     <t xml:space="preserve">17.9419708251953</t>
@@ -2258,43 +2258,43 @@
     <t xml:space="preserve">18.2322940826416</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2516460418701</t>
+    <t xml:space="preserve">18.2516498565674</t>
   </si>
   <si>
     <t xml:space="preserve">18.5806827545166</t>
   </si>
   <si>
-    <t xml:space="preserve">18.445198059082</t>
+    <t xml:space="preserve">18.4451961517334</t>
   </si>
   <si>
     <t xml:space="preserve">18.1161632537842</t>
   </si>
   <si>
-    <t xml:space="preserve">18.038745880127</t>
+    <t xml:space="preserve">18.0387420654297</t>
   </si>
   <si>
     <t xml:space="preserve">18.8322944641113</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7742309570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.677453994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9097137451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0451965332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5968112945557</t>
+    <t xml:space="preserve">18.7742290496826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6774559020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9097118377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0451984405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5968132019043</t>
   </si>
   <si>
     <t xml:space="preserve">19.3548755645752</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9484233856201</t>
+    <t xml:space="preserve">18.9484252929688</t>
   </si>
   <si>
     <t xml:space="preserve">19.1032619476318</t>
@@ -2303,7 +2303,7 @@
     <t xml:space="preserve">18.4645500183105</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6581020355225</t>
+    <t xml:space="preserve">18.6581001281738</t>
   </si>
   <si>
     <t xml:space="preserve">19.500036239624</t>
@@ -2312,16 +2312,16 @@
     <t xml:space="preserve">19.6451988220215</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0806827545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3226203918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6129417419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5645542144775</t>
+    <t xml:space="preserve">20.0806846618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3226184844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.612943649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5645561218262</t>
   </si>
   <si>
     <t xml:space="preserve">21.0484275817871</t>
@@ -2330,16 +2330,16 @@
     <t xml:space="preserve">21.2903633117676</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7258491516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1935901641846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5806884765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8710079193115</t>
+    <t xml:space="preserve">21.7258472442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1935882568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5806865692139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8710117340088</t>
   </si>
   <si>
     <t xml:space="preserve">21.532299041748</t>
@@ -2354,37 +2354,37 @@
     <t xml:space="preserve">22.4516563415527</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9355297088623</t>
+    <t xml:space="preserve">22.9355278015137</t>
   </si>
   <si>
     <t xml:space="preserve">22.7903652191162</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3226261138916</t>
+    <t xml:space="preserve">23.322624206543</t>
   </si>
   <si>
     <t xml:space="preserve">23.4194011688232</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0968189239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.72585105896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4839172363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0484352111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7581081390381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.95166015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6613368988037</t>
+    <t xml:space="preserve">24.0968208312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7258529663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4839191436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0484313964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7581100463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9516582489014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6613349914551</t>
   </si>
   <si>
     <t xml:space="preserve">22.741979598999</t>
@@ -2396,10 +2396,10 @@
     <t xml:space="preserve">23.4677867889404</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0806903839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8871383666992</t>
+    <t xml:space="preserve">23.0806884765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8871421813965</t>
   </si>
   <si>
     <t xml:space="preserve">22.5484294891357</t>
@@ -2411,31 +2411,31 @@
     <t xml:space="preserve">22.0645580291748</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2419776916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6290740966797</t>
+    <t xml:space="preserve">21.2419757843018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6290760040283</t>
   </si>
   <si>
     <t xml:space="preserve">20.4677810668945</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3871383666992</t>
+    <t xml:space="preserve">21.3871402740479</t>
   </si>
   <si>
     <t xml:space="preserve">21.0968151092529</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4839115142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2097225189209</t>
+    <t xml:space="preserve">21.4839134216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2097206115723</t>
   </si>
   <si>
     <t xml:space="preserve">21.9677848815918</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9516544342041</t>
+    <t xml:space="preserve">20.9516525268555</t>
   </si>
   <si>
     <t xml:space="preserve">22.1129455566406</t>
@@ -2444,7 +2444,7 @@
     <t xml:space="preserve">22.3548812866211</t>
   </si>
   <si>
-    <t xml:space="preserve">21.919397354126</t>
+    <t xml:space="preserve">21.9193954467773</t>
   </si>
   <si>
     <t xml:space="preserve">22.838752746582</t>
@@ -2456,10 +2456,10 @@
     <t xml:space="preserve">24.4355316162109</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3387565612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.241979598999</t>
+    <t xml:space="preserve">24.3387546539307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2419815063477</t>
   </si>
   <si>
     <t xml:space="preserve">25.7419853210449</t>
@@ -2468,10 +2468,10 @@
     <t xml:space="preserve">26.1774673461914</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0000534057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6613426208496</t>
+    <t xml:space="preserve">27.0000514984131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.661340713501</t>
   </si>
   <si>
     <t xml:space="preserve">26.6129550933838</t>
@@ -2480,19 +2480,19 @@
     <t xml:space="preserve">26.3710193634033</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6774730682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6452159881592</t>
+    <t xml:space="preserve">27.6774711608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6452178955078</t>
   </si>
   <si>
     <t xml:space="preserve">29.9032821655273</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9355392456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7581195831299</t>
+    <t xml:space="preserve">28.9355373382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7581214904785</t>
   </si>
   <si>
     <t xml:space="preserve">30.3871536254883</t>
@@ -2501,31 +2501,31 @@
     <t xml:space="preserve">30.9194164276123</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7419948577881</t>
+    <t xml:space="preserve">31.7419967651367</t>
   </si>
   <si>
     <t xml:space="preserve">32.0323143005371</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5484485626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0807075500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2581233978271</t>
+    <t xml:space="preserve">31.5484447479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0807113647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2581253051758</t>
   </si>
   <si>
     <t xml:space="preserve">32.1774787902832</t>
   </si>
   <si>
-    <t xml:space="preserve">32.322639465332</t>
+    <t xml:space="preserve">32.3226432800293</t>
   </si>
   <si>
     <t xml:space="preserve">33.2903861999512</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1936111450195</t>
+    <t xml:space="preserve">33.1936149597168</t>
   </si>
   <si>
     <t xml:space="preserve">32.8065147399902</t>
@@ -2540,7 +2540,7 @@
     <t xml:space="preserve">34.1129684448242</t>
   </si>
   <si>
-    <t xml:space="preserve">34.742000579834</t>
+    <t xml:space="preserve">34.7420043945312</t>
   </si>
   <si>
     <t xml:space="preserve">34.5968399047852</t>
@@ -2549,7 +2549,7 @@
     <t xml:space="preserve">35.371036529541</t>
   </si>
   <si>
-    <t xml:space="preserve">35.4678115844727</t>
+    <t xml:space="preserve">35.4678077697754</t>
   </si>
   <si>
     <t xml:space="preserve">36.8226509094238</t>
@@ -2558,37 +2558,37 @@
     <t xml:space="preserve">37.1613655090332</t>
   </si>
   <si>
-    <t xml:space="preserve">36.1936225891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3065185546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.564582824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6613540649414</t>
+    <t xml:space="preserve">36.1936187744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3065223693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5645790100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6613464355469</t>
   </si>
   <si>
     <t xml:space="preserve">32.758129119873</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7097434997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9355430603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3387699127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.822639465332</t>
+    <t xml:space="preserve">32.7097396850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.935546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3387680053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8226413726807</t>
   </si>
   <si>
     <t xml:space="preserve">30.5807037353516</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4839305877686</t>
+    <t xml:space="preserve">30.4839286804199</t>
   </si>
   <si>
     <t xml:space="preserve">31.112964630127</t>
@@ -2603,22 +2603,22 @@
     <t xml:space="preserve">35.2742652893066</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6613616943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7097434997559</t>
+    <t xml:space="preserve">35.6613540649414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7097473144531</t>
   </si>
   <si>
     <t xml:space="preserve">37.2581367492676</t>
   </si>
   <si>
-    <t xml:space="preserve">37.0161972045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.9678115844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9516830444336</t>
+    <t xml:space="preserve">37.0162010192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.9678153991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9516868591309</t>
   </si>
   <si>
     <t xml:space="preserve">36.4355545043945</t>
@@ -2627,25 +2627,25 @@
     <t xml:space="preserve">35.0807113647461</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9839363098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6774940490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.064582824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6452331542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.0323295593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.612979888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.7581367492676</t>
+    <t xml:space="preserve">34.9839401245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.677490234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.0645866394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6452369689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.0323333740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6129760742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.7581405639648</t>
   </si>
   <si>
     <t xml:space="preserve">39.8226585388184</t>
@@ -2654,40 +2654,40 @@
     <t xml:space="preserve">39.6774940490723</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5645942687988</t>
+    <t xml:space="preserve">38.5645866394043</t>
   </si>
   <si>
     <t xml:space="preserve">38.7097511291504</t>
   </si>
   <si>
-    <t xml:space="preserve">39.6291046142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4516868591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.1613655090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4355621337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2581405639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.0807266235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.9033088684082</t>
+    <t xml:space="preserve">39.6291084289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4516906738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.1613693237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4355583190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2581443786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.0807304382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.9033050537109</t>
   </si>
   <si>
     <t xml:space="preserve">40.0645942687988</t>
   </si>
   <si>
-    <t xml:space="preserve">41.1774978637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8549156188965</t>
+    <t xml:space="preserve">41.1775016784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8549194335938</t>
   </si>
   <si>
     <t xml:space="preserve">42.3387908935547</t>
@@ -2702,10 +2702,10 @@
     <t xml:space="preserve">41.6129837036133</t>
   </si>
   <si>
-    <t xml:space="preserve">42.3871803283691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.5000877380371</t>
+    <t xml:space="preserve">42.3871765136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.5000801086426</t>
   </si>
   <si>
     <t xml:space="preserve">44.1291160583496</t>
@@ -2720,13 +2720,13 @@
     <t xml:space="preserve">45.6775054931641</t>
   </si>
   <si>
-    <t xml:space="preserve">44.4194450378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.0000839233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.0162200927734</t>
+    <t xml:space="preserve">44.4194412231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.0000915527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.0162162780762</t>
   </si>
   <si>
     <t xml:space="preserve">45.483959197998</t>
@@ -2738,28 +2738,28 @@
     <t xml:space="preserve">46.2581520080566</t>
   </si>
   <si>
-    <t xml:space="preserve">45.1452484130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.6129875183105</t>
+    <t xml:space="preserve">45.1452522277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.6129837036133</t>
   </si>
   <si>
     <t xml:space="preserve">44.5162162780762</t>
   </si>
   <si>
-    <t xml:space="preserve">44.2742767333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.838794708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.161376953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.3065376281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.2581481933594</t>
+    <t xml:space="preserve">44.2742729187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8387908935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.1613731384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.3065338134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.2581520080566</t>
   </si>
   <si>
     <t xml:space="preserve">42.8710479736328</t>
@@ -2768,7 +2768,7 @@
     <t xml:space="preserve">43.0645980834961</t>
   </si>
   <si>
-    <t xml:space="preserve">44.0323448181152</t>
+    <t xml:space="preserve">44.0323486328125</t>
   </si>
   <si>
     <t xml:space="preserve">43.4033088684082</t>
@@ -2777,16 +2777,16 @@
     <t xml:space="preserve">42.4355621337891</t>
   </si>
   <si>
-    <t xml:space="preserve">41.8992881774902</t>
+    <t xml:space="preserve">41.8992919921875</t>
   </si>
   <si>
     <t xml:space="preserve">40.0436096191406</t>
   </si>
   <si>
-    <t xml:space="preserve">39.7994422912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4576072692871</t>
+    <t xml:space="preserve">39.799446105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4576110839844</t>
   </si>
   <si>
     <t xml:space="preserve">40.0924415588379</t>
@@ -2804,7 +2804,7 @@
     <t xml:space="preserve">40.6784477233887</t>
   </si>
   <si>
-    <t xml:space="preserve">40.190113067627</t>
+    <t xml:space="preserve">40.1901092529297</t>
   </si>
   <si>
     <t xml:space="preserve">39.8971061706543</t>
@@ -2822,7 +2822,7 @@
     <t xml:space="preserve">39.2622680664062</t>
   </si>
   <si>
-    <t xml:space="preserve">40.2877731323242</t>
+    <t xml:space="preserve">40.2877769470215</t>
   </si>
   <si>
     <t xml:space="preserve">39.9459419250488</t>
@@ -2834,19 +2834,19 @@
     <t xml:space="preserve">36.7229194641113</t>
   </si>
   <si>
-    <t xml:space="preserve">37.6019287109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.090259552002</t>
+    <t xml:space="preserve">37.601921081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.0902633666992</t>
   </si>
   <si>
     <t xml:space="preserve">39.5552711486816</t>
   </si>
   <si>
-    <t xml:space="preserve">41.7039527893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.0946197509766</t>
+    <t xml:space="preserve">41.7039566040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.0946235656738</t>
   </si>
   <si>
     <t xml:space="preserve">41.4597854614258</t>
@@ -2855,7 +2855,7 @@
     <t xml:space="preserve">41.0691184997559</t>
   </si>
   <si>
-    <t xml:space="preserve">40.385440826416</t>
+    <t xml:space="preserve">40.3854446411133</t>
   </si>
   <si>
     <t xml:space="preserve">40.4342803955078</t>
@@ -2870,7 +2870,7 @@
     <t xml:space="preserve">41.9481239318848</t>
   </si>
   <si>
-    <t xml:space="preserve">41.4109535217285</t>
+    <t xml:space="preserve">41.4109573364258</t>
   </si>
   <si>
     <t xml:space="preserve">42.7294616699219</t>
@@ -2882,31 +2882,31 @@
     <t xml:space="preserve">45.4153137207031</t>
   </si>
   <si>
-    <t xml:space="preserve">46.1966514587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.8569984436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.31982421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.8081665039062</t>
+    <t xml:space="preserve">46.1966552734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.8569946289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.3198280334473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.808162689209</t>
   </si>
   <si>
     <t xml:space="preserve">48.5406684875488</t>
   </si>
   <si>
-    <t xml:space="preserve">48.5895004272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.8336715698242</t>
+    <t xml:space="preserve">48.5895042419434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.833667755127</t>
   </si>
   <si>
     <t xml:space="preserve">48.1988296508789</t>
   </si>
   <si>
-    <t xml:space="preserve">49.7126770019531</t>
+    <t xml:space="preserve">49.7126808166504</t>
   </si>
   <si>
     <t xml:space="preserve">49.9080085754395</t>
@@ -2918,25 +2918,25 @@
     <t xml:space="preserve">50.0056800842285</t>
   </si>
   <si>
-    <t xml:space="preserve">50.6893539428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.3730201721191</t>
+    <t xml:space="preserve">50.6893501281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.3730163574219</t>
   </si>
   <si>
     <t xml:space="preserve">50.2986793518066</t>
   </si>
   <si>
-    <t xml:space="preserve">50.591682434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4940147399902</t>
+    <t xml:space="preserve">50.5916786193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4940185546875</t>
   </si>
   <si>
     <t xml:space="preserve">51.2753524780273</t>
   </si>
   <si>
-    <t xml:space="preserve">50.2010154724121</t>
+    <t xml:space="preserve">50.2010116577148</t>
   </si>
   <si>
     <t xml:space="preserve">50.7870178222656</t>
@@ -2945,22 +2945,22 @@
     <t xml:space="preserve">50.9823532104492</t>
   </si>
   <si>
-    <t xml:space="preserve">51.8613586425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.9590301513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.8846855163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2688102722168</t>
+    <t xml:space="preserve">51.8613548278809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.9590263366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.8846817016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.2688140869141</t>
   </si>
   <si>
     <t xml:space="preserve">44.536304473877</t>
   </si>
   <si>
-    <t xml:space="preserve">43.5107955932617</t>
+    <t xml:space="preserve">43.510799407959</t>
   </si>
   <si>
     <t xml:space="preserve">44.2433052062988</t>
@@ -2969,13 +2969,13 @@
     <t xml:space="preserve">44.2921371459961</t>
   </si>
   <si>
-    <t xml:space="preserve">44.9269752502441</t>
+    <t xml:space="preserve">44.9269790649414</t>
   </si>
   <si>
     <t xml:space="preserve">44.0479698181152</t>
   </si>
   <si>
-    <t xml:space="preserve">43.8037986755371</t>
+    <t xml:space="preserve">43.8038024902344</t>
   </si>
   <si>
     <t xml:space="preserve">44.4386405944824</t>
@@ -2999,10 +2999,10 @@
     <t xml:space="preserve">42.2899589538574</t>
   </si>
   <si>
-    <t xml:space="preserve">43.0712928771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.2666320800781</t>
+    <t xml:space="preserve">43.0712966918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.2666282653809</t>
   </si>
   <si>
     <t xml:space="preserve">43.7061347961426</t>
@@ -3011,10 +3011,10 @@
     <t xml:space="preserve">44.3409729003906</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4641494750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.0989875793457</t>
+    <t xml:space="preserve">45.4641456604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.0989799499512</t>
   </si>
   <si>
     <t xml:space="preserve">45.659481048584</t>
@@ -3026,16 +3026,16 @@
     <t xml:space="preserve">42.7782936096191</t>
   </si>
   <si>
-    <t xml:space="preserve">41.2644462585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.6806259155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.1201286315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4364585876465</t>
+    <t xml:space="preserve">41.2644538879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.6806297302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.1201324462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4364624023438</t>
   </si>
   <si>
     <t xml:space="preserve">41.508617401123</t>
@@ -3044,16 +3044,16 @@
     <t xml:space="preserve">41.0202827453613</t>
   </si>
   <si>
-    <t xml:space="preserve">38.8715972900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.2367668151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0669326782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8482704162598</t>
+    <t xml:space="preserve">38.8716011047363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.2367630004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0669364929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.848274230957</t>
   </si>
   <si>
     <t xml:space="preserve">40.5319442749023</t>
@@ -3065,7 +3065,7 @@
     <t xml:space="preserve">41.1179466247559</t>
   </si>
   <si>
-    <t xml:space="preserve">40.8249435424805</t>
+    <t xml:space="preserve">40.824951171875</t>
   </si>
   <si>
     <t xml:space="preserve">41.6551208496094</t>
@@ -3074,10 +3074,10 @@
     <t xml:space="preserve">41.6062850952148</t>
   </si>
   <si>
-    <t xml:space="preserve">42.485294342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9736289978027</t>
+    <t xml:space="preserve">42.4852905273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.9736328125</t>
   </si>
   <si>
     <t xml:space="preserve">41.8016166687012</t>
@@ -3086,7 +3086,7 @@
     <t xml:space="preserve">41.362117767334</t>
   </si>
   <si>
-    <t xml:space="preserve">40.238941192627</t>
+    <t xml:space="preserve">40.2389450073242</t>
   </si>
   <si>
     <t xml:space="preserve">40.6296119689941</t>
@@ -3101,19 +3101,19 @@
     <t xml:space="preserve">43.999137878418</t>
   </si>
   <si>
-    <t xml:space="preserve">40.9226150512695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1157684326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5829620361328</t>
+    <t xml:space="preserve">40.9226188659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1157722473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5829582214355</t>
   </si>
   <si>
     <t xml:space="preserve">42.6317977905273</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5785980224609</t>
+    <t xml:space="preserve">38.5785942077637</t>
   </si>
   <si>
     <t xml:space="preserve">36.4299163818359</t>
@@ -3122,40 +3122,40 @@
     <t xml:space="preserve">38.6274299621582</t>
   </si>
   <si>
-    <t xml:space="preserve">37.1135902404785</t>
+    <t xml:space="preserve">37.1135864257812</t>
   </si>
   <si>
     <t xml:space="preserve">35.7950820922852</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7207374572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5997467041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.5275917053223</t>
+    <t xml:space="preserve">34.7207336425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5997505187988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.5275840759277</t>
   </si>
   <si>
     <t xml:space="preserve">36.6252555847168</t>
   </si>
   <si>
-    <t xml:space="preserve">36.0880851745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.1369132995605</t>
+    <t xml:space="preserve">36.0880813598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.1369171142578</t>
   </si>
   <si>
     <t xml:space="preserve">35.4532432556152</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5254020690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3810882568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3555793762207</t>
+    <t xml:space="preserve">34.5254058837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3810844421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3555755615234</t>
   </si>
   <si>
     <t xml:space="preserve">33.9393997192383</t>
@@ -3167,19 +3167,19 @@
     <t xml:space="preserve">31.4977169036865</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6442184448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0115661621094</t>
+    <t xml:space="preserve">31.6442203521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0115585327148</t>
   </si>
   <si>
     <t xml:space="preserve">32.3767280578613</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4510650634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7695732116699</t>
+    <t xml:space="preserve">33.4510612487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7695693969727</t>
   </si>
   <si>
     <t xml:space="preserve">34.5742416381836</t>
@@ -3188,7 +3188,7 @@
     <t xml:space="preserve">35.3067474365234</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0348854064941</t>
+    <t xml:space="preserve">32.0348892211914</t>
   </si>
   <si>
     <t xml:space="preserve">31.4000511169434</t>
@@ -3218,16 +3218,16 @@
     <t xml:space="preserve">32.767391204834</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2144813537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0191459655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9019451141357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6518058776855</t>
+    <t xml:space="preserve">31.2144832611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0191478729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9019470214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6518039703369</t>
   </si>
   <si>
     <t xml:space="preserve">30.4722099304199</t>
@@ -3236,7 +3236,7 @@
     <t xml:space="preserve">32.2302207946777</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0739555358887</t>
+    <t xml:space="preserve">32.0739593505859</t>
   </si>
   <si>
     <t xml:space="preserve">31.937219619751</t>
@@ -3260,7 +3260,7 @@
     <t xml:space="preserve">29.9643402099609</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3821296691895</t>
+    <t xml:space="preserve">28.3821277618408</t>
   </si>
   <si>
     <t xml:space="preserve">28.4993305206299</t>
@@ -3269,10 +3269,10 @@
     <t xml:space="preserve">29.2025337219238</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8704662322998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.929069519043</t>
+    <t xml:space="preserve">28.8704643249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9290676116943</t>
   </si>
   <si>
     <t xml:space="preserve">29.085334777832</t>
@@ -3284,7 +3284,7 @@
     <t xml:space="preserve">28.4211959838867</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0147876739502</t>
+    <t xml:space="preserve">27.0147857666016</t>
   </si>
   <si>
     <t xml:space="preserve">28.3235282897949</t>
@@ -3293,10 +3293,10 @@
     <t xml:space="preserve">28.5969982147217</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2258605957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5579280853271</t>
+    <t xml:space="preserve">28.2258625030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5579299926758</t>
   </si>
   <si>
     <t xml:space="preserve">28.1816463470459</t>
@@ -15119,7 +15119,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G373" t="s">
-        <v>263</v>
+        <v>242</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -15145,7 +15145,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G374" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -15171,7 +15171,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G375" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -15197,7 +15197,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G376" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -15223,7 +15223,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G377" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -15249,7 +15249,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G378" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -15275,7 +15275,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G379" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -15301,7 +15301,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G380" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -15327,7 +15327,7 @@
         <v>12</v>
       </c>
       <c r="G381" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -15353,7 +15353,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G382" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -15379,7 +15379,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G383" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -15405,7 +15405,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G384" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -15431,7 +15431,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G385" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -15457,7 +15457,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G386" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -15483,7 +15483,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G387" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -15509,7 +15509,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G388" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -15535,7 +15535,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G389" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -15561,7 +15561,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G390" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -15587,7 +15587,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G391" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -15613,7 +15613,7 @@
         <v>13.5</v>
       </c>
       <c r="G392" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -15639,7 +15639,7 @@
         <v>13.5100002288818</v>
       </c>
       <c r="G393" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -15665,7 +15665,7 @@
         <v>13.6700000762939</v>
       </c>
       <c r="G394" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -15691,7 +15691,7 @@
         <v>13.75</v>
       </c>
       <c r="G395" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -15717,7 +15717,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G396" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -15743,7 +15743,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G397" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -15769,7 +15769,7 @@
         <v>13.7299995422363</v>
       </c>
       <c r="G398" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -15795,7 +15795,7 @@
         <v>13.5299997329712</v>
       </c>
       <c r="G399" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -15821,7 +15821,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G400" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -15847,7 +15847,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G401" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -15873,7 +15873,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G402" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -15899,7 +15899,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G403" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -15925,7 +15925,7 @@
         <v>13.4700002670288</v>
       </c>
       <c r="G404" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -15951,7 +15951,7 @@
         <v>13.5299997329712</v>
       </c>
       <c r="G405" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -15977,7 +15977,7 @@
         <v>13.6800003051758</v>
       </c>
       <c r="G406" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -16003,7 +16003,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G407" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -16029,7 +16029,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G408" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -16055,7 +16055,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G409" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -16081,7 +16081,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G410" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -16107,7 +16107,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G411" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -16133,7 +16133,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G412" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -16159,7 +16159,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G413" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -16185,7 +16185,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G414" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -16211,7 +16211,7 @@
         <v>13.25</v>
       </c>
       <c r="G415" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -16237,7 +16237,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G416" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -16263,7 +16263,7 @@
         <v>13</v>
       </c>
       <c r="G417" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -16289,7 +16289,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G418" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -16315,7 +16315,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G419" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -16341,7 +16341,7 @@
         <v>13.2299995422363</v>
       </c>
       <c r="G420" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -16367,7 +16367,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G421" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -16393,7 +16393,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G422" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -16419,7 +16419,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G423" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -16445,7 +16445,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G424" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -16471,7 +16471,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G425" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -16497,7 +16497,7 @@
         <v>13</v>
       </c>
       <c r="G426" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -16523,7 +16523,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G427" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -16549,7 +16549,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G428" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -16575,7 +16575,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G429" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -16601,7 +16601,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G430" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -16627,7 +16627,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G431" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -16653,7 +16653,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G432" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -16679,7 +16679,7 @@
         <v>13.25</v>
       </c>
       <c r="G433" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -16705,7 +16705,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G434" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -16731,7 +16731,7 @@
         <v>13.2299995422363</v>
       </c>
       <c r="G435" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -16757,7 +16757,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G436" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -16783,7 +16783,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G437" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -16809,7 +16809,7 @@
         <v>13</v>
       </c>
       <c r="G438" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -16835,7 +16835,7 @@
         <v>13.210000038147</v>
       </c>
       <c r="G439" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -16861,7 +16861,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G440" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -16887,7 +16887,7 @@
         <v>13.4300003051758</v>
       </c>
       <c r="G441" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -16913,7 +16913,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G442" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -16939,7 +16939,7 @@
         <v>13.4099998474121</v>
       </c>
       <c r="G443" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -16965,7 +16965,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G444" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -16991,7 +16991,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G445" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -17017,7 +17017,7 @@
         <v>13.2700004577637</v>
       </c>
       <c r="G446" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -17043,7 +17043,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G447" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -17069,7 +17069,7 @@
         <v>13.2700004577637</v>
       </c>
       <c r="G448" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -17095,7 +17095,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G449" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -17121,7 +17121,7 @@
         <v>13.25</v>
       </c>
       <c r="G450" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -17147,7 +17147,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G451" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -17173,7 +17173,7 @@
         <v>12.9700002670288</v>
       </c>
       <c r="G452" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -17199,7 +17199,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G453" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -17225,7 +17225,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G454" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -17251,7 +17251,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G455" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -17277,7 +17277,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G456" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -17303,7 +17303,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G457" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -17329,7 +17329,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G458" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -17355,7 +17355,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G459" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -17381,7 +17381,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G460" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -17407,7 +17407,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G461" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -17433,7 +17433,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G462" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -17485,7 +17485,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G464" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -17537,7 +17537,7 @@
         <v>12.75</v>
       </c>
       <c r="G466" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -17563,7 +17563,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G467" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -17589,7 +17589,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G468" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -17615,7 +17615,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G469" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -17641,7 +17641,7 @@
         <v>13.1899995803833</v>
       </c>
       <c r="G470" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -17667,7 +17667,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G471" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -17693,7 +17693,7 @@
         <v>13.1899995803833</v>
       </c>
       <c r="G472" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -17719,7 +17719,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G473" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -17771,7 +17771,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G475" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -17797,7 +17797,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G476" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -17823,7 +17823,7 @@
         <v>12.6899995803833</v>
       </c>
       <c r="G477" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -17849,7 +17849,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G478" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -17875,7 +17875,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G479" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -17901,7 +17901,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G480" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -17927,7 +17927,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G481" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -17953,7 +17953,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G482" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -17979,7 +17979,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G483" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -18005,7 +18005,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G484" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -18031,7 +18031,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G485" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -18083,7 +18083,7 @@
         <v>12.3699998855591</v>
       </c>
       <c r="G487" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -18109,7 +18109,7 @@
         <v>12.5100002288818</v>
       </c>
       <c r="G488" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -18135,7 +18135,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G489" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -18161,7 +18161,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G490" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -18187,7 +18187,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G491" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -18213,7 +18213,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G492" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -18239,7 +18239,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G493" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -18265,7 +18265,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G494" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -18291,7 +18291,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G495" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -18317,7 +18317,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G496" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -18343,7 +18343,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G497" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -18369,7 +18369,7 @@
         <v>12.75</v>
       </c>
       <c r="G498" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -18395,7 +18395,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G499" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -18421,7 +18421,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G500" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -18447,7 +18447,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G501" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -18473,7 +18473,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G502" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -18499,7 +18499,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G503" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -18525,7 +18525,7 @@
         <v>13</v>
       </c>
       <c r="G504" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -18551,7 +18551,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G505" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -18577,7 +18577,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G506" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -18603,7 +18603,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G507" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -18629,7 +18629,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G508" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -18655,7 +18655,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G509" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -18681,7 +18681,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G510" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -18707,7 +18707,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G511" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -18733,7 +18733,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G512" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -18759,7 +18759,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G513" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -18785,7 +18785,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G514" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -18811,7 +18811,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G515" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -18837,7 +18837,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G516" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -18863,7 +18863,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G517" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -18889,7 +18889,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G518" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -18915,7 +18915,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G519" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -18941,7 +18941,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G520" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -18967,7 +18967,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G521" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -18993,7 +18993,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G522" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -19019,7 +19019,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G523" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -19045,7 +19045,7 @@
         <v>15</v>
       </c>
       <c r="G524" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -19071,7 +19071,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G525" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -19097,7 +19097,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G526" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -19123,7 +19123,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G527" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -19149,7 +19149,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G528" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -19175,7 +19175,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G529" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -19201,7 +19201,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G530" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -19227,7 +19227,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G531" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -19253,7 +19253,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G532" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -19279,7 +19279,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G533" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -19305,7 +19305,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G534" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -19331,7 +19331,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G535" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -19357,7 +19357,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G536" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -19383,7 +19383,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G537" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -19409,7 +19409,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G538" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -19435,7 +19435,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G539" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -19461,7 +19461,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G540" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -19487,7 +19487,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G541" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -19513,7 +19513,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G542" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -19539,7 +19539,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G543" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -19565,7 +19565,7 @@
         <v>14</v>
       </c>
       <c r="G544" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -19591,7 +19591,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G545" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -19617,7 +19617,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G546" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -19643,7 +19643,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G547" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -19669,7 +19669,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G548" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -19695,7 +19695,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G549" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -19721,7 +19721,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G550" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -19747,7 +19747,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G551" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -19773,7 +19773,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G552" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -19799,7 +19799,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G553" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -19851,7 +19851,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G555" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -19877,7 +19877,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G556" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -19903,7 +19903,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G557" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -19929,7 +19929,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G558" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -19955,7 +19955,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G559" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -19981,7 +19981,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G560" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -20007,7 +20007,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G561" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -20033,7 +20033,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G562" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -20059,7 +20059,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G563" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -20085,7 +20085,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G564" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -20111,7 +20111,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G565" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -20137,7 +20137,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G566" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -20163,7 +20163,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G567" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -20189,7 +20189,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G568" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -20215,7 +20215,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G569" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -20241,7 +20241,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G570" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -20267,7 +20267,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G571" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -20293,7 +20293,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G572" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -20319,7 +20319,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G573" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -20345,7 +20345,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G574" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -20371,7 +20371,7 @@
         <v>13</v>
       </c>
       <c r="G575" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -20397,7 +20397,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G576" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -20423,7 +20423,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G577" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -20449,7 +20449,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G578" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -20475,7 +20475,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G579" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -20501,7 +20501,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G580" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -20527,7 +20527,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G581" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -20553,7 +20553,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G582" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -20579,7 +20579,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G583" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -20605,7 +20605,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G584" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -20631,7 +20631,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G585" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -20657,7 +20657,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G586" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -20683,7 +20683,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G587" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -20709,7 +20709,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G588" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -20735,7 +20735,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G589" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -20761,7 +20761,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G590" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -20787,7 +20787,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G591" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -20813,7 +20813,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G592" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -20839,7 +20839,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G593" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -20865,7 +20865,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G594" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -20891,7 +20891,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G595" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -20917,7 +20917,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G596" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -20943,7 +20943,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G597" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -20969,7 +20969,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G598" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -20995,7 +20995,7 @@
         <v>16</v>
       </c>
       <c r="G599" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -21021,7 +21021,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G600" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -21047,7 +21047,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G601" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -21073,7 +21073,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G602" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -21099,7 +21099,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G603" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -21125,7 +21125,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G604" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -21151,7 +21151,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G605" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -21177,7 +21177,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G606" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -21203,7 +21203,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G607" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -21229,7 +21229,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G608" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -21255,7 +21255,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G609" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -21281,7 +21281,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G610" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -21307,7 +21307,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G611" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -21333,7 +21333,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G612" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -21359,7 +21359,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G613" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -21385,7 +21385,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G614" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -21411,7 +21411,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G615" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -21437,7 +21437,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G616" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -21463,7 +21463,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G617" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -21489,7 +21489,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G618" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -21515,7 +21515,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G619" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -21541,7 +21541,7 @@
         <v>13.5</v>
       </c>
       <c r="G620" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -21567,7 +21567,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G621" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -21593,7 +21593,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G622" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -21619,7 +21619,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G623" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -21645,7 +21645,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G624" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -21671,7 +21671,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G625" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -21697,7 +21697,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G626" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -21723,7 +21723,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G627" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -21749,7 +21749,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G628" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -21775,7 +21775,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G629" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -21801,7 +21801,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G630" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -21827,7 +21827,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G631" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -21853,7 +21853,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G632" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -21879,7 +21879,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G633" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -21905,7 +21905,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G634" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -21931,7 +21931,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G635" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -21957,7 +21957,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G636" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -21983,7 +21983,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G637" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -22009,7 +22009,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G638" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -22035,7 +22035,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G639" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -22061,7 +22061,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G640" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -22087,7 +22087,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G641" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -22113,7 +22113,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G642" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -22139,7 +22139,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G643" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -22165,7 +22165,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G644" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -22191,7 +22191,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G645" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -22217,7 +22217,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G646" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -22243,7 +22243,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G647" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -22269,7 +22269,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G648" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -22295,7 +22295,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G649" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -22321,7 +22321,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G650" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -22347,7 +22347,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G651" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -22373,7 +22373,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G652" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -22399,7 +22399,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G653" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -22425,7 +22425,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G654" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -22451,7 +22451,7 @@
         <v>13</v>
       </c>
       <c r="G655" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -22477,7 +22477,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G656" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -22503,7 +22503,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G657" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -22529,7 +22529,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G658" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -22555,7 +22555,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G659" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -22581,7 +22581,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G660" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -22607,7 +22607,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G661" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -22633,7 +22633,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G662" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -22659,7 +22659,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G663" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -22685,7 +22685,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G664" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -22711,7 +22711,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G665" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -22737,7 +22737,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G666" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -22763,7 +22763,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G667" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -22789,7 +22789,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G668" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -22815,7 +22815,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G669" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -22841,7 +22841,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G670" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -22867,7 +22867,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G671" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -22893,7 +22893,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G672" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -22919,7 +22919,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G673" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -22945,7 +22945,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G674" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -22971,7 +22971,7 @@
         <v>14.9399995803833</v>
       </c>
       <c r="G675" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -22997,7 +22997,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G676" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -23023,7 +23023,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G677" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -23049,7 +23049,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G678" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -23075,7 +23075,7 @@
         <v>14.5</v>
       </c>
       <c r="G679" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -23101,7 +23101,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G680" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -23127,7 +23127,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G681" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -23153,7 +23153,7 @@
         <v>14.5600004196167</v>
       </c>
       <c r="G682" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -23179,7 +23179,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G683" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -23205,7 +23205,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G684" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -23231,7 +23231,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G685" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -23257,7 +23257,7 @@
         <v>15</v>
       </c>
       <c r="G686" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -23283,7 +23283,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G687" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -23309,7 +23309,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G688" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -23335,7 +23335,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G689" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -23361,7 +23361,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G690" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -23387,7 +23387,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G691" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -23413,7 +23413,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G692" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -23439,7 +23439,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G693" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -23465,7 +23465,7 @@
         <v>17.5</v>
       </c>
       <c r="G694" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -23491,7 +23491,7 @@
         <v>17.6800003051758</v>
       </c>
       <c r="G695" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -23517,7 +23517,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G696" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -23543,7 +23543,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G697" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -23569,7 +23569,7 @@
         <v>17.5</v>
       </c>
       <c r="G698" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -23595,7 +23595,7 @@
         <v>17.5</v>
       </c>
       <c r="G699" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -23621,7 +23621,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G700" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -23647,7 +23647,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G701" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -23673,7 +23673,7 @@
         <v>16.5</v>
       </c>
       <c r="G702" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -23699,7 +23699,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G703" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -23725,7 +23725,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G704" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -23751,7 +23751,7 @@
         <v>16.5</v>
       </c>
       <c r="G705" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -23777,7 +23777,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G706" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -23803,7 +23803,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G707" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -23829,7 +23829,7 @@
         <v>16</v>
       </c>
       <c r="G708" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -23855,7 +23855,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G709" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -23881,7 +23881,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G710" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -23907,7 +23907,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G711" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -23933,7 +23933,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G712" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -23959,7 +23959,7 @@
         <v>15.5</v>
       </c>
       <c r="G713" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -23985,7 +23985,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G714" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -24011,7 +24011,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G715" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -24037,7 +24037,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G716" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -24063,7 +24063,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G717" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -24089,7 +24089,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G718" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -24115,7 +24115,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G719" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -24141,7 +24141,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G720" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -24167,7 +24167,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G721" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -24193,7 +24193,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G722" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -24219,7 +24219,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G723" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -24245,7 +24245,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G724" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -24271,7 +24271,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G725" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -24297,7 +24297,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G726" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -24323,7 +24323,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G727" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -24349,7 +24349,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G728" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -24375,7 +24375,7 @@
         <v>16.5</v>
       </c>
       <c r="G729" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -24401,7 +24401,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G730" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -24427,7 +24427,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G731" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -24453,7 +24453,7 @@
         <v>16</v>
       </c>
       <c r="G732" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -24479,7 +24479,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G733" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -24505,7 +24505,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G734" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -24531,7 +24531,7 @@
         <v>17</v>
       </c>
       <c r="G735" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -24557,7 +24557,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G736" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -24583,7 +24583,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G737" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -24609,7 +24609,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G738" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -24635,7 +24635,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G739" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -24661,7 +24661,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G740" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -24687,7 +24687,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G741" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -24713,7 +24713,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G742" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -24739,7 +24739,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G743" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -24765,7 +24765,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G744" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -24791,7 +24791,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G745" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -24817,7 +24817,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G746" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -24843,7 +24843,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G747" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -24869,7 +24869,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G748" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -24895,7 +24895,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G749" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -24921,7 +24921,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G750" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -24947,7 +24947,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G751" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -24973,7 +24973,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G752" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -24999,7 +24999,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G753" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -25025,7 +25025,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G754" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -25051,7 +25051,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G755" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -25077,7 +25077,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G756" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -25103,7 +25103,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G757" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -25129,7 +25129,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G758" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -25155,7 +25155,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G759" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -25181,7 +25181,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G760" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -25207,7 +25207,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G761" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -25233,7 +25233,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G762" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -25259,7 +25259,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G763" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -25285,7 +25285,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G764" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -25311,7 +25311,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G765" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -25337,7 +25337,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G766" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -25363,7 +25363,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G767" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -25389,7 +25389,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G768" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -25415,7 +25415,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G769" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -25441,7 +25441,7 @@
         <v>16.5</v>
       </c>
       <c r="G770" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -25467,7 +25467,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G771" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -25493,7 +25493,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G772" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -25519,7 +25519,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G773" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -25545,7 +25545,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G774" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -25571,7 +25571,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G775" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -25597,7 +25597,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G776" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -25623,7 +25623,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G777" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -25649,7 +25649,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G778" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -25675,7 +25675,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G779" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -25701,7 +25701,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G780" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -25727,7 +25727,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G781" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -25753,7 +25753,7 @@
         <v>17</v>
       </c>
       <c r="G782" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -25779,7 +25779,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G783" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -25805,7 +25805,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G784" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -25831,7 +25831,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G785" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -25857,7 +25857,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G786" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -25883,7 +25883,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G787" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -25909,7 +25909,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G788" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -25935,7 +25935,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G789" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -25961,7 +25961,7 @@
         <v>16.5</v>
       </c>
       <c r="G790" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -25987,7 +25987,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G791" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -26013,7 +26013,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G792" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -26039,7 +26039,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G793" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -26065,7 +26065,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G794" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -26091,7 +26091,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G795" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -26117,7 +26117,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G796" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -26143,7 +26143,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G797" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -26169,7 +26169,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G798" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -26195,7 +26195,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G799" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -26221,7 +26221,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G800" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -26247,7 +26247,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G801" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -26273,7 +26273,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G802" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -26299,7 +26299,7 @@
         <v>16</v>
       </c>
       <c r="G803" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -26325,7 +26325,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G804" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -26351,7 +26351,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G805" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -26377,7 +26377,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G806" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -26403,7 +26403,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G807" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -26429,7 +26429,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G808" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -26455,7 +26455,7 @@
         <v>18</v>
       </c>
       <c r="G809" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -26481,7 +26481,7 @@
         <v>18.2399997711182</v>
       </c>
       <c r="G810" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -26507,7 +26507,7 @@
         <v>18.2600002288818</v>
       </c>
       <c r="G811" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -26533,7 +26533,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G812" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -26559,7 +26559,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G813" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -26585,7 +26585,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G814" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -26611,7 +26611,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G815" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -26637,7 +26637,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G816" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -26663,7 +26663,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G817" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -26689,7 +26689,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G818" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -26715,7 +26715,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G819" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -26741,7 +26741,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G820" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -26767,7 +26767,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G821" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -26793,7 +26793,7 @@
         <v>18</v>
       </c>
       <c r="G822" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -26819,7 +26819,7 @@
         <v>18</v>
       </c>
       <c r="G823" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -26845,7 +26845,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G824" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -26871,7 +26871,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G825" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -26897,7 +26897,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G826" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -26923,7 +26923,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G827" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -26949,7 +26949,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G828" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -26975,7 +26975,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G829" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -27001,7 +27001,7 @@
         <v>18.8600006103516</v>
       </c>
       <c r="G830" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -27027,7 +27027,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G831" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -27053,7 +27053,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G832" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -27079,7 +27079,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G833" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -27105,7 +27105,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G834" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -27131,7 +27131,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G835" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -27157,7 +27157,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G836" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -27183,7 +27183,7 @@
         <v>18</v>
       </c>
       <c r="G837" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -27209,7 +27209,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G838" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -27235,7 +27235,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G839" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -27261,7 +27261,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G840" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -27287,7 +27287,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G841" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -27313,7 +27313,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G842" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -27339,7 +27339,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G843" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -27365,7 +27365,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G844" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -27391,7 +27391,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G845" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -27417,7 +27417,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G846" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -27443,7 +27443,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G847" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -27469,7 +27469,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G848" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -27495,7 +27495,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G849" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -27521,7 +27521,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G850" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -27547,7 +27547,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G851" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -27573,7 +27573,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G852" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -27599,7 +27599,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G853" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -27625,7 +27625,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G854" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -27651,7 +27651,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G855" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -27677,7 +27677,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G856" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -27703,7 +27703,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G857" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -27729,7 +27729,7 @@
         <v>17.5</v>
       </c>
       <c r="G858" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -27755,7 +27755,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G859" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -27781,7 +27781,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G860" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -27807,7 +27807,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G861" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -27833,7 +27833,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G862" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -27859,7 +27859,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G863" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -27885,7 +27885,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G864" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -27911,7 +27911,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G865" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -27937,7 +27937,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G866" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -27963,7 +27963,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G867" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -27989,7 +27989,7 @@
         <v>17.1200008392334</v>
       </c>
       <c r="G868" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -28015,7 +28015,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G869" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -28041,7 +28041,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G870" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -28067,7 +28067,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G871" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -28093,7 +28093,7 @@
         <v>16.5</v>
       </c>
       <c r="G872" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -28119,7 +28119,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G873" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -28145,7 +28145,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G874" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -28171,7 +28171,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G875" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -28197,7 +28197,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G876" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -28223,7 +28223,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G877" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -28249,7 +28249,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G878" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -28275,7 +28275,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G879" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -28301,7 +28301,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G880" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -28327,7 +28327,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G881" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -28353,7 +28353,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G882" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -28379,7 +28379,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G883" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -28405,7 +28405,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G884" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -28431,7 +28431,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G885" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -28457,7 +28457,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G886" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -28483,7 +28483,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G887" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -28509,7 +28509,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G888" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -28535,7 +28535,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G889" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -28561,7 +28561,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G890" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -28587,7 +28587,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G891" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -28613,7 +28613,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G892" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -28639,7 +28639,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G893" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -28665,7 +28665,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G894" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -28691,7 +28691,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G895" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -28717,7 +28717,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G896" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -28743,7 +28743,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G897" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -28769,7 +28769,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G898" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -28795,7 +28795,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G899" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -28821,7 +28821,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G900" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -28847,7 +28847,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G901" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -28873,7 +28873,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G902" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -28899,7 +28899,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G903" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -28925,7 +28925,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G904" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -28951,7 +28951,7 @@
         <v>15.5</v>
       </c>
       <c r="G905" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -28977,7 +28977,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G906" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -29003,7 +29003,7 @@
         <v>15.5</v>
       </c>
       <c r="G907" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -29029,7 +29029,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G908" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -29055,7 +29055,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G909" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -29081,7 +29081,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G910" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -29107,7 +29107,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G911" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -29133,7 +29133,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G912" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -29159,7 +29159,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G913" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -29185,7 +29185,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G914" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -29211,7 +29211,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G915" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -29237,7 +29237,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G916" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -29263,7 +29263,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G917" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -29289,7 +29289,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G918" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -29315,7 +29315,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G919" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -29341,7 +29341,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G920" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -29367,7 +29367,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G921" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -29393,7 +29393,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G922" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -29419,7 +29419,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G923" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -29445,7 +29445,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G924" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -29471,7 +29471,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G925" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -29497,7 +29497,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G926" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -29523,7 +29523,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G927" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -29549,7 +29549,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G928" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -29575,7 +29575,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G929" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -29601,7 +29601,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G930" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -29627,7 +29627,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G931" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -29653,7 +29653,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G932" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -29679,7 +29679,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G933" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -29705,7 +29705,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G934" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -29731,7 +29731,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G935" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -29757,7 +29757,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G936" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -29783,7 +29783,7 @@
         <v>16</v>
       </c>
       <c r="G937" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -29809,7 +29809,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G938" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -29835,7 +29835,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G939" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -29861,7 +29861,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G940" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -29887,7 +29887,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G941" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -29913,7 +29913,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G942" t="s">
-        <v>554</v>
+        <v>619</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -29965,7 +29965,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G944" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -30017,7 +30017,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G946" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -30121,7 +30121,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G950" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -30147,7 +30147,7 @@
         <v>16.5</v>
       </c>
       <c r="G951" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -30199,7 +30199,7 @@
         <v>16.5</v>
       </c>
       <c r="G953" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -30225,7 +30225,7 @@
         <v>16.5</v>
       </c>
       <c r="G954" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -30303,7 +30303,7 @@
         <v>16</v>
       </c>
       <c r="G957" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -30329,7 +30329,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G958" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -30381,7 +30381,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G960" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -30433,7 +30433,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G962" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -30485,7 +30485,7 @@
         <v>16.5</v>
       </c>
       <c r="G964" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -30511,7 +30511,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G965" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -30563,7 +30563,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G967" t="s">
-        <v>554</v>
+        <v>619</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -30589,7 +30589,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G968" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -30693,7 +30693,7 @@
         <v>17.5</v>
       </c>
       <c r="G972" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -30823,7 +30823,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G977" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -33059,7 +33059,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G1063" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -33475,7 +33475,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G1079" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -33501,7 +33501,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1080" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -33527,7 +33527,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G1081" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -33683,7 +33683,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G1087" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -33813,7 +33813,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G1092" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -33839,7 +33839,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G1093" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -33943,7 +33943,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G1097" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -33969,7 +33969,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1098" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -34047,7 +34047,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G1101" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -34073,7 +34073,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G1102" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -34099,7 +34099,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1103" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -34151,7 +34151,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G1105" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -34203,7 +34203,7 @@
         <v>16</v>
       </c>
       <c r="G1107" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -34229,7 +34229,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1108" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -34281,7 +34281,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1110" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -34307,7 +34307,7 @@
         <v>16</v>
       </c>
       <c r="G1111" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -34411,7 +34411,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G1115" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -34437,7 +34437,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G1116" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -34463,7 +34463,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1117" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -70299,7 +70299,7 @@
     </row>
     <row r="2496">
       <c r="A2496" s="1" t="n">
-        <v>45953.6495949074</v>
+        <v>45953.2916666667</v>
       </c>
       <c r="B2496" t="n">
         <v>17801</v>
@@ -70320,6 +70320,32 @@
         <v>1638</v>
       </c>
       <c r="H2496" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2497">
+      <c r="A2497" s="1" t="n">
+        <v>45954.6495833333</v>
+      </c>
+      <c r="B2497" t="n">
+        <v>18983</v>
+      </c>
+      <c r="C2497" t="n">
+        <v>45.0499992370605</v>
+      </c>
+      <c r="D2497" t="n">
+        <v>43.7000007629395</v>
+      </c>
+      <c r="E2497" t="n">
+        <v>44.2000007629395</v>
+      </c>
+      <c r="F2497" t="n">
+        <v>44.2999992370605</v>
+      </c>
+      <c r="G2497" t="s">
+        <v>1637</v>
+      </c>
+      <c r="H2497" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MOL.MI.xlsx
+++ b/data/MOL.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1695" uniqueCount="1695">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1696" uniqueCount="1696">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,37 +38,37 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85066175460815</t>
+    <t xml:space="preserve">6.850661277771</t>
   </si>
   <si>
     <t xml:space="preserve">MOL.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75772571563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66036605834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77100229263306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63823795318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72674798965454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81525754928589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54972791671753</t>
+    <t xml:space="preserve">6.75772619247437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66036558151245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77100324630737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63823747634888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72674751281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81525850296021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54972839355469</t>
   </si>
   <si>
     <t xml:space="preserve">6.31960296630859</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09832811355591</t>
+    <t xml:space="preserve">6.09832763671875</t>
   </si>
   <si>
     <t xml:space="preserve">6.35058116912842</t>
@@ -80,28 +80,28 @@
     <t xml:space="preserve">6.5585789680481</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46121883392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89475440979004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52317523956299</t>
+    <t xml:space="preserve">6.46121835708618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89475584030151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52317571640015</t>
   </si>
   <si>
     <t xml:space="preserve">6.65594005584717</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76215171813965</t>
+    <t xml:space="preserve">6.76215219497681</t>
   </si>
   <si>
     <t xml:space="preserve">6.66479158401489</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69134426116943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68249320983887</t>
+    <t xml:space="preserve">6.69134378433228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68249368667603</t>
   </si>
   <si>
     <t xml:space="preserve">6.01866960525513</t>
@@ -110,91 +110,91 @@
     <t xml:space="preserve">5.8991813659668</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28419876098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0629243850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2532205581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39926147460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34172964096069</t>
+    <t xml:space="preserve">6.28419923782349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06292390823364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25321960449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39926195144653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34173011779785</t>
   </si>
   <si>
     <t xml:space="preserve">6.50989866256714</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33287954330444</t>
+    <t xml:space="preserve">6.33287906646729</t>
   </si>
   <si>
     <t xml:space="preserve">6.42581462860107</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39040994644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30632591247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40811157226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35500621795654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63381242752075</t>
+    <t xml:space="preserve">6.39041042327881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30632543563843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40811204910278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35500574111938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63381290435791</t>
   </si>
   <si>
     <t xml:space="preserve">6.43466567993164</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2266674041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24436950683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27534770965576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26649761199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62938642501831</t>
+    <t xml:space="preserve">6.22666645050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24436902999878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27534818649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2664966583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62938737869263</t>
   </si>
   <si>
     <t xml:space="preserve">6.43909072875977</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41253757476807</t>
+    <t xml:space="preserve">6.41253805160522</t>
   </si>
   <si>
     <t xml:space="preserve">6.45236730575562</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45679330825806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36828327178955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19568872451782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06734895706177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28862476348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20454120635986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29304933547974</t>
+    <t xml:space="preserve">6.4567928314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36828279495239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19568920135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06734991073608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28862428665161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20453929901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29304981231689</t>
   </si>
   <si>
     <t xml:space="preserve">6.24879455566406</t>
@@ -209,22 +209,22 @@
     <t xml:space="preserve">6.15585947036743</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19126319885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58955764770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47892045974731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49662303924561</t>
+    <t xml:space="preserve">6.19126272201538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58955669403076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47891998291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49662256240845</t>
   </si>
   <si>
     <t xml:space="preserve">6.42138910293579</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63348960876465</t>
+    <t xml:space="preserve">6.63348865509033</t>
   </si>
   <si>
     <t xml:space="preserve">6.45274019241333</t>
@@ -233,61 +233,61 @@
     <t xml:space="preserve">6.54311513900757</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44370222091675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50696468353271</t>
+    <t xml:space="preserve">6.44370269775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50696516036987</t>
   </si>
   <si>
     <t xml:space="preserve">6.55667114257812</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36688470840454</t>
+    <t xml:space="preserve">6.3668851852417</t>
   </si>
   <si>
     <t xml:space="preserve">6.61993312835693</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69223308563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59734010696411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68319511413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70578908920288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75097608566284</t>
+    <t xml:space="preserve">6.69223356246948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59733963012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6831955909729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70578956604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75097560882568</t>
   </si>
   <si>
     <t xml:space="preserve">6.85038805007935</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94528102874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9859504699707</t>
+    <t xml:space="preserve">6.94528150558472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98594999313354</t>
   </si>
   <si>
     <t xml:space="preserve">7.1034369468689</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25255393981934</t>
+    <t xml:space="preserve">7.25255489349365</t>
   </si>
   <si>
     <t xml:space="preserve">7.32033634185791</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45589780807495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30226039886475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37907934188843</t>
+    <t xml:space="preserve">7.45589828491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3022608757019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37907981872559</t>
   </si>
   <si>
     <t xml:space="preserve">7.25707340240479</t>
@@ -305,16 +305,16 @@
     <t xml:space="preserve">7.09439897537231</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13958597183228</t>
+    <t xml:space="preserve">7.13958644866943</t>
   </si>
   <si>
     <t xml:space="preserve">7.00402450561523</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08084344863892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95883798599243</t>
+    <t xml:space="preserve">7.08084392547607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95883750915527</t>
   </si>
   <si>
     <t xml:space="preserve">6.84135103225708</t>
@@ -323,13 +323,13 @@
     <t xml:space="preserve">7.11699342727661</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16669893264771</t>
+    <t xml:space="preserve">7.16669845581055</t>
   </si>
   <si>
     <t xml:space="preserve">7.31129884719849</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32485437393188</t>
+    <t xml:space="preserve">7.32485389709473</t>
   </si>
   <si>
     <t xml:space="preserve">6.9995059967041</t>
@@ -338,16 +338,16 @@
     <t xml:space="preserve">6.73290109634399</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08988046646118</t>
+    <t xml:space="preserve">7.08988094329834</t>
   </si>
   <si>
     <t xml:space="preserve">7.18477392196655</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85942554473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67867708206177</t>
+    <t xml:space="preserve">6.85942602157593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67867660522461</t>
   </si>
   <si>
     <t xml:space="preserve">6.49792718887329</t>
@@ -359,55 +359,52 @@
     <t xml:space="preserve">6.57926511764526</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41659021377563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74645709991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65156412124634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55215215682983</t>
+    <t xml:space="preserve">6.41658973693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74645757675171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65156507492065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55215167999268</t>
   </si>
   <si>
     <t xml:space="preserve">6.46177816390991</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43466520309448</t>
-  </si>
-  <si>
     <t xml:space="preserve">6.75549459457397</t>
   </si>
   <si>
     <t xml:space="preserve">6.56570816040039</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77808809280396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71030855178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48889017105103</t>
+    <t xml:space="preserve">6.77808904647827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71030807495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48888969421387</t>
   </si>
   <si>
     <t xml:space="preserve">6.53859615325928</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66060209274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68771457672119</t>
+    <t xml:space="preserve">6.66060161590576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68771409988403</t>
   </si>
   <si>
     <t xml:space="preserve">6.76001405715942</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87750053405762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70126962661743</t>
+    <t xml:space="preserve">6.87750005722046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70127010345459</t>
   </si>
   <si>
     <t xml:space="preserve">6.78712606430054</t>
@@ -419,7 +416,7 @@
     <t xml:space="preserve">6.81423759460449</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81875801086426</t>
+    <t xml:space="preserve">6.8187575340271</t>
   </si>
   <si>
     <t xml:space="preserve">6.82327604293823</t>
@@ -440,46 +437,46 @@
     <t xml:space="preserve">6.98143148422241</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17573595046997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01306295394897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97691202163696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64252662658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69675159454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88653802871704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93172550201416</t>
+    <t xml:space="preserve">7.17573642730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01306247711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97691249847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64252758026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69675064086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88653755187988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.931725025177</t>
   </si>
   <si>
     <t xml:space="preserve">7.02209997177124</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99046850204468</t>
+    <t xml:space="preserve">6.99046802520752</t>
   </si>
   <si>
     <t xml:space="preserve">7.19381141662598</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05824947357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04921293258667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06728744506836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1486234664917</t>
+    <t xml:space="preserve">7.05824899673462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04921245574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0672869682312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14862442016602</t>
   </si>
   <si>
     <t xml:space="preserve">7.08536243438721</t>
@@ -491,79 +488,79 @@
     <t xml:space="preserve">7.15766191482544</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21188592910767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38359832763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22092390060425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24803686141968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18929290771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35648584365845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37004089355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88201999664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03565549850464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18025588989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91365003585815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51915836334229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47849082946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50108432769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41071033477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27514886856079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.609534740448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66375780105591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72702026367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68183326721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6773157119751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63664674758911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77220964431763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97103071212769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34156703948975</t>
+    <t xml:space="preserve">7.21188688278198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38359785079956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22092294692993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24803638458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18929195404053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35648536682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.370041847229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88201856613159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03565645217896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18025493621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91365051269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5191593170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47849035263062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50108480453491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41070938110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27514791488647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60953426361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66375875473022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72702264785767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68183374404907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67731428146362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63664579391479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77220869064331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97103118896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34156608581543</t>
   </si>
   <si>
     <t xml:space="preserve">8.41386604309082</t>
@@ -575,13 +572,13 @@
     <t xml:space="preserve">8.57654094696045</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37771701812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40934944152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35964202880859</t>
+    <t xml:space="preserve">8.37771797180176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40934753417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35964298248291</t>
   </si>
   <si>
     <t xml:space="preserve">8.22408103942871</t>
@@ -590,67 +587,67 @@
     <t xml:space="preserve">8.24215602874756</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33704948425293</t>
+    <t xml:space="preserve">8.33705043792725</t>
   </si>
   <si>
     <t xml:space="preserve">8.32801151275635</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32349395751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36416053771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37320041656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.468092918396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30541610717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30089855194092</t>
+    <t xml:space="preserve">8.3234920501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36416244506836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37319946289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46809196472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30541801452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30089950561523</t>
   </si>
   <si>
     <t xml:space="preserve">8.09755611419678</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26926898956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20600605010986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07496452331543</t>
+    <t xml:space="preserve">8.26926803588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20600509643555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07496356964111</t>
   </si>
   <si>
     <t xml:space="preserve">8.11111164093018</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28282356262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29638004302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40482997894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48164749145508</t>
+    <t xml:space="preserve">8.28282451629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2963809967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40482902526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48164939880371</t>
   </si>
   <si>
     <t xml:space="preserve">8.4229040145874</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22859859466553</t>
+    <t xml:space="preserve">8.22859954833984</t>
   </si>
   <si>
     <t xml:space="preserve">8.2737865447998</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02977561950684</t>
+    <t xml:space="preserve">8.02977466583252</t>
   </si>
   <si>
     <t xml:space="preserve">8.13370609283447</t>
@@ -659,34 +656,34 @@
     <t xml:space="preserve">8.27830505371094</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43194198608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69402694702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57969760894775</t>
+    <t xml:space="preserve">8.4319429397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69402885437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57969856262207</t>
   </si>
   <si>
     <t xml:space="preserve">9.25435066223145</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21820163726807</t>
+    <t xml:space="preserve">9.21820068359375</t>
   </si>
   <si>
     <t xml:space="preserve">9.01937580108643</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16397666931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20012664794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20916271209717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2272367477417</t>
+    <t xml:space="preserve">9.16397762298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2001256942749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20916175842285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22723770141602</t>
   </si>
   <si>
     <t xml:space="preserve">8.94707679748535</t>
@@ -695,43 +692,43 @@
     <t xml:space="preserve">9.03745174407959</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12782573699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35376167297363</t>
+    <t xml:space="preserve">9.12782669067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35376262664795</t>
   </si>
   <si>
     <t xml:space="preserve">9.55258560180664</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47124767303467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80563354492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89600944519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2123203277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94119644165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4472951889038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8449420928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8087921142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9082040786743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9353151321411</t>
+    <t xml:space="preserve">9.47124862670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80563449859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89600849151611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2123212814331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94119739532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4472961425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8449411392212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8087911605835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.908203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9353170394897</t>
   </si>
   <si>
     <t xml:space="preserve">10.7364921569824</t>
@@ -743,58 +740,58 @@
     <t xml:space="preserve">10.754566192627</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4764308929443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2261095046997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0128736495972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3837194442749</t>
+    <t xml:space="preserve">10.476432800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.226110458374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0128746032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3837184906006</t>
   </si>
   <si>
     <t xml:space="preserve">10.4300756454468</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2817373275757</t>
+    <t xml:space="preserve">10.2817363739014</t>
   </si>
   <si>
     <t xml:space="preserve">10.4022617340088</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5135164260864</t>
+    <t xml:space="preserve">10.5135173797607</t>
   </si>
   <si>
     <t xml:space="preserve">10.4949741363525</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5413303375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7452955245972</t>
+    <t xml:space="preserve">10.5413293838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7452964782715</t>
   </si>
   <si>
     <t xml:space="preserve">11.0790586471558</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7743978500366</t>
+    <t xml:space="preserve">11.7743968963623</t>
   </si>
   <si>
     <t xml:space="preserve">11.5889739990234</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2181262969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3015670776367</t>
+    <t xml:space="preserve">11.2181272506714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3015661239624</t>
   </si>
   <si>
     <t xml:space="preserve">11.0976009368896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1439561843872</t>
+    <t xml:space="preserve">11.1439571380615</t>
   </si>
   <si>
     <t xml:space="preserve">11.0327024459839</t>
@@ -803,100 +800,103 @@
     <t xml:space="preserve">10.8287363052368</t>
   </si>
   <si>
+    <t xml:space="preserve">10.7545671463013</t>
+  </si>
+  <si>
     <t xml:space="preserve">10.7360248565674</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9863471984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8658218383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5691423416138</t>
+    <t xml:space="preserve">10.986346244812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8658208847046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5691452026367</t>
   </si>
   <si>
     <t xml:space="preserve">11.1254138946533</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0605173110962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4869899749756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0697860717773</t>
+    <t xml:space="preserve">11.0605154037476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4869918823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0697870254517</t>
   </si>
   <si>
     <t xml:space="preserve">10.9399909973145</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4499053955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4035482406616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7094974517822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0988874435425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3213958740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.894923210144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.516092300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5253620147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6737012863159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7478704452515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5346345901489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.794225692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7293272018433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5439033508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5809888839722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5624475479126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4697360992432</t>
+    <t xml:space="preserve">11.4499073028564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4035501480103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7094984054565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0988883972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3213968276978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8949213027954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5160913467407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5253629684448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6737003326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7478713989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5346336364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7942266464233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7293300628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5439052581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5809879302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5624465942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4697351455688</t>
   </si>
   <si>
     <t xml:space="preserve">12.4975481033325</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4882774353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.68297290802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6273460388184</t>
+    <t xml:space="preserve">12.4882793426514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6829719543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6273469924927</t>
   </si>
   <si>
     <t xml:space="preserve">12.5531759262085</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1823282241821</t>
+    <t xml:space="preserve">12.1823291778564</t>
   </si>
   <si>
     <t xml:space="preserve">12.3955659866333</t>
@@ -905,13 +905,13 @@
     <t xml:space="preserve">12.4233798980713</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2935829162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.367751121521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8856506347656</t>
+    <t xml:space="preserve">12.2935838699341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3677530288696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8856515884399</t>
   </si>
   <si>
     <t xml:space="preserve">12.28431224823</t>
@@ -932,52 +932,52 @@
     <t xml:space="preserve">12.2657690048218</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9412784576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9598197937012</t>
+    <t xml:space="preserve">11.9412775039673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9598207473755</t>
   </si>
   <si>
     <t xml:space="preserve">12.3306674957275</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4419231414795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3492107391357</t>
+    <t xml:space="preserve">12.4419212341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3492097854614</t>
   </si>
   <si>
     <t xml:space="preserve">12.3770236968994</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1545162200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2472286224365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.339940071106</t>
+    <t xml:space="preserve">12.1545152664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2472267150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.339937210083</t>
   </si>
   <si>
     <t xml:space="preserve">12.451192855835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2008714675903</t>
+    <t xml:space="preserve">12.200870513916</t>
   </si>
   <si>
     <t xml:space="preserve">12.4326505661011</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3028545379639</t>
+    <t xml:space="preserve">12.3028535842896</t>
   </si>
   <si>
     <t xml:space="preserve">12.256498336792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.061803817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0247182846069</t>
+    <t xml:space="preserve">12.0618028640747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0247192382812</t>
   </si>
   <si>
     <t xml:space="preserve">11.440634727478</t>
@@ -986,52 +986,52 @@
     <t xml:space="preserve">11.6353302001953</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7929391860962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6631412506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6816864013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7465829849243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9227342605591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8207530975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8671083450317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7373113632202</t>
+    <t xml:space="preserve">11.7929382324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6631422042847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6816844940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7465839385986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9227361679077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8207521438599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8671092987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7373123168945</t>
   </si>
   <si>
     <t xml:space="preserve">12.2286834716797</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1915988922119</t>
+    <t xml:space="preserve">12.1915998458862</t>
   </si>
   <si>
     <t xml:space="preserve">11.7651252746582</t>
   </si>
   <si>
-    <t xml:space="preserve">11.718770980835</t>
+    <t xml:space="preserve">11.7187700271606</t>
   </si>
   <si>
     <t xml:space="preserve">11.1903123855591</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2922945022583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1624994277954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5426177978516</t>
+    <t xml:space="preserve">11.2922954559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1624984741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5426168441772</t>
   </si>
   <si>
     <t xml:space="preserve">11.4684476852417</t>
@@ -1043,25 +1043,25 @@
     <t xml:space="preserve">11.579701423645</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4962615966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6724138259888</t>
+    <t xml:space="preserve">11.4962606430054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6724147796631</t>
   </si>
   <si>
     <t xml:space="preserve">11.857837677002</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1452436447144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.006175994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9134635925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9240226745605</t>
+    <t xml:space="preserve">12.1452445983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0061750411987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9134645462036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9240217208862</t>
   </si>
   <si>
     <t xml:space="preserve">13.9253101348877</t>
@@ -1073,10 +1073,10 @@
     <t xml:space="preserve">14.092191696167</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9438533782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9994792938232</t>
+    <t xml:space="preserve">13.9438524246216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9994802474976</t>
   </si>
   <si>
     <t xml:space="preserve">14.629919052124</t>
@@ -1085,70 +1085,70 @@
     <t xml:space="preserve">13.9067678451538</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6286315917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2034463882446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0180215835571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7028017044067</t>
+    <t xml:space="preserve">13.6286334991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2034454345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0180225372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7028007507324</t>
   </si>
   <si>
     <t xml:space="preserve">14.3888702392578</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5186653137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5742931365967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4815816879272</t>
+    <t xml:space="preserve">14.518666267395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.574294090271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4815807342529</t>
   </si>
   <si>
     <t xml:space="preserve">14.1849031448364</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8325977325439</t>
+    <t xml:space="preserve">13.8325996398926</t>
   </si>
   <si>
     <t xml:space="preserve">12.9981918334961</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7756843566895</t>
+    <t xml:space="preserve">12.7756834030151</t>
   </si>
   <si>
     <t xml:space="preserve">13.3690395355225</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0352783203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7385988235474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9796514511108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5173788070679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3134117126465</t>
+    <t xml:space="preserve">13.0352764129639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7385997772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9796504974365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5173778533936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3134126663208</t>
   </si>
   <si>
     <t xml:space="preserve">12.6644296646118</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1081600189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0154476165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8300228118896</t>
+    <t xml:space="preserve">12.1081609725952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0154466629028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.830023765564</t>
   </si>
   <si>
     <t xml:space="preserve">12.5902605056763</t>
@@ -1157,10 +1157,10 @@
     <t xml:space="preserve">12.7200574874878</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6088037490845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1637868881226</t>
+    <t xml:space="preserve">12.6088047027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1637859344482</t>
   </si>
   <si>
     <t xml:space="preserve">12.033989906311</t>
@@ -1172,85 +1172,85 @@
     <t xml:space="preserve">11.6075162887573</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4604635238647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8114824295044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8485670089722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2379560470581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3862934112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3504972457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5359210968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7213430404663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2590742111206</t>
+    <t xml:space="preserve">12.4604625701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8114814758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8485679626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2379541397095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3862953186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3504962921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5359220504761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7213439941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2590732574463</t>
   </si>
   <si>
     <t xml:space="preserve">14.908055305481</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7782592773438</t>
+    <t xml:space="preserve">14.7782583236694</t>
   </si>
   <si>
     <t xml:space="preserve">14.7411727905273</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7968015670776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0235719680786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.684986114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4015226364136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2314462661743</t>
+    <t xml:space="preserve">14.796802520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0235710144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6849870681763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4015235900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2314443588257</t>
   </si>
   <si>
     <t xml:space="preserve">15.0802659988403</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1180601119995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1747522354126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3070363998413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1353855133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8141279220581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2660980224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6062545776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6818428039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0771217346191</t>
+    <t xml:space="preserve">15.1180610656738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1747512817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.307035446167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.13538646698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8141269683838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2660970687866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6062526702881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6818437576294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0771207809448</t>
   </si>
   <si>
     <t xml:space="preserve">12.9448385238647</t>
@@ -1259,64 +1259,64 @@
     <t xml:space="preserve">13.1149168014526</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8881454467773</t>
+    <t xml:space="preserve">12.8881464004517</t>
   </si>
   <si>
     <t xml:space="preserve">12.0944480895996</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5479888916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0015306472778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6235790252686</t>
+    <t xml:space="preserve">12.5479898452759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0015316009521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6235799789429</t>
   </si>
   <si>
     <t xml:space="preserve">12.6991701126099</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7558641433716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8692483901978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3401165008545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7369651794434</t>
+    <t xml:space="preserve">12.7558631896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8692493438721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3401174545288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.736964225769</t>
   </si>
   <si>
     <t xml:space="preserve">12.7180681228638</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7747602462769</t>
+    <t xml:space="preserve">12.7747611999512</t>
   </si>
   <si>
     <t xml:space="preserve">12.2645254135132</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7385368347168</t>
+    <t xml:space="preserve">13.7385358810425</t>
   </si>
   <si>
     <t xml:space="preserve">13.7763319015503</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9653062820435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8708190917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0786924362183</t>
+    <t xml:space="preserve">13.9653072357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8708200454712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0786933898926</t>
   </si>
   <si>
     <t xml:space="preserve">13.6251516342163</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5873575210571</t>
+    <t xml:space="preserve">13.5873565673828</t>
   </si>
   <si>
     <t xml:space="preserve">13.4172782897949</t>
@@ -1328,22 +1328,22 @@
     <t xml:space="preserve">13.4361753463745</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2472009658813</t>
+    <t xml:space="preserve">13.2471990585327</t>
   </si>
   <si>
     <t xml:space="preserve">13.1338138580322</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3227910995483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4739713668823</t>
+    <t xml:space="preserve">13.322790145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.473970413208</t>
   </si>
   <si>
     <t xml:space="preserve">13.2094039916992</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3605852127075</t>
+    <t xml:space="preserve">13.3605861663818</t>
   </si>
   <si>
     <t xml:space="preserve">12.5668869018555</t>
@@ -1352,46 +1352,46 @@
     <t xml:space="preserve">12.5101938247681</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2834234237671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6802730560303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0393266677856</t>
+    <t xml:space="preserve">12.2834243774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.680272102356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.03932762146</t>
   </si>
   <si>
     <t xml:space="preserve">12.9826335906982</t>
   </si>
   <si>
-    <t xml:space="preserve">12.812557220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.963737487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7952289581299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1164875030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2676696777344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3054637908936</t>
+    <t xml:space="preserve">12.8125553131104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9637355804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7952299118042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1164865493774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2676677703857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3054647445679</t>
   </si>
   <si>
     <t xml:space="preserve">14.059796333313</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7007427215576</t>
+    <t xml:space="preserve">13.7007398605347</t>
   </si>
   <si>
     <t xml:space="preserve">13.4928684234619</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7574338912964</t>
+    <t xml:space="preserve">13.7574348449707</t>
   </si>
   <si>
     <t xml:space="preserve">13.549560546875</t>
@@ -1400,13 +1400,13 @@
     <t xml:space="preserve">14.1731815338135</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9290819168091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4960117340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2692413330078</t>
+    <t xml:space="preserve">14.929084777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4960079193115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2692403793335</t>
   </si>
   <si>
     <t xml:space="preserve">15.155855178833</t>
@@ -1415,22 +1415,22 @@
     <t xml:space="preserve">16.5353775024414</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7054576873779</t>
+    <t xml:space="preserve">16.7054557800293</t>
   </si>
   <si>
     <t xml:space="preserve">16.913330078125</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6298656463623</t>
+    <t xml:space="preserve">16.6298675537109</t>
   </si>
   <si>
     <t xml:space="preserve">16.2330169677734</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9117565155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5904970169067</t>
+    <t xml:space="preserve">15.9117584228516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5904979705811</t>
   </si>
   <si>
     <t xml:space="preserve">15.5149097442627</t>
@@ -1442,7 +1442,7 @@
     <t xml:space="preserve">15.2125473022461</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3810539245605</t>
+    <t xml:space="preserve">14.3810548782349</t>
   </si>
   <si>
     <t xml:space="preserve">14.6078252792358</t>
@@ -1451,37 +1451,37 @@
     <t xml:space="preserve">14.4377470016479</t>
   </si>
   <si>
-    <t xml:space="preserve">14.645619392395</t>
+    <t xml:space="preserve">14.6456203460693</t>
   </si>
   <si>
     <t xml:space="preserve">14.2487707138062</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1920776367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8897171020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5306625366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8519220352173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0219993591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.872389793396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4755420684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4188480377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5527038574219</t>
+    <t xml:space="preserve">14.1920785903931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8897180557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5306634902954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.851921081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0220012664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8723907470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4755430221558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.418848991394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5527048110962</t>
   </si>
   <si>
     <t xml:space="preserve">14.9668798446655</t>
@@ -1493,40 +1493,40 @@
     <t xml:space="preserve">16.0629386901855</t>
   </si>
   <si>
-    <t xml:space="preserve">16.251916885376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0440406799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8739624023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4582166671753</t>
+    <t xml:space="preserve">16.2519149780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0440425872803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8739633560181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.458215713501</t>
   </si>
   <si>
     <t xml:space="preserve">16.0251426696777</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3464012145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1007328033447</t>
+    <t xml:space="preserve">16.3464031219482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.100736618042</t>
   </si>
   <si>
     <t xml:space="preserve">16.327507019043</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6471910476685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7983713150024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9306554794312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0613670349121</t>
+    <t xml:space="preserve">15.6471891403198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7983722686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9306545257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0613660812378</t>
   </si>
   <si>
     <t xml:space="preserve">15.8550653457642</t>
@@ -1535,16 +1535,16 @@
     <t xml:space="preserve">15.4771127700806</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7401075363159</t>
+    <t xml:space="preserve">14.7401084899902</t>
   </si>
   <si>
     <t xml:space="preserve">14.9101858139038</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5511312484741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8156976699829</t>
+    <t xml:space="preserve">14.5511322021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8156995773315</t>
   </si>
   <si>
     <t xml:space="preserve">14.9857759475708</t>
@@ -1553,76 +1553,76 @@
     <t xml:space="preserve">15.5338068008423</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7416801452637</t>
+    <t xml:space="preserve">15.741678237915</t>
   </si>
   <si>
     <t xml:space="preserve">15.0424690246582</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4204206466675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7605762481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6282978057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.892861366272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9684524536133</t>
+    <t xml:space="preserve">15.4204196929932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7605791091919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6282939910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8928594589233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9684467315674</t>
   </si>
   <si>
     <t xml:space="preserve">16.0062465667725</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9873456954956</t>
+    <t xml:space="preserve">15.9873485565186</t>
   </si>
   <si>
     <t xml:space="preserve">15.6093978881836</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6834154129028</t>
+    <t xml:space="preserve">14.6834173202515</t>
   </si>
   <si>
     <t xml:space="preserve">14.6267223358154</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8534936904907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1936511993408</t>
+    <t xml:space="preserve">14.853494644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1936502456665</t>
   </si>
   <si>
     <t xml:space="preserve">15.0991621017456</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2881374359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1952228546143</t>
+    <t xml:space="preserve">15.2881383895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1952209472656</t>
   </si>
   <si>
     <t xml:space="preserve">17.0078163146973</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2345905303955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2534828186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.29128074646</t>
+    <t xml:space="preserve">17.2345886230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2534866333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2912769317627</t>
   </si>
   <si>
     <t xml:space="preserve">17.1023063659668</t>
   </si>
   <si>
-    <t xml:space="preserve">17.064510345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0471820831299</t>
+    <t xml:space="preserve">17.0645065307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0471839904785</t>
   </si>
   <si>
     <t xml:space="preserve">17.4046649932861</t>
@@ -1631,25 +1631,25 @@
     <t xml:space="preserve">17.347972869873</t>
   </si>
   <si>
-    <t xml:space="preserve">17.366870880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4991550445557</t>
+    <t xml:space="preserve">17.3668689727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.499153137207</t>
   </si>
   <si>
     <t xml:space="preserve">17.0456142425537</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3857707977295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4424591064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8582077026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8204097747803</t>
+    <t xml:space="preserve">17.3857688903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4424610137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8582096099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8204135894775</t>
   </si>
   <si>
     <t xml:space="preserve">17.5558471679688</t>
@@ -1661,28 +1661,28 @@
     <t xml:space="preserve">17.140100479126</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5731716156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5920734405518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2897090911865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8566379547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1574268341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5805950164795</t>
+    <t xml:space="preserve">16.5731754302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5920696258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2897109985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8566360473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1574249267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5805969238281</t>
   </si>
   <si>
     <t xml:space="preserve">16.5421276092529</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3882465362549</t>
+    <t xml:space="preserve">16.3882484436035</t>
   </si>
   <si>
     <t xml:space="preserve">16.4459533691406</t>
@@ -1691,37 +1691,37 @@
     <t xml:space="preserve">16.2343654632568</t>
   </si>
   <si>
-    <t xml:space="preserve">16.003547668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9843130111694</t>
+    <t xml:space="preserve">16.0035438537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9843101501465</t>
   </si>
   <si>
     <t xml:space="preserve">16.6767711639404</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8114185333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8306522369385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7537117004395</t>
+    <t xml:space="preserve">16.8114166259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8306503295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7537097930908</t>
   </si>
   <si>
     <t xml:space="preserve">16.6383018493652</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4267139434814</t>
+    <t xml:space="preserve">16.4267158508301</t>
   </si>
   <si>
     <t xml:space="preserve">16.522891998291</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9458389282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4651889801025</t>
+    <t xml:space="preserve">15.9458417892456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4651851654053</t>
   </si>
   <si>
     <t xml:space="preserve">15.9650754928589</t>
@@ -1730,13 +1730,13 @@
     <t xml:space="preserve">16.0227813720703</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8688993453979</t>
+    <t xml:space="preserve">15.8689012527466</t>
   </si>
   <si>
     <t xml:space="preserve">15.7342557907104</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6573171615601</t>
+    <t xml:space="preserve">15.6573162078857</t>
   </si>
   <si>
     <t xml:space="preserve">15.426495552063</t>
@@ -1748,13 +1748,13 @@
     <t xml:space="preserve">15.3110847473145</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9840898513794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1956739425659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2341461181641</t>
+    <t xml:space="preserve">14.9840879440308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1956748962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2341451644897</t>
   </si>
   <si>
     <t xml:space="preserve">15.1379690170288</t>
@@ -1766,19 +1766,19 @@
     <t xml:space="preserve">15.003324508667</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1187343597412</t>
+    <t xml:space="preserve">15.1187353134155</t>
   </si>
   <si>
     <t xml:space="preserve">15.253378868103</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0610303878784</t>
+    <t xml:space="preserve">15.0610284805298</t>
   </si>
   <si>
     <t xml:space="preserve">14.8686800003052</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8494434356689</t>
+    <t xml:space="preserve">14.8494443893433</t>
   </si>
   <si>
     <t xml:space="preserve">14.7147989273071</t>
@@ -1793,10 +1793,10 @@
     <t xml:space="preserve">14.8302097320557</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0802640914917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9648542404175</t>
+    <t xml:space="preserve">15.080265045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9648551940918</t>
   </si>
   <si>
     <t xml:space="preserve">15.1572046279907</t>
@@ -1811,19 +1811,19 @@
     <t xml:space="preserve">14.9071483612061</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0225591659546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8109731674194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8879137039185</t>
+    <t xml:space="preserve">15.0225582122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8109741210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8879146575928</t>
   </si>
   <si>
     <t xml:space="preserve">14.5416841506958</t>
   </si>
   <si>
-    <t xml:space="preserve">14.580153465271</t>
+    <t xml:space="preserve">14.5801544189453</t>
   </si>
   <si>
     <t xml:space="preserve">14.5993890762329</t>
@@ -1838,10 +1838,10 @@
     <t xml:space="preserve">14.6186237335205</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4647445678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4455080032349</t>
+    <t xml:space="preserve">14.4647436141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4455089569092</t>
   </si>
   <si>
     <t xml:space="preserve">14.65709400177</t>
@@ -1850,58 +1850,58 @@
     <t xml:space="preserve">14.9263849258423</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5609188079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.349555015564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3880252838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6765489578247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.522668838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7150211334229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7919597625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.77272605896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8111963272095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9073734283447</t>
+    <t xml:space="preserve">14.5609197616577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3495559692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3880262374878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.676549911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5226707458496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7150201797485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7919616699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.772723197937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8111972808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9073705673218</t>
   </si>
   <si>
     <t xml:space="preserve">15.6380805969238</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6188459396362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8496656417847</t>
+    <t xml:space="preserve">15.6188449859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8496646881104</t>
   </si>
   <si>
     <t xml:space="preserve">15.5803756713867</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5034351348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8304300308228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9266052246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1189556121826</t>
+    <t xml:space="preserve">15.5034341812134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8304309844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9266042709351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1189575195312</t>
   </si>
   <si>
     <t xml:space="preserve">17.1576480865479</t>
@@ -1913,19 +1913,19 @@
     <t xml:space="preserve">16.9460639953613</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8883590698242</t>
+    <t xml:space="preserve">16.8883571624756</t>
   </si>
   <si>
     <t xml:space="preserve">16.9845314025879</t>
   </si>
   <si>
-    <t xml:space="preserve">17.119176864624</t>
+    <t xml:space="preserve">17.1191787719727</t>
   </si>
   <si>
     <t xml:space="preserve">17.2730579376221</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2732791900635</t>
+    <t xml:space="preserve">18.2732772827148</t>
   </si>
   <si>
     <t xml:space="preserve">18.1771049499512</t>
@@ -1934,10 +1934,10 @@
     <t xml:space="preserve">17.6000518798828</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6577587127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1001663208008</t>
+    <t xml:space="preserve">17.6577606201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1001644134521</t>
   </si>
   <si>
     <t xml:space="preserve">17.9847564697266</t>
@@ -1946,40 +1946,40 @@
     <t xml:space="preserve">18.1193981170654</t>
   </si>
   <si>
-    <t xml:space="preserve">17.965518951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9462833404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.061695098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9270496368408</t>
+    <t xml:space="preserve">17.9655170440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9462852478027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0616931915283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9270477294922</t>
   </si>
   <si>
     <t xml:space="preserve">18.3117504119873</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7541542053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1003856658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0234470367432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5425720214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9657421112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9080371856689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4273834228516</t>
+    <t xml:space="preserve">18.7541561126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1003875732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0234489440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5425701141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9657382965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9080352783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4273815155029</t>
   </si>
   <si>
     <t xml:space="preserve">19.8120822906494</t>
@@ -2006,58 +2006,58 @@
     <t xml:space="preserve">19.7639923095703</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3312072753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.571647644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1967811584473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2448692321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.216459274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1585330963135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1104488372803</t>
+    <t xml:space="preserve">19.331205368042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5716438293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1967849731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2448711395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2164630889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1585350036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1104469299316</t>
   </si>
   <si>
     <t xml:space="preserve">20.8219223022461</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6295738220215</t>
+    <t xml:space="preserve">20.6295719146729</t>
   </si>
   <si>
     <t xml:space="preserve">21.0142726898193</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7257423400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6776561737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9563446044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2929573059082</t>
+    <t xml:space="preserve">20.7257461547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6776599884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9563465118408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2929553985596</t>
   </si>
   <si>
     <t xml:space="preserve">20.0044326782227</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8601703643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0811500549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.773832321167</t>
+    <t xml:space="preserve">19.8601684570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0811519622803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7738361358643</t>
   </si>
   <si>
     <t xml:space="preserve">20.9180965423584</t>
@@ -2066,13 +2066,13 @@
     <t xml:space="preserve">20.5814819335938</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2547092437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3989734649658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2066230773926</t>
+    <t xml:space="preserve">21.254711151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3989715576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2066192626953</t>
   </si>
   <si>
     <t xml:space="preserve">21.6394100189209</t>
@@ -2084,7 +2084,7 @@
     <t xml:space="preserve">21.8317604064941</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0525226593018</t>
+    <t xml:space="preserve">20.0525188446045</t>
   </si>
   <si>
     <t xml:space="preserve">20.100606918335</t>
@@ -2093,22 +2093,22 @@
     <t xml:space="preserve">18.734920501709</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1963386535645</t>
+    <t xml:space="preserve">18.1963405609131</t>
   </si>
   <si>
     <t xml:space="preserve">17.6192893981934</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3113059997559</t>
+    <t xml:space="preserve">16.3113040924072</t>
   </si>
   <si>
     <t xml:space="preserve">16.1958961486816</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4839792251587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4262742996216</t>
+    <t xml:space="preserve">14.4839782714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4262733459473</t>
   </si>
   <si>
     <t xml:space="preserve">12.464301109314</t>
@@ -2120,76 +2120,76 @@
     <t xml:space="preserve">12.1373043060303</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6951217651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9067068099976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9834241867065</t>
+    <t xml:space="preserve">12.6951198577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9067058563232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9834251403809</t>
   </si>
   <si>
     <t xml:space="preserve">13.3106412887573</t>
   </si>
   <si>
-    <t xml:space="preserve">13.560697555542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0223388671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1954536437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2916278839111</t>
+    <t xml:space="preserve">13.5606966018677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0223369598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1954526901245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2916269302368</t>
   </si>
   <si>
     <t xml:space="preserve">14.1185131072998</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7340335845947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0992784500122</t>
+    <t xml:space="preserve">14.734034538269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0992774963379</t>
   </si>
   <si>
     <t xml:space="preserve">15.4072599411011</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8691215515137</t>
+    <t xml:space="preserve">16.8691253662109</t>
   </si>
   <si>
     <t xml:space="preserve">16.1766624450684</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2151317596436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4649658203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0612506866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1381931304932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0420150756836</t>
+    <t xml:space="preserve">16.2151298522949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4649648666382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0612525939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1381912231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0420169830322</t>
   </si>
   <si>
     <t xml:space="preserve">16.59983253479</t>
   </si>
   <si>
-    <t xml:space="preserve">17.215353012085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7152423858643</t>
+    <t xml:space="preserve">17.2153511047363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7152404785156</t>
   </si>
   <si>
     <t xml:space="preserve">16.9268283843994</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0614738464355</t>
+    <t xml:space="preserve">17.0614700317383</t>
   </si>
   <si>
     <t xml:space="preserve">18.2540454864502</t>
@@ -2201,10 +2201,10 @@
     <t xml:space="preserve">18.0774536132812</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7677764892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.458101272583</t>
+    <t xml:space="preserve">17.7677783966064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4580993652344</t>
   </si>
   <si>
     <t xml:space="preserve">17.43874168396</t>
@@ -2216,16 +2216,16 @@
     <t xml:space="preserve">16.954870223999</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4193859100342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6129379272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1677761077881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.651647567749</t>
+    <t xml:space="preserve">17.4193878173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6129398345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1677742004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6516456604004</t>
   </si>
   <si>
     <t xml:space="preserve">17.4968070983887</t>
@@ -2234,7 +2234,7 @@
     <t xml:space="preserve">17.7290668487549</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2903594970703</t>
+    <t xml:space="preserve">18.290355682373</t>
   </si>
   <si>
     <t xml:space="preserve">17.9419708251953</t>
@@ -2246,22 +2246,22 @@
     <t xml:space="preserve">18.3871307373047</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4064865112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9032611846924</t>
+    <t xml:space="preserve">18.4064884185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9032592773438</t>
   </si>
   <si>
     <t xml:space="preserve">18.232292175293</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2516460418701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.580680847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4451999664307</t>
+    <t xml:space="preserve">18.2516498565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5806827545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4451961517334</t>
   </si>
   <si>
     <t xml:space="preserve">18.1161632537842</t>
@@ -2270,40 +2270,40 @@
     <t xml:space="preserve">18.0387439727783</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8322944641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7742309570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6774559020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9097156524658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0451965332031</t>
+    <t xml:space="preserve">18.8322925567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7742290496826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.677453994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9097137451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0452003479004</t>
   </si>
   <si>
     <t xml:space="preserve">19.5968132019043</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3548755645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9484214782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1032638549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4645500183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6581020355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.500036239624</t>
+    <t xml:space="preserve">19.3548774719238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9484252929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1032619476318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4645519256592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6580982208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5000381469727</t>
   </si>
   <si>
     <t xml:space="preserve">19.6451988220215</t>
@@ -2330,40 +2330,40 @@
     <t xml:space="preserve">21.7258491516113</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1935901641846</t>
+    <t xml:space="preserve">21.1935863494873</t>
   </si>
   <si>
     <t xml:space="preserve">21.5806884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8710079193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.532299041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3387508392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7742347717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4516544342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9355297088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7903652191162</t>
+    <t xml:space="preserve">21.8710117340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5323009490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3387489318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7742328643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4516582489014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9355278015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7903633117676</t>
   </si>
   <si>
     <t xml:space="preserve">23.3226261138916</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4194011688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0968208312988</t>
+    <t xml:space="preserve">23.4193992614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0968189239502</t>
   </si>
   <si>
     <t xml:space="preserve">24.7258529663086</t>
@@ -2372,16 +2372,16 @@
     <t xml:space="preserve">24.4839172363281</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0484352111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7581081390381</t>
+    <t xml:space="preserve">24.048433303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7581119537354</t>
   </si>
   <si>
     <t xml:space="preserve">23.9516582489014</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6613368988037</t>
+    <t xml:space="preserve">23.6613349914551</t>
   </si>
   <si>
     <t xml:space="preserve">22.7419815063477</t>
@@ -2390,13 +2390,13 @@
     <t xml:space="preserve">23.0323028564453</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4677848815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0806903839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8871383666992</t>
+    <t xml:space="preserve">23.4677886962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0806884765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8871421813965</t>
   </si>
   <si>
     <t xml:space="preserve">22.5484294891357</t>
@@ -2405,7 +2405,7 @@
     <t xml:space="preserve">21.8226222991943</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0645561218262</t>
+    <t xml:space="preserve">22.0645580291748</t>
   </si>
   <si>
     <t xml:space="preserve">21.2419776916504</t>
@@ -2414,34 +2414,34 @@
     <t xml:space="preserve">21.6290740966797</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4677791595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3871383666992</t>
+    <t xml:space="preserve">20.4677810668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3871402740479</t>
   </si>
   <si>
     <t xml:space="preserve">21.0968151092529</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4839115142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2097206115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9677848815918</t>
+    <t xml:space="preserve">21.4839134216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2097187042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9677867889404</t>
   </si>
   <si>
     <t xml:space="preserve">20.9516544342041</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1129455566406</t>
+    <t xml:space="preserve">22.1129474639893</t>
   </si>
   <si>
     <t xml:space="preserve">22.3548812866211</t>
   </si>
   <si>
-    <t xml:space="preserve">21.919397354126</t>
+    <t xml:space="preserve">21.9193954467773</t>
   </si>
   <si>
     <t xml:space="preserve">22.838752746582</t>
@@ -2474,7 +2474,7 @@
     <t xml:space="preserve">26.6129550933838</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3710174560547</t>
+    <t xml:space="preserve">26.3710193634033</t>
   </si>
   <si>
     <t xml:space="preserve">27.6774730682373</t>
@@ -2483,43 +2483,43 @@
     <t xml:space="preserve">28.6452159881592</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9032821655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9355392456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7581195831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3871555328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9194145202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7419986724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0323143005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5484447479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0807037353516</t>
+    <t xml:space="preserve">29.903284072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9355373382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7581233978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3871536254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9194164276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.742000579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0323181152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5484466552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0807113647461</t>
   </si>
   <si>
     <t xml:space="preserve">31.2581233978271</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1774787902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.322639465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2903900146484</t>
+    <t xml:space="preserve">32.1774826049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3226470947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2903861999512</t>
   </si>
   <si>
     <t xml:space="preserve">33.1936111450195</t>
@@ -2531,28 +2531,28 @@
     <t xml:space="preserve">33.4839363098145</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7258682250977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.112964630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.742000579834</t>
+    <t xml:space="preserve">33.7258644104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1129722595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7420043945312</t>
   </si>
   <si>
     <t xml:space="preserve">34.5968399047852</t>
   </si>
   <si>
-    <t xml:space="preserve">35.3710327148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4678115844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.8226509094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.1613616943359</t>
+    <t xml:space="preserve">35.3710403442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4678077697754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.8226547241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.1613655090332</t>
   </si>
   <si>
     <t xml:space="preserve">36.1936225891113</t>
@@ -2561,19 +2561,19 @@
     <t xml:space="preserve">34.3065185546875</t>
   </si>
   <si>
-    <t xml:space="preserve">32.564582824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6613578796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.758129119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7097434997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9355430603027</t>
+    <t xml:space="preserve">32.5645790100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6613502502441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7581253051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7097396850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.935546875</t>
   </si>
   <si>
     <t xml:space="preserve">30.3387699127197</t>
@@ -2582,7 +2582,7 @@
     <t xml:space="preserve">30.822639465332</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5807018280029</t>
+    <t xml:space="preserve">30.5807037353516</t>
   </si>
   <si>
     <t xml:space="preserve">30.4839305877686</t>
@@ -2594,43 +2594,43 @@
     <t xml:space="preserve">33.435546875</t>
   </si>
   <si>
-    <t xml:space="preserve">33.871036529541</t>
+    <t xml:space="preserve">33.8710327148438</t>
   </si>
   <si>
     <t xml:space="preserve">35.2742614746094</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6613616943359</t>
+    <t xml:space="preserve">35.6613578796387</t>
   </si>
   <si>
     <t xml:space="preserve">35.7097473144531</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2581367492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.0161972045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.9678115844727</t>
+    <t xml:space="preserve">37.2581405639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.0162010192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.9678153991699</t>
   </si>
   <si>
     <t xml:space="preserve">35.9516868591309</t>
   </si>
   <si>
-    <t xml:space="preserve">36.4355583190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0807075500488</t>
+    <t xml:space="preserve">36.4355506896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0807151794434</t>
   </si>
   <si>
     <t xml:space="preserve">34.9839363098145</t>
   </si>
   <si>
-    <t xml:space="preserve">36.6774940490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.0645866394043</t>
+    <t xml:space="preserve">36.677490234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.064582824707</t>
   </si>
   <si>
     <t xml:space="preserve">37.6452331542969</t>
@@ -2642,7 +2642,7 @@
     <t xml:space="preserve">38.612979888916</t>
   </si>
   <si>
-    <t xml:space="preserve">38.7581405639648</t>
+    <t xml:space="preserve">38.7581367492676</t>
   </si>
   <si>
     <t xml:space="preserve">39.8226585388184</t>
@@ -2654,19 +2654,19 @@
     <t xml:space="preserve">38.5645904541016</t>
   </si>
   <si>
-    <t xml:space="preserve">38.7097511291504</t>
+    <t xml:space="preserve">38.7097549438477</t>
   </si>
   <si>
     <t xml:space="preserve">39.6291084289551</t>
   </si>
   <si>
-    <t xml:space="preserve">40.4516868591309</t>
+    <t xml:space="preserve">40.4516906738281</t>
   </si>
   <si>
     <t xml:space="preserve">40.1613693237305</t>
   </si>
   <si>
-    <t xml:space="preserve">39.4355621337891</t>
+    <t xml:space="preserve">39.4355545043945</t>
   </si>
   <si>
     <t xml:space="preserve">40.2581405639648</t>
@@ -2696,49 +2696,49 @@
     <t xml:space="preserve">42.6291160583496</t>
   </si>
   <si>
-    <t xml:space="preserve">41.612979888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.3871803283691</t>
+    <t xml:space="preserve">41.6129837036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.3871726989746</t>
   </si>
   <si>
     <t xml:space="preserve">43.5000839233398</t>
   </si>
   <si>
-    <t xml:space="preserve">44.1291122436523</t>
+    <t xml:space="preserve">44.1291160583496</t>
   </si>
   <si>
     <t xml:space="preserve">44.7097625732422</t>
   </si>
   <si>
-    <t xml:space="preserve">44.7581481933594</t>
+    <t xml:space="preserve">44.7581520080566</t>
   </si>
   <si>
     <t xml:space="preserve">45.6775054931641</t>
   </si>
   <si>
-    <t xml:space="preserve">44.4194412231445</t>
+    <t xml:space="preserve">44.4194374084473</t>
   </si>
   <si>
     <t xml:space="preserve">45.0000877380371</t>
   </si>
   <si>
-    <t xml:space="preserve">46.0162162780762</t>
+    <t xml:space="preserve">46.0162200927734</t>
   </si>
   <si>
     <t xml:space="preserve">45.4839630126953</t>
   </si>
   <si>
-    <t xml:space="preserve">44.9517021179199</t>
+    <t xml:space="preserve">44.9516983032227</t>
   </si>
   <si>
     <t xml:space="preserve">46.2581520080566</t>
   </si>
   <si>
-    <t xml:space="preserve">45.1452484130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.6129837036133</t>
+    <t xml:space="preserve">45.1452522277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.6129875183105</t>
   </si>
   <si>
     <t xml:space="preserve">44.5162162780762</t>
@@ -2747,43 +2747,43 @@
     <t xml:space="preserve">44.2742767333984</t>
   </si>
   <si>
-    <t xml:space="preserve">43.838794708252</t>
+    <t xml:space="preserve">43.8387908935547</t>
   </si>
   <si>
     <t xml:space="preserve">43.161376953125</t>
   </si>
   <si>
-    <t xml:space="preserve">43.3065376281738</t>
+    <t xml:space="preserve">43.3065338134766</t>
   </si>
   <si>
     <t xml:space="preserve">43.2581481933594</t>
   </si>
   <si>
-    <t xml:space="preserve">42.8710479736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.0645980834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.0323448181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.4033126831055</t>
+    <t xml:space="preserve">42.8710517883301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.0646018981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.0323486328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.4033088684082</t>
   </si>
   <si>
     <t xml:space="preserve">42.4355659484863</t>
   </si>
   <si>
-    <t xml:space="preserve">41.8992881774902</t>
+    <t xml:space="preserve">41.8992919921875</t>
   </si>
   <si>
     <t xml:space="preserve">40.0436096191406</t>
   </si>
   <si>
-    <t xml:space="preserve">39.7994422912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4576072692871</t>
+    <t xml:space="preserve">39.799446105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4576110839844</t>
   </si>
   <si>
     <t xml:space="preserve">40.0924415588379</t>
@@ -2792,16 +2792,16 @@
     <t xml:space="preserve">40.873779296875</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9947776794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.7761116027832</t>
+    <t xml:space="preserve">39.9947738647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.7761154174805</t>
   </si>
   <si>
     <t xml:space="preserve">40.6784477233887</t>
   </si>
   <si>
-    <t xml:space="preserve">40.190113067627</t>
+    <t xml:space="preserve">40.1901092529297</t>
   </si>
   <si>
     <t xml:space="preserve">39.8971061706543</t>
@@ -2816,7 +2816,7 @@
     <t xml:space="preserve">39.7506065368652</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2622718811035</t>
+    <t xml:space="preserve">39.2622680664062</t>
   </si>
   <si>
     <t xml:space="preserve">40.2877769470215</t>
@@ -2828,58 +2828,58 @@
     <t xml:space="preserve">37.8949279785156</t>
   </si>
   <si>
-    <t xml:space="preserve">36.7229232788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6019287109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.090259552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.5552749633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.7039527893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.0946197509766</t>
+    <t xml:space="preserve">36.7229194641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.601921081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.0902633666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.5552711486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.7039566040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.0946235656738</t>
   </si>
   <si>
     <t xml:space="preserve">41.4597854614258</t>
   </si>
   <si>
-    <t xml:space="preserve">41.0691146850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.385440826416</t>
+    <t xml:space="preserve">41.0691184997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.3854446411133</t>
   </si>
   <si>
     <t xml:space="preserve">40.4342803955078</t>
   </si>
   <si>
-    <t xml:space="preserve">42.1922874450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.0457878112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.9481201171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.4109535217285</t>
+    <t xml:space="preserve">42.1922912597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.0457916259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.9481239318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4109573364258</t>
   </si>
   <si>
     <t xml:space="preserve">42.7294616699219</t>
   </si>
   <si>
-    <t xml:space="preserve">45.3664817810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4153175354004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1966514587402</t>
+    <t xml:space="preserve">45.3664779663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4153137207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1966552734375</t>
   </si>
   <si>
     <t xml:space="preserve">47.8569946289062</t>
@@ -2888,7 +2888,7 @@
     <t xml:space="preserve">47.3198280334473</t>
   </si>
   <si>
-    <t xml:space="preserve">47.8081665039062</t>
+    <t xml:space="preserve">47.808162689209</t>
   </si>
   <si>
     <t xml:space="preserve">48.5406684875488</t>
@@ -2897,16 +2897,16 @@
     <t xml:space="preserve">48.5895042419434</t>
   </si>
   <si>
-    <t xml:space="preserve">48.8336715698242</t>
+    <t xml:space="preserve">48.833667755127</t>
   </si>
   <si>
     <t xml:space="preserve">48.1988296508789</t>
   </si>
   <si>
-    <t xml:space="preserve">49.7126770019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.9080123901367</t>
+    <t xml:space="preserve">49.7126808166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.9080085754395</t>
   </si>
   <si>
     <t xml:space="preserve">49.8103446960449</t>
@@ -2924,16 +2924,16 @@
     <t xml:space="preserve">50.2986793518066</t>
   </si>
   <si>
-    <t xml:space="preserve">50.591682434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4940147399902</t>
+    <t xml:space="preserve">50.5916786193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4940185546875</t>
   </si>
   <si>
     <t xml:space="preserve">51.2753524780273</t>
   </si>
   <si>
-    <t xml:space="preserve">50.2010154724121</t>
+    <t xml:space="preserve">50.2010116577148</t>
   </si>
   <si>
     <t xml:space="preserve">50.7870178222656</t>
@@ -2942,16 +2942,16 @@
     <t xml:space="preserve">50.9823532104492</t>
   </si>
   <si>
-    <t xml:space="preserve">51.8613586425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.9590301513672</t>
+    <t xml:space="preserve">51.8613548278809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.9590263366699</t>
   </si>
   <si>
     <t xml:space="preserve">50.8846817016602</t>
   </si>
   <si>
-    <t xml:space="preserve">45.2688064575195</t>
+    <t xml:space="preserve">45.2688140869141</t>
   </si>
   <si>
     <t xml:space="preserve">44.536304473877</t>
@@ -2966,7 +2966,7 @@
     <t xml:space="preserve">44.2921371459961</t>
   </si>
   <si>
-    <t xml:space="preserve">44.9269752502441</t>
+    <t xml:space="preserve">44.9269790649414</t>
   </si>
   <si>
     <t xml:space="preserve">44.0479698181152</t>
@@ -2987,10 +2987,10 @@
     <t xml:space="preserve">41.2156181335449</t>
   </si>
   <si>
-    <t xml:space="preserve">40.9714508056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.7527847290039</t>
+    <t xml:space="preserve">40.9714469909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.7527885437012</t>
   </si>
   <si>
     <t xml:space="preserve">42.2899589538574</t>
@@ -2999,7 +2999,7 @@
     <t xml:space="preserve">43.0712966918945</t>
   </si>
   <si>
-    <t xml:space="preserve">43.2666320800781</t>
+    <t xml:space="preserve">43.2666282653809</t>
   </si>
   <si>
     <t xml:space="preserve">43.7061347961426</t>
@@ -3008,52 +3008,52 @@
     <t xml:space="preserve">44.3409729003906</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4641494750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.0989875793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6594848632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.7571487426758</t>
+    <t xml:space="preserve">45.4641456604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.0989799499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.659481048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.7571449279785</t>
   </si>
   <si>
     <t xml:space="preserve">42.7782936096191</t>
   </si>
   <si>
-    <t xml:space="preserve">41.2644462585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.6806259155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.1201286315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4364585876465</t>
+    <t xml:space="preserve">41.2644538879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.6806297302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.1201324462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4364624023438</t>
   </si>
   <si>
     <t xml:space="preserve">41.508617401123</t>
   </si>
   <si>
-    <t xml:space="preserve">41.0202789306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8715972900391</t>
+    <t xml:space="preserve">41.0202827453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8716011047363</t>
   </si>
   <si>
     <t xml:space="preserve">38.2367630004883</t>
   </si>
   <si>
-    <t xml:space="preserve">39.0669326782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8482704162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5319480895996</t>
+    <t xml:space="preserve">39.0669364929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.848274230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5319442749023</t>
   </si>
   <si>
     <t xml:space="preserve">41.8504524230957</t>
@@ -3062,7 +3062,7 @@
     <t xml:space="preserve">41.1179466247559</t>
   </si>
   <si>
-    <t xml:space="preserve">40.8249435424805</t>
+    <t xml:space="preserve">40.824951171875</t>
   </si>
   <si>
     <t xml:space="preserve">41.6551208496094</t>
@@ -3071,16 +3071,16 @@
     <t xml:space="preserve">41.6062850952148</t>
   </si>
   <si>
-    <t xml:space="preserve">42.485294342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9736289978027</t>
+    <t xml:space="preserve">42.4852905273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.9736328125</t>
   </si>
   <si>
     <t xml:space="preserve">41.8016166687012</t>
   </si>
   <si>
-    <t xml:space="preserve">41.3621139526367</t>
+    <t xml:space="preserve">41.362117767334</t>
   </si>
   <si>
     <t xml:space="preserve">40.2389450073242</t>
@@ -3089,7 +3089,7 @@
     <t xml:space="preserve">40.6296119689941</t>
   </si>
   <si>
-    <t xml:space="preserve">42.8759651184082</t>
+    <t xml:space="preserve">42.8759613037109</t>
   </si>
   <si>
     <t xml:space="preserve">43.4619674682617</t>
@@ -3098,46 +3098,46 @@
     <t xml:space="preserve">43.999137878418</t>
   </si>
   <si>
-    <t xml:space="preserve">40.9226150512695</t>
+    <t xml:space="preserve">40.9226188659668</t>
   </si>
   <si>
     <t xml:space="preserve">39.1157722473145</t>
   </si>
   <si>
-    <t xml:space="preserve">42.5829620361328</t>
+    <t xml:space="preserve">42.5829582214355</t>
   </si>
   <si>
     <t xml:space="preserve">42.6317977905273</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5785980224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4299201965332</t>
+    <t xml:space="preserve">38.5785942077637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4299163818359</t>
   </si>
   <si>
     <t xml:space="preserve">38.6274299621582</t>
   </si>
   <si>
-    <t xml:space="preserve">37.1135902404785</t>
+    <t xml:space="preserve">37.1135864257812</t>
   </si>
   <si>
     <t xml:space="preserve">35.7950820922852</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7207374572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5997428894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.5275917053223</t>
+    <t xml:space="preserve">34.7207336425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5997505187988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.5275840759277</t>
   </si>
   <si>
     <t xml:space="preserve">36.6252555847168</t>
   </si>
   <si>
-    <t xml:space="preserve">36.0880851745605</t>
+    <t xml:space="preserve">36.0880813598633</t>
   </si>
   <si>
     <t xml:space="preserve">36.1369171142578</t>
@@ -3146,37 +3146,37 @@
     <t xml:space="preserve">35.4532432556152</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5254020690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3810882568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3555793762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9394035339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1325531005859</t>
+    <t xml:space="preserve">34.5254058837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3810844421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3555755615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9393997192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1325569152832</t>
   </si>
   <si>
     <t xml:space="preserve">31.4977169036865</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6442184448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0115661621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3767242431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4510688781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7695732116699</t>
+    <t xml:space="preserve">31.6442203521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0115585327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3767280578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4510612487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7695693969727</t>
   </si>
   <si>
     <t xml:space="preserve">34.5742416381836</t>
@@ -3191,22 +3191,22 @@
     <t xml:space="preserve">31.4000511169434</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5975685119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9627304077148</t>
+    <t xml:space="preserve">33.5975646972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9627265930176</t>
   </si>
   <si>
     <t xml:space="preserve">32.5232238769531</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4255561828613</t>
+    <t xml:space="preserve">32.4255599975586</t>
   </si>
   <si>
     <t xml:space="preserve">32.6208915710449</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4488830566406</t>
+    <t xml:space="preserve">31.4488849639893</t>
   </si>
   <si>
     <t xml:space="preserve">32.6697235107422</t>
@@ -3215,16 +3215,16 @@
     <t xml:space="preserve">32.767391204834</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2144813537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0191459655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9019451141357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6518058776855</t>
+    <t xml:space="preserve">31.2144832611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0191478729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9019470214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6518039703369</t>
   </si>
   <si>
     <t xml:space="preserve">30.4722099304199</t>
@@ -3233,7 +3233,7 @@
     <t xml:space="preserve">32.2302207946777</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0739555358887</t>
+    <t xml:space="preserve">32.0739593505859</t>
   </si>
   <si>
     <t xml:space="preserve">31.937219619751</t>
@@ -3242,7 +3242,7 @@
     <t xml:space="preserve">31.3316841125488</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1716156005859</t>
+    <t xml:space="preserve">32.1716194152832</t>
   </si>
   <si>
     <t xml:space="preserve">31.3902816772461</t>
@@ -3251,7 +3251,7 @@
     <t xml:space="preserve">31.6637496948242</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8862075805664</t>
+    <t xml:space="preserve">29.8862056732178</t>
   </si>
   <si>
     <t xml:space="preserve">29.9643402099609</t>
@@ -3260,7 +3260,7 @@
     <t xml:space="preserve">28.3821277618408</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4993286132812</t>
+    <t xml:space="preserve">28.4993305206299</t>
   </si>
   <si>
     <t xml:space="preserve">29.2025337219238</t>
@@ -3269,10 +3269,10 @@
     <t xml:space="preserve">28.8704643249512</t>
   </si>
   <si>
-    <t xml:space="preserve">28.929069519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0853328704834</t>
+    <t xml:space="preserve">28.9290676116943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.085334777832</t>
   </si>
   <si>
     <t xml:space="preserve">28.3039951324463</t>
@@ -3281,7 +3281,7 @@
     <t xml:space="preserve">28.4211959838867</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0147876739502</t>
+    <t xml:space="preserve">27.0147857666016</t>
   </si>
   <si>
     <t xml:space="preserve">28.3235282897949</t>
@@ -3290,13 +3290,13 @@
     <t xml:space="preserve">28.5969982147217</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2258605957031</t>
+    <t xml:space="preserve">28.2258625030518</t>
   </si>
   <si>
     <t xml:space="preserve">28.5579299926758</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1816444396973</t>
+    <t xml:space="preserve">28.1816463470459</t>
   </si>
   <si>
     <t xml:space="preserve">26.8943614959717</t>
@@ -3308,7 +3308,7 @@
     <t xml:space="preserve">26.6765117645264</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8745536804199</t>
+    <t xml:space="preserve">26.8745555877686</t>
   </si>
   <si>
     <t xml:space="preserve">27.5280990600586</t>
@@ -3317,16 +3317,16 @@
     <t xml:space="preserve">26.4784679412842</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7359275817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2508392333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0628185272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3994960784912</t>
+    <t xml:space="preserve">26.7359256744385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2508411407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0628204345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3994941711426</t>
   </si>
   <si>
     <t xml:space="preserve">28.320276260376</t>
@@ -3338,7 +3338,7 @@
     <t xml:space="preserve">27.9439926147461</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4192981719971</t>
+    <t xml:space="preserve">28.4193000793457</t>
   </si>
   <si>
     <t xml:space="preserve">29.013427734375</t>
@@ -3368,13 +3368,13 @@
     <t xml:space="preserve">24.4584217071533</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4288368225098</t>
+    <t xml:space="preserve">25.4288349151611</t>
   </si>
   <si>
     <t xml:space="preserve">25.6070766448975</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4684429168701</t>
+    <t xml:space="preserve">25.4684448242188</t>
   </si>
   <si>
     <t xml:space="preserve">24.8148994445801</t>
@@ -3386,16 +3386,16 @@
     <t xml:space="preserve">25.3694229125977</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5376377105713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8840923309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2405700683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8444862365723</t>
+    <t xml:space="preserve">24.5376396179199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8840942382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.240571975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8444843292236</t>
   </si>
   <si>
     <t xml:space="preserve">23.0523090362549</t>
@@ -3404,28 +3404,28 @@
     <t xml:space="preserve">23.547420501709</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2009658813477</t>
+    <t xml:space="preserve">24.200963973999</t>
   </si>
   <si>
     <t xml:space="preserve">23.6068325042725</t>
   </si>
   <si>
-    <t xml:space="preserve">23.190938949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9136791229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4185695648193</t>
+    <t xml:space="preserve">23.1909408569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9136772155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4185676574707</t>
   </si>
   <si>
     <t xml:space="preserve">21.5669803619385</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8146572113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9532871246338</t>
+    <t xml:space="preserve">22.8146591186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9532890319824</t>
   </si>
   <si>
     <t xml:space="preserve">24.4188117980957</t>
@@ -3434,7 +3434,7 @@
     <t xml:space="preserve">23.7058544158936</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7356796264648</t>
+    <t xml:space="preserve">24.7356815338135</t>
   </si>
   <si>
     <t xml:space="preserve">24.597053527832</t>
@@ -3446,7 +3446,7 @@
     <t xml:space="preserve">25.9239444732666</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8249225616455</t>
+    <t xml:space="preserve">25.8249244689941</t>
   </si>
   <si>
     <t xml:space="preserve">26.0823802947998</t>
@@ -3458,19 +3458,19 @@
     <t xml:space="preserve">25.3892269134521</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1317691802979</t>
+    <t xml:space="preserve">25.1317672729492</t>
   </si>
   <si>
     <t xml:space="preserve">25.5674648284912</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0427703857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1417961120605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8843364715576</t>
+    <t xml:space="preserve">26.0427722930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1417942047119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.884334564209</t>
   </si>
   <si>
     <t xml:space="preserve">25.4882469177246</t>
@@ -3482,25 +3482,25 @@
     <t xml:space="preserve">24.0227241516113</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2207679748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1217460632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6860485076904</t>
+    <t xml:space="preserve">24.2207660675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1217479705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6860504150391</t>
   </si>
   <si>
     <t xml:space="preserve">24.3197898864746</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2603759765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3593978881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6266384124756</t>
+    <t xml:space="preserve">24.2603778839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3593997955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.626636505127</t>
   </si>
   <si>
     <t xml:space="preserve">24.4980297088623</t>
@@ -3518,7 +3518,7 @@
     <t xml:space="preserve">24.8743133544922</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9535331726074</t>
+    <t xml:space="preserve">24.9535312652588</t>
   </si>
   <si>
     <t xml:space="preserve">24.2999877929688</t>
@@ -3530,7 +3530,7 @@
     <t xml:space="preserve">22.8344593048096</t>
   </si>
   <si>
-    <t xml:space="preserve">22.557201385498</t>
+    <t xml:space="preserve">22.5571994781494</t>
   </si>
   <si>
     <t xml:space="preserve">22.7156352996826</t>
@@ -3554,10 +3554,10 @@
     <t xml:space="preserve">19.2696704864502</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8836059570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2400856018066</t>
+    <t xml:space="preserve">19.8836078643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2400875091553</t>
   </si>
   <si>
     <t xml:space="preserve">21.4481525421143</t>
@@ -3569,7 +3569,7 @@
     <t xml:space="preserve">21.2501087188721</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2897167205811</t>
+    <t xml:space="preserve">21.2897186279297</t>
   </si>
   <si>
     <t xml:space="preserve">21.586784362793</t>
@@ -3578,7 +3578,7 @@
     <t xml:space="preserve">20.8540210723877</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3887386322021</t>
+    <t xml:space="preserve">21.3887405395508</t>
   </si>
   <si>
     <t xml:space="preserve">21.6065902709961</t>
@@ -3590,7 +3590,7 @@
     <t xml:space="preserve">22.2007217407227</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6660003662109</t>
+    <t xml:space="preserve">21.6660022735596</t>
   </si>
   <si>
     <t xml:space="preserve">21.5075664520264</t>
@@ -3605,13 +3605,13 @@
     <t xml:space="preserve">22.1809158325195</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4383735656738</t>
+    <t xml:space="preserve">22.4383716583252</t>
   </si>
   <si>
     <t xml:space="preserve">21.7848281860352</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0620918273926</t>
+    <t xml:space="preserve">22.0620899200439</t>
   </si>
   <si>
     <t xml:space="preserve">23.0721130371094</t>
@@ -3647,31 +3647,31 @@
     <t xml:space="preserve">25.2505970001221</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2012062072754</t>
+    <t xml:space="preserve">26.201208114624</t>
   </si>
   <si>
     <t xml:space="preserve">26.4190540313721</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6963157653809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.716121673584</t>
+    <t xml:space="preserve">26.6963176727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7161197662354</t>
   </si>
   <si>
     <t xml:space="preserve">24.7554874420166</t>
   </si>
   <si>
-    <t xml:space="preserve">24.715877532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9733333587646</t>
+    <t xml:space="preserve">24.7158756256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9733352661133</t>
   </si>
   <si>
     <t xml:space="preserve">23.8246803283691</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9730911254883</t>
+    <t xml:space="preserve">22.9730930328369</t>
   </si>
   <si>
     <t xml:space="preserve">24.7950973510742</t>
@@ -3683,10 +3683,10 @@
     <t xml:space="preserve">26.1219882965088</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0625762939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7853164672852</t>
+    <t xml:space="preserve">26.0625743865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7853145599365</t>
   </si>
   <si>
     <t xml:space="preserve">26.2606220245361</t>
@@ -3695,46 +3695,46 @@
     <t xml:space="preserve">27.0725994110107</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7953395843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0232105255127</t>
+    <t xml:space="preserve">26.795337677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0232086181641</t>
   </si>
   <si>
     <t xml:space="preserve">27.5875148773193</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4884929656982</t>
+    <t xml:space="preserve">27.4884948730469</t>
   </si>
   <si>
     <t xml:space="preserve">28.6965599060059</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7757759094238</t>
+    <t xml:space="preserve">28.7757778167725</t>
   </si>
   <si>
     <t xml:space="preserve">28.2212543487549</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5777339935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.280668258667</t>
+    <t xml:space="preserve">28.5777320861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2806701660156</t>
   </si>
   <si>
     <t xml:space="preserve">28.8153858184814</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8747997283936</t>
+    <t xml:space="preserve">28.8747978210449</t>
   </si>
   <si>
     <t xml:space="preserve">28.7163639068604</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6569499969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9540176391602</t>
+    <t xml:space="preserve">28.6569519042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9540157318115</t>
   </si>
   <si>
     <t xml:space="preserve">28.8549957275391</t>
@@ -3791,16 +3791,16 @@
     <t xml:space="preserve">28.0430164337158</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6469287872314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7063388824463</t>
+    <t xml:space="preserve">27.6469268798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7063407897949</t>
   </si>
   <si>
     <t xml:space="preserve">27.0131874084473</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7755336761475</t>
+    <t xml:space="preserve">26.7755355834961</t>
   </si>
   <si>
     <t xml:space="preserve">25.6664886474609</t>
@@ -3809,22 +3809,22 @@
     <t xml:space="preserve">24.4782257080078</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3097667694092</t>
+    <t xml:space="preserve">23.3097686767578</t>
   </si>
   <si>
     <t xml:space="preserve">22.3789596557617</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2801818847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5574436187744</t>
+    <t xml:space="preserve">24.280179977417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5574417114258</t>
   </si>
   <si>
     <t xml:space="preserve">24.8347034454346</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0921611785889</t>
+    <t xml:space="preserve">25.0921630859375</t>
   </si>
   <si>
     <t xml:space="preserve">25.8447284698486</t>
@@ -3842,7 +3842,7 @@
     <t xml:space="preserve">27.2805442810059</t>
   </si>
   <si>
-    <t xml:space="preserve">27.478588104248</t>
+    <t xml:space="preserve">27.4785900115967</t>
   </si>
   <si>
     <t xml:space="preserve">28.0727214813232</t>
@@ -3869,7 +3869,7 @@
     <t xml:space="preserve">26.8844585418701</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7261447906494</t>
+    <t xml:space="preserve">27.7261428833008</t>
   </si>
   <si>
     <t xml:space="preserve">26.9834804534912</t>
@@ -3878,10 +3878,10 @@
     <t xml:space="preserve">27.330057144165</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6271209716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9241905212402</t>
+    <t xml:space="preserve">27.6271228790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9241886138916</t>
   </si>
   <si>
     <t xml:space="preserve">28.4688091278076</t>
@@ -3893,19 +3893,19 @@
     <t xml:space="preserve">30.5482711791992</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3007164001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9443588256836</t>
+    <t xml:space="preserve">30.3007144927979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.944356918335</t>
   </si>
   <si>
     <t xml:space="preserve">32.0831108093262</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6375122070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1821327209473</t>
+    <t xml:space="preserve">31.6375141143799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1821365356445</t>
   </si>
   <si>
     <t xml:space="preserve">32.9247970581055</t>
@@ -3929,10 +3929,10 @@
     <t xml:space="preserve">30.7958240509033</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6472930908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2016925811768</t>
+    <t xml:space="preserve">30.6472949981689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2016944885254</t>
   </si>
   <si>
     <t xml:space="preserve">30.3997383117676</t>
@@ -5097,6 +5097,9 @@
   </si>
   <si>
     <t xml:space="preserve">47.0499992370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4500007629395</t>
   </si>
 </sst>
 </file>
@@ -9171,7 +9174,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G144" t="s">
-        <v>120</v>
+        <v>45</v>
       </c>
       <c r="H144" t="s">
         <v>9</v>
@@ -9197,7 +9200,7 @@
         <v>7.47499990463257</v>
       </c>
       <c r="G145" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H145" t="s">
         <v>9</v>
@@ -9223,7 +9226,7 @@
         <v>7.2649998664856</v>
       </c>
       <c r="G146" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H146" t="s">
         <v>9</v>
@@ -9275,7 +9278,7 @@
         <v>7.5</v>
       </c>
       <c r="G148" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H148" t="s">
         <v>9</v>
@@ -9301,7 +9304,7 @@
         <v>7.5</v>
       </c>
       <c r="G149" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H149" t="s">
         <v>9</v>
@@ -9327,7 +9330,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G150" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H150" t="s">
         <v>9</v>
@@ -9353,7 +9356,7 @@
         <v>7.2649998664856</v>
       </c>
       <c r="G151" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H151" t="s">
         <v>9</v>
@@ -9379,7 +9382,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G152" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H152" t="s">
         <v>9</v>
@@ -9405,7 +9408,7 @@
         <v>7.2350001335144</v>
       </c>
       <c r="G153" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H153" t="s">
         <v>9</v>
@@ -9431,7 +9434,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G154" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H154" t="s">
         <v>9</v>
@@ -9457,7 +9460,7 @@
         <v>7.5</v>
       </c>
       <c r="G155" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H155" t="s">
         <v>9</v>
@@ -9535,7 +9538,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G158" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H158" t="s">
         <v>9</v>
@@ -9561,7 +9564,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G159" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H159" t="s">
         <v>9</v>
@@ -9587,7 +9590,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G160" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H160" t="s">
         <v>9</v>
@@ -9613,7 +9616,7 @@
         <v>7.41499996185303</v>
       </c>
       <c r="G161" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H161" t="s">
         <v>9</v>
@@ -9665,7 +9668,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G163" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H163" t="s">
         <v>9</v>
@@ -9691,7 +9694,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G164" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H164" t="s">
         <v>9</v>
@@ -9743,7 +9746,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G166" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H166" t="s">
         <v>9</v>
@@ -9769,7 +9772,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G167" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H167" t="s">
         <v>9</v>
@@ -9795,7 +9798,7 @@
         <v>7.54500007629395</v>
       </c>
       <c r="G168" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H168" t="s">
         <v>9</v>
@@ -9821,7 +9824,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G169" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H169" t="s">
         <v>9</v>
@@ -9847,7 +9850,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G170" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H170" t="s">
         <v>9</v>
@@ -9873,7 +9876,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G171" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H171" t="s">
         <v>9</v>
@@ -9899,7 +9902,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G172" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H172" t="s">
         <v>9</v>
@@ -9925,7 +9928,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G173" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H173" t="s">
         <v>9</v>
@@ -9951,7 +9954,7 @@
         <v>7.72499990463257</v>
       </c>
       <c r="G174" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H174" t="s">
         <v>9</v>
@@ -10003,7 +10006,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G176" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H176" t="s">
         <v>9</v>
@@ -10185,7 +10188,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G183" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H183" t="s">
         <v>9</v>
@@ -10211,7 +10214,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G184" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H184" t="s">
         <v>9</v>
@@ -10237,7 +10240,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G185" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H185" t="s">
         <v>9</v>
@@ -10263,7 +10266,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G186" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H186" t="s">
         <v>9</v>
@@ -10315,7 +10318,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G188" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H188" t="s">
         <v>9</v>
@@ -10341,7 +10344,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G189" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H189" t="s">
         <v>9</v>
@@ -10393,7 +10396,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G191" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H191" t="s">
         <v>9</v>
@@ -10445,7 +10448,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G193" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H193" t="s">
         <v>9</v>
@@ -10471,7 +10474,7 @@
         <v>7.5</v>
       </c>
       <c r="G194" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H194" t="s">
         <v>9</v>
@@ -10497,7 +10500,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G195" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H195" t="s">
         <v>9</v>
@@ -10523,7 +10526,7 @@
         <v>7.67000007629395</v>
       </c>
       <c r="G196" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H196" t="s">
         <v>9</v>
@@ -10549,7 +10552,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G197" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H197" t="s">
         <v>9</v>
@@ -10575,7 +10578,7 @@
         <v>7.7350001335144</v>
       </c>
       <c r="G198" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H198" t="s">
         <v>9</v>
@@ -10601,7 +10604,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G199" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H199" t="s">
         <v>9</v>
@@ -10653,7 +10656,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G201" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H201" t="s">
         <v>9</v>
@@ -10679,7 +10682,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G202" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H202" t="s">
         <v>9</v>
@@ -10705,7 +10708,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G203" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H203" t="s">
         <v>9</v>
@@ -10757,7 +10760,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G205" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H205" t="s">
         <v>9</v>
@@ -10783,7 +10786,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G206" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H206" t="s">
         <v>9</v>
@@ -10809,7 +10812,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G207" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H207" t="s">
         <v>9</v>
@@ -10835,7 +10838,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G208" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H208" t="s">
         <v>9</v>
@@ -10861,7 +10864,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G209" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -10887,7 +10890,7 @@
         <v>7.81500005722046</v>
       </c>
       <c r="G210" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H210" t="s">
         <v>9</v>
@@ -10913,7 +10916,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G211" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H211" t="s">
         <v>9</v>
@@ -10939,7 +10942,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G212" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H212" t="s">
         <v>9</v>
@@ -11017,7 +11020,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G215" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -11043,7 +11046,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G216" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -11069,7 +11072,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G217" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -11121,7 +11124,7 @@
         <v>7.95499992370605</v>
       </c>
       <c r="G219" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -11173,7 +11176,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G221" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -11199,7 +11202,7 @@
         <v>8.15499973297119</v>
       </c>
       <c r="G222" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -11251,7 +11254,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G224" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -11277,7 +11280,7 @@
         <v>7.61499977111816</v>
       </c>
       <c r="G225" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -11303,7 +11306,7 @@
         <v>7.5</v>
       </c>
       <c r="G226" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -11329,7 +11332,7 @@
         <v>7.78499984741211</v>
       </c>
       <c r="G227" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -11355,7 +11358,7 @@
         <v>7.94500017166138</v>
       </c>
       <c r="G228" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -11381,7 +11384,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G229" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -11407,7 +11410,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G230" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -11563,7 +11566,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G236" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -11589,7 +11592,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G237" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -11641,7 +11644,7 @@
         <v>7.94500017166138</v>
       </c>
       <c r="G239" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H239" t="s">
         <v>9</v>
@@ -11693,7 +11696,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G241" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H241" t="s">
         <v>9</v>
@@ -11719,7 +11722,7 @@
         <v>8.27499961853027</v>
       </c>
       <c r="G242" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H242" t="s">
         <v>9</v>
@@ -11745,7 +11748,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G243" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -11797,7 +11800,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G245" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H245" t="s">
         <v>9</v>
@@ -11823,7 +11826,7 @@
         <v>7.94500017166138</v>
       </c>
       <c r="G246" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -11849,7 +11852,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G247" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H247" t="s">
         <v>9</v>
@@ -11875,7 +11878,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G248" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -11901,7 +11904,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G249" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H249" t="s">
         <v>9</v>
@@ -11927,7 +11930,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G250" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -11953,7 +11956,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G251" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -11979,7 +11982,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G252" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H252" t="s">
         <v>9</v>
@@ -12005,7 +12008,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G253" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H253" t="s">
         <v>9</v>
@@ -12031,7 +12034,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G254" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -12057,7 +12060,7 @@
         <v>8.5</v>
       </c>
       <c r="G255" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -12083,7 +12086,7 @@
         <v>8.49499988555908</v>
       </c>
       <c r="G256" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H256" t="s">
         <v>9</v>
@@ -12109,7 +12112,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G257" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -12135,7 +12138,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G258" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -12161,7 +12164,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G259" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -12187,7 +12190,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G260" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -12213,7 +12216,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G261" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -12239,7 +12242,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G262" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -12265,7 +12268,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G263" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -12291,7 +12294,7 @@
         <v>9.27000045776367</v>
       </c>
       <c r="G264" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -12317,7 +12320,7 @@
         <v>9.30500030517578</v>
       </c>
       <c r="G265" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -12343,7 +12346,7 @@
         <v>9.25</v>
       </c>
       <c r="G266" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -12369,7 +12372,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G267" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -12395,7 +12398,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G268" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -12421,7 +12424,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G269" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -12447,7 +12450,7 @@
         <v>9.22500038146973</v>
       </c>
       <c r="G270" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -12473,7 +12476,7 @@
         <v>9.25</v>
       </c>
       <c r="G271" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -12499,7 +12502,7 @@
         <v>9.21500015258789</v>
       </c>
       <c r="G272" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -12525,7 +12528,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G273" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -12551,7 +12554,7 @@
         <v>9.25500011444092</v>
       </c>
       <c r="G274" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -12577,7 +12580,7 @@
         <v>9.26500034332275</v>
       </c>
       <c r="G275" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H275" t="s">
         <v>9</v>
@@ -12603,7 +12606,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G276" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -12629,7 +12632,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G277" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -12655,7 +12658,7 @@
         <v>9.1850004196167</v>
       </c>
       <c r="G278" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -12681,7 +12684,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G279" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -12707,7 +12710,7 @@
         <v>9.22500038146973</v>
       </c>
       <c r="G280" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -12733,7 +12736,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G281" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -12759,7 +12762,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G282" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -12785,7 +12788,7 @@
         <v>9.25</v>
       </c>
       <c r="G283" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -12811,7 +12814,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G284" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -12837,7 +12840,7 @@
         <v>8.9350004196167</v>
       </c>
       <c r="G285" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -12863,7 +12866,7 @@
         <v>8.97500038146973</v>
       </c>
       <c r="G286" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -12889,7 +12892,7 @@
         <v>9.16499996185303</v>
       </c>
       <c r="G287" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -12915,7 +12918,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G288" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -12941,7 +12944,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G289" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -12967,7 +12970,7 @@
         <v>9.38500022888184</v>
       </c>
       <c r="G290" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -12993,7 +12996,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G291" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -13019,7 +13022,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G292" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -13045,7 +13048,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G293" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -13071,7 +13074,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G294" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -13097,7 +13100,7 @@
         <v>9.10499954223633</v>
       </c>
       <c r="G295" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -13123,7 +13126,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G296" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -13149,7 +13152,7 @@
         <v>8.88500022888184</v>
       </c>
       <c r="G297" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -13175,7 +13178,7 @@
         <v>9</v>
       </c>
       <c r="G298" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -13201,7 +13204,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G299" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -13227,7 +13230,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G300" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -13253,7 +13256,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G301" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -13279,7 +13282,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G302" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -13305,7 +13308,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G303" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -13331,7 +13334,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G304" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -13357,7 +13360,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G305" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -13383,7 +13386,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G306" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -13409,7 +13412,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G307" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -13435,7 +13438,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G308" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -13461,7 +13464,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G309" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -13487,7 +13490,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G310" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -13513,7 +13516,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G311" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -13539,7 +13542,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G312" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -13565,7 +13568,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G313" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -13591,7 +13594,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G314" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -13617,7 +13620,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G315" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -13643,7 +13646,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G316" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -13669,7 +13672,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G317" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -13695,7 +13698,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G318" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -13721,7 +13724,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G319" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -13747,7 +13750,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G320" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -13773,7 +13776,7 @@
         <v>10</v>
       </c>
       <c r="G321" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -13799,7 +13802,7 @@
         <v>10</v>
       </c>
       <c r="G322" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -13825,7 +13828,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G323" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -13851,7 +13854,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G324" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -13877,7 +13880,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G325" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -13903,7 +13906,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G326" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -13929,7 +13932,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G327" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -13955,7 +13958,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G328" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -13981,7 +13984,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G329" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -14007,7 +14010,7 @@
         <v>10.5699996948242</v>
       </c>
       <c r="G330" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -14033,7 +14036,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G331" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -14059,7 +14062,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G332" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -14085,7 +14088,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G333" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -14111,7 +14114,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G334" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -14137,7 +14140,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G335" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -14163,7 +14166,7 @@
         <v>11</v>
       </c>
       <c r="G336" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -14189,7 +14192,7 @@
         <v>11.5600004196167</v>
       </c>
       <c r="G337" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
@@ -14215,7 +14218,7 @@
         <v>12</v>
       </c>
       <c r="G338" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -14241,7 +14244,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G339" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -14267,7 +14270,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G340" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -14293,7 +14296,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G341" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -14319,7 +14322,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G342" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -14345,7 +14348,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G343" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -14371,7 +14374,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G344" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -14397,7 +14400,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G345" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -14423,7 +14426,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G346" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -14449,7 +14452,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G347" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -14475,7 +14478,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G348" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -14501,7 +14504,7 @@
         <v>11.25</v>
       </c>
       <c r="G349" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -14527,7 +14530,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G350" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -14553,7 +14556,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G351" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -14579,7 +14582,7 @@
         <v>11.0900001525879</v>
       </c>
       <c r="G352" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -14605,7 +14608,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G353" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -14631,7 +14634,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G354" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -14657,7 +14660,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G355" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -14683,7 +14686,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G356" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -14709,7 +14712,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G357" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -14735,7 +14738,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G358" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -14761,7 +14764,7 @@
         <v>11.25</v>
       </c>
       <c r="G359" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -14787,7 +14790,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G360" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -14813,7 +14816,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G361" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -14839,7 +14842,7 @@
         <v>11.3699998855591</v>
       </c>
       <c r="G362" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -14865,7 +14868,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G363" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -14891,7 +14894,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G364" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -14917,7 +14920,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G365" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -14943,7 +14946,7 @@
         <v>12.5</v>
       </c>
       <c r="G366" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -14969,7 +14972,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G367" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -14995,7 +14998,7 @@
         <v>12.1899995803833</v>
       </c>
       <c r="G368" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -15021,7 +15024,7 @@
         <v>11.9700002670288</v>
       </c>
       <c r="G369" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -15047,7 +15050,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G370" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -15073,7 +15076,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G371" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -15099,7 +15102,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G372" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -15125,7 +15128,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G373" t="s">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -17465,7 +17468,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G463" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -17517,7 +17520,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G465" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -17751,7 +17754,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G474" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -18063,7 +18066,7 @@
         <v>12.5</v>
       </c>
       <c r="G486" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -19831,7 +19834,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G554" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -70461,7 +70464,7 @@
     </row>
     <row r="2502">
       <c r="A2502" s="1" t="n">
-        <v>45961.691087963</v>
+        <v>45961.3333333333</v>
       </c>
       <c r="B2502" t="n">
         <v>20558</v>
@@ -70482,6 +70485,32 @@
         <v>1694</v>
       </c>
       <c r="H2502" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2503">
+      <c r="A2503" s="1" t="n">
+        <v>45964.6911226852</v>
+      </c>
+      <c r="B2503" t="n">
+        <v>18906</v>
+      </c>
+      <c r="C2503" t="n">
+        <v>47.4000015258789</v>
+      </c>
+      <c r="D2503" t="n">
+        <v>46.2999992370605</v>
+      </c>
+      <c r="E2503" t="n">
+        <v>47</v>
+      </c>
+      <c r="F2503" t="n">
+        <v>46.4500007629395</v>
+      </c>
+      <c r="G2503" t="s">
+        <v>1695</v>
+      </c>
+      <c r="H2503" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MOL.MI.xlsx
+++ b/data/MOL.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1700" uniqueCount="1700">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1701" uniqueCount="1701">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,25 +38,25 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85066175460815</t>
+    <t xml:space="preserve">6.850661277771</t>
   </si>
   <si>
     <t xml:space="preserve">MOL.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75772619247437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66036510467529</t>
+    <t xml:space="preserve">6.75772714614868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66036558151245</t>
   </si>
   <si>
     <t xml:space="preserve">6.77100276947021</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63823843002319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72674751281738</t>
+    <t xml:space="preserve">6.63823795318604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72674798965454</t>
   </si>
   <si>
     <t xml:space="preserve">6.81525754928589</t>
@@ -65,106 +65,106 @@
     <t xml:space="preserve">6.54972791671753</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31960201263428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09832859039307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35058069229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23994302749634</t>
+    <t xml:space="preserve">6.31960248947144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09832906723022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35058116912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2399435043335</t>
   </si>
   <si>
     <t xml:space="preserve">6.5585789680481</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46121835708618</t>
+    <t xml:space="preserve">6.46121883392334</t>
   </si>
   <si>
     <t xml:space="preserve">5.8947548866272</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52317571640015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65594005584717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76215124130249</t>
+    <t xml:space="preserve">6.52317476272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65594053268433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76215171813965</t>
   </si>
   <si>
     <t xml:space="preserve">6.66479110717773</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69134378433228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68249320983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01866912841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89918088912964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28419923782349</t>
+    <t xml:space="preserve">6.69134330749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68249225616455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01866865158081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8991813659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28419828414917</t>
   </si>
   <si>
     <t xml:space="preserve">6.06292486190796</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2532205581665</t>
+    <t xml:space="preserve">6.25321960449219</t>
   </si>
   <si>
     <t xml:space="preserve">6.39926147460938</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34173011779785</t>
+    <t xml:space="preserve">6.34172964096069</t>
   </si>
   <si>
     <t xml:space="preserve">6.50989866256714</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33287954330444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42581462860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39041042327881</t>
+    <t xml:space="preserve">6.3328800201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42581415176392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39041137695312</t>
   </si>
   <si>
     <t xml:space="preserve">6.30632591247559</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40811204910278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35500574111938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63381195068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43466472625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22666645050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24436855316162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27534770965576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26649713516235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62938594818115</t>
+    <t xml:space="preserve">6.40811157226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3550066947937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63381242752075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43466520309448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2266674041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24436950683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27534818649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2664966583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62938737869263</t>
   </si>
   <si>
     <t xml:space="preserve">6.43909072875977</t>
@@ -173,22 +173,22 @@
     <t xml:space="preserve">6.41253805160522</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45236778259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45679330825806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36828374862671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19568872451782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06735038757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28862380981445</t>
+    <t xml:space="preserve">6.45236682891846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4567928314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36828231811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19568824768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06734943389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28862428665161</t>
   </si>
   <si>
     <t xml:space="preserve">6.20453977584839</t>
@@ -197,10 +197,10 @@
     <t xml:space="preserve">6.29304981231689</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2487940788269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22224187850952</t>
+    <t xml:space="preserve">6.24879455566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22224140167236</t>
   </si>
   <si>
     <t xml:space="preserve">6.25764608383179</t>
@@ -215,10 +215,10 @@
     <t xml:space="preserve">6.58955812454224</t>
   </si>
   <si>
-    <t xml:space="preserve">6.478919506073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49662256240845</t>
+    <t xml:space="preserve">6.47892093658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49662208557129</t>
   </si>
   <si>
     <t xml:space="preserve">6.42138862609863</t>
@@ -227,40 +227,40 @@
     <t xml:space="preserve">6.63348960876465</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45273971557617</t>
+    <t xml:space="preserve">6.45274066925049</t>
   </si>
   <si>
     <t xml:space="preserve">6.54311466217041</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44370365142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50696468353271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55667114257812</t>
+    <t xml:space="preserve">6.44370269775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50696516036987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55667161941528</t>
   </si>
   <si>
     <t xml:space="preserve">6.36688470840454</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61993312835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69223260879517</t>
+    <t xml:space="preserve">6.61993360519409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69223308563232</t>
   </si>
   <si>
     <t xml:space="preserve">6.59733963012695</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68319511413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70578956604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75097513198853</t>
+    <t xml:space="preserve">6.6831955909729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70578908920288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7509765625</t>
   </si>
   <si>
     <t xml:space="preserve">6.8503885269165</t>
@@ -269,43 +269,43 @@
     <t xml:space="preserve">6.94528150558472</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98594951629639</t>
+    <t xml:space="preserve">6.9859504699707</t>
   </si>
   <si>
     <t xml:space="preserve">7.1034369468689</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25255441665649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32033634185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45589780807495</t>
+    <t xml:space="preserve">7.25255393981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32033586502075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45589733123779</t>
   </si>
   <si>
     <t xml:space="preserve">7.3022608757019</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37907886505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25707340240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22996091842651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22544288635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19832992553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09439945220947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13958644866943</t>
+    <t xml:space="preserve">7.37907838821411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25707292556763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22996044158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22544145584106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19832944869995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09439897537231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13958597183228</t>
   </si>
   <si>
     <t xml:space="preserve">7.00402498245239</t>
@@ -314,16 +314,16 @@
     <t xml:space="preserve">7.08084297180176</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95883750915527</t>
+    <t xml:space="preserve">6.95883798599243</t>
   </si>
   <si>
     <t xml:space="preserve">6.84135103225708</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11699342727661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16669940948486</t>
+    <t xml:space="preserve">7.11699247360229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16669797897339</t>
   </si>
   <si>
     <t xml:space="preserve">7.31129837036133</t>
@@ -338,43 +338,40 @@
     <t xml:space="preserve">6.73290109634399</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08988094329834</t>
+    <t xml:space="preserve">7.08987998962402</t>
   </si>
   <si>
     <t xml:space="preserve">7.18477392196655</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85942602157593</t>
+    <t xml:space="preserve">6.85942554473877</t>
   </si>
   <si>
     <t xml:space="preserve">6.67867660522461</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49792766571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57022666931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57926511764526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41659116744995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74645757675171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6515645980835</t>
+    <t xml:space="preserve">6.49792718887329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57022714614868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57926464080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41658973693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74645805358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65156412124634</t>
   </si>
   <si>
     <t xml:space="preserve">6.55215263366699</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46177816390991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43466520309448</t>
+    <t xml:space="preserve">6.46177768707275</t>
   </si>
   <si>
     <t xml:space="preserve">6.75549459457397</t>
@@ -383,10 +380,10 @@
     <t xml:space="preserve">6.56570816040039</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77808809280396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71030807495117</t>
+    <t xml:space="preserve">6.77808856964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71030855178833</t>
   </si>
   <si>
     <t xml:space="preserve">6.48888969421387</t>
@@ -395,13 +392,13 @@
     <t xml:space="preserve">6.53859615325928</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66060161590576</t>
+    <t xml:space="preserve">6.66060209274292</t>
   </si>
   <si>
     <t xml:space="preserve">6.68771409988403</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76001405715942</t>
+    <t xml:space="preserve">6.76001358032227</t>
   </si>
   <si>
     <t xml:space="preserve">6.87750053405762</t>
@@ -410,34 +407,34 @@
     <t xml:space="preserve">6.70127010345459</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7871265411377</t>
+    <t xml:space="preserve">6.78712606430054</t>
   </si>
   <si>
     <t xml:space="preserve">6.79616355895996</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81423902511597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8187575340271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82327651977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80520057678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92268705368042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90461254119873</t>
+    <t xml:space="preserve">6.81423854827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81875705718994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82327604293823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80520153045654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92268753051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90461349487305</t>
   </si>
   <si>
     <t xml:space="preserve">6.86846256256104</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98143196105957</t>
+    <t xml:space="preserve">6.98143100738525</t>
   </si>
   <si>
     <t xml:space="preserve">7.17573642730713</t>
@@ -449,34 +446,34 @@
     <t xml:space="preserve">6.97691202163696</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64252614974976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6967511177063</t>
+    <t xml:space="preserve">6.64252662658691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69675064086914</t>
   </si>
   <si>
     <t xml:space="preserve">6.88653755187988</t>
   </si>
   <si>
-    <t xml:space="preserve">6.931725025177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0221004486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99046897888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19381093978882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05824947357178</t>
+    <t xml:space="preserve">6.93172597885132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02210092544556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99046945571899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19381141662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05824851989746</t>
   </si>
   <si>
     <t xml:space="preserve">7.04921245574951</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06728744506836</t>
+    <t xml:space="preserve">7.06728649139404</t>
   </si>
   <si>
     <t xml:space="preserve">7.1486234664917</t>
@@ -485,22 +482,22 @@
     <t xml:space="preserve">7.08536243438721</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06276893615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15766143798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21188592910767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3835973739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22092390060425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24803733825684</t>
+    <t xml:space="preserve">7.06276845932007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15766191482544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21188688278198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38359832763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22092342376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24803638458252</t>
   </si>
   <si>
     <t xml:space="preserve">7.18929243087769</t>
@@ -521,64 +518,64 @@
     <t xml:space="preserve">7.18025493621826</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91365003585815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5191593170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47849130630493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50108528137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41071033477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27514839172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60953330993652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66375875473022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72702121734619</t>
+    <t xml:space="preserve">6.91365098953247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51915884017944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47849035263062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50108480453491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41070985794067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27514886856079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.609534740448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66375923156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72702217102051</t>
   </si>
   <si>
     <t xml:space="preserve">7.68183374404907</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6773157119751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63664722442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77220773696899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.971031665802</t>
+    <t xml:space="preserve">7.67731523513794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63664674758911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77220869064331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97103118896484</t>
   </si>
   <si>
     <t xml:space="preserve">8.34156799316406</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41386795043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45001888275146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57654190063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37771701812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40934944152832</t>
+    <t xml:space="preserve">8.41386699676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45001697540283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57654094696045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37771797180176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.409348487854</t>
   </si>
   <si>
     <t xml:space="preserve">8.35964202880859</t>
@@ -587,70 +584,70 @@
     <t xml:space="preserve">8.22408103942871</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24215602874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33704948425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32801151275635</t>
+    <t xml:space="preserve">8.24215507507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33704853057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32801055908203</t>
   </si>
   <si>
     <t xml:space="preserve">8.3234920501709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36416053771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37319755554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46809196472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30541801452637</t>
+    <t xml:space="preserve">8.36416149139404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37319946289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.468092918396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30541706085205</t>
   </si>
   <si>
     <t xml:space="preserve">8.30089855194092</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09755802154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26926708221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20600605010986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0749626159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11111259460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28282260894775</t>
+    <t xml:space="preserve">8.09755611419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26926803588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20600509643555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07496356964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11111450195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28282451629639</t>
   </si>
   <si>
     <t xml:space="preserve">8.2963809967041</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40483093261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48164939880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42290592193604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22859764099121</t>
+    <t xml:space="preserve">8.40482997894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48164844512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42290496826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22859954833984</t>
   </si>
   <si>
     <t xml:space="preserve">8.27378749847412</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02977561950684</t>
+    <t xml:space="preserve">8.02977657318115</t>
   </si>
   <si>
     <t xml:space="preserve">8.13370609283447</t>
@@ -659,19 +656,19 @@
     <t xml:space="preserve">8.27830505371094</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43194103240967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69402694702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57969760894775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25435066223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21820068359375</t>
+    <t xml:space="preserve">8.43194198608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6940279006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57969951629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25434875488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21819972991943</t>
   </si>
   <si>
     <t xml:space="preserve">9.01937770843506</t>
@@ -680,7 +677,7 @@
     <t xml:space="preserve">9.16397476196289</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2001256942749</t>
+    <t xml:space="preserve">9.20012474060059</t>
   </si>
   <si>
     <t xml:space="preserve">9.20916175842285</t>
@@ -695,13 +692,13 @@
     <t xml:space="preserve">9.03745174407959</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12782669067383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35376262664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55258655548096</t>
+    <t xml:space="preserve">9.12782573699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35376358032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55258560180664</t>
   </si>
   <si>
     <t xml:space="preserve">9.47124767303467</t>
@@ -710,43 +707,43 @@
     <t xml:space="preserve">9.80563449859619</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89601039886475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2123203277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94119548797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4472951889038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8449401855469</t>
+    <t xml:space="preserve">9.89600849151611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2123222351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94119644165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4472942352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8449411392212</t>
   </si>
   <si>
     <t xml:space="preserve">10.8087921142578</t>
   </si>
   <si>
-    <t xml:space="preserve">10.908203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9353160858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7364940643311</t>
+    <t xml:space="preserve">10.9082021713257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9353170394897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7364931106567</t>
   </si>
   <si>
     <t xml:space="preserve">10.7093801498413</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7545671463013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4764318466187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2261095046997</t>
+    <t xml:space="preserve">10.7545680999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.476432800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2261085510254</t>
   </si>
   <si>
     <t xml:space="preserve">10.0128726959229</t>
@@ -755,58 +752,61 @@
     <t xml:space="preserve">10.3837203979492</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4300756454468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2817363739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4022626876831</t>
+    <t xml:space="preserve">10.4300746917725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2817373275757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4022636413574</t>
   </si>
   <si>
     <t xml:space="preserve">10.5135164260864</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4949731826782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5413293838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7452964782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0790576934814</t>
+    <t xml:space="preserve">10.4949722290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5413312911987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7452955245972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0790586471558</t>
   </si>
   <si>
     <t xml:space="preserve">11.7743968963623</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5889739990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2181262969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3015661239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0976009368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1439580917358</t>
+    <t xml:space="preserve">11.5889730453491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2181253433228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3015670776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.097601890564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1439571380615</t>
   </si>
   <si>
     <t xml:space="preserve">11.0327024459839</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8287372589111</t>
+    <t xml:space="preserve">10.8287382125854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7545690536499</t>
   </si>
   <si>
     <t xml:space="preserve">10.7360248565674</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9863471984863</t>
+    <t xml:space="preserve">10.986346244812</t>
   </si>
   <si>
     <t xml:space="preserve">10.8658218383789</t>
@@ -815,76 +815,76 @@
     <t xml:space="preserve">10.5691432952881</t>
   </si>
   <si>
-    <t xml:space="preserve">11.125412940979</t>
+    <t xml:space="preserve">11.1254138946533</t>
   </si>
   <si>
     <t xml:space="preserve">11.0605163574219</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4869909286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0697860717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9399919509888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4499053955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4035482406616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7094993591309</t>
+    <t xml:space="preserve">11.4869899749756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0697870254517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9399909973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4499073028564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4035511016846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7094974517822</t>
   </si>
   <si>
     <t xml:space="preserve">12.0988883972168</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3213977813721</t>
+    <t xml:space="preserve">12.3213968276978</t>
   </si>
   <si>
     <t xml:space="preserve">11.894923210144</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5160894393921</t>
+    <t xml:space="preserve">12.5160913467407</t>
   </si>
   <si>
     <t xml:space="preserve">12.5253629684448</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6737003326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7478713989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5346345901489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.794225692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7293272018433</t>
+    <t xml:space="preserve">12.6737012863159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7478704452515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5346336364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7942266464233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7293262481689</t>
   </si>
   <si>
     <t xml:space="preserve">12.5439052581787</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5809898376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5624465942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4697351455688</t>
+    <t xml:space="preserve">12.5809888839722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5624485015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4697341918945</t>
   </si>
   <si>
     <t xml:space="preserve">12.4975490570068</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4882774353027</t>
+    <t xml:space="preserve">12.4882783889771</t>
   </si>
   <si>
     <t xml:space="preserve">12.6829719543457</t>
@@ -902,25 +902,25 @@
     <t xml:space="preserve">12.3955659866333</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4233798980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2935819625854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3677520751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8856496810913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2843112945557</t>
+    <t xml:space="preserve">12.423378944397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2935829162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3677539825439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8856506347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.28431224823</t>
   </si>
   <si>
     <t xml:space="preserve">12.1730575561523</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0525321960449</t>
+    <t xml:space="preserve">12.0525331497192</t>
   </si>
   <si>
     <t xml:space="preserve">11.9505500793457</t>
@@ -932,10 +932,10 @@
     <t xml:space="preserve">12.2657690048218</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9412775039673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9598188400269</t>
+    <t xml:space="preserve">11.9412794113159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9598207473755</t>
   </si>
   <si>
     <t xml:space="preserve">12.3306674957275</t>
@@ -944,34 +944,34 @@
     <t xml:space="preserve">12.4419212341309</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3492097854614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3770246505737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1545162200928</t>
+    <t xml:space="preserve">12.3492107391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3770236968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1545143127441</t>
   </si>
   <si>
     <t xml:space="preserve">12.2472267150879</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3399381637573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4511919021606</t>
+    <t xml:space="preserve">12.339940071106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4511938095093</t>
   </si>
   <si>
     <t xml:space="preserve">12.200870513916</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4326515197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3028545379639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2564992904663</t>
+    <t xml:space="preserve">12.4326505661011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3028554916382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.256498336792</t>
   </si>
   <si>
     <t xml:space="preserve">12.061803817749</t>
@@ -980,13 +980,13 @@
     <t xml:space="preserve">12.0247192382812</t>
   </si>
   <si>
-    <t xml:space="preserve">11.440634727478</t>
+    <t xml:space="preserve">11.4406337738037</t>
   </si>
   <si>
     <t xml:space="preserve">11.635329246521</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7929391860962</t>
+    <t xml:space="preserve">11.7929401397705</t>
   </si>
   <si>
     <t xml:space="preserve">11.663143157959</t>
@@ -1001,19 +1001,19 @@
     <t xml:space="preserve">11.9227352142334</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8207540512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8671092987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7373132705688</t>
+    <t xml:space="preserve">11.8207521438599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8671083450317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7373113632202</t>
   </si>
   <si>
     <t xml:space="preserve">12.2286834716797</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1915998458862</t>
+    <t xml:space="preserve">12.1915979385376</t>
   </si>
   <si>
     <t xml:space="preserve">11.7651252746582</t>
@@ -1022,52 +1022,52 @@
     <t xml:space="preserve">11.7187690734863</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1903123855591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2922954559326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1624984741211</t>
+    <t xml:space="preserve">11.1903114318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2922973632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1625003814697</t>
   </si>
   <si>
     <t xml:space="preserve">11.5426168441772</t>
   </si>
   <si>
-    <t xml:space="preserve">11.468448638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5982456207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5797023773193</t>
+    <t xml:space="preserve">11.4684476852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5982446670532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.579701423645</t>
   </si>
   <si>
     <t xml:space="preserve">11.4962615966797</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6724147796631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.857837677002</t>
+    <t xml:space="preserve">11.6724138259888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8578386306763</t>
   </si>
   <si>
     <t xml:space="preserve">12.1452445983887</t>
   </si>
   <si>
-    <t xml:space="preserve">12.006175994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9134654998779</t>
+    <t xml:space="preserve">12.0061769485474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9134645462036</t>
   </si>
   <si>
     <t xml:space="preserve">12.9240226745605</t>
   </si>
   <si>
-    <t xml:space="preserve">13.925311088562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1107330322266</t>
+    <t xml:space="preserve">13.9253101348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1107339859009</t>
   </si>
   <si>
     <t xml:space="preserve">14.092191696167</t>
@@ -1079,13 +1079,13 @@
     <t xml:space="preserve">13.9994802474976</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6299209594727</t>
+    <t xml:space="preserve">14.629919052124</t>
   </si>
   <si>
     <t xml:space="preserve">13.9067678451538</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6286306381226</t>
+    <t xml:space="preserve">13.6286315917969</t>
   </si>
   <si>
     <t xml:space="preserve">14.203444480896</t>
@@ -1109,19 +1109,19 @@
     <t xml:space="preserve">14.4815807342529</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1849021911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8325986862183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9981918334961</t>
+    <t xml:space="preserve">14.1849031448364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8325996398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9981937408447</t>
   </si>
   <si>
     <t xml:space="preserve">12.7756843566895</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3690385818481</t>
+    <t xml:space="preserve">13.3690395355225</t>
   </si>
   <si>
     <t xml:space="preserve">13.0352783203125</t>
@@ -1136,10 +1136,10 @@
     <t xml:space="preserve">13.5173778533936</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3134117126465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6644296646118</t>
+    <t xml:space="preserve">13.3134126663208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6644287109375</t>
   </si>
   <si>
     <t xml:space="preserve">12.1081590652466</t>
@@ -1148,13 +1148,13 @@
     <t xml:space="preserve">12.0154476165771</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8300228118896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5902605056763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7200574874878</t>
+    <t xml:space="preserve">11.8300256729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5902614593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7200565338135</t>
   </si>
   <si>
     <t xml:space="preserve">12.6088037490845</t>
@@ -1163,19 +1163,19 @@
     <t xml:space="preserve">12.1637859344482</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0339879989624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0710754394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.607515335083</t>
+    <t xml:space="preserve">12.033989906311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0710744857788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6075162887573</t>
   </si>
   <si>
     <t xml:space="preserve">12.4604635238647</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8114814758301</t>
+    <t xml:space="preserve">11.8114824295044</t>
   </si>
   <si>
     <t xml:space="preserve">11.8485660552979</t>
@@ -1184,31 +1184,31 @@
     <t xml:space="preserve">12.2379560470581</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3862934112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3504962921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5359220504761</t>
+    <t xml:space="preserve">12.3862943649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3504972457886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5359210968018</t>
   </si>
   <si>
     <t xml:space="preserve">13.7213449478149</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2590732574463</t>
+    <t xml:space="preserve">14.2590742111206</t>
   </si>
   <si>
     <t xml:space="preserve">14.908055305481</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7782592773438</t>
+    <t xml:space="preserve">14.7782583236694</t>
   </si>
   <si>
     <t xml:space="preserve">14.7411737442017</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7968006134033</t>
+    <t xml:space="preserve">14.7968015670776</t>
   </si>
   <si>
     <t xml:space="preserve">15.0235710144043</t>
@@ -1217,7 +1217,7 @@
     <t xml:space="preserve">15.6849870681763</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4015235900879</t>
+    <t xml:space="preserve">15.4015226364136</t>
   </si>
   <si>
     <t xml:space="preserve">15.2314462661743</t>
@@ -1229,7 +1229,7 @@
     <t xml:space="preserve">15.1180591583252</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1747531890869</t>
+    <t xml:space="preserve">15.1747522354126</t>
   </si>
   <si>
     <t xml:space="preserve">15.3070363998413</t>
@@ -1238,13 +1238,13 @@
     <t xml:space="preserve">14.1353855133057</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8141269683838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2660970687866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6062536239624</t>
+    <t xml:space="preserve">13.8141279220581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2660980224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6062545776367</t>
   </si>
   <si>
     <t xml:space="preserve">13.6818428039551</t>
@@ -1253,10 +1253,10 @@
     <t xml:space="preserve">13.0771217346191</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9448394775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1149168014526</t>
+    <t xml:space="preserve">12.9448375701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1149158477783</t>
   </si>
   <si>
     <t xml:space="preserve">12.8881454467773</t>
@@ -1268,52 +1268,52 @@
     <t xml:space="preserve">12.5479898452759</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0015306472778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6235790252686</t>
+    <t xml:space="preserve">13.0015316009521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6235799789429</t>
   </si>
   <si>
     <t xml:space="preserve">12.6991701126099</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7558612823486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8692474365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3401165008545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7369651794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7180690765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7747611999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2645235061646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7385349273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7763319015503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9653062820435</t>
+    <t xml:space="preserve">12.7558631896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8692483901978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3401155471802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.736964225769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7180681228638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7747602462769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2645254135132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7385368347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.776330947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9653072357178</t>
   </si>
   <si>
     <t xml:space="preserve">13.8708200454712</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0786924362183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6251497268677</t>
+    <t xml:space="preserve">14.0786933898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.625150680542</t>
   </si>
   <si>
     <t xml:space="preserve">13.5873565673828</t>
@@ -1322,31 +1322,31 @@
     <t xml:space="preserve">13.4172782897949</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4550724029541</t>
+    <t xml:space="preserve">13.4550733566284</t>
   </si>
   <si>
     <t xml:space="preserve">13.4361763000488</t>
   </si>
   <si>
-    <t xml:space="preserve">13.247200012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1338148117065</t>
+    <t xml:space="preserve">13.2472009658813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1338138580322</t>
   </si>
   <si>
     <t xml:space="preserve">13.322790145874</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4739723205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2094049453735</t>
+    <t xml:space="preserve">13.4739694595337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2094058990479</t>
   </si>
   <si>
     <t xml:space="preserve">13.3605861663818</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5668878555298</t>
+    <t xml:space="preserve">12.5668869018555</t>
   </si>
   <si>
     <t xml:space="preserve">12.5101938247681</t>
@@ -1358,7 +1358,7 @@
     <t xml:space="preserve">12.680272102356</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0393257141113</t>
+    <t xml:space="preserve">13.0393266677856</t>
   </si>
   <si>
     <t xml:space="preserve">12.9826326370239</t>
@@ -1367,25 +1367,25 @@
     <t xml:space="preserve">12.8125562667847</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9637365341187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7952289581299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1164865493774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2676696777344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3054647445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.059796333313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7007427215576</t>
+    <t xml:space="preserve">12.9637355804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7952299118042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1164875030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2676687240601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3054656982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0597953796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7007417678833</t>
   </si>
   <si>
     <t xml:space="preserve">13.4928674697876</t>
@@ -1394,49 +1394,49 @@
     <t xml:space="preserve">13.7574348449707</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5495615005493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1731815338135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9290838241577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4960117340088</t>
+    <t xml:space="preserve">13.549560546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1731805801392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9290828704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4960126876831</t>
   </si>
   <si>
     <t xml:space="preserve">15.2692394256592</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1558561325073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5353775024414</t>
+    <t xml:space="preserve">15.1558570861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5353755950928</t>
   </si>
   <si>
     <t xml:space="preserve">16.7054557800293</t>
   </si>
   <si>
-    <t xml:space="preserve">16.913330078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6298656463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2330150604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9117565155029</t>
+    <t xml:space="preserve">16.9133319854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6298675537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2330188751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9117574691772</t>
   </si>
   <si>
     <t xml:space="preserve">15.5904989242554</t>
   </si>
   <si>
-    <t xml:space="preserve">15.514910697937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.004674911499</t>
+    <t xml:space="preserve">15.5149078369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0046739578247</t>
   </si>
   <si>
     <t xml:space="preserve">15.2125473022461</t>
@@ -1445,28 +1445,28 @@
     <t xml:space="preserve">14.3810539245605</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6078252792358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4377460479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6456203460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2487716674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1920795440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8897161483765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5306634902954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8519220352173</t>
+    <t xml:space="preserve">14.6078262329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4377470016479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.645622253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2487726211548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1920785903931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8897171020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5306625366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8519229888916</t>
   </si>
   <si>
     <t xml:space="preserve">14.0220003128052</t>
@@ -1475,10 +1475,10 @@
     <t xml:space="preserve">14.8723907470703</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4755401611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4188508987427</t>
+    <t xml:space="preserve">14.4755411148071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.418848991394</t>
   </si>
   <si>
     <t xml:space="preserve">15.5527029037476</t>
@@ -1487,7 +1487,7 @@
     <t xml:space="preserve">14.9668779373169</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0818386077881</t>
+    <t xml:space="preserve">16.0818367004395</t>
   </si>
   <si>
     <t xml:space="preserve">16.0629386901855</t>
@@ -1502,7 +1502,7 @@
     <t xml:space="preserve">15.8739624023438</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4582166671753</t>
+    <t xml:space="preserve">15.4582176208496</t>
   </si>
   <si>
     <t xml:space="preserve">16.0251426696777</t>
@@ -1514,19 +1514,19 @@
     <t xml:space="preserve">16.1007347106934</t>
   </si>
   <si>
-    <t xml:space="preserve">16.327507019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6471929550171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7983713150024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9306554794312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0613689422607</t>
+    <t xml:space="preserve">16.3275051116943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6471910476685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7983732223511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9306564331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0613660812378</t>
   </si>
   <si>
     <t xml:space="preserve">15.8550653457642</t>
@@ -1535,52 +1535,52 @@
     <t xml:space="preserve">15.4771118164062</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7401084899902</t>
+    <t xml:space="preserve">14.7401094436646</t>
   </si>
   <si>
     <t xml:space="preserve">14.9101867675781</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5511322021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8156986236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9857778549194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5338077545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7416791915894</t>
+    <t xml:space="preserve">14.5511312484741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8156976699829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9857749938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.533805847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7416801452637</t>
   </si>
   <si>
     <t xml:space="preserve">15.0424690246582</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4204225540161</t>
+    <t xml:space="preserve">15.4204187393188</t>
   </si>
   <si>
     <t xml:space="preserve">15.7605781555176</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6282958984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8928575515747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9684524536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0062446594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9873456954956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6093988418579</t>
+    <t xml:space="preserve">15.6282978057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8928604125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9684505462646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0062484741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9873495101929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6093969345093</t>
   </si>
   <si>
     <t xml:space="preserve">14.6834154129028</t>
@@ -1589,16 +1589,16 @@
     <t xml:space="preserve">14.6267223358154</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8534936904907</t>
+    <t xml:space="preserve">14.853494644165</t>
   </si>
   <si>
     <t xml:space="preserve">15.1936502456665</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0991611480713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2881393432617</t>
+    <t xml:space="preserve">15.0991630554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2881383895874</t>
   </si>
   <si>
     <t xml:space="preserve">16.1952209472656</t>
@@ -1607,10 +1607,10 @@
     <t xml:space="preserve">17.0078182220459</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2345886230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2534885406494</t>
+    <t xml:space="preserve">17.2345867156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2534866333008</t>
   </si>
   <si>
     <t xml:space="preserve">17.29128074646</t>
@@ -1619,58 +1619,58 @@
     <t xml:space="preserve">17.1023063659668</t>
   </si>
   <si>
-    <t xml:space="preserve">17.064510345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0471858978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4046649932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3479747772217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.366870880127</t>
+    <t xml:space="preserve">17.0645084381104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0471839904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4046669006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.347972869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3668689727783</t>
   </si>
   <si>
     <t xml:space="preserve">17.4991550445557</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0456123352051</t>
+    <t xml:space="preserve">17.0456142425537</t>
   </si>
   <si>
     <t xml:space="preserve">17.3857688903809</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4424610137939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8582038879395</t>
+    <t xml:space="preserve">17.4424591064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8582057952881</t>
   </si>
   <si>
     <t xml:space="preserve">17.8204135894775</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5558490753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3290748596191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.140100479126</t>
+    <t xml:space="preserve">17.5558452606201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3290786743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1400985717773</t>
   </si>
   <si>
     <t xml:space="preserve">16.5731735229492</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5920715332031</t>
+    <t xml:space="preserve">16.5920696258545</t>
   </si>
   <si>
     <t xml:space="preserve">16.2897090911865</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8566341400146</t>
+    <t xml:space="preserve">16.8566360473633</t>
   </si>
   <si>
     <t xml:space="preserve">16.1574268341064</t>
@@ -1679,7 +1679,7 @@
     <t xml:space="preserve">16.5805969238281</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5421276092529</t>
+    <t xml:space="preserve">16.5421295166016</t>
   </si>
   <si>
     <t xml:space="preserve">16.3882465362549</t>
@@ -1691,19 +1691,19 @@
     <t xml:space="preserve">16.2343654632568</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0035457611084</t>
+    <t xml:space="preserve">16.0035438537598</t>
   </si>
   <si>
     <t xml:space="preserve">15.9843111038208</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6767749786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8114185333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8306503295898</t>
+    <t xml:space="preserve">16.6767730712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8114147186279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8306541442871</t>
   </si>
   <si>
     <t xml:space="preserve">16.7537117004395</t>
@@ -1712,67 +1712,67 @@
     <t xml:space="preserve">16.6382999420166</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4267139434814</t>
+    <t xml:space="preserve">16.4267158508301</t>
   </si>
   <si>
     <t xml:space="preserve">16.522891998291</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9458389282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4651889801025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9650754928589</t>
+    <t xml:space="preserve">15.9458417892456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4651870727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9650745391846</t>
   </si>
   <si>
     <t xml:space="preserve">16.0227813720703</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8689012527466</t>
+    <t xml:space="preserve">15.8689002990723</t>
   </si>
   <si>
     <t xml:space="preserve">15.7342557907104</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6573171615601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.426495552063</t>
+    <t xml:space="preserve">15.6573162078857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4264965057373</t>
   </si>
   <si>
     <t xml:space="preserve">15.3687906265259</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3110857009888</t>
+    <t xml:space="preserve">15.3110847473145</t>
   </si>
   <si>
     <t xml:space="preserve">14.9840898513794</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1956739425659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2341451644897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1379690170288</t>
+    <t xml:space="preserve">15.1956748962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2341442108154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1379709243774</t>
   </si>
   <si>
     <t xml:space="preserve">15.0994997024536</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0033254623413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1187343597412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2533798217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0610303878784</t>
+    <t xml:space="preserve">15.003324508667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1187353134155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2533779144287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0610294342041</t>
   </si>
   <si>
     <t xml:space="preserve">14.8686800003052</t>
@@ -1781,13 +1781,13 @@
     <t xml:space="preserve">14.8494434356689</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7147989273071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4457311630249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1764392852783</t>
+    <t xml:space="preserve">14.7147998809814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4457302093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.176438331604</t>
   </si>
   <si>
     <t xml:space="preserve">14.8302087783813</t>
@@ -1796,7 +1796,7 @@
     <t xml:space="preserve">14.9648542404175</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1572046279907</t>
+    <t xml:space="preserve">15.157205581665</t>
   </si>
   <si>
     <t xml:space="preserve">14.7917394638062</t>
@@ -1805,52 +1805,52 @@
     <t xml:space="preserve">14.7532682418823</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9071483612061</t>
+    <t xml:space="preserve">14.9071502685547</t>
   </si>
   <si>
     <t xml:space="preserve">15.0225582122803</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8109731674194</t>
+    <t xml:space="preserve">14.8109722137451</t>
   </si>
   <si>
     <t xml:space="preserve">14.8879137039185</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5416841506958</t>
+    <t xml:space="preserve">14.5416831970215</t>
   </si>
   <si>
     <t xml:space="preserve">14.580153465271</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5993900299072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.503212928772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6378583908081</t>
+    <t xml:space="preserve">14.5993881225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5032138824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6378593444824</t>
   </si>
   <si>
     <t xml:space="preserve">14.6186237335205</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4647445678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4455089569092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.65709400177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9263858795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5609188079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3495531082153</t>
+    <t xml:space="preserve">14.4647436141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4455080032349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6570930480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9263849258423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5609197616577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3495559692383</t>
   </si>
   <si>
     <t xml:space="preserve">15.3880252838135</t>
@@ -1859,67 +1859,67 @@
     <t xml:space="preserve">15.676549911499</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5226697921753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7150211334229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7919616699219</t>
+    <t xml:space="preserve">15.5226707458496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7150201797485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7919607162476</t>
   </si>
   <si>
     <t xml:space="preserve">16.1574249267578</t>
   </si>
   <si>
-    <t xml:space="preserve">15.77272605896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8111963272095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9073715209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6380796432495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6188449859619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.849663734436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5803775787354</t>
+    <t xml:space="preserve">15.7727270126343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8111953735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9073734283447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6380815505981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6188459396362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8496646881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5803747177124</t>
   </si>
   <si>
     <t xml:space="preserve">15.5034351348877</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8304300308228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.926607131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1189556121826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1576461791992</t>
+    <t xml:space="preserve">15.8304290771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9266042709351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1189575195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1576480865479</t>
   </si>
   <si>
     <t xml:space="preserve">17.0037689208984</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9460620880127</t>
+    <t xml:space="preserve">16.9460639953613</t>
   </si>
   <si>
     <t xml:space="preserve">16.8883571624756</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9845333099365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1191787719727</t>
+    <t xml:space="preserve">16.9845314025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.119176864624</t>
   </si>
   <si>
     <t xml:space="preserve">17.2730560302734</t>
@@ -1928,37 +1928,37 @@
     <t xml:space="preserve">18.2732791900635</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1771011352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6000518798828</t>
+    <t xml:space="preserve">18.1771030426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6000537872314</t>
   </si>
   <si>
     <t xml:space="preserve">17.6577606201172</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1001663208008</t>
+    <t xml:space="preserve">18.1001644134521</t>
   </si>
   <si>
     <t xml:space="preserve">17.9847564697266</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1194000244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.965518951416</t>
+    <t xml:space="preserve">18.1193981170654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9655170440674</t>
   </si>
   <si>
     <t xml:space="preserve">17.9462852478027</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0616931915283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9270496368408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3117504119873</t>
+    <t xml:space="preserve">18.0616970062256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9270477294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3117523193359</t>
   </si>
   <si>
     <t xml:space="preserve">18.7541561126709</t>
@@ -1970,7 +1970,7 @@
     <t xml:space="preserve">19.0234470367432</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5425720214844</t>
+    <t xml:space="preserve">18.5425701141357</t>
   </si>
   <si>
     <t xml:space="preserve">18.9657421112061</t>
@@ -1979,25 +1979,25 @@
     <t xml:space="preserve">18.9080371856689</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4273834228516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8120803833008</t>
+    <t xml:space="preserve">19.4273815155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.812084197998</t>
   </si>
   <si>
     <t xml:space="preserve">19.5235576629639</t>
   </si>
   <si>
-    <t xml:space="preserve">19.667818069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2831153869629</t>
+    <t xml:space="preserve">19.6678199768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2831172943115</t>
   </si>
   <si>
     <t xml:space="preserve">18.8503284454346</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6197338104248</t>
+    <t xml:space="preserve">19.6197319030762</t>
   </si>
   <si>
     <t xml:space="preserve">19.7159061431885</t>
@@ -2009,22 +2009,22 @@
     <t xml:space="preserve">19.331205368042</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5716457366943</t>
+    <t xml:space="preserve">19.5716438293457</t>
   </si>
   <si>
     <t xml:space="preserve">20.1967830657959</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2448692321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.216459274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1585311889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1104469299316</t>
+    <t xml:space="preserve">20.2448711395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2164611816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1585350036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1104488372803</t>
   </si>
   <si>
     <t xml:space="preserve">20.8219203948975</t>
@@ -2033,28 +2033,28 @@
     <t xml:space="preserve">20.6295719146729</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0142688751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7257461547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6776561737061</t>
+    <t xml:space="preserve">21.0142726898193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7257442474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6776599884033</t>
   </si>
   <si>
     <t xml:space="preserve">19.9563465118408</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2929573059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0044326782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8601722717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0811519622803</t>
+    <t xml:space="preserve">20.2929553985596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0044288635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8601684570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0811500549316</t>
   </si>
   <si>
     <t xml:space="preserve">20.7738342285156</t>
@@ -2066,19 +2066,19 @@
     <t xml:space="preserve">20.5814819335938</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2547092437744</t>
+    <t xml:space="preserve">21.254711151123</t>
   </si>
   <si>
     <t xml:space="preserve">21.3989734649658</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2066230773926</t>
+    <t xml:space="preserve">21.2066211700439</t>
   </si>
   <si>
     <t xml:space="preserve">21.6394100189209</t>
   </si>
   <si>
-    <t xml:space="preserve">21.447057723999</t>
+    <t xml:space="preserve">21.4470596313477</t>
   </si>
   <si>
     <t xml:space="preserve">21.8317623138428</t>
@@ -2087,13 +2087,13 @@
     <t xml:space="preserve">20.0525207519531</t>
   </si>
   <si>
-    <t xml:space="preserve">20.100606918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7349185943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1963386535645</t>
+    <t xml:space="preserve">20.1006088256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.734920501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1963405609131</t>
   </si>
   <si>
     <t xml:space="preserve">17.6192874908447</t>
@@ -2114,10 +2114,10 @@
     <t xml:space="preserve">12.464301109314</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0218954086304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.137303352356</t>
+    <t xml:space="preserve">12.0218944549561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1373043060303</t>
   </si>
   <si>
     <t xml:space="preserve">12.6951208114624</t>
@@ -2126,13 +2126,13 @@
     <t xml:space="preserve">12.9067058563232</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9834241867065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3106412887573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5606966018677</t>
+    <t xml:space="preserve">11.9834251403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3106422424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.560697555542</t>
   </si>
   <si>
     <t xml:space="preserve">14.0223369598389</t>
@@ -2141,28 +2141,28 @@
     <t xml:space="preserve">14.1954526901245</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2916278839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1185140609741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.734034538269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0992774963379</t>
+    <t xml:space="preserve">14.2916269302368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1185131072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7340335845947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0992784500122</t>
   </si>
   <si>
     <t xml:space="preserve">15.4072599411011</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8691215515137</t>
+    <t xml:space="preserve">16.8691234588623</t>
   </si>
   <si>
     <t xml:space="preserve">16.1766605377197</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2151317596436</t>
+    <t xml:space="preserve">16.2151298522949</t>
   </si>
   <si>
     <t xml:space="preserve">15.4649648666382</t>
@@ -2171,16 +2171,16 @@
     <t xml:space="preserve">16.0612525939941</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1381931304932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0420169830322</t>
+    <t xml:space="preserve">16.1381912231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0420188903809</t>
   </si>
   <si>
     <t xml:space="preserve">16.59983253479</t>
   </si>
   <si>
-    <t xml:space="preserve">17.215353012085</t>
+    <t xml:space="preserve">17.2153511047363</t>
   </si>
   <si>
     <t xml:space="preserve">16.7152404785156</t>
@@ -2189,22 +2189,22 @@
     <t xml:space="preserve">16.9268283843994</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0614738464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2540454864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6387462615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0774536132812</t>
+    <t xml:space="preserve">17.0614700317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2540416717529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.638744354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0774517059326</t>
   </si>
   <si>
     <t xml:space="preserve">17.7677764892578</t>
   </si>
   <si>
-    <t xml:space="preserve">17.458101272583</t>
+    <t xml:space="preserve">17.4580993652344</t>
   </si>
   <si>
     <t xml:space="preserve">17.4387435913086</t>
@@ -2216,28 +2216,28 @@
     <t xml:space="preserve">16.9548721313477</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4193878173828</t>
+    <t xml:space="preserve">17.4193897247314</t>
   </si>
   <si>
     <t xml:space="preserve">17.6129379272461</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1677761077881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.651647567749</t>
+    <t xml:space="preserve">17.1677742004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6516456604004</t>
   </si>
   <si>
     <t xml:space="preserve">17.4968070983887</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7290649414062</t>
+    <t xml:space="preserve">17.7290668487549</t>
   </si>
   <si>
     <t xml:space="preserve">18.290355682373</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9419708251953</t>
+    <t xml:space="preserve">17.9419727325439</t>
   </si>
   <si>
     <t xml:space="preserve">18.0580997467041</t>
@@ -2246,112 +2246,112 @@
     <t xml:space="preserve">18.3871307373047</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4064865112305</t>
+    <t xml:space="preserve">18.4064884185791</t>
   </si>
   <si>
     <t xml:space="preserve">17.9032611846924</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2322940826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2516479492188</t>
+    <t xml:space="preserve">18.2322902679443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2516498565674</t>
   </si>
   <si>
     <t xml:space="preserve">18.5806827545166</t>
   </si>
   <si>
-    <t xml:space="preserve">18.445198059082</t>
+    <t xml:space="preserve">18.4451942443848</t>
   </si>
   <si>
     <t xml:space="preserve">18.1161632537842</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0387420654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8322906494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7742290496826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6774559020996</t>
+    <t xml:space="preserve">18.038745880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8322925567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7742309570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.677453994751</t>
   </si>
   <si>
     <t xml:space="preserve">18.9097137451172</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0451965332031</t>
+    <t xml:space="preserve">19.0451984405518</t>
   </si>
   <si>
     <t xml:space="preserve">19.5968132019043</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3548755645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9484214782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1032638549805</t>
+    <t xml:space="preserve">19.3548774719238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9484233856201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1032600402832</t>
   </si>
   <si>
     <t xml:space="preserve">18.4645519256592</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6581020355225</t>
+    <t xml:space="preserve">18.6581001281738</t>
   </si>
   <si>
     <t xml:space="preserve">19.5000381469727</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6452007293701</t>
+    <t xml:space="preserve">19.6451988220215</t>
   </si>
   <si>
     <t xml:space="preserve">20.0806846618652</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3226203918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6129417419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5645561218262</t>
+    <t xml:space="preserve">20.3226184844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6129398345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5645523071289</t>
   </si>
   <si>
     <t xml:space="preserve">21.0484275817871</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2903614044189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7258472442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1935901641846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5806865692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8710098266602</t>
+    <t xml:space="preserve">21.2903633117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7258491516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1935882568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5806884765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8710117340088</t>
   </si>
   <si>
     <t xml:space="preserve">21.5323009490967</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3387508392334</t>
+    <t xml:space="preserve">21.3387489318848</t>
   </si>
   <si>
     <t xml:space="preserve">21.7742347717285</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4516563415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9355297088623</t>
+    <t xml:space="preserve">22.4516582489014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9355278015137</t>
   </si>
   <si>
     <t xml:space="preserve">22.7903633117676</t>
@@ -2360,28 +2360,28 @@
     <t xml:space="preserve">23.3226261138916</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4193992614746</t>
+    <t xml:space="preserve">23.4194011688232</t>
   </si>
   <si>
     <t xml:space="preserve">24.0968208312988</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7258548736572</t>
+    <t xml:space="preserve">24.7258529663086</t>
   </si>
   <si>
     <t xml:space="preserve">24.4839153289795</t>
   </si>
   <si>
-    <t xml:space="preserve">24.048433303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7581100463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.95166015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6613388061523</t>
+    <t xml:space="preserve">24.0484352111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7581119537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9516582489014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6613349914551</t>
   </si>
   <si>
     <t xml:space="preserve">22.741979598999</t>
@@ -2396,52 +2396,52 @@
     <t xml:space="preserve">23.0806903839111</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8871383666992</t>
+    <t xml:space="preserve">22.8871402740479</t>
   </si>
   <si>
     <t xml:space="preserve">22.5484294891357</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8226203918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0645599365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2419776916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6290760040283</t>
+    <t xml:space="preserve">21.8226222991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0645561218262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2419757843018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6290740966797</t>
   </si>
   <si>
     <t xml:space="preserve">20.4677810668945</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3871364593506</t>
+    <t xml:space="preserve">21.3871383666992</t>
   </si>
   <si>
     <t xml:space="preserve">21.0968151092529</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4839134216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2097206115723</t>
+    <t xml:space="preserve">21.4839115142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2097187042236</t>
   </si>
   <si>
     <t xml:space="preserve">21.9677867889404</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9516525268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1129455566406</t>
+    <t xml:space="preserve">20.9516544342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1129474639893</t>
   </si>
   <si>
     <t xml:space="preserve">22.3548812866211</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9193954467773</t>
+    <t xml:space="preserve">21.919397354126</t>
   </si>
   <si>
     <t xml:space="preserve">22.838752746582</t>
@@ -2459,13 +2459,13 @@
     <t xml:space="preserve">24.241979598999</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7419853210449</t>
+    <t xml:space="preserve">25.7419834136963</t>
   </si>
   <si>
     <t xml:space="preserve">26.17746925354</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0000534057617</t>
+    <t xml:space="preserve">27.0000514984131</t>
   </si>
   <si>
     <t xml:space="preserve">26.661340713501</t>
@@ -2474,28 +2474,28 @@
     <t xml:space="preserve">26.6129550933838</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3710174560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6774730682373</t>
+    <t xml:space="preserve">26.3710193634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6774749755859</t>
   </si>
   <si>
     <t xml:space="preserve">28.6452159881592</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9032821655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9355411529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7581214904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3871574401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9194164276123</t>
+    <t xml:space="preserve">29.903284072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9355392456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7581233978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3871536254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9194145202637</t>
   </si>
   <si>
     <t xml:space="preserve">31.7419986724854</t>
@@ -2507,28 +2507,28 @@
     <t xml:space="preserve">31.5484466552734</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0807075500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2581214904785</t>
+    <t xml:space="preserve">32.0807113647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2581233978271</t>
   </si>
   <si>
     <t xml:space="preserve">32.1774826049805</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3226432800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2903900146484</t>
+    <t xml:space="preserve">32.3226470947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2903861999512</t>
   </si>
   <si>
     <t xml:space="preserve">33.1936111450195</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8065147399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4839324951172</t>
+    <t xml:space="preserve">32.8065185546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4839363098145</t>
   </si>
   <si>
     <t xml:space="preserve">33.7258682250977</t>
@@ -2540,16 +2540,16 @@
     <t xml:space="preserve">34.7420043945312</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5968437194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3710327148438</t>
+    <t xml:space="preserve">34.5968399047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.371036529541</t>
   </si>
   <si>
     <t xml:space="preserve">35.4678115844727</t>
   </si>
   <si>
-    <t xml:space="preserve">36.8226509094238</t>
+    <t xml:space="preserve">36.8226547241211</t>
   </si>
   <si>
     <t xml:space="preserve">37.1613655090332</t>
@@ -2558,16 +2558,16 @@
     <t xml:space="preserve">36.1936225891113</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3065185546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5645866394043</t>
+    <t xml:space="preserve">34.3065147399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.564582824707</t>
   </si>
   <si>
     <t xml:space="preserve">32.6613540649414</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7581253051758</t>
+    <t xml:space="preserve">32.758129119873</t>
   </si>
   <si>
     <t xml:space="preserve">32.7097396850586</t>
@@ -2579,19 +2579,19 @@
     <t xml:space="preserve">30.3387680053711</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8226413726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5807018280029</t>
+    <t xml:space="preserve">30.822639465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5807037353516</t>
   </si>
   <si>
     <t xml:space="preserve">30.4839305877686</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1129627227783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4355506896973</t>
+    <t xml:space="preserve">31.112964630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.435546875</t>
   </si>
   <si>
     <t xml:space="preserve">33.8710327148438</t>
@@ -2600,52 +2600,52 @@
     <t xml:space="preserve">35.2742614746094</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6613578796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7097434997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2581329345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.0161972045898</t>
+    <t xml:space="preserve">35.6613616943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7097473144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2581367492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.0162010192871</t>
   </si>
   <si>
     <t xml:space="preserve">36.9678115844727</t>
   </si>
   <si>
-    <t xml:space="preserve">35.9516830444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4355506896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0807075500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9839401245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6774940490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.0645904541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6452331542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.0323333740234</t>
+    <t xml:space="preserve">35.9516868591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4355545043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0807151794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9839363098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.677490234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.064582824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6452369689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.0323295593262</t>
   </si>
   <si>
     <t xml:space="preserve">38.612979888916</t>
   </si>
   <si>
-    <t xml:space="preserve">38.7581405639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8226623535156</t>
+    <t xml:space="preserve">38.7581367492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8226585388184</t>
   </si>
   <si>
     <t xml:space="preserve">39.6774940490723</t>
@@ -2654,13 +2654,13 @@
     <t xml:space="preserve">38.5645942687988</t>
   </si>
   <si>
-    <t xml:space="preserve">38.7097511291504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6291122436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4516868591309</t>
+    <t xml:space="preserve">38.7097549438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6291084289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4516906738281</t>
   </si>
   <si>
     <t xml:space="preserve">40.1613693237305</t>
@@ -2669,43 +2669,43 @@
     <t xml:space="preserve">39.4355583190918</t>
   </si>
   <si>
-    <t xml:space="preserve">40.2581405639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.0807266235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.9033050537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.0645980834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1775016784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.854923248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.3387870788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.048469543457</t>
+    <t xml:space="preserve">40.2581367492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.0807304382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.9033088684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.0645942687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1774978637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8549156188965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.3387908935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.0484657287598</t>
   </si>
   <si>
     <t xml:space="preserve">42.6291160583496</t>
   </si>
   <si>
-    <t xml:space="preserve">41.612979888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.3871803283691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.5000877380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.1291198730469</t>
+    <t xml:space="preserve">41.6129837036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.3871765136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.5000839233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.1291122436523</t>
   </si>
   <si>
     <t xml:space="preserve">44.7097625732422</t>
@@ -2717,7 +2717,7 @@
     <t xml:space="preserve">45.6775054931641</t>
   </si>
   <si>
-    <t xml:space="preserve">44.4194412231445</t>
+    <t xml:space="preserve">44.4194374084473</t>
   </si>
   <si>
     <t xml:space="preserve">45.0000877380371</t>
@@ -2729,7 +2729,7 @@
     <t xml:space="preserve">45.483959197998</t>
   </si>
   <si>
-    <t xml:space="preserve">44.9517021179199</t>
+    <t xml:space="preserve">44.9516983032227</t>
   </si>
   <si>
     <t xml:space="preserve">46.2581520080566</t>
@@ -2741,25 +2741,25 @@
     <t xml:space="preserve">44.6129875183105</t>
   </si>
   <si>
-    <t xml:space="preserve">44.5162124633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.2742767333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8387908935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.1613731384277</t>
+    <t xml:space="preserve">44.5162162780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2742805480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.838794708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.161376953125</t>
   </si>
   <si>
     <t xml:space="preserve">43.3065338134766</t>
   </si>
   <si>
-    <t xml:space="preserve">43.2581520080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.8710479736328</t>
+    <t xml:space="preserve">43.2581481933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.8710517883301</t>
   </si>
   <si>
     <t xml:space="preserve">43.0646018981934</t>
@@ -2771,7 +2771,7 @@
     <t xml:space="preserve">43.4033088684082</t>
   </si>
   <si>
-    <t xml:space="preserve">42.4355621337891</t>
+    <t xml:space="preserve">42.4355697631836</t>
   </si>
   <si>
     <t xml:space="preserve">41.8992919921875</t>
@@ -2780,22 +2780,22 @@
     <t xml:space="preserve">40.0436096191406</t>
   </si>
   <si>
-    <t xml:space="preserve">39.7994422912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4576110839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.0924453735352</t>
+    <t xml:space="preserve">39.799446105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4576072692871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.0924415588379</t>
   </si>
   <si>
     <t xml:space="preserve">40.8737831115723</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9947776794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.7761116027832</t>
+    <t xml:space="preserve">39.9947738647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.7761154174805</t>
   </si>
   <si>
     <t xml:space="preserve">40.6784477233887</t>
@@ -2804,25 +2804,25 @@
     <t xml:space="preserve">40.190113067627</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8971061706543</t>
+    <t xml:space="preserve">39.8971099853516</t>
   </si>
   <si>
     <t xml:space="preserve">39.6529388427734</t>
   </si>
   <si>
-    <t xml:space="preserve">39.6041069030762</t>
+    <t xml:space="preserve">39.6041030883789</t>
   </si>
   <si>
     <t xml:space="preserve">39.7506065368652</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2622718811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2877769470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9459419250488</t>
+    <t xml:space="preserve">39.2622680664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2877807617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9459457397461</t>
   </si>
   <si>
     <t xml:space="preserve">37.8949279785156</t>
@@ -2831,19 +2831,19 @@
     <t xml:space="preserve">36.7229194641113</t>
   </si>
   <si>
-    <t xml:space="preserve">37.6019248962402</t>
+    <t xml:space="preserve">37.601921081543</t>
   </si>
   <si>
     <t xml:space="preserve">38.090259552002</t>
   </si>
   <si>
-    <t xml:space="preserve">39.5552749633789</t>
+    <t xml:space="preserve">39.5552711486816</t>
   </si>
   <si>
     <t xml:space="preserve">41.7039566040039</t>
   </si>
   <si>
-    <t xml:space="preserve">42.0946235656738</t>
+    <t xml:space="preserve">42.0946197509766</t>
   </si>
   <si>
     <t xml:space="preserve">41.4597854614258</t>
@@ -2852,13 +2852,13 @@
     <t xml:space="preserve">41.0691146850586</t>
   </si>
   <si>
-    <t xml:space="preserve">40.385440826416</t>
+    <t xml:space="preserve">40.3854446411133</t>
   </si>
   <si>
     <t xml:space="preserve">40.4342803955078</t>
   </si>
   <si>
-    <t xml:space="preserve">42.1922950744629</t>
+    <t xml:space="preserve">42.1922912597656</t>
   </si>
   <si>
     <t xml:space="preserve">42.0457916259766</t>
@@ -2870,40 +2870,40 @@
     <t xml:space="preserve">41.4109535217285</t>
   </si>
   <si>
-    <t xml:space="preserve">42.7294654846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3664779663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4153099060059</t>
+    <t xml:space="preserve">42.7294578552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3664817810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4153175354004</t>
   </si>
   <si>
     <t xml:space="preserve">46.1966514587402</t>
   </si>
   <si>
-    <t xml:space="preserve">47.8569946289062</t>
+    <t xml:space="preserve">47.856990814209</t>
   </si>
   <si>
     <t xml:space="preserve">47.3198280334473</t>
   </si>
   <si>
-    <t xml:space="preserve">47.8081665039062</t>
+    <t xml:space="preserve">47.808162689209</t>
   </si>
   <si>
     <t xml:space="preserve">48.5406646728516</t>
   </si>
   <si>
-    <t xml:space="preserve">48.5895004272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.8336715698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.1988296508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.7126770019531</t>
+    <t xml:space="preserve">48.5895042419434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.833667755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.1988258361816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.7126808166504</t>
   </si>
   <si>
     <t xml:space="preserve">49.9080123901367</t>
@@ -2912,7 +2912,7 @@
     <t xml:space="preserve">49.8103446960449</t>
   </si>
   <si>
-    <t xml:space="preserve">50.0056762695312</t>
+    <t xml:space="preserve">50.0056800842285</t>
   </si>
   <si>
     <t xml:space="preserve">50.6893501281738</t>
@@ -2921,13 +2921,13 @@
     <t xml:space="preserve">51.3730163574219</t>
   </si>
   <si>
-    <t xml:space="preserve">50.2986755371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.591682434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4940147399902</t>
+    <t xml:space="preserve">50.2986793518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.5916786193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4940185546875</t>
   </si>
   <si>
     <t xml:space="preserve">51.2753524780273</t>
@@ -2945,37 +2945,37 @@
     <t xml:space="preserve">51.8613548278809</t>
   </si>
   <si>
-    <t xml:space="preserve">51.9590301513672</t>
+    <t xml:space="preserve">51.9590263366699</t>
   </si>
   <si>
     <t xml:space="preserve">50.8846855163574</t>
   </si>
   <si>
-    <t xml:space="preserve">45.2688102722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.536304473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.5107955932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.2433052062988</t>
+    <t xml:space="preserve">45.2688140869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.5363082885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.510799407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2433013916016</t>
   </si>
   <si>
     <t xml:space="preserve">44.2921371459961</t>
   </si>
   <si>
-    <t xml:space="preserve">44.9269752502441</t>
+    <t xml:space="preserve">44.9269790649414</t>
   </si>
   <si>
     <t xml:space="preserve">44.047966003418</t>
   </si>
   <si>
-    <t xml:space="preserve">43.8038024902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.4386405944824</t>
+    <t xml:space="preserve">43.8037986755371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.4386444091797</t>
   </si>
   <si>
     <t xml:space="preserve">43.9503021240234</t>
@@ -2984,28 +2984,28 @@
     <t xml:space="preserve">44.1944694519043</t>
   </si>
   <si>
-    <t xml:space="preserve">41.2156181335449</t>
+    <t xml:space="preserve">41.2156219482422</t>
   </si>
   <si>
     <t xml:space="preserve">40.9714508056641</t>
   </si>
   <si>
-    <t xml:space="preserve">41.7527885437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.2899551391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.0712966918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.2666320800781</t>
+    <t xml:space="preserve">41.7527847290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.2899589538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.0712928771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.2666282653809</t>
   </si>
   <si>
     <t xml:space="preserve">43.7061347961426</t>
   </si>
   <si>
-    <t xml:space="preserve">44.3409767150879</t>
+    <t xml:space="preserve">44.3409729003906</t>
   </si>
   <si>
     <t xml:space="preserve">45.4641456604004</t>
@@ -3023,10 +3023,10 @@
     <t xml:space="preserve">42.7782936096191</t>
   </si>
   <si>
-    <t xml:space="preserve">41.2644462585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.6806259155273</t>
+    <t xml:space="preserve">41.2644538879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.6806297302246</t>
   </si>
   <si>
     <t xml:space="preserve">43.1201324462891</t>
@@ -3035,7 +3035,7 @@
     <t xml:space="preserve">42.4364585876465</t>
   </si>
   <si>
-    <t xml:space="preserve">41.5086212158203</t>
+    <t xml:space="preserve">41.508617401123</t>
   </si>
   <si>
     <t xml:space="preserve">41.0202827453613</t>
@@ -3044,7 +3044,7 @@
     <t xml:space="preserve">38.8715972900391</t>
   </si>
   <si>
-    <t xml:space="preserve">38.2367668151855</t>
+    <t xml:space="preserve">38.2367630004883</t>
   </si>
   <si>
     <t xml:space="preserve">39.0669364929199</t>
@@ -3059,31 +3059,31 @@
     <t xml:space="preserve">41.8504524230957</t>
   </si>
   <si>
-    <t xml:space="preserve">41.1179504394531</t>
+    <t xml:space="preserve">41.1179466247559</t>
   </si>
   <si>
     <t xml:space="preserve">40.8249473571777</t>
   </si>
   <si>
-    <t xml:space="preserve">41.6551246643066</t>
+    <t xml:space="preserve">41.6551208496094</t>
   </si>
   <si>
     <t xml:space="preserve">41.6062850952148</t>
   </si>
   <si>
-    <t xml:space="preserve">42.485294342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9736251831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8016166687012</t>
+    <t xml:space="preserve">42.4852905273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.9736289978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8016204833984</t>
   </si>
   <si>
     <t xml:space="preserve">41.362117767334</t>
   </si>
   <si>
-    <t xml:space="preserve">40.238941192627</t>
+    <t xml:space="preserve">40.2389488220215</t>
   </si>
   <si>
     <t xml:space="preserve">40.6296157836914</t>
@@ -3095,25 +3095,25 @@
     <t xml:space="preserve">43.4619674682617</t>
   </si>
   <si>
-    <t xml:space="preserve">43.999137878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.9226150512695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1157722473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5829620361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.6317939758301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5786018371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4299163818359</t>
+    <t xml:space="preserve">43.9991340637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.9226188659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1157684326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5829582214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.6317977905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.5785980224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4299201965332</t>
   </si>
   <si>
     <t xml:space="preserve">38.6274299621582</t>
@@ -3125,61 +3125,61 @@
     <t xml:space="preserve">35.7950820922852</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7207374572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5997428894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.527587890625</t>
+    <t xml:space="preserve">34.7207336425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5997505187988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.5275840759277</t>
   </si>
   <si>
     <t xml:space="preserve">36.6252517700195</t>
   </si>
   <si>
-    <t xml:space="preserve">36.0880813598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.1369132995605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4532470703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5253982543945</t>
+    <t xml:space="preserve">36.0880851745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.1369171142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4532432556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5254058837891</t>
   </si>
   <si>
     <t xml:space="preserve">36.3810844421387</t>
   </si>
   <si>
-    <t xml:space="preserve">35.3555755615234</t>
+    <t xml:space="preserve">35.3555793762207</t>
   </si>
   <si>
     <t xml:space="preserve">33.9393997192383</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1325531005859</t>
+    <t xml:space="preserve">32.1325607299805</t>
   </si>
   <si>
     <t xml:space="preserve">31.4977169036865</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6442222595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0115623474121</t>
+    <t xml:space="preserve">31.6442203521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0115585327148</t>
   </si>
   <si>
     <t xml:space="preserve">32.3767280578613</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4510612487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7695732116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5742416381836</t>
+    <t xml:space="preserve">33.4510650634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7695693969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5742378234863</t>
   </si>
   <si>
     <t xml:space="preserve">35.3067474365234</t>
@@ -3194,13 +3194,13 @@
     <t xml:space="preserve">33.5975646972656</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9627265930176</t>
+    <t xml:space="preserve">32.9627227783203</t>
   </si>
   <si>
     <t xml:space="preserve">32.5232238769531</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4255561828613</t>
+    <t xml:space="preserve">32.4255599975586</t>
   </si>
   <si>
     <t xml:space="preserve">32.6208915710449</t>
@@ -3212,13 +3212,13 @@
     <t xml:space="preserve">32.6697235107422</t>
   </si>
   <si>
-    <t xml:space="preserve">32.767391204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2144832611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0191459655762</t>
+    <t xml:space="preserve">32.7673950195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2144813537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0191478729248</t>
   </si>
   <si>
     <t xml:space="preserve">30.9019451141357</t>
@@ -3236,37 +3236,37 @@
     <t xml:space="preserve">32.0739555358887</t>
   </si>
   <si>
-    <t xml:space="preserve">31.937219619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3316860198975</t>
+    <t xml:space="preserve">31.9372215270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3316822052002</t>
   </si>
   <si>
     <t xml:space="preserve">32.1716194152832</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3902835845947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6637496948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8862075805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9643383026123</t>
+    <t xml:space="preserve">31.3902816772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6637516021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8862056732178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9643402099609</t>
   </si>
   <si>
     <t xml:space="preserve">28.3821277618408</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4993286132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2025337219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8704681396484</t>
+    <t xml:space="preserve">28.4993305206299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2025356292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8704643249512</t>
   </si>
   <si>
     <t xml:space="preserve">28.9290676116943</t>
@@ -3275,22 +3275,22 @@
     <t xml:space="preserve">29.085334777832</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3039970397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4211978912354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0147876739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3235301971436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5969982147217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2258605957031</t>
+    <t xml:space="preserve">28.3039932250977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4211959838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0147857666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3235282897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.596996307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2258625030518</t>
   </si>
   <si>
     <t xml:space="preserve">28.5579299926758</t>
@@ -3305,19 +3305,19 @@
     <t xml:space="preserve">26.5972957611084</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6765117645264</t>
+    <t xml:space="preserve">26.676513671875</t>
   </si>
   <si>
     <t xml:space="preserve">26.8745555877686</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5280990600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4784679412842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7359237670898</t>
+    <t xml:space="preserve">27.5281009674072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4784698486328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7359256744385</t>
   </si>
   <si>
     <t xml:space="preserve">27.2508392333984</t>
@@ -3326,13 +3326,13 @@
     <t xml:space="preserve">28.0628204345703</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3994941711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.320276260376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7657527923584</t>
+    <t xml:space="preserve">28.3994960784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3202781677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.765754699707</t>
   </si>
   <si>
     <t xml:space="preserve">27.9439926147461</t>
@@ -3350,16 +3350,16 @@
     <t xml:space="preserve">29.5481491088867</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1322555541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9933834075928</t>
+    <t xml:space="preserve">29.1322574615479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9933815002441</t>
   </si>
   <si>
     <t xml:space="preserve">24.9931392669678</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0129451751709</t>
+    <t xml:space="preserve">25.0129432678223</t>
   </si>
   <si>
     <t xml:space="preserve">25.6466846466064</t>
@@ -3401,10 +3401,10 @@
     <t xml:space="preserve">23.0523090362549</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5474185943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.200963973999</t>
+    <t xml:space="preserve">23.547420501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2009620666504</t>
   </si>
   <si>
     <t xml:space="preserve">23.6068325042725</t>
@@ -3419,16 +3419,16 @@
     <t xml:space="preserve">22.4185676574707</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5669822692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8146572113037</t>
+    <t xml:space="preserve">21.5669803619385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8146591186523</t>
   </si>
   <si>
     <t xml:space="preserve">22.9532890319824</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4188117980957</t>
+    <t xml:space="preserve">24.4188098907471</t>
   </si>
   <si>
     <t xml:space="preserve">23.7058544158936</t>
@@ -3437,7 +3437,7 @@
     <t xml:space="preserve">24.7356834411621</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5970497131348</t>
+    <t xml:space="preserve">24.597053527832</t>
   </si>
   <si>
     <t xml:space="preserve">25.1911849975586</t>
@@ -3449,13 +3449,13 @@
     <t xml:space="preserve">25.8249244689941</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0823802947998</t>
+    <t xml:space="preserve">26.0823822021484</t>
   </si>
   <si>
     <t xml:space="preserve">26.1615982055664</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3892250061035</t>
+    <t xml:space="preserve">25.3892269134521</t>
   </si>
   <si>
     <t xml:space="preserve">25.1317691802979</t>
@@ -3464,7 +3464,7 @@
     <t xml:space="preserve">25.5674667358398</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0427703857422</t>
+    <t xml:space="preserve">26.0427722930908</t>
   </si>
   <si>
     <t xml:space="preserve">26.1417922973633</t>
@@ -3485,7 +3485,7 @@
     <t xml:space="preserve">24.2207679748535</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1217460632324</t>
+    <t xml:space="preserve">24.1217479705811</t>
   </si>
   <si>
     <t xml:space="preserve">23.6860504150391</t>
@@ -3494,7 +3494,7 @@
     <t xml:space="preserve">24.3197898864746</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2603759765625</t>
+    <t xml:space="preserve">24.2603778839111</t>
   </si>
   <si>
     <t xml:space="preserve">24.3593978881836</t>
@@ -3503,7 +3503,7 @@
     <t xml:space="preserve">23.626636505127</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4980297088623</t>
+    <t xml:space="preserve">24.4980278015137</t>
   </si>
   <si>
     <t xml:space="preserve">23.8642902374268</t>
@@ -3512,7 +3512,7 @@
     <t xml:space="preserve">23.9435081481934</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7850704193115</t>
+    <t xml:space="preserve">23.7850723266602</t>
   </si>
   <si>
     <t xml:space="preserve">24.8743133544922</t>
@@ -3521,19 +3521,19 @@
     <t xml:space="preserve">24.9535312652588</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2999858856201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7652683258057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8344612121582</t>
+    <t xml:space="preserve">24.2999877929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7652645111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8344593048096</t>
   </si>
   <si>
     <t xml:space="preserve">22.5571994781494</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7156372070312</t>
+    <t xml:space="preserve">22.715633392334</t>
   </si>
   <si>
     <t xml:space="preserve">22.0422859191895</t>
@@ -3542,7 +3542,7 @@
     <t xml:space="preserve">21.071870803833</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1212596893311</t>
+    <t xml:space="preserve">20.1212577819824</t>
   </si>
   <si>
     <t xml:space="preserve">19.8638019561768</t>
@@ -3551,22 +3551,22 @@
     <t xml:space="preserve">20.0618476867676</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2696704864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8836059570312</t>
+    <t xml:space="preserve">19.2696685791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8836078643799</t>
   </si>
   <si>
     <t xml:space="preserve">20.2400875091553</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4481544494629</t>
+    <t xml:space="preserve">21.4481525421143</t>
   </si>
   <si>
     <t xml:space="preserve">20.9926528930664</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2501087188721</t>
+    <t xml:space="preserve">21.2501106262207</t>
   </si>
   <si>
     <t xml:space="preserve">21.2897186279297</t>
@@ -3584,7 +3584,7 @@
     <t xml:space="preserve">21.6065883636475</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0026741027832</t>
+    <t xml:space="preserve">22.0026760101318</t>
   </si>
   <si>
     <t xml:space="preserve">22.200719833374</t>
@@ -3608,7 +3608,7 @@
     <t xml:space="preserve">22.4383735656738</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7848262786865</t>
+    <t xml:space="preserve">21.7848281860352</t>
   </si>
   <si>
     <t xml:space="preserve">22.0620899200439</t>
@@ -3623,28 +3623,28 @@
     <t xml:space="preserve">23.6662445068359</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1415481567383</t>
+    <t xml:space="preserve">24.1415500640869</t>
   </si>
   <si>
     <t xml:space="preserve">25.7457065582275</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0329914093018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6369037628174</t>
+    <t xml:space="preserve">27.0329895019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6369018554688</t>
   </si>
   <si>
     <t xml:space="preserve">26.5576858520508</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9831161499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0525512695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2505970001221</t>
+    <t xml:space="preserve">23.9831123352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0525531768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2505950927734</t>
   </si>
   <si>
     <t xml:space="preserve">26.2012062072754</t>
@@ -3653,7 +3653,7 @@
     <t xml:space="preserve">26.4190540313721</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6963157653809</t>
+    <t xml:space="preserve">26.6963176727295</t>
   </si>
   <si>
     <t xml:space="preserve">26.7161197662354</t>
@@ -3674,28 +3674,28 @@
     <t xml:space="preserve">22.9730930328369</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7950973510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2704010009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1219902038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0625762939453</t>
+    <t xml:space="preserve">24.7950954437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2704029083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1219882965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0625743865967</t>
   </si>
   <si>
     <t xml:space="preserve">25.7853164672852</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2606201171875</t>
+    <t xml:space="preserve">26.2606220245361</t>
   </si>
   <si>
     <t xml:space="preserve">27.0725994110107</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7953395843506</t>
+    <t xml:space="preserve">26.795337677002</t>
   </si>
   <si>
     <t xml:space="preserve">28.0232105255127</t>
@@ -3704,13 +3704,13 @@
     <t xml:space="preserve">27.5875148773193</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4884929656982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6965618133545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7757759094238</t>
+    <t xml:space="preserve">27.4884948730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6965599060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7757778167725</t>
   </si>
   <si>
     <t xml:space="preserve">28.2212543487549</t>
@@ -3719,46 +3719,46 @@
     <t xml:space="preserve">28.5777339935303</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2806663513184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8153877258301</t>
+    <t xml:space="preserve">28.280668258667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8153858184814</t>
   </si>
   <si>
     <t xml:space="preserve">28.8747997283936</t>
   </si>
   <si>
-    <t xml:space="preserve">28.716365814209</t>
+    <t xml:space="preserve">28.7163639068604</t>
   </si>
   <si>
     <t xml:space="preserve">28.6569519042969</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9540176391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8549938201904</t>
+    <t xml:space="preserve">28.9540157318115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8549957275391</t>
   </si>
   <si>
     <t xml:space="preserve">28.9738216400146</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7955799102783</t>
+    <t xml:space="preserve">28.795581817627</t>
   </si>
   <si>
     <t xml:space="preserve">30.280912399292</t>
   </si>
   <si>
-    <t xml:space="preserve">29.924430847168</t>
+    <t xml:space="preserve">29.9244327545166</t>
   </si>
   <si>
     <t xml:space="preserve">29.9838466644287</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7065830230713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5877552032471</t>
+    <t xml:space="preserve">29.7065849304199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5877571105957</t>
   </si>
   <si>
     <t xml:space="preserve">29.33030128479</t>
@@ -3773,7 +3773,7 @@
     <t xml:space="preserve">29.2510833740234</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9342136383057</t>
+    <t xml:space="preserve">28.934211730957</t>
   </si>
   <si>
     <t xml:space="preserve">28.2608642578125</t>
@@ -3782,10 +3782,10 @@
     <t xml:space="preserve">27.805362701416</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3004722595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4787139892578</t>
+    <t xml:space="preserve">28.3004703521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4787120819092</t>
   </si>
   <si>
     <t xml:space="preserve">28.0430145263672</t>
@@ -3806,7 +3806,7 @@
     <t xml:space="preserve">25.6664886474609</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4782238006592</t>
+    <t xml:space="preserve">24.4782257080078</t>
   </si>
   <si>
     <t xml:space="preserve">23.3097667694092</t>
@@ -3815,19 +3815,19 @@
     <t xml:space="preserve">22.3789615631104</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2801837921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5574436187744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8347015380859</t>
+    <t xml:space="preserve">24.280179977417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5574417114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8347053527832</t>
   </si>
   <si>
     <t xml:space="preserve">25.0921611785889</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8447284698486</t>
+    <t xml:space="preserve">25.8447265625</t>
   </si>
   <si>
     <t xml:space="preserve">26.3893489837646</t>
@@ -3836,7 +3836,7 @@
     <t xml:space="preserve">27.0825023651123</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8349475860596</t>
+    <t xml:space="preserve">26.8349494934082</t>
   </si>
   <si>
     <t xml:space="preserve">27.2805442810059</t>
@@ -3848,16 +3848,16 @@
     <t xml:space="preserve">28.0727214813232</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7756538391113</t>
+    <t xml:space="preserve">27.77565574646</t>
   </si>
   <si>
     <t xml:space="preserve">27.6766357421875</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4290809631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.181526184082</t>
+    <t xml:space="preserve">27.4290790557861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1815242767334</t>
   </si>
   <si>
     <t xml:space="preserve">26.9339694976807</t>
@@ -3866,13 +3866,13 @@
     <t xml:space="preserve">27.3795680999756</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8844604492188</t>
+    <t xml:space="preserve">26.8844566345215</t>
   </si>
   <si>
     <t xml:space="preserve">27.7261447906494</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9834785461426</t>
+    <t xml:space="preserve">26.9834823608398</t>
   </si>
   <si>
     <t xml:space="preserve">27.330057144165</t>
@@ -3881,19 +3881,19 @@
     <t xml:space="preserve">27.6271228790283</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9241905212402</t>
+    <t xml:space="preserve">27.9241886138916</t>
   </si>
   <si>
     <t xml:space="preserve">28.4688110351562</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5085411071777</t>
+    <t xml:space="preserve">29.5085391998291</t>
   </si>
   <si>
     <t xml:space="preserve">30.5482711791992</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3007164001465</t>
+    <t xml:space="preserve">30.3007144927979</t>
   </si>
   <si>
     <t xml:space="preserve">30.944356918335</t>
@@ -3902,7 +3902,7 @@
     <t xml:space="preserve">32.0831146240234</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6375141143799</t>
+    <t xml:space="preserve">31.6375122070312</t>
   </si>
   <si>
     <t xml:space="preserve">32.1821327209473</t>
@@ -3914,22 +3914,22 @@
     <t xml:space="preserve">32.4296875</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2316436767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9840850830078</t>
+    <t xml:space="preserve">32.2316398620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9840888977051</t>
   </si>
   <si>
     <t xml:space="preserve">31.1919136047363</t>
   </si>
   <si>
-    <t xml:space="preserve">31.340446472168</t>
+    <t xml:space="preserve">31.3404445648193</t>
   </si>
   <si>
     <t xml:space="preserve">30.795825958252</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6472930908203</t>
+    <t xml:space="preserve">30.6472949981689</t>
   </si>
   <si>
     <t xml:space="preserve">30.2016944885254</t>
@@ -3938,13 +3938,13 @@
     <t xml:space="preserve">30.3997383117676</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2512035369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5977821350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4492492675781</t>
+    <t xml:space="preserve">30.2512054443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5977802276611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4492473602295</t>
   </si>
   <si>
     <t xml:space="preserve">29.9219970703125</t>
@@ -3953,13 +3953,13 @@
     <t xml:space="preserve">29.6237697601318</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8225860595703</t>
+    <t xml:space="preserve">29.8225879669189</t>
   </si>
   <si>
     <t xml:space="preserve">29.6734752655029</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4687423706055</t>
+    <t xml:space="preserve">30.4687442779541</t>
   </si>
   <si>
     <t xml:space="preserve">30.717264175415</t>
@@ -3971,10 +3971,10 @@
     <t xml:space="preserve">30.3196315765381</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1148986816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3137187957764</t>
+    <t xml:space="preserve">31.1149005889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3137168884277</t>
   </si>
   <si>
     <t xml:space="preserve">31.5125350952148</t>
@@ -3983,13 +3983,13 @@
     <t xml:space="preserve">31.1646041870117</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4131259918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0592842102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7551460266113</t>
+    <t xml:space="preserve">31.4131278991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0592803955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7551422119141</t>
   </si>
   <si>
     <t xml:space="preserve">31.8107604980469</t>
@@ -4001,7 +4001,7 @@
     <t xml:space="preserve">32.3575057983398</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8166732788086</t>
+    <t xml:space="preserve">30.8166751861572</t>
   </si>
   <si>
     <t xml:space="preserve">30.7669715881348</t>
@@ -4013,28 +4013,28 @@
     <t xml:space="preserve">28.0829372406006</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9894428253174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6912174224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.398904800415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3551120758057</t>
+    <t xml:space="preserve">26.9894409179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6912155151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3989028930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3551139831543</t>
   </si>
   <si>
     <t xml:space="preserve">24.8024520874023</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6533393859863</t>
+    <t xml:space="preserve">24.6533374786377</t>
   </si>
   <si>
     <t xml:space="preserve">24.4545211791992</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6036357879639</t>
+    <t xml:space="preserve">24.6036338806152</t>
   </si>
   <si>
     <t xml:space="preserve">24.4048175811768</t>
@@ -4055,13 +4055,13 @@
     <t xml:space="preserve">25.6971302032471</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9456520080566</t>
+    <t xml:space="preserve">25.945650100708</t>
   </si>
   <si>
     <t xml:space="preserve">25.2000865936279</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7030429840088</t>
+    <t xml:space="preserve">24.7030448913574</t>
   </si>
   <si>
     <t xml:space="preserve">25.647424697876</t>
@@ -4073,19 +4073,19 @@
     <t xml:space="preserve">26.8403282165527</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2935810089111</t>
+    <t xml:space="preserve">26.2935829162598</t>
   </si>
   <si>
     <t xml:space="preserve">25.7965393066406</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2994976043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5539302825928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7527484893799</t>
+    <t xml:space="preserve">25.2994956970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5539321899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7527465820312</t>
   </si>
   <si>
     <t xml:space="preserve">24.1065921783447</t>
@@ -4094,7 +4094,7 @@
     <t xml:space="preserve">24.5042266845703</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1562957763672</t>
+    <t xml:space="preserve">24.1562938690186</t>
   </si>
   <si>
     <t xml:space="preserve">25.3491992950439</t>
@@ -4106,16 +4106,16 @@
     <t xml:space="preserve">25.8462429046631</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5421047210693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4923973083496</t>
+    <t xml:space="preserve">26.5421028137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4923992156982</t>
   </si>
   <si>
     <t xml:space="preserve">26.4426956176758</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9397373199463</t>
+    <t xml:space="preserve">26.9397392272949</t>
   </si>
   <si>
     <t xml:space="preserve">27.6355972290039</t>
@@ -4136,7 +4136,7 @@
     <t xml:space="preserve">29.7231788635254</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6296844482422</t>
+    <t xml:space="preserve">28.6296825408936</t>
   </si>
   <si>
     <t xml:space="preserve">29.7728843688965</t>
@@ -4160,19 +4160,19 @@
     <t xml:space="preserve">27.7847118377686</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0332336425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1823463439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3752498626709</t>
+    <t xml:space="preserve">28.0332317352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1823444366455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3752479553223</t>
   </si>
   <si>
     <t xml:space="preserve">29.2261352539062</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5681533813477</t>
+    <t xml:space="preserve">30.568151473999</t>
   </si>
   <si>
     <t xml:space="preserve">31.5622386932373</t>
@@ -4202,7 +4202,7 @@
     <t xml:space="preserve">31.3634204864502</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9101676940918</t>
+    <t xml:space="preserve">31.9101657867432</t>
   </si>
   <si>
     <t xml:space="preserve">31.7610569000244</t>
@@ -4229,10 +4229,10 @@
     <t xml:space="preserve">30.6675624847412</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2640132904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3693332672119</t>
+    <t xml:space="preserve">31.2640151977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3693351745605</t>
   </si>
   <si>
     <t xml:space="preserve">30.6178569793701</t>
@@ -4241,13 +4241,13 @@
     <t xml:space="preserve">33.5504112243652</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6936149597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8486328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7989349365234</t>
+    <t xml:space="preserve">34.6936111450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8486366271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7989311218262</t>
   </si>
   <si>
     <t xml:space="preserve">34.1468620300293</t>
@@ -4262,16 +4262,16 @@
     <t xml:space="preserve">33.3018913269043</t>
   </si>
   <si>
-    <t xml:space="preserve">32.606029510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9042549133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5563278198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8048439025879</t>
+    <t xml:space="preserve">32.6060256958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9042510986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.556324005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8048477172852</t>
   </si>
   <si>
     <t xml:space="preserve">34.4947929382324</t>
@@ -4289,7 +4289,7 @@
     <t xml:space="preserve">37.1788291931152</t>
   </si>
   <si>
-    <t xml:space="preserve">36.781192779541</t>
+    <t xml:space="preserve">36.7811889648438</t>
   </si>
   <si>
     <t xml:space="preserve">36.3835563659668</t>
@@ -4301,10 +4301,10 @@
     <t xml:space="preserve">37.2285308837891</t>
   </si>
   <si>
-    <t xml:space="preserve">36.8805961608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.4711380004883</t>
+    <t xml:space="preserve">36.8805999755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.4711418151855</t>
   </si>
   <si>
     <t xml:space="preserve">37.9740943908691</t>
@@ -4316,16 +4316,16 @@
     <t xml:space="preserve">35.8368072509766</t>
   </si>
   <si>
-    <t xml:space="preserve">36.1350364685059</t>
+    <t xml:space="preserve">36.1350326538086</t>
   </si>
   <si>
     <t xml:space="preserve">34.7930183410645</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1409454345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4391746520996</t>
+    <t xml:space="preserve">35.1409492492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4391784667969</t>
   </si>
   <si>
     <t xml:space="preserve">34.2462730407715</t>
@@ -4334,13 +4334,13 @@
     <t xml:space="preserve">35.0415420532227</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6995239257812</t>
+    <t xml:space="preserve">33.6995277404785</t>
   </si>
   <si>
     <t xml:space="preserve">34.1965675354004</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6439056396484</t>
+    <t xml:space="preserve">34.6439018249512</t>
   </si>
   <si>
     <t xml:space="preserve">35.0912437438965</t>
@@ -4349,7 +4349,7 @@
     <t xml:space="preserve">34.5444984436035</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0474548339844</t>
+    <t xml:space="preserve">34.0474510192871</t>
   </si>
   <si>
     <t xml:space="preserve">34.8924293518066</t>
@@ -4358,13 +4358,13 @@
     <t xml:space="preserve">34.9421310424805</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7433128356934</t>
+    <t xml:space="preserve">34.7433166503906</t>
   </si>
   <si>
     <t xml:space="preserve">35.3894691467285</t>
   </si>
   <si>
-    <t xml:space="preserve">36.3338508605957</t>
+    <t xml:space="preserve">36.333854675293</t>
   </si>
   <si>
     <t xml:space="preserve">36.0853309631348</t>
@@ -4376,10 +4376,10 @@
     <t xml:space="preserve">37.7255744934082</t>
   </si>
   <si>
-    <t xml:space="preserve">38.620246887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5705490112305</t>
+    <t xml:space="preserve">38.6202507019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.5705451965332</t>
   </si>
   <si>
     <t xml:space="preserve">36.7314872741699</t>
@@ -4391,7 +4391,7 @@
     <t xml:space="preserve">37.327938079834</t>
   </si>
   <si>
-    <t xml:space="preserve">36.6817817687988</t>
+    <t xml:space="preserve">36.6817855834961</t>
   </si>
   <si>
     <t xml:space="preserve">36.9800109863281</t>
@@ -4409,7 +4409,7 @@
     <t xml:space="preserve">33.9480476379395</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3456802368164</t>
+    <t xml:space="preserve">34.3456764221191</t>
   </si>
   <si>
     <t xml:space="preserve">34.0971565246582</t>
@@ -4418,7 +4418,7 @@
     <t xml:space="preserve">35.2900619506836</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1906547546387</t>
+    <t xml:space="preserve">35.1906585693359</t>
   </si>
   <si>
     <t xml:space="preserve">33.8983383178711</t>
@@ -5112,6 +5112,9 @@
   </si>
   <si>
     <t xml:space="preserve">42.5999984741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.9000015258789</t>
   </si>
 </sst>
 </file>
@@ -9186,7 +9189,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G144" t="s">
-        <v>120</v>
+        <v>45</v>
       </c>
       <c r="H144" t="s">
         <v>9</v>
@@ -9212,7 +9215,7 @@
         <v>7.47499990463257</v>
       </c>
       <c r="G145" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H145" t="s">
         <v>9</v>
@@ -9238,7 +9241,7 @@
         <v>7.2649998664856</v>
       </c>
       <c r="G146" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H146" t="s">
         <v>9</v>
@@ -9290,7 +9293,7 @@
         <v>7.5</v>
       </c>
       <c r="G148" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H148" t="s">
         <v>9</v>
@@ -9316,7 +9319,7 @@
         <v>7.5</v>
       </c>
       <c r="G149" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H149" t="s">
         <v>9</v>
@@ -9342,7 +9345,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G150" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H150" t="s">
         <v>9</v>
@@ -9368,7 +9371,7 @@
         <v>7.2649998664856</v>
       </c>
       <c r="G151" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H151" t="s">
         <v>9</v>
@@ -9394,7 +9397,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G152" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H152" t="s">
         <v>9</v>
@@ -9420,7 +9423,7 @@
         <v>7.2350001335144</v>
       </c>
       <c r="G153" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H153" t="s">
         <v>9</v>
@@ -9446,7 +9449,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G154" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H154" t="s">
         <v>9</v>
@@ -9472,7 +9475,7 @@
         <v>7.5</v>
       </c>
       <c r="G155" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H155" t="s">
         <v>9</v>
@@ -9550,7 +9553,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G158" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H158" t="s">
         <v>9</v>
@@ -9576,7 +9579,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G159" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H159" t="s">
         <v>9</v>
@@ -9602,7 +9605,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G160" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H160" t="s">
         <v>9</v>
@@ -9628,7 +9631,7 @@
         <v>7.41499996185303</v>
       </c>
       <c r="G161" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H161" t="s">
         <v>9</v>
@@ -9680,7 +9683,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G163" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H163" t="s">
         <v>9</v>
@@ -9706,7 +9709,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G164" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H164" t="s">
         <v>9</v>
@@ -9758,7 +9761,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G166" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H166" t="s">
         <v>9</v>
@@ -9784,7 +9787,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G167" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H167" t="s">
         <v>9</v>
@@ -9810,7 +9813,7 @@
         <v>7.54500007629395</v>
       </c>
       <c r="G168" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H168" t="s">
         <v>9</v>
@@ -9836,7 +9839,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G169" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H169" t="s">
         <v>9</v>
@@ -9862,7 +9865,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G170" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H170" t="s">
         <v>9</v>
@@ -9888,7 +9891,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G171" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H171" t="s">
         <v>9</v>
@@ -9914,7 +9917,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G172" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H172" t="s">
         <v>9</v>
@@ -9940,7 +9943,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G173" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H173" t="s">
         <v>9</v>
@@ -9966,7 +9969,7 @@
         <v>7.72499990463257</v>
       </c>
       <c r="G174" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H174" t="s">
         <v>9</v>
@@ -10018,7 +10021,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G176" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H176" t="s">
         <v>9</v>
@@ -10200,7 +10203,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G183" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H183" t="s">
         <v>9</v>
@@ -10226,7 +10229,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G184" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H184" t="s">
         <v>9</v>
@@ -10252,7 +10255,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G185" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H185" t="s">
         <v>9</v>
@@ -10278,7 +10281,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G186" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H186" t="s">
         <v>9</v>
@@ -10330,7 +10333,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G188" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H188" t="s">
         <v>9</v>
@@ -10356,7 +10359,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G189" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H189" t="s">
         <v>9</v>
@@ -10408,7 +10411,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G191" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H191" t="s">
         <v>9</v>
@@ -10460,7 +10463,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G193" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H193" t="s">
         <v>9</v>
@@ -10486,7 +10489,7 @@
         <v>7.5</v>
       </c>
       <c r="G194" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H194" t="s">
         <v>9</v>
@@ -10512,7 +10515,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G195" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H195" t="s">
         <v>9</v>
@@ -10538,7 +10541,7 @@
         <v>7.67000007629395</v>
       </c>
       <c r="G196" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H196" t="s">
         <v>9</v>
@@ -10564,7 +10567,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G197" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H197" t="s">
         <v>9</v>
@@ -10590,7 +10593,7 @@
         <v>7.7350001335144</v>
       </c>
       <c r="G198" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H198" t="s">
         <v>9</v>
@@ -10616,7 +10619,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G199" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H199" t="s">
         <v>9</v>
@@ -10668,7 +10671,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G201" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H201" t="s">
         <v>9</v>
@@ -10694,7 +10697,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G202" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H202" t="s">
         <v>9</v>
@@ -10720,7 +10723,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G203" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H203" t="s">
         <v>9</v>
@@ -10772,7 +10775,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G205" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H205" t="s">
         <v>9</v>
@@ -10798,7 +10801,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G206" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H206" t="s">
         <v>9</v>
@@ -10824,7 +10827,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G207" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H207" t="s">
         <v>9</v>
@@ -10850,7 +10853,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G208" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H208" t="s">
         <v>9</v>
@@ -10876,7 +10879,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G209" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -10902,7 +10905,7 @@
         <v>7.81500005722046</v>
       </c>
       <c r="G210" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H210" t="s">
         <v>9</v>
@@ -10928,7 +10931,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G211" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H211" t="s">
         <v>9</v>
@@ -10954,7 +10957,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G212" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H212" t="s">
         <v>9</v>
@@ -11032,7 +11035,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G215" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -11058,7 +11061,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G216" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -11084,7 +11087,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G217" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -11136,7 +11139,7 @@
         <v>7.95499992370605</v>
       </c>
       <c r="G219" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -11188,7 +11191,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G221" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -11214,7 +11217,7 @@
         <v>8.15499973297119</v>
       </c>
       <c r="G222" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -11266,7 +11269,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G224" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -11292,7 +11295,7 @@
         <v>7.61499977111816</v>
       </c>
       <c r="G225" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -11318,7 +11321,7 @@
         <v>7.5</v>
       </c>
       <c r="G226" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -11344,7 +11347,7 @@
         <v>7.78499984741211</v>
       </c>
       <c r="G227" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -11370,7 +11373,7 @@
         <v>7.94500017166138</v>
       </c>
       <c r="G228" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -11396,7 +11399,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G229" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -11422,7 +11425,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G230" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -11578,7 +11581,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G236" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -11604,7 +11607,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G237" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -11656,7 +11659,7 @@
         <v>7.94500017166138</v>
       </c>
       <c r="G239" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H239" t="s">
         <v>9</v>
@@ -11708,7 +11711,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G241" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H241" t="s">
         <v>9</v>
@@ -11734,7 +11737,7 @@
         <v>8.27499961853027</v>
       </c>
       <c r="G242" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H242" t="s">
         <v>9</v>
@@ -11760,7 +11763,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G243" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -11812,7 +11815,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G245" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H245" t="s">
         <v>9</v>
@@ -11838,7 +11841,7 @@
         <v>7.94500017166138</v>
       </c>
       <c r="G246" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -11864,7 +11867,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G247" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H247" t="s">
         <v>9</v>
@@ -11890,7 +11893,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G248" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -11916,7 +11919,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G249" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H249" t="s">
         <v>9</v>
@@ -11942,7 +11945,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G250" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -11968,7 +11971,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G251" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -11994,7 +11997,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G252" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H252" t="s">
         <v>9</v>
@@ -12020,7 +12023,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G253" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H253" t="s">
         <v>9</v>
@@ -12046,7 +12049,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G254" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -12072,7 +12075,7 @@
         <v>8.5</v>
       </c>
       <c r="G255" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -12098,7 +12101,7 @@
         <v>8.49499988555908</v>
       </c>
       <c r="G256" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H256" t="s">
         <v>9</v>
@@ -12124,7 +12127,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G257" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -12150,7 +12153,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G258" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -12176,7 +12179,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G259" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -12202,7 +12205,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G260" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -12228,7 +12231,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G261" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -12254,7 +12257,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G262" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -12280,7 +12283,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G263" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -12306,7 +12309,7 @@
         <v>9.27000045776367</v>
       </c>
       <c r="G264" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -12332,7 +12335,7 @@
         <v>9.30500030517578</v>
       </c>
       <c r="G265" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -12358,7 +12361,7 @@
         <v>9.25</v>
       </c>
       <c r="G266" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -12384,7 +12387,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G267" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -12410,7 +12413,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G268" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -12436,7 +12439,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G269" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -12462,7 +12465,7 @@
         <v>9.22500038146973</v>
       </c>
       <c r="G270" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -12488,7 +12491,7 @@
         <v>9.25</v>
       </c>
       <c r="G271" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -12514,7 +12517,7 @@
         <v>9.21500015258789</v>
       </c>
       <c r="G272" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -12540,7 +12543,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G273" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -12566,7 +12569,7 @@
         <v>9.25500011444092</v>
       </c>
       <c r="G274" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -12592,7 +12595,7 @@
         <v>9.26500034332275</v>
       </c>
       <c r="G275" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H275" t="s">
         <v>9</v>
@@ -12618,7 +12621,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G276" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -12644,7 +12647,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G277" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -12670,7 +12673,7 @@
         <v>9.1850004196167</v>
       </c>
       <c r="G278" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -12696,7 +12699,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G279" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -12722,7 +12725,7 @@
         <v>9.22500038146973</v>
       </c>
       <c r="G280" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -12748,7 +12751,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G281" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -12774,7 +12777,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G282" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -12800,7 +12803,7 @@
         <v>9.25</v>
       </c>
       <c r="G283" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -12826,7 +12829,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G284" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -12852,7 +12855,7 @@
         <v>8.9350004196167</v>
       </c>
       <c r="G285" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -12878,7 +12881,7 @@
         <v>8.97500038146973</v>
       </c>
       <c r="G286" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -12904,7 +12907,7 @@
         <v>9.16499996185303</v>
       </c>
       <c r="G287" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -12930,7 +12933,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G288" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -12956,7 +12959,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G289" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -12982,7 +12985,7 @@
         <v>9.38500022888184</v>
       </c>
       <c r="G290" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -13008,7 +13011,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G291" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -13034,7 +13037,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G292" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -13060,7 +13063,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G293" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -13086,7 +13089,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G294" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -13112,7 +13115,7 @@
         <v>9.10499954223633</v>
       </c>
       <c r="G295" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -13138,7 +13141,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G296" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -13164,7 +13167,7 @@
         <v>8.88500022888184</v>
       </c>
       <c r="G297" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -13190,7 +13193,7 @@
         <v>9</v>
       </c>
       <c r="G298" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -13216,7 +13219,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G299" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -13242,7 +13245,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G300" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -13268,7 +13271,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G301" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -13294,7 +13297,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G302" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -13320,7 +13323,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G303" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -13346,7 +13349,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G304" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -13372,7 +13375,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G305" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -13398,7 +13401,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G306" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -13424,7 +13427,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G307" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -13450,7 +13453,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G308" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -13476,7 +13479,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G309" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -13502,7 +13505,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G310" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -13528,7 +13531,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G311" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -13554,7 +13557,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G312" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -13580,7 +13583,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G313" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -13606,7 +13609,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G314" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -13632,7 +13635,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G315" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -13658,7 +13661,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G316" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -13684,7 +13687,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G317" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -13710,7 +13713,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G318" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -13736,7 +13739,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G319" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -13762,7 +13765,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G320" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -13788,7 +13791,7 @@
         <v>10</v>
       </c>
       <c r="G321" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -13814,7 +13817,7 @@
         <v>10</v>
       </c>
       <c r="G322" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -13840,7 +13843,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G323" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -13866,7 +13869,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G324" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -13892,7 +13895,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G325" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -13918,7 +13921,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G326" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -13944,7 +13947,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G327" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -13970,7 +13973,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G328" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -13996,7 +13999,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G329" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -14022,7 +14025,7 @@
         <v>10.5699996948242</v>
       </c>
       <c r="G330" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -14048,7 +14051,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G331" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -14074,7 +14077,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G332" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -14100,7 +14103,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G333" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -14126,7 +14129,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G334" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -14152,7 +14155,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G335" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -14178,7 +14181,7 @@
         <v>11</v>
       </c>
       <c r="G336" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -14204,7 +14207,7 @@
         <v>11.5600004196167</v>
       </c>
       <c r="G337" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
@@ -14230,7 +14233,7 @@
         <v>12</v>
       </c>
       <c r="G338" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -14256,7 +14259,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G339" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -14282,7 +14285,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G340" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -14308,7 +14311,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G341" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -14334,7 +14337,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G342" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -14360,7 +14363,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G343" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -14386,7 +14389,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G344" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -14412,7 +14415,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G345" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -14438,7 +14441,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G346" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -14464,7 +14467,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G347" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -14490,7 +14493,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G348" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -14516,7 +14519,7 @@
         <v>11.25</v>
       </c>
       <c r="G349" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -14542,7 +14545,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G350" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -14568,7 +14571,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G351" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -14594,7 +14597,7 @@
         <v>11.0900001525879</v>
       </c>
       <c r="G352" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -14620,7 +14623,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G353" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -14646,7 +14649,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G354" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -14672,7 +14675,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G355" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -14698,7 +14701,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G356" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -14724,7 +14727,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G357" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -14750,7 +14753,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G358" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -14776,7 +14779,7 @@
         <v>11.25</v>
       </c>
       <c r="G359" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -14802,7 +14805,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G360" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -14828,7 +14831,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G361" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -14854,7 +14857,7 @@
         <v>11.3699998855591</v>
       </c>
       <c r="G362" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -14880,7 +14883,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G363" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -14906,7 +14909,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G364" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -14932,7 +14935,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G365" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -14958,7 +14961,7 @@
         <v>12.5</v>
       </c>
       <c r="G366" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -14984,7 +14987,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G367" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -15010,7 +15013,7 @@
         <v>12.1899995803833</v>
       </c>
       <c r="G368" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -15036,7 +15039,7 @@
         <v>11.9700002670288</v>
       </c>
       <c r="G369" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -15062,7 +15065,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G370" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -15088,7 +15091,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G371" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -15114,7 +15117,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G372" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -15140,7 +15143,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G373" t="s">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -17480,7 +17483,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G463" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -17532,7 +17535,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G465" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -17766,7 +17769,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G474" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -18078,7 +18081,7 @@
         <v>12.5</v>
       </c>
       <c r="G486" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -19846,7 +19849,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G554" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -70658,7 +70661,7 @@
     </row>
     <row r="2509">
       <c r="A2509" s="1" t="n">
-        <v>45972.6910763889</v>
+        <v>45972.3333333333</v>
       </c>
       <c r="B2509" t="n">
         <v>12392</v>
@@ -70679,6 +70682,32 @@
         <v>1699</v>
       </c>
       <c r="H2509" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2510">
+      <c r="A2510" s="1" t="n">
+        <v>45973.6910648148</v>
+      </c>
+      <c r="B2510" t="n">
+        <v>48491</v>
+      </c>
+      <c r="C2510" t="n">
+        <v>43.2000007629395</v>
+      </c>
+      <c r="D2510" t="n">
+        <v>41.6500015258789</v>
+      </c>
+      <c r="E2510" t="n">
+        <v>43.2000007629395</v>
+      </c>
+      <c r="F2510" t="n">
+        <v>41.9000015258789</v>
+      </c>
+      <c r="G2510" t="s">
+        <v>1700</v>
+      </c>
+      <c r="H2510" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MOL.MI.xlsx
+++ b/data/MOL.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1705" uniqueCount="1705">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1706" uniqueCount="1706">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85066175460815</t>
+    <t xml:space="preserve">6.850661277771</t>
   </si>
   <si>
     <t xml:space="preserve">MOL.MI</t>
@@ -47,22 +47,22 @@
     <t xml:space="preserve">6.75772619247437</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66036510467529</t>
+    <t xml:space="preserve">6.66036605834961</t>
   </si>
   <si>
     <t xml:space="preserve">6.77100276947021</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63823843002319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72674751281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81525802612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54972839355469</t>
+    <t xml:space="preserve">6.63823795318604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72674798965454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81525754928589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54972887039185</t>
   </si>
   <si>
     <t xml:space="preserve">6.31960201263428</t>
@@ -74,31 +74,31 @@
     <t xml:space="preserve">6.35058069229126</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23994398117065</t>
+    <t xml:space="preserve">6.2399435043335</t>
   </si>
   <si>
     <t xml:space="preserve">6.5585789680481</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46121835708618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8947548866272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52317476272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65594100952148</t>
+    <t xml:space="preserve">6.46121883392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89475536346436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52317523956299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65594053268433</t>
   </si>
   <si>
     <t xml:space="preserve">6.76215171813965</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66479158401489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69134330749512</t>
+    <t xml:space="preserve">6.66479110717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69134473800659</t>
   </si>
   <si>
     <t xml:space="preserve">6.68249368667603</t>
@@ -107,10 +107,10 @@
     <t xml:space="preserve">6.01866912841797</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89918088912964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28419923782349</t>
+    <t xml:space="preserve">5.89918041229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28419828414917</t>
   </si>
   <si>
     <t xml:space="preserve">6.06292390823364</t>
@@ -125,73 +125,73 @@
     <t xml:space="preserve">6.34173011779785</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50989866256714</t>
+    <t xml:space="preserve">6.50989770889282</t>
   </si>
   <si>
     <t xml:space="preserve">6.33287906646729</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42581462860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39040994644165</t>
+    <t xml:space="preserve">6.42581415176392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39041042327881</t>
   </si>
   <si>
     <t xml:space="preserve">6.30632591247559</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40811157226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35500574111938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63381242752075</t>
+    <t xml:space="preserve">6.40811204910278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35500621795654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63381290435791</t>
   </si>
   <si>
     <t xml:space="preserve">6.43466567993164</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2266674041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2443699836731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27534770965576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26649618148804</t>
+    <t xml:space="preserve">6.22666597366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24436902999878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2753472328186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2664966583252</t>
   </si>
   <si>
     <t xml:space="preserve">6.62938690185547</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43909120559692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41253852844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4523663520813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45679235458374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36828374862671</t>
+    <t xml:space="preserve">6.43909072875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41253757476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45236778259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4567928314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36828327178955</t>
   </si>
   <si>
     <t xml:space="preserve">6.19568920135498</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06734991073608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28862476348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20453977584839</t>
+    <t xml:space="preserve">6.06734943389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28862380981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20454025268555</t>
   </si>
   <si>
     <t xml:space="preserve">6.29304981231689</t>
@@ -203,28 +203,28 @@
     <t xml:space="preserve">6.22224140167236</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25764560699463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15585899353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19126415252686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58955764770508</t>
+    <t xml:space="preserve">6.25764608383179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15585994720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1912636756897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58955812454224</t>
   </si>
   <si>
     <t xml:space="preserve">6.47892093658447</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49662208557129</t>
+    <t xml:space="preserve">6.49662256240845</t>
   </si>
   <si>
     <t xml:space="preserve">6.42138910293579</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63348913192749</t>
+    <t xml:space="preserve">6.63349008560181</t>
   </si>
   <si>
     <t xml:space="preserve">6.45273971557617</t>
@@ -233,82 +233,82 @@
     <t xml:space="preserve">6.54311466217041</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44370317459106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50696468353271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55667161941528</t>
+    <t xml:space="preserve">6.44370222091675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50696516036987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55667114257812</t>
   </si>
   <si>
     <t xml:space="preserve">6.36688470840454</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61993265151978</t>
+    <t xml:space="preserve">6.61993312835693</t>
   </si>
   <si>
     <t xml:space="preserve">6.69223356246948</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59734010696411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6831955909729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70578861236572</t>
+    <t xml:space="preserve">6.59733963012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68319511413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70578908920288</t>
   </si>
   <si>
     <t xml:space="preserve">6.75097608566284</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85038805007935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94528198242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9859504699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1034369468689</t>
+    <t xml:space="preserve">6.8503885269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94528102874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98594951629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10343742370605</t>
   </si>
   <si>
     <t xml:space="preserve">7.25255441665649</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32033586502075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45589780807495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3022608757019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37907838821411</t>
+    <t xml:space="preserve">7.32033634185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45589685440063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30226039886475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37907886505127</t>
   </si>
   <si>
     <t xml:space="preserve">7.25707340240479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22996187210083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22544288635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19833087921143</t>
+    <t xml:space="preserve">7.22996139526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22544240951538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19833040237427</t>
   </si>
   <si>
     <t xml:space="preserve">7.09439945220947</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13958692550659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00402498245239</t>
+    <t xml:space="preserve">7.13958597183228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00402545928955</t>
   </si>
   <si>
     <t xml:space="preserve">7.08084297180176</t>
@@ -317,34 +317,34 @@
     <t xml:space="preserve">6.95883750915527</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84135103225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11699342727661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16669893264771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31129837036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32485437393188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9995059967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73290109634399</t>
+    <t xml:space="preserve">6.84135150909424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11699295043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16669940948486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31129932403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32485389709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99950647354126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73290157318115</t>
   </si>
   <si>
     <t xml:space="preserve">7.08988046646118</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18477439880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85942602157593</t>
+    <t xml:space="preserve">7.18477392196655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85942649841309</t>
   </si>
   <si>
     <t xml:space="preserve">6.67867612838745</t>
@@ -353,13 +353,13 @@
     <t xml:space="preserve">6.49792766571045</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57022714614868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57926416397095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41659069061279</t>
+    <t xml:space="preserve">6.57022666931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57926511764526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41659021377563</t>
   </si>
   <si>
     <t xml:space="preserve">6.74645757675171</t>
@@ -371,25 +371,25 @@
     <t xml:space="preserve">6.55215215682983</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46177816390991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75549554824829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56570816040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77808904647827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71030807495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48888969421387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53859567642212</t>
+    <t xml:space="preserve">6.46177768707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75549507141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56570768356323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77808856964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71030712127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48889017105103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53859615325928</t>
   </si>
   <si>
     <t xml:space="preserve">6.6606011390686</t>
@@ -398,52 +398,52 @@
     <t xml:space="preserve">6.68771362304688</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76001405715942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87750053405762</t>
+    <t xml:space="preserve">6.76001358032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87750005722046</t>
   </si>
   <si>
     <t xml:space="preserve">6.70127058029175</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78712606430054</t>
+    <t xml:space="preserve">6.7871265411377</t>
   </si>
   <si>
     <t xml:space="preserve">6.79616403579712</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81423759460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81875705718994</t>
+    <t xml:space="preserve">6.81423854827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8187575340271</t>
   </si>
   <si>
     <t xml:space="preserve">6.82327604293823</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8052020072937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92268800735474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90461301803589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86846303939819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98143100738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17573642730713</t>
+    <t xml:space="preserve">6.80520105361938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92268753051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90461254119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86846256256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98143148422241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17573690414429</t>
   </si>
   <si>
     <t xml:space="preserve">7.01306247711182</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97691249847412</t>
+    <t xml:space="preserve">6.97691202163696</t>
   </si>
   <si>
     <t xml:space="preserve">6.64252662658691</t>
@@ -452,7 +452,7 @@
     <t xml:space="preserve">6.69675159454346</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88653802871704</t>
+    <t xml:space="preserve">6.88653755187988</t>
   </si>
   <si>
     <t xml:space="preserve">6.93172550201416</t>
@@ -464,31 +464,31 @@
     <t xml:space="preserve">6.99046897888184</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19381093978882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05824947357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04921245574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06728649139404</t>
+    <t xml:space="preserve">7.19381141662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05824899673462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04921197891235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0672869682312</t>
   </si>
   <si>
     <t xml:space="preserve">7.14862442016602</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08536243438721</t>
+    <t xml:space="preserve">7.08536195755005</t>
   </si>
   <si>
     <t xml:space="preserve">7.06276845932007</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15766191482544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21188592910767</t>
+    <t xml:space="preserve">7.15766096115112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21188640594482</t>
   </si>
   <si>
     <t xml:space="preserve">7.38359832763672</t>
@@ -497,25 +497,25 @@
     <t xml:space="preserve">7.22092342376709</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24803590774536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18929243087769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35648584365845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37004232406616</t>
+    <t xml:space="preserve">7.24803686141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.189293384552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35648632049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.370041847229</t>
   </si>
   <si>
     <t xml:space="preserve">6.88201904296875</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0356559753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18025541305542</t>
+    <t xml:space="preserve">7.03565549850464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18025493621826</t>
   </si>
   <si>
     <t xml:space="preserve">6.91365003585815</t>
@@ -524,175 +524,175 @@
     <t xml:space="preserve">7.51915884017944</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47849035263062</t>
+    <t xml:space="preserve">7.47849082946777</t>
   </si>
   <si>
     <t xml:space="preserve">7.50108432769775</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41071033477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27514791488647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60953378677368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66375923156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72702264785767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68183326721191</t>
+    <t xml:space="preserve">7.41070938110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27514839172363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60953426361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66375827789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72702074050903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6818323135376</t>
   </si>
   <si>
     <t xml:space="preserve">7.67731475830078</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63664722442627</t>
+    <t xml:space="preserve">7.63664674758911</t>
   </si>
   <si>
     <t xml:space="preserve">7.77220964431763</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97103214263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34156703948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41386795043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45001792907715</t>
+    <t xml:space="preserve">7.971031665802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34156608581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41386985778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45001888275146</t>
   </si>
   <si>
     <t xml:space="preserve">8.57654094696045</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37771701812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40934753417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35964298248291</t>
+    <t xml:space="preserve">8.37771797180176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40935039520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35964202880859</t>
   </si>
   <si>
     <t xml:space="preserve">8.22408199310303</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24215602874756</t>
+    <t xml:space="preserve">8.24215507507324</t>
   </si>
   <si>
     <t xml:space="preserve">8.33704948425293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32801055908203</t>
+    <t xml:space="preserve">8.32801342010498</t>
   </si>
   <si>
     <t xml:space="preserve">8.3234920501709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36416244506836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37319946289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46809101104736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30541801452637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30089950561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09755516052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26926612854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20600605010986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0749626159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11111164093018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28282451629639</t>
+    <t xml:space="preserve">8.36416149139404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37319850921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46809196472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30541706085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30089855194092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09755611419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26926803588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20600700378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07496166229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11111259460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28282356262207</t>
   </si>
   <si>
     <t xml:space="preserve">8.2963809967041</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40483093261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48164939880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42290496826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22859859466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2737865447998</t>
+    <t xml:space="preserve">8.40482997894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48164749145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42290592193604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22859954833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27378463745117</t>
   </si>
   <si>
     <t xml:space="preserve">8.02977561950684</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13370800018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27830696105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43194103240967</t>
+    <t xml:space="preserve">8.13370704650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27830600738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4319429397583</t>
   </si>
   <si>
     <t xml:space="preserve">8.6940279006958</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57969951629639</t>
+    <t xml:space="preserve">9.57969856262207</t>
   </si>
   <si>
     <t xml:space="preserve">9.25434970855713</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21820068359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01937580108643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16397666931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2001256942749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20916366577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22723865509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94707679748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03745079040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12782573699951</t>
+    <t xml:space="preserve">9.21819972991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01937484741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16397571563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20012664794922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20916175842285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22723770141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94707584381104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03745174407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12782669067383</t>
   </si>
   <si>
     <t xml:space="preserve">9.35376358032227</t>
@@ -701,28 +701,28 @@
     <t xml:space="preserve">9.55258655548096</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4712495803833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80563640594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89600849151611</t>
+    <t xml:space="preserve">9.47124862670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80563545227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89601039886475</t>
   </si>
   <si>
     <t xml:space="preserve">10.2123193740845</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94119644165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4472942352295</t>
+    <t xml:space="preserve">9.94119548797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4472951889038</t>
   </si>
   <si>
     <t xml:space="preserve">10.8449411392212</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8087930679321</t>
+    <t xml:space="preserve">10.8087902069092</t>
   </si>
   <si>
     <t xml:space="preserve">10.908203125</t>
@@ -740,28 +740,28 @@
     <t xml:space="preserve">10.7545671463013</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4764308929443</t>
+    <t xml:space="preserve">10.4764318466187</t>
   </si>
   <si>
     <t xml:space="preserve">10.2261095046997</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0128726959229</t>
+    <t xml:space="preserve">10.0128736495972</t>
   </si>
   <si>
     <t xml:space="preserve">10.3837194442749</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4300756454468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2817373275757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4022617340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5135164260864</t>
+    <t xml:space="preserve">10.4300765991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.28173828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4022626876831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5135183334351</t>
   </si>
   <si>
     <t xml:space="preserve">10.4949741363525</t>
@@ -770,13 +770,13 @@
     <t xml:space="preserve">10.5413303375244</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7452955245972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0790596008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7743968963623</t>
+    <t xml:space="preserve">10.7452964782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0790576934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.774395942688</t>
   </si>
   <si>
     <t xml:space="preserve">11.5889730453491</t>
@@ -788,19 +788,22 @@
     <t xml:space="preserve">11.3015661239624</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0976009368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1439571380615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0327024459839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8287363052368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7360248565674</t>
+    <t xml:space="preserve">11.0975999832153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1439561843872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0327033996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8287372589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7545680999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7360258102417</t>
   </si>
   <si>
     <t xml:space="preserve">10.9863471984863</t>
@@ -809,13 +812,13 @@
     <t xml:space="preserve">10.8658208847046</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5691423416138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1254148483276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0605163574219</t>
+    <t xml:space="preserve">10.5691432952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1254138946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0605154037476</t>
   </si>
   <si>
     <t xml:space="preserve">11.4869909286499</t>
@@ -824,52 +827,52 @@
     <t xml:space="preserve">11.0697870254517</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9399919509888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4499044418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4035501480103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7094984054565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0988874435425</t>
+    <t xml:space="preserve">10.9399909973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4499063491821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4035491943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7094993591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0988883972168</t>
   </si>
   <si>
     <t xml:space="preserve">12.3213958740234</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8949222564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5160903930664</t>
+    <t xml:space="preserve">11.894923210144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5160913467407</t>
   </si>
   <si>
     <t xml:space="preserve">12.5253629684448</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6737003326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7478713989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5346326828003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.794225692749</t>
+    <t xml:space="preserve">12.6737012863159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7478704452515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5346336364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7942266464233</t>
   </si>
   <si>
     <t xml:space="preserve">12.7293281555176</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5439052581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5809888839722</t>
+    <t xml:space="preserve">12.5439033508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5809879302979</t>
   </si>
   <si>
     <t xml:space="preserve">12.5624475479126</t>
@@ -878,25 +881,25 @@
     <t xml:space="preserve">12.4697360992432</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4975471496582</t>
+    <t xml:space="preserve">12.4975481033325</t>
   </si>
   <si>
     <t xml:space="preserve">12.4882783889771</t>
   </si>
   <si>
-    <t xml:space="preserve">12.68297290802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.627345085144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5531759262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1823291778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3955659866333</t>
+    <t xml:space="preserve">12.6829719543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6273441314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5531749725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1823272705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.395565032959</t>
   </si>
   <si>
     <t xml:space="preserve">12.4233798980713</t>
@@ -905,22 +908,22 @@
     <t xml:space="preserve">12.2935829162598</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3677530288696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8856525421143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.28431224823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1730575561523</t>
+    <t xml:space="preserve">12.3677520751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8856506347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2843112945557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1730585098267</t>
   </si>
   <si>
     <t xml:space="preserve">12.0525312423706</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9505481719971</t>
+    <t xml:space="preserve">11.9505491256714</t>
   </si>
   <si>
     <t xml:space="preserve">12.3121252059937</t>
@@ -929,19 +932,19 @@
     <t xml:space="preserve">12.2657690048218</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9412784576416</t>
+    <t xml:space="preserve">11.9412794113159</t>
   </si>
   <si>
     <t xml:space="preserve">11.9598207473755</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3306674957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4419202804565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3492107391357</t>
+    <t xml:space="preserve">12.3306655883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4419221878052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3492097854614</t>
   </si>
   <si>
     <t xml:space="preserve">12.3770246505737</t>
@@ -956,10 +959,10 @@
     <t xml:space="preserve">12.3399391174316</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4511947631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2008724212646</t>
+    <t xml:space="preserve">12.4511938095093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.200870513916</t>
   </si>
   <si>
     <t xml:space="preserve">12.4326496124268</t>
@@ -968,91 +971,91 @@
     <t xml:space="preserve">12.3028545379639</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2564992904663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.061803817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0247192382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.440634727478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6353282928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7929391860962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.663143157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6816873550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7465829849243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9227352142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8207521438599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8671092987061</t>
+    <t xml:space="preserve">12.256498336792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0618028640747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0247182846069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4406356811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.635329246521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7929401397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6631441116333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6816864013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7465848922729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9227361679077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8207530975342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8671073913574</t>
   </si>
   <si>
     <t xml:space="preserve">11.7373123168945</t>
   </si>
   <si>
-    <t xml:space="preserve">12.228684425354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1915979385376</t>
+    <t xml:space="preserve">12.2286853790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1916007995605</t>
   </si>
   <si>
     <t xml:space="preserve">11.7651252746582</t>
   </si>
   <si>
-    <t xml:space="preserve">11.718770980835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1903114318848</t>
+    <t xml:space="preserve">11.7187700271606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1903142929077</t>
   </si>
   <si>
     <t xml:space="preserve">11.2922964096069</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1624994277954</t>
+    <t xml:space="preserve">11.1624984741211</t>
   </si>
   <si>
     <t xml:space="preserve">11.5426177978516</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4684476852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5982456207275</t>
+    <t xml:space="preserve">11.468448638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5982446670532</t>
   </si>
   <si>
     <t xml:space="preserve">11.579701423645</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4962615966797</t>
+    <t xml:space="preserve">11.4962606430054</t>
   </si>
   <si>
     <t xml:space="preserve">11.6724138259888</t>
   </si>
   <si>
-    <t xml:space="preserve">11.857837677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1452436447144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.006175994873</t>
+    <t xml:space="preserve">11.8578367233276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1452445983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0061769485474</t>
   </si>
   <si>
     <t xml:space="preserve">11.9134645462036</t>
@@ -1061,7 +1064,7 @@
     <t xml:space="preserve">12.9240217208862</t>
   </si>
   <si>
-    <t xml:space="preserve">13.925311088562</t>
+    <t xml:space="preserve">13.9253101348877</t>
   </si>
   <si>
     <t xml:space="preserve">14.1107339859009</t>
@@ -1070,46 +1073,46 @@
     <t xml:space="preserve">14.092191696167</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9438533782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9994812011719</t>
+    <t xml:space="preserve">13.9438524246216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9994802474976</t>
   </si>
   <si>
     <t xml:space="preserve">14.6299200057983</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9067687988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6286325454712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2034463882446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0180215835571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7027997970581</t>
+    <t xml:space="preserve">13.9067697525024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6286334991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2034454345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0180225372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7028017044067</t>
   </si>
   <si>
     <t xml:space="preserve">14.3888692855835</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5186672210693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5742931365967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4815816879272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1849021911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8325986862183</t>
+    <t xml:space="preserve">14.5186653137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.574294090271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4815807342529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1849040985107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8325996398926</t>
   </si>
   <si>
     <t xml:space="preserve">12.9981927871704</t>
@@ -1118,10 +1121,10 @@
     <t xml:space="preserve">12.7756834030151</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3690395355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0352764129639</t>
+    <t xml:space="preserve">13.3690385818481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0352773666382</t>
   </si>
   <si>
     <t xml:space="preserve">12.7385988235474</t>
@@ -1133,25 +1136,25 @@
     <t xml:space="preserve">13.5173778533936</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3134117126465</t>
+    <t xml:space="preserve">13.3134136199951</t>
   </si>
   <si>
     <t xml:space="preserve">12.6644296646118</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1081609725952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0154466629028</t>
+    <t xml:space="preserve">12.1081590652466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0154476165771</t>
   </si>
   <si>
     <t xml:space="preserve">11.830023765564</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5902614593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7200565338135</t>
+    <t xml:space="preserve">12.5902605056763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7200593948364</t>
   </si>
   <si>
     <t xml:space="preserve">12.6088027954102</t>
@@ -1163,16 +1166,16 @@
     <t xml:space="preserve">12.0339889526367</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0710754394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6075172424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4604644775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8114805221558</t>
+    <t xml:space="preserve">12.0710744857788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.607515335083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4604625701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8114814758301</t>
   </si>
   <si>
     <t xml:space="preserve">11.8485660552979</t>
@@ -1181,88 +1184,88 @@
     <t xml:space="preserve">12.2379560470581</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3862943649292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3504962921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5359220504761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7213430404663</t>
+    <t xml:space="preserve">12.3862953186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3504981994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5359210968018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7213439941406</t>
   </si>
   <si>
     <t xml:space="preserve">14.2590742111206</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9080562591553</t>
+    <t xml:space="preserve">14.908055305481</t>
   </si>
   <si>
     <t xml:space="preserve">14.7782592773438</t>
   </si>
   <si>
-    <t xml:space="preserve">14.741174697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7968006134033</t>
+    <t xml:space="preserve">14.7411737442017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.796802520752</t>
   </si>
   <si>
     <t xml:space="preserve">15.0235719680786</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6849870681763</t>
+    <t xml:space="preserve">15.6849880218506</t>
   </si>
   <si>
     <t xml:space="preserve">15.4015226364136</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2314462661743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0802640914917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1180610656738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1747512817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.307035446167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1353855133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8141260147095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2660961151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6062526702881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6818428039551</t>
+    <t xml:space="preserve">15.2314453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.080265045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1180601119995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.174750328064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3070363998413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.13538646698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8141279220581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2660970687866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6062545776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6818437576294</t>
   </si>
   <si>
     <t xml:space="preserve">13.0771207809448</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9448375701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1149168014526</t>
+    <t xml:space="preserve">12.9448385238647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.114917755127</t>
   </si>
   <si>
     <t xml:space="preserve">12.8881464004517</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0944480895996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5479898452759</t>
+    <t xml:space="preserve">12.0944471359253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5479888916016</t>
   </si>
   <si>
     <t xml:space="preserve">13.0015306472778</t>
@@ -1271,19 +1274,19 @@
     <t xml:space="preserve">12.6235799789429</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6991701126099</t>
+    <t xml:space="preserve">12.6991691589355</t>
   </si>
   <si>
     <t xml:space="preserve">12.7558631896973</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8692483901978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3401174545288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.736964225769</t>
+    <t xml:space="preserve">12.8692474365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3401165008545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7369651794434</t>
   </si>
   <si>
     <t xml:space="preserve">12.7180681228638</t>
@@ -1295,28 +1298,28 @@
     <t xml:space="preserve">12.2645254135132</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7385368347168</t>
+    <t xml:space="preserve">13.7385377883911</t>
   </si>
   <si>
     <t xml:space="preserve">13.7763319015503</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9653053283691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8708190917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0786924362183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6251516342163</t>
+    <t xml:space="preserve">13.9653072357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8708200454712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0786933898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.625150680542</t>
   </si>
   <si>
     <t xml:space="preserve">13.5873565673828</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4172782897949</t>
+    <t xml:space="preserve">13.4172773361206</t>
   </si>
   <si>
     <t xml:space="preserve">13.4550733566284</t>
@@ -1325,13 +1328,13 @@
     <t xml:space="preserve">13.4361753463745</t>
   </si>
   <si>
-    <t xml:space="preserve">13.247200012207</t>
+    <t xml:space="preserve">13.2472009658813</t>
   </si>
   <si>
     <t xml:space="preserve">13.1338138580322</t>
   </si>
   <si>
-    <t xml:space="preserve">13.322790145874</t>
+    <t xml:space="preserve">13.3227920532227</t>
   </si>
   <si>
     <t xml:space="preserve">13.4739713668823</t>
@@ -1343,16 +1346,16 @@
     <t xml:space="preserve">13.3605852127075</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5668869018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5101938247681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2834234237671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6802711486816</t>
+    <t xml:space="preserve">12.5668859481812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5101947784424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2834224700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6802730560303</t>
   </si>
   <si>
     <t xml:space="preserve">13.0393266677856</t>
@@ -1364,13 +1367,13 @@
     <t xml:space="preserve">12.8125562667847</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9637355804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7952308654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1164875030518</t>
+    <t xml:space="preserve">12.963737487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7952299118042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1164865493774</t>
   </si>
   <si>
     <t xml:space="preserve">14.2676696777344</t>
@@ -1379,7 +1382,7 @@
     <t xml:space="preserve">14.3054647445679</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0597953796387</t>
+    <t xml:space="preserve">14.059796333313</t>
   </si>
   <si>
     <t xml:space="preserve">13.700740814209</t>
@@ -1388,7 +1391,7 @@
     <t xml:space="preserve">13.4928674697876</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7574329376221</t>
+    <t xml:space="preserve">13.7574338912964</t>
   </si>
   <si>
     <t xml:space="preserve">13.549560546875</t>
@@ -1397,34 +1400,34 @@
     <t xml:space="preserve">14.1731815338135</t>
   </si>
   <si>
-    <t xml:space="preserve">14.929084777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4960117340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2692413330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.155855178833</t>
+    <t xml:space="preserve">14.9290828704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4960107803345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2692403793335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1558561325073</t>
   </si>
   <si>
     <t xml:space="preserve">16.5353755950928</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7054538726807</t>
+    <t xml:space="preserve">16.7054557800293</t>
   </si>
   <si>
     <t xml:space="preserve">16.9133281707764</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6298656463623</t>
+    <t xml:space="preserve">16.6298637390137</t>
   </si>
   <si>
     <t xml:space="preserve">16.2330169677734</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9117574691772</t>
+    <t xml:space="preserve">15.9117565155029</t>
   </si>
   <si>
     <t xml:space="preserve">15.5904989242554</t>
@@ -1433,10 +1436,10 @@
     <t xml:space="preserve">15.5149078369141</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0046739578247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2125473022461</t>
+    <t xml:space="preserve">15.004674911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2125482559204</t>
   </si>
   <si>
     <t xml:space="preserve">14.3810548782349</t>
@@ -1445,7 +1448,7 @@
     <t xml:space="preserve">14.6078262329102</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4377470016479</t>
+    <t xml:space="preserve">14.4377460479736</t>
   </si>
   <si>
     <t xml:space="preserve">14.6456203460693</t>
@@ -1454,88 +1457,88 @@
     <t xml:space="preserve">14.2487707138062</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1920795440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8897171020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5306615829468</t>
+    <t xml:space="preserve">14.1920785903931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8897180557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5306644439697</t>
   </si>
   <si>
     <t xml:space="preserve">13.8519220352173</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0219993591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8723907470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4755430221558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4188499450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5527048110962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9668798446655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0818386077881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0629386901855</t>
+    <t xml:space="preserve">14.0220003128052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8723917007446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4755411148071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.418848991394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5527029037476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9668788909912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0818367004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0629367828369</t>
   </si>
   <si>
     <t xml:space="preserve">16.251916885376</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0440406799316</t>
+    <t xml:space="preserve">16.0440425872803</t>
   </si>
   <si>
     <t xml:space="preserve">15.8739624023438</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4582166671753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0251445770264</t>
+    <t xml:space="preserve">15.458215713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0251426696777</t>
   </si>
   <si>
     <t xml:space="preserve">16.3464012145996</t>
   </si>
   <si>
-    <t xml:space="preserve">16.100736618042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.327507019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6471920013428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7983741760254</t>
+    <t xml:space="preserve">16.1007347106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3275051116943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6471929550171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7983722686768</t>
   </si>
   <si>
     <t xml:space="preserve">15.9306545257568</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0613670349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8550672531128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4771108627319</t>
+    <t xml:space="preserve">15.0613660812378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8550634384155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4771127700806</t>
   </si>
   <si>
     <t xml:space="preserve">14.7401084899902</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9101867675781</t>
+    <t xml:space="preserve">14.9101858139038</t>
   </si>
   <si>
     <t xml:space="preserve">14.5511331558228</t>
@@ -1544,52 +1547,52 @@
     <t xml:space="preserve">14.8156995773315</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9857769012451</t>
+    <t xml:space="preserve">14.9857759475708</t>
   </si>
   <si>
     <t xml:space="preserve">15.533805847168</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7416791915894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0424680709839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4204196929932</t>
+    <t xml:space="preserve">15.7416801452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0424699783325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4204206466675</t>
   </si>
   <si>
     <t xml:space="preserve">15.7605762481689</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6282949447632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.892858505249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9684524536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0062465667725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9873485565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6093969345093</t>
+    <t xml:space="preserve">15.6282968521118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8928594589233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9684505462646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0062446594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9873495101929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6093988418579</t>
   </si>
   <si>
     <t xml:space="preserve">14.6834154129028</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6267232894897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8534936904907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1936511993408</t>
+    <t xml:space="preserve">14.6267223358154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.853494644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1936483383179</t>
   </si>
   <si>
     <t xml:space="preserve">15.0991621017456</t>
@@ -1598,7 +1601,7 @@
     <t xml:space="preserve">15.2881383895874</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1952209472656</t>
+    <t xml:space="preserve">16.1952228546143</t>
   </si>
   <si>
     <t xml:space="preserve">17.0078182220459</t>
@@ -1607,19 +1610,19 @@
     <t xml:space="preserve">17.2345886230469</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2534866333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2912769317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1023025512695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0645084381104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0471820831299</t>
+    <t xml:space="preserve">17.2534847259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2912788391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1023063659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.064510345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0471858978271</t>
   </si>
   <si>
     <t xml:space="preserve">17.4046649932861</t>
@@ -1628,19 +1631,19 @@
     <t xml:space="preserve">17.347972869873</t>
   </si>
   <si>
-    <t xml:space="preserve">17.366870880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4991569519043</t>
+    <t xml:space="preserve">17.3668689727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.499153137207</t>
   </si>
   <si>
     <t xml:space="preserve">17.0456123352051</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3857707977295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4424610137939</t>
+    <t xml:space="preserve">17.3857669830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4424591064453</t>
   </si>
   <si>
     <t xml:space="preserve">17.8582077026367</t>
@@ -1649,10 +1652,10 @@
     <t xml:space="preserve">17.8204135894775</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5558471679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3290748596191</t>
+    <t xml:space="preserve">17.5558490753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3290767669678</t>
   </si>
   <si>
     <t xml:space="preserve">17.140100479126</t>
@@ -1667,40 +1670,40 @@
     <t xml:space="preserve">16.2897090911865</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8566398620605</t>
+    <t xml:space="preserve">16.8566360473633</t>
   </si>
   <si>
     <t xml:space="preserve">16.1574287414551</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5805950164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5421295166016</t>
+    <t xml:space="preserve">16.5805988311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5421276092529</t>
   </si>
   <si>
     <t xml:space="preserve">16.3882484436035</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4459552764893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2343654632568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0035438537598</t>
+    <t xml:space="preserve">16.4459533691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2343673706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0035457611084</t>
   </si>
   <si>
     <t xml:space="preserve">15.9843101501465</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6767730712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8114166259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8306503295898</t>
+    <t xml:space="preserve">16.6767711639404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8114185333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8306522369385</t>
   </si>
   <si>
     <t xml:space="preserve">16.7537117004395</t>
@@ -1712,31 +1715,31 @@
     <t xml:space="preserve">16.4267158508301</t>
   </si>
   <si>
-    <t xml:space="preserve">16.522891998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.945839881897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4651870727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9650754928589</t>
+    <t xml:space="preserve">16.5228939056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9458417892456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4651889801025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9650783538818</t>
   </si>
   <si>
     <t xml:space="preserve">16.0227813720703</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8689012527466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7342567443848</t>
+    <t xml:space="preserve">15.8688993453979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7342576980591</t>
   </si>
   <si>
     <t xml:space="preserve">15.6573171615601</t>
   </si>
   <si>
-    <t xml:space="preserve">15.426495552063</t>
+    <t xml:space="preserve">15.4264965057373</t>
   </si>
   <si>
     <t xml:space="preserve">15.3687896728516</t>
@@ -1745,7 +1748,7 @@
     <t xml:space="preserve">15.3110837936401</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9840879440308</t>
+    <t xml:space="preserve">14.9840888977051</t>
   </si>
   <si>
     <t xml:space="preserve">15.1956748962402</t>
@@ -1757,7 +1760,7 @@
     <t xml:space="preserve">15.1379690170288</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0994997024536</t>
+    <t xml:space="preserve">15.0994987487793</t>
   </si>
   <si>
     <t xml:space="preserve">15.003324508667</t>
@@ -1766,13 +1769,13 @@
     <t xml:space="preserve">15.1187343597412</t>
   </si>
   <si>
-    <t xml:space="preserve">15.253378868103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0610303878784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8686800003052</t>
+    <t xml:space="preserve">15.2533798217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0610294342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8686790466309</t>
   </si>
   <si>
     <t xml:space="preserve">14.8494434356689</t>
@@ -1781,31 +1784,28 @@
     <t xml:space="preserve">14.7147979736328</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4457292556763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1764402389526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.830207824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.080265045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9648561477661</t>
+    <t xml:space="preserve">15.445728302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1764392852783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8302087783813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9648542404175</t>
   </si>
   <si>
     <t xml:space="preserve">15.1572046279907</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7917394638062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.753270149231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9071483612061</t>
+    <t xml:space="preserve">14.7917385101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7532691955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9071493148804</t>
   </si>
   <si>
     <t xml:space="preserve">15.0225591659546</t>
@@ -1814,28 +1814,28 @@
     <t xml:space="preserve">14.8109741210938</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8879146575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5416822433472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.580153465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5993890762329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5032119750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6378583908081</t>
+    <t xml:space="preserve">14.8879127502441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5416831970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5801525115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5993900299072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.503212928772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6378593444824</t>
   </si>
   <si>
     <t xml:space="preserve">14.6186227798462</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4647445678711</t>
+    <t xml:space="preserve">14.4647436141968</t>
   </si>
   <si>
     <t xml:space="preserve">14.4455089569092</t>
@@ -1844,43 +1844,43 @@
     <t xml:space="preserve">14.6570930480957</t>
   </si>
   <si>
-    <t xml:space="preserve">14.926383972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5609188079834</t>
+    <t xml:space="preserve">14.9263849258423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5609178543091</t>
   </si>
   <si>
     <t xml:space="preserve">15.3495540618896</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3880262374878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6765489578247</t>
+    <t xml:space="preserve">15.3880252838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.676549911499</t>
   </si>
   <si>
     <t xml:space="preserve">15.522668838501</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7150220870972</t>
+    <t xml:space="preserve">15.7150192260742</t>
   </si>
   <si>
     <t xml:space="preserve">15.7919597625732</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1574249267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.77272605896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8111953735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9073715209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6380796432495</t>
+    <t xml:space="preserve">16.1574268341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7727241516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8111963272095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.907374382019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6380786895752</t>
   </si>
   <si>
     <t xml:space="preserve">15.6188459396362</t>
@@ -1892,82 +1892,82 @@
     <t xml:space="preserve">15.5803756713867</t>
   </si>
   <si>
-    <t xml:space="preserve">15.503436088562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8304309844971</t>
+    <t xml:space="preserve">15.5034351348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8304290771484</t>
   </si>
   <si>
     <t xml:space="preserve">15.9266061782837</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1189556121826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1576499938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0037651062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9460620880127</t>
+    <t xml:space="preserve">16.1189575195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1576519012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0037689208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9460639953613</t>
   </si>
   <si>
     <t xml:space="preserve">16.8883571624756</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9845333099365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1191749572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2730579376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2732810974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1771030426025</t>
+    <t xml:space="preserve">16.9845314025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.119176864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2730598449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2732791900635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1771049499512</t>
   </si>
   <si>
     <t xml:space="preserve">17.6000518798828</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6577587127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1001644134521</t>
+    <t xml:space="preserve">17.6577606201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1001625061035</t>
   </si>
   <si>
     <t xml:space="preserve">17.9847564697266</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1193981170654</t>
+    <t xml:space="preserve">18.1194000244141</t>
   </si>
   <si>
     <t xml:space="preserve">17.965518951416</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9462814331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0616931915283</t>
+    <t xml:space="preserve">17.9462833404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0616970062256</t>
   </si>
   <si>
     <t xml:space="preserve">17.9270496368408</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3117485046387</t>
+    <t xml:space="preserve">18.3117504119873</t>
   </si>
   <si>
     <t xml:space="preserve">18.7541542053223</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1003875732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0234432220459</t>
+    <t xml:space="preserve">19.1003856658936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0234489440918</t>
   </si>
   <si>
     <t xml:space="preserve">18.5425701141357</t>
@@ -1976,46 +1976,46 @@
     <t xml:space="preserve">18.9657402038574</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9080371856689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4273815155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8120822906494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5235576629639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6678199768066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2831192016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8503303527832</t>
+    <t xml:space="preserve">18.9080333709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4273834228516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8120784759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5235557556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.667818069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2831172943115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8503284454346</t>
   </si>
   <si>
     <t xml:space="preserve">19.6197319030762</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7159099578857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7639923095703</t>
+    <t xml:space="preserve">19.7159080505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7639942169189</t>
   </si>
   <si>
     <t xml:space="preserve">19.3312072753906</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5716438293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1967830657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2448711395264</t>
+    <t xml:space="preserve">19.571647644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1967811584473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2448692321777</t>
   </si>
   <si>
     <t xml:space="preserve">22.2164611816406</t>
@@ -2027,61 +2027,61 @@
     <t xml:space="preserve">21.1104469299316</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8219223022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6295700073242</t>
+    <t xml:space="preserve">20.8219203948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6295719146729</t>
   </si>
   <si>
     <t xml:space="preserve">21.0142726898193</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7257461547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6776561737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9563465118408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2929573059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0044326782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8601703643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0811500549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7738342285156</t>
+    <t xml:space="preserve">20.7257442474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6776599884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9563446044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2929592132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.004430770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8601684570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0811519622803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.773832321167</t>
   </si>
   <si>
     <t xml:space="preserve">20.9180965423584</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5814838409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.254711151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3989715576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2066211700439</t>
+    <t xml:space="preserve">20.5814819335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2547092437744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3989734649658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2066192626953</t>
   </si>
   <si>
     <t xml:space="preserve">21.6394100189209</t>
   </si>
   <si>
-    <t xml:space="preserve">21.447057723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8317623138428</t>
+    <t xml:space="preserve">21.4470596313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8317604064941</t>
   </si>
   <si>
     <t xml:space="preserve">20.0525188446045</t>
@@ -2093,7 +2093,7 @@
     <t xml:space="preserve">18.734920501709</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1963405609131</t>
+    <t xml:space="preserve">18.1963386535645</t>
   </si>
   <si>
     <t xml:space="preserve">17.6192893981934</t>
@@ -2102,7 +2102,7 @@
     <t xml:space="preserve">16.3113059997559</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1958961486816</t>
+    <t xml:space="preserve">16.1958980560303</t>
   </si>
   <si>
     <t xml:space="preserve">14.4839792251587</t>
@@ -2111,7 +2111,7 @@
     <t xml:space="preserve">14.4262733459473</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4642992019653</t>
+    <t xml:space="preserve">12.4643001556396</t>
   </si>
   <si>
     <t xml:space="preserve">12.0218944549561</t>
@@ -2120,13 +2120,13 @@
     <t xml:space="preserve">12.1373043060303</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6951208114624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9067049026489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9834241867065</t>
+    <t xml:space="preserve">12.6951198577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9067058563232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9834251403809</t>
   </si>
   <si>
     <t xml:space="preserve">13.3106412887573</t>
@@ -2135,10 +2135,10 @@
     <t xml:space="preserve">13.5606966018677</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0223379135132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1954536437988</t>
+    <t xml:space="preserve">14.0223369598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1954526901245</t>
   </si>
   <si>
     <t xml:space="preserve">14.2916278839111</t>
@@ -2147,70 +2147,70 @@
     <t xml:space="preserve">14.1185131072998</t>
   </si>
   <si>
-    <t xml:space="preserve">14.734034538269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0992784500122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4072599411011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8691234588623</t>
+    <t xml:space="preserve">14.7340326309204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0992774963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4072608947754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8691253662109</t>
   </si>
   <si>
     <t xml:space="preserve">16.1766605377197</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2151298522949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4649658203125</t>
+    <t xml:space="preserve">16.2151336669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4649648666382</t>
   </si>
   <si>
     <t xml:space="preserve">16.0612506866455</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1381931304932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0420150756836</t>
+    <t xml:space="preserve">16.1381912231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0420169830322</t>
   </si>
   <si>
     <t xml:space="preserve">16.59983253479</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2153511047363</t>
+    <t xml:space="preserve">17.2153549194336</t>
   </si>
   <si>
     <t xml:space="preserve">16.7152404785156</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9268264770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0614700317383</t>
+    <t xml:space="preserve">16.926830291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0614719390869</t>
   </si>
   <si>
     <t xml:space="preserve">18.2540435791016</t>
   </si>
   <si>
-    <t xml:space="preserve">18.638744354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0774536132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7677783966064</t>
+    <t xml:space="preserve">18.6387424468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0774555206299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7677764892578</t>
   </si>
   <si>
     <t xml:space="preserve">17.4580993652344</t>
   </si>
   <si>
-    <t xml:space="preserve">17.43874168396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2064838409424</t>
+    <t xml:space="preserve">17.4387435913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.206485748291</t>
   </si>
   <si>
     <t xml:space="preserve">16.9548721313477</t>
@@ -2228,19 +2228,19 @@
     <t xml:space="preserve">17.651647567749</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4968070983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7290687561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.290355682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9419708251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0580978393555</t>
+    <t xml:space="preserve">17.4968090057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7290668487549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2903575897217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9419727325439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0580997467041</t>
   </si>
   <si>
     <t xml:space="preserve">18.3871326446533</t>
@@ -2255,22 +2255,22 @@
     <t xml:space="preserve">18.2322940826416</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2516479492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5806827545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.445198059082</t>
+    <t xml:space="preserve">18.2516460418701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5806846618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4451961517334</t>
   </si>
   <si>
     <t xml:space="preserve">18.1161632537842</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0387439727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8322944641113</t>
+    <t xml:space="preserve">18.038745880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8322925567627</t>
   </si>
   <si>
     <t xml:space="preserve">18.7742290496826</t>
@@ -2282,16 +2282,16 @@
     <t xml:space="preserve">18.9097137451172</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0452003479004</t>
+    <t xml:space="preserve">19.0451965332031</t>
   </si>
   <si>
     <t xml:space="preserve">19.5968112945557</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3548736572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9484233856201</t>
+    <t xml:space="preserve">19.3548755645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9484252929688</t>
   </si>
   <si>
     <t xml:space="preserve">19.1032619476318</t>
@@ -2300,7 +2300,7 @@
     <t xml:space="preserve">18.4645519256592</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6581001281738</t>
+    <t xml:space="preserve">18.6581020355225</t>
   </si>
   <si>
     <t xml:space="preserve">19.5000381469727</t>
@@ -2309,31 +2309,31 @@
     <t xml:space="preserve">19.6451988220215</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0806846618652</t>
+    <t xml:space="preserve">20.0806827545166</t>
   </si>
   <si>
     <t xml:space="preserve">20.3226203918457</t>
   </si>
   <si>
-    <t xml:space="preserve">20.612943649292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5645561218262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0484294891357</t>
+    <t xml:space="preserve">20.6129417419434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5645542144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0484275817871</t>
   </si>
   <si>
     <t xml:space="preserve">21.2903633117676</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7258491516113</t>
+    <t xml:space="preserve">21.7258472442627</t>
   </si>
   <si>
     <t xml:space="preserve">21.1935901641846</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5806884765625</t>
+    <t xml:space="preserve">21.5806865692139</t>
   </si>
   <si>
     <t xml:space="preserve">21.8710098266602</t>
@@ -2342,10 +2342,10 @@
     <t xml:space="preserve">21.5323009490967</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3387508392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7742366790771</t>
+    <t xml:space="preserve">21.3387489318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7742347717285</t>
   </si>
   <si>
     <t xml:space="preserve">22.4516563415527</t>
@@ -2360,10 +2360,10 @@
     <t xml:space="preserve">23.3226261138916</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4194011688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0968208312988</t>
+    <t xml:space="preserve">23.4193992614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0968189239502</t>
   </si>
   <si>
     <t xml:space="preserve">24.7258529663086</t>
@@ -2375,28 +2375,28 @@
     <t xml:space="preserve">24.048433303833</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7581081390381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9516582489014</t>
+    <t xml:space="preserve">23.7581100463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.95166015625</t>
   </si>
   <si>
     <t xml:space="preserve">23.6613368988037</t>
   </si>
   <si>
-    <t xml:space="preserve">22.741979598999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0323028564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4677886962891</t>
+    <t xml:space="preserve">22.7419776916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0323009490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4677867889404</t>
   </si>
   <si>
     <t xml:space="preserve">23.0806903839111</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8871421813965</t>
+    <t xml:space="preserve">22.8871402740479</t>
   </si>
   <si>
     <t xml:space="preserve">22.5484313964844</t>
@@ -2414,22 +2414,22 @@
     <t xml:space="preserve">21.6290740966797</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4677829742432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3871402740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0968151092529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4839134216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2097206115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9677867889404</t>
+    <t xml:space="preserve">20.4677810668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3871383666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0968132019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4839115142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2097225189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9677848815918</t>
   </si>
   <si>
     <t xml:space="preserve">20.9516544342041</t>
@@ -2444,16 +2444,16 @@
     <t xml:space="preserve">21.919397354126</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8387546539307</t>
+    <t xml:space="preserve">22.838752746582</t>
   </si>
   <si>
     <t xml:space="preserve">22.6452045440674</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4355316162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3387565612793</t>
+    <t xml:space="preserve">24.4355297088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3387584686279</t>
   </si>
   <si>
     <t xml:space="preserve">24.2419815063477</t>
@@ -2465,16 +2465,16 @@
     <t xml:space="preserve">26.1774673461914</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0000495910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.661340713501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6129531860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3710174560547</t>
+    <t xml:space="preserve">27.0000534057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6613426208496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6129550933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3710193634033</t>
   </si>
   <si>
     <t xml:space="preserve">27.6774730682373</t>
@@ -2492,7 +2492,7 @@
     <t xml:space="preserve">29.7581214904785</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3871555328369</t>
+    <t xml:space="preserve">30.3871536254883</t>
   </si>
   <si>
     <t xml:space="preserve">30.9194145202637</t>
@@ -2501,16 +2501,16 @@
     <t xml:space="preserve">31.7419948577881</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0323181152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5484447479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0807075500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2581233978271</t>
+    <t xml:space="preserve">32.0323143005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5484466552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0807113647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2581253051758</t>
   </si>
   <si>
     <t xml:space="preserve">32.1774787902832</t>
@@ -2519,7 +2519,7 @@
     <t xml:space="preserve">32.3226432800293</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2903900146484</t>
+    <t xml:space="preserve">33.2903861999512</t>
   </si>
   <si>
     <t xml:space="preserve">33.1936111450195</t>
@@ -2528,16 +2528,16 @@
     <t xml:space="preserve">32.8065147399902</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4839363098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7258720397949</t>
+    <t xml:space="preserve">33.4839324951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7258682250977</t>
   </si>
   <si>
     <t xml:space="preserve">34.1129684448242</t>
   </si>
   <si>
-    <t xml:space="preserve">34.742000579834</t>
+    <t xml:space="preserve">34.7420043945312</t>
   </si>
   <si>
     <t xml:space="preserve">34.5968399047852</t>
@@ -2552,25 +2552,25 @@
     <t xml:space="preserve">36.8226509094238</t>
   </si>
   <si>
-    <t xml:space="preserve">37.1613655090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.1936187744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3065223693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5645790100098</t>
+    <t xml:space="preserve">37.1613693237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.1936225891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3065185546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.564582824707</t>
   </si>
   <si>
     <t xml:space="preserve">32.6613540649414</t>
   </si>
   <si>
-    <t xml:space="preserve">32.758129119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7097396850586</t>
+    <t xml:space="preserve">32.7581253051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7097434997559</t>
   </si>
   <si>
     <t xml:space="preserve">31.9355430603027</t>
@@ -2579,7 +2579,7 @@
     <t xml:space="preserve">30.3387699127197</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8226413726807</t>
+    <t xml:space="preserve">30.822639465332</t>
   </si>
   <si>
     <t xml:space="preserve">30.5807056427002</t>
@@ -2591,7 +2591,7 @@
     <t xml:space="preserve">31.112964630127</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4355506896973</t>
+    <t xml:space="preserve">33.435546875</t>
   </si>
   <si>
     <t xml:space="preserve">33.8710327148438</t>
@@ -2612,16 +2612,16 @@
     <t xml:space="preserve">37.0162010192871</t>
   </si>
   <si>
-    <t xml:space="preserve">36.9678115844727</t>
+    <t xml:space="preserve">36.9678153991699</t>
   </si>
   <si>
     <t xml:space="preserve">35.9516868591309</t>
   </si>
   <si>
-    <t xml:space="preserve">36.4355545043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0807151794434</t>
+    <t xml:space="preserve">36.4355506896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0807113647461</t>
   </si>
   <si>
     <t xml:space="preserve">34.9839401245117</t>
@@ -2642,19 +2642,19 @@
     <t xml:space="preserve">38.6129760742188</t>
   </si>
   <si>
-    <t xml:space="preserve">38.7581405639648</t>
+    <t xml:space="preserve">38.7581367492676</t>
   </si>
   <si>
     <t xml:space="preserve">39.8226585388184</t>
   </si>
   <si>
-    <t xml:space="preserve">39.6774940490723</t>
+    <t xml:space="preserve">39.6774978637695</t>
   </si>
   <si>
     <t xml:space="preserve">38.5645866394043</t>
   </si>
   <si>
-    <t xml:space="preserve">38.7097473144531</t>
+    <t xml:space="preserve">38.7097511291504</t>
   </si>
   <si>
     <t xml:space="preserve">39.6291084289551</t>
@@ -2663,10 +2663,10 @@
     <t xml:space="preserve">40.4516906738281</t>
   </si>
   <si>
-    <t xml:space="preserve">40.1613693237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4355583190918</t>
+    <t xml:space="preserve">40.1613655090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4355659484863</t>
   </si>
   <si>
     <t xml:space="preserve">40.2581405639648</t>
@@ -2681,10 +2681,10 @@
     <t xml:space="preserve">40.0645942687988</t>
   </si>
   <si>
-    <t xml:space="preserve">41.1774978637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.854923248291</t>
+    <t xml:space="preserve">41.1774940490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8549156188965</t>
   </si>
   <si>
     <t xml:space="preserve">42.3387908935547</t>
@@ -2702,7 +2702,7 @@
     <t xml:space="preserve">42.3871803283691</t>
   </si>
   <si>
-    <t xml:space="preserve">43.5000839233398</t>
+    <t xml:space="preserve">43.5000877380371</t>
   </si>
   <si>
     <t xml:space="preserve">44.1291160583496</t>
@@ -2711,25 +2711,25 @@
     <t xml:space="preserve">44.7097625732422</t>
   </si>
   <si>
-    <t xml:space="preserve">44.7581481933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6775093078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.4194412231445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.0000915527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.0162162780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.483959197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.9517021179199</t>
+    <t xml:space="preserve">44.7581558227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6775054931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.4194450378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.0000839233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.0162200927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4839553833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.9516983032227</t>
   </si>
   <si>
     <t xml:space="preserve">46.2581520080566</t>
@@ -2744,13 +2744,13 @@
     <t xml:space="preserve">44.5162124633789</t>
   </si>
   <si>
-    <t xml:space="preserve">44.2742729187012</t>
+    <t xml:space="preserve">44.2742767333984</t>
   </si>
   <si>
     <t xml:space="preserve">43.838794708252</t>
   </si>
   <si>
-    <t xml:space="preserve">43.161376953125</t>
+    <t xml:space="preserve">43.1613731384277</t>
   </si>
   <si>
     <t xml:space="preserve">43.3065338134766</t>
@@ -2792,10 +2792,10 @@
     <t xml:space="preserve">40.873779296875</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9947776794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.7761116027832</t>
+    <t xml:space="preserve">39.9947738647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.7761154174805</t>
   </si>
   <si>
     <t xml:space="preserve">40.6784477233887</t>
@@ -2816,10 +2816,10 @@
     <t xml:space="preserve">39.7506103515625</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2622718811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2877769470215</t>
+    <t xml:space="preserve">39.2622680664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2877731323242</t>
   </si>
   <si>
     <t xml:space="preserve">39.9459419250488</t>
@@ -2828,7 +2828,7 @@
     <t xml:space="preserve">37.8949279785156</t>
   </si>
   <si>
-    <t xml:space="preserve">36.7229232788086</t>
+    <t xml:space="preserve">36.7229194641113</t>
   </si>
   <si>
     <t xml:space="preserve">37.6019248962402</t>
@@ -2837,7 +2837,7 @@
     <t xml:space="preserve">38.0902633666992</t>
   </si>
   <si>
-    <t xml:space="preserve">39.5552749633789</t>
+    <t xml:space="preserve">39.5552711486816</t>
   </si>
   <si>
     <t xml:space="preserve">41.7039566040039</t>
@@ -2849,7 +2849,7 @@
     <t xml:space="preserve">41.4597854614258</t>
   </si>
   <si>
-    <t xml:space="preserve">41.0691146850586</t>
+    <t xml:space="preserve">41.0691184997559</t>
   </si>
   <si>
     <t xml:space="preserve">40.3854446411133</t>
@@ -2861,10 +2861,10 @@
     <t xml:space="preserve">42.1922912597656</t>
   </si>
   <si>
-    <t xml:space="preserve">42.0457878112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.9481201171875</t>
+    <t xml:space="preserve">42.0457916259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.9481239318848</t>
   </si>
   <si>
     <t xml:space="preserve">41.4109535217285</t>
@@ -2873,19 +2873,19 @@
     <t xml:space="preserve">42.7294616699219</t>
   </si>
   <si>
-    <t xml:space="preserve">45.3664817810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4153137207031</t>
+    <t xml:space="preserve">45.3664779663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4153099060059</t>
   </si>
   <si>
     <t xml:space="preserve">46.1966514587402</t>
   </si>
   <si>
-    <t xml:space="preserve">47.8569946289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.3198280334473</t>
+    <t xml:space="preserve">47.8569984436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.31982421875</t>
   </si>
   <si>
     <t xml:space="preserve">47.808162689209</t>
@@ -2894,7 +2894,7 @@
     <t xml:space="preserve">48.5406684875488</t>
   </si>
   <si>
-    <t xml:space="preserve">48.5895042419434</t>
+    <t xml:space="preserve">48.5895004272461</t>
   </si>
   <si>
     <t xml:space="preserve">48.833667755127</t>
@@ -2906,7 +2906,7 @@
     <t xml:space="preserve">49.7126770019531</t>
   </si>
   <si>
-    <t xml:space="preserve">49.9080123901367</t>
+    <t xml:space="preserve">49.9080085754395</t>
   </si>
   <si>
     <t xml:space="preserve">49.8103446960449</t>
@@ -2915,10 +2915,10 @@
     <t xml:space="preserve">50.0056762695312</t>
   </si>
   <si>
-    <t xml:space="preserve">50.6893501281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.3730163574219</t>
+    <t xml:space="preserve">50.6893539428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.3730201721191</t>
   </si>
   <si>
     <t xml:space="preserve">50.2986831665039</t>
@@ -2948,16 +2948,16 @@
     <t xml:space="preserve">51.9590263366699</t>
   </si>
   <si>
-    <t xml:space="preserve">50.8846778869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2688102722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.5363006591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.510799407959</t>
+    <t xml:space="preserve">50.8846817016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.2688140869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.536304473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.5107955932617</t>
   </si>
   <si>
     <t xml:space="preserve">44.2433052062988</t>
@@ -2972,7 +2972,7 @@
     <t xml:space="preserve">44.0479698181152</t>
   </si>
   <si>
-    <t xml:space="preserve">43.8038024902344</t>
+    <t xml:space="preserve">43.8037986755371</t>
   </si>
   <si>
     <t xml:space="preserve">44.4386405944824</t>
@@ -2987,16 +2987,16 @@
     <t xml:space="preserve">41.2156181335449</t>
   </si>
   <si>
-    <t xml:space="preserve">40.9714508056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.7527885437012</t>
+    <t xml:space="preserve">40.9714469909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.7527923583984</t>
   </si>
   <si>
     <t xml:space="preserve">42.2899589538574</t>
   </si>
   <si>
-    <t xml:space="preserve">43.0712966918945</t>
+    <t xml:space="preserve">43.0712928771973</t>
   </si>
   <si>
     <t xml:space="preserve">43.2666320800781</t>
@@ -3014,10 +3014,10 @@
     <t xml:space="preserve">46.0989837646484</t>
   </si>
   <si>
-    <t xml:space="preserve">45.6594848632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.7571449279785</t>
+    <t xml:space="preserve">45.659481048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.7571411132812</t>
   </si>
   <si>
     <t xml:space="preserve">42.7782974243164</t>
@@ -3044,7 +3044,7 @@
     <t xml:space="preserve">38.8716011047363</t>
   </si>
   <si>
-    <t xml:space="preserve">38.2367630004883</t>
+    <t xml:space="preserve">38.2367668151855</t>
   </si>
   <si>
     <t xml:space="preserve">39.0669364929199</t>
@@ -3053,7 +3053,7 @@
     <t xml:space="preserve">39.848274230957</t>
   </si>
   <si>
-    <t xml:space="preserve">40.5319480895996</t>
+    <t xml:space="preserve">40.5319442749023</t>
   </si>
   <si>
     <t xml:space="preserve">41.8504524230957</t>
@@ -3080,16 +3080,16 @@
     <t xml:space="preserve">41.8016204833984</t>
   </si>
   <si>
-    <t xml:space="preserve">41.362117767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2389488220215</t>
+    <t xml:space="preserve">41.3621215820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2389450073242</t>
   </si>
   <si>
     <t xml:space="preserve">40.6296119689941</t>
   </si>
   <si>
-    <t xml:space="preserve">42.8759689331055</t>
+    <t xml:space="preserve">42.8759651184082</t>
   </si>
   <si>
     <t xml:space="preserve">43.4619674682617</t>
@@ -3101,7 +3101,7 @@
     <t xml:space="preserve">40.9226188659668</t>
   </si>
   <si>
-    <t xml:space="preserve">39.1157722473145</t>
+    <t xml:space="preserve">39.1157684326172</t>
   </si>
   <si>
     <t xml:space="preserve">42.5829582214355</t>
@@ -3113,7 +3113,7 @@
     <t xml:space="preserve">38.5785980224609</t>
   </si>
   <si>
-    <t xml:space="preserve">36.4299163818359</t>
+    <t xml:space="preserve">36.4299125671387</t>
   </si>
   <si>
     <t xml:space="preserve">38.6274337768555</t>
@@ -3128,7 +3128,7 @@
     <t xml:space="preserve">34.7207374572754</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5997428894043</t>
+    <t xml:space="preserve">35.5997467041016</t>
   </si>
   <si>
     <t xml:space="preserve">36.527587890625</t>
@@ -3140,7 +3140,7 @@
     <t xml:space="preserve">36.0880813598633</t>
   </si>
   <si>
-    <t xml:space="preserve">36.1369171142578</t>
+    <t xml:space="preserve">36.1369132995605</t>
   </si>
   <si>
     <t xml:space="preserve">35.4532432556152</t>
@@ -3155,10 +3155,10 @@
     <t xml:space="preserve">35.3555793762207</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9394035339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1325531005859</t>
+    <t xml:space="preserve">33.9393997192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1325569152832</t>
   </si>
   <si>
     <t xml:space="preserve">31.4977169036865</t>
@@ -3170,10 +3170,10 @@
     <t xml:space="preserve">33.0115623474121</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3767242431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4510650634766</t>
+    <t xml:space="preserve">32.3767280578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4510612487793</t>
   </si>
   <si>
     <t xml:space="preserve">34.7695732116699</t>
@@ -3185,28 +3185,28 @@
     <t xml:space="preserve">35.3067436218262</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0348892211914</t>
+    <t xml:space="preserve">32.0348854064941</t>
   </si>
   <si>
     <t xml:space="preserve">31.4000511169434</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5975685119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9627304077148</t>
+    <t xml:space="preserve">33.5975646972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9627265930176</t>
   </si>
   <si>
     <t xml:space="preserve">32.5232238769531</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4255561828613</t>
+    <t xml:space="preserve">32.4255599975586</t>
   </si>
   <si>
     <t xml:space="preserve">32.6208915710449</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4488830566406</t>
+    <t xml:space="preserve">31.4488849639893</t>
   </si>
   <si>
     <t xml:space="preserve">32.6697235107422</t>
@@ -3242,7 +3242,7 @@
     <t xml:space="preserve">31.3316841125488</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1716194152832</t>
+    <t xml:space="preserve">32.1716232299805</t>
   </si>
   <si>
     <t xml:space="preserve">31.3902816772461</t>
@@ -3251,28 +3251,28 @@
     <t xml:space="preserve">31.6637496948242</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8862056732178</t>
+    <t xml:space="preserve">29.8862037658691</t>
   </si>
   <si>
     <t xml:space="preserve">29.9643402099609</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3821277618408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4993305206299</t>
+    <t xml:space="preserve">28.3821296691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4993324279785</t>
   </si>
   <si>
     <t xml:space="preserve">29.2025337219238</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8704643249512</t>
+    <t xml:space="preserve">28.8704662322998</t>
   </si>
   <si>
     <t xml:space="preserve">28.9290676116943</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0853328704834</t>
+    <t xml:space="preserve">29.085334777832</t>
   </si>
   <si>
     <t xml:space="preserve">28.3039951324463</t>
@@ -3293,10 +3293,10 @@
     <t xml:space="preserve">28.2258625030518</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5579299926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1816444396973</t>
+    <t xml:space="preserve">28.5579280853271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1816463470459</t>
   </si>
   <si>
     <t xml:space="preserve">26.8943614959717</t>
@@ -3308,7 +3308,7 @@
     <t xml:space="preserve">26.6765117645264</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8745536804199</t>
+    <t xml:space="preserve">26.8745555877686</t>
   </si>
   <si>
     <t xml:space="preserve">27.5280990600586</t>
@@ -3317,16 +3317,16 @@
     <t xml:space="preserve">26.4784679412842</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7359275817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2508392333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0628185272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3994960784912</t>
+    <t xml:space="preserve">26.7359256744385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2508411407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0628204345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3994941711426</t>
   </si>
   <si>
     <t xml:space="preserve">28.320276260376</t>
@@ -3338,7 +3338,7 @@
     <t xml:space="preserve">27.9439926147461</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4192981719971</t>
+    <t xml:space="preserve">28.4193000793457</t>
   </si>
   <si>
     <t xml:space="preserve">29.013427734375</t>
@@ -3368,13 +3368,13 @@
     <t xml:space="preserve">24.4584217071533</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4288368225098</t>
+    <t xml:space="preserve">25.4288349151611</t>
   </si>
   <si>
     <t xml:space="preserve">25.6070766448975</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4684429168701</t>
+    <t xml:space="preserve">25.4684448242188</t>
   </si>
   <si>
     <t xml:space="preserve">24.8148994445801</t>
@@ -3386,16 +3386,16 @@
     <t xml:space="preserve">25.3694229125977</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5376377105713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8840923309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2405700683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8444862365723</t>
+    <t xml:space="preserve">24.5376396179199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8840942382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.240571975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8444843292236</t>
   </si>
   <si>
     <t xml:space="preserve">23.0523090362549</t>
@@ -3404,28 +3404,28 @@
     <t xml:space="preserve">23.547420501709</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2009658813477</t>
+    <t xml:space="preserve">24.200963973999</t>
   </si>
   <si>
     <t xml:space="preserve">23.6068325042725</t>
   </si>
   <si>
-    <t xml:space="preserve">23.190938949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9136791229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4185695648193</t>
+    <t xml:space="preserve">23.1909408569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9136772155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4185676574707</t>
   </si>
   <si>
     <t xml:space="preserve">21.5669803619385</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8146572113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9532871246338</t>
+    <t xml:space="preserve">22.8146591186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9532890319824</t>
   </si>
   <si>
     <t xml:space="preserve">24.4188117980957</t>
@@ -3434,7 +3434,7 @@
     <t xml:space="preserve">23.7058544158936</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7356796264648</t>
+    <t xml:space="preserve">24.7356815338135</t>
   </si>
   <si>
     <t xml:space="preserve">24.597053527832</t>
@@ -3446,7 +3446,7 @@
     <t xml:space="preserve">25.9239444732666</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8249225616455</t>
+    <t xml:space="preserve">25.8249244689941</t>
   </si>
   <si>
     <t xml:space="preserve">26.0823802947998</t>
@@ -3458,19 +3458,19 @@
     <t xml:space="preserve">25.3892269134521</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1317691802979</t>
+    <t xml:space="preserve">25.1317672729492</t>
   </si>
   <si>
     <t xml:space="preserve">25.5674648284912</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0427703857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1417961120605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8843364715576</t>
+    <t xml:space="preserve">26.0427722930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1417942047119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.884334564209</t>
   </si>
   <si>
     <t xml:space="preserve">25.4882469177246</t>
@@ -3482,25 +3482,25 @@
     <t xml:space="preserve">24.0227241516113</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2207679748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1217460632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6860485076904</t>
+    <t xml:space="preserve">24.2207660675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1217479705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6860504150391</t>
   </si>
   <si>
     <t xml:space="preserve">24.3197898864746</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2603759765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3593978881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6266384124756</t>
+    <t xml:space="preserve">24.2603778839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3593997955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.626636505127</t>
   </si>
   <si>
     <t xml:space="preserve">24.4980297088623</t>
@@ -3518,7 +3518,7 @@
     <t xml:space="preserve">24.8743133544922</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9535331726074</t>
+    <t xml:space="preserve">24.9535312652588</t>
   </si>
   <si>
     <t xml:space="preserve">24.2999877929688</t>
@@ -3530,7 +3530,7 @@
     <t xml:space="preserve">22.8344593048096</t>
   </si>
   <si>
-    <t xml:space="preserve">22.557201385498</t>
+    <t xml:space="preserve">22.5571994781494</t>
   </si>
   <si>
     <t xml:space="preserve">22.7156352996826</t>
@@ -3554,10 +3554,10 @@
     <t xml:space="preserve">19.2696704864502</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8836059570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2400856018066</t>
+    <t xml:space="preserve">19.8836078643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2400875091553</t>
   </si>
   <si>
     <t xml:space="preserve">21.4481525421143</t>
@@ -3569,7 +3569,7 @@
     <t xml:space="preserve">21.2501087188721</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2897167205811</t>
+    <t xml:space="preserve">21.2897186279297</t>
   </si>
   <si>
     <t xml:space="preserve">21.586784362793</t>
@@ -3578,7 +3578,7 @@
     <t xml:space="preserve">20.8540210723877</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3887386322021</t>
+    <t xml:space="preserve">21.3887405395508</t>
   </si>
   <si>
     <t xml:space="preserve">21.6065902709961</t>
@@ -3590,7 +3590,7 @@
     <t xml:space="preserve">22.2007217407227</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6660003662109</t>
+    <t xml:space="preserve">21.6660022735596</t>
   </si>
   <si>
     <t xml:space="preserve">21.5075664520264</t>
@@ -3605,13 +3605,13 @@
     <t xml:space="preserve">22.1809158325195</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4383735656738</t>
+    <t xml:space="preserve">22.4383716583252</t>
   </si>
   <si>
     <t xml:space="preserve">21.7848281860352</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0620918273926</t>
+    <t xml:space="preserve">22.0620899200439</t>
   </si>
   <si>
     <t xml:space="preserve">23.0721130371094</t>
@@ -3647,31 +3647,31 @@
     <t xml:space="preserve">25.2505970001221</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2012062072754</t>
+    <t xml:space="preserve">26.201208114624</t>
   </si>
   <si>
     <t xml:space="preserve">26.4190540313721</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6963157653809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.716121673584</t>
+    <t xml:space="preserve">26.6963176727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7161197662354</t>
   </si>
   <si>
     <t xml:space="preserve">24.7554874420166</t>
   </si>
   <si>
-    <t xml:space="preserve">24.715877532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9733333587646</t>
+    <t xml:space="preserve">24.7158756256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9733352661133</t>
   </si>
   <si>
     <t xml:space="preserve">23.8246803283691</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9730911254883</t>
+    <t xml:space="preserve">22.9730930328369</t>
   </si>
   <si>
     <t xml:space="preserve">24.7950973510742</t>
@@ -3683,10 +3683,10 @@
     <t xml:space="preserve">26.1219882965088</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0625762939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7853164672852</t>
+    <t xml:space="preserve">26.0625743865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7853145599365</t>
   </si>
   <si>
     <t xml:space="preserve">26.2606220245361</t>
@@ -3695,46 +3695,46 @@
     <t xml:space="preserve">27.0725994110107</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7953395843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0232105255127</t>
+    <t xml:space="preserve">26.795337677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0232086181641</t>
   </si>
   <si>
     <t xml:space="preserve">27.5875148773193</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4884929656982</t>
+    <t xml:space="preserve">27.4884948730469</t>
   </si>
   <si>
     <t xml:space="preserve">28.6965599060059</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7757759094238</t>
+    <t xml:space="preserve">28.7757778167725</t>
   </si>
   <si>
     <t xml:space="preserve">28.2212543487549</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5777339935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.280668258667</t>
+    <t xml:space="preserve">28.5777320861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2806701660156</t>
   </si>
   <si>
     <t xml:space="preserve">28.8153858184814</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8747997283936</t>
+    <t xml:space="preserve">28.8747978210449</t>
   </si>
   <si>
     <t xml:space="preserve">28.7163639068604</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6569499969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9540176391602</t>
+    <t xml:space="preserve">28.6569519042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9540157318115</t>
   </si>
   <si>
     <t xml:space="preserve">28.8549957275391</t>
@@ -3791,16 +3791,16 @@
     <t xml:space="preserve">28.0430164337158</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6469287872314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7063388824463</t>
+    <t xml:space="preserve">27.6469268798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7063407897949</t>
   </si>
   <si>
     <t xml:space="preserve">27.0131874084473</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7755336761475</t>
+    <t xml:space="preserve">26.7755355834961</t>
   </si>
   <si>
     <t xml:space="preserve">25.6664886474609</t>
@@ -3809,22 +3809,22 @@
     <t xml:space="preserve">24.4782257080078</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3097667694092</t>
+    <t xml:space="preserve">23.3097686767578</t>
   </si>
   <si>
     <t xml:space="preserve">22.3789596557617</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2801818847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5574436187744</t>
+    <t xml:space="preserve">24.280179977417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5574417114258</t>
   </si>
   <si>
     <t xml:space="preserve">24.8347034454346</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0921611785889</t>
+    <t xml:space="preserve">25.0921630859375</t>
   </si>
   <si>
     <t xml:space="preserve">25.8447284698486</t>
@@ -3842,7 +3842,7 @@
     <t xml:space="preserve">27.2805442810059</t>
   </si>
   <si>
-    <t xml:space="preserve">27.478588104248</t>
+    <t xml:space="preserve">27.4785900115967</t>
   </si>
   <si>
     <t xml:space="preserve">28.0727214813232</t>
@@ -3869,7 +3869,7 @@
     <t xml:space="preserve">26.8844585418701</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7261447906494</t>
+    <t xml:space="preserve">27.7261428833008</t>
   </si>
   <si>
     <t xml:space="preserve">26.9834804534912</t>
@@ -3878,10 +3878,10 @@
     <t xml:space="preserve">27.330057144165</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6271209716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9241905212402</t>
+    <t xml:space="preserve">27.6271228790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9241886138916</t>
   </si>
   <si>
     <t xml:space="preserve">28.4688091278076</t>
@@ -3893,19 +3893,19 @@
     <t xml:space="preserve">30.5482711791992</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3007164001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9443588256836</t>
+    <t xml:space="preserve">30.3007144927979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.944356918335</t>
   </si>
   <si>
     <t xml:space="preserve">32.0831108093262</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6375122070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1821327209473</t>
+    <t xml:space="preserve">31.6375141143799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1821365356445</t>
   </si>
   <si>
     <t xml:space="preserve">32.9247970581055</t>
@@ -3929,10 +3929,10 @@
     <t xml:space="preserve">30.7958240509033</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6472930908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2016925811768</t>
+    <t xml:space="preserve">30.6472949981689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2016944885254</t>
   </si>
   <si>
     <t xml:space="preserve">30.3997383117676</t>
@@ -5127,6 +5127,9 @@
   </si>
   <si>
     <t xml:space="preserve">41.25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5</t>
   </si>
 </sst>
 </file>
@@ -15155,7 +15158,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G373" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -15181,7 +15184,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G374" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -15207,7 +15210,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G375" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -15233,7 +15236,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G376" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -15259,7 +15262,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G377" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -15285,7 +15288,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G378" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -15311,7 +15314,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G379" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -15337,7 +15340,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G380" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -15363,7 +15366,7 @@
         <v>12</v>
       </c>
       <c r="G381" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -15389,7 +15392,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G382" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -15415,7 +15418,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G383" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -15441,7 +15444,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G384" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -15467,7 +15470,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G385" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -15493,7 +15496,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G386" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -15519,7 +15522,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G387" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -15545,7 +15548,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G388" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -15571,7 +15574,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G389" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -15597,7 +15600,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G390" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -15623,7 +15626,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G391" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -15649,7 +15652,7 @@
         <v>13.5</v>
       </c>
       <c r="G392" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -15675,7 +15678,7 @@
         <v>13.5100002288818</v>
       </c>
       <c r="G393" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -15701,7 +15704,7 @@
         <v>13.6700000762939</v>
       </c>
       <c r="G394" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -15727,7 +15730,7 @@
         <v>13.75</v>
       </c>
       <c r="G395" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -15753,7 +15756,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G396" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -15779,7 +15782,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G397" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -15805,7 +15808,7 @@
         <v>13.7299995422363</v>
       </c>
       <c r="G398" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -15831,7 +15834,7 @@
         <v>13.5299997329712</v>
       </c>
       <c r="G399" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -15857,7 +15860,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G400" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -15883,7 +15886,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G401" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -15909,7 +15912,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G402" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -15935,7 +15938,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G403" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -15961,7 +15964,7 @@
         <v>13.4700002670288</v>
       </c>
       <c r="G404" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -15987,7 +15990,7 @@
         <v>13.5299997329712</v>
       </c>
       <c r="G405" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -16013,7 +16016,7 @@
         <v>13.6800003051758</v>
       </c>
       <c r="G406" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -16039,7 +16042,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G407" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -16065,7 +16068,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G408" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -16091,7 +16094,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G409" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -16117,7 +16120,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G410" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -16143,7 +16146,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G411" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -16169,7 +16172,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G412" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -16195,7 +16198,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G413" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -16221,7 +16224,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G414" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -16247,7 +16250,7 @@
         <v>13.25</v>
       </c>
       <c r="G415" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -16273,7 +16276,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G416" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -16299,7 +16302,7 @@
         <v>13</v>
       </c>
       <c r="G417" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -16325,7 +16328,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G418" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -16351,7 +16354,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G419" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -16377,7 +16380,7 @@
         <v>13.2299995422363</v>
       </c>
       <c r="G420" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -16403,7 +16406,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G421" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -16429,7 +16432,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G422" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -16455,7 +16458,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G423" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -16481,7 +16484,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G424" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -16507,7 +16510,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G425" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -16533,7 +16536,7 @@
         <v>13</v>
       </c>
       <c r="G426" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -16559,7 +16562,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G427" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -16585,7 +16588,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G428" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -16611,7 +16614,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G429" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -16637,7 +16640,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G430" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -16663,7 +16666,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G431" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -16689,7 +16692,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G432" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -16715,7 +16718,7 @@
         <v>13.25</v>
       </c>
       <c r="G433" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -16741,7 +16744,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G434" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -16767,7 +16770,7 @@
         <v>13.2299995422363</v>
       </c>
       <c r="G435" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -16793,7 +16796,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G436" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -16819,7 +16822,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G437" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -16845,7 +16848,7 @@
         <v>13</v>
       </c>
       <c r="G438" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -16871,7 +16874,7 @@
         <v>13.210000038147</v>
       </c>
       <c r="G439" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -16897,7 +16900,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G440" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -16923,7 +16926,7 @@
         <v>13.4300003051758</v>
       </c>
       <c r="G441" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -16949,7 +16952,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G442" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -16975,7 +16978,7 @@
         <v>13.4099998474121</v>
       </c>
       <c r="G443" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -17001,7 +17004,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G444" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -17027,7 +17030,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G445" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -17053,7 +17056,7 @@
         <v>13.2700004577637</v>
       </c>
       <c r="G446" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -17079,7 +17082,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G447" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -17105,7 +17108,7 @@
         <v>13.2700004577637</v>
       </c>
       <c r="G448" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -17131,7 +17134,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G449" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -17157,7 +17160,7 @@
         <v>13.25</v>
       </c>
       <c r="G450" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -17183,7 +17186,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G451" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -17209,7 +17212,7 @@
         <v>12.9700002670288</v>
       </c>
       <c r="G452" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -17235,7 +17238,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G453" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -17261,7 +17264,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G454" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -17287,7 +17290,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G455" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -17313,7 +17316,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G456" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -17339,7 +17342,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G457" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -17365,7 +17368,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G458" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -17391,7 +17394,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G459" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -17417,7 +17420,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G460" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -17443,7 +17446,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G461" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -17469,7 +17472,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G462" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -17521,7 +17524,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G464" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -17573,7 +17576,7 @@
         <v>12.75</v>
       </c>
       <c r="G466" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -17599,7 +17602,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G467" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -17625,7 +17628,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G468" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -17651,7 +17654,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G469" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -17677,7 +17680,7 @@
         <v>13.1899995803833</v>
       </c>
       <c r="G470" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -17703,7 +17706,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G471" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -17729,7 +17732,7 @@
         <v>13.1899995803833</v>
       </c>
       <c r="G472" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -17755,7 +17758,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G473" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -17807,7 +17810,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G475" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -17833,7 +17836,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G476" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -17859,7 +17862,7 @@
         <v>12.6899995803833</v>
       </c>
       <c r="G477" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -17885,7 +17888,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G478" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -17911,7 +17914,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G479" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -17937,7 +17940,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G480" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -17963,7 +17966,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G481" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -17989,7 +17992,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G482" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -18015,7 +18018,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G483" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -18041,7 +18044,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G484" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -18067,7 +18070,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G485" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -18119,7 +18122,7 @@
         <v>12.3699998855591</v>
       </c>
       <c r="G487" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -18145,7 +18148,7 @@
         <v>12.5100002288818</v>
       </c>
       <c r="G488" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -18171,7 +18174,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G489" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -18197,7 +18200,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G490" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -18223,7 +18226,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G491" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -18249,7 +18252,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G492" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -18275,7 +18278,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G493" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -18301,7 +18304,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G494" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -18327,7 +18330,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G495" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -18353,7 +18356,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G496" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -18379,7 +18382,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G497" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -18405,7 +18408,7 @@
         <v>12.75</v>
       </c>
       <c r="G498" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -18431,7 +18434,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G499" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -18457,7 +18460,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G500" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -18483,7 +18486,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G501" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -18509,7 +18512,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G502" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -18535,7 +18538,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G503" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -18561,7 +18564,7 @@
         <v>13</v>
       </c>
       <c r="G504" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -18587,7 +18590,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G505" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -18613,7 +18616,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G506" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -18639,7 +18642,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G507" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -18665,7 +18668,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G508" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -18691,7 +18694,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G509" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -18717,7 +18720,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G510" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -18743,7 +18746,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G511" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -18769,7 +18772,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G512" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -18795,7 +18798,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G513" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -18821,7 +18824,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G514" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -18847,7 +18850,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G515" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -18873,7 +18876,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G516" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -18899,7 +18902,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G517" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -18925,7 +18928,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G518" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -18951,7 +18954,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G519" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -18977,7 +18980,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G520" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -19003,7 +19006,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G521" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -19029,7 +19032,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G522" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -19055,7 +19058,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G523" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -19081,7 +19084,7 @@
         <v>15</v>
       </c>
       <c r="G524" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -19107,7 +19110,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G525" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -19133,7 +19136,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G526" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -19159,7 +19162,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G527" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -19185,7 +19188,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G528" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -19211,7 +19214,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G529" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -19237,7 +19240,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G530" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -19263,7 +19266,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G531" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -19289,7 +19292,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G532" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -19315,7 +19318,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G533" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -19341,7 +19344,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G534" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -19367,7 +19370,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G535" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -19393,7 +19396,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G536" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -19419,7 +19422,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G537" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -19445,7 +19448,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G538" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -19471,7 +19474,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G539" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -19497,7 +19500,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G540" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -19523,7 +19526,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G541" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -19549,7 +19552,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G542" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -19575,7 +19578,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G543" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -19601,7 +19604,7 @@
         <v>14</v>
       </c>
       <c r="G544" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -19627,7 +19630,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G545" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -19653,7 +19656,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G546" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -19679,7 +19682,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G547" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -19705,7 +19708,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G548" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -19731,7 +19734,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G549" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -19757,7 +19760,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G550" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -19783,7 +19786,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G551" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -19809,7 +19812,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G552" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -19835,7 +19838,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G553" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -19887,7 +19890,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G555" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -19913,7 +19916,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G556" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -19939,7 +19942,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G557" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -19965,7 +19968,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G558" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -19991,7 +19994,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G559" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -20017,7 +20020,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G560" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -20043,7 +20046,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G561" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -20069,7 +20072,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G562" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -20095,7 +20098,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G563" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -20121,7 +20124,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G564" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -20147,7 +20150,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G565" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -20173,7 +20176,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G566" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -20199,7 +20202,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G567" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -20225,7 +20228,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G568" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -20251,7 +20254,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G569" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -20277,7 +20280,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G570" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -20303,7 +20306,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G571" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -20329,7 +20332,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G572" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -20355,7 +20358,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G573" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -20381,7 +20384,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G574" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -20407,7 +20410,7 @@
         <v>13</v>
       </c>
       <c r="G575" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -20433,7 +20436,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G576" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -20459,7 +20462,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G577" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -20485,7 +20488,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G578" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -20511,7 +20514,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G579" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -20537,7 +20540,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G580" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -20563,7 +20566,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G581" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -20589,7 +20592,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G582" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -20615,7 +20618,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G583" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -20641,7 +20644,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G584" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -20667,7 +20670,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G585" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -20693,7 +20696,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G586" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -20719,7 +20722,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G587" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -20745,7 +20748,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G588" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -20771,7 +20774,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G589" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -20797,7 +20800,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G590" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -20823,7 +20826,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G591" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -20849,7 +20852,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G592" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -20875,7 +20878,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G593" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -20901,7 +20904,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G594" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -20927,7 +20930,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G595" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -20953,7 +20956,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G596" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -20979,7 +20982,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G597" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -21005,7 +21008,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G598" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -21031,7 +21034,7 @@
         <v>16</v>
       </c>
       <c r="G599" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -21057,7 +21060,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G600" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -21083,7 +21086,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G601" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -21109,7 +21112,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G602" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -21135,7 +21138,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G603" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -21161,7 +21164,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G604" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -21187,7 +21190,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G605" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -21213,7 +21216,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G606" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -21239,7 +21242,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G607" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -21265,7 +21268,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G608" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -21291,7 +21294,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G609" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -21317,7 +21320,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G610" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -21343,7 +21346,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G611" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -21369,7 +21372,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G612" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -21395,7 +21398,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G613" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -21421,7 +21424,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G614" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -21447,7 +21450,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G615" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -21473,7 +21476,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G616" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -21499,7 +21502,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G617" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -21525,7 +21528,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G618" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -21551,7 +21554,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G619" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -21577,7 +21580,7 @@
         <v>13.5</v>
       </c>
       <c r="G620" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -21603,7 +21606,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G621" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -21629,7 +21632,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G622" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -21655,7 +21658,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G623" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -21681,7 +21684,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G624" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -21707,7 +21710,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G625" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -21733,7 +21736,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G626" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -21759,7 +21762,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G627" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -21785,7 +21788,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G628" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -21811,7 +21814,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G629" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -21837,7 +21840,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G630" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -21863,7 +21866,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G631" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -21889,7 +21892,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G632" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -21915,7 +21918,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G633" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -21941,7 +21944,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G634" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -21967,7 +21970,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G635" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -21993,7 +21996,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G636" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -22019,7 +22022,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G637" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -22045,7 +22048,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G638" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -22071,7 +22074,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G639" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -22097,7 +22100,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G640" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -22123,7 +22126,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G641" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -22149,7 +22152,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G642" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -22175,7 +22178,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G643" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -22201,7 +22204,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G644" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -22227,7 +22230,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G645" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -22253,7 +22256,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G646" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -22279,7 +22282,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G647" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -22305,7 +22308,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G648" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -22331,7 +22334,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G649" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -22357,7 +22360,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G650" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -22383,7 +22386,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G651" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -22409,7 +22412,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G652" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -22435,7 +22438,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G653" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -22461,7 +22464,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G654" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -22487,7 +22490,7 @@
         <v>13</v>
       </c>
       <c r="G655" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -22513,7 +22516,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G656" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -22539,7 +22542,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G657" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -22565,7 +22568,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G658" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -22591,7 +22594,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G659" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -22617,7 +22620,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G660" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -22643,7 +22646,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G661" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -22669,7 +22672,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G662" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -22695,7 +22698,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G663" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -22721,7 +22724,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G664" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -22747,7 +22750,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G665" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -22773,7 +22776,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G666" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -22799,7 +22802,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G667" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -22825,7 +22828,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G668" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -22851,7 +22854,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G669" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -22877,7 +22880,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G670" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -22903,7 +22906,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G671" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -22929,7 +22932,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G672" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -22955,7 +22958,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G673" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -22981,7 +22984,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G674" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -23007,7 +23010,7 @@
         <v>14.9399995803833</v>
       </c>
       <c r="G675" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -23033,7 +23036,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G676" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -23059,7 +23062,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G677" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -23085,7 +23088,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G678" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -23111,7 +23114,7 @@
         <v>14.5</v>
       </c>
       <c r="G679" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -23137,7 +23140,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G680" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -23163,7 +23166,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G681" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -23189,7 +23192,7 @@
         <v>14.5600004196167</v>
       </c>
       <c r="G682" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -23215,7 +23218,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G683" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -23241,7 +23244,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G684" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -23267,7 +23270,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G685" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -23293,7 +23296,7 @@
         <v>15</v>
       </c>
       <c r="G686" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -23319,7 +23322,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G687" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -23345,7 +23348,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G688" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -23371,7 +23374,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G689" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -23397,7 +23400,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G690" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -23423,7 +23426,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G691" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -23449,7 +23452,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G692" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -23475,7 +23478,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G693" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -23501,7 +23504,7 @@
         <v>17.5</v>
       </c>
       <c r="G694" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -23527,7 +23530,7 @@
         <v>17.6800003051758</v>
       </c>
       <c r="G695" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -23553,7 +23556,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G696" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -23579,7 +23582,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G697" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -23605,7 +23608,7 @@
         <v>17.5</v>
       </c>
       <c r="G698" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -23631,7 +23634,7 @@
         <v>17.5</v>
       </c>
       <c r="G699" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -23657,7 +23660,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G700" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -23683,7 +23686,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G701" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -23709,7 +23712,7 @@
         <v>16.5</v>
       </c>
       <c r="G702" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -23735,7 +23738,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G703" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -23761,7 +23764,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G704" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -23787,7 +23790,7 @@
         <v>16.5</v>
       </c>
       <c r="G705" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -23813,7 +23816,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G706" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -23839,7 +23842,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G707" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -23865,7 +23868,7 @@
         <v>16</v>
       </c>
       <c r="G708" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -23891,7 +23894,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G709" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -23917,7 +23920,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G710" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -23943,7 +23946,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G711" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -23969,7 +23972,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G712" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -23995,7 +23998,7 @@
         <v>15.5</v>
       </c>
       <c r="G713" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -24021,7 +24024,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G714" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -24047,7 +24050,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G715" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -24073,7 +24076,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G716" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -24099,7 +24102,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G717" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -24125,7 +24128,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G718" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -24151,7 +24154,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G719" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -24177,7 +24180,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G720" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -24203,7 +24206,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G721" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -24229,7 +24232,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G722" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -24255,7 +24258,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G723" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -24281,7 +24284,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G724" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -24307,7 +24310,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G725" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -24333,7 +24336,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G726" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -24359,7 +24362,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G727" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -24385,7 +24388,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G728" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -24411,7 +24414,7 @@
         <v>16.5</v>
       </c>
       <c r="G729" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -24437,7 +24440,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G730" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -24463,7 +24466,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G731" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -24489,7 +24492,7 @@
         <v>16</v>
       </c>
       <c r="G732" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -24515,7 +24518,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G733" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -24541,7 +24544,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G734" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -24567,7 +24570,7 @@
         <v>17</v>
       </c>
       <c r="G735" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -24593,7 +24596,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G736" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -24619,7 +24622,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G737" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -24645,7 +24648,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G738" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -24671,7 +24674,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G739" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -24697,7 +24700,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G740" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -24723,7 +24726,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G741" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -24749,7 +24752,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G742" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -24775,7 +24778,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G743" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -24801,7 +24804,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G744" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -24827,7 +24830,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G745" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -24853,7 +24856,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G746" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -24879,7 +24882,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G747" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -24905,7 +24908,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G748" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -24931,7 +24934,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G749" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -24957,7 +24960,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G750" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -24983,7 +24986,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G751" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -25009,7 +25012,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G752" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -25035,7 +25038,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G753" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -25061,7 +25064,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G754" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -25087,7 +25090,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G755" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -25113,7 +25116,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G756" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -25139,7 +25142,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G757" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -25165,7 +25168,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G758" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -25191,7 +25194,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G759" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -25217,7 +25220,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G760" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -25243,7 +25246,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G761" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -25269,7 +25272,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G762" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -25295,7 +25298,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G763" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -25321,7 +25324,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G764" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -25347,7 +25350,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G765" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -25373,7 +25376,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G766" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -25399,7 +25402,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G767" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -25425,7 +25428,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G768" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -25451,7 +25454,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G769" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -25477,7 +25480,7 @@
         <v>16.5</v>
       </c>
       <c r="G770" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -25503,7 +25506,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G771" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -25529,7 +25532,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G772" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -25555,7 +25558,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G773" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -25581,7 +25584,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G774" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -25607,7 +25610,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G775" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -25633,7 +25636,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G776" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -25659,7 +25662,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G777" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -25685,7 +25688,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G778" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -25711,7 +25714,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G779" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -25737,7 +25740,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G780" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -25763,7 +25766,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G781" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -25789,7 +25792,7 @@
         <v>17</v>
       </c>
       <c r="G782" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -25815,7 +25818,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G783" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -25841,7 +25844,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G784" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -25867,7 +25870,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G785" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -25893,7 +25896,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G786" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -25919,7 +25922,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G787" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -25945,7 +25948,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G788" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -25971,7 +25974,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G789" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -25997,7 +26000,7 @@
         <v>16.5</v>
       </c>
       <c r="G790" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -26023,7 +26026,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G791" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -26049,7 +26052,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G792" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -26075,7 +26078,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G793" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -26101,7 +26104,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G794" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -26127,7 +26130,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G795" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -26153,7 +26156,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G796" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -26179,7 +26182,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G797" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -26205,7 +26208,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G798" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -26231,7 +26234,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G799" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -26257,7 +26260,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G800" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -26283,7 +26286,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G801" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -26309,7 +26312,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G802" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -26335,7 +26338,7 @@
         <v>16</v>
       </c>
       <c r="G803" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -26361,7 +26364,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G804" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -26387,7 +26390,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G805" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -26413,7 +26416,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G806" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -26439,7 +26442,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G807" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -26465,7 +26468,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G808" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -26491,7 +26494,7 @@
         <v>18</v>
       </c>
       <c r="G809" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -26517,7 +26520,7 @@
         <v>18.2399997711182</v>
       </c>
       <c r="G810" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -26543,7 +26546,7 @@
         <v>18.2600002288818</v>
       </c>
       <c r="G811" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -26569,7 +26572,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G812" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -26595,7 +26598,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G813" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -26621,7 +26624,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G814" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -26647,7 +26650,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G815" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -26673,7 +26676,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G816" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -26699,7 +26702,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G817" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -26725,7 +26728,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G818" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -26751,7 +26754,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G819" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -26777,7 +26780,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G820" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -26803,7 +26806,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G821" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -26829,7 +26832,7 @@
         <v>18</v>
       </c>
       <c r="G822" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -26855,7 +26858,7 @@
         <v>18</v>
       </c>
       <c r="G823" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -26881,7 +26884,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G824" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -26907,7 +26910,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G825" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -26933,7 +26936,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G826" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -26959,7 +26962,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G827" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -26985,7 +26988,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G828" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -27011,7 +27014,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G829" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -27037,7 +27040,7 @@
         <v>18.8600006103516</v>
       </c>
       <c r="G830" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -27063,7 +27066,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G831" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -27089,7 +27092,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G832" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -27115,7 +27118,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G833" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -27141,7 +27144,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G834" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -27167,7 +27170,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G835" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -27193,7 +27196,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G836" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -27219,7 +27222,7 @@
         <v>18</v>
       </c>
       <c r="G837" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -27245,7 +27248,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G838" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -27271,7 +27274,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G839" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -27297,7 +27300,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G840" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -27323,7 +27326,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G841" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -27349,7 +27352,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G842" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -27375,7 +27378,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G843" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -27401,7 +27404,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G844" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -27427,7 +27430,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G845" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -27453,7 +27456,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G846" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -27479,7 +27482,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G847" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -27505,7 +27508,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G848" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -27531,7 +27534,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G849" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -27557,7 +27560,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G850" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -27583,7 +27586,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G851" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -27609,7 +27612,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G852" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -27635,7 +27638,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G853" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -27661,7 +27664,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G854" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -27687,7 +27690,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G855" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -27713,7 +27716,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G856" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -27739,7 +27742,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G857" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -27765,7 +27768,7 @@
         <v>17.5</v>
       </c>
       <c r="G858" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -27791,7 +27794,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G859" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -27817,7 +27820,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G860" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -27843,7 +27846,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G861" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -27869,7 +27872,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G862" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -27895,7 +27898,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G863" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -27921,7 +27924,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G864" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -27947,7 +27950,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G865" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -27973,7 +27976,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G866" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -27999,7 +28002,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G867" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -28025,7 +28028,7 @@
         <v>17.1200008392334</v>
       </c>
       <c r="G868" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -28051,7 +28054,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G869" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -28077,7 +28080,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G870" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -28103,7 +28106,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G871" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -28129,7 +28132,7 @@
         <v>16.5</v>
       </c>
       <c r="G872" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -28155,7 +28158,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G873" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -28181,7 +28184,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G874" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -28207,7 +28210,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G875" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -28233,7 +28236,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G876" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -28259,7 +28262,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G877" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -28285,7 +28288,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G878" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -28311,7 +28314,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G879" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -28337,7 +28340,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G880" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -28363,7 +28366,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G881" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -28389,7 +28392,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G882" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -28415,7 +28418,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G883" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -28441,7 +28444,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G884" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -28467,7 +28470,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G885" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -28493,7 +28496,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G886" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -28519,7 +28522,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G887" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -28545,7 +28548,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G888" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -28571,7 +28574,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G889" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -28597,7 +28600,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G890" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -28623,7 +28626,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G891" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -28649,7 +28652,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G892" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -28675,7 +28678,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G893" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -28701,7 +28704,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G894" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -28727,7 +28730,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G895" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -28753,7 +28756,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G896" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -28779,7 +28782,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G897" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -28805,7 +28808,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G898" t="s">
-        <v>592</v>
+        <v>403</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -28883,7 +28886,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G901" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -28935,7 +28938,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G903" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -29065,7 +29068,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G908" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -29091,7 +29094,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G909" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -29143,7 +29146,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G911" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -29169,7 +29172,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G912" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -29221,7 +29224,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G914" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -29611,7 +29614,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G929" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -29663,7 +29666,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G931" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -29715,7 +29718,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G933" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -30001,7 +30004,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G944" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -30053,7 +30056,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G946" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -30157,7 +30160,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G950" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -30183,7 +30186,7 @@
         <v>16.5</v>
       </c>
       <c r="G951" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -30235,7 +30238,7 @@
         <v>16.5</v>
       </c>
       <c r="G953" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -30261,7 +30264,7 @@
         <v>16.5</v>
       </c>
       <c r="G954" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -30365,7 +30368,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G958" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -30417,7 +30420,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G960" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -30521,7 +30524,7 @@
         <v>16.5</v>
       </c>
       <c r="G964" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -30547,7 +30550,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G965" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -30625,7 +30628,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G968" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -30729,7 +30732,7 @@
         <v>17.5</v>
       </c>
       <c r="G972" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -30859,7 +30862,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G977" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -33095,7 +33098,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G1063" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -33537,7 +33540,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1080" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -33719,7 +33722,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G1087" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -33875,7 +33878,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G1093" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -33979,7 +33982,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G1097" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -34109,7 +34112,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G1102" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -34135,7 +34138,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1103" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -34187,7 +34190,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G1105" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -34473,7 +34476,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G1116" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -34499,7 +34502,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1117" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -70855,7 +70858,7 @@
     </row>
     <row r="2516">
       <c r="A2516" s="1" t="n">
-        <v>45981.6925</v>
+        <v>45981.3333333333</v>
       </c>
       <c r="B2516" t="n">
         <v>15892</v>
@@ -70876,6 +70879,32 @@
         <v>1704</v>
       </c>
       <c r="H2516" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2517">
+      <c r="A2517" s="1" t="n">
+        <v>45982.691099537</v>
+      </c>
+      <c r="B2517" t="n">
+        <v>32302</v>
+      </c>
+      <c r="C2517" t="n">
+        <v>41.4000015258789</v>
+      </c>
+      <c r="D2517" t="n">
+        <v>40.4000015258789</v>
+      </c>
+      <c r="E2517" t="n">
+        <v>40.9000015258789</v>
+      </c>
+      <c r="F2517" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="G2517" t="s">
+        <v>1705</v>
+      </c>
+      <c r="H2517" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MOL.MI.xlsx
+++ b/data/MOL.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1719" uniqueCount="1719">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1720" uniqueCount="1720">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85066080093384</t>
+    <t xml:space="preserve">6.85066032409668</t>
   </si>
   <si>
     <t xml:space="preserve">MOL.MI</t>
@@ -47,13 +47,13 @@
     <t xml:space="preserve">6.75772619247437</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66036605834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77100324630737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63823843002319</t>
+    <t xml:space="preserve">6.66036558151245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77100229263306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63823699951172</t>
   </si>
   <si>
     <t xml:space="preserve">6.72674751281738</t>
@@ -62,34 +62,34 @@
     <t xml:space="preserve">6.81525754928589</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54972791671753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31960296630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09832859039307</t>
+    <t xml:space="preserve">6.54972839355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31960153579712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09832715988159</t>
   </si>
   <si>
     <t xml:space="preserve">6.35058116912842</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23994302749634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55857944488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46121883392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89475584030151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52317571640015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65593957901001</t>
+    <t xml:space="preserve">6.23994398117065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5585789680481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46121835708618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89475440979004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52317523956299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65594053268433</t>
   </si>
   <si>
     <t xml:space="preserve">6.76215124130249</t>
@@ -98,10 +98,10 @@
     <t xml:space="preserve">6.66479110717773</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69134473800659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68249273300171</t>
+    <t xml:space="preserve">6.69134426116943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68249320983887</t>
   </si>
   <si>
     <t xml:space="preserve">6.01866912841797</t>
@@ -113,52 +113,52 @@
     <t xml:space="preserve">6.28419828414917</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06292486190796</t>
+    <t xml:space="preserve">6.06292343139648</t>
   </si>
   <si>
     <t xml:space="preserve">6.25322008132935</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39926099777222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34173011779785</t>
+    <t xml:space="preserve">6.39926147460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34172964096069</t>
   </si>
   <si>
     <t xml:space="preserve">6.50989866256714</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33287954330444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42581415176392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39040994644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30632591247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40811204910278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35500764846802</t>
+    <t xml:space="preserve">6.33287858963013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42581462860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39041042327881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30632638931274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40811157226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3550066947937</t>
   </si>
   <si>
     <t xml:space="preserve">6.63381195068359</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43466520309448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2266674041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24436950683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27534818649292</t>
+    <t xml:space="preserve">6.43466567993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22666692733765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24436902999878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2753472328186</t>
   </si>
   <si>
     <t xml:space="preserve">6.26649713516235</t>
@@ -167,34 +167,34 @@
     <t xml:space="preserve">6.62938642501831</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43909168243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41253757476807</t>
+    <t xml:space="preserve">6.43909120559692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41253709793091</t>
   </si>
   <si>
     <t xml:space="preserve">6.45236730575562</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45679330825806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36828327178955</t>
+    <t xml:space="preserve">6.4567928314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36828374862671</t>
   </si>
   <si>
     <t xml:space="preserve">6.19568872451782</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06734895706177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28862333297729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20454025268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29304933547974</t>
+    <t xml:space="preserve">6.06734943389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28862380981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20454072952271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29304981231689</t>
   </si>
   <si>
     <t xml:space="preserve">6.24879455566406</t>
@@ -203,34 +203,34 @@
     <t xml:space="preserve">6.22224235534668</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25764608383179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15585947036743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1912636756897</t>
+    <t xml:space="preserve">6.25764513015747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15585851669312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19126272201538</t>
   </si>
   <si>
     <t xml:space="preserve">6.58955764770508</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47892045974731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49662208557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42138862609863</t>
+    <t xml:space="preserve">6.47892093658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49662303924561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42138910293579</t>
   </si>
   <si>
     <t xml:space="preserve">6.63349008560181</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45274066925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54311466217041</t>
+    <t xml:space="preserve">6.45273923873901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54311418533325</t>
   </si>
   <si>
     <t xml:space="preserve">6.44370269775391</t>
@@ -239,13 +239,13 @@
     <t xml:space="preserve">6.50696468353271</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55667066574097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36688470840454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61993312835693</t>
+    <t xml:space="preserve">6.55667114257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36688423156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61993265151978</t>
   </si>
   <si>
     <t xml:space="preserve">6.69223260879517</t>
@@ -254,16 +254,16 @@
     <t xml:space="preserve">6.59733963012695</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68319606781006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70578908920288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75097513198853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85038757324219</t>
+    <t xml:space="preserve">6.68319463729858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70578861236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75097608566284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85038805007935</t>
   </si>
   <si>
     <t xml:space="preserve">6.94528102874756</t>
@@ -278,37 +278,37 @@
     <t xml:space="preserve">7.25255393981934</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32033586502075</t>
+    <t xml:space="preserve">7.32033634185791</t>
   </si>
   <si>
     <t xml:space="preserve">7.45589733123779</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3022608757019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37907934188843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25707340240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22996139526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22544240951538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19832944869995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09439897537231</t>
+    <t xml:space="preserve">7.30226039886475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37907838821411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25707244873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22996091842651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22544193267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19833087921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09439992904663</t>
   </si>
   <si>
     <t xml:space="preserve">7.13958644866943</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00402498245239</t>
+    <t xml:space="preserve">7.00402450561523</t>
   </si>
   <si>
     <t xml:space="preserve">7.08084297180176</t>
@@ -317,46 +317,46 @@
     <t xml:space="preserve">6.95883750915527</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84135150909424</t>
+    <t xml:space="preserve">6.84135103225708</t>
   </si>
   <si>
     <t xml:space="preserve">7.11699342727661</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16669940948486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31129884719849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32485389709473</t>
+    <t xml:space="preserve">7.16669893264771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31129789352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32485437393188</t>
   </si>
   <si>
     <t xml:space="preserve">6.9995059967041</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73290061950684</t>
+    <t xml:space="preserve">6.73290014266968</t>
   </si>
   <si>
     <t xml:space="preserve">7.08988094329834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18477392196655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85942554473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67867565155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49792766571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57022714614868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57926416397095</t>
+    <t xml:space="preserve">7.18477344512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85942602157593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67867612838745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49792671203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57022762298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57926464080811</t>
   </si>
   <si>
     <t xml:space="preserve">6.41659021377563</t>
@@ -371,61 +371,61 @@
     <t xml:space="preserve">6.55215215682983</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46177864074707</t>
+    <t xml:space="preserve">6.46177768707275</t>
   </si>
   <si>
     <t xml:space="preserve">6.43466472625732</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75549411773682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56570816040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77808904647827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71030759811401</t>
+    <t xml:space="preserve">6.75549459457397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56570863723755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7780876159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71030807495117</t>
   </si>
   <si>
     <t xml:space="preserve">6.48889017105103</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53859615325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66060209274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68771505355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76001358032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87750053405762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70127058029175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78712701797485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7961630821228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81423807144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8187575340271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82327556610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8052020072937</t>
+    <t xml:space="preserve">6.53859567642212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66060161590576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68771409988403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76001262664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87750148773193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70126962661743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7871265411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79616403579712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81423854827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81875705718994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82327604293823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80520105361938</t>
   </si>
   <si>
     <t xml:space="preserve">6.92268753051758</t>
@@ -434,16 +434,16 @@
     <t xml:space="preserve">6.90461254119873</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86846351623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98143148422241</t>
+    <t xml:space="preserve">6.86846256256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98143196105957</t>
   </si>
   <si>
     <t xml:space="preserve">7.17573642730713</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01306295394897</t>
+    <t xml:space="preserve">7.01306247711182</t>
   </si>
   <si>
     <t xml:space="preserve">6.97691202163696</t>
@@ -458,37 +458,37 @@
     <t xml:space="preserve">6.88653802871704</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93172550201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02209949493408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99046802520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19381093978882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05824899673462</t>
+    <t xml:space="preserve">6.93172454833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02209997177124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99046850204468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19381141662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05824947357178</t>
   </si>
   <si>
     <t xml:space="preserve">7.04921197891235</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06728649139404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14862442016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08536195755005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06276845932007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15766191482544</t>
+    <t xml:space="preserve">7.06728744506836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14862298965454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08536243438721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06276798248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15766143798828</t>
   </si>
   <si>
     <t xml:space="preserve">7.21188545227051</t>
@@ -506,64 +506,64 @@
     <t xml:space="preserve">7.18929290771484</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35648536682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37004137039185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88201951980591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03565645217896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18025541305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91365051269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51915884017944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47848987579346</t>
+    <t xml:space="preserve">7.35648584365845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37004089355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88201904296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03565502166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18025493621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91365003585815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51915979385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47849082946777</t>
   </si>
   <si>
     <t xml:space="preserve">7.50108480453491</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41070985794067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27514886856079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60953378677368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66375923156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72702169418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68183422088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67731332778931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63664579391479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77220869064331</t>
+    <t xml:space="preserve">7.41070938110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27514839172363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.609534740448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66375875473022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72702121734619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68183374404907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67731475830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63664674758911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77220821380615</t>
   </si>
   <si>
     <t xml:space="preserve">7.971031665802</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34156799316406</t>
+    <t xml:space="preserve">8.34156703948975</t>
   </si>
   <si>
     <t xml:space="preserve">8.41386795043945</t>
@@ -572,31 +572,31 @@
     <t xml:space="preserve">8.45001792907715</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57654094696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37771797180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.409348487854</t>
+    <t xml:space="preserve">8.57654285430908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37771892547607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40934944152832</t>
   </si>
   <si>
     <t xml:space="preserve">8.35964298248291</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22408103942871</t>
+    <t xml:space="preserve">8.22408199310303</t>
   </si>
   <si>
     <t xml:space="preserve">8.24215507507324</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33704853057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32801151275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32349395751953</t>
+    <t xml:space="preserve">8.33704948425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32801246643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32349300384521</t>
   </si>
   <si>
     <t xml:space="preserve">8.36416149139404</t>
@@ -605,22 +605,22 @@
     <t xml:space="preserve">8.37319946289062</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46809196472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30541706085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30089950561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09755802154541</t>
+    <t xml:space="preserve">8.468092918396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30541801452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3008975982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09755706787109</t>
   </si>
   <si>
     <t xml:space="preserve">8.26926803588867</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20600605010986</t>
+    <t xml:space="preserve">8.20600700378418</t>
   </si>
   <si>
     <t xml:space="preserve">8.07496356964111</t>
@@ -629,16 +629,16 @@
     <t xml:space="preserve">8.11111259460449</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28282451629639</t>
+    <t xml:space="preserve">8.28282260894775</t>
   </si>
   <si>
     <t xml:space="preserve">8.29638195037842</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40482997894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48164749145508</t>
+    <t xml:space="preserve">8.40482902526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48164939880371</t>
   </si>
   <si>
     <t xml:space="preserve">8.42290592193604</t>
@@ -647,43 +647,43 @@
     <t xml:space="preserve">8.22859954833984</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27378559112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02977657318115</t>
+    <t xml:space="preserve">8.2737865447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02977466583252</t>
   </si>
   <si>
     <t xml:space="preserve">8.13370704650879</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27830410003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43194103240967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6940279006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57969856262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25434970855713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21820068359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01937675476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16397476196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2001256942749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20916175842285</t>
+    <t xml:space="preserve">8.27830600738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4319429397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69402885437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57969760894775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25435066223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21820163726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01937580108643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16397571563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20012664794922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20916271209717</t>
   </si>
   <si>
     <t xml:space="preserve">9.22723770141602</t>
@@ -698,10 +698,10 @@
     <t xml:space="preserve">9.12782573699951</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35376262664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55258560180664</t>
+    <t xml:space="preserve">9.35376167297363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55258655548096</t>
   </si>
   <si>
     <t xml:space="preserve">9.47124862670898</t>
@@ -713,43 +713,43 @@
     <t xml:space="preserve">9.89600944519043</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2123184204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94119644165039</t>
+    <t xml:space="preserve">10.2123193740845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94119548797607</t>
   </si>
   <si>
     <t xml:space="preserve">10.4472942352295</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8449411392212</t>
+    <t xml:space="preserve">10.8449430465698</t>
   </si>
   <si>
     <t xml:space="preserve">10.8087921142578</t>
   </si>
   <si>
-    <t xml:space="preserve">10.908203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9353179931641</t>
+    <t xml:space="preserve">10.9082040786743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9353151321411</t>
   </si>
   <si>
     <t xml:space="preserve">10.7364921569824</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7093811035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.754566192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4764318466187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.226110458374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0128726959229</t>
+    <t xml:space="preserve">10.7093801498413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7545671463013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4764308929443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2261095046997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0128736495972</t>
   </si>
   <si>
     <t xml:space="preserve">10.3837194442749</t>
@@ -758,40 +758,40 @@
     <t xml:space="preserve">10.4300756454468</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2817373275757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4022617340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5135173797607</t>
+    <t xml:space="preserve">10.2817363739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4022626876831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5135164260864</t>
   </si>
   <si>
     <t xml:space="preserve">10.4949731826782</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5413293838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7452955245972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0790576934814</t>
+    <t xml:space="preserve">10.5413303375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7452964782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0790596008301</t>
   </si>
   <si>
     <t xml:space="preserve">11.774395942688</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5889720916748</t>
+    <t xml:space="preserve">11.5889730453491</t>
   </si>
   <si>
     <t xml:space="preserve">11.2181253433228</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3015661239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0976009368896</t>
+    <t xml:space="preserve">11.3015670776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0976028442383</t>
   </si>
   <si>
     <t xml:space="preserve">11.1439571380615</t>
@@ -800,10 +800,10 @@
     <t xml:space="preserve">11.0327014923096</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8287372589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7545671463013</t>
+    <t xml:space="preserve">10.8287363052368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7545680999756</t>
   </si>
   <si>
     <t xml:space="preserve">10.7360248565674</t>
@@ -821,40 +821,40 @@
     <t xml:space="preserve">11.1254138946533</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0605163574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4869909286499</t>
+    <t xml:space="preserve">11.0605154037476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4869899749756</t>
   </si>
   <si>
     <t xml:space="preserve">11.0697860717773</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9399909973145</t>
+    <t xml:space="preserve">10.9399900436401</t>
   </si>
   <si>
     <t xml:space="preserve">11.4499063491821</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4035482406616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7094993591309</t>
+    <t xml:space="preserve">11.4035491943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7094984054565</t>
   </si>
   <si>
     <t xml:space="preserve">12.0988883972168</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3213968276978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.894923210144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5160913467407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5253620147705</t>
+    <t xml:space="preserve">12.3213958740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8949222564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5160903930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5253629684448</t>
   </si>
   <si>
     <t xml:space="preserve">12.6737003326416</t>
@@ -863,79 +863,79 @@
     <t xml:space="preserve">12.7478704452515</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5346355438232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.794225692749</t>
+    <t xml:space="preserve">12.5346345901489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7942266464233</t>
   </si>
   <si>
     <t xml:space="preserve">12.7293272018433</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5439052581787</t>
+    <t xml:space="preserve">12.5439033508301</t>
   </si>
   <si>
     <t xml:space="preserve">12.5809888839722</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5624485015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4697351455688</t>
+    <t xml:space="preserve">12.5624465942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4697360992432</t>
   </si>
   <si>
     <t xml:space="preserve">12.4975490570068</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4882783889771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.68297290802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6273460388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5531759262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1823291778564</t>
+    <t xml:space="preserve">12.4882774353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6829719543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6273441314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5531768798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1823282241821</t>
   </si>
   <si>
     <t xml:space="preserve">12.3955659866333</t>
   </si>
   <si>
-    <t xml:space="preserve">12.423378944397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2935838699341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3677520751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8856506347656</t>
+    <t xml:space="preserve">12.4233798980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2935829162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3677530288696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8856515884399</t>
   </si>
   <si>
     <t xml:space="preserve">12.28431224823</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1730585098267</t>
+    <t xml:space="preserve">12.1730575561523</t>
   </si>
   <si>
     <t xml:space="preserve">12.0525321960449</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9505500793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.312126159668</t>
+    <t xml:space="preserve">11.9505491256714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3121252059937</t>
   </si>
   <si>
     <t xml:space="preserve">12.2657699584961</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9412794113159</t>
+    <t xml:space="preserve">11.9412775039673</t>
   </si>
   <si>
     <t xml:space="preserve">11.9598197937012</t>
@@ -944,64 +944,64 @@
     <t xml:space="preserve">12.3306684494019</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4419240951538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3492107391357</t>
+    <t xml:space="preserve">12.4419212341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3492088317871</t>
   </si>
   <si>
     <t xml:space="preserve">12.3770246505737</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1545152664185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2472267150879</t>
+    <t xml:space="preserve">12.1545143127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2472286224365</t>
   </si>
   <si>
     <t xml:space="preserve">12.3399391174316</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4511938095093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2008714675903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4326496124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3028545379639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2564992904663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.061803817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0247182846069</t>
+    <t xml:space="preserve">12.451192855835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.200870513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4326505661011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3028554916382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.256498336792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0618028640747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0247192382812</t>
   </si>
   <si>
     <t xml:space="preserve">11.440634727478</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6353311538696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7929410934448</t>
+    <t xml:space="preserve">11.6353302001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7929401397705</t>
   </si>
   <si>
     <t xml:space="preserve">11.663143157959</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6816854476929</t>
+    <t xml:space="preserve">11.6816844940186</t>
   </si>
   <si>
     <t xml:space="preserve">11.7465839385986</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9227342605591</t>
+    <t xml:space="preserve">11.9227361679077</t>
   </si>
   <si>
     <t xml:space="preserve">11.8207540512085</t>
@@ -1013,25 +1013,25 @@
     <t xml:space="preserve">11.7373123168945</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2286853790283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1915998458862</t>
+    <t xml:space="preserve">12.2286834716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1916007995605</t>
   </si>
   <si>
     <t xml:space="preserve">11.7651252746582</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7187690734863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1903123855591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2922964096069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1624984741211</t>
+    <t xml:space="preserve">11.7187700271606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1903142929077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2922945022583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1624994277954</t>
   </si>
   <si>
     <t xml:space="preserve">11.5426168441772</t>
@@ -1040,10 +1040,10 @@
     <t xml:space="preserve">11.4684476852417</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5982456207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5797023773193</t>
+    <t xml:space="preserve">11.5982437133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.579701423645</t>
   </si>
   <si>
     <t xml:space="preserve">11.4962606430054</t>
@@ -1055,34 +1055,34 @@
     <t xml:space="preserve">11.857837677002</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1452445983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0061779022217</t>
+    <t xml:space="preserve">12.1452436447144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.006175994873</t>
   </si>
   <si>
     <t xml:space="preserve">11.9134654998779</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9240217208862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.925311088562</t>
+    <t xml:space="preserve">12.9240226745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9253120422363</t>
   </si>
   <si>
     <t xml:space="preserve">14.1107349395752</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0921907424927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9438514709473</t>
+    <t xml:space="preserve">14.092191696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9438533782959</t>
   </si>
   <si>
     <t xml:space="preserve">13.9994802474976</t>
   </si>
   <si>
-    <t xml:space="preserve">14.629919052124</t>
+    <t xml:space="preserve">14.6299180984497</t>
   </si>
   <si>
     <t xml:space="preserve">13.9067668914795</t>
@@ -1094,22 +1094,22 @@
     <t xml:space="preserve">14.2034463882446</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0180215835571</t>
+    <t xml:space="preserve">14.0180225372314</t>
   </si>
   <si>
     <t xml:space="preserve">13.7028017044067</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3888711929321</t>
+    <t xml:space="preserve">14.3888702392578</t>
   </si>
   <si>
     <t xml:space="preserve">14.5186653137207</t>
   </si>
   <si>
-    <t xml:space="preserve">14.574294090271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4815807342529</t>
+    <t xml:space="preserve">14.5742931365967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4815816879272</t>
   </si>
   <si>
     <t xml:space="preserve">14.1849031448364</t>
@@ -1121,25 +1121,25 @@
     <t xml:space="preserve">12.9981918334961</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7756843566895</t>
+    <t xml:space="preserve">12.7756834030151</t>
   </si>
   <si>
     <t xml:space="preserve">13.3690395355225</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0352783203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.738597869873</t>
+    <t xml:space="preserve">13.0352773666382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7385997772217</t>
   </si>
   <si>
     <t xml:space="preserve">12.9796495437622</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5173788070679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3134117126465</t>
+    <t xml:space="preserve">13.5173768997192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3134126663208</t>
   </si>
   <si>
     <t xml:space="preserve">12.6644296646118</t>
@@ -1148,106 +1148,106 @@
     <t xml:space="preserve">12.1081600189209</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0154485702515</t>
+    <t xml:space="preserve">12.0154476165771</t>
   </si>
   <si>
     <t xml:space="preserve">11.830023765564</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5902605056763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7200574874878</t>
+    <t xml:space="preserve">12.5902614593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7200565338135</t>
   </si>
   <si>
     <t xml:space="preserve">12.6088027954102</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1637868881226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0339908599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0710754394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6075172424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4604625701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8114795684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8485679626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2379550933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3862953186035</t>
+    <t xml:space="preserve">12.1637849807739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0339889526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0710744857788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6075162887573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4604644775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8114814758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8485651016235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2379560470581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3862943649292</t>
   </si>
   <si>
     <t xml:space="preserve">13.3504962921143</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5359201431274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7213439941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2590713500977</t>
+    <t xml:space="preserve">13.5359220504761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7213449478149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2590732574463</t>
   </si>
   <si>
     <t xml:space="preserve">14.908055305481</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7782583236694</t>
+    <t xml:space="preserve">14.7782592773438</t>
   </si>
   <si>
     <t xml:space="preserve">14.7411727905273</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7968015670776</t>
+    <t xml:space="preserve">14.796802520752</t>
   </si>
   <si>
     <t xml:space="preserve">15.02357006073</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6849880218506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4015216827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2314453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0802631378174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1180601119995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1747531890869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3070373535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.13538646698</t>
+    <t xml:space="preserve">15.6849851608276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4015207290649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2314443588257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.080265045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1180591583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1747512817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.307035446167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1353845596313</t>
   </si>
   <si>
     <t xml:space="preserve">13.8141279220581</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2660961151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6062517166138</t>
+    <t xml:space="preserve">13.2660970687866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6062536239624</t>
   </si>
   <si>
     <t xml:space="preserve">13.6818437576294</t>
@@ -1256,7 +1256,7 @@
     <t xml:space="preserve">13.0771207809448</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9448385238647</t>
+    <t xml:space="preserve">12.9448394775391</t>
   </si>
   <si>
     <t xml:space="preserve">13.1149168014526</t>
@@ -1268,28 +1268,28 @@
     <t xml:space="preserve">12.0944480895996</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5479888916016</t>
+    <t xml:space="preserve">12.5479898452759</t>
   </si>
   <si>
     <t xml:space="preserve">13.0015316009521</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6235790252686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6991691589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7558612823486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8692474365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3401174545288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.736964225769</t>
+    <t xml:space="preserve">12.6235799789429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6991701126099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7558622360229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8692493438721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3401165008545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7369651794434</t>
   </si>
   <si>
     <t xml:space="preserve">12.7180671691895</t>
@@ -1298,67 +1298,67 @@
     <t xml:space="preserve">12.7747611999512</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2645254135132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7385349273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7763328552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9653081893921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8708190917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0786924362183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6251497268677</t>
+    <t xml:space="preserve">12.2645244598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7385358810425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7763319015503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9653062820435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8708200454712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0786933898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6251516342163</t>
   </si>
   <si>
     <t xml:space="preserve">13.5873565673828</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4172792434692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4550733566284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4361763000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2471990585327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1338129043579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3227910995483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4739723205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2094039916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3605852127075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5668888092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5101947784424</t>
+    <t xml:space="preserve">13.4172782897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4550724029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4361753463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2472009658813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1338138580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.322790145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.473970413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2094030380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3605861663818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5668869018555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5101938247681</t>
   </si>
   <si>
     <t xml:space="preserve">12.2834234237671</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6802740097046</t>
+    <t xml:space="preserve">12.680272102356</t>
   </si>
   <si>
     <t xml:space="preserve">13.0393266677856</t>
@@ -1367,10 +1367,10 @@
     <t xml:space="preserve">12.9826335906982</t>
   </si>
   <si>
-    <t xml:space="preserve">12.812557220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9637365341187</t>
+    <t xml:space="preserve">12.8125553131104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9637355804443</t>
   </si>
   <si>
     <t xml:space="preserve">13.7952299118042</t>
@@ -1382,70 +1382,70 @@
     <t xml:space="preserve">14.2676696777344</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3054647445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0597944259644</t>
+    <t xml:space="preserve">14.3054637908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0597953796387</t>
   </si>
   <si>
     <t xml:space="preserve">13.7007417678833</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4928674697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7574338912964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5495615005493</t>
+    <t xml:space="preserve">13.4928693771362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7574348449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5495595932007</t>
   </si>
   <si>
     <t xml:space="preserve">14.1731805801392</t>
   </si>
   <si>
-    <t xml:space="preserve">14.929084777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4960126876831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2692394256592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1558570861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5353775024414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7054557800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9133319854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6298675537109</t>
+    <t xml:space="preserve">14.9290828704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4960088729858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2692413330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.155855178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5353755950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7054576873779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9133281707764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6298656463623</t>
   </si>
   <si>
     <t xml:space="preserve">16.2330169677734</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9117565155029</t>
+    <t xml:space="preserve">15.9117584228516</t>
   </si>
   <si>
     <t xml:space="preserve">15.5904979705811</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5149078369141</t>
+    <t xml:space="preserve">15.5149097442627</t>
   </si>
   <si>
     <t xml:space="preserve">15.0046739578247</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2125482559204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3810548782349</t>
+    <t xml:space="preserve">15.2125473022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3810539245605</t>
   </si>
   <si>
     <t xml:space="preserve">14.6078252792358</t>
@@ -1463,46 +1463,46 @@
     <t xml:space="preserve">14.1920785903931</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8897171020508</t>
+    <t xml:space="preserve">13.8897180557251</t>
   </si>
   <si>
     <t xml:space="preserve">13.5306644439697</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8519220352173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0220012664795</t>
+    <t xml:space="preserve">13.8519229888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0220003128052</t>
   </si>
   <si>
     <t xml:space="preserve">14.8723907470703</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4755420684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4188499450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5527009963989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9668798446655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0818367004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0629386901855</t>
+    <t xml:space="preserve">14.4755411148071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4188508987427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5527019500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9668788909912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0818347930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0629405975342</t>
   </si>
   <si>
     <t xml:space="preserve">16.2519149780273</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0440406799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8739604949951</t>
+    <t xml:space="preserve">16.044038772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8739624023438</t>
   </si>
   <si>
     <t xml:space="preserve">15.4582147598267</t>
@@ -1511,37 +1511,37 @@
     <t xml:space="preserve">16.0251426696777</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3464012145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1007328033447</t>
+    <t xml:space="preserve">16.3464031219482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1007347106934</t>
   </si>
   <si>
     <t xml:space="preserve">16.3275051116943</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6471920013428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7983703613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9306564331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0613651275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8550691604614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4771127700806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7401084899902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9101867675781</t>
+    <t xml:space="preserve">15.6471900939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7983713150024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9306554794312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0613670349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8550672531128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4771108627319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7401094436646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9101858139038</t>
   </si>
   <si>
     <t xml:space="preserve">14.5511322021484</t>
@@ -1556,205 +1556,205 @@
     <t xml:space="preserve">15.5338077545166</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7416801452637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0424699783325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4204216003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7605781555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6282978057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.892861366272</t>
+    <t xml:space="preserve">15.7416772842407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0424680709839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4204206466675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7605772018433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6282958984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8928594589233</t>
   </si>
   <si>
     <t xml:space="preserve">15.9684505462646</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0062446594238</t>
+    <t xml:space="preserve">16.0062465667725</t>
   </si>
   <si>
     <t xml:space="preserve">15.9873495101929</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6093978881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6834163665771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6267223358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8534936904907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1936492919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0991621017456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2881383895874</t>
+    <t xml:space="preserve">15.609395980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6834144592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6267232894897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8534927368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1936502456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0991611480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2881393432617</t>
   </si>
   <si>
     <t xml:space="preserve">16.1952209472656</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0078201293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2345905303955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2534847259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2912769317627</t>
+    <t xml:space="preserve">17.0078182220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2345886230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2534828186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.29128074646</t>
   </si>
   <si>
     <t xml:space="preserve">17.1023063659668</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0645084381104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0471858978271</t>
+    <t xml:space="preserve">17.064510345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0471839904785</t>
   </si>
   <si>
     <t xml:space="preserve">17.4046669006348</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3479747772217</t>
+    <t xml:space="preserve">17.347972869873</t>
   </si>
   <si>
     <t xml:space="preserve">17.366870880127</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4991569519043</t>
+    <t xml:space="preserve">17.4991512298584</t>
   </si>
   <si>
     <t xml:space="preserve">17.0456142425537</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3857688903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4424629211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8582096099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8204135894775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5558490753174</t>
+    <t xml:space="preserve">17.3857707977295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4424610137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8582077026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8204154968262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5558452606201</t>
   </si>
   <si>
     <t xml:space="preserve">17.3290748596191</t>
   </si>
   <si>
-    <t xml:space="preserve">17.140100479126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5731716156006</t>
+    <t xml:space="preserve">17.1400985717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5731735229492</t>
   </si>
   <si>
     <t xml:space="preserve">16.5920715332031</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2897109985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8566360473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1574287414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5805988311768</t>
+    <t xml:space="preserve">16.2897090911865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8566379547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1574268341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5805950164795</t>
   </si>
   <si>
     <t xml:space="preserve">16.5421276092529</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3882465362549</t>
+    <t xml:space="preserve">16.3882484436035</t>
   </si>
   <si>
     <t xml:space="preserve">16.4459533691406</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2343654632568</t>
+    <t xml:space="preserve">16.2343635559082</t>
   </si>
   <si>
     <t xml:space="preserve">16.0035457611084</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9843101501465</t>
+    <t xml:space="preserve">15.9843111038208</t>
   </si>
   <si>
     <t xml:space="preserve">16.6767711639404</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8114185333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8306522369385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7537117004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6382999420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4267158508301</t>
+    <t xml:space="preserve">16.8114166259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8306503295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7537136077881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6383018493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4267139434814</t>
   </si>
   <si>
     <t xml:space="preserve">16.522891998291</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9458417892456</t>
+    <t xml:space="preserve">15.9458408355713</t>
   </si>
   <si>
     <t xml:space="preserve">16.4651889801025</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9650774002075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0227813720703</t>
+    <t xml:space="preserve">15.9650754928589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0227794647217</t>
   </si>
   <si>
     <t xml:space="preserve">15.8688993453979</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7342538833618</t>
+    <t xml:space="preserve">15.7342548370361</t>
   </si>
   <si>
     <t xml:space="preserve">15.6573152542114</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4264974594116</t>
+    <t xml:space="preserve">15.4264945983887</t>
   </si>
   <si>
     <t xml:space="preserve">15.3687896728516</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3110857009888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9840888977051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1956758499146</t>
+    <t xml:space="preserve">15.3110847473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9840898513794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1956748962402</t>
   </si>
   <si>
     <t xml:space="preserve">15.2341451644897</t>
@@ -1763,67 +1763,67 @@
     <t xml:space="preserve">15.1379690170288</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0994987487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.003324508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1187343597412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2533798217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0610303878784</t>
+    <t xml:space="preserve">15.0994997024536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0033254623413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1187334060669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.253378868103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0610313415527</t>
   </si>
   <si>
     <t xml:space="preserve">14.8686790466309</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8494434356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7147998809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4457302093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1764402389526</t>
+    <t xml:space="preserve">14.8494443893433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7147989273071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4457292556763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.176438331604</t>
   </si>
   <si>
     <t xml:space="preserve">14.8302097320557</t>
   </si>
   <si>
-    <t xml:space="preserve">15.080265045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9648542404175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1572046279907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7917385101318</t>
+    <t xml:space="preserve">15.0802659988403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9648551940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1572036743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7917394638062</t>
   </si>
   <si>
     <t xml:space="preserve">14.7532682418823</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9071474075317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0225582122803</t>
+    <t xml:space="preserve">14.9071483612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0225591659546</t>
   </si>
   <si>
     <t xml:space="preserve">14.8109741210938</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8879137039185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5416831970215</t>
+    <t xml:space="preserve">14.8879127502441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5416841506958</t>
   </si>
   <si>
     <t xml:space="preserve">14.580153465271</t>
@@ -1832,58 +1832,58 @@
     <t xml:space="preserve">14.5993890762329</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5032138824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6378593444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6186237335205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4647426605225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4455089569092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.65709400177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9263849258423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5609188079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3495540618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3880252838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6765489578247</t>
+    <t xml:space="preserve">14.503212928772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6378583908081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6186227798462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4647436141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4455080032349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6570930480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9263868331909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5609197616577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.349555015564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3880243301392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6765480041504</t>
   </si>
   <si>
     <t xml:space="preserve">15.5226697921753</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7150211334229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7919597625732</t>
+    <t xml:space="preserve">15.7150192260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7919616699219</t>
   </si>
   <si>
     <t xml:space="preserve">16.1574249267578</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7727270126343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8111972808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.907374382019</t>
+    <t xml:space="preserve">15.7727222442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8111963272095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9073715209961</t>
   </si>
   <si>
     <t xml:space="preserve">15.6380805969238</t>
@@ -1892,10 +1892,10 @@
     <t xml:space="preserve">15.6188440322876</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8496646881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5803775787354</t>
+    <t xml:space="preserve">15.8496656417847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5803756713867</t>
   </si>
   <si>
     <t xml:space="preserve">15.5034351348877</t>
@@ -1904,7 +1904,7 @@
     <t xml:space="preserve">15.8304281234741</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9266061782837</t>
+    <t xml:space="preserve">15.9266052246094</t>
   </si>
   <si>
     <t xml:space="preserve">16.1189556121826</t>
@@ -1913,7 +1913,7 @@
     <t xml:space="preserve">17.1576480865479</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0037651062012</t>
+    <t xml:space="preserve">17.0037689208984</t>
   </si>
   <si>
     <t xml:space="preserve">16.9460639953613</t>
@@ -1922,19 +1922,19 @@
     <t xml:space="preserve">16.8883590698242</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9845333099365</t>
+    <t xml:space="preserve">16.9845314025879</t>
   </si>
   <si>
     <t xml:space="preserve">17.119176864624</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2730560302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2732791900635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1771049499512</t>
+    <t xml:space="preserve">17.2730579376221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2732810974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1771030426025</t>
   </si>
   <si>
     <t xml:space="preserve">17.6000518798828</t>
@@ -1946,28 +1946,28 @@
     <t xml:space="preserve">18.1001644134521</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9847583770752</t>
+    <t xml:space="preserve">17.9847526550293</t>
   </si>
   <si>
     <t xml:space="preserve">18.1193981170654</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9655170440674</t>
+    <t xml:space="preserve">17.965518951416</t>
   </si>
   <si>
     <t xml:space="preserve">17.9462852478027</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0616931915283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9270477294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3117542266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7541542053223</t>
+    <t xml:space="preserve">18.061695098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9270496368408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3117504119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7541561126709</t>
   </si>
   <si>
     <t xml:space="preserve">19.1003875732422</t>
@@ -1976,7 +1976,7 @@
     <t xml:space="preserve">19.0234470367432</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5425720214844</t>
+    <t xml:space="preserve">18.542573928833</t>
   </si>
   <si>
     <t xml:space="preserve">18.9657402038574</t>
@@ -1985,13 +1985,13 @@
     <t xml:space="preserve">18.9080352783203</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4273853302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8120803833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5235557556152</t>
+    <t xml:space="preserve">19.4273815155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8120822906494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5235538482666</t>
   </si>
   <si>
     <t xml:space="preserve">19.6678199768066</t>
@@ -2000,31 +2000,31 @@
     <t xml:space="preserve">19.2831153869629</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8503303527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6197338104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7159080505371</t>
+    <t xml:space="preserve">18.8503322601318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6197319030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7159061431885</t>
   </si>
   <si>
     <t xml:space="preserve">19.7639923095703</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3312091827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.571647644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1967811584473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2448692321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2164611816406</t>
+    <t xml:space="preserve">19.3312072753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5716438293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1967830657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2448711395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2164630889893</t>
   </si>
   <si>
     <t xml:space="preserve">21.1585330963135</t>
@@ -2036,25 +2036,25 @@
     <t xml:space="preserve">20.8219203948975</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6295738220215</t>
+    <t xml:space="preserve">20.6295700073242</t>
   </si>
   <si>
     <t xml:space="preserve">21.0142726898193</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7257442474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6776580810547</t>
+    <t xml:space="preserve">20.7257461547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6776599884033</t>
   </si>
   <si>
     <t xml:space="preserve">19.9563446044922</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2929592132568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.004430770874</t>
+    <t xml:space="preserve">20.2929573059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0044326782227</t>
   </si>
   <si>
     <t xml:space="preserve">19.8601703643799</t>
@@ -2063,10 +2063,10 @@
     <t xml:space="preserve">19.0811519622803</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7738361358643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9180965423584</t>
+    <t xml:space="preserve">20.7738342285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.918098449707</t>
   </si>
   <si>
     <t xml:space="preserve">20.5814819335938</t>
@@ -2084,64 +2084,64 @@
     <t xml:space="preserve">21.6394100189209</t>
   </si>
   <si>
-    <t xml:space="preserve">21.447057723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8317642211914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0525188446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1006088256836</t>
+    <t xml:space="preserve">21.4470596313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8317604064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0525207519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.100606918335</t>
   </si>
   <si>
     <t xml:space="preserve">18.734920501709</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1963386535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6192893981934</t>
+    <t xml:space="preserve">18.1963405609131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6192855834961</t>
   </si>
   <si>
     <t xml:space="preserve">16.3113040924072</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1958961486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4839792251587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4262723922729</t>
+    <t xml:space="preserve">16.1958980560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4839782714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4262742996216</t>
   </si>
   <si>
     <t xml:space="preserve">12.4643001556396</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0218944549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1373043060303</t>
+    <t xml:space="preserve">12.0218954086304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.137303352356</t>
   </si>
   <si>
     <t xml:space="preserve">12.6951208114624</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9067068099976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9834251403809</t>
+    <t xml:space="preserve">12.9067058563232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9834241867065</t>
   </si>
   <si>
     <t xml:space="preserve">13.310640335083</t>
   </si>
   <si>
-    <t xml:space="preserve">13.560697555542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0223379135132</t>
+    <t xml:space="preserve">13.5606966018677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0223398208618</t>
   </si>
   <si>
     <t xml:space="preserve">14.1954526901245</t>
@@ -2150,103 +2150,103 @@
     <t xml:space="preserve">14.2916278839111</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1185131072998</t>
+    <t xml:space="preserve">14.1185121536255</t>
   </si>
   <si>
     <t xml:space="preserve">14.7340335845947</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0992774963379</t>
+    <t xml:space="preserve">14.0992784500122</t>
   </si>
   <si>
     <t xml:space="preserve">15.4072599411011</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8691215515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1766624450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2151336669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4649648666382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0612506866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1381950378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0420169830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5998306274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2153549194336</t>
+    <t xml:space="preserve">16.8691234588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1766605377197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2151317596436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4649658203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0612525939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1381931304932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0420150756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5998344421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.215353012085</t>
   </si>
   <si>
     <t xml:space="preserve">16.7152404785156</t>
   </si>
   <si>
-    <t xml:space="preserve">16.926830291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0614719390869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2540454864502</t>
+    <t xml:space="preserve">16.9268283843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0614738464355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2540435791016</t>
   </si>
   <si>
     <t xml:space="preserve">18.638744354248</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0774517059326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7677764892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4580974578857</t>
+    <t xml:space="preserve">18.0774536132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7677783966064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.458101272583</t>
   </si>
   <si>
     <t xml:space="preserve">17.4387435913086</t>
   </si>
   <si>
-    <t xml:space="preserve">17.206485748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.954870223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4193916320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6129360198975</t>
+    <t xml:space="preserve">17.2064876556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9548721313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4193878173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6129379272461</t>
   </si>
   <si>
     <t xml:space="preserve">17.1677742004395</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6516494750977</t>
+    <t xml:space="preserve">17.651647567749</t>
   </si>
   <si>
     <t xml:space="preserve">17.4968070983887</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7290668487549</t>
+    <t xml:space="preserve">17.7290649414062</t>
   </si>
   <si>
     <t xml:space="preserve">18.2903575897217</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9419708251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0580997467041</t>
+    <t xml:space="preserve">17.9419689178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0580978393555</t>
   </si>
   <si>
     <t xml:space="preserve">18.3871307373047</t>
@@ -2255,19 +2255,19 @@
     <t xml:space="preserve">18.4064865112305</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9032611846924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2322940826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2516460418701</t>
+    <t xml:space="preserve">17.903263092041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2322959899902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2516479492188</t>
   </si>
   <si>
     <t xml:space="preserve">18.580680847168</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4451961517334</t>
+    <t xml:space="preserve">18.445198059082</t>
   </si>
   <si>
     <t xml:space="preserve">18.1161632537842</t>
@@ -2279,13 +2279,13 @@
     <t xml:space="preserve">18.8322925567627</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7742290496826</t>
+    <t xml:space="preserve">18.7742309570312</t>
   </si>
   <si>
     <t xml:space="preserve">18.6774559020996</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9097156524658</t>
+    <t xml:space="preserve">18.9097137451172</t>
   </si>
   <si>
     <t xml:space="preserve">19.0451984405518</t>
@@ -2297,16 +2297,16 @@
     <t xml:space="preserve">19.3548755645752</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9484233856201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1032657623291</t>
+    <t xml:space="preserve">18.9484214782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1032638549805</t>
   </si>
   <si>
     <t xml:space="preserve">18.4645500183105</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6581020355225</t>
+    <t xml:space="preserve">18.6581039428711</t>
   </si>
   <si>
     <t xml:space="preserve">19.500036239624</t>
@@ -2315,16 +2315,16 @@
     <t xml:space="preserve">19.6451988220215</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0806827545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3226203918457</t>
+    <t xml:space="preserve">20.0806846618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3226222991943</t>
   </si>
   <si>
     <t xml:space="preserve">20.6129417419434</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5645561218262</t>
+    <t xml:space="preserve">20.5645542144775</t>
   </si>
   <si>
     <t xml:space="preserve">21.0484275817871</t>
@@ -2336,10 +2336,10 @@
     <t xml:space="preserve">21.7258472442627</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1935901641846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5806846618652</t>
+    <t xml:space="preserve">21.1935882568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5806865692139</t>
   </si>
   <si>
     <t xml:space="preserve">21.8710117340088</t>
@@ -2348,13 +2348,13 @@
     <t xml:space="preserve">21.532299041748</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3387508392334</t>
+    <t xml:space="preserve">21.3387489318848</t>
   </si>
   <si>
     <t xml:space="preserve">21.7742347717285</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4516563415527</t>
+    <t xml:space="preserve">22.4516544342041</t>
   </si>
   <si>
     <t xml:space="preserve">22.9355297088623</t>
@@ -2366,16 +2366,16 @@
     <t xml:space="preserve">23.3226261138916</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4193992614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0968189239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7258529663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4839153289795</t>
+    <t xml:space="preserve">23.4194011688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0968208312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7258548736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4839172363281</t>
   </si>
   <si>
     <t xml:space="preserve">24.048433303833</t>
@@ -2384,16 +2384,16 @@
     <t xml:space="preserve">23.7581100463867</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9516582489014</t>
+    <t xml:space="preserve">23.95166015625</t>
   </si>
   <si>
     <t xml:space="preserve">23.6613368988037</t>
   </si>
   <si>
-    <t xml:space="preserve">22.741979598999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.032299041748</t>
+    <t xml:space="preserve">22.7419815063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0323009490967</t>
   </si>
   <si>
     <t xml:space="preserve">23.4677867889404</t>
@@ -2402,10 +2402,10 @@
     <t xml:space="preserve">23.0806903839111</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8871402740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5484313964844</t>
+    <t xml:space="preserve">22.8871383666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5484275817871</t>
   </si>
   <si>
     <t xml:space="preserve">21.8226203918457</t>
@@ -2417,7 +2417,7 @@
     <t xml:space="preserve">21.2419776916504</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6290740966797</t>
+    <t xml:space="preserve">21.6290760040283</t>
   </si>
   <si>
     <t xml:space="preserve">20.4677791595459</t>
@@ -2426,13 +2426,13 @@
     <t xml:space="preserve">21.3871383666992</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0968132019043</t>
+    <t xml:space="preserve">21.0968151092529</t>
   </si>
   <si>
     <t xml:space="preserve">21.4839134216309</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2097187042236</t>
+    <t xml:space="preserve">22.2097225189209</t>
   </si>
   <si>
     <t xml:space="preserve">21.9677867889404</t>
@@ -2441,13 +2441,13 @@
     <t xml:space="preserve">20.9516525268555</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1129493713379</t>
+    <t xml:space="preserve">22.1129455566406</t>
   </si>
   <si>
     <t xml:space="preserve">22.3548812866211</t>
   </si>
   <si>
-    <t xml:space="preserve">21.919397354126</t>
+    <t xml:space="preserve">21.9193954467773</t>
   </si>
   <si>
     <t xml:space="preserve">22.838752746582</t>
@@ -2456,19 +2456,19 @@
     <t xml:space="preserve">22.645206451416</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4355316162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3387565612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2419815063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7419872283936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1774673461914</t>
+    <t xml:space="preserve">24.4355297088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3387546539307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.241979598999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7419853210449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1774711608887</t>
   </si>
   <si>
     <t xml:space="preserve">27.0000514984131</t>
@@ -2477,67 +2477,67 @@
     <t xml:space="preserve">26.661340713501</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6129550933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3710174560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6774711608887</t>
+    <t xml:space="preserve">26.6129570007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3710193634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6774730682373</t>
   </si>
   <si>
     <t xml:space="preserve">28.6452159881592</t>
   </si>
   <si>
-    <t xml:space="preserve">29.903284072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9355392456055</t>
+    <t xml:space="preserve">29.9032821655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9355411529541</t>
   </si>
   <si>
     <t xml:space="preserve">29.7581233978271</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3871555328369</t>
+    <t xml:space="preserve">30.3871536254883</t>
   </si>
   <si>
     <t xml:space="preserve">30.9194145202637</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7419986724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0323143005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5484447479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0807075500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2581214904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1774826049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3226432800293</t>
+    <t xml:space="preserve">31.7419948577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0323219299316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5484466552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0807113647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2581233978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1774787902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.322639465332</t>
   </si>
   <si>
     <t xml:space="preserve">33.2903861999512</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1936149597168</t>
+    <t xml:space="preserve">33.1936111450195</t>
   </si>
   <si>
     <t xml:space="preserve">32.8065147399902</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4839363098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7258720397949</t>
+    <t xml:space="preserve">33.4839324951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7258682250977</t>
   </si>
   <si>
     <t xml:space="preserve">34.1129684448242</t>
@@ -2549,7 +2549,7 @@
     <t xml:space="preserve">34.5968437194824</t>
   </si>
   <si>
-    <t xml:space="preserve">35.3710327148438</t>
+    <t xml:space="preserve">35.371036529541</t>
   </si>
   <si>
     <t xml:space="preserve">35.4678115844727</t>
@@ -2564,10 +2564,10 @@
     <t xml:space="preserve">36.1936225891113</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3065223693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.564582824707</t>
+    <t xml:space="preserve">34.3065185546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5645790100098</t>
   </si>
   <si>
     <t xml:space="preserve">32.6613540649414</t>
@@ -2588,7 +2588,7 @@
     <t xml:space="preserve">30.822639465332</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5807056427002</t>
+    <t xml:space="preserve">30.5807037353516</t>
   </si>
   <si>
     <t xml:space="preserve">30.4839305877686</t>
@@ -2597,64 +2597,64 @@
     <t xml:space="preserve">31.112964630127</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4355506896973</t>
+    <t xml:space="preserve">33.435546875</t>
   </si>
   <si>
     <t xml:space="preserve">33.8710327148438</t>
   </si>
   <si>
-    <t xml:space="preserve">35.2742576599121</t>
+    <t xml:space="preserve">35.2742614746094</t>
   </si>
   <si>
     <t xml:space="preserve">35.6613578796387</t>
   </si>
   <si>
-    <t xml:space="preserve">35.7097473144531</t>
+    <t xml:space="preserve">35.7097434997559</t>
   </si>
   <si>
     <t xml:space="preserve">37.2581367492676</t>
   </si>
   <si>
-    <t xml:space="preserve">37.0162010192871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.9678153991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9516868591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4355583190918</t>
+    <t xml:space="preserve">37.0161972045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.9678115844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9516830444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4355545043945</t>
   </si>
   <si>
     <t xml:space="preserve">35.0807113647461</t>
   </si>
   <si>
-    <t xml:space="preserve">34.983943939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.677490234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.0645904541016</t>
+    <t xml:space="preserve">34.9839401245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6774940490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.0645866394043</t>
   </si>
   <si>
     <t xml:space="preserve">37.6452331542969</t>
   </si>
   <si>
-    <t xml:space="preserve">38.0323333740234</t>
+    <t xml:space="preserve">38.0323295593262</t>
   </si>
   <si>
     <t xml:space="preserve">38.612979888916</t>
   </si>
   <si>
-    <t xml:space="preserve">38.7581367492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8226585388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6774940490723</t>
+    <t xml:space="preserve">38.7581405639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8226623535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.677490234375</t>
   </si>
   <si>
     <t xml:space="preserve">38.5645904541016</t>
@@ -2663,16 +2663,16 @@
     <t xml:space="preserve">38.7097511291504</t>
   </si>
   <si>
-    <t xml:space="preserve">39.6291122436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4516944885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.1613655090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4355621337891</t>
+    <t xml:space="preserve">39.6291084289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4516906738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.1613693237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4355583190918</t>
   </si>
   <si>
     <t xml:space="preserve">40.2581405639648</t>
@@ -2693,19 +2693,19 @@
     <t xml:space="preserve">41.854923248291</t>
   </si>
   <si>
-    <t xml:space="preserve">42.338794708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.0484657287598</t>
+    <t xml:space="preserve">42.3387908935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.048469543457</t>
   </si>
   <si>
     <t xml:space="preserve">42.6291160583496</t>
   </si>
   <si>
-    <t xml:space="preserve">41.6129837036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.3871803283691</t>
+    <t xml:space="preserve">41.612979888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.3871765136719</t>
   </si>
   <si>
     <t xml:space="preserve">43.5000839233398</t>
@@ -2723,7 +2723,7 @@
     <t xml:space="preserve">45.6775054931641</t>
   </si>
   <si>
-    <t xml:space="preserve">44.4194374084473</t>
+    <t xml:space="preserve">44.4194450378418</t>
   </si>
   <si>
     <t xml:space="preserve">45.0000839233398</t>
@@ -2732,7 +2732,7 @@
     <t xml:space="preserve">46.0162162780762</t>
   </si>
   <si>
-    <t xml:space="preserve">45.483959197998</t>
+    <t xml:space="preserve">45.4839630126953</t>
   </si>
   <si>
     <t xml:space="preserve">44.9516983032227</t>
@@ -2741,28 +2741,28 @@
     <t xml:space="preserve">46.2581520080566</t>
   </si>
   <si>
-    <t xml:space="preserve">45.1452522277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.6129875183105</t>
+    <t xml:space="preserve">45.1452484130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.6129913330078</t>
   </si>
   <si>
     <t xml:space="preserve">44.5162124633789</t>
   </si>
   <si>
-    <t xml:space="preserve">44.2742805480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.838794708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.1613693237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.3065299987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.2581481933594</t>
+    <t xml:space="preserve">44.2742767333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8387908935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.1613731384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.3065376281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.2581520080566</t>
   </si>
   <si>
     <t xml:space="preserve">42.8710517883301</t>
@@ -2783,43 +2783,43 @@
     <t xml:space="preserve">41.8992919921875</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0436096191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.7994422912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4576110839844</t>
+    <t xml:space="preserve">40.0436058044434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.7994384765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4576072692871</t>
   </si>
   <si>
     <t xml:space="preserve">40.0924415588379</t>
   </si>
   <si>
-    <t xml:space="preserve">40.8737831115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9947776794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.7761116027832</t>
+    <t xml:space="preserve">40.873779296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9947814941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.7761154174805</t>
   </si>
   <si>
     <t xml:space="preserve">40.6784477233887</t>
   </si>
   <si>
-    <t xml:space="preserve">40.190113067627</t>
+    <t xml:space="preserve">40.1901168823242</t>
   </si>
   <si>
     <t xml:space="preserve">39.8971061706543</t>
   </si>
   <si>
-    <t xml:space="preserve">39.6529388427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6041069030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.7506103515625</t>
+    <t xml:space="preserve">39.6529426574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6041030883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.7506065368652</t>
   </si>
   <si>
     <t xml:space="preserve">39.2622718811035</t>
@@ -2828,7 +2828,7 @@
     <t xml:space="preserve">40.2877769470215</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9459457397461</t>
+    <t xml:space="preserve">39.9459419250488</t>
   </si>
   <si>
     <t xml:space="preserve">37.8949279785156</t>
@@ -2852,22 +2852,22 @@
     <t xml:space="preserve">42.0946235656738</t>
   </si>
   <si>
-    <t xml:space="preserve">41.459789276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0691108703613</t>
+    <t xml:space="preserve">41.4597854614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0691146850586</t>
   </si>
   <si>
     <t xml:space="preserve">40.385440826416</t>
   </si>
   <si>
-    <t xml:space="preserve">40.4342765808105</t>
+    <t xml:space="preserve">40.4342803955078</t>
   </si>
   <si>
     <t xml:space="preserve">42.1922912597656</t>
   </si>
   <si>
-    <t xml:space="preserve">42.0457878112793</t>
+    <t xml:space="preserve">42.0457916259766</t>
   </si>
   <si>
     <t xml:space="preserve">41.9481201171875</t>
@@ -2876,13 +2876,13 @@
     <t xml:space="preserve">41.4109535217285</t>
   </si>
   <si>
-    <t xml:space="preserve">42.7294654846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3664779663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4153099060059</t>
+    <t xml:space="preserve">42.7294616699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3664817810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4153137207031</t>
   </si>
   <si>
     <t xml:space="preserve">46.1966514587402</t>
@@ -2891,16 +2891,16 @@
     <t xml:space="preserve">47.8569946289062</t>
   </si>
   <si>
-    <t xml:space="preserve">47.3198280334473</t>
+    <t xml:space="preserve">47.31982421875</t>
   </si>
   <si>
     <t xml:space="preserve">47.8081665039062</t>
   </si>
   <si>
-    <t xml:space="preserve">48.5406684875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.5895004272461</t>
+    <t xml:space="preserve">48.5406646728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.5895042419434</t>
   </si>
   <si>
     <t xml:space="preserve">48.8336715698242</t>
@@ -2909,28 +2909,28 @@
     <t xml:space="preserve">48.1988296508789</t>
   </si>
   <si>
-    <t xml:space="preserve">49.7126770019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.9080085754395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.8103446960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0056762695312</t>
+    <t xml:space="preserve">49.7126808166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.9080123901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.8103408813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0056800842285</t>
   </si>
   <si>
     <t xml:space="preserve">50.6893501281738</t>
   </si>
   <si>
-    <t xml:space="preserve">51.3730163574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.2986755371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.5916862487793</t>
+    <t xml:space="preserve">51.3730201721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.2986793518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.591682434082</t>
   </si>
   <si>
     <t xml:space="preserve">50.4940147399902</t>
@@ -2951,22 +2951,22 @@
     <t xml:space="preserve">51.8613548278809</t>
   </si>
   <si>
-    <t xml:space="preserve">51.9590301513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.8846855163574</t>
+    <t xml:space="preserve">51.9590263366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.8846817016602</t>
   </si>
   <si>
     <t xml:space="preserve">45.2688102722168</t>
   </si>
   <si>
-    <t xml:space="preserve">44.5363082885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.5107955932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.2433052062988</t>
+    <t xml:space="preserve">44.536304473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.510799407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2433013916016</t>
   </si>
   <si>
     <t xml:space="preserve">44.2921371459961</t>
@@ -2981,7 +2981,7 @@
     <t xml:space="preserve">43.8038024902344</t>
   </si>
   <si>
-    <t xml:space="preserve">44.4386405944824</t>
+    <t xml:space="preserve">44.4386444091797</t>
   </si>
   <si>
     <t xml:space="preserve">43.9503021240234</t>
@@ -2999,7 +2999,7 @@
     <t xml:space="preserve">41.7527885437012</t>
   </si>
   <si>
-    <t xml:space="preserve">42.2899551391602</t>
+    <t xml:space="preserve">42.2899589538574</t>
   </si>
   <si>
     <t xml:space="preserve">43.0712966918945</t>
@@ -3008,7 +3008,7 @@
     <t xml:space="preserve">43.2666320800781</t>
   </si>
   <si>
-    <t xml:space="preserve">43.7061309814453</t>
+    <t xml:space="preserve">43.7061347961426</t>
   </si>
   <si>
     <t xml:space="preserve">44.3409767150879</t>
@@ -3020,13 +3020,13 @@
     <t xml:space="preserve">46.0989837646484</t>
   </si>
   <si>
-    <t xml:space="preserve">45.659481048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.7571487426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.7782974243164</t>
+    <t xml:space="preserve">45.6594848632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.7571449279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.7782936096191</t>
   </si>
   <si>
     <t xml:space="preserve">41.2644500732422</t>
@@ -3035,13 +3035,13 @@
     <t xml:space="preserve">42.6806259155273</t>
   </si>
   <si>
-    <t xml:space="preserve">43.1201362609863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.3387908935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4364585876465</t>
+    <t xml:space="preserve">43.1201324462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.3387870788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4364624023438</t>
   </si>
   <si>
     <t xml:space="preserve">41.5086212158203</t>
@@ -3059,22 +3059,22 @@
     <t xml:space="preserve">39.0669364929199</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8482780456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5319442749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8504524230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1179504394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.824951171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.6551208496094</t>
+    <t xml:space="preserve">39.848274230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5319480895996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.850456237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1179466247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.8249473571777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.6551246643066</t>
   </si>
   <si>
     <t xml:space="preserve">41.6062850952148</t>
@@ -3083,55 +3083,55 @@
     <t xml:space="preserve">42.485294342041</t>
   </si>
   <si>
-    <t xml:space="preserve">42.9736289978027</t>
+    <t xml:space="preserve">42.9736251831055</t>
   </si>
   <si>
     <t xml:space="preserve">41.8016166687012</t>
   </si>
   <si>
-    <t xml:space="preserve">41.3621215820312</t>
+    <t xml:space="preserve">41.362117767334</t>
   </si>
   <si>
     <t xml:space="preserve">40.238941192627</t>
   </si>
   <si>
-    <t xml:space="preserve">40.6296119689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.8759651184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.4619636535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.999137878418</t>
+    <t xml:space="preserve">40.6296157836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.8759613037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.4619674682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.9991416931152</t>
   </si>
   <si>
     <t xml:space="preserve">40.9226150512695</t>
   </si>
   <si>
-    <t xml:space="preserve">39.1157684326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5829582214355</t>
+    <t xml:space="preserve">39.1157722473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5829620361328</t>
   </si>
   <si>
     <t xml:space="preserve">42.6317939758301</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5785980224609</t>
+    <t xml:space="preserve">38.5786018371582</t>
   </si>
   <si>
     <t xml:space="preserve">36.4299163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">38.6274299621582</t>
+    <t xml:space="preserve">38.6274337768555</t>
   </si>
   <si>
     <t xml:space="preserve">37.1135864257812</t>
   </si>
   <si>
-    <t xml:space="preserve">35.7950820922852</t>
+    <t xml:space="preserve">35.7950782775879</t>
   </si>
   <si>
     <t xml:space="preserve">34.7207374572754</t>
@@ -3140,10 +3140,10 @@
     <t xml:space="preserve">35.5997428894043</t>
   </si>
   <si>
-    <t xml:space="preserve">36.5275917053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6252517700195</t>
+    <t xml:space="preserve">36.527587890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6252555847168</t>
   </si>
   <si>
     <t xml:space="preserve">36.0880813598633</t>
@@ -3155,13 +3155,13 @@
     <t xml:space="preserve">35.4532432556152</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5254020690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3810806274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3555755615234</t>
+    <t xml:space="preserve">34.5253982543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3810844421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3555793762207</t>
   </si>
   <si>
     <t xml:space="preserve">33.9393997192383</t>
@@ -3179,10 +3179,10 @@
     <t xml:space="preserve">33.0115623474121</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3767242431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4510612487793</t>
+    <t xml:space="preserve">32.3767280578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4510650634766</t>
   </si>
   <si>
     <t xml:space="preserve">34.7695732116699</t>
@@ -3215,7 +3215,7 @@
     <t xml:space="preserve">32.6208915710449</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4488849639893</t>
+    <t xml:space="preserve">31.4488830566406</t>
   </si>
   <si>
     <t xml:space="preserve">32.6697235107422</t>
@@ -3236,16 +3236,16 @@
     <t xml:space="preserve">29.6518058776855</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4722118377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2302207946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0739517211914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9372234344482</t>
+    <t xml:space="preserve">30.4722099304199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2302169799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0739555358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.937219619751</t>
   </si>
   <si>
     <t xml:space="preserve">31.3316860198975</t>
@@ -3257,10 +3257,10 @@
     <t xml:space="preserve">31.3902835845947</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6637477874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8862056732178</t>
+    <t xml:space="preserve">31.6637496948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8862075805664</t>
   </si>
   <si>
     <t xml:space="preserve">29.9643383026123</t>
@@ -3275,7 +3275,7 @@
     <t xml:space="preserve">29.2025337219238</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8704662322998</t>
+    <t xml:space="preserve">28.8704681396484</t>
   </si>
   <si>
     <t xml:space="preserve">28.9290676116943</t>
@@ -3296,13 +3296,13 @@
     <t xml:space="preserve">28.3235301971436</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5969982147217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2258605957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5579299926758</t>
+    <t xml:space="preserve">28.596996307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2258625030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5579280853271</t>
   </si>
   <si>
     <t xml:space="preserve">28.1816463470459</t>
@@ -3311,22 +3311,22 @@
     <t xml:space="preserve">26.8943614959717</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5972957611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6765117645264</t>
+    <t xml:space="preserve">26.5972938537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.676513671875</t>
   </si>
   <si>
     <t xml:space="preserve">26.8745555877686</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5280990600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4784679412842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7359237670898</t>
+    <t xml:space="preserve">27.5281009674072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4784698486328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7359256744385</t>
   </si>
   <si>
     <t xml:space="preserve">27.2508392333984</t>
@@ -3335,19 +3335,19 @@
     <t xml:space="preserve">28.0628204345703</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3994941711426</t>
+    <t xml:space="preserve">28.3994960784912</t>
   </si>
   <si>
     <t xml:space="preserve">28.320276260376</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7657527923584</t>
+    <t xml:space="preserve">27.765754699707</t>
   </si>
   <si>
     <t xml:space="preserve">27.9439926147461</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4193000793457</t>
+    <t xml:space="preserve">28.4192981719971</t>
   </si>
   <si>
     <t xml:space="preserve">29.0134296417236</t>
@@ -3368,13 +3368,13 @@
     <t xml:space="preserve">24.9931392669678</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0129451751709</t>
+    <t xml:space="preserve">25.0129432678223</t>
   </si>
   <si>
     <t xml:space="preserve">25.6466846466064</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4584217071533</t>
+    <t xml:space="preserve">24.4584197998047</t>
   </si>
   <si>
     <t xml:space="preserve">25.4288368225098</t>
@@ -3386,7 +3386,7 @@
     <t xml:space="preserve">25.4684429168701</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8148994445801</t>
+    <t xml:space="preserve">24.8148975372314</t>
   </si>
   <si>
     <t xml:space="preserve">25.2902050018311</t>
@@ -3407,7 +3407,7 @@
     <t xml:space="preserve">23.8444843292236</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0523090362549</t>
+    <t xml:space="preserve">23.0523109436035</t>
   </si>
   <si>
     <t xml:space="preserve">23.5474185943604</t>
@@ -3419,19 +3419,19 @@
     <t xml:space="preserve">23.6068325042725</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1909408569336</t>
+    <t xml:space="preserve">23.190938949585</t>
   </si>
   <si>
     <t xml:space="preserve">22.9136772155762</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4185676574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5669822692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8146572113037</t>
+    <t xml:space="preserve">22.4185695648193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5669803619385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8146591186523</t>
   </si>
   <si>
     <t xml:space="preserve">22.9532890319824</t>
@@ -3446,13 +3446,13 @@
     <t xml:space="preserve">24.7356834411621</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5970497131348</t>
+    <t xml:space="preserve">24.5970516204834</t>
   </si>
   <si>
     <t xml:space="preserve">25.1911849975586</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9239444732666</t>
+    <t xml:space="preserve">25.9239463806152</t>
   </si>
   <si>
     <t xml:space="preserve">25.8249244689941</t>
@@ -3464,7 +3464,7 @@
     <t xml:space="preserve">26.1615982055664</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3892250061035</t>
+    <t xml:space="preserve">25.3892269134521</t>
   </si>
   <si>
     <t xml:space="preserve">25.1317691802979</t>
@@ -3473,10 +3473,10 @@
     <t xml:space="preserve">25.5674667358398</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0427703857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1417922973633</t>
+    <t xml:space="preserve">26.0427722930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1417942047119</t>
   </si>
   <si>
     <t xml:space="preserve">25.8843364715576</t>
@@ -3494,7 +3494,7 @@
     <t xml:space="preserve">24.2207679748535</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1217460632324</t>
+    <t xml:space="preserve">24.1217479705811</t>
   </si>
   <si>
     <t xml:space="preserve">23.6860504150391</t>
@@ -3512,7 +3512,7 @@
     <t xml:space="preserve">23.626636505127</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4980297088623</t>
+    <t xml:space="preserve">24.4980278015137</t>
   </si>
   <si>
     <t xml:space="preserve">23.8642902374268</t>
@@ -3521,19 +3521,19 @@
     <t xml:space="preserve">23.9435081481934</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7850704193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8743133544922</t>
+    <t xml:space="preserve">23.7850723266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8743152618408</t>
   </si>
   <si>
     <t xml:space="preserve">24.9535312652588</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2999858856201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7652683258057</t>
+    <t xml:space="preserve">24.2999877929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.765266418457</t>
   </si>
   <si>
     <t xml:space="preserve">22.8344612121582</t>
@@ -3542,7 +3542,7 @@
     <t xml:space="preserve">22.5571994781494</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7156372070312</t>
+    <t xml:space="preserve">22.7156352996826</t>
   </si>
   <si>
     <t xml:space="preserve">22.0422859191895</t>
@@ -3560,10 +3560,10 @@
     <t xml:space="preserve">20.0618476867676</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2696704864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8836059570312</t>
+    <t xml:space="preserve">19.2696685791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8836078643799</t>
   </si>
   <si>
     <t xml:space="preserve">20.2400875091553</t>
@@ -3587,7 +3587,7 @@
     <t xml:space="preserve">20.8540210723877</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3887424468994</t>
+    <t xml:space="preserve">21.3887405395508</t>
   </si>
   <si>
     <t xml:space="preserve">21.6065883636475</t>
@@ -3596,7 +3596,7 @@
     <t xml:space="preserve">22.0026741027832</t>
   </si>
   <si>
-    <t xml:space="preserve">22.200719833374</t>
+    <t xml:space="preserve">22.2007217407227</t>
   </si>
   <si>
     <t xml:space="preserve">21.6660003662109</t>
@@ -3605,16 +3605,16 @@
     <t xml:space="preserve">21.5075664520264</t>
   </si>
   <si>
-    <t xml:space="preserve">22.676025390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3195476531982</t>
+    <t xml:space="preserve">22.6760234832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3195457458496</t>
   </si>
   <si>
     <t xml:space="preserve">22.1809158325195</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4383735656738</t>
+    <t xml:space="preserve">22.4383716583252</t>
   </si>
   <si>
     <t xml:space="preserve">21.7848262786865</t>
@@ -3638,22 +3638,22 @@
     <t xml:space="preserve">25.7457065582275</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0329914093018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6369037628174</t>
+    <t xml:space="preserve">27.0329895019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6369018554688</t>
   </si>
   <si>
     <t xml:space="preserve">26.5576858520508</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9831161499023</t>
+    <t xml:space="preserve">23.9831142425537</t>
   </si>
   <si>
     <t xml:space="preserve">25.0525512695312</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2505970001221</t>
+    <t xml:space="preserve">25.2505950927734</t>
   </si>
   <si>
     <t xml:space="preserve">26.2012062072754</t>
@@ -3662,7 +3662,7 @@
     <t xml:space="preserve">26.4190540313721</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6963157653809</t>
+    <t xml:space="preserve">26.6963176727295</t>
   </si>
   <si>
     <t xml:space="preserve">26.7161197662354</t>
@@ -3680,25 +3680,25 @@
     <t xml:space="preserve">23.8246803283691</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9730930328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7950973510742</t>
+    <t xml:space="preserve">22.9730911254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7950954437256</t>
   </si>
   <si>
     <t xml:space="preserve">25.2704010009766</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1219902038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0625762939453</t>
+    <t xml:space="preserve">26.1219882965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0625743865967</t>
   </si>
   <si>
     <t xml:space="preserve">25.7853164672852</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2606201171875</t>
+    <t xml:space="preserve">26.2606220245361</t>
   </si>
   <si>
     <t xml:space="preserve">27.0725994110107</t>
@@ -3716,7 +3716,7 @@
     <t xml:space="preserve">27.4884929656982</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6965618133545</t>
+    <t xml:space="preserve">28.6965599060059</t>
   </si>
   <si>
     <t xml:space="preserve">28.7757759094238</t>
@@ -3725,10 +3725,10 @@
     <t xml:space="preserve">28.2212543487549</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5777339935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2806663513184</t>
+    <t xml:space="preserve">28.5777359008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.280668258667</t>
   </si>
   <si>
     <t xml:space="preserve">28.8153877258301</t>
@@ -3743,7 +3743,7 @@
     <t xml:space="preserve">28.6569519042969</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9540176391602</t>
+    <t xml:space="preserve">28.9540157318115</t>
   </si>
   <si>
     <t xml:space="preserve">28.8549938201904</t>
@@ -3752,7 +3752,7 @@
     <t xml:space="preserve">28.9738216400146</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7955799102783</t>
+    <t xml:space="preserve">28.795581817627</t>
   </si>
   <si>
     <t xml:space="preserve">30.280912399292</t>
@@ -3767,7 +3767,7 @@
     <t xml:space="preserve">29.7065830230713</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5877552032471</t>
+    <t xml:space="preserve">29.5877571105957</t>
   </si>
   <si>
     <t xml:space="preserve">29.33030128479</t>
@@ -3794,7 +3794,7 @@
     <t xml:space="preserve">28.3004722595215</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4787139892578</t>
+    <t xml:space="preserve">28.4787120819092</t>
   </si>
   <si>
     <t xml:space="preserve">28.0430145263672</t>
@@ -3806,7 +3806,7 @@
     <t xml:space="preserve">27.7063407897949</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0131874084473</t>
+    <t xml:space="preserve">27.0131893157959</t>
   </si>
   <si>
     <t xml:space="preserve">26.7755355834961</t>
@@ -3824,22 +3824,22 @@
     <t xml:space="preserve">22.3789615631104</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2801837921143</t>
+    <t xml:space="preserve">24.2801818847656</t>
   </si>
   <si>
     <t xml:space="preserve">24.5574436187744</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8347015380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0921611785889</t>
+    <t xml:space="preserve">24.8347034454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0921630859375</t>
   </si>
   <si>
     <t xml:space="preserve">25.8447284698486</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3893489837646</t>
+    <t xml:space="preserve">26.389347076416</t>
   </si>
   <si>
     <t xml:space="preserve">27.0825023651123</t>
@@ -3854,7 +3854,7 @@
     <t xml:space="preserve">27.4785900115967</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0727214813232</t>
+    <t xml:space="preserve">28.0727233886719</t>
   </si>
   <si>
     <t xml:space="preserve">27.7756538391113</t>
@@ -3863,10 +3863,10 @@
     <t xml:space="preserve">27.6766357421875</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4290809631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.181526184082</t>
+    <t xml:space="preserve">27.4290790557861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1815242767334</t>
   </si>
   <si>
     <t xml:space="preserve">26.9339694976807</t>
@@ -3875,13 +3875,13 @@
     <t xml:space="preserve">27.3795680999756</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8844604492188</t>
+    <t xml:space="preserve">26.8844585418701</t>
   </si>
   <si>
     <t xml:space="preserve">27.7261447906494</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9834785461426</t>
+    <t xml:space="preserve">26.9834804534912</t>
   </si>
   <si>
     <t xml:space="preserve">27.330057144165</t>
@@ -3896,7 +3896,7 @@
     <t xml:space="preserve">28.4688110351562</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5085411071777</t>
+    <t xml:space="preserve">29.5085391998291</t>
   </si>
   <si>
     <t xml:space="preserve">30.5482711791992</t>
@@ -3911,7 +3911,7 @@
     <t xml:space="preserve">32.0831146240234</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6375141143799</t>
+    <t xml:space="preserve">31.6375122070312</t>
   </si>
   <si>
     <t xml:space="preserve">32.1821327209473</t>
@@ -3920,25 +3920,25 @@
     <t xml:space="preserve">32.9247970581055</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2316436767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9840850830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1919136047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.340446472168</t>
+    <t xml:space="preserve">32.4296913146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2316398620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9840888977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.191915512085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3404445648193</t>
   </si>
   <si>
     <t xml:space="preserve">30.795825958252</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6472930908203</t>
+    <t xml:space="preserve">30.6472949981689</t>
   </si>
   <si>
     <t xml:space="preserve">30.2016944885254</t>
@@ -3950,7 +3950,7 @@
     <t xml:space="preserve">30.2512035369873</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5977821350098</t>
+    <t xml:space="preserve">30.5977802276611</t>
   </si>
   <si>
     <t xml:space="preserve">30.4492492675781</t>
@@ -5169,6 +5169,9 @@
   </si>
   <si>
     <t xml:space="preserve">36.7999992370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2999992370605</t>
   </si>
 </sst>
 </file>
@@ -71209,7 +71212,7 @@
     </row>
     <row r="2528">
       <c r="A2528" s="1" t="n">
-        <v>45999.6911342593</v>
+        <v>45999.3333333333</v>
       </c>
       <c r="B2528" t="n">
         <v>53811</v>
@@ -71230,6 +71233,32 @@
         <v>1718</v>
       </c>
       <c r="H2528" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2529">
+      <c r="A2529" s="1" t="n">
+        <v>46000.6911921296</v>
+      </c>
+      <c r="B2529" t="n">
+        <v>72291</v>
+      </c>
+      <c r="C2529" t="n">
+        <v>37.7000007629395</v>
+      </c>
+      <c r="D2529" t="n">
+        <v>36.4000015258789</v>
+      </c>
+      <c r="E2529" t="n">
+        <v>36.7999992370605</v>
+      </c>
+      <c r="F2529" t="n">
+        <v>37.2999992370605</v>
+      </c>
+      <c r="G2529" t="s">
+        <v>1719</v>
+      </c>
+      <c r="H2529" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MOL.MI.xlsx
+++ b/data/MOL.MI.xlsx
@@ -44,19 +44,19 @@
     <t xml:space="preserve">MOL.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75772666931152</t>
+    <t xml:space="preserve">6.75772762298584</t>
   </si>
   <si>
     <t xml:space="preserve">6.66036558151245</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77100229263306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63823795318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72674798965454</t>
+    <t xml:space="preserve">6.77100324630737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63823843002319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72674703598022</t>
   </si>
   <si>
     <t xml:space="preserve">6.81525754928589</t>
@@ -65,16 +65,16 @@
     <t xml:space="preserve">6.54972839355469</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31960296630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09832763671875</t>
+    <t xml:space="preserve">6.31960344314575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09832811355591</t>
   </si>
   <si>
     <t xml:space="preserve">6.35058116912842</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23994302749634</t>
+    <t xml:space="preserve">6.2399435043335</t>
   </si>
   <si>
     <t xml:space="preserve">6.5585789680481</t>
@@ -86,31 +86,31 @@
     <t xml:space="preserve">5.89475536346436</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52317476272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65593957901001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76215171813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66479110717773</t>
+    <t xml:space="preserve">6.52317523956299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65594005584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76215124130249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66479158401489</t>
   </si>
   <si>
     <t xml:space="preserve">6.69134378433228</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68249368667603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01866865158081</t>
+    <t xml:space="preserve">6.68249320983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01866912841797</t>
   </si>
   <si>
     <t xml:space="preserve">5.89918041229248</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28419971466064</t>
+    <t xml:space="preserve">6.28419876098633</t>
   </si>
   <si>
     <t xml:space="preserve">6.06292390823364</t>
@@ -122,43 +122,43 @@
     <t xml:space="preserve">6.39926099777222</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34173011779785</t>
+    <t xml:space="preserve">6.34173059463501</t>
   </si>
   <si>
     <t xml:space="preserve">6.50989866256714</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33287954330444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42581415176392</t>
+    <t xml:space="preserve">6.33287906646729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42581462860107</t>
   </si>
   <si>
     <t xml:space="preserve">6.39041042327881</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30632591247559</t>
+    <t xml:space="preserve">6.3063268661499</t>
   </si>
   <si>
     <t xml:space="preserve">6.4081130027771</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3550066947937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63381338119507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43466567993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22666692733765</t>
+    <t xml:space="preserve">6.35500717163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63381290435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43466520309448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2266674041748</t>
   </si>
   <si>
     <t xml:space="preserve">6.24436902999878</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27534770965576</t>
+    <t xml:space="preserve">6.27534818649292</t>
   </si>
   <si>
     <t xml:space="preserve">6.2664966583252</t>
@@ -167,43 +167,43 @@
     <t xml:space="preserve">6.62938690185547</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43909120559692</t>
+    <t xml:space="preserve">6.43909168243408</t>
   </si>
   <si>
     <t xml:space="preserve">6.41253757476807</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45236730575562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4567928314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36828231811523</t>
+    <t xml:space="preserve">6.45236778259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45679330825806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36828327178955</t>
   </si>
   <si>
     <t xml:space="preserve">6.19568872451782</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06734943389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28862380981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20454025268555</t>
+    <t xml:space="preserve">6.06734895706177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28862428665161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20453977584839</t>
   </si>
   <si>
     <t xml:space="preserve">6.29304981231689</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24879455566406</t>
+    <t xml:space="preserve">6.2487940788269</t>
   </si>
   <si>
     <t xml:space="preserve">6.22224235534668</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25764608383179</t>
+    <t xml:space="preserve">6.25764656066895</t>
   </si>
   <si>
     <t xml:space="preserve">6.15585899353027</t>
@@ -212,67 +212,67 @@
     <t xml:space="preserve">6.19126272201538</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58955860137939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47892141342163</t>
+    <t xml:space="preserve">6.58955764770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47892045974731</t>
   </si>
   <si>
     <t xml:space="preserve">6.49662160873413</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42138862609863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63348865509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45274066925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54311513900757</t>
+    <t xml:space="preserve">6.42138910293579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63348913192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45274114608765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54311561584473</t>
   </si>
   <si>
     <t xml:space="preserve">6.44370317459106</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50696420669556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55667066574097</t>
+    <t xml:space="preserve">6.50696516036987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55667114257812</t>
   </si>
   <si>
     <t xml:space="preserve">6.36688470840454</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61993312835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69223308563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59733915328979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68319463729858</t>
+    <t xml:space="preserve">6.61993360519409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69223260879517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59733963012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6831955909729</t>
   </si>
   <si>
     <t xml:space="preserve">6.70578956604004</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75097560882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85038805007935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94528102874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98594999313354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1034369468689</t>
+    <t xml:space="preserve">6.75097608566284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85038900375366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94528150558472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98594951629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10343647003174</t>
   </si>
   <si>
     <t xml:space="preserve">7.25255393981934</t>
@@ -287,25 +287,25 @@
     <t xml:space="preserve">7.3022608757019</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37907886505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25707387924194</t>
+    <t xml:space="preserve">7.37907934188843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25707292556763</t>
   </si>
   <si>
     <t xml:space="preserve">7.22996139526367</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22544193267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19833040237427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09439897537231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13958644866943</t>
+    <t xml:space="preserve">7.22544240951538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19832992553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09439945220947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13958597183228</t>
   </si>
   <si>
     <t xml:space="preserve">7.00402498245239</t>
@@ -317,52 +317,52 @@
     <t xml:space="preserve">6.95883750915527</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84135150909424</t>
+    <t xml:space="preserve">6.8413519859314</t>
   </si>
   <si>
     <t xml:space="preserve">7.11699295043945</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16669940948486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31129884719849</t>
+    <t xml:space="preserve">7.16669845581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31129932403564</t>
   </si>
   <si>
     <t xml:space="preserve">7.32485342025757</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9995059967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73290157318115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08988046646118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18477392196655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85942602157593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67867708206177</t>
+    <t xml:space="preserve">6.99950551986694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73290061950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08987998962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18477344512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85942554473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67867612838745</t>
   </si>
   <si>
     <t xml:space="preserve">6.49792766571045</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57022666931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57926464080811</t>
+    <t xml:space="preserve">6.57022714614868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57926511764526</t>
   </si>
   <si>
     <t xml:space="preserve">6.41659069061279</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74645805358887</t>
+    <t xml:space="preserve">6.74645757675171</t>
   </si>
   <si>
     <t xml:space="preserve">6.65156412124634</t>
@@ -374,19 +374,19 @@
     <t xml:space="preserve">6.46177816390991</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4346661567688</t>
+    <t xml:space="preserve">6.43466472625732</t>
   </si>
   <si>
     <t xml:space="preserve">6.75549507141113</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56570816040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77808856964111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71030807495117</t>
+    <t xml:space="preserve">6.56570768356323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77808904647827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71030855178833</t>
   </si>
   <si>
     <t xml:space="preserve">6.48889017105103</t>
@@ -395,58 +395,58 @@
     <t xml:space="preserve">6.53859615325928</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66060209274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68771409988403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76001358032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87750053405762</t>
+    <t xml:space="preserve">6.66060161590576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68771457672119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76001405715942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87750101089478</t>
   </si>
   <si>
     <t xml:space="preserve">6.70127010345459</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78712606430054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79616403579712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81423807144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8187575340271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82327651977539</t>
+    <t xml:space="preserve">6.7871265411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79616355895996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81423854827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81875658035278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82327556610107</t>
   </si>
   <si>
     <t xml:space="preserve">6.80520153045654</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92268753051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90461301803589</t>
+    <t xml:space="preserve">6.92268800735474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90461206436157</t>
   </si>
   <si>
     <t xml:space="preserve">6.86846256256104</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98143100738525</t>
+    <t xml:space="preserve">6.98143196105957</t>
   </si>
   <si>
     <t xml:space="preserve">7.17573642730713</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01306247711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97691202163696</t>
+    <t xml:space="preserve">7.01306295394897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97691297531128</t>
   </si>
   <si>
     <t xml:space="preserve">6.64252710342407</t>
@@ -455,118 +455,118 @@
     <t xml:space="preserve">6.69675159454346</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88653802871704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.931725025177</t>
+    <t xml:space="preserve">6.88653755187988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93172550201416</t>
   </si>
   <si>
     <t xml:space="preserve">7.02209997177124</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99046850204468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19381141662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05824851989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0492115020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06728649139404</t>
+    <t xml:space="preserve">6.99046897888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19381093978882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05824947357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04921197891235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0672869682312</t>
   </si>
   <si>
     <t xml:space="preserve">7.14862442016602</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08536243438721</t>
+    <t xml:space="preserve">7.08536195755005</t>
   </si>
   <si>
     <t xml:space="preserve">7.06276798248291</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15766096115112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21188545227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38359785079956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22092390060425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24803638458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18929290771484</t>
+    <t xml:space="preserve">7.15766143798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21188640594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3835973739624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22092294692993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24803686141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18929243087769</t>
   </si>
   <si>
     <t xml:space="preserve">7.35648584365845</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37004137039185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88201904296875</t>
+    <t xml:space="preserve">7.370041847229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88201951980591</t>
   </si>
   <si>
     <t xml:space="preserve">7.03565549850464</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18025541305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91365003585815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51915884017944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47848987579346</t>
+    <t xml:space="preserve">7.18025493621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91365051269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51915979385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47849035263062</t>
   </si>
   <si>
     <t xml:space="preserve">7.50108480453491</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41070985794067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27514886856079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60953378677368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66375970840454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72702121734619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68183374404907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67731523513794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63664674758911</t>
+    <t xml:space="preserve">7.41070938110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27514839172363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.609534740448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66375780105591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72702169418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68183469772339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67731618881226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63664627075195</t>
   </si>
   <si>
     <t xml:space="preserve">7.77220821380615</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97103071212769</t>
+    <t xml:space="preserve">7.971031665802</t>
   </si>
   <si>
     <t xml:space="preserve">8.34156703948975</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41386890411377</t>
+    <t xml:space="preserve">8.41386699676514</t>
   </si>
   <si>
     <t xml:space="preserve">8.45001792907715</t>
@@ -575,25 +575,25 @@
     <t xml:space="preserve">8.57654094696045</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37771892547607</t>
+    <t xml:space="preserve">8.37771701812744</t>
   </si>
   <si>
     <t xml:space="preserve">8.40934944152832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35964202880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22408103942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24215507507324</t>
+    <t xml:space="preserve">8.35964298248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22408199310303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24215602874756</t>
   </si>
   <si>
     <t xml:space="preserve">8.33705043792725</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32801246643066</t>
+    <t xml:space="preserve">8.32801151275635</t>
   </si>
   <si>
     <t xml:space="preserve">8.32349300384521</t>
@@ -602,13 +602,13 @@
     <t xml:space="preserve">8.36416244506836</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37319850921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46809196472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30541801452637</t>
+    <t xml:space="preserve">8.37319755554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46809101104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30541706085205</t>
   </si>
   <si>
     <t xml:space="preserve">8.30089950561523</t>
@@ -620,16 +620,16 @@
     <t xml:space="preserve">8.26926803588867</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20600414276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07496356964111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11111354827881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28282451629639</t>
+    <t xml:space="preserve">8.20600605010986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07496452331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11111259460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2828254699707</t>
   </si>
   <si>
     <t xml:space="preserve">8.29638195037842</t>
@@ -647,7 +647,7 @@
     <t xml:space="preserve">8.22859954833984</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27378559112549</t>
+    <t xml:space="preserve">8.2737865447998</t>
   </si>
   <si>
     <t xml:space="preserve">8.02977561950684</t>
@@ -656,19 +656,19 @@
     <t xml:space="preserve">8.13370609283447</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27830791473389</t>
+    <t xml:space="preserve">8.27830600738525</t>
   </si>
   <si>
     <t xml:space="preserve">8.4319429397583</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69402694702148</t>
+    <t xml:space="preserve">8.69402885437012</t>
   </si>
   <si>
     <t xml:space="preserve">9.57969856262207</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25434970855713</t>
+    <t xml:space="preserve">9.25434875488281</t>
   </si>
   <si>
     <t xml:space="preserve">9.21820068359375</t>
@@ -683,7 +683,7 @@
     <t xml:space="preserve">9.20012664794922</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20916175842285</t>
+    <t xml:space="preserve">9.20916271209717</t>
   </si>
   <si>
     <t xml:space="preserve">9.22723770141602</t>
@@ -698,25 +698,25 @@
     <t xml:space="preserve">9.12782573699951</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35376358032227</t>
+    <t xml:space="preserve">9.35376167297363</t>
   </si>
   <si>
     <t xml:space="preserve">9.55258655548096</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47124767303467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80563545227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89601135253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2123193740845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94119644165039</t>
+    <t xml:space="preserve">9.47124862670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80563640594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8960075378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2123203277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94119739532471</t>
   </si>
   <si>
     <t xml:space="preserve">10.4472951889038</t>
@@ -725,52 +725,52 @@
     <t xml:space="preserve">10.8449420928955</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8087921142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.908203125</t>
+    <t xml:space="preserve">10.8087930679321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9082040786743</t>
   </si>
   <si>
     <t xml:space="preserve">10.9353170394897</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7364912033081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7093801498413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.754566192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4764318466187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2261095046997</t>
+    <t xml:space="preserve">10.7364921569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7093811035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7545671463013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.476432800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.226110458374</t>
   </si>
   <si>
     <t xml:space="preserve">10.0128726959229</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3837203979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4300765991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2817392349243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4022626876831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5135173797607</t>
+    <t xml:space="preserve">10.3837213516235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4300746917725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2817373275757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4022617340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5135164260864</t>
   </si>
   <si>
     <t xml:space="preserve">10.4949731826782</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5413303375244</t>
+    <t xml:space="preserve">10.5413293838501</t>
   </si>
   <si>
     <t xml:space="preserve">10.7452964782715</t>
@@ -779,43 +779,43 @@
     <t xml:space="preserve">11.0790586471558</t>
   </si>
   <si>
-    <t xml:space="preserve">11.774395942688</t>
+    <t xml:space="preserve">11.7743968963623</t>
   </si>
   <si>
     <t xml:space="preserve">11.5889739990234</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2181282043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3015670776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0976009368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1439571380615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0327033996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8287363052368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7545671463013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7360239028931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.986346244812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8658199310303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5691423416138</t>
+    <t xml:space="preserve">11.2181272506714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3015661239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0976028442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1439561843872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0327014923096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8287372589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7545680999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7360248565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9863481521606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8658218383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5691442489624</t>
   </si>
   <si>
     <t xml:space="preserve">11.1254138946533</t>
@@ -824,34 +824,34 @@
     <t xml:space="preserve">11.0605144500732</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4869918823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0697889328003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9399909973145</t>
+    <t xml:space="preserve">11.4869899749756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.069787979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9399919509888</t>
   </si>
   <si>
     <t xml:space="preserve">11.4499063491821</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4035511016846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7094984054565</t>
+    <t xml:space="preserve">11.4035501480103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7094993591309</t>
   </si>
   <si>
     <t xml:space="preserve">12.0988883972168</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3213968276978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.894923210144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5160903930664</t>
+    <t xml:space="preserve">12.3213958740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8949213027954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5160894393921</t>
   </si>
   <si>
     <t xml:space="preserve">12.5253620147705</t>
@@ -860,13 +860,13 @@
     <t xml:space="preserve">12.6737003326416</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7478694915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5346345901489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7942276000977</t>
+    <t xml:space="preserve">12.7478704452515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5346355438232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.794225692749</t>
   </si>
   <si>
     <t xml:space="preserve">12.7293281555176</t>
@@ -881,13 +881,13 @@
     <t xml:space="preserve">12.5624475479126</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4697351455688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4975490570068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4882783889771</t>
+    <t xml:space="preserve">12.4697360992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4975481033325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4882774353027</t>
   </si>
   <si>
     <t xml:space="preserve">12.68297290802</t>
@@ -896,37 +896,37 @@
     <t xml:space="preserve">12.6273460388184</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5531749725342</t>
+    <t xml:space="preserve">12.5531759262085</t>
   </si>
   <si>
     <t xml:space="preserve">12.1823282241821</t>
   </si>
   <si>
-    <t xml:space="preserve">12.395565032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4233798980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2935829162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3677501678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8856515884399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2843112945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1730575561523</t>
+    <t xml:space="preserve">12.3955659866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.423378944397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2935838699341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3677520751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8856506347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.28431224823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1730585098267</t>
   </si>
   <si>
     <t xml:space="preserve">12.0525321960449</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9505491256714</t>
+    <t xml:space="preserve">11.95055103302</t>
   </si>
   <si>
     <t xml:space="preserve">12.312126159668</t>
@@ -938,34 +938,34 @@
     <t xml:space="preserve">11.9412784576416</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9598207473755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3306674957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4419221878052</t>
+    <t xml:space="preserve">11.9598197937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3306665420532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4419212341309</t>
   </si>
   <si>
     <t xml:space="preserve">12.3492097854614</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3770246505737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1545152664185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2472257614136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.339940071106</t>
+    <t xml:space="preserve">12.3770236968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1545133590698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2472267150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.339937210083</t>
   </si>
   <si>
     <t xml:space="preserve">12.451192855835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2008714675903</t>
+    <t xml:space="preserve">12.200870513916</t>
   </si>
   <si>
     <t xml:space="preserve">12.4326496124268</t>
@@ -980,25 +980,25 @@
     <t xml:space="preserve">12.0618028640747</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0247182846069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4406366348267</t>
+    <t xml:space="preserve">12.0247192382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.440634727478</t>
   </si>
   <si>
     <t xml:space="preserve">11.635329246521</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7929401397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.663143157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6816864013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7465839385986</t>
+    <t xml:space="preserve">11.7929382324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6631441116333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6816854476929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7465829849243</t>
   </si>
   <si>
     <t xml:space="preserve">11.9227352142334</t>
@@ -1016,19 +1016,19 @@
     <t xml:space="preserve">12.2286853790283</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1916007995605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7651243209839</t>
+    <t xml:space="preserve">12.1915998458862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7651252746582</t>
   </si>
   <si>
     <t xml:space="preserve">11.7187700271606</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1903133392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2922973632812</t>
+    <t xml:space="preserve">11.1903123855591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2922964096069</t>
   </si>
   <si>
     <t xml:space="preserve">11.1624984741211</t>
@@ -1037,13 +1037,13 @@
     <t xml:space="preserve">11.5426168441772</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4684467315674</t>
+    <t xml:space="preserve">11.468448638916</t>
   </si>
   <si>
     <t xml:space="preserve">11.5982456207275</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5797004699707</t>
+    <t xml:space="preserve">11.5797033309937</t>
   </si>
   <si>
     <t xml:space="preserve">11.4962606430054</t>
@@ -1055,40 +1055,40 @@
     <t xml:space="preserve">11.857837677002</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1452436447144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.006175994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9134654998779</t>
+    <t xml:space="preserve">12.1452445983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0061769485474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9134645462036</t>
   </si>
   <si>
     <t xml:space="preserve">12.9240217208862</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9253101348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1107339859009</t>
+    <t xml:space="preserve">13.925311088562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1107330322266</t>
   </si>
   <si>
     <t xml:space="preserve">14.092191696167</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9438533782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9994802474976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6299209594727</t>
+    <t xml:space="preserve">13.9438524246216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9994792938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6299200057983</t>
   </si>
   <si>
     <t xml:space="preserve">13.9067687988281</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6286334991455</t>
+    <t xml:space="preserve">13.6286325454712</t>
   </si>
   <si>
     <t xml:space="preserve">14.2034463882446</t>
@@ -1097,16 +1097,16 @@
     <t xml:space="preserve">14.0180225372314</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7028017044067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3888692855835</t>
+    <t xml:space="preserve">13.7027997970581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3888702392578</t>
   </si>
   <si>
     <t xml:space="preserve">14.5186653137207</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5742931365967</t>
+    <t xml:space="preserve">14.574294090271</t>
   </si>
   <si>
     <t xml:space="preserve">14.4815807342529</t>
@@ -1118,19 +1118,19 @@
     <t xml:space="preserve">13.8325986862183</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9981937408447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7756824493408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3690385818481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0352783203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.738597869873</t>
+    <t xml:space="preserve">12.9981918334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7756843566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3690395355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0352773666382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7385997772217</t>
   </si>
   <si>
     <t xml:space="preserve">12.9796504974365</t>
@@ -1139,16 +1139,16 @@
     <t xml:space="preserve">13.5173778533936</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3134136199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6644296646118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1081590652466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0154485702515</t>
+    <t xml:space="preserve">13.3134126663208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6644306182861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1081609725952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0154476165771</t>
   </si>
   <si>
     <t xml:space="preserve">11.8300256729126</t>
@@ -1157,52 +1157,52 @@
     <t xml:space="preserve">12.5902605056763</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7200584411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6088037490845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1637868881226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0339889526367</t>
+    <t xml:space="preserve">12.7200574874878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6088027954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1637859344482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.033989906311</t>
   </si>
   <si>
     <t xml:space="preserve">12.0710744857788</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6075162887573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4604644775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8114824295044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8485670089722</t>
+    <t xml:space="preserve">11.607515335083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4604616165161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8114814758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8485660552979</t>
   </si>
   <si>
     <t xml:space="preserve">12.2379550933838</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3862943649292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3504972457886</t>
+    <t xml:space="preserve">12.3862953186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3504962921143</t>
   </si>
   <si>
     <t xml:space="preserve">13.5359210968018</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7213449478149</t>
+    <t xml:space="preserve">13.7213459014893</t>
   </si>
   <si>
     <t xml:space="preserve">14.2590732574463</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9080562591553</t>
+    <t xml:space="preserve">14.9080572128296</t>
   </si>
   <si>
     <t xml:space="preserve">14.7782592773438</t>
@@ -1211,13 +1211,13 @@
     <t xml:space="preserve">14.7411737442017</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7968006134033</t>
+    <t xml:space="preserve">14.796802520752</t>
   </si>
   <si>
     <t xml:space="preserve">15.0235719680786</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6849880218506</t>
+    <t xml:space="preserve">15.684986114502</t>
   </si>
   <si>
     <t xml:space="preserve">15.4015226364136</t>
@@ -1226,598 +1226,598 @@
     <t xml:space="preserve">15.2314453125</t>
   </si>
   <si>
+    <t xml:space="preserve">15.080265045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1180591583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1747512817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3070363998413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.13538646698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8141269683838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2660980224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6062526702881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6818437576294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0771217346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9448385238647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.114917755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8881464004517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0944480895996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5479898452759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0015316009521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6235799789429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6991691589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7558622360229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8692483901978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3401184082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7369651794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7180681228638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7747611999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2645254135132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7385358810425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7763328552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9653062820435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8708190917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0786914825439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6251516342163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5873565673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4172782897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4550724029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4361753463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.247200012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1338129043579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3227891921997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.473970413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2094049453735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3605852127075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5668869018555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5101938247681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2834224700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6802730560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0393266677856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9826345443726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8125553131104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9637365341187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7952289581299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1164865493774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2676696777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3054647445679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0597953796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7007417678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4928684234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7574348449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5495615005493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1731815338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9290838241577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4960098266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2692394256592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.155855178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5353755950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7054576873779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9133281707764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6298656463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2330169677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9117565155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5904998779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.514910697937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0046739578247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2125482559204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3810548782349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6078252792358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4377470016479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6456203460693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2487707138062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1920785903931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8897171020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5306644439697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8519220352173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0220012664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8723917007446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4755420684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4188508987427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5527048110962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9668798446655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0818347930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0629405975342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2519130706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0440425872803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8739624023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4582166671753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0251407623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3464031219482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.100736618042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.327507019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6471900939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7983703613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9306564331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0613660812378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8550634384155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4771118164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7401084899902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9101858139038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5511312484741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8156986236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9857769012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5338077545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7416791915894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0424690246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4204187393188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7605772018433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6282930374146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8928594589233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.968448638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0062465667725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9873476028442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6093969345093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6834154129028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6267213821411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.853494644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1936502456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0991621017456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2881374359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.195219039917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0078182220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2345867156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2534866333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2912769317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1023063659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0645084381104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0471820831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4046649932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.347972869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.366870880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4991550445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0456123352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3857688903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4424610137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8582096099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8204135894775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5558471679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3290767669678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1400985717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5731716156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5920715332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2897109985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8566360473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1574287414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5805988311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5421276092529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3882484436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4459533691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2343673706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0035438537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9843120574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6767711639404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8114166259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8306522369385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7537136077881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6382999420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4267177581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5228900909424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.945839881897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4651870727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9650754928589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0227813720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8689012527466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7342548370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6573171615601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.426495552063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3687887191772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3110837936401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9840888977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1956758499146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2341461181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1379690170288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0994987487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0033235549927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1187343597412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2533798217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0610303878784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8686800003052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8494443893433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7147989273071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4457292556763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1764392852783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8302097320557</t>
+  </si>
+  <si>
     <t xml:space="preserve">15.0802640914917</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1180591583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1747512817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3070363998413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.13538646698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8141269683838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2660980224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6062545776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6818437576294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0771217346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9448394775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.114917755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8881464004517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0944471359253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5479888916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0015325546265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6235790252686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6991701126099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7558622360229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8692483901978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3401165008545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7369651794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7180681228638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7747621536255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2645244598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7385358810425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7763319015503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9653072357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8708190917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0786924362183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.625150680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5873565673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4172782897949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4550743103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4361763000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.247200012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1338129043579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3227910995483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.473970413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2094049453735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3605842590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5668869018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5101938247681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2834234237671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.680272102356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0393266677856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9826335906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8125562667847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9637365341187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7952299118042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1164865493774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2676706314087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3054647445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0597953796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.700740814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4928693771362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7574338912964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5495624542236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1731805801392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9290838241577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4960107803345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2692403793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.155855178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5353775024414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7054557800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.913330078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6298656463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2330169677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9117565155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5904979705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5149087905884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0046739578247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2125492095947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3810558319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6078252792358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4377470016479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6456212997437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2487707138062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1920795440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8897180557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5306634902954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8519220352173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0220003128052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8723926544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4755420684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4188499450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5527038574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9668788909912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0818367004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0629386901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2519149780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0440406799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8739624023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4582176208496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0251445770264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3464012145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1007347106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3275032043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6471891403198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7983722686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9306583404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0613660812378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8550653457642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4771137237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7401084899902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9101858139038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5511312484741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8156995773315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9857769012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.533805847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7416791915894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0424690246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4204206466675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7605762481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6282958984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8928575515747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9684505462646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0062446594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9873476028442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6093997955322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6834154129028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6267223358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8534936904907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1936492919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0991630554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2881383895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1952209472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0078163146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2345886230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2534847259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.29128074646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1023044586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.064510345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0471839904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4046688079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.347972869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.366870880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4991550445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0456123352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3857688903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4424610137939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8582077026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8204135894775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5558471679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3290767669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.140100479126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5731716156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5920677185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2897090911865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8566379547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1574287414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5805969238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5421295166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3882484436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4459533691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2343673706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0035457611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9843120574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6767711639404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8114147186279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8306522369385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7537117004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6382999420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4267158508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5228939056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9458417892456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4651870727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9650774002075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0227794647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8688993453979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7342567443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6573152542114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.426495552063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3687915802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3110847473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9840888977051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1956748962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2341451644897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1379690170288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0994987487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.003324508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1187343597412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2533807754517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0610294342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8686790466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8494434356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7147989273071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4457292556763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1764392852783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8302087783813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.080265045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9648542404175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1572046279907</t>
+    <t xml:space="preserve">14.9648551940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.157205581665</t>
   </si>
   <si>
     <t xml:space="preserve">14.7917394638062</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7532682418823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9071493148804</t>
+    <t xml:space="preserve">14.7532691955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9071474075317</t>
   </si>
   <si>
     <t xml:space="preserve">15.0225591659546</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8109731674194</t>
+    <t xml:space="preserve">14.8109741210938</t>
   </si>
   <si>
     <t xml:space="preserve">14.8879127502441</t>
@@ -1826,43 +1826,43 @@
     <t xml:space="preserve">14.5416831970215</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5801525115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5993890762329</t>
+    <t xml:space="preserve">14.580153465271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5993881225586</t>
   </si>
   <si>
     <t xml:space="preserve">14.503212928772</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6378602981567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6186237335205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4647445678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4455089569092</t>
+    <t xml:space="preserve">14.6378593444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6186227798462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4647436141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4455099105835</t>
   </si>
   <si>
     <t xml:space="preserve">14.6570930480957</t>
   </si>
   <si>
-    <t xml:space="preserve">14.926383972168</t>
+    <t xml:space="preserve">14.9263849258423</t>
   </si>
   <si>
     <t xml:space="preserve">14.5609188079834</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3495540618896</t>
+    <t xml:space="preserve">15.3495559692383</t>
   </si>
   <si>
     <t xml:space="preserve">15.3880252838135</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6765508651733</t>
+    <t xml:space="preserve">15.6765489578247</t>
   </si>
   <si>
     <t xml:space="preserve">15.5226707458496</t>
@@ -1871,34 +1871,34 @@
     <t xml:space="preserve">15.7150192260742</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7919597625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1574249267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7727251052856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8111963272095</t>
+    <t xml:space="preserve">15.7919616699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1574268341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.77272605896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8111972808838</t>
   </si>
   <si>
     <t xml:space="preserve">15.9073724746704</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6380786895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6188449859619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8496646881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.580376625061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5034341812134</t>
+    <t xml:space="preserve">15.6380805969238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6188459396362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8496656417847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5803775787354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5034351348877</t>
   </si>
   <si>
     <t xml:space="preserve">15.8304309844971</t>
@@ -1913,37 +1913,37 @@
     <t xml:space="preserve">17.1576499938965</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0037689208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9460639953613</t>
+    <t xml:space="preserve">17.0037670135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.94606590271</t>
   </si>
   <si>
     <t xml:space="preserve">16.8883571624756</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9845314025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1191749572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2730560302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2732791900635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1771030426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6000537872314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6577587127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1001644134521</t>
+    <t xml:space="preserve">16.9845333099365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.119176864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2730579376221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2732810974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1771049499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6000518798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6577606201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1001625061035</t>
   </si>
   <si>
     <t xml:space="preserve">17.9847545623779</t>
@@ -1952,10 +1952,10 @@
     <t xml:space="preserve">18.1194000244141</t>
   </si>
   <si>
-    <t xml:space="preserve">17.965518951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9462833404541</t>
+    <t xml:space="preserve">17.9655208587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9462871551514</t>
   </si>
   <si>
     <t xml:space="preserve">18.061695098877</t>
@@ -1970,85 +1970,85 @@
     <t xml:space="preserve">18.7541542053223</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1003856658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0234489440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5425720214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9657402038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9080333709717</t>
+    <t xml:space="preserve">19.1003875732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0234470367432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5425701141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9657382965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9080352783203</t>
   </si>
   <si>
     <t xml:space="preserve">19.4273834228516</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8120803833008</t>
+    <t xml:space="preserve">19.8120822906494</t>
   </si>
   <si>
     <t xml:space="preserve">19.5235538482666</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6678199768066</t>
+    <t xml:space="preserve">19.6678218841553</t>
   </si>
   <si>
     <t xml:space="preserve">19.2831172943115</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8503303527832</t>
+    <t xml:space="preserve">18.8503322601318</t>
   </si>
   <si>
     <t xml:space="preserve">19.6197319030762</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7159099578857</t>
+    <t xml:space="preserve">19.7159061431885</t>
   </si>
   <si>
     <t xml:space="preserve">19.7639942169189</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3312072753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5716457366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1967811584473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2448692321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2164611816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1585350036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1104469299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8219223022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6295719146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0142726898193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7257442474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6776580810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9563426971436</t>
+    <t xml:space="preserve">19.331205368042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5716438293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1967830657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2448711395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2164630889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1585369110107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.110445022583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8219184875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6295738220215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0142707824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7257461547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6776599884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9563465118408</t>
   </si>
   <si>
     <t xml:space="preserve">20.2929573059082</t>
@@ -2066,73 +2066,73 @@
     <t xml:space="preserve">20.7738342285156</t>
   </si>
   <si>
-    <t xml:space="preserve">20.918098449707</t>
+    <t xml:space="preserve">20.9180965423584</t>
   </si>
   <si>
     <t xml:space="preserve">20.5814819335938</t>
   </si>
   <si>
-    <t xml:space="preserve">21.254711151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3989753723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2066173553467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6394081115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.447057723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8317623138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0525207519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.100606918335</t>
+    <t xml:space="preserve">21.2547092437744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3989734649658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2066211700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6394100189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4470596313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8317604064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0525188446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1006050109863</t>
   </si>
   <si>
     <t xml:space="preserve">18.734920501709</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1963405609131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6192893981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3113059997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.195894241333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4839792251587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4262723922729</t>
+    <t xml:space="preserve">18.1963386535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6192874908447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3113040924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1958961486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4839782714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4262733459473</t>
   </si>
   <si>
     <t xml:space="preserve">12.4643001556396</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0218944549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1373043060303</t>
+    <t xml:space="preserve">12.0218954086304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.137303352356</t>
   </si>
   <si>
     <t xml:space="preserve">12.6951198577881</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9067058563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9834251403809</t>
+    <t xml:space="preserve">12.9067068099976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9834241867065</t>
   </si>
   <si>
     <t xml:space="preserve">13.3106412887573</t>
@@ -2141,19 +2141,19 @@
     <t xml:space="preserve">13.560697555542</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0223369598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1954517364502</t>
+    <t xml:space="preserve">14.0223388671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1954526901245</t>
   </si>
   <si>
     <t xml:space="preserve">14.2916278839111</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1185131072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7340326309204</t>
+    <t xml:space="preserve">14.1185121536255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7340335845947</t>
   </si>
   <si>
     <t xml:space="preserve">14.0992774963379</t>
@@ -2165,7 +2165,7 @@
     <t xml:space="preserve">16.8691253662109</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1766605377197</t>
+    <t xml:space="preserve">16.1766624450684</t>
   </si>
   <si>
     <t xml:space="preserve">16.2151336669922</t>
@@ -2174,10 +2174,10 @@
     <t xml:space="preserve">15.4649648666382</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0612506866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1381912231445</t>
+    <t xml:space="preserve">16.0612525939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1381931304932</t>
   </si>
   <si>
     <t xml:space="preserve">16.0420150756836</t>
@@ -2186,7 +2186,7 @@
     <t xml:space="preserve">16.59983253479</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2153549194336</t>
+    <t xml:space="preserve">17.215353012085</t>
   </si>
   <si>
     <t xml:space="preserve">16.7152404785156</t>
@@ -2195,13 +2195,13 @@
     <t xml:space="preserve">16.9268283843994</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0614719390869</t>
+    <t xml:space="preserve">17.0614700317383</t>
   </si>
   <si>
     <t xml:space="preserve">18.2540454864502</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6387424468994</t>
+    <t xml:space="preserve">18.638744354248</t>
   </si>
   <si>
     <t xml:space="preserve">18.0774555206299</t>
@@ -2210,16 +2210,16 @@
     <t xml:space="preserve">17.7677764892578</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4580993652344</t>
+    <t xml:space="preserve">17.4580974578857</t>
   </si>
   <si>
     <t xml:space="preserve">17.4387435913086</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2064838409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9548721313477</t>
+    <t xml:space="preserve">17.206485748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.954870223999</t>
   </si>
   <si>
     <t xml:space="preserve">17.4193878173828</t>
@@ -2228,16 +2228,16 @@
     <t xml:space="preserve">17.6129379272461</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1677761077881</t>
+    <t xml:space="preserve">17.1677742004395</t>
   </si>
   <si>
     <t xml:space="preserve">17.651647567749</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4968090057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7290668487549</t>
+    <t xml:space="preserve">17.4968070983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7290687561035</t>
   </si>
   <si>
     <t xml:space="preserve">18.2903575897217</t>
@@ -2246,28 +2246,28 @@
     <t xml:space="preserve">17.9419727325439</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0580997467041</t>
+    <t xml:space="preserve">18.0580978393555</t>
   </si>
   <si>
     <t xml:space="preserve">18.3871326446533</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4064865112305</t>
+    <t xml:space="preserve">18.4064846038818</t>
   </si>
   <si>
     <t xml:space="preserve">17.9032592773438</t>
   </si>
   <si>
-    <t xml:space="preserve">18.232292175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2516460418701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5806827545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.445198059082</t>
+    <t xml:space="preserve">18.2322940826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2516479492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5806846618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4451961517334</t>
   </si>
   <si>
     <t xml:space="preserve">18.1161632537842</t>
@@ -2276,13 +2276,13 @@
     <t xml:space="preserve">18.0387439727783</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8322925567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7742290496826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.677453994751</t>
+    <t xml:space="preserve">18.8322906494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.774227142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6774559020996</t>
   </si>
   <si>
     <t xml:space="preserve">18.9097137451172</t>
@@ -2291,43 +2291,43 @@
     <t xml:space="preserve">19.0451965332031</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5968112945557</t>
+    <t xml:space="preserve">19.5968132019043</t>
   </si>
   <si>
     <t xml:space="preserve">19.3548755645752</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9484233856201</t>
+    <t xml:space="preserve">18.9484252929688</t>
   </si>
   <si>
     <t xml:space="preserve">19.1032638549805</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4645519256592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6581001281738</t>
+    <t xml:space="preserve">18.4645500183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6581020355225</t>
   </si>
   <si>
     <t xml:space="preserve">19.5000381469727</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6451988220215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.080680847168</t>
+    <t xml:space="preserve">19.6452007293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0806827545166</t>
   </si>
   <si>
     <t xml:space="preserve">20.3226203918457</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6129417419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5645542144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0484275817871</t>
+    <t xml:space="preserve">20.612943649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5645561218262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0484294891357</t>
   </si>
   <si>
     <t xml:space="preserve">21.2903633117676</t>
@@ -2351,19 +2351,19 @@
     <t xml:space="preserve">21.3387508392334</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7742347717285</t>
+    <t xml:space="preserve">21.7742328643799</t>
   </si>
   <si>
     <t xml:space="preserve">22.4516582489014</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9355316162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7903633117676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.322624206543</t>
+    <t xml:space="preserve">22.9355297088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7903652191162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3226261138916</t>
   </si>
   <si>
     <t xml:space="preserve">23.4194011688232</t>
@@ -2378,7 +2378,7 @@
     <t xml:space="preserve">24.4839172363281</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0484352111816</t>
+    <t xml:space="preserve">24.048433303833</t>
   </si>
   <si>
     <t xml:space="preserve">23.7581100463867</t>
@@ -2387,7 +2387,7 @@
     <t xml:space="preserve">23.9516582489014</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6613368988037</t>
+    <t xml:space="preserve">23.6613349914551</t>
   </si>
   <si>
     <t xml:space="preserve">22.7419776916504</t>
@@ -2396,16 +2396,16 @@
     <t xml:space="preserve">23.0323009490967</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4677848815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0806922912598</t>
+    <t xml:space="preserve">23.4677886962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0806903839111</t>
   </si>
   <si>
     <t xml:space="preserve">22.8871402740479</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5484313964844</t>
+    <t xml:space="preserve">22.5484294891357</t>
   </si>
   <si>
     <t xml:space="preserve">21.8226222991943</t>
@@ -2414,25 +2414,25 @@
     <t xml:space="preserve">22.0645580291748</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2419776916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6290740966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4677791595459</t>
+    <t xml:space="preserve">21.2419757843018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6290721893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4677810668945</t>
   </si>
   <si>
     <t xml:space="preserve">21.3871383666992</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0968132019043</t>
+    <t xml:space="preserve">21.0968151092529</t>
   </si>
   <si>
     <t xml:space="preserve">21.4839134216309</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2097206115723</t>
+    <t xml:space="preserve">22.2097187042236</t>
   </si>
   <si>
     <t xml:space="preserve">21.9677848815918</t>
@@ -2447,7 +2447,7 @@
     <t xml:space="preserve">22.3548812866211</t>
   </si>
   <si>
-    <t xml:space="preserve">21.919397354126</t>
+    <t xml:space="preserve">21.9193954467773</t>
   </si>
   <si>
     <t xml:space="preserve">22.838752746582</t>
@@ -2471,13 +2471,13 @@
     <t xml:space="preserve">26.1774673461914</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0000534057617</t>
+    <t xml:space="preserve">27.0000514984131</t>
   </si>
   <si>
     <t xml:space="preserve">26.661340713501</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6129570007324</t>
+    <t xml:space="preserve">26.6129550933838</t>
   </si>
   <si>
     <t xml:space="preserve">26.3710193634033</t>
@@ -2486,7 +2486,7 @@
     <t xml:space="preserve">27.6774749755859</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6452178955078</t>
+    <t xml:space="preserve">28.6452159881592</t>
   </si>
   <si>
     <t xml:space="preserve">29.9032821655273</t>
@@ -2495,13 +2495,13 @@
     <t xml:space="preserve">28.9355392456055</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7581214904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3871555328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9194164276123</t>
+    <t xml:space="preserve">29.7581195831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3871536254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9194145202637</t>
   </si>
   <si>
     <t xml:space="preserve">31.7419948577881</t>
@@ -2513,13 +2513,13 @@
     <t xml:space="preserve">31.5484485626221</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0807113647461</t>
+    <t xml:space="preserve">32.0807075500488</t>
   </si>
   <si>
     <t xml:space="preserve">31.2581253051758</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1774787902832</t>
+    <t xml:space="preserve">32.1774826049805</t>
   </si>
   <si>
     <t xml:space="preserve">32.3226432800293</t>
@@ -2531,46 +2531,46 @@
     <t xml:space="preserve">33.1936111450195</t>
   </si>
   <si>
-    <t xml:space="preserve">32.806510925293</t>
+    <t xml:space="preserve">32.8065147399902</t>
   </si>
   <si>
     <t xml:space="preserve">33.4839324951172</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7258720397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1129684448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.742000579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5968437194824</t>
+    <t xml:space="preserve">33.7258682250977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1129722595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7420043945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5968399047852</t>
   </si>
   <si>
     <t xml:space="preserve">35.371036529541</t>
   </si>
   <si>
-    <t xml:space="preserve">35.4678115844727</t>
+    <t xml:space="preserve">35.4678077697754</t>
   </si>
   <si>
     <t xml:space="preserve">36.8226509094238</t>
   </si>
   <si>
-    <t xml:space="preserve">37.1613655090332</t>
+    <t xml:space="preserve">37.1613693237305</t>
   </si>
   <si>
     <t xml:space="preserve">36.1936225891113</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3065185546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.564582824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6613578796387</t>
+    <t xml:space="preserve">34.3065147399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5645790100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6613540649414</t>
   </si>
   <si>
     <t xml:space="preserve">32.7581253051758</t>
@@ -2588,25 +2588,25 @@
     <t xml:space="preserve">30.822639465332</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5807056427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4839286804199</t>
+    <t xml:space="preserve">30.5807075500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4839305877686</t>
   </si>
   <si>
     <t xml:space="preserve">31.112964630127</t>
   </si>
   <si>
-    <t xml:space="preserve">33.435546875</t>
+    <t xml:space="preserve">33.4355430603027</t>
   </si>
   <si>
     <t xml:space="preserve">33.8710327148438</t>
   </si>
   <si>
-    <t xml:space="preserve">35.2742614746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6613578796387</t>
+    <t xml:space="preserve">35.2742576599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6613616943359</t>
   </si>
   <si>
     <t xml:space="preserve">35.7097473144531</t>
@@ -2618,7 +2618,7 @@
     <t xml:space="preserve">37.0162010192871</t>
   </si>
   <si>
-    <t xml:space="preserve">36.9678153991699</t>
+    <t xml:space="preserve">36.9678115844727</t>
   </si>
   <si>
     <t xml:space="preserve">35.9516868591309</t>
@@ -2627,13 +2627,13 @@
     <t xml:space="preserve">36.4355545043945</t>
   </si>
   <si>
-    <t xml:space="preserve">35.0807113647461</t>
+    <t xml:space="preserve">35.0807151794434</t>
   </si>
   <si>
     <t xml:space="preserve">34.9839401245117</t>
   </si>
   <si>
-    <t xml:space="preserve">36.677490234375</t>
+    <t xml:space="preserve">36.6774864196777</t>
   </si>
   <si>
     <t xml:space="preserve">37.0645866394043</t>
@@ -2651,31 +2651,31 @@
     <t xml:space="preserve">38.7581367492676</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8226547241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6774978637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5645866394043</t>
+    <t xml:space="preserve">39.8226585388184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6774940490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.5645904541016</t>
   </si>
   <si>
     <t xml:space="preserve">38.7097511291504</t>
   </si>
   <si>
-    <t xml:space="preserve">39.6291084289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4516944885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.1613616943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4355659484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2581405639648</t>
+    <t xml:space="preserve">39.6291122436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4516868591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.1613655090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4355621337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2581443786621</t>
   </si>
   <si>
     <t xml:space="preserve">44.0807304382324</t>
@@ -2684,13 +2684,13 @@
     <t xml:space="preserve">41.9033088684082</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0645942687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1774940490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8549194335938</t>
+    <t xml:space="preserve">40.0645980834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1774978637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8549156188965</t>
   </si>
   <si>
     <t xml:space="preserve">42.3387908935547</t>
@@ -2717,25 +2717,25 @@
     <t xml:space="preserve">44.7097625732422</t>
   </si>
   <si>
-    <t xml:space="preserve">44.7581520080566</t>
+    <t xml:space="preserve">44.7581481933594</t>
   </si>
   <si>
     <t xml:space="preserve">45.6775054931641</t>
   </si>
   <si>
-    <t xml:space="preserve">44.4194412231445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.0000839233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.0162162780762</t>
+    <t xml:space="preserve">44.4194374084473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.0000877380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.0162200927734</t>
   </si>
   <si>
     <t xml:space="preserve">45.4839553833008</t>
   </si>
   <si>
-    <t xml:space="preserve">44.9516983032227</t>
+    <t xml:space="preserve">44.9517021179199</t>
   </si>
   <si>
     <t xml:space="preserve">46.2581520080566</t>
@@ -2747,13 +2747,13 @@
     <t xml:space="preserve">44.6129875183105</t>
   </si>
   <si>
-    <t xml:space="preserve">44.5162162780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.2742805480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.838794708252</t>
+    <t xml:space="preserve">44.5162124633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2742767333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8387908935547</t>
   </si>
   <si>
     <t xml:space="preserve">43.1613731384277</t>
@@ -2762,16 +2762,16 @@
     <t xml:space="preserve">43.3065338134766</t>
   </si>
   <si>
-    <t xml:space="preserve">43.2581481933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.8710479736328</t>
+    <t xml:space="preserve">43.2581443786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.8710517883301</t>
   </si>
   <si>
     <t xml:space="preserve">43.0646018981934</t>
   </si>
   <si>
-    <t xml:space="preserve">44.0323448181152</t>
+    <t xml:space="preserve">44.0323486328125</t>
   </si>
   <si>
     <t xml:space="preserve">43.4033050537109</t>
@@ -2780,13 +2780,13 @@
     <t xml:space="preserve">42.4355621337891</t>
   </si>
   <si>
-    <t xml:space="preserve">41.8992881774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.0436134338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.799446105957</t>
+    <t xml:space="preserve">41.8992919921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.0436096191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.7994422912598</t>
   </si>
   <si>
     <t xml:space="preserve">39.4576072692871</t>
@@ -2798,7 +2798,7 @@
     <t xml:space="preserve">40.873779296875</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9947738647461</t>
+    <t xml:space="preserve">39.9947776794434</t>
   </si>
   <si>
     <t xml:space="preserve">40.7761154174805</t>
@@ -2807,22 +2807,22 @@
     <t xml:space="preserve">40.6784477233887</t>
   </si>
   <si>
-    <t xml:space="preserve">40.1901092529297</t>
+    <t xml:space="preserve">40.190113067627</t>
   </si>
   <si>
     <t xml:space="preserve">39.8971061706543</t>
   </si>
   <si>
-    <t xml:space="preserve">39.6529388427734</t>
+    <t xml:space="preserve">39.6529426574707</t>
   </si>
   <si>
     <t xml:space="preserve">39.6041030883789</t>
   </si>
   <si>
-    <t xml:space="preserve">39.7506103515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2622680664062</t>
+    <t xml:space="preserve">39.7506065368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2622718811035</t>
   </si>
   <si>
     <t xml:space="preserve">40.2877769470215</t>
@@ -2831,7 +2831,7 @@
     <t xml:space="preserve">39.9459419250488</t>
   </si>
   <si>
-    <t xml:space="preserve">37.8949279785156</t>
+    <t xml:space="preserve">37.8949241638184</t>
   </si>
   <si>
     <t xml:space="preserve">36.7229156494141</t>
@@ -2843,25 +2843,25 @@
     <t xml:space="preserve">38.0902633666992</t>
   </si>
   <si>
-    <t xml:space="preserve">39.5552711486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.7039566040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.0946235656738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.459789276123</t>
+    <t xml:space="preserve">39.5552749633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.7039527893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.0946197509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4597854614258</t>
   </si>
   <si>
     <t xml:space="preserve">41.0691184997559</t>
   </si>
   <si>
-    <t xml:space="preserve">40.3854446411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4342803955078</t>
+    <t xml:space="preserve">40.385440826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4342842102051</t>
   </si>
   <si>
     <t xml:space="preserve">42.1922950744629</t>
@@ -2870,19 +2870,19 @@
     <t xml:space="preserve">42.0457916259766</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9481239318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.4109573364258</t>
+    <t xml:space="preserve">41.9481201171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4109535217285</t>
   </si>
   <si>
     <t xml:space="preserve">42.7294616699219</t>
   </si>
   <si>
-    <t xml:space="preserve">45.3664779663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4153099060059</t>
+    <t xml:space="preserve">45.3664817810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4153137207031</t>
   </si>
   <si>
     <t xml:space="preserve">46.1966514587402</t>
@@ -2897,16 +2897,16 @@
     <t xml:space="preserve">47.808162689209</t>
   </si>
   <si>
-    <t xml:space="preserve">48.5406723022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.5895004272461</t>
+    <t xml:space="preserve">48.5406684875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.5895042419434</t>
   </si>
   <si>
     <t xml:space="preserve">48.8336715698242</t>
   </si>
   <si>
-    <t xml:space="preserve">48.1988334655762</t>
+    <t xml:space="preserve">48.1988296508789</t>
   </si>
   <si>
     <t xml:space="preserve">49.7126770019531</t>
@@ -2915,13 +2915,13 @@
     <t xml:space="preserve">49.9080085754395</t>
   </si>
   <si>
-    <t xml:space="preserve">49.8103446960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0056762695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.6893539428711</t>
+    <t xml:space="preserve">49.8103408813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0056800842285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.6893501281738</t>
   </si>
   <si>
     <t xml:space="preserve">51.3730201721191</t>
@@ -2930,22 +2930,22 @@
     <t xml:space="preserve">50.2986793518066</t>
   </si>
   <si>
-    <t xml:space="preserve">50.5916786193848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4940185546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.2753524780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.2010116577148</t>
+    <t xml:space="preserve">50.591682434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4940147399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.2753486633301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.2010154724121</t>
   </si>
   <si>
     <t xml:space="preserve">50.7870178222656</t>
   </si>
   <si>
-    <t xml:space="preserve">50.9823532104492</t>
+    <t xml:space="preserve">50.982349395752</t>
   </si>
   <si>
     <t xml:space="preserve">51.8613548278809</t>
@@ -2954,25 +2954,25 @@
     <t xml:space="preserve">51.9590263366699</t>
   </si>
   <si>
-    <t xml:space="preserve">50.8846778869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2688140869141</t>
+    <t xml:space="preserve">50.8846817016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.2688102722168</t>
   </si>
   <si>
     <t xml:space="preserve">44.536304473877</t>
   </si>
   <si>
-    <t xml:space="preserve">43.5107955932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.2433052062988</t>
+    <t xml:space="preserve">43.510799407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2433013916016</t>
   </si>
   <si>
     <t xml:space="preserve">44.2921371459961</t>
   </si>
   <si>
-    <t xml:space="preserve">44.9269790649414</t>
+    <t xml:space="preserve">44.9269752502441</t>
   </si>
   <si>
     <t xml:space="preserve">44.0479698181152</t>
@@ -2981,22 +2981,22 @@
     <t xml:space="preserve">43.8037986755371</t>
   </si>
   <si>
-    <t xml:space="preserve">44.4386405944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.9503021240234</t>
+    <t xml:space="preserve">44.4386444091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.9502983093262</t>
   </si>
   <si>
     <t xml:space="preserve">44.1944694519043</t>
   </si>
   <si>
-    <t xml:space="preserve">41.2156181335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.9714469909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.7527923583984</t>
+    <t xml:space="preserve">41.2156219482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.9714508056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.7527885437012</t>
   </si>
   <si>
     <t xml:space="preserve">42.2899589538574</t>
@@ -3005,7 +3005,7 @@
     <t xml:space="preserve">43.0712966918945</t>
   </si>
   <si>
-    <t xml:space="preserve">43.2666282653809</t>
+    <t xml:space="preserve">43.2666320800781</t>
   </si>
   <si>
     <t xml:space="preserve">43.7061347961426</t>
@@ -3020,7 +3020,7 @@
     <t xml:space="preserve">46.0989837646484</t>
   </si>
   <si>
-    <t xml:space="preserve">45.659481048584</t>
+    <t xml:space="preserve">45.6594848632812</t>
   </si>
   <si>
     <t xml:space="preserve">45.7571449279785</t>
@@ -3035,19 +3035,19 @@
     <t xml:space="preserve">42.6806259155273</t>
   </si>
   <si>
-    <t xml:space="preserve">43.1201324462891</t>
+    <t xml:space="preserve">43.1201286315918</t>
   </si>
   <si>
     <t xml:space="preserve">42.4364624023438</t>
   </si>
   <si>
-    <t xml:space="preserve">41.508617401123</t>
+    <t xml:space="preserve">41.5086212158203</t>
   </si>
   <si>
     <t xml:space="preserve">41.0202827453613</t>
   </si>
   <si>
-    <t xml:space="preserve">38.8716011047363</t>
+    <t xml:space="preserve">38.8715972900391</t>
   </si>
   <si>
     <t xml:space="preserve">38.2367668151855</t>
@@ -3059,25 +3059,25 @@
     <t xml:space="preserve">39.848274230957</t>
   </si>
   <si>
-    <t xml:space="preserve">40.5319404602051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8504524230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1179504394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.824951171875</t>
+    <t xml:space="preserve">40.5319442749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.850456237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1179466247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.8249435424805</t>
   </si>
   <si>
     <t xml:space="preserve">41.6551208496094</t>
   </si>
   <si>
-    <t xml:space="preserve">41.6062850952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.485294342041</t>
+    <t xml:space="preserve">41.6062889099121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4852981567383</t>
   </si>
   <si>
     <t xml:space="preserve">42.9736289978027</t>
@@ -3092,10 +3092,10 @@
     <t xml:space="preserve">40.238941192627</t>
   </si>
   <si>
-    <t xml:space="preserve">40.6296119689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.8759651184082</t>
+    <t xml:space="preserve">40.6296157836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.8759613037109</t>
   </si>
   <si>
     <t xml:space="preserve">43.4619674682617</t>
@@ -3110,31 +3110,31 @@
     <t xml:space="preserve">39.1157684326172</t>
   </si>
   <si>
-    <t xml:space="preserve">42.5829582214355</t>
+    <t xml:space="preserve">42.5829620361328</t>
   </si>
   <si>
     <t xml:space="preserve">42.6317977905273</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5785942077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4299125671387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6274299621582</t>
+    <t xml:space="preserve">38.5786018371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4299163818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6274337768555</t>
   </si>
   <si>
     <t xml:space="preserve">37.1135902404785</t>
   </si>
   <si>
-    <t xml:space="preserve">35.7950820922852</t>
+    <t xml:space="preserve">35.7950782775879</t>
   </si>
   <si>
     <t xml:space="preserve">34.7207336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5997467041016</t>
+    <t xml:space="preserve">35.5997428894043</t>
   </si>
   <si>
     <t xml:space="preserve">36.527587890625</t>
@@ -3158,7 +3158,7 @@
     <t xml:space="preserve">36.3810844421387</t>
   </si>
   <si>
-    <t xml:space="preserve">35.3555755615234</t>
+    <t xml:space="preserve">35.3555793762207</t>
   </si>
   <si>
     <t xml:space="preserve">33.9393997192383</t>
@@ -3167,22 +3167,22 @@
     <t xml:space="preserve">32.1325569152832</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4977169036865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6442203521729</t>
+    <t xml:space="preserve">31.4977149963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6442222595215</t>
   </si>
   <si>
     <t xml:space="preserve">33.0115623474121</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3767280578613</t>
+    <t xml:space="preserve">32.3767242431641</t>
   </si>
   <si>
     <t xml:space="preserve">33.4510612487793</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7695693969727</t>
+    <t xml:space="preserve">34.7695732116699</t>
   </si>
   <si>
     <t xml:space="preserve">34.5742454528809</t>
@@ -3200,7 +3200,7 @@
     <t xml:space="preserve">33.5975646972656</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9627304077148</t>
+    <t xml:space="preserve">32.9627265930176</t>
   </si>
   <si>
     <t xml:space="preserve">32.5232238769531</t>
@@ -3212,22 +3212,22 @@
     <t xml:space="preserve">32.6208915710449</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4488849639893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6697273254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7673873901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2144832611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0191478729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9019470214844</t>
+    <t xml:space="preserve">31.4488830566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6697235107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.767391204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2144813537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0191459655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9019451141357</t>
   </si>
   <si>
     <t xml:space="preserve">29.6518058776855</t>
@@ -3248,7 +3248,7 @@
     <t xml:space="preserve">31.3316860198975</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1716232299805</t>
+    <t xml:space="preserve">32.1716194152832</t>
   </si>
   <si>
     <t xml:space="preserve">31.3902816772461</t>
@@ -3260,13 +3260,13 @@
     <t xml:space="preserve">29.8862056732178</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9643402099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3821277618408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4993305206299</t>
+    <t xml:space="preserve">29.9643383026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3821296691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4993286132812</t>
   </si>
   <si>
     <t xml:space="preserve">29.2025337219238</t>
@@ -3281,7 +3281,7 @@
     <t xml:space="preserve">29.085334777832</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3039970397949</t>
+    <t xml:space="preserve">28.3039951324463</t>
   </si>
   <si>
     <t xml:space="preserve">28.4211959838867</t>
@@ -3290,16 +3290,16 @@
     <t xml:space="preserve">27.0147857666016</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3235263824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5970001220703</t>
+    <t xml:space="preserve">28.3235282897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5969982147217</t>
   </si>
   <si>
     <t xml:space="preserve">28.2258625030518</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5579299926758</t>
+    <t xml:space="preserve">28.5579280853271</t>
   </si>
   <si>
     <t xml:space="preserve">28.1816463470459</t>
@@ -3311,31 +3311,31 @@
     <t xml:space="preserve">26.5972957611084</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6765117645264</t>
+    <t xml:space="preserve">26.676513671875</t>
   </si>
   <si>
     <t xml:space="preserve">26.8745555877686</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5280990600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4784679412842</t>
+    <t xml:space="preserve">27.5281009674072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4784698486328</t>
   </si>
   <si>
     <t xml:space="preserve">26.7359256744385</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2508411407471</t>
+    <t xml:space="preserve">27.2508392333984</t>
   </si>
   <si>
     <t xml:space="preserve">28.0628204345703</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3994941711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.320276260376</t>
+    <t xml:space="preserve">28.3994960784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3202781677246</t>
   </si>
   <si>
     <t xml:space="preserve">27.765754699707</t>
@@ -3347,7 +3347,7 @@
     <t xml:space="preserve">28.4193000793457</t>
   </si>
   <si>
-    <t xml:space="preserve">29.013427734375</t>
+    <t xml:space="preserve">29.0134296417236</t>
   </si>
   <si>
     <t xml:space="preserve">29.1124515533447</t>
@@ -3359,7 +3359,7 @@
     <t xml:space="preserve">29.1322574615479</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9933834075928</t>
+    <t xml:space="preserve">26.9933815002441</t>
   </si>
   <si>
     <t xml:space="preserve">24.9931392669678</t>
@@ -3374,19 +3374,19 @@
     <t xml:space="preserve">24.4584217071533</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4288349151611</t>
+    <t xml:space="preserve">25.4288368225098</t>
   </si>
   <si>
     <t xml:space="preserve">25.6070766448975</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4684448242188</t>
+    <t xml:space="preserve">25.4684429168701</t>
   </si>
   <si>
     <t xml:space="preserve">24.8148994445801</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2902069091797</t>
+    <t xml:space="preserve">25.2902050018311</t>
   </si>
   <si>
     <t xml:space="preserve">25.3694229125977</t>
@@ -3410,7 +3410,7 @@
     <t xml:space="preserve">23.547420501709</t>
   </si>
   <si>
-    <t xml:space="preserve">24.200963973999</t>
+    <t xml:space="preserve">24.2009620666504</t>
   </si>
   <si>
     <t xml:space="preserve">23.6068325042725</t>
@@ -3434,13 +3434,13 @@
     <t xml:space="preserve">22.9532890319824</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4188117980957</t>
+    <t xml:space="preserve">24.4188098907471</t>
   </si>
   <si>
     <t xml:space="preserve">23.7058544158936</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7356815338135</t>
+    <t xml:space="preserve">24.7356834411621</t>
   </si>
   <si>
     <t xml:space="preserve">24.597053527832</t>
@@ -3455,7 +3455,7 @@
     <t xml:space="preserve">25.8249244689941</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0823802947998</t>
+    <t xml:space="preserve">26.0823822021484</t>
   </si>
   <si>
     <t xml:space="preserve">26.1615982055664</t>
@@ -3464,31 +3464,31 @@
     <t xml:space="preserve">25.3892269134521</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1317672729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5674648284912</t>
+    <t xml:space="preserve">25.1317691802979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5674667358398</t>
   </si>
   <si>
     <t xml:space="preserve">26.0427722930908</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1417942047119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.884334564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4882469177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5178337097168</t>
+    <t xml:space="preserve">26.1417922973633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8843364715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4882488250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5178356170654</t>
   </si>
   <si>
     <t xml:space="preserve">24.0227241516113</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2207660675049</t>
+    <t xml:space="preserve">24.2207679748535</t>
   </si>
   <si>
     <t xml:space="preserve">24.1217479705811</t>
@@ -3503,22 +3503,22 @@
     <t xml:space="preserve">24.2603778839111</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3593997955322</t>
+    <t xml:space="preserve">24.3593978881836</t>
   </si>
   <si>
     <t xml:space="preserve">23.626636505127</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4980297088623</t>
+    <t xml:space="preserve">24.4980278015137</t>
   </si>
   <si>
     <t xml:space="preserve">23.8642902374268</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9435062408447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7850704193115</t>
+    <t xml:space="preserve">23.9435081481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7850723266602</t>
   </si>
   <si>
     <t xml:space="preserve">24.8743133544922</t>
@@ -3530,7 +3530,7 @@
     <t xml:space="preserve">24.2999877929688</t>
   </si>
   <si>
-    <t xml:space="preserve">23.765266418457</t>
+    <t xml:space="preserve">23.7652645111084</t>
   </si>
   <si>
     <t xml:space="preserve">22.8344593048096</t>
@@ -3539,7 +3539,7 @@
     <t xml:space="preserve">22.5571994781494</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7156352996826</t>
+    <t xml:space="preserve">22.715633392334</t>
   </si>
   <si>
     <t xml:space="preserve">22.0422859191895</t>
@@ -3548,7 +3548,7 @@
     <t xml:space="preserve">21.071870803833</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1212596893311</t>
+    <t xml:space="preserve">20.1212577819824</t>
   </si>
   <si>
     <t xml:space="preserve">19.8638019561768</t>
@@ -3557,7 +3557,7 @@
     <t xml:space="preserve">20.0618476867676</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2696704864502</t>
+    <t xml:space="preserve">19.2696685791016</t>
   </si>
   <si>
     <t xml:space="preserve">19.8836078643799</t>
@@ -3572,7 +3572,7 @@
     <t xml:space="preserve">20.9926528930664</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2501087188721</t>
+    <t xml:space="preserve">21.2501106262207</t>
   </si>
   <si>
     <t xml:space="preserve">21.2897186279297</t>
@@ -3584,19 +3584,19 @@
     <t xml:space="preserve">20.8540210723877</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3887405395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6065902709961</t>
+    <t xml:space="preserve">21.3887424468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6065883636475</t>
   </si>
   <si>
     <t xml:space="preserve">22.0026760101318</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2007217407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6660022735596</t>
+    <t xml:space="preserve">22.200719833374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6660003662109</t>
   </si>
   <si>
     <t xml:space="preserve">21.5075664520264</t>
@@ -3611,7 +3611,7 @@
     <t xml:space="preserve">22.1809158325195</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4383716583252</t>
+    <t xml:space="preserve">22.4383735656738</t>
   </si>
   <si>
     <t xml:space="preserve">21.7848281860352</t>
@@ -3629,7 +3629,7 @@
     <t xml:space="preserve">23.6662445068359</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1415481567383</t>
+    <t xml:space="preserve">24.1415500640869</t>
   </si>
   <si>
     <t xml:space="preserve">25.7457065582275</t>
@@ -3638,22 +3638,22 @@
     <t xml:space="preserve">27.0329895019531</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6369037628174</t>
+    <t xml:space="preserve">26.6369018554688</t>
   </si>
   <si>
     <t xml:space="preserve">26.5576858520508</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9831142425537</t>
+    <t xml:space="preserve">23.9831123352051</t>
   </si>
   <si>
     <t xml:space="preserve">25.0525531768799</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2505970001221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.201208114624</t>
+    <t xml:space="preserve">25.2505950927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2012062072754</t>
   </si>
   <si>
     <t xml:space="preserve">26.4190540313721</t>
@@ -3680,10 +3680,10 @@
     <t xml:space="preserve">22.9730930328369</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7950973510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2704010009766</t>
+    <t xml:space="preserve">24.7950954437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2704029083252</t>
   </si>
   <si>
     <t xml:space="preserve">26.1219882965088</t>
@@ -3692,7 +3692,7 @@
     <t xml:space="preserve">26.0625743865967</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7853145599365</t>
+    <t xml:space="preserve">25.7853164672852</t>
   </si>
   <si>
     <t xml:space="preserve">26.2606220245361</t>
@@ -3704,7 +3704,7 @@
     <t xml:space="preserve">26.795337677002</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0232086181641</t>
+    <t xml:space="preserve">28.0232105255127</t>
   </si>
   <si>
     <t xml:space="preserve">27.5875148773193</t>
@@ -3722,16 +3722,16 @@
     <t xml:space="preserve">28.2212543487549</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5777320861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2806701660156</t>
+    <t xml:space="preserve">28.5777339935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.280668258667</t>
   </si>
   <si>
     <t xml:space="preserve">28.8153858184814</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8747978210449</t>
+    <t xml:space="preserve">28.8747997283936</t>
   </si>
   <si>
     <t xml:space="preserve">28.7163639068604</t>
@@ -3767,7 +3767,7 @@
     <t xml:space="preserve">29.5877571105957</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3303031921387</t>
+    <t xml:space="preserve">29.33030128479</t>
   </si>
   <si>
     <t xml:space="preserve">29.4491271972656</t>
@@ -3788,13 +3788,13 @@
     <t xml:space="preserve">27.805362701416</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3004722595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4787139892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0430164337158</t>
+    <t xml:space="preserve">28.3004703521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4787120819092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0430145263672</t>
   </si>
   <si>
     <t xml:space="preserve">27.6469268798828</t>
@@ -3815,10 +3815,10 @@
     <t xml:space="preserve">24.4782257080078</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3097686767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3789596557617</t>
+    <t xml:space="preserve">23.3097667694092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3789615631104</t>
   </si>
   <si>
     <t xml:space="preserve">24.280179977417</t>
@@ -3827,13 +3827,13 @@
     <t xml:space="preserve">24.5574417114258</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8347034454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0921630859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8447284698486</t>
+    <t xml:space="preserve">24.8347053527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0921611785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8447265625</t>
   </si>
   <si>
     <t xml:space="preserve">26.3893489837646</t>
@@ -3857,7 +3857,7 @@
     <t xml:space="preserve">27.77565574646</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6766338348389</t>
+    <t xml:space="preserve">27.6766357421875</t>
   </si>
   <si>
     <t xml:space="preserve">27.4290790557861</t>
@@ -3866,19 +3866,19 @@
     <t xml:space="preserve">27.1815242767334</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9339714050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.379566192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8844585418701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7261428833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9834804534912</t>
+    <t xml:space="preserve">26.9339694976807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3795680999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8844566345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7261447906494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9834823608398</t>
   </si>
   <si>
     <t xml:space="preserve">27.330057144165</t>
@@ -3890,7 +3890,7 @@
     <t xml:space="preserve">27.9241886138916</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4688091278076</t>
+    <t xml:space="preserve">28.4688110351562</t>
   </si>
   <si>
     <t xml:space="preserve">29.5085391998291</t>
@@ -3905,13 +3905,13 @@
     <t xml:space="preserve">30.944356918335</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0831108093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6375141143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1821365356445</t>
+    <t xml:space="preserve">32.0831146240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6375122070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1821327209473</t>
   </si>
   <si>
     <t xml:space="preserve">32.9247970581055</t>
@@ -3920,7 +3920,7 @@
     <t xml:space="preserve">32.4296875</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2316436767578</t>
+    <t xml:space="preserve">32.2316398620605</t>
   </si>
   <si>
     <t xml:space="preserve">31.9840888977051</t>
@@ -3929,10 +3929,10 @@
     <t xml:space="preserve">31.1919136047363</t>
   </si>
   <si>
-    <t xml:space="preserve">31.340446472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7958240509033</t>
+    <t xml:space="preserve">31.3404445648193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.795825958252</t>
   </si>
   <si>
     <t xml:space="preserve">30.6472949981689</t>
@@ -3944,7 +3944,7 @@
     <t xml:space="preserve">30.3997383117676</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2512035369873</t>
+    <t xml:space="preserve">30.2512054443359</t>
   </si>
   <si>
     <t xml:space="preserve">30.5977802276611</t>

--- a/data/MOL.MI.xlsx
+++ b/data/MOL.MI.xlsx
@@ -50,100 +50,100 @@
     <t xml:space="preserve">6.66036558151245</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7710018157959</t>
+    <t xml:space="preserve">6.77100276947021</t>
   </si>
   <si>
     <t xml:space="preserve">6.63823795318604</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72674798965454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81525707244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54972839355469</t>
+    <t xml:space="preserve">6.72674751281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81525754928589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54972791671753</t>
   </si>
   <si>
     <t xml:space="preserve">6.31960248947144</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09832811355591</t>
+    <t xml:space="preserve">6.09832715988159</t>
   </si>
   <si>
     <t xml:space="preserve">6.35058116912842</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2399435043335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5585789680481</t>
+    <t xml:space="preserve">6.23994302749634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55857801437378</t>
   </si>
   <si>
     <t xml:space="preserve">6.46121883392334</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89475536346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52317476272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65594053268433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76215171813965</t>
+    <t xml:space="preserve">5.89475584030151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52317523956299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65594005584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76215219497681</t>
   </si>
   <si>
     <t xml:space="preserve">6.66479110717773</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69134330749512</t>
+    <t xml:space="preserve">6.69134426116943</t>
   </si>
   <si>
     <t xml:space="preserve">6.68249368667603</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01866912841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89918088912964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28419876098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06292390823364</t>
+    <t xml:space="preserve">6.01866865158081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8991813659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28419828414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06292343139648</t>
   </si>
   <si>
     <t xml:space="preserve">6.25322008132935</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39926099777222</t>
+    <t xml:space="preserve">6.39926195144653</t>
   </si>
   <si>
     <t xml:space="preserve">6.34173011779785</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5098991394043</t>
+    <t xml:space="preserve">6.50989866256714</t>
   </si>
   <si>
     <t xml:space="preserve">6.33287906646729</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42581510543823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39040994644165</t>
+    <t xml:space="preserve">6.42581415176392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39041042327881</t>
   </si>
   <si>
     <t xml:space="preserve">6.30632591247559</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40811252593994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35500574111938</t>
+    <t xml:space="preserve">6.40811204910278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3550066947937</t>
   </si>
   <si>
     <t xml:space="preserve">6.63381242752075</t>
@@ -152,91 +152,91 @@
     <t xml:space="preserve">6.43466520309448</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2266674041748</t>
+    <t xml:space="preserve">6.22666645050049</t>
   </si>
   <si>
     <t xml:space="preserve">6.24436950683594</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27534770965576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26649618148804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62938737869263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43909072875977</t>
+    <t xml:space="preserve">6.27534818649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26649713516235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62938642501831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43909025192261</t>
   </si>
   <si>
     <t xml:space="preserve">6.41253757476807</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45236682891846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4567928314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36828374862671</t>
+    <t xml:space="preserve">6.45236730575562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45679330825806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36828279495239</t>
   </si>
   <si>
     <t xml:space="preserve">6.19568920135498</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06734943389893</t>
+    <t xml:space="preserve">6.06734895706177</t>
   </si>
   <si>
     <t xml:space="preserve">6.28862428665161</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20454072952271</t>
+    <t xml:space="preserve">6.20454120635986</t>
   </si>
   <si>
     <t xml:space="preserve">6.29304981231689</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24879455566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22224235534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25764513015747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15585899353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19126272201538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58955812454224</t>
+    <t xml:space="preserve">6.24879503250122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22224140167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25764656066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15585947036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19126319885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58955717086792</t>
   </si>
   <si>
     <t xml:space="preserve">6.47892045974731</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49662208557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42138957977295</t>
+    <t xml:space="preserve">6.49662256240845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42138814926147</t>
   </si>
   <si>
     <t xml:space="preserve">6.63348960876465</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45273971557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54311466217041</t>
+    <t xml:space="preserve">6.45274066925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54311513900757</t>
   </si>
   <si>
     <t xml:space="preserve">6.44370269775391</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50696420669556</t>
+    <t xml:space="preserve">6.50696468353271</t>
   </si>
   <si>
     <t xml:space="preserve">6.55667114257812</t>
@@ -245,10 +245,10 @@
     <t xml:space="preserve">6.36688470840454</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61993312835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69223308563232</t>
+    <t xml:space="preserve">6.61993265151978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69223260879517</t>
   </si>
   <si>
     <t xml:space="preserve">6.59733963012695</t>
@@ -257,43 +257,43 @@
     <t xml:space="preserve">6.68319511413574</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70578861236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75097560882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8503885269165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94528150558472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98594999313354</t>
+    <t xml:space="preserve">6.70578956604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75097608566284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85038805007935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94528102874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98595094680786</t>
   </si>
   <si>
     <t xml:space="preserve">7.1034369468689</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25255489349365</t>
+    <t xml:space="preserve">7.25255441665649</t>
   </si>
   <si>
     <t xml:space="preserve">7.32033634185791</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45589685440063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30226135253906</t>
+    <t xml:space="preserve">7.45589780807495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3022608757019</t>
   </si>
   <si>
     <t xml:space="preserve">7.37907981872559</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25707340240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22996139526367</t>
+    <t xml:space="preserve">7.25707292556763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22996091842651</t>
   </si>
   <si>
     <t xml:space="preserve">7.22544193267822</t>
@@ -302,7 +302,7 @@
     <t xml:space="preserve">7.19833040237427</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09439992904663</t>
+    <t xml:space="preserve">7.09439897537231</t>
   </si>
   <si>
     <t xml:space="preserve">7.13958644866943</t>
@@ -314,28 +314,28 @@
     <t xml:space="preserve">7.08084344863892</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95883703231812</t>
+    <t xml:space="preserve">6.95883750915527</t>
   </si>
   <si>
     <t xml:space="preserve">6.84135103225708</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11699295043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16669845581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31129884719849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32485389709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99950647354126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73290061950684</t>
+    <t xml:space="preserve">7.11699342727661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16669940948486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31129789352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32485437393188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9995059967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73290109634399</t>
   </si>
   <si>
     <t xml:space="preserve">7.08988094329834</t>
@@ -344,19 +344,19 @@
     <t xml:space="preserve">7.18477344512939</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85942602157593</t>
+    <t xml:space="preserve">6.85942506790161</t>
   </si>
   <si>
     <t xml:space="preserve">6.67867660522461</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49792766571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57022714614868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57926559448242</t>
+    <t xml:space="preserve">6.49792814254761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57022666931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57926511764526</t>
   </si>
   <si>
     <t xml:space="preserve">6.41659069061279</t>
@@ -365,55 +365,55 @@
     <t xml:space="preserve">6.74645757675171</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65156412124634</t>
+    <t xml:space="preserve">6.65156364440918</t>
   </si>
   <si>
     <t xml:space="preserve">6.55215215682983</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46177816390991</t>
+    <t xml:space="preserve">6.46177768707275</t>
   </si>
   <si>
     <t xml:space="preserve">6.75549507141113</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56570863723755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77808856964111</t>
+    <t xml:space="preserve">6.56570768356323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77808809280396</t>
   </si>
   <si>
     <t xml:space="preserve">6.71030855178833</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48889017105103</t>
+    <t xml:space="preserve">6.48888969421387</t>
   </si>
   <si>
     <t xml:space="preserve">6.53859663009644</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66060161590576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68771457672119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76001358032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87750053405762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70127058029175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7871265411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79616403579712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81423759460449</t>
+    <t xml:space="preserve">6.66060209274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68771409988403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76001310348511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87750005722046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70127010345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78712606430054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79616355895996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81423807144165</t>
   </si>
   <si>
     <t xml:space="preserve">6.81875705718994</t>
@@ -434,34 +434,34 @@
     <t xml:space="preserve">6.86846303939819</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98143100738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17573642730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01306295394897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97691202163696</t>
+    <t xml:space="preserve">6.98143148422241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17573595046997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01306247711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9769115447998</t>
   </si>
   <si>
     <t xml:space="preserve">6.64252662658691</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69675159454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88653802871704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93172597885132</t>
+    <t xml:space="preserve">6.6967511177063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88653755187988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.931725025177</t>
   </si>
   <si>
     <t xml:space="preserve">7.02209997177124</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99046897888184</t>
+    <t xml:space="preserve">6.99046850204468</t>
   </si>
   <si>
     <t xml:space="preserve">7.19381093978882</t>
@@ -476,40 +476,40 @@
     <t xml:space="preserve">7.06728744506836</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14862442016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08536148071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06276798248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15766191482544</t>
+    <t xml:space="preserve">7.14862394332886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08536195755005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06276750564575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15766143798828</t>
   </si>
   <si>
     <t xml:space="preserve">7.21188640594482</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38359832763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22092342376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24803638458252</t>
+    <t xml:space="preserve">7.38359785079956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22092294692993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24803686141968</t>
   </si>
   <si>
     <t xml:space="preserve">7.18929243087769</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35648584365845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.370041847229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88201904296875</t>
+    <t xml:space="preserve">7.35648536682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37004137039185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88201856613159</t>
   </si>
   <si>
     <t xml:space="preserve">7.0356559753418</t>
@@ -518,55 +518,55 @@
     <t xml:space="preserve">7.18025493621826</t>
   </si>
   <si>
-    <t xml:space="preserve">6.913649559021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5191593170166</t>
+    <t xml:space="preserve">6.91365098953247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51915836334229</t>
   </si>
   <si>
     <t xml:space="preserve">7.47849082946777</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50108432769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41070938110352</t>
+    <t xml:space="preserve">7.50108480453491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41070890426636</t>
   </si>
   <si>
     <t xml:space="preserve">7.27514839172363</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60953378677368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66375875473022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72702074050903</t>
+    <t xml:space="preserve">7.60953426361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66375827789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72702217102051</t>
   </si>
   <si>
     <t xml:space="preserve">7.68183374404907</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67731428146362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63664674758911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77220821380615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97103071212769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34156703948975</t>
+    <t xml:space="preserve">7.67731475830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63664579391479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77220773696899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.971031665802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34156799316406</t>
   </si>
   <si>
     <t xml:space="preserve">8.41386699676514</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45001792907715</t>
+    <t xml:space="preserve">8.45001888275146</t>
   </si>
   <si>
     <t xml:space="preserve">8.57654190063477</t>
@@ -578,64 +578,64 @@
     <t xml:space="preserve">8.409348487854</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35964298248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22407913208008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24215602874756</t>
+    <t xml:space="preserve">8.35964107513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22408199310303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24215507507324</t>
   </si>
   <si>
     <t xml:space="preserve">8.33704853057861</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32800960540771</t>
+    <t xml:space="preserve">8.32801246643066</t>
   </si>
   <si>
     <t xml:space="preserve">8.3234920501709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36416053771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37319850921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46809196472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30541706085205</t>
+    <t xml:space="preserve">8.36416149139404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37320041656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46809101104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30541896820068</t>
   </si>
   <si>
     <t xml:space="preserve">8.30090045928955</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09755706787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26926708221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20600509643555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07496356964111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11111259460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28282451629639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29638004302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40482997894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48164939880371</t>
+    <t xml:space="preserve">8.09755611419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26926612854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20600605010986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0749626159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11111164093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2828254699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29638195037842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40482902526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48164844512939</t>
   </si>
   <si>
     <t xml:space="preserve">8.42290496826172</t>
@@ -644,37 +644,37 @@
     <t xml:space="preserve">8.22859954833984</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27378749847412</t>
+    <t xml:space="preserve">8.27378559112549</t>
   </si>
   <si>
     <t xml:space="preserve">8.02977561950684</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13370513916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27830600738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43194103240967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6940279006958</t>
+    <t xml:space="preserve">8.13370609283447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27830505371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43194198608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69402885437012</t>
   </si>
   <si>
     <t xml:space="preserve">9.57969856262207</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25434970855713</t>
+    <t xml:space="preserve">9.25434875488281</t>
   </si>
   <si>
     <t xml:space="preserve">9.21820068359375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01937675476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16397571563721</t>
+    <t xml:space="preserve">9.01937484741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16397762298584</t>
   </si>
   <si>
     <t xml:space="preserve">9.2001256942749</t>
@@ -683,28 +683,28 @@
     <t xml:space="preserve">9.20916366577148</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22723865509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94707584381104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03744983673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12782573699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35376262664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55258560180664</t>
+    <t xml:space="preserve">9.22723770141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94707679748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03745174407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12782669067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35376358032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55258655548096</t>
   </si>
   <si>
     <t xml:space="preserve">9.47124767303467</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80563735961914</t>
+    <t xml:space="preserve">9.80563449859619</t>
   </si>
   <si>
     <t xml:space="preserve">9.89600849151611</t>
@@ -719,97 +719,97 @@
     <t xml:space="preserve">10.4472951889038</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8449420928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8087921142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.908203125</t>
+    <t xml:space="preserve">10.8449411392212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8087911605835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9082040786743</t>
   </si>
   <si>
     <t xml:space="preserve">10.9353160858154</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7364921569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7093811035156</t>
+    <t xml:space="preserve">10.7364931106567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7093801498413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7545652389526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4764318466187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2261085510254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0128736495972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3837184906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4300765991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2817373275757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4022626876831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5135164260864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4949741363525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5413293838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7452964782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0790586471558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7743968963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5889739990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2181282043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3015651702881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0975999832153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1439571380615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0327014923096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8287382125854</t>
   </si>
   <si>
     <t xml:space="preserve">10.754566192627</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4764318466187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.226110458374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0128726959229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3837194442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4300756454468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2817373275757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4022617340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5135173797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4949741363525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5413303375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7452955245972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0790567398071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.774395942688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5889739990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2181262969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3015661239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0975999832153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1439571380615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0327014923096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8287363052368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7545671463013</t>
-  </si>
-  <si>
     <t xml:space="preserve">10.7360248565674</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9863481521606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8658218383789</t>
+    <t xml:space="preserve">10.9863471984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8658208847046</t>
   </si>
   <si>
     <t xml:space="preserve">10.5691432952881</t>
@@ -827,40 +827,40 @@
     <t xml:space="preserve">11.0697870254517</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9399919509888</t>
+    <t xml:space="preserve">10.9399909973145</t>
   </si>
   <si>
     <t xml:space="preserve">11.4499063491821</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4035491943359</t>
+    <t xml:space="preserve">11.4035501480103</t>
   </si>
   <si>
     <t xml:space="preserve">11.7094984054565</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0988883972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3213958740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.894923210144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5160903930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5253629684448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6737003326416</t>
+    <t xml:space="preserve">12.0988874435425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3213968276978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8949213027954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5160894393921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5253620147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6737012863159</t>
   </si>
   <si>
     <t xml:space="preserve">12.7478704452515</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5346345901489</t>
+    <t xml:space="preserve">12.5346326828003</t>
   </si>
   <si>
     <t xml:space="preserve">12.7942276000977</t>
@@ -875,28 +875,28 @@
     <t xml:space="preserve">12.5809888839722</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5624485015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4697351455688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4975481033325</t>
+    <t xml:space="preserve">12.5624475479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4697360992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4975490570068</t>
   </si>
   <si>
     <t xml:space="preserve">12.4882783889771</t>
   </si>
   <si>
-    <t xml:space="preserve">12.68297290802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.627345085144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5531768798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1823291778564</t>
+    <t xml:space="preserve">12.6829719543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6273460388184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5531759262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1823282241821</t>
   </si>
   <si>
     <t xml:space="preserve">12.3955659866333</t>
@@ -905,49 +905,49 @@
     <t xml:space="preserve">12.423378944397</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2935829162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3677539825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8856506347656</t>
+    <t xml:space="preserve">12.2935838699341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3677530288696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8856515884399</t>
   </si>
   <si>
     <t xml:space="preserve">12.28431224823</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1730585098267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0525312423706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.95055103302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3121242523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2657680511475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9412794113159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9598188400269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3306684494019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4419212341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3492088317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3770236968994</t>
+    <t xml:space="preserve">12.1730575561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0525331497192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9505491256714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.312123298645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2657690048218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9412775039673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9598197937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3306665420532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4419221878052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3492107391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3770246505737</t>
   </si>
   <si>
     <t xml:space="preserve">12.1545152664185</t>
@@ -956,13 +956,13 @@
     <t xml:space="preserve">12.2472267150879</t>
   </si>
   <si>
-    <t xml:space="preserve">12.339940071106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4511938095093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2008714675903</t>
+    <t xml:space="preserve">12.3399381637573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4511919021606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.200870513916</t>
   </si>
   <si>
     <t xml:space="preserve">12.4326486587524</t>
@@ -971,67 +971,67 @@
     <t xml:space="preserve">12.3028545379639</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2564992904663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.061803817749</t>
+    <t xml:space="preserve">12.2565002441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0618028640747</t>
   </si>
   <si>
     <t xml:space="preserve">12.0247192382812</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4406356811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6353302001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7929382324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6631412506104</t>
+    <t xml:space="preserve">11.440634727478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.635329246521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7929391860962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.663143157959</t>
   </si>
   <si>
     <t xml:space="preserve">11.6816854476929</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7465829849243</t>
+    <t xml:space="preserve">11.7465839385986</t>
   </si>
   <si>
     <t xml:space="preserve">11.9227352142334</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8207530975342</t>
+    <t xml:space="preserve">11.8207521438599</t>
   </si>
   <si>
     <t xml:space="preserve">11.8671102523804</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7373113632202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.228684425354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1915988922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7651252746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.718770980835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1903114318848</t>
+    <t xml:space="preserve">11.7373123168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2286825180054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1916017532349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7651262283325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7187700271606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1903123855591</t>
   </si>
   <si>
     <t xml:space="preserve">11.2922954559326</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1624994277954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5426168441772</t>
+    <t xml:space="preserve">11.1624984741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5426187515259</t>
   </si>
   <si>
     <t xml:space="preserve">11.4684476852417</t>
@@ -1040,109 +1040,109 @@
     <t xml:space="preserve">11.5982446670532</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5797004699707</t>
+    <t xml:space="preserve">11.579701423645</t>
   </si>
   <si>
     <t xml:space="preserve">11.4962615966797</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6724147796631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8578367233276</t>
+    <t xml:space="preserve">11.6724138259888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.857837677002</t>
   </si>
   <si>
     <t xml:space="preserve">12.1452445983887</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0061750411987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9134664535522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9240226745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.925311088562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1107339859009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.092191696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9438533782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9994812011719</t>
+    <t xml:space="preserve">12.006175994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9134654998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9240236282349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9253101348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1107330322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0921907424927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9438514709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9994792938232</t>
   </si>
   <si>
     <t xml:space="preserve">14.6299200057983</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9067678451538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6286315917969</t>
+    <t xml:space="preserve">13.9067687988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6286334991455</t>
   </si>
   <si>
     <t xml:space="preserve">14.2034454345703</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0180196762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7028017044067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3888711929321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.518666267395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5742921829224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4815797805786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1849021911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8325977325439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9981937408447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7756843566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3690376281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0352783203125</t>
+    <t xml:space="preserve">14.0180215835571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7028036117554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3888692855835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5186653137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5742931365967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4815816879272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1849031448364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8325996398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.998194694519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7756834030151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3690385818481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0352764129639</t>
   </si>
   <si>
     <t xml:space="preserve">12.7385988235474</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9796495437622</t>
+    <t xml:space="preserve">12.9796504974365</t>
   </si>
   <si>
     <t xml:space="preserve">13.5173778533936</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3134126663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6644296646118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1081609725952</t>
+    <t xml:space="preserve">13.3134117126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6644287109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1081590652466</t>
   </si>
   <si>
     <t xml:space="preserve">12.0154476165771</t>
@@ -1160,73 +1160,73 @@
     <t xml:space="preserve">12.6088037490845</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1637868881226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.033989906311</t>
+    <t xml:space="preserve">12.1637849807739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0339879989624</t>
   </si>
   <si>
     <t xml:space="preserve">12.0710754394531</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6075162887573</t>
+    <t xml:space="preserve">11.607515335083</t>
   </si>
   <si>
     <t xml:space="preserve">12.4604635238647</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8114814758301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8485660552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2379560470581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3862953186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3504953384399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5359210968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7213449478149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2590732574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.908055305481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7782592773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7411727905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7968006134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0235719680786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6849851608276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4015226364136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2314453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.080265045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1180610656738</t>
+    <t xml:space="preserve">11.8114795684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8485670089722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2379550933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3862943649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3504962921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5359201431274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7213430404663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2590751647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9080572128296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7782583236694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7411737442017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7968015670776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0235710144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6849889755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4015235900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2314443588257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0802659988403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1180601119995</t>
   </si>
   <si>
     <t xml:space="preserve">15.174750328064</t>
@@ -1250,10 +1250,10 @@
     <t xml:space="preserve">13.6818437576294</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0771226882935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9448385238647</t>
+    <t xml:space="preserve">13.0771207809448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9448394775391</t>
   </si>
   <si>
     <t xml:space="preserve">13.114917755127</t>
@@ -1268,19 +1268,19 @@
     <t xml:space="preserve">12.5479888916016</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0015306472778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6235809326172</t>
+    <t xml:space="preserve">13.0015325546265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6235799789429</t>
   </si>
   <si>
     <t xml:space="preserve">12.6991701126099</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7558622360229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8692483901978</t>
+    <t xml:space="preserve">12.7558641433716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8692493438721</t>
   </si>
   <si>
     <t xml:space="preserve">12.3401165008545</t>
@@ -1289,19 +1289,19 @@
     <t xml:space="preserve">12.736964225769</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7180671691895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7747592926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2645244598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7385358810425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7763319015503</t>
+    <t xml:space="preserve">12.7180681228638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7747602462769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2645254135132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7385368347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.776330947876</t>
   </si>
   <si>
     <t xml:space="preserve">13.9653072357178</t>
@@ -1310,25 +1310,25 @@
     <t xml:space="preserve">13.8708190917969</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0786933898926</t>
+    <t xml:space="preserve">14.0786924362183</t>
   </si>
   <si>
     <t xml:space="preserve">13.625150680542</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5873575210571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4172763824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4550743103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4361753463745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.247200012207</t>
+    <t xml:space="preserve">13.5873556137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4172782897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4550714492798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4361763000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2472009658813</t>
   </si>
   <si>
     <t xml:space="preserve">13.1338138580322</t>
@@ -1337,64 +1337,64 @@
     <t xml:space="preserve">13.322790145874</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4739713668823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2094039916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3605842590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5668878555298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5101938247681</t>
+    <t xml:space="preserve">13.473970413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2094030380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3605861663818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5668869018555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5101947784424</t>
   </si>
   <si>
     <t xml:space="preserve">12.2834234237671</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6802711486816</t>
+    <t xml:space="preserve">12.6802730560303</t>
   </si>
   <si>
     <t xml:space="preserve">13.0393266677856</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9826326370239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8125562667847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9637365341187</t>
+    <t xml:space="preserve">12.9826345443726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8125553131104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9637355804443</t>
   </si>
   <si>
     <t xml:space="preserve">13.7952299118042</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1164884567261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2676687240601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3054637908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0597953796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7007417678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4928674697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7574338912964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5495615005493</t>
+    <t xml:space="preserve">14.1164865493774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2676696777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3054647445679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.059796333313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.700740814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4928684234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7574367523193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.549560546875</t>
   </si>
   <si>
     <t xml:space="preserve">14.1731815338135</t>
@@ -1406,64 +1406,64 @@
     <t xml:space="preserve">15.4960098266602</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2692413330078</t>
+    <t xml:space="preserve">15.2692403793335</t>
   </si>
   <si>
     <t xml:space="preserve">15.155855178833</t>
   </si>
   <si>
-    <t xml:space="preserve">16.53537940979</t>
+    <t xml:space="preserve">16.5353755950928</t>
   </si>
   <si>
     <t xml:space="preserve">16.7054557800293</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9133281707764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6298675537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2330150604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9117555618286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5904998779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5149087905884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.004674911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2125482559204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3810548782349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6078262329102</t>
+    <t xml:space="preserve">16.913330078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6298656463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2330188751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9117565155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5904989242554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5149097442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0046758651733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2125463485718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3810539245605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6078252792358</t>
   </si>
   <si>
     <t xml:space="preserve">14.4377470016479</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6456184387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2487707138062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1920776367188</t>
+    <t xml:space="preserve">14.6456203460693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2487716674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1920795440674</t>
   </si>
   <si>
     <t xml:space="preserve">13.8897180557251</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5306634902954</t>
+    <t xml:space="preserve">13.5306625366211</t>
   </si>
   <si>
     <t xml:space="preserve">13.8519220352173</t>
@@ -1472,7 +1472,7 @@
     <t xml:space="preserve">14.0220003128052</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8723917007446</t>
+    <t xml:space="preserve">14.8723907470703</t>
   </si>
   <si>
     <t xml:space="preserve">14.4755420684814</t>
@@ -1481,67 +1481,67 @@
     <t xml:space="preserve">14.4188499450684</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5527029037476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9668788909912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0818367004395</t>
+    <t xml:space="preserve">15.5527048110962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9668798446655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0818386077881</t>
   </si>
   <si>
     <t xml:space="preserve">16.0629405975342</t>
   </si>
   <si>
-    <t xml:space="preserve">16.251916885376</t>
+    <t xml:space="preserve">16.2519130706787</t>
   </si>
   <si>
     <t xml:space="preserve">16.0440406799316</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8739652633667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4582176208496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0251407623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.346399307251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1007347106934</t>
+    <t xml:space="preserve">15.8739614486694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4582166671753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0251426696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3464031219482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.100736618042</t>
   </si>
   <si>
     <t xml:space="preserve">16.327507019043</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6471929550171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7983703613281</t>
+    <t xml:space="preserve">15.6471910476685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7983722686768</t>
   </si>
   <si>
     <t xml:space="preserve">15.9306545257568</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0613679885864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8550662994385</t>
+    <t xml:space="preserve">15.0613670349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8550653457642</t>
   </si>
   <si>
     <t xml:space="preserve">15.4771127700806</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7401075363159</t>
+    <t xml:space="preserve">14.7401094436646</t>
   </si>
   <si>
     <t xml:space="preserve">14.9101858139038</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5511322021484</t>
+    <t xml:space="preserve">14.5511331558228</t>
   </si>
   <si>
     <t xml:space="preserve">14.8156995773315</t>
@@ -1553,55 +1553,55 @@
     <t xml:space="preserve">15.5338068008423</t>
   </si>
   <si>
-    <t xml:space="preserve">15.741678237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0424690246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4204196929932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7605781555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6282949447632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8928604125977</t>
+    <t xml:space="preserve">15.7416791915894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0424699783325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4204187393188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7605772018433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6282930374146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.892861366272</t>
   </si>
   <si>
     <t xml:space="preserve">15.9684495925903</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0062465667725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9873495101929</t>
+    <t xml:space="preserve">16.0062446594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9873504638672</t>
   </si>
   <si>
     <t xml:space="preserve">15.6093978881836</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6834144592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6267242431641</t>
+    <t xml:space="preserve">14.6834163665771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6267223358154</t>
   </si>
   <si>
     <t xml:space="preserve">14.8534936904907</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1936492919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0991621017456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2881374359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1952228546143</t>
+    <t xml:space="preserve">15.1936502456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0991611480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2881383895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1952209472656</t>
   </si>
   <si>
     <t xml:space="preserve">17.0078163146973</t>
@@ -1610,19 +1610,19 @@
     <t xml:space="preserve">17.2345886230469</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2534847259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.29128074646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1023044586182</t>
+    <t xml:space="preserve">17.2534866333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2912769317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1023082733154</t>
   </si>
   <si>
     <t xml:space="preserve">17.0645084381104</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0471820831299</t>
+    <t xml:space="preserve">18.0471839904785</t>
   </si>
   <si>
     <t xml:space="preserve">17.4046669006348</t>
@@ -1637,19 +1637,19 @@
     <t xml:space="preserve">17.499153137207</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0456161499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3857688903809</t>
+    <t xml:space="preserve">17.0456142425537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3857669830322</t>
   </si>
   <si>
     <t xml:space="preserve">17.4424591064453</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8582077026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8204135894775</t>
+    <t xml:space="preserve">17.858211517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8204116821289</t>
   </si>
   <si>
     <t xml:space="preserve">17.5558452606201</t>
@@ -1661,13 +1661,13 @@
     <t xml:space="preserve">17.1400985717773</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5731735229492</t>
+    <t xml:space="preserve">16.5731754302979</t>
   </si>
   <si>
     <t xml:space="preserve">16.5920696258545</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2897071838379</t>
+    <t xml:space="preserve">16.2897090911865</t>
   </si>
   <si>
     <t xml:space="preserve">16.8566379547119</t>
@@ -1676,7 +1676,7 @@
     <t xml:space="preserve">16.1574268341064</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5805950164795</t>
+    <t xml:space="preserve">16.5805969238281</t>
   </si>
   <si>
     <t xml:space="preserve">16.5421257019043</t>
@@ -1688,34 +1688,34 @@
     <t xml:space="preserve">16.445951461792</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2343635559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0035457611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9843130111694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6767730712891</t>
+    <t xml:space="preserve">16.2343654632568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0035438537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9843101501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6767711639404</t>
   </si>
   <si>
     <t xml:space="preserve">16.8114185333252</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8306541442871</t>
+    <t xml:space="preserve">16.8306503295898</t>
   </si>
   <si>
     <t xml:space="preserve">16.7537097930908</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6382999420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4267158508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5228939056396</t>
+    <t xml:space="preserve">16.6383018493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4267177581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.522891998291</t>
   </si>
   <si>
     <t xml:space="preserve">15.945839881897</t>
@@ -1724,7 +1724,7 @@
     <t xml:space="preserve">16.4651870727539</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9650735855103</t>
+    <t xml:space="preserve">15.9650774002075</t>
   </si>
   <si>
     <t xml:space="preserve">16.0227813720703</t>
@@ -1733,16 +1733,16 @@
     <t xml:space="preserve">15.8689002990723</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7342557907104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6573171615601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4264965057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3687906265259</t>
+    <t xml:space="preserve">15.7342548370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6573152542114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.426495552063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3687887191772</t>
   </si>
   <si>
     <t xml:space="preserve">15.3110847473145</t>
@@ -1754,31 +1754,31 @@
     <t xml:space="preserve">15.1956748962402</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2341461181641</t>
+    <t xml:space="preserve">15.2341451644897</t>
   </si>
   <si>
     <t xml:space="preserve">15.1379690170288</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0994987487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0033235549927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1187343597412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.253378868103</t>
+    <t xml:space="preserve">15.0994997024536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0033254623413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1187353134155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2533807754517</t>
   </si>
   <si>
     <t xml:space="preserve">15.0610294342041</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8686800003052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8494434356689</t>
+    <t xml:space="preserve">14.8686790466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8494443893433</t>
   </si>
   <si>
     <t xml:space="preserve">14.7147989273071</t>
@@ -1790,10 +1790,7 @@
     <t xml:space="preserve">15.1764392852783</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8302097320557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0802659988403</t>
+    <t xml:space="preserve">14.8302087783813</t>
   </si>
   <si>
     <t xml:space="preserve">14.9648551940918</t>
@@ -1802,19 +1799,19 @@
     <t xml:space="preserve">15.1572046279907</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7917394638062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7532691955566</t>
+    <t xml:space="preserve">14.7917385101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7532682418823</t>
   </si>
   <si>
     <t xml:space="preserve">14.9071493148804</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0225601196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8109731674194</t>
+    <t xml:space="preserve">15.0225591659546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8109741210938</t>
   </si>
   <si>
     <t xml:space="preserve">14.8879137039185</t>
@@ -1835,13 +1832,13 @@
     <t xml:space="preserve">14.6378583908081</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6186246871948</t>
+    <t xml:space="preserve">14.6186227798462</t>
   </si>
   <si>
     <t xml:space="preserve">14.4647436141968</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4455089569092</t>
+    <t xml:space="preserve">14.4455080032349</t>
   </si>
   <si>
     <t xml:space="preserve">14.6570930480957</t>
@@ -1853,73 +1850,76 @@
     <t xml:space="preserve">14.5609197616577</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3495540618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3880262374878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.676549911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5226678848267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7150220870972</t>
+    <t xml:space="preserve">15.3495559692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3880252838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6765508651733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5226707458496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7150201797485</t>
   </si>
   <si>
     <t xml:space="preserve">15.7919616699219</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7727241516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8111972808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9073753356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6380815505981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6188459396362</t>
+    <t xml:space="preserve">16.1574249267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.772723197937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8111963272095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9073686599731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6380805969238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6188440322876</t>
   </si>
   <si>
     <t xml:space="preserve">15.8496656417847</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5803747177124</t>
+    <t xml:space="preserve">15.5803756713867</t>
   </si>
   <si>
     <t xml:space="preserve">15.5034351348877</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8304290771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9266033172607</t>
+    <t xml:space="preserve">15.8304309844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9266052246094</t>
   </si>
   <si>
     <t xml:space="preserve">16.1189575195312</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1576480865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0037689208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9460620880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.888355255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9845333099365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.119176864624</t>
+    <t xml:space="preserve">17.1576499938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0037670135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9460639953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8883571624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9845314025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1191787719727</t>
   </si>
   <si>
     <t xml:space="preserve">17.2730579376221</t>
@@ -1931,10 +1931,10 @@
     <t xml:space="preserve">18.1771049499512</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6000537872314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6577568054199</t>
+    <t xml:space="preserve">17.6000518798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6577606201172</t>
   </si>
   <si>
     <t xml:space="preserve">18.1001644134521</t>
@@ -1946,52 +1946,52 @@
     <t xml:space="preserve">18.1193981170654</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9655170440674</t>
+    <t xml:space="preserve">17.965518951416</t>
   </si>
   <si>
     <t xml:space="preserve">17.9462852478027</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0616970062256</t>
+    <t xml:space="preserve">18.0616931915283</t>
   </si>
   <si>
     <t xml:space="preserve">17.9270496368408</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3117504119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7541561126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1003856658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0234470367432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.542573928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9657402038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9080333709717</t>
+    <t xml:space="preserve">18.3117523193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7541542053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1003875732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0234489440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5425701141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9657382965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9080352783203</t>
   </si>
   <si>
     <t xml:space="preserve">19.4273815155029</t>
   </si>
   <si>
-    <t xml:space="preserve">19.812084197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5235538482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.667818069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2831192016602</t>
+    <t xml:space="preserve">19.8120822906494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5235557556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6678218841553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2831172943115</t>
   </si>
   <si>
     <t xml:space="preserve">18.8503303527832</t>
@@ -2000,34 +2000,34 @@
     <t xml:space="preserve">19.6197319030762</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7159061431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7639923095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3312091827393</t>
+    <t xml:space="preserve">19.7159080505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7639942169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3312072753906</t>
   </si>
   <si>
     <t xml:space="preserve">19.5716457366943</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1967830657959</t>
+    <t xml:space="preserve">20.1967811584473</t>
   </si>
   <si>
     <t xml:space="preserve">20.2448692321777</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2164611816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1585330963135</t>
+    <t xml:space="preserve">22.2164630889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1585369110107</t>
   </si>
   <si>
     <t xml:space="preserve">21.1104488372803</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8219223022461</t>
+    <t xml:space="preserve">20.8219203948975</t>
   </si>
   <si>
     <t xml:space="preserve">20.6295719146729</t>
@@ -2036,28 +2036,28 @@
     <t xml:space="preserve">21.0142726898193</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7257423400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6776580810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9563446044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2929592132568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0044288635254</t>
+    <t xml:space="preserve">20.7257461547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6776599884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9563465118408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2929553985596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0044326782227</t>
   </si>
   <si>
     <t xml:space="preserve">19.8601703643799</t>
   </si>
   <si>
-    <t xml:space="preserve">19.081148147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.773832321167</t>
+    <t xml:space="preserve">19.0811519622803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7738342285156</t>
   </si>
   <si>
     <t xml:space="preserve">20.9180965423584</t>
@@ -2066,40 +2066,40 @@
     <t xml:space="preserve">20.5814819335938</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2547092437744</t>
+    <t xml:space="preserve">21.254711151123</t>
   </si>
   <si>
     <t xml:space="preserve">21.3989715576172</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2066192626953</t>
+    <t xml:space="preserve">21.2066211700439</t>
   </si>
   <si>
     <t xml:space="preserve">21.6394100189209</t>
   </si>
   <si>
-    <t xml:space="preserve">21.447057723999</t>
+    <t xml:space="preserve">21.4470596313477</t>
   </si>
   <si>
     <t xml:space="preserve">21.8317604064941</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0525207519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1006050109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7349185943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1963405609131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.619291305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3113040924072</t>
+    <t xml:space="preserve">20.0525188446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.100606918335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.734920501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1963386535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6192874908447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3113059997559</t>
   </si>
   <si>
     <t xml:space="preserve">16.1958961486816</t>
@@ -2108,25 +2108,25 @@
     <t xml:space="preserve">14.4839782714844</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4262733459473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4642992019653</t>
+    <t xml:space="preserve">14.4262742996216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4643001556396</t>
   </si>
   <si>
     <t xml:space="preserve">12.0218954086304</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1373043060303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6951208114624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9067049026489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9834241867065</t>
+    <t xml:space="preserve">12.137303352356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6951198577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9067058563232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9834251403809</t>
   </si>
   <si>
     <t xml:space="preserve">13.3106412887573</t>
@@ -2141,97 +2141,97 @@
     <t xml:space="preserve">14.1954526901245</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2916288375854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1185140609741</t>
+    <t xml:space="preserve">14.2916269302368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1185121536255</t>
   </si>
   <si>
     <t xml:space="preserve">14.734034538269</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0992784500122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4072589874268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8691215515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1766624450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2151336669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4649648666382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0612506866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1381893157959</t>
+    <t xml:space="preserve">14.0992774963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4072599411011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8691253662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1766605377197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2151317596436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4649658203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0612525939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1381912231445</t>
   </si>
   <si>
     <t xml:space="preserve">16.0420169830322</t>
   </si>
   <si>
-    <t xml:space="preserve">16.59983253479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2153511047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7152404785156</t>
+    <t xml:space="preserve">16.5998306274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.215353012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7152423858643</t>
   </si>
   <si>
     <t xml:space="preserve">16.9268283843994</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0614700317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2540454864502</t>
+    <t xml:space="preserve">17.0614719390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2540435791016</t>
   </si>
   <si>
     <t xml:space="preserve">18.638744354248</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0774517059326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7677745819092</t>
+    <t xml:space="preserve">18.0774536132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7677764892578</t>
   </si>
   <si>
     <t xml:space="preserve">17.4580993652344</t>
   </si>
   <si>
-    <t xml:space="preserve">17.43874168396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.206485748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9548721313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4193897247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6129360198975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1677722930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.651647567749</t>
+    <t xml:space="preserve">17.4387435913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2064838409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.954870223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4193878173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6129379272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1677742004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6516456604004</t>
   </si>
   <si>
     <t xml:space="preserve">17.4968070983887</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7290687561035</t>
+    <t xml:space="preserve">17.7290668487549</t>
   </si>
   <si>
     <t xml:space="preserve">18.2903575897217</t>
@@ -2243,16 +2243,16 @@
     <t xml:space="preserve">18.0580997467041</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3871307373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4064865112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.903263092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.232292175293</t>
+    <t xml:space="preserve">18.3871326446533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4064884185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9032611846924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2322902679443</t>
   </si>
   <si>
     <t xml:space="preserve">18.2516479492188</t>
@@ -2267,16 +2267,16 @@
     <t xml:space="preserve">18.1161632537842</t>
   </si>
   <si>
-    <t xml:space="preserve">18.038745880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8322944641113</t>
+    <t xml:space="preserve">18.0387439727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8322925567627</t>
   </si>
   <si>
     <t xml:space="preserve">18.7742290496826</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6774559020996</t>
+    <t xml:space="preserve">18.6774520874023</t>
   </si>
   <si>
     <t xml:space="preserve">18.9097156524658</t>
@@ -2285,7 +2285,7 @@
     <t xml:space="preserve">19.0451984405518</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5968112945557</t>
+    <t xml:space="preserve">19.5968132019043</t>
   </si>
   <si>
     <t xml:space="preserve">19.3548755645752</t>
@@ -2294,55 +2294,55 @@
     <t xml:space="preserve">18.9484233856201</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1032638549805</t>
+    <t xml:space="preserve">19.1032600402832</t>
   </si>
   <si>
     <t xml:space="preserve">18.4645519256592</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6581039428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5000381469727</t>
+    <t xml:space="preserve">18.6581001281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.500036239624</t>
   </si>
   <si>
     <t xml:space="preserve">19.6451969146729</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0806827545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3226203918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6129417419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5645561218262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0484275817871</t>
+    <t xml:space="preserve">20.0806846618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3226184844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6129398345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5645542144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0484256744385</t>
   </si>
   <si>
     <t xml:space="preserve">21.2903633117676</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7258491516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1935901641846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5806846618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8710079193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.532299041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3387489318848</t>
+    <t xml:space="preserve">21.72585105896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1935863494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5806865692139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8710117340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5323009490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3387470245361</t>
   </si>
   <si>
     <t xml:space="preserve">21.7742347717285</t>
@@ -2354,28 +2354,28 @@
     <t xml:space="preserve">22.9355297088623</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7903671264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.322624206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4194011688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0968208312988</t>
+    <t xml:space="preserve">22.7903652191162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3226280212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4193992614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0968189239502</t>
   </si>
   <si>
     <t xml:space="preserve">24.7258548736572</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4839191436768</t>
+    <t xml:space="preserve">24.4839172363281</t>
   </si>
   <si>
     <t xml:space="preserve">24.0484352111816</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7581081390381</t>
+    <t xml:space="preserve">23.7581119537354</t>
   </si>
   <si>
     <t xml:space="preserve">23.9516582489014</t>
@@ -2387,55 +2387,55 @@
     <t xml:space="preserve">22.741979598999</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0323028564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4677867889404</t>
+    <t xml:space="preserve">23.0323047637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4677886962891</t>
   </si>
   <si>
     <t xml:space="preserve">23.0806903839111</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8871402740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5484313964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8226203918457</t>
+    <t xml:space="preserve">22.8871421813965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5484294891357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8226222991943</t>
   </si>
   <si>
     <t xml:space="preserve">22.0645580291748</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2419776916504</t>
+    <t xml:space="preserve">21.241979598999</t>
   </si>
   <si>
     <t xml:space="preserve">21.6290740966797</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4677810668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3871383666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0968132019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4839134216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2097225189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9677848815918</t>
+    <t xml:space="preserve">20.4677791595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3871402740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0968151092529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4839115142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2097206115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9677867889404</t>
   </si>
   <si>
     <t xml:space="preserve">20.9516544342041</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1129455566406</t>
+    <t xml:space="preserve">22.1129474639893</t>
   </si>
   <si>
     <t xml:space="preserve">22.3548812866211</t>
@@ -2444,28 +2444,28 @@
     <t xml:space="preserve">21.9193954467773</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8387546539307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6452045440674</t>
+    <t xml:space="preserve">22.838752746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6452026367188</t>
   </si>
   <si>
     <t xml:space="preserve">24.4355316162109</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3387584686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2419834136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7419872283936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1774711608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0000514984131</t>
+    <t xml:space="preserve">24.3387565612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2419815063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7419853210449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.17746925354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0000534057617</t>
   </si>
   <si>
     <t xml:space="preserve">26.661340713501</t>
@@ -2480,16 +2480,16 @@
     <t xml:space="preserve">27.6774730682373</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6452159881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9032821655273</t>
+    <t xml:space="preserve">28.6452178955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.903284072876</t>
   </si>
   <si>
     <t xml:space="preserve">28.9355392456055</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7581214904785</t>
+    <t xml:space="preserve">29.7581233978271</t>
   </si>
   <si>
     <t xml:space="preserve">30.3871536254883</t>
@@ -2498,46 +2498,46 @@
     <t xml:space="preserve">30.9194164276123</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7419929504395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0323181152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5484466552734</t>
+    <t xml:space="preserve">31.7419986724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0323219299316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5484447479248</t>
   </si>
   <si>
     <t xml:space="preserve">32.0807113647461</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2581253051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1774787902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3226432800293</t>
+    <t xml:space="preserve">31.2581214904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1774826049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3226470947266</t>
   </si>
   <si>
     <t xml:space="preserve">33.2903861999512</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1936111450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8065185546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4839324951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7258758544922</t>
+    <t xml:space="preserve">33.1936149597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8065147399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4839363098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7258682250977</t>
   </si>
   <si>
     <t xml:space="preserve">34.1129722595215</t>
   </si>
   <si>
-    <t xml:space="preserve">34.742000579834</t>
+    <t xml:space="preserve">34.7420043945312</t>
   </si>
   <si>
     <t xml:space="preserve">34.5968399047852</t>
@@ -2546,10 +2546,10 @@
     <t xml:space="preserve">35.3710327148438</t>
   </si>
   <si>
-    <t xml:space="preserve">35.4678077697754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.8226470947266</t>
+    <t xml:space="preserve">35.4678115844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.8226547241211</t>
   </si>
   <si>
     <t xml:space="preserve">37.1613616943359</t>
@@ -2561,7 +2561,7 @@
     <t xml:space="preserve">34.3065185546875</t>
   </si>
   <si>
-    <t xml:space="preserve">32.564582824707</t>
+    <t xml:space="preserve">32.5645790100098</t>
   </si>
   <si>
     <t xml:space="preserve">32.6613540649414</t>
@@ -2588,19 +2588,19 @@
     <t xml:space="preserve">30.4839305877686</t>
   </si>
   <si>
-    <t xml:space="preserve">31.112964630127</t>
+    <t xml:space="preserve">31.1129627227783</t>
   </si>
   <si>
     <t xml:space="preserve">33.4355430603027</t>
   </si>
   <si>
-    <t xml:space="preserve">33.871036529541</t>
+    <t xml:space="preserve">33.8710327148438</t>
   </si>
   <si>
     <t xml:space="preserve">35.2742614746094</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6613616943359</t>
+    <t xml:space="preserve">35.6613578796387</t>
   </si>
   <si>
     <t xml:space="preserve">35.7097473144531</t>
@@ -2615,7 +2615,7 @@
     <t xml:space="preserve">36.9678153991699</t>
   </si>
   <si>
-    <t xml:space="preserve">35.9516830444336</t>
+    <t xml:space="preserve">35.9516868591309</t>
   </si>
   <si>
     <t xml:space="preserve">36.4355545043945</t>
@@ -2627,22 +2627,22 @@
     <t xml:space="preserve">34.9839401245117</t>
   </si>
   <si>
-    <t xml:space="preserve">36.6774864196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.0645904541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6452331542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.0323295593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6129760742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.7581405639648</t>
+    <t xml:space="preserve">36.677490234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.064582824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6452293395996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.0323333740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.612979888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.7581367492676</t>
   </si>
   <si>
     <t xml:space="preserve">39.8226585388184</t>
@@ -2651,7 +2651,7 @@
     <t xml:space="preserve">39.6774940490723</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5645904541016</t>
+    <t xml:space="preserve">38.5645942687988</t>
   </si>
   <si>
     <t xml:space="preserve">38.7097511291504</t>
@@ -2660,10 +2660,10 @@
     <t xml:space="preserve">39.6291084289551</t>
   </si>
   <si>
-    <t xml:space="preserve">40.4516868591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.1613655090332</t>
+    <t xml:space="preserve">40.4516944885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.1613693237305</t>
   </si>
   <si>
     <t xml:space="preserve">39.4355583190918</t>
@@ -2672,34 +2672,34 @@
     <t xml:space="preserve">40.2581367492676</t>
   </si>
   <si>
-    <t xml:space="preserve">44.0807304382324</t>
+    <t xml:space="preserve">44.0807266235352</t>
   </si>
   <si>
     <t xml:space="preserve">41.9033088684082</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0645942687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1775016784668</t>
+    <t xml:space="preserve">40.0645980834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1774978637695</t>
   </si>
   <si>
     <t xml:space="preserve">41.8549194335938</t>
   </si>
   <si>
-    <t xml:space="preserve">42.338794708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.048469543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.6291160583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.6129837036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.3871803283691</t>
+    <t xml:space="preserve">42.3387908935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.0484657287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.6291122436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.6129875183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.3871726989746</t>
   </si>
   <si>
     <t xml:space="preserve">43.5000801086426</t>
@@ -2714,13 +2714,13 @@
     <t xml:space="preserve">44.7581520080566</t>
   </si>
   <si>
-    <t xml:space="preserve">45.6775093078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.4194450378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.0000877380371</t>
+    <t xml:space="preserve">45.6775054931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.4194412231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.0000839233398</t>
   </si>
   <si>
     <t xml:space="preserve">46.0162162780762</t>
@@ -2735,10 +2735,10 @@
     <t xml:space="preserve">46.2581481933594</t>
   </si>
   <si>
-    <t xml:space="preserve">45.1452522277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.6129875183105</t>
+    <t xml:space="preserve">45.1452484130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.6129913330078</t>
   </si>
   <si>
     <t xml:space="preserve">44.5162162780762</t>
@@ -2750,10 +2750,10 @@
     <t xml:space="preserve">43.8387908935547</t>
   </si>
   <si>
-    <t xml:space="preserve">43.1613693237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.3065338134766</t>
+    <t xml:space="preserve">43.1613731384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.3065376281738</t>
   </si>
   <si>
     <t xml:space="preserve">43.2581481933594</t>
@@ -2762,28 +2762,28 @@
     <t xml:space="preserve">42.8710517883301</t>
   </si>
   <si>
-    <t xml:space="preserve">43.0645980834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.032341003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.4033050537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4355659484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8992881774902</t>
+    <t xml:space="preserve">43.0646018981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.0323448181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.4033088684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4355697631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8992919921875</t>
   </si>
   <si>
     <t xml:space="preserve">40.0436096191406</t>
   </si>
   <si>
-    <t xml:space="preserve">39.7994422912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4576110839844</t>
+    <t xml:space="preserve">39.7994384765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4576072692871</t>
   </si>
   <si>
     <t xml:space="preserve">40.0924415588379</t>
@@ -2792,10 +2792,10 @@
     <t xml:space="preserve">40.873779296875</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9947776794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.7761116027832</t>
+    <t xml:space="preserve">39.9947738647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.7761154174805</t>
   </si>
   <si>
     <t xml:space="preserve">40.6784477233887</t>
@@ -2804,7 +2804,7 @@
     <t xml:space="preserve">40.190113067627</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8971099853516</t>
+    <t xml:space="preserve">39.8971061706543</t>
   </si>
   <si>
     <t xml:space="preserve">39.6529388427734</t>
@@ -2813,10 +2813,10 @@
     <t xml:space="preserve">39.6041069030762</t>
   </si>
   <si>
-    <t xml:space="preserve">39.7506103515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2622718811035</t>
+    <t xml:space="preserve">39.7506065368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2622680664062</t>
   </si>
   <si>
     <t xml:space="preserve">40.2877769470215</t>
@@ -2828,13 +2828,13 @@
     <t xml:space="preserve">37.8949241638184</t>
   </si>
   <si>
-    <t xml:space="preserve">36.7229194641113</t>
+    <t xml:space="preserve">36.7229156494141</t>
   </si>
   <si>
     <t xml:space="preserve">37.6019248962402</t>
   </si>
   <si>
-    <t xml:space="preserve">38.0902633666992</t>
+    <t xml:space="preserve">38.090259552002</t>
   </si>
   <si>
     <t xml:space="preserve">39.5552749633789</t>
@@ -2843,37 +2843,37 @@
     <t xml:space="preserve">41.7039527893066</t>
   </si>
   <si>
-    <t xml:space="preserve">42.0946197509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.459789276123</t>
+    <t xml:space="preserve">42.0946235656738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4597854614258</t>
   </si>
   <si>
     <t xml:space="preserve">41.0691146850586</t>
   </si>
   <si>
-    <t xml:space="preserve">40.385440826416</t>
+    <t xml:space="preserve">40.3854446411133</t>
   </si>
   <si>
     <t xml:space="preserve">40.4342765808105</t>
   </si>
   <si>
-    <t xml:space="preserve">42.1922874450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.045783996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.9481201171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.4109535217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.7294654846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3664817810059</t>
+    <t xml:space="preserve">42.1922912597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.0457916259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.9481239318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4109573364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.7294616699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3664779663086</t>
   </si>
   <si>
     <t xml:space="preserve">45.4153137207031</t>
@@ -2882,7 +2882,7 @@
     <t xml:space="preserve">46.1966552734375</t>
   </si>
   <si>
-    <t xml:space="preserve">47.8569984436035</t>
+    <t xml:space="preserve">47.8569946289062</t>
   </si>
   <si>
     <t xml:space="preserve">47.3198280334473</t>
@@ -2897,13 +2897,13 @@
     <t xml:space="preserve">48.5895042419434</t>
   </si>
   <si>
-    <t xml:space="preserve">48.8336715698242</t>
+    <t xml:space="preserve">48.833667755127</t>
   </si>
   <si>
     <t xml:space="preserve">48.1988296508789</t>
   </si>
   <si>
-    <t xml:space="preserve">49.7126770019531</t>
+    <t xml:space="preserve">49.7126808166504</t>
   </si>
   <si>
     <t xml:space="preserve">49.9080085754395</t>
@@ -2921,7 +2921,7 @@
     <t xml:space="preserve">51.3730163574219</t>
   </si>
   <si>
-    <t xml:space="preserve">50.2986793518066</t>
+    <t xml:space="preserve">50.2986755371094</t>
   </si>
   <si>
     <t xml:space="preserve">50.591682434082</t>
@@ -2930,7 +2930,7 @@
     <t xml:space="preserve">50.4940147399902</t>
   </si>
   <si>
-    <t xml:space="preserve">51.2753486633301</t>
+    <t xml:space="preserve">51.2753524780273</t>
   </si>
   <si>
     <t xml:space="preserve">50.2010154724121</t>
@@ -2942,16 +2942,16 @@
     <t xml:space="preserve">50.9823532104492</t>
   </si>
   <si>
-    <t xml:space="preserve">51.8613586425781</t>
+    <t xml:space="preserve">51.8613548278809</t>
   </si>
   <si>
     <t xml:space="preserve">51.9590301513672</t>
   </si>
   <si>
-    <t xml:space="preserve">50.8846817016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2688102722168</t>
+    <t xml:space="preserve">50.8846855163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.2688140869141</t>
   </si>
   <si>
     <t xml:space="preserve">44.536304473877</t>
@@ -2963,16 +2963,16 @@
     <t xml:space="preserve">44.2433052062988</t>
   </si>
   <si>
-    <t xml:space="preserve">44.2921371459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.9269752502441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.0479698181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8037986755371</t>
+    <t xml:space="preserve">44.2921409606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.9269790649414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.047966003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8038024902344</t>
   </si>
   <si>
     <t xml:space="preserve">44.4386405944824</t>
@@ -2984,19 +2984,19 @@
     <t xml:space="preserve">44.1944694519043</t>
   </si>
   <si>
-    <t xml:space="preserve">41.2156181335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.9714508056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.7527847290039</t>
+    <t xml:space="preserve">41.2156219482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.9714469909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.7527885437012</t>
   </si>
   <si>
     <t xml:space="preserve">42.2899589538574</t>
   </si>
   <si>
-    <t xml:space="preserve">43.0712966918945</t>
+    <t xml:space="preserve">43.0712928771973</t>
   </si>
   <si>
     <t xml:space="preserve">43.2666320800781</t>
@@ -3005,70 +3005,70 @@
     <t xml:space="preserve">43.7061309814453</t>
   </si>
   <si>
-    <t xml:space="preserve">44.3409729003906</t>
+    <t xml:space="preserve">44.3409690856934</t>
   </si>
   <si>
     <t xml:space="preserve">45.4641456604004</t>
   </si>
   <si>
-    <t xml:space="preserve">46.0989875793457</t>
+    <t xml:space="preserve">46.0989837646484</t>
   </si>
   <si>
     <t xml:space="preserve">45.6594848632812</t>
   </si>
   <si>
-    <t xml:space="preserve">45.757152557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.7782974243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2644500732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.6806297302246</t>
+    <t xml:space="preserve">45.7571487426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.7782936096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2644538879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.6806259155273</t>
   </si>
   <si>
     <t xml:space="preserve">43.1201362609863</t>
   </si>
   <si>
-    <t xml:space="preserve">42.4364624023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.5086212158203</t>
+    <t xml:space="preserve">42.4364585876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.508617401123</t>
   </si>
   <si>
     <t xml:space="preserve">41.0202827453613</t>
   </si>
   <si>
-    <t xml:space="preserve">38.8715972900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.2367668151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0669364929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8482780456543</t>
+    <t xml:space="preserve">38.8716011047363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.2367630004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0669326782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.848274230957</t>
   </si>
   <si>
     <t xml:space="preserve">40.5319442749023</t>
   </si>
   <si>
-    <t xml:space="preserve">41.8504524230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1179504394531</t>
+    <t xml:space="preserve">41.850456237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1179466247559</t>
   </si>
   <si>
     <t xml:space="preserve">40.8249473571777</t>
   </si>
   <si>
-    <t xml:space="preserve">41.6551170349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.6062889099121</t>
+    <t xml:space="preserve">41.6551208496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.6062850952148</t>
   </si>
   <si>
     <t xml:space="preserve">42.485294342041</t>
@@ -3083,22 +3083,22 @@
     <t xml:space="preserve">41.362117767334</t>
   </si>
   <si>
-    <t xml:space="preserve">40.2389450073242</t>
+    <t xml:space="preserve">40.2389488220215</t>
   </si>
   <si>
     <t xml:space="preserve">40.6296119689941</t>
   </si>
   <si>
-    <t xml:space="preserve">42.8759651184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.4619636535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.999137878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.9226150512695</t>
+    <t xml:space="preserve">42.8759613037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.4619674682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.9991340637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.9226188659668</t>
   </si>
   <si>
     <t xml:space="preserve">39.1157684326172</t>
@@ -3122,34 +3122,34 @@
     <t xml:space="preserve">37.1135864257812</t>
   </si>
   <si>
-    <t xml:space="preserve">35.7950782775879</t>
+    <t xml:space="preserve">35.7950859069824</t>
   </si>
   <si>
     <t xml:space="preserve">34.7207374572754</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5997428894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.5275917053223</t>
+    <t xml:space="preserve">35.5997467041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.527587890625</t>
   </si>
   <si>
     <t xml:space="preserve">36.6252517700195</t>
   </si>
   <si>
-    <t xml:space="preserve">36.0880851745605</t>
+    <t xml:space="preserve">36.0880813598633</t>
   </si>
   <si>
     <t xml:space="preserve">36.1369209289551</t>
   </si>
   <si>
-    <t xml:space="preserve">35.453239440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5254020690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3810844421387</t>
+    <t xml:space="preserve">35.4532432556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5254058837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3810806274414</t>
   </si>
   <si>
     <t xml:space="preserve">35.3555755615234</t>
@@ -3170,10 +3170,10 @@
     <t xml:space="preserve">33.0115623474121</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3767242431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4510650634766</t>
+    <t xml:space="preserve">32.3767280578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4510612487793</t>
   </si>
   <si>
     <t xml:space="preserve">34.7695732116699</t>
@@ -3191,16 +3191,16 @@
     <t xml:space="preserve">31.4000511169434</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5975685119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9627265930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5232200622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4255523681641</t>
+    <t xml:space="preserve">33.5975646972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9627227783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5232238769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4255561828613</t>
   </si>
   <si>
     <t xml:space="preserve">32.6208915710449</t>
@@ -3215,10 +3215,10 @@
     <t xml:space="preserve">32.767391204834</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2144813537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0191459655762</t>
+    <t xml:space="preserve">31.2144794464111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0191478729248</t>
   </si>
   <si>
     <t xml:space="preserve">30.9019451141357</t>
@@ -3227,28 +3227,28 @@
     <t xml:space="preserve">29.6518058776855</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4722099304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2302207946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0739517211914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9372234344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3316860198975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1716156005859</t>
+    <t xml:space="preserve">30.4722118377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.230224609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0739555358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.937219619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3316841125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1716194152832</t>
   </si>
   <si>
     <t xml:space="preserve">31.3902816772461</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6637477874756</t>
+    <t xml:space="preserve">31.6637496948242</t>
   </si>
   <si>
     <t xml:space="preserve">29.8862056732178</t>
@@ -3257,10 +3257,10 @@
     <t xml:space="preserve">29.9643383026123</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3821277618408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4993286132812</t>
+    <t xml:space="preserve">28.3821258544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4993305206299</t>
   </si>
   <si>
     <t xml:space="preserve">29.2025337219238</t>
@@ -3272,7 +3272,7 @@
     <t xml:space="preserve">28.9290676116943</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0853328704834</t>
+    <t xml:space="preserve">29.085334777832</t>
   </si>
   <si>
     <t xml:space="preserve">28.3039932250977</t>
@@ -3293,7 +3293,7 @@
     <t xml:space="preserve">28.2258605957031</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5579299926758</t>
+    <t xml:space="preserve">28.5579280853271</t>
   </si>
   <si>
     <t xml:space="preserve">28.1816444396973</t>
@@ -28871,7 +28871,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G898" t="s">
-        <v>593</v>
+        <v>403</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -28897,7 +28897,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G899" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -28923,7 +28923,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G900" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -28975,7 +28975,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G902" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -29027,7 +29027,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G904" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -29053,7 +29053,7 @@
         <v>15.5</v>
       </c>
       <c r="G905" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -29079,7 +29079,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G906" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -29105,7 +29105,7 @@
         <v>15.5</v>
       </c>
       <c r="G907" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -29183,7 +29183,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G910" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -29261,7 +29261,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G913" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -29313,7 +29313,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G915" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -29339,7 +29339,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G916" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -29365,7 +29365,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G917" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -29391,7 +29391,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G918" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -29417,7 +29417,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G919" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -29443,7 +29443,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G920" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -29469,7 +29469,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G921" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -29495,7 +29495,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G922" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -29521,7 +29521,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G923" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -29547,7 +29547,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G924" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -29573,7 +29573,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G925" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -29599,7 +29599,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G926" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -29625,7 +29625,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G927" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -29651,7 +29651,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G928" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -29703,7 +29703,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G930" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -29755,7 +29755,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G932" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -29807,7 +29807,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G934" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -29833,7 +29833,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G935" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -29859,7 +29859,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G936" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -29885,7 +29885,7 @@
         <v>16</v>
       </c>
       <c r="G937" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -29911,7 +29911,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G938" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -29937,7 +29937,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G939" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -29963,7 +29963,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G940" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -29989,7 +29989,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G941" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -30015,7 +30015,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G942" t="s">
-        <v>553</v>
+        <v>618</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -30405,7 +30405,7 @@
         <v>16</v>
       </c>
       <c r="G957" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -30535,7 +30535,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G962" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -30665,7 +30665,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G967" t="s">
-        <v>553</v>
+        <v>618</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -33577,7 +33577,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G1079" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -33629,7 +33629,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G1081" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -33915,7 +33915,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G1092" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -34071,7 +34071,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1098" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -34149,7 +34149,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G1101" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -34305,7 +34305,7 @@
         <v>16</v>
       </c>
       <c r="G1107" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -34331,7 +34331,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1108" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -34383,7 +34383,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1110" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -34409,7 +34409,7 @@
         <v>16</v>
       </c>
       <c r="G1111" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -34513,7 +34513,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G1115" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -71571,7 +71571,7 @@
     </row>
     <row r="2541">
       <c r="A2541" s="1" t="n">
-        <v>46021.6911458333</v>
+        <v>46021.3333333333</v>
       </c>
       <c r="B2541" t="n">
         <v>30082</v>

--- a/data/MOL.MI.xlsx
+++ b/data/MOL.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85066175460815</t>
+    <t xml:space="preserve">6.850661277771</t>
   </si>
   <si>
     <t xml:space="preserve">MOL.MI</t>
@@ -47,22 +47,22 @@
     <t xml:space="preserve">6.75772666931152</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66036558151245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77100229263306</t>
+    <t xml:space="preserve">6.66036653518677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77100276947021</t>
   </si>
   <si>
     <t xml:space="preserve">6.63823795318604</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72674703598022</t>
+    <t xml:space="preserve">6.72674751281738</t>
   </si>
   <si>
     <t xml:space="preserve">6.81525754928589</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54972791671753</t>
+    <t xml:space="preserve">6.54972839355469</t>
   </si>
   <si>
     <t xml:space="preserve">6.31960248947144</t>
@@ -74,46 +74,46 @@
     <t xml:space="preserve">6.35058116912842</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2399435043335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55857944488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46121835708618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89475536346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52317523956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65594005584717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76215124130249</t>
+    <t xml:space="preserve">6.23994398117065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55857849121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4612193107605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89475584030151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52317571640015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65593957901001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76215219497681</t>
   </si>
   <si>
     <t xml:space="preserve">6.66479110717773</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69134378433228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68249273300171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01866912841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89918041229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28419828414917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06292486190796</t>
+    <t xml:space="preserve">6.69134426116943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68249368667603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01866960525513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8991813659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28419733047485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06292390823364</t>
   </si>
   <si>
     <t xml:space="preserve">6.25321960449219</t>
@@ -122,16 +122,16 @@
     <t xml:space="preserve">6.39926147460938</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34173059463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5098991394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33287906646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42581415176392</t>
+    <t xml:space="preserve">6.34172964096069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50989818572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33287954330444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42581462860107</t>
   </si>
   <si>
     <t xml:space="preserve">6.39041042327881</t>
@@ -143,49 +143,49 @@
     <t xml:space="preserve">6.40811252593994</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35500621795654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63381290435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43466567993164</t>
+    <t xml:space="preserve">6.3550066947937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63381147384644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43466472625732</t>
   </si>
   <si>
     <t xml:space="preserve">6.22666788101196</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24436902999878</t>
+    <t xml:space="preserve">6.24436950683594</t>
   </si>
   <si>
     <t xml:space="preserve">6.27534818649292</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26649618148804</t>
+    <t xml:space="preserve">6.2664966583252</t>
   </si>
   <si>
     <t xml:space="preserve">6.62938690185547</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43909120559692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41253805160522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45236682891846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45679330825806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36828327178955</t>
+    <t xml:space="preserve">6.43909072875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41253757476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45236730575562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4567928314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36828422546387</t>
   </si>
   <si>
     <t xml:space="preserve">6.19568872451782</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06734991073608</t>
+    <t xml:space="preserve">6.06734895706177</t>
   </si>
   <si>
     <t xml:space="preserve">6.28862428665161</t>
@@ -194,13 +194,13 @@
     <t xml:space="preserve">6.20453977584839</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29305028915405</t>
+    <t xml:space="preserve">6.29304981231689</t>
   </si>
   <si>
     <t xml:space="preserve">6.24879455566406</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22224235534668</t>
+    <t xml:space="preserve">6.22224187850952</t>
   </si>
   <si>
     <t xml:space="preserve">6.25764608383179</t>
@@ -215,7 +215,7 @@
     <t xml:space="preserve">6.58955764770508</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47892045974731</t>
+    <t xml:space="preserve">6.47891998291016</t>
   </si>
   <si>
     <t xml:space="preserve">6.49662208557129</t>
@@ -224,16 +224,16 @@
     <t xml:space="preserve">6.42138910293579</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63348913192749</t>
+    <t xml:space="preserve">6.63348960876465</t>
   </si>
   <si>
     <t xml:space="preserve">6.45273971557617</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54311418533325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44370222091675</t>
+    <t xml:space="preserve">6.54311466217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44370269775391</t>
   </si>
   <si>
     <t xml:space="preserve">6.50696516036987</t>
@@ -242,34 +242,34 @@
     <t xml:space="preserve">6.55667114257812</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3668851852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61993312835693</t>
+    <t xml:space="preserve">6.36688375473022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61993265151978</t>
   </si>
   <si>
     <t xml:space="preserve">6.69223308563232</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59733963012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68319463729858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70578908920288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75097560882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85038805007935</t>
+    <t xml:space="preserve">6.59733915328979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68319511413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70578861236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75097703933716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85038757324219</t>
   </si>
   <si>
     <t xml:space="preserve">6.94528150558472</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98594951629639</t>
+    <t xml:space="preserve">6.9859504699707</t>
   </si>
   <si>
     <t xml:space="preserve">7.10343647003174</t>
@@ -287,55 +287,55 @@
     <t xml:space="preserve">7.3022608757019</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37907934188843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25707387924194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22996044158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22544193267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19833040237427</t>
+    <t xml:space="preserve">7.37907886505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25707292556763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22996091842651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22544145584106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19832992553711</t>
   </si>
   <si>
     <t xml:space="preserve">7.09439897537231</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13958787918091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00402498245239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08084344863892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95883798599243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84135103225708</t>
+    <t xml:space="preserve">7.13958644866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00402545928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08084297180176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95883703231812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84135150909424</t>
   </si>
   <si>
     <t xml:space="preserve">7.11699295043945</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16669845581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31129884719849</t>
+    <t xml:space="preserve">7.16669893264771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31129789352417</t>
   </si>
   <si>
     <t xml:space="preserve">7.32485485076904</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99950551986694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73290109634399</t>
+    <t xml:space="preserve">6.99950647354126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73290157318115</t>
   </si>
   <si>
     <t xml:space="preserve">7.08988046646118</t>
@@ -344,49 +344,49 @@
     <t xml:space="preserve">7.18477344512939</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85942554473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67867612838745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49792671203613</t>
+    <t xml:space="preserve">6.85942649841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67867660522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49792766571045</t>
   </si>
   <si>
     <t xml:space="preserve">6.57022762298584</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57926559448242</t>
+    <t xml:space="preserve">6.57926511764526</t>
   </si>
   <si>
     <t xml:space="preserve">6.41658973693848</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74645709991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6515645980835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55215311050415</t>
+    <t xml:space="preserve">6.74645757675171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65156412124634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55215215682983</t>
   </si>
   <si>
     <t xml:space="preserve">6.46177816390991</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75549507141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56570816040039</t>
+    <t xml:space="preserve">6.75549459457397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56570863723755</t>
   </si>
   <si>
     <t xml:space="preserve">6.77808856964111</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71030807495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48888969421387</t>
+    <t xml:space="preserve">6.71030759811401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48888921737671</t>
   </si>
   <si>
     <t xml:space="preserve">6.53859567642212</t>
@@ -395,28 +395,28 @@
     <t xml:space="preserve">6.66060161590576</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68771409988403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76001358032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87750101089478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70127058029175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78712606430054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79616403579712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81423759460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81875658035278</t>
+    <t xml:space="preserve">6.68771457672119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76001405715942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87750053405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70127010345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7871265411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79616355895996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81423854827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8187575340271</t>
   </si>
   <si>
     <t xml:space="preserve">6.82327651977539</t>
@@ -425,94 +425,94 @@
     <t xml:space="preserve">6.80520153045654</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92268753051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90461254119873</t>
+    <t xml:space="preserve">6.92268800735474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90461349487305</t>
   </si>
   <si>
     <t xml:space="preserve">6.86846303939819</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98143100738525</t>
+    <t xml:space="preserve">6.98143148422241</t>
   </si>
   <si>
     <t xml:space="preserve">7.17573595046997</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01306247711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97691249847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64252710342407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6967511177063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88653802871704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.931725025177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02209949493408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99046897888184</t>
+    <t xml:space="preserve">7.01306295394897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97691297531128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64252758026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69675159454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88653755187988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93172550201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02209997177124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99046945571899</t>
   </si>
   <si>
     <t xml:space="preserve">7.19381189346313</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05824995040894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04921197891235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06728744506836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1486234664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08536195755005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06276798248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15766191482544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21188640594482</t>
+    <t xml:space="preserve">7.05824899673462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04921245574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06728649139404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14862394332886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08536243438721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06276845932007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1576623916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21188545227051</t>
   </si>
   <si>
     <t xml:space="preserve">7.38359785079956</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22092342376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24803590774536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18929290771484</t>
+    <t xml:space="preserve">7.22092390060425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24803638458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18929243087769</t>
   </si>
   <si>
     <t xml:space="preserve">7.35648584365845</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37004137039185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88201856613159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0356559753418</t>
+    <t xml:space="preserve">7.370041847229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88201951980591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03565549850464</t>
   </si>
   <si>
     <t xml:space="preserve">7.18025541305542</t>
@@ -524,40 +524,40 @@
     <t xml:space="preserve">7.5191593170166</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47849035263062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50108575820923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41070938110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27514839172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60953378677368</t>
+    <t xml:space="preserve">7.47849082946777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50108480453491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41071081161499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27514886856079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60953426361084</t>
   </si>
   <si>
     <t xml:space="preserve">7.66375875473022</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72702169418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68183469772339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67731523513794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63664627075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77220916748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97103309631348</t>
+    <t xml:space="preserve">7.72701930999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68183422088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6773157119751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63664579391479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77220869064331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97103214263916</t>
   </si>
   <si>
     <t xml:space="preserve">8.34156799316406</t>
@@ -575,25 +575,25 @@
     <t xml:space="preserve">8.37771797180176</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40935039520264</t>
+    <t xml:space="preserve">8.409348487854</t>
   </si>
   <si>
     <t xml:space="preserve">8.35964202880859</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22408008575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24215507507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33704948425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32801246643066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3234920501709</t>
+    <t xml:space="preserve">8.22407913208008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24215602874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33704853057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32801055908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32349395751953</t>
   </si>
   <si>
     <t xml:space="preserve">8.36416149139404</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">8.37319850921631</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46809101104736</t>
+    <t xml:space="preserve">8.46809387207031</t>
   </si>
   <si>
     <t xml:space="preserve">8.30541801452637</t>
@@ -614,94 +614,94 @@
     <t xml:space="preserve">8.09755516052246</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26926898956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20600605010986</t>
+    <t xml:space="preserve">8.26926803588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20600509643555</t>
   </si>
   <si>
     <t xml:space="preserve">8.07496452331543</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11111164093018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28282451629639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2963809967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40483093261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48164749145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4229040145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22859859466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2737865447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02977561950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13370609283447</t>
+    <t xml:space="preserve">8.11111450195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2828254699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29638195037842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40482997894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48164844512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42290496826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22859954833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27378559112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02977657318115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13370704650879</t>
   </si>
   <si>
     <t xml:space="preserve">8.27830600738525</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43194198608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6940279006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57969760894775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25435066223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21819877624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01937580108643</t>
+    <t xml:space="preserve">8.4319429397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69402694702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57969856262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25434970855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21820068359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01937675476074</t>
   </si>
   <si>
     <t xml:space="preserve">9.16397571563721</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2001256942749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20916080474854</t>
+    <t xml:space="preserve">9.20012474060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20916271209717</t>
   </si>
   <si>
     <t xml:space="preserve">9.22723770141602</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94707679748535</t>
+    <t xml:space="preserve">8.94707775115967</t>
   </si>
   <si>
     <t xml:space="preserve">9.03745174407959</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12782669067383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35376358032227</t>
+    <t xml:space="preserve">9.12782573699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35376262664795</t>
   </si>
   <si>
     <t xml:space="preserve">9.55258655548096</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47124767303467</t>
+    <t xml:space="preserve">9.47124862670898</t>
   </si>
   <si>
     <t xml:space="preserve">9.80563545227051</t>
@@ -710,7 +710,7 @@
     <t xml:space="preserve">9.89600944519043</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2123193740845</t>
+    <t xml:space="preserve">10.2123203277588</t>
   </si>
   <si>
     <t xml:space="preserve">9.94119548797607</t>
@@ -719,151 +719,154 @@
     <t xml:space="preserve">10.4472951889038</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8449430465698</t>
+    <t xml:space="preserve">10.8449420928955</t>
   </si>
   <si>
     <t xml:space="preserve">10.8087902069092</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9082040786743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9353170394897</t>
+    <t xml:space="preserve">10.908203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9353151321411</t>
   </si>
   <si>
     <t xml:space="preserve">10.7364940643311</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7093801498413</t>
+    <t xml:space="preserve">10.7093820571899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.754566192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4764318466187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.226110458374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0128736495972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3837194442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4300765991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2817363739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4022626876831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5135173797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4949731826782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5413303375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7452955245972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0790596008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.774395942688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5889739990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2181262969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3015661239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0976009368896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1439571380615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0327024459839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8287363052368</t>
   </si>
   <si>
     <t xml:space="preserve">10.7545671463013</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4764318466187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.226110458374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0128717422485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3837203979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4300756454468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2817373275757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4022617340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5135173797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4949741363525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5413293838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7452964782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0790576934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7743978500366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5889739990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2181272506714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3015661239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0975999832153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1439571380615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0327024459839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8287363052368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7360258102417</t>
+    <t xml:space="preserve">10.7360239028931</t>
   </si>
   <si>
     <t xml:space="preserve">10.986346244812</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8658208847046</t>
+    <t xml:space="preserve">10.8658218383789</t>
   </si>
   <si>
     <t xml:space="preserve">10.5691432952881</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1254148483276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0605173110962</t>
+    <t xml:space="preserve">11.1254138946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0605163574219</t>
   </si>
   <si>
     <t xml:space="preserve">11.4869909286499</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0697870254517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9399900436401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4499063491821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4035501480103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7094993591309</t>
+    <t xml:space="preserve">11.069787979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9399909973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4499073028564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4035491943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7094984054565</t>
   </si>
   <si>
     <t xml:space="preserve">12.0988883972168</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3213958740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8949222564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5160913467407</t>
+    <t xml:space="preserve">12.3213968276978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.894923210144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.516092300415</t>
   </si>
   <si>
     <t xml:space="preserve">12.5253620147705</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6737003326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7478704452515</t>
+    <t xml:space="preserve">12.6737012863159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7478723526001</t>
   </si>
   <si>
     <t xml:space="preserve">12.5346336364746</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7942276000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7293281555176</t>
+    <t xml:space="preserve">12.7942266464233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7293300628662</t>
   </si>
   <si>
     <t xml:space="preserve">12.5439052581787</t>
@@ -872,31 +875,31 @@
     <t xml:space="preserve">12.5809879302979</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5624475479126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4697360992432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4975490570068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4882774353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6829738616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6273460388184</t>
+    <t xml:space="preserve">12.5624485015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4697341918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4975481033325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4882793426514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6829719543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.627345085144</t>
   </si>
   <si>
     <t xml:space="preserve">12.5531759262085</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1823282241821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3955659866333</t>
+    <t xml:space="preserve">12.1823301315308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3955640792847</t>
   </si>
   <si>
     <t xml:space="preserve">12.4233779907227</t>
@@ -905,34 +908,34 @@
     <t xml:space="preserve">12.2935838699341</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3677520751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8856506347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2843112945557</t>
+    <t xml:space="preserve">12.367751121521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8856515884399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2843132019043</t>
   </si>
   <si>
     <t xml:space="preserve">12.1730575561523</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0525321960449</t>
+    <t xml:space="preserve">12.0525331497192</t>
   </si>
   <si>
     <t xml:space="preserve">11.9505491256714</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3121252059937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2657680511475</t>
+    <t xml:space="preserve">12.312126159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2657690048218</t>
   </si>
   <si>
     <t xml:space="preserve">11.9412775039673</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9598207473755</t>
+    <t xml:space="preserve">11.9598188400269</t>
   </si>
   <si>
     <t xml:space="preserve">12.3306674957275</t>
@@ -941,10 +944,10 @@
     <t xml:space="preserve">12.4419212341309</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3492078781128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.377025604248</t>
+    <t xml:space="preserve">12.3492097854614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3770236968994</t>
   </si>
   <si>
     <t xml:space="preserve">12.1545152664185</t>
@@ -959,97 +962,97 @@
     <t xml:space="preserve">12.451192855835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2008714675903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4326505661011</t>
+    <t xml:space="preserve">12.200870513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4326496124268</t>
   </si>
   <si>
     <t xml:space="preserve">12.3028545379639</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2564973831177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.061803817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0247163772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4406328201294</t>
+    <t xml:space="preserve">12.2565002441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0618028640747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0247201919556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4406337738037</t>
   </si>
   <si>
     <t xml:space="preserve">11.6353302001953</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7929410934448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.663143157959</t>
+    <t xml:space="preserve">11.7929391860962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6631412506104</t>
   </si>
   <si>
     <t xml:space="preserve">11.6816854476929</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7465829849243</t>
+    <t xml:space="preserve">11.7465839385986</t>
   </si>
   <si>
     <t xml:space="preserve">11.9227352142334</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8207540512085</t>
+    <t xml:space="preserve">11.8207530975342</t>
   </si>
   <si>
     <t xml:space="preserve">11.8671092987061</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7373113632202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2286853790283</t>
+    <t xml:space="preserve">11.7373123168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.228684425354</t>
   </si>
   <si>
     <t xml:space="preserve">12.1915988922119</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7651243209839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7187690734863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1903104782104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2922973632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1624994277954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5426187515259</t>
+    <t xml:space="preserve">11.7651262283325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7187700271606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1903123855591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2922954559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1624975204468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5426158905029</t>
   </si>
   <si>
     <t xml:space="preserve">11.4684476852417</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5982446670532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5797023773193</t>
+    <t xml:space="preserve">11.5982437133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5797033309937</t>
   </si>
   <si>
     <t xml:space="preserve">11.4962615966797</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6724138259888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8578367233276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.145245552063</t>
+    <t xml:space="preserve">11.6724128723145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8578386306763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1452436447144</t>
   </si>
   <si>
     <t xml:space="preserve">12.006175994873</t>
@@ -1058,22 +1061,22 @@
     <t xml:space="preserve">11.9134654998779</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9240217208862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.925311088562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1107349395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0921926498413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9438524246216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9994792938232</t>
+    <t xml:space="preserve">12.9240226745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9253120422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1107339859009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0921907424927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9438514709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9994802474976</t>
   </si>
   <si>
     <t xml:space="preserve">14.629919052124</t>
@@ -1082,37 +1085,37 @@
     <t xml:space="preserve">13.9067678451538</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6286334991455</t>
+    <t xml:space="preserve">13.6286315917969</t>
   </si>
   <si>
     <t xml:space="preserve">14.2034454345703</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0180225372314</t>
+    <t xml:space="preserve">14.0180215835571</t>
   </si>
   <si>
     <t xml:space="preserve">13.7028007507324</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3888692855835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5186653137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5742931365967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4815816879272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1849040985107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8325986862183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9981937408447</t>
+    <t xml:space="preserve">14.3888702392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.518666267395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.574294090271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4815797805786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1849031448364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8325977325439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.998194694519</t>
   </si>
   <si>
     <t xml:space="preserve">12.7756843566895</t>
@@ -1121,19 +1124,19 @@
     <t xml:space="preserve">13.3690395355225</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0352764129639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7385988235474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9796504974365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5173778533936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3134136199951</t>
+    <t xml:space="preserve">13.0352773666382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7385997772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9796514511108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5173788070679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3134126663208</t>
   </si>
   <si>
     <t xml:space="preserve">12.6644296646118</t>
@@ -1142,34 +1145,34 @@
     <t xml:space="preserve">12.1081590652466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0154476165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8300256729126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.590259552002</t>
+    <t xml:space="preserve">12.0154485702515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8300247192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5902605056763</t>
   </si>
   <si>
     <t xml:space="preserve">12.7200574874878</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6088027954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1637859344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.033989906311</t>
+    <t xml:space="preserve">12.6088037490845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1637849807739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0339879989624</t>
   </si>
   <si>
     <t xml:space="preserve">12.0710754394531</t>
   </si>
   <si>
-    <t xml:space="preserve">11.607515335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4604644775391</t>
+    <t xml:space="preserve">11.6075162887573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4604635238647</t>
   </si>
   <si>
     <t xml:space="preserve">11.8114814758301</t>
@@ -1178,67 +1181,67 @@
     <t xml:space="preserve">11.8485670089722</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2379550933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3862943649292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3504972457886</t>
+    <t xml:space="preserve">12.2379560470581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3862953186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3504962921143</t>
   </si>
   <si>
     <t xml:space="preserve">13.5359220504761</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7213449478149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2590732574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9080543518066</t>
+    <t xml:space="preserve">13.7213439941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2590742111206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9080562591553</t>
   </si>
   <si>
     <t xml:space="preserve">14.7782592773438</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7411727905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7968015670776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0235710144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.684986114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4015216827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2314462661743</t>
+    <t xml:space="preserve">14.7411737442017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.796802520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.02357006073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6849870681763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4015226364136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2314443588257</t>
   </si>
   <si>
     <t xml:space="preserve">15.080265045166</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1180591583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1747522354126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.307035446167</t>
+    <t xml:space="preserve">15.1180601119995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1747512817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3070363998413</t>
   </si>
   <si>
     <t xml:space="preserve">14.13538646698</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8141269683838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2660970687866</t>
+    <t xml:space="preserve">13.8141279220581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2660980224609</t>
   </si>
   <si>
     <t xml:space="preserve">13.6062536239624</t>
@@ -1247,19 +1250,19 @@
     <t xml:space="preserve">13.6818437576294</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0771226882935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9448385238647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1149168014526</t>
+    <t xml:space="preserve">13.0771207809448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9448375701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.114917755127</t>
   </si>
   <si>
     <t xml:space="preserve">12.8881464004517</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0944490432739</t>
+    <t xml:space="preserve">12.0944480895996</t>
   </si>
   <si>
     <t xml:space="preserve">12.5479898452759</t>
@@ -1268,13 +1271,13 @@
     <t xml:space="preserve">13.0015316009521</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6235799789429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6991710662842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7558622360229</t>
+    <t xml:space="preserve">12.6235809326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6991701126099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7558631896973</t>
   </si>
   <si>
     <t xml:space="preserve">12.8692483901978</t>
@@ -1283,61 +1286,61 @@
     <t xml:space="preserve">12.3401165008545</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7369651794434</t>
+    <t xml:space="preserve">12.736964225769</t>
   </si>
   <si>
     <t xml:space="preserve">12.7180681228638</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7747611999512</t>
+    <t xml:space="preserve">12.7747602462769</t>
   </si>
   <si>
     <t xml:space="preserve">12.2645254135132</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7385377883911</t>
+    <t xml:space="preserve">13.7385368347168</t>
   </si>
   <si>
     <t xml:space="preserve">13.776330947876</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9653072357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8708200454712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0786943435669</t>
+    <t xml:space="preserve">13.9653081893921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8708190917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0786914825439</t>
   </si>
   <si>
     <t xml:space="preserve">13.625150680542</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5873575210571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4172773361206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4550733566284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4361743927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.247200012207</t>
+    <t xml:space="preserve">13.5873556137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4172782897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4550714492798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4361753463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2472009658813</t>
   </si>
   <si>
     <t xml:space="preserve">13.1338138580322</t>
   </si>
   <si>
-    <t xml:space="preserve">13.322790145874</t>
+    <t xml:space="preserve">13.3227891921997</t>
   </si>
   <si>
     <t xml:space="preserve">13.473970413208</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2094058990479</t>
+    <t xml:space="preserve">13.2094039916992</t>
   </si>
   <si>
     <t xml:space="preserve">13.3605861663818</t>
@@ -1346,13 +1349,13 @@
     <t xml:space="preserve">12.5668869018555</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5101928710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2834224700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.680272102356</t>
+    <t xml:space="preserve">12.5101938247681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2834243774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6802730560303</t>
   </si>
   <si>
     <t xml:space="preserve">13.0393266677856</t>
@@ -1361,10 +1364,10 @@
     <t xml:space="preserve">12.9826335906982</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8125553131104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.963737487793</t>
+    <t xml:space="preserve">12.8125562667847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9637365341187</t>
   </si>
   <si>
     <t xml:space="preserve">13.7952299118042</t>
@@ -1373,37 +1376,37 @@
     <t xml:space="preserve">14.1164884567261</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2676696777344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3054628372192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0597953796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7007417678833</t>
+    <t xml:space="preserve">14.2676687240601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3054656982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.059796333313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.700740814209</t>
   </si>
   <si>
     <t xml:space="preserve">13.4928684234619</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7574348449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5495615005493</t>
+    <t xml:space="preserve">13.7574367523193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5495624542236</t>
   </si>
   <si>
     <t xml:space="preserve">14.1731805801392</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9290838241577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4960107803345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2692413330078</t>
+    <t xml:space="preserve">14.929084777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4960098266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2692403793335</t>
   </si>
   <si>
     <t xml:space="preserve">15.155855178833</t>
@@ -1412,31 +1415,31 @@
     <t xml:space="preserve">16.5353775024414</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7054576873779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.913330078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6298656463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2330150604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9117555618286</t>
+    <t xml:space="preserve">16.7054557800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9133319854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6298675537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2330169677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9117565155029</t>
   </si>
   <si>
     <t xml:space="preserve">15.5904989242554</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5149097442627</t>
+    <t xml:space="preserve">15.5149087905884</t>
   </si>
   <si>
     <t xml:space="preserve">15.004674911499</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2125482559204</t>
+    <t xml:space="preserve">15.2125473022461</t>
   </si>
   <si>
     <t xml:space="preserve">14.3810548782349</t>
@@ -1445,49 +1448,49 @@
     <t xml:space="preserve">14.6078252792358</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4377460479736</t>
+    <t xml:space="preserve">14.4377470016479</t>
   </si>
   <si>
     <t xml:space="preserve">14.6456203460693</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2487716674805</t>
+    <t xml:space="preserve">14.2487707138062</t>
   </si>
   <si>
     <t xml:space="preserve">14.1920795440674</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8897180557251</t>
+    <t xml:space="preserve">13.8897171020508</t>
   </si>
   <si>
     <t xml:space="preserve">13.5306634902954</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8519220352173</t>
+    <t xml:space="preserve">13.851921081543</t>
   </si>
   <si>
     <t xml:space="preserve">14.0220003128052</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8723917007446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4755420684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4188508987427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5527029037476</t>
+    <t xml:space="preserve">14.8723907470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4755411148071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.418848991394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5527048110962</t>
   </si>
   <si>
     <t xml:space="preserve">14.9668788909912</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0818347930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0629386901855</t>
+    <t xml:space="preserve">16.0818367004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0629405975342</t>
   </si>
   <si>
     <t xml:space="preserve">16.2519130706787</t>
@@ -1499,43 +1502,43 @@
     <t xml:space="preserve">15.8739614486694</t>
   </si>
   <si>
-    <t xml:space="preserve">15.458215713501</t>
+    <t xml:space="preserve">15.4582166671753</t>
   </si>
   <si>
     <t xml:space="preserve">16.0251426696777</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3464012145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1007328033447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.327507019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6471929550171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7983703613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9306554794312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0613660812378</t>
+    <t xml:space="preserve">16.346399307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1007347106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3275051116943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6471910476685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7983751296997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9306564331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0613670349121</t>
   </si>
   <si>
     <t xml:space="preserve">15.8550672531128</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4771146774292</t>
+    <t xml:space="preserve">15.4771118164062</t>
   </si>
   <si>
     <t xml:space="preserve">14.7401084899902</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9101848602295</t>
+    <t xml:space="preserve">14.9101867675781</t>
   </si>
   <si>
     <t xml:space="preserve">14.5511322021484</t>
@@ -1547,139 +1550,139 @@
     <t xml:space="preserve">14.9857769012451</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5338068008423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7416801452637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0424699783325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4204196929932</t>
+    <t xml:space="preserve">15.5338077545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.741681098938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0424690246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4204187393188</t>
   </si>
   <si>
     <t xml:space="preserve">15.7605781555176</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6282930374146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.892861366272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9684505462646</t>
+    <t xml:space="preserve">15.6282949447632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8928604125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9684467315674</t>
   </si>
   <si>
     <t xml:space="preserve">16.0062465667725</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9873485565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6093950271606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6834144592285</t>
+    <t xml:space="preserve">15.9873456954956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6093978881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6834154129028</t>
   </si>
   <si>
     <t xml:space="preserve">14.6267213821411</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8534936904907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1936492919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0991630554199</t>
+    <t xml:space="preserve">14.853494644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1936511993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0991611480713</t>
   </si>
   <si>
     <t xml:space="preserve">15.2881383895874</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1952228546143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0078201293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2345867156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2534847259521</t>
+    <t xml:space="preserve">16.195219039917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0078163146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2345886230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2534866333008</t>
   </si>
   <si>
     <t xml:space="preserve">17.2912788391113</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1023025512695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.064510345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0471820831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4046649932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3479709625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3668689727783</t>
+    <t xml:space="preserve">17.1023063659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0645084381104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0471839904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4046669006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3479747772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.366870880127</t>
   </si>
   <si>
     <t xml:space="preserve">17.499153137207</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0456123352051</t>
+    <t xml:space="preserve">17.0456142425537</t>
   </si>
   <si>
     <t xml:space="preserve">17.3857688903809</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4424591064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8582057952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8204135894775</t>
+    <t xml:space="preserve">17.4424610137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8582077026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8204154968262</t>
   </si>
   <si>
     <t xml:space="preserve">17.5558471679688</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3290748596191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.140100479126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5731735229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5920677185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2897052764893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8566360473633</t>
+    <t xml:space="preserve">17.3290767669678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1400966644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5731754302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5920696258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2897071838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8566379547119</t>
   </si>
   <si>
     <t xml:space="preserve">16.1574287414551</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5805931091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5421257019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3882465362549</t>
+    <t xml:space="preserve">16.5805969238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5421276092529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3882503509521</t>
   </si>
   <si>
     <t xml:space="preserve">16.4459533691406</t>
@@ -1688,19 +1691,19 @@
     <t xml:space="preserve">16.2343654632568</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0035457611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9843130111694</t>
+    <t xml:space="preserve">16.0035438537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9843111038208</t>
   </si>
   <si>
     <t xml:space="preserve">16.6767730712891</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8114185333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8306522369385</t>
+    <t xml:space="preserve">16.8114147186279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8306503295898</t>
   </si>
   <si>
     <t xml:space="preserve">16.7537117004395</t>
@@ -1709,40 +1712,40 @@
     <t xml:space="preserve">16.6383018493652</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4267139434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5228900909424</t>
+    <t xml:space="preserve">16.4267158508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.522891998291</t>
   </si>
   <si>
     <t xml:space="preserve">15.945839881897</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4651870727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9650754928589</t>
+    <t xml:space="preserve">16.4651851654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9650764465332</t>
   </si>
   <si>
     <t xml:space="preserve">16.0227813720703</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8689002990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7342548370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6573171615601</t>
+    <t xml:space="preserve">15.8689022064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7342538833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6573152542114</t>
   </si>
   <si>
     <t xml:space="preserve">15.426495552063</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3687906265259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3110857009888</t>
+    <t xml:space="preserve">15.3687896728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3110837936401</t>
   </si>
   <si>
     <t xml:space="preserve">14.9840898513794</t>
@@ -1751,19 +1754,19 @@
     <t xml:space="preserve">15.1956748962402</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2341442108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1379699707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0994987487793</t>
+    <t xml:space="preserve">15.2341451644897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1379690170288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0994997024536</t>
   </si>
   <si>
     <t xml:space="preserve">15.003324508667</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1187343597412</t>
+    <t xml:space="preserve">15.1187362670898</t>
   </si>
   <si>
     <t xml:space="preserve">15.2533798217773</t>
@@ -1772,16 +1775,16 @@
     <t xml:space="preserve">15.0610294342041</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8686790466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8494434356689</t>
+    <t xml:space="preserve">14.8686800003052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8494424819946</t>
   </si>
   <si>
     <t xml:space="preserve">14.7147989273071</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4457302093506</t>
+    <t xml:space="preserve">15.4457292556763</t>
   </si>
   <si>
     <t xml:space="preserve">15.176438331604</t>
@@ -1790,166 +1793,163 @@
     <t xml:space="preserve">14.8302087783813</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0802640914917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9648561477661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1572046279907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7917394638062</t>
+    <t xml:space="preserve">14.9648542404175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1572036743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7917404174805</t>
   </si>
   <si>
     <t xml:space="preserve">14.7532691955566</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9071493148804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0225601196289</t>
+    <t xml:space="preserve">14.9071483612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0225582122803</t>
   </si>
   <si>
     <t xml:space="preserve">14.8109741210938</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8879127502441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5416831970215</t>
+    <t xml:space="preserve">14.8879137039185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5416841506958</t>
   </si>
   <si>
     <t xml:space="preserve">14.580153465271</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5993881225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5032138824463</t>
+    <t xml:space="preserve">14.5993871688843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.503212928772</t>
   </si>
   <si>
     <t xml:space="preserve">14.6378593444824</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6186237335205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4647445678711</t>
+    <t xml:space="preserve">14.6186227798462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4647436141968</t>
   </si>
   <si>
     <t xml:space="preserve">14.4455089569092</t>
   </si>
   <si>
-    <t xml:space="preserve">14.65709400177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.926383972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5609178543091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.349555015564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3880243301392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6765489578247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.522668838501</t>
+    <t xml:space="preserve">14.6570930480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9263849258423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5609197616577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3495559692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3880252838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6765508651733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5226707458496</t>
   </si>
   <si>
     <t xml:space="preserve">15.7150192260742</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7919616699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1574249267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7727251052856</t>
+    <t xml:space="preserve">15.7919626235962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1574268341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7727241516113</t>
   </si>
   <si>
     <t xml:space="preserve">15.8111963272095</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9073696136475</t>
+    <t xml:space="preserve">15.9073705673218</t>
   </si>
   <si>
     <t xml:space="preserve">15.6380796432495</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6188459396362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.849663734436</t>
+    <t xml:space="preserve">15.6188449859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8496646881104</t>
   </si>
   <si>
     <t xml:space="preserve">15.5803756713867</t>
   </si>
   <si>
-    <t xml:space="preserve">15.503436088562</t>
+    <t xml:space="preserve">15.5034341812134</t>
   </si>
   <si>
     <t xml:space="preserve">15.8304300308228</t>
   </si>
   <si>
-    <t xml:space="preserve">15.926607131958</t>
+    <t xml:space="preserve">15.9266052246094</t>
   </si>
   <si>
     <t xml:space="preserve">16.1189575195312</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1576480865479</t>
+    <t xml:space="preserve">17.1576461791992</t>
   </si>
   <si>
     <t xml:space="preserve">17.0037689208984</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9460639953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.888355255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9845314025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1191749572754</t>
+    <t xml:space="preserve">16.94606590271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8883571624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9845333099365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1191787719727</t>
   </si>
   <si>
     <t xml:space="preserve">17.2730579376221</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2732772827148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1771030426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6000518798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6577568054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1001625061035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9847545623779</t>
+    <t xml:space="preserve">18.2732791900635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1771049499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6000537872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6577606201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1001644134521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9847564697266</t>
   </si>
   <si>
     <t xml:space="preserve">18.1193981170654</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9655208587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9462852478027</t>
+    <t xml:space="preserve">17.965518951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9462833404541</t>
   </si>
   <si>
     <t xml:space="preserve">18.061695098877</t>
@@ -1961,22 +1961,22 @@
     <t xml:space="preserve">18.3117504119873</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7541561126709</t>
+    <t xml:space="preserve">18.7541580200195</t>
   </si>
   <si>
     <t xml:space="preserve">19.1003875732422</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0234470367432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5425720214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9657382965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9080371856689</t>
+    <t xml:space="preserve">19.0234489440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5425701141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9657421112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9080333709717</t>
   </si>
   <si>
     <t xml:space="preserve">19.4273815155029</t>
@@ -1991,16 +1991,16 @@
     <t xml:space="preserve">19.6678199768066</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2831192016602</t>
+    <t xml:space="preserve">19.2831172943115</t>
   </si>
   <si>
     <t xml:space="preserve">18.8503303527832</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6197299957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7159061431885</t>
+    <t xml:space="preserve">19.6197319030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7159080505371</t>
   </si>
   <si>
     <t xml:space="preserve">19.7639942169189</t>
@@ -2009,16 +2009,16 @@
     <t xml:space="preserve">19.3312072753906</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5716438293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1967811584473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2448692321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2164611816406</t>
+    <t xml:space="preserve">19.5716419219971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1967830657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2448711395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2164630889893</t>
   </si>
   <si>
     <t xml:space="preserve">21.1585330963135</t>
@@ -2030,13 +2030,13 @@
     <t xml:space="preserve">20.8219203948975</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6295719146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0142726898193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7257442474365</t>
+    <t xml:space="preserve">20.6295700073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.014274597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7257461547852</t>
   </si>
   <si>
     <t xml:space="preserve">20.6776580810547</t>
@@ -2045,25 +2045,25 @@
     <t xml:space="preserve">19.9563465118408</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2929611206055</t>
+    <t xml:space="preserve">20.2929553985596</t>
   </si>
   <si>
     <t xml:space="preserve">20.004430770874</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8601684570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0811519622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.773832321167</t>
+    <t xml:space="preserve">19.8601703643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0811500549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7738342285156</t>
   </si>
   <si>
     <t xml:space="preserve">20.9180965423584</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5814800262451</t>
+    <t xml:space="preserve">20.5814838409424</t>
   </si>
   <si>
     <t xml:space="preserve">21.2547092437744</t>
@@ -2072,10 +2072,10 @@
     <t xml:space="preserve">21.3989715576172</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2066192626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6394119262695</t>
+    <t xml:space="preserve">21.2066211700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6394100189209</t>
   </si>
   <si>
     <t xml:space="preserve">21.4470596313477</t>
@@ -2084,25 +2084,25 @@
     <t xml:space="preserve">21.8317604064941</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0525207519531</t>
+    <t xml:space="preserve">20.0525188446045</t>
   </si>
   <si>
     <t xml:space="preserve">20.100606918335</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7349185943604</t>
+    <t xml:space="preserve">18.734920501709</t>
   </si>
   <si>
     <t xml:space="preserve">18.1963405609131</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6192893981934</t>
+    <t xml:space="preserve">17.6192874908447</t>
   </si>
   <si>
     <t xml:space="preserve">16.3113059997559</t>
   </si>
   <si>
-    <t xml:space="preserve">16.195894241333</t>
+    <t xml:space="preserve">16.1958961486816</t>
   </si>
   <si>
     <t xml:space="preserve">14.4839792251587</t>
@@ -2111,16 +2111,16 @@
     <t xml:space="preserve">14.4262733459473</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4643001556396</t>
+    <t xml:space="preserve">12.464301109314</t>
   </si>
   <si>
     <t xml:space="preserve">12.0218954086304</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1373052597046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6951198577881</t>
+    <t xml:space="preserve">12.1373043060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6951217651367</t>
   </si>
   <si>
     <t xml:space="preserve">12.9067058563232</t>
@@ -2129,22 +2129,22 @@
     <t xml:space="preserve">11.9834251403809</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3106422424316</t>
+    <t xml:space="preserve">13.3106412887573</t>
   </si>
   <si>
     <t xml:space="preserve">13.5606966018677</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0223369598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1954526901245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2916278839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1185131072998</t>
+    <t xml:space="preserve">14.0223379135132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1954536437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2916269302368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1185121536255</t>
   </si>
   <si>
     <t xml:space="preserve">14.7340335845947</t>
@@ -2159,16 +2159,16 @@
     <t xml:space="preserve">16.8691234588623</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1766624450684</t>
+    <t xml:space="preserve">16.1766605377197</t>
   </si>
   <si>
     <t xml:space="preserve">16.2151317596436</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4649639129639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0612506866455</t>
+    <t xml:space="preserve">15.4649658203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0612525939941</t>
   </si>
   <si>
     <t xml:space="preserve">16.1381931304932</t>
@@ -2186,37 +2186,37 @@
     <t xml:space="preserve">16.7152404785156</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9268264770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0614719390869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2540435791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.638744354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0774555206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7677745819092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4580993652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4387454986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2064838409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9548721313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4193916320801</t>
+    <t xml:space="preserve">16.9268283843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0614700317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2540454864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6387424468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0774536132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7677764892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4580974578857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4387435913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.206485748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.954870223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4193878173828</t>
   </si>
   <si>
     <t xml:space="preserve">17.6129379272461</t>
@@ -2225,10 +2225,10 @@
     <t xml:space="preserve">17.1677742004395</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6516456604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4968090057373</t>
+    <t xml:space="preserve">17.651647567749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4968070983887</t>
   </si>
   <si>
     <t xml:space="preserve">17.7290668487549</t>
@@ -2237,22 +2237,22 @@
     <t xml:space="preserve">18.290355682373</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9419727325439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0580997467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3871307373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4064865112305</t>
+    <t xml:space="preserve">17.9419746398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0580978393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3871326446533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4064884185791</t>
   </si>
   <si>
     <t xml:space="preserve">17.9032611846924</t>
   </si>
   <si>
-    <t xml:space="preserve">18.232292175293</t>
+    <t xml:space="preserve">18.2322902679443</t>
   </si>
   <si>
     <t xml:space="preserve">18.2516498565674</t>
@@ -2261,7 +2261,7 @@
     <t xml:space="preserve">18.5806827545166</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4451942443848</t>
+    <t xml:space="preserve">18.4451961517334</t>
   </si>
   <si>
     <t xml:space="preserve">18.1161632537842</t>
@@ -2270,19 +2270,19 @@
     <t xml:space="preserve">18.0387439727783</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8322944641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7742309570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6774559020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9097118377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0451965332031</t>
+    <t xml:space="preserve">18.8322925567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7742290496826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.677453994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9097137451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0451984405518</t>
   </si>
   <si>
     <t xml:space="preserve">19.5968132019043</t>
@@ -2294,16 +2294,16 @@
     <t xml:space="preserve">18.9484233856201</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1032600402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4645500183105</t>
+    <t xml:space="preserve">19.1032619476318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4645519256592</t>
   </si>
   <si>
     <t xml:space="preserve">18.6581020355225</t>
   </si>
   <si>
-    <t xml:space="preserve">19.500036239624</t>
+    <t xml:space="preserve">19.5000381469727</t>
   </si>
   <si>
     <t xml:space="preserve">19.6451988220215</t>
@@ -2315,10 +2315,10 @@
     <t xml:space="preserve">20.3226184844971</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6129417419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5645542144775</t>
+    <t xml:space="preserve">20.6129398345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5645561218262</t>
   </si>
   <si>
     <t xml:space="preserve">21.0484275817871</t>
@@ -2327,7 +2327,7 @@
     <t xml:space="preserve">21.2903633117676</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7258472442627</t>
+    <t xml:space="preserve">21.7258491516113</t>
   </si>
   <si>
     <t xml:space="preserve">21.1935901641846</t>
@@ -2336,7 +2336,7 @@
     <t xml:space="preserve">21.5806865692139</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8710117340088</t>
+    <t xml:space="preserve">21.8710098266602</t>
   </si>
   <si>
     <t xml:space="preserve">21.532299041748</t>
@@ -2345,10 +2345,10 @@
     <t xml:space="preserve">21.3387489318848</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7742366790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4516563415527</t>
+    <t xml:space="preserve">21.7742347717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4516582489014</t>
   </si>
   <si>
     <t xml:space="preserve">22.9355278015137</t>
@@ -2357,13 +2357,13 @@
     <t xml:space="preserve">22.7903652191162</t>
   </si>
   <si>
-    <t xml:space="preserve">23.322624206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4194030761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0968227386475</t>
+    <t xml:space="preserve">23.3226261138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4194011688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0968208312988</t>
   </si>
   <si>
     <t xml:space="preserve">24.7258529663086</t>
@@ -2372,10 +2372,10 @@
     <t xml:space="preserve">24.4839172363281</t>
   </si>
   <si>
-    <t xml:space="preserve">24.048433303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7581100463867</t>
+    <t xml:space="preserve">24.0484352111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7581081390381</t>
   </si>
   <si>
     <t xml:space="preserve">23.9516582489014</t>
@@ -2390,28 +2390,28 @@
     <t xml:space="preserve">23.0323028564453</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4677848815918</t>
+    <t xml:space="preserve">23.4677886962891</t>
   </si>
   <si>
     <t xml:space="preserve">23.0806903839111</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8871402740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5484294891357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8226222991943</t>
+    <t xml:space="preserve">22.8871421813965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5484275817871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.822624206543</t>
   </si>
   <si>
     <t xml:space="preserve">22.0645561218262</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2419757843018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6290760040283</t>
+    <t xml:space="preserve">21.2419776916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6290721893311</t>
   </si>
   <si>
     <t xml:space="preserve">20.4677810668945</t>
@@ -2429,16 +2429,16 @@
     <t xml:space="preserve">22.2097206115723</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9677848815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9516525268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1129455566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3548812866211</t>
+    <t xml:space="preserve">21.9677867889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9516544342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1129474639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3548831939697</t>
   </si>
   <si>
     <t xml:space="preserve">21.919397354126</t>
@@ -2450,13 +2450,13 @@
     <t xml:space="preserve">22.6452045440674</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4355316162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3387546539307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.241979598999</t>
+    <t xml:space="preserve">24.4355297088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3387565612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2419815063477</t>
   </si>
   <si>
     <t xml:space="preserve">25.7419834136963</t>
@@ -2468,7 +2468,7 @@
     <t xml:space="preserve">27.0000514984131</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6613388061523</t>
+    <t xml:space="preserve">26.6613426208496</t>
   </si>
   <si>
     <t xml:space="preserve">26.6129550933838</t>
@@ -2477,19 +2477,19 @@
     <t xml:space="preserve">26.3710193634033</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6774730682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6452178955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9032821655273</t>
+    <t xml:space="preserve">27.6774749755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6452159881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.903284072876</t>
   </si>
   <si>
     <t xml:space="preserve">28.9355392456055</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7581214904785</t>
+    <t xml:space="preserve">29.7581233978271</t>
   </si>
   <si>
     <t xml:space="preserve">30.3871536254883</t>
@@ -2501,16 +2501,16 @@
     <t xml:space="preserve">31.7419948577881</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0323143005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5484447479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0807113647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2581253051758</t>
+    <t xml:space="preserve">32.0323181152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5484466552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0807075500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2581233978271</t>
   </si>
   <si>
     <t xml:space="preserve">32.1774787902832</t>
@@ -2519,13 +2519,13 @@
     <t xml:space="preserve">32.3226432800293</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2903861999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1936149597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8065185546875</t>
+    <t xml:space="preserve">33.2903900146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1936111450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8065147399902</t>
   </si>
   <si>
     <t xml:space="preserve">33.4839363098145</t>
@@ -2534,16 +2534,16 @@
     <t xml:space="preserve">33.7258720397949</t>
   </si>
   <si>
-    <t xml:space="preserve">34.1129684448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7420043945312</t>
+    <t xml:space="preserve">34.1129722595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7420082092285</t>
   </si>
   <si>
     <t xml:space="preserve">34.5968399047852</t>
   </si>
   <si>
-    <t xml:space="preserve">35.3710327148438</t>
+    <t xml:space="preserve">35.3710403442383</t>
   </si>
   <si>
     <t xml:space="preserve">35.4678115844727</t>
@@ -2558,25 +2558,25 @@
     <t xml:space="preserve">36.1936187744141</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3065185546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.564582824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6613502502441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7581329345703</t>
+    <t xml:space="preserve">34.3065147399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5645790100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6613540649414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.758129119873</t>
   </si>
   <si>
     <t xml:space="preserve">32.7097396850586</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9355449676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3387660980225</t>
+    <t xml:space="preserve">31.9355411529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3387680053711</t>
   </si>
   <si>
     <t xml:space="preserve">30.8226413726807</t>
@@ -2585,10 +2585,10 @@
     <t xml:space="preserve">30.5807037353516</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4839286804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.112964630127</t>
+    <t xml:space="preserve">30.4839305877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1129665374756</t>
   </si>
   <si>
     <t xml:space="preserve">33.435546875</t>
@@ -2597,16 +2597,16 @@
     <t xml:space="preserve">33.8710327148438</t>
   </si>
   <si>
-    <t xml:space="preserve">35.2742652893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6613578796387</t>
+    <t xml:space="preserve">35.2742614746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6613616943359</t>
   </si>
   <si>
     <t xml:space="preserve">35.7097473144531</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2581329345703</t>
+    <t xml:space="preserve">37.2581367492676</t>
   </si>
   <si>
     <t xml:space="preserve">37.0162010192871</t>
@@ -2615,10 +2615,10 @@
     <t xml:space="preserve">36.9678115844727</t>
   </si>
   <si>
-    <t xml:space="preserve">35.9516868591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4355583190918</t>
+    <t xml:space="preserve">35.9516830444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4355506896973</t>
   </si>
   <si>
     <t xml:space="preserve">35.0807113647461</t>
@@ -2627,13 +2627,13 @@
     <t xml:space="preserve">34.9839401245117</t>
   </si>
   <si>
-    <t xml:space="preserve">36.677490234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.0645866394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6452407836914</t>
+    <t xml:space="preserve">36.6774864196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.064582824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6452369689941</t>
   </si>
   <si>
     <t xml:space="preserve">38.0323333740234</t>
@@ -2642,10 +2642,10 @@
     <t xml:space="preserve">38.6129760742188</t>
   </si>
   <si>
-    <t xml:space="preserve">38.7581405639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8226585388184</t>
+    <t xml:space="preserve">38.7581367492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8226623535156</t>
   </si>
   <si>
     <t xml:space="preserve">39.6774940490723</t>
@@ -2657,43 +2657,43 @@
     <t xml:space="preserve">38.7097511291504</t>
   </si>
   <si>
-    <t xml:space="preserve">39.6291084289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4516906738281</t>
+    <t xml:space="preserve">39.6291122436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4516868591309</t>
   </si>
   <si>
     <t xml:space="preserve">40.1613693237305</t>
   </si>
   <si>
-    <t xml:space="preserve">39.4355621337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2581405639648</t>
+    <t xml:space="preserve">39.4355583190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2581443786621</t>
   </si>
   <si>
     <t xml:space="preserve">44.0807304382324</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9033050537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.0645942687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1775016784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8549156188965</t>
+    <t xml:space="preserve">41.9033088684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.0645980834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1774978637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8549194335938</t>
   </si>
   <si>
     <t xml:space="preserve">42.3387908935547</t>
   </si>
   <si>
-    <t xml:space="preserve">42.0484657287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.6291160583496</t>
+    <t xml:space="preserve">42.048469543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.6291084289551</t>
   </si>
   <si>
     <t xml:space="preserve">41.6129837036133</t>
@@ -2708,10 +2708,10 @@
     <t xml:space="preserve">44.1291122436523</t>
   </si>
   <si>
-    <t xml:space="preserve">44.7097625732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.7581520080566</t>
+    <t xml:space="preserve">44.7097663879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.7581481933594</t>
   </si>
   <si>
     <t xml:space="preserve">45.6775054931641</t>
@@ -2720,10 +2720,10 @@
     <t xml:space="preserve">44.4194412231445</t>
   </si>
   <si>
-    <t xml:space="preserve">45.0000915527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.0162162780762</t>
+    <t xml:space="preserve">45.0000839233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.0162200927734</t>
   </si>
   <si>
     <t xml:space="preserve">45.4839553833008</t>
@@ -2738,13 +2738,13 @@
     <t xml:space="preserve">45.1452522277832</t>
   </si>
   <si>
-    <t xml:space="preserve">44.6129837036133</t>
+    <t xml:space="preserve">44.6129875183105</t>
   </si>
   <si>
     <t xml:space="preserve">44.5162162780762</t>
   </si>
   <si>
-    <t xml:space="preserve">44.2742767333984</t>
+    <t xml:space="preserve">44.274284362793</t>
   </si>
   <si>
     <t xml:space="preserve">43.838794708252</t>
@@ -2753,13 +2753,13 @@
     <t xml:space="preserve">43.1613731384277</t>
   </si>
   <si>
-    <t xml:space="preserve">43.3065338134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.2581520080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.8710479736328</t>
+    <t xml:space="preserve">43.3065299987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.2581443786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.8710441589355</t>
   </si>
   <si>
     <t xml:space="preserve">43.0645980834961</t>
@@ -2777,7 +2777,7 @@
     <t xml:space="preserve">41.8992919921875</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0436096191406</t>
+    <t xml:space="preserve">40.0436134338379</t>
   </si>
   <si>
     <t xml:space="preserve">39.799446105957</t>
@@ -2792,7 +2792,7 @@
     <t xml:space="preserve">40.8737831115723</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9947738647461</t>
+    <t xml:space="preserve">39.9947776794434</t>
   </si>
   <si>
     <t xml:space="preserve">40.7761154174805</t>
@@ -2804,7 +2804,7 @@
     <t xml:space="preserve">40.190113067627</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8971099853516</t>
+    <t xml:space="preserve">39.8971061706543</t>
   </si>
   <si>
     <t xml:space="preserve">39.6529388427734</t>
@@ -2813,100 +2813,100 @@
     <t xml:space="preserve">39.6041030883789</t>
   </si>
   <si>
-    <t xml:space="preserve">39.7506065368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2622680664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2877807617188</t>
+    <t xml:space="preserve">39.7506103515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2622718811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2877769470215</t>
   </si>
   <si>
     <t xml:space="preserve">39.9459457397461</t>
   </si>
   <si>
-    <t xml:space="preserve">37.8949279785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.7229194641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.601921081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.090259552002</t>
+    <t xml:space="preserve">37.8949241638184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.7229156494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6019248962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.0902633666992</t>
   </si>
   <si>
     <t xml:space="preserve">39.5552711486816</t>
   </si>
   <si>
-    <t xml:space="preserve">41.7039566040039</t>
+    <t xml:space="preserve">41.7039527893066</t>
   </si>
   <si>
     <t xml:space="preserve">42.0946197509766</t>
   </si>
   <si>
-    <t xml:space="preserve">41.4597854614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0691146850586</t>
+    <t xml:space="preserve">41.459789276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0691184997559</t>
   </si>
   <si>
     <t xml:space="preserve">40.3854446411133</t>
   </si>
   <si>
-    <t xml:space="preserve">40.4342803955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.1922912597656</t>
+    <t xml:space="preserve">40.4342842102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.1922950744629</t>
   </si>
   <si>
     <t xml:space="preserve">42.0457916259766</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9481239318848</t>
+    <t xml:space="preserve">41.9481201171875</t>
   </si>
   <si>
     <t xml:space="preserve">41.4109535217285</t>
   </si>
   <si>
-    <t xml:space="preserve">42.7294578552246</t>
+    <t xml:space="preserve">42.7294616699219</t>
   </si>
   <si>
     <t xml:space="preserve">45.3664817810059</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4153175354004</t>
+    <t xml:space="preserve">45.4153137207031</t>
   </si>
   <si>
     <t xml:space="preserve">46.1966514587402</t>
   </si>
   <si>
-    <t xml:space="preserve">47.856990814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.3198280334473</t>
+    <t xml:space="preserve">47.8569984436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.31982421875</t>
   </si>
   <si>
     <t xml:space="preserve">47.808162689209</t>
   </si>
   <si>
-    <t xml:space="preserve">48.5406646728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.5895042419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.833667755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.1988258361816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.7126808166504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.9080123901367</t>
+    <t xml:space="preserve">48.5406684875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.5895004272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.8336715698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.1988296508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.7126770019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.9080085754395</t>
   </si>
   <si>
     <t xml:space="preserve">49.8103446960449</t>
@@ -2918,19 +2918,19 @@
     <t xml:space="preserve">50.6893501281738</t>
   </si>
   <si>
-    <t xml:space="preserve">51.3730163574219</t>
+    <t xml:space="preserve">51.3730201721191</t>
   </si>
   <si>
     <t xml:space="preserve">50.2986793518066</t>
   </si>
   <si>
-    <t xml:space="preserve">50.5916786193848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4940185546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.2753524780273</t>
+    <t xml:space="preserve">50.591682434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4940147399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.2753486633301</t>
   </si>
   <si>
     <t xml:space="preserve">50.2010154724121</t>
@@ -2939,7 +2939,7 @@
     <t xml:space="preserve">50.7870178222656</t>
   </si>
   <si>
-    <t xml:space="preserve">50.9823532104492</t>
+    <t xml:space="preserve">50.982349395752</t>
   </si>
   <si>
     <t xml:space="preserve">51.8613548278809</t>
@@ -2948,28 +2948,28 @@
     <t xml:space="preserve">51.9590263366699</t>
   </si>
   <si>
-    <t xml:space="preserve">50.8846855163574</t>
+    <t xml:space="preserve">50.8846817016602</t>
   </si>
   <si>
     <t xml:space="preserve">45.2688140869141</t>
   </si>
   <si>
-    <t xml:space="preserve">44.5363082885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.510799407959</t>
+    <t xml:space="preserve">44.536304473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.5107955932617</t>
   </si>
   <si>
     <t xml:space="preserve">44.2433013916016</t>
   </si>
   <si>
-    <t xml:space="preserve">44.2921371459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.9269790649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.047966003418</t>
+    <t xml:space="preserve">44.2921333312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.9269752502441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.0479698181152</t>
   </si>
   <si>
     <t xml:space="preserve">43.8037986755371</t>
@@ -2978,7 +2978,7 @@
     <t xml:space="preserve">44.4386444091797</t>
   </si>
   <si>
-    <t xml:space="preserve">43.9503021240234</t>
+    <t xml:space="preserve">43.9502983093262</t>
   </si>
   <si>
     <t xml:space="preserve">44.1944694519043</t>
@@ -2990,73 +2990,73 @@
     <t xml:space="preserve">40.9714508056641</t>
   </si>
   <si>
-    <t xml:space="preserve">41.7527847290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.2899589538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.0712928771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.2666282653809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.7061347961426</t>
+    <t xml:space="preserve">41.7527885437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.2899551391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.0712966918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.2666320800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.7061309814453</t>
   </si>
   <si>
     <t xml:space="preserve">44.3409729003906</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4641456604004</t>
+    <t xml:space="preserve">45.4641494750977</t>
   </si>
   <si>
     <t xml:space="preserve">46.0989837646484</t>
   </si>
   <si>
-    <t xml:space="preserve">45.659481048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.7571487426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.7782936096191</t>
+    <t xml:space="preserve">45.6594848632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.7571449279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.7782974243164</t>
   </si>
   <si>
     <t xml:space="preserve">41.2644538879395</t>
   </si>
   <si>
-    <t xml:space="preserve">42.6806297302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.1201324462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4364585876465</t>
+    <t xml:space="preserve">42.6806259155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.1201286315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4364624023438</t>
   </si>
   <si>
     <t xml:space="preserve">41.508617401123</t>
   </si>
   <si>
-    <t xml:space="preserve">41.0202827453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8715972900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.2367630004883</t>
+    <t xml:space="preserve">41.0202865600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8716011047363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.2367668151855</t>
   </si>
   <si>
     <t xml:space="preserve">39.0669364929199</t>
   </si>
   <si>
-    <t xml:space="preserve">39.848274230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5319480895996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8504524230957</t>
+    <t xml:space="preserve">39.8482780456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5319442749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.850456237793</t>
   </si>
   <si>
     <t xml:space="preserve">41.1179466247559</t>
@@ -3068,10 +3068,10 @@
     <t xml:space="preserve">41.6551208496094</t>
   </si>
   <si>
-    <t xml:space="preserve">41.6062850952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4852905273438</t>
+    <t xml:space="preserve">41.6062889099121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.485294342041</t>
   </si>
   <si>
     <t xml:space="preserve">42.9736289978027</t>
@@ -3083,7 +3083,7 @@
     <t xml:space="preserve">41.362117767334</t>
   </si>
   <si>
-    <t xml:space="preserve">40.2389488220215</t>
+    <t xml:space="preserve">40.2389450073242</t>
   </si>
   <si>
     <t xml:space="preserve">40.6296157836914</t>
@@ -3101,7 +3101,7 @@
     <t xml:space="preserve">40.9226188659668</t>
   </si>
   <si>
-    <t xml:space="preserve">39.1157684326172</t>
+    <t xml:space="preserve">39.1157646179199</t>
   </si>
   <si>
     <t xml:space="preserve">42.5829582214355</t>
@@ -3113,13 +3113,13 @@
     <t xml:space="preserve">38.5785980224609</t>
   </si>
   <si>
-    <t xml:space="preserve">36.4299201965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6274299621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.1135864257812</t>
+    <t xml:space="preserve">36.4299163818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6274337768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.1135902404785</t>
   </si>
   <si>
     <t xml:space="preserve">35.7950820922852</t>
@@ -3128,25 +3128,25 @@
     <t xml:space="preserve">34.7207336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5997505187988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.5275840759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6252517700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.0880851745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.1369171142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4532432556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5254058837891</t>
+    <t xml:space="preserve">35.5997467041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.527587890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6252555847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.0880813598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.1369132995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4532470703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5254020690918</t>
   </si>
   <si>
     <t xml:space="preserve">36.3810844421387</t>
@@ -3158,7 +3158,7 @@
     <t xml:space="preserve">33.9393997192383</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1325607299805</t>
+    <t xml:space="preserve">32.1325569152832</t>
   </si>
   <si>
     <t xml:space="preserve">31.4977169036865</t>
@@ -3167,25 +3167,25 @@
     <t xml:space="preserve">31.6442203521729</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0115585327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3767280578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4510650634766</t>
+    <t xml:space="preserve">33.0115623474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3767242431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4510612487793</t>
   </si>
   <si>
     <t xml:space="preserve">34.7695693969727</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5742378234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3067474365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0348892211914</t>
+    <t xml:space="preserve">34.5742416381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3067436218262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0348854064941</t>
   </si>
   <si>
     <t xml:space="preserve">31.4000511169434</t>
@@ -3194,7 +3194,7 @@
     <t xml:space="preserve">33.5975646972656</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9627227783203</t>
+    <t xml:space="preserve">32.9627265930176</t>
   </si>
   <si>
     <t xml:space="preserve">32.5232238769531</t>
@@ -3206,19 +3206,19 @@
     <t xml:space="preserve">32.6208915710449</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4488849639893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6697235107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7673950195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2144813537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0191478729248</t>
+    <t xml:space="preserve">31.4488830566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6697273254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.767391204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2144794464111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0191459655762</t>
   </si>
   <si>
     <t xml:space="preserve">30.9019451141357</t>
@@ -3230,7 +3230,7 @@
     <t xml:space="preserve">30.4722099304199</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2302207946777</t>
+    <t xml:space="preserve">32.230224609375</t>
   </si>
   <si>
     <t xml:space="preserve">32.0739555358887</t>
@@ -3239,10 +3239,10 @@
     <t xml:space="preserve">31.9372215270996</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3316822052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1716194152832</t>
+    <t xml:space="preserve">31.3316841125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1716232299805</t>
   </si>
   <si>
     <t xml:space="preserve">31.3902816772461</t>
@@ -3257,10 +3257,10 @@
     <t xml:space="preserve">29.9643402099609</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3821277618408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4993305206299</t>
+    <t xml:space="preserve">28.3821296691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4993286132812</t>
   </si>
   <si>
     <t xml:space="preserve">29.2025356292725</t>
@@ -3269,13 +3269,13 @@
     <t xml:space="preserve">28.8704643249512</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9290676116943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.085334777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3039932250977</t>
+    <t xml:space="preserve">28.9290657043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0853328704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3039951324463</t>
   </si>
   <si>
     <t xml:space="preserve">28.4211959838867</t>
@@ -3287,13 +3287,13 @@
     <t xml:space="preserve">28.3235282897949</t>
   </si>
   <si>
-    <t xml:space="preserve">28.596996307373</t>
+    <t xml:space="preserve">28.5969982147217</t>
   </si>
   <si>
     <t xml:space="preserve">28.2258625030518</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5579299926758</t>
+    <t xml:space="preserve">28.5579280853271</t>
   </si>
   <si>
     <t xml:space="preserve">28.1816463470459</t>
@@ -15224,7 +15224,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G373" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -15250,7 +15250,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G374" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -15276,7 +15276,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G375" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -15302,7 +15302,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G376" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -15328,7 +15328,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G377" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -15354,7 +15354,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G378" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -15380,7 +15380,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G379" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -15406,7 +15406,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G380" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -15432,7 +15432,7 @@
         <v>12</v>
       </c>
       <c r="G381" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -15458,7 +15458,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G382" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -15484,7 +15484,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G383" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -15510,7 +15510,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G384" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -15536,7 +15536,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G385" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -15562,7 +15562,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G386" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -15588,7 +15588,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G387" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -15614,7 +15614,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G388" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -15640,7 +15640,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G389" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -15666,7 +15666,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G390" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -15692,7 +15692,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G391" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -15718,7 +15718,7 @@
         <v>13.5</v>
       </c>
       <c r="G392" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -15744,7 +15744,7 @@
         <v>13.5100002288818</v>
       </c>
       <c r="G393" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -15770,7 +15770,7 @@
         <v>13.6700000762939</v>
       </c>
       <c r="G394" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -15796,7 +15796,7 @@
         <v>13.75</v>
       </c>
       <c r="G395" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -15822,7 +15822,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G396" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -15848,7 +15848,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G397" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -15874,7 +15874,7 @@
         <v>13.7299995422363</v>
       </c>
       <c r="G398" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -15900,7 +15900,7 @@
         <v>13.5299997329712</v>
       </c>
       <c r="G399" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -15926,7 +15926,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G400" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -15952,7 +15952,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G401" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -15978,7 +15978,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G402" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -16004,7 +16004,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G403" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -16030,7 +16030,7 @@
         <v>13.4700002670288</v>
       </c>
       <c r="G404" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -16056,7 +16056,7 @@
         <v>13.5299997329712</v>
       </c>
       <c r="G405" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -16082,7 +16082,7 @@
         <v>13.6800003051758</v>
       </c>
       <c r="G406" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -16108,7 +16108,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G407" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -16134,7 +16134,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G408" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -16160,7 +16160,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G409" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -16186,7 +16186,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G410" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -16212,7 +16212,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G411" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -16238,7 +16238,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G412" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -16264,7 +16264,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G413" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -16290,7 +16290,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G414" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -16316,7 +16316,7 @@
         <v>13.25</v>
       </c>
       <c r="G415" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -16342,7 +16342,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G416" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -16368,7 +16368,7 @@
         <v>13</v>
       </c>
       <c r="G417" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -16394,7 +16394,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G418" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -16420,7 +16420,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G419" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -16446,7 +16446,7 @@
         <v>13.2299995422363</v>
       </c>
       <c r="G420" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -16472,7 +16472,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G421" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -16498,7 +16498,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G422" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -16524,7 +16524,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G423" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -16550,7 +16550,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G424" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -16576,7 +16576,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G425" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -16602,7 +16602,7 @@
         <v>13</v>
       </c>
       <c r="G426" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -16628,7 +16628,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G427" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -16654,7 +16654,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G428" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -16680,7 +16680,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G429" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -16706,7 +16706,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G430" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -16732,7 +16732,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G431" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -16758,7 +16758,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G432" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -16784,7 +16784,7 @@
         <v>13.25</v>
       </c>
       <c r="G433" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -16810,7 +16810,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G434" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -16836,7 +16836,7 @@
         <v>13.2299995422363</v>
       </c>
       <c r="G435" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -16862,7 +16862,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G436" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -16888,7 +16888,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G437" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -16914,7 +16914,7 @@
         <v>13</v>
       </c>
       <c r="G438" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -16940,7 +16940,7 @@
         <v>13.210000038147</v>
       </c>
       <c r="G439" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -16966,7 +16966,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G440" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -16992,7 +16992,7 @@
         <v>13.4300003051758</v>
       </c>
       <c r="G441" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -17018,7 +17018,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G442" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -17044,7 +17044,7 @@
         <v>13.4099998474121</v>
       </c>
       <c r="G443" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -17070,7 +17070,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G444" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -17096,7 +17096,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G445" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -17122,7 +17122,7 @@
         <v>13.2700004577637</v>
       </c>
       <c r="G446" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -17148,7 +17148,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G447" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -17174,7 +17174,7 @@
         <v>13.2700004577637</v>
       </c>
       <c r="G448" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -17200,7 +17200,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G449" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -17226,7 +17226,7 @@
         <v>13.25</v>
       </c>
       <c r="G450" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -17252,7 +17252,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G451" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -17278,7 +17278,7 @@
         <v>12.9700002670288</v>
       </c>
       <c r="G452" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -17304,7 +17304,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G453" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -17330,7 +17330,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G454" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -17356,7 +17356,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G455" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -17382,7 +17382,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G456" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -17408,7 +17408,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G457" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -17434,7 +17434,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G458" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -17460,7 +17460,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G459" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -17486,7 +17486,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G460" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -17512,7 +17512,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G461" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -17538,7 +17538,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G462" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -17590,7 +17590,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G464" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -17642,7 +17642,7 @@
         <v>12.75</v>
       </c>
       <c r="G466" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -17668,7 +17668,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G467" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -17694,7 +17694,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G468" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -17720,7 +17720,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G469" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -17746,7 +17746,7 @@
         <v>13.1899995803833</v>
       </c>
       <c r="G470" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -17772,7 +17772,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G471" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -17798,7 +17798,7 @@
         <v>13.1899995803833</v>
       </c>
       <c r="G472" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -17824,7 +17824,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G473" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -17876,7 +17876,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G475" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -17902,7 +17902,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G476" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -17928,7 +17928,7 @@
         <v>12.6899995803833</v>
       </c>
       <c r="G477" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -17954,7 +17954,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G478" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -17980,7 +17980,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G479" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -18006,7 +18006,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G480" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -18032,7 +18032,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G481" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -18058,7 +18058,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G482" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -18084,7 +18084,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G483" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -18110,7 +18110,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G484" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -18136,7 +18136,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G485" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -18188,7 +18188,7 @@
         <v>12.3699998855591</v>
       </c>
       <c r="G487" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -18214,7 +18214,7 @@
         <v>12.5100002288818</v>
       </c>
       <c r="G488" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -18240,7 +18240,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G489" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -18266,7 +18266,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G490" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -18292,7 +18292,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G491" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -18318,7 +18318,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G492" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -18344,7 +18344,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G493" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -18370,7 +18370,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G494" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -18396,7 +18396,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G495" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -18422,7 +18422,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G496" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -18448,7 +18448,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G497" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -18474,7 +18474,7 @@
         <v>12.75</v>
       </c>
       <c r="G498" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -18500,7 +18500,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G499" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -18526,7 +18526,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G500" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -18552,7 +18552,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G501" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -18578,7 +18578,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G502" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -18604,7 +18604,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G503" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -18630,7 +18630,7 @@
         <v>13</v>
       </c>
       <c r="G504" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -18656,7 +18656,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G505" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -18682,7 +18682,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G506" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -18708,7 +18708,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G507" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -18734,7 +18734,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G508" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -18760,7 +18760,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G509" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -18786,7 +18786,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G510" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -18812,7 +18812,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G511" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -18838,7 +18838,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G512" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -18864,7 +18864,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G513" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -18890,7 +18890,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G514" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -18916,7 +18916,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G515" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -18942,7 +18942,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G516" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -18968,7 +18968,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G517" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -18994,7 +18994,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G518" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -19020,7 +19020,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G519" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -19046,7 +19046,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G520" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -19072,7 +19072,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G521" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -19098,7 +19098,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G522" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -19124,7 +19124,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G523" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -19150,7 +19150,7 @@
         <v>15</v>
       </c>
       <c r="G524" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -19176,7 +19176,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G525" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -19202,7 +19202,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G526" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -19228,7 +19228,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G527" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -19254,7 +19254,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G528" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -19280,7 +19280,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G529" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -19306,7 +19306,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G530" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -19332,7 +19332,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G531" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -19358,7 +19358,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G532" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -19384,7 +19384,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G533" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -19410,7 +19410,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G534" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -19436,7 +19436,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G535" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -19462,7 +19462,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G536" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -19488,7 +19488,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G537" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -19514,7 +19514,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G538" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -19540,7 +19540,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G539" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -19566,7 +19566,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G540" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -19592,7 +19592,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G541" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -19618,7 +19618,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G542" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -19644,7 +19644,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G543" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -19670,7 +19670,7 @@
         <v>14</v>
       </c>
       <c r="G544" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -19696,7 +19696,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G545" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -19722,7 +19722,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G546" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -19748,7 +19748,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G547" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -19774,7 +19774,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G548" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -19800,7 +19800,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G549" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -19826,7 +19826,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G550" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -19852,7 +19852,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G551" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -19878,7 +19878,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G552" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -19904,7 +19904,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G553" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -19956,7 +19956,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G555" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -19982,7 +19982,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G556" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -20008,7 +20008,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G557" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -20034,7 +20034,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G558" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -20060,7 +20060,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G559" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -20086,7 +20086,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G560" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -20112,7 +20112,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G561" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -20138,7 +20138,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G562" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -20164,7 +20164,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G563" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -20190,7 +20190,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G564" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -20216,7 +20216,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G565" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -20242,7 +20242,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G566" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -20268,7 +20268,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G567" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -20294,7 +20294,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G568" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -20320,7 +20320,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G569" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -20346,7 +20346,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G570" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -20372,7 +20372,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G571" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -20398,7 +20398,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G572" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -20424,7 +20424,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G573" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -20450,7 +20450,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G574" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -20476,7 +20476,7 @@
         <v>13</v>
       </c>
       <c r="G575" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -20502,7 +20502,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G576" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -20528,7 +20528,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G577" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -20554,7 +20554,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G578" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -20580,7 +20580,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G579" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -20606,7 +20606,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G580" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -20632,7 +20632,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G581" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -20658,7 +20658,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G582" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -20684,7 +20684,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G583" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -20710,7 +20710,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G584" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -20736,7 +20736,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G585" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -20762,7 +20762,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G586" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -20788,7 +20788,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G587" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -20814,7 +20814,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G588" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -20840,7 +20840,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G589" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -20866,7 +20866,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G590" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -20892,7 +20892,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G591" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -20918,7 +20918,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G592" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -20944,7 +20944,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G593" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -20970,7 +20970,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G594" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -20996,7 +20996,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G595" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -21022,7 +21022,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G596" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -21048,7 +21048,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G597" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -21074,7 +21074,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G598" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -21100,7 +21100,7 @@
         <v>16</v>
       </c>
       <c r="G599" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -21126,7 +21126,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G600" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -21152,7 +21152,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G601" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -21178,7 +21178,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G602" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -21204,7 +21204,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G603" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -21230,7 +21230,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G604" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -21256,7 +21256,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G605" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -21282,7 +21282,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G606" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -21308,7 +21308,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G607" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -21334,7 +21334,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G608" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -21360,7 +21360,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G609" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -21386,7 +21386,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G610" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -21412,7 +21412,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G611" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -21438,7 +21438,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G612" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -21464,7 +21464,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G613" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -21490,7 +21490,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G614" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -21516,7 +21516,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G615" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -21542,7 +21542,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G616" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -21568,7 +21568,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G617" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -21594,7 +21594,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G618" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -21620,7 +21620,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G619" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -21646,7 +21646,7 @@
         <v>13.5</v>
       </c>
       <c r="G620" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -21672,7 +21672,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G621" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -21698,7 +21698,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G622" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -21724,7 +21724,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G623" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -21750,7 +21750,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G624" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -21776,7 +21776,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G625" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -21802,7 +21802,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G626" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -21828,7 +21828,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G627" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -21854,7 +21854,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G628" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -21880,7 +21880,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G629" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -21906,7 +21906,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G630" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -21932,7 +21932,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G631" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -21958,7 +21958,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G632" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -21984,7 +21984,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G633" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -22010,7 +22010,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G634" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -22036,7 +22036,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G635" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -22062,7 +22062,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G636" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -22088,7 +22088,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G637" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -22114,7 +22114,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G638" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -22140,7 +22140,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G639" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -22166,7 +22166,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G640" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -22192,7 +22192,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G641" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -22218,7 +22218,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G642" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -22244,7 +22244,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G643" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -22270,7 +22270,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G644" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -22296,7 +22296,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G645" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -22322,7 +22322,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G646" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -22348,7 +22348,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G647" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -22374,7 +22374,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G648" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -22400,7 +22400,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G649" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -22426,7 +22426,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G650" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -22452,7 +22452,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G651" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -22478,7 +22478,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G652" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -22504,7 +22504,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G653" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -22530,7 +22530,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G654" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -22556,7 +22556,7 @@
         <v>13</v>
       </c>
       <c r="G655" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -22582,7 +22582,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G656" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -22608,7 +22608,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G657" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -22634,7 +22634,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G658" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -22660,7 +22660,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G659" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -22686,7 +22686,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G660" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -22712,7 +22712,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G661" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -22738,7 +22738,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G662" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -22764,7 +22764,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G663" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -22790,7 +22790,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G664" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -22816,7 +22816,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G665" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -22842,7 +22842,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G666" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -22868,7 +22868,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G667" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -22894,7 +22894,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G668" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -22920,7 +22920,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G669" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -22946,7 +22946,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G670" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -22972,7 +22972,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G671" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -22998,7 +22998,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G672" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -23024,7 +23024,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G673" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -23050,7 +23050,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G674" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -23076,7 +23076,7 @@
         <v>14.9399995803833</v>
       </c>
       <c r="G675" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -23102,7 +23102,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G676" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -23128,7 +23128,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G677" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -23154,7 +23154,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G678" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -23180,7 +23180,7 @@
         <v>14.5</v>
       </c>
       <c r="G679" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -23206,7 +23206,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G680" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -23232,7 +23232,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G681" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -23258,7 +23258,7 @@
         <v>14.5600004196167</v>
       </c>
       <c r="G682" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -23284,7 +23284,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G683" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -23310,7 +23310,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G684" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -23336,7 +23336,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G685" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -23362,7 +23362,7 @@
         <v>15</v>
       </c>
       <c r="G686" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -23388,7 +23388,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G687" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -23414,7 +23414,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G688" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -23440,7 +23440,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G689" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -23466,7 +23466,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G690" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -23492,7 +23492,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G691" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -23518,7 +23518,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G692" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -23544,7 +23544,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G693" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -23570,7 +23570,7 @@
         <v>17.5</v>
       </c>
       <c r="G694" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -23596,7 +23596,7 @@
         <v>17.6800003051758</v>
       </c>
       <c r="G695" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -23622,7 +23622,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G696" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -23648,7 +23648,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G697" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -23674,7 +23674,7 @@
         <v>17.5</v>
       </c>
       <c r="G698" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -23700,7 +23700,7 @@
         <v>17.5</v>
       </c>
       <c r="G699" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -23726,7 +23726,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G700" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -23752,7 +23752,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G701" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -23778,7 +23778,7 @@
         <v>16.5</v>
       </c>
       <c r="G702" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -23804,7 +23804,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G703" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -23830,7 +23830,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G704" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -23856,7 +23856,7 @@
         <v>16.5</v>
       </c>
       <c r="G705" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -23882,7 +23882,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G706" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -23908,7 +23908,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G707" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -23934,7 +23934,7 @@
         <v>16</v>
       </c>
       <c r="G708" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -23960,7 +23960,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G709" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -23986,7 +23986,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G710" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -24012,7 +24012,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G711" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -24038,7 +24038,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G712" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -24064,7 +24064,7 @@
         <v>15.5</v>
       </c>
       <c r="G713" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -24090,7 +24090,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G714" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -24116,7 +24116,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G715" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -24142,7 +24142,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G716" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -24168,7 +24168,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G717" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -24194,7 +24194,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G718" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -24220,7 +24220,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G719" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -24246,7 +24246,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G720" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -24272,7 +24272,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G721" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -24298,7 +24298,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G722" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -24324,7 +24324,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G723" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -24350,7 +24350,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G724" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -24376,7 +24376,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G725" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -24402,7 +24402,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G726" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -24428,7 +24428,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G727" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -24454,7 +24454,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G728" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -24480,7 +24480,7 @@
         <v>16.5</v>
       </c>
       <c r="G729" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -24506,7 +24506,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G730" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -24532,7 +24532,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G731" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -24558,7 +24558,7 @@
         <v>16</v>
       </c>
       <c r="G732" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -24584,7 +24584,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G733" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -24610,7 +24610,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G734" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -24636,7 +24636,7 @@
         <v>17</v>
       </c>
       <c r="G735" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -24662,7 +24662,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G736" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -24688,7 +24688,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G737" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -24714,7 +24714,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G738" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -24740,7 +24740,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G739" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -24766,7 +24766,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G740" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -24792,7 +24792,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G741" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -24818,7 +24818,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G742" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -24844,7 +24844,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G743" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -24870,7 +24870,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G744" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -24896,7 +24896,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G745" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -24922,7 +24922,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G746" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -24948,7 +24948,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G747" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -24974,7 +24974,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G748" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -25000,7 +25000,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G749" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -25026,7 +25026,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G750" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -25052,7 +25052,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G751" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -25078,7 +25078,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G752" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -25104,7 +25104,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G753" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -25130,7 +25130,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G754" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -25156,7 +25156,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G755" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -25182,7 +25182,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G756" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -25208,7 +25208,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G757" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -25234,7 +25234,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G758" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -25260,7 +25260,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G759" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -25286,7 +25286,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G760" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -25312,7 +25312,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G761" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -25338,7 +25338,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G762" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -25364,7 +25364,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G763" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -25390,7 +25390,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G764" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -25416,7 +25416,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G765" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -25442,7 +25442,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G766" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -25468,7 +25468,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G767" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -25494,7 +25494,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G768" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -25520,7 +25520,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G769" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -25546,7 +25546,7 @@
         <v>16.5</v>
       </c>
       <c r="G770" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -25572,7 +25572,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G771" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -25598,7 +25598,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G772" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -25624,7 +25624,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G773" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -25650,7 +25650,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G774" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -25676,7 +25676,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G775" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -25702,7 +25702,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G776" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -25728,7 +25728,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G777" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -25754,7 +25754,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G778" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -25780,7 +25780,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G779" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -25806,7 +25806,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G780" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -25832,7 +25832,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G781" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -25858,7 +25858,7 @@
         <v>17</v>
       </c>
       <c r="G782" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -25884,7 +25884,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G783" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -25910,7 +25910,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G784" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -25936,7 +25936,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G785" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -25962,7 +25962,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G786" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -25988,7 +25988,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G787" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -26014,7 +26014,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G788" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -26040,7 +26040,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G789" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -26066,7 +26066,7 @@
         <v>16.5</v>
       </c>
       <c r="G790" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -26092,7 +26092,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G791" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -26118,7 +26118,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G792" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -26144,7 +26144,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G793" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -26170,7 +26170,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G794" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -26196,7 +26196,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G795" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -26222,7 +26222,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G796" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -26248,7 +26248,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G797" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -26274,7 +26274,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G798" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -26300,7 +26300,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G799" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -26326,7 +26326,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G800" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -26352,7 +26352,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G801" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -26378,7 +26378,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G802" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -26404,7 +26404,7 @@
         <v>16</v>
       </c>
       <c r="G803" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -26430,7 +26430,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G804" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -26456,7 +26456,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G805" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -26482,7 +26482,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G806" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -26508,7 +26508,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G807" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -26534,7 +26534,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G808" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -26560,7 +26560,7 @@
         <v>18</v>
       </c>
       <c r="G809" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -26586,7 +26586,7 @@
         <v>18.2399997711182</v>
       </c>
       <c r="G810" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -26612,7 +26612,7 @@
         <v>18.2600002288818</v>
       </c>
       <c r="G811" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -26638,7 +26638,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G812" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -26664,7 +26664,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G813" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -26690,7 +26690,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G814" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -26716,7 +26716,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G815" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -26742,7 +26742,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G816" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -26768,7 +26768,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G817" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -26794,7 +26794,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G818" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -26820,7 +26820,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G819" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -26846,7 +26846,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G820" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -26872,7 +26872,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G821" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -26898,7 +26898,7 @@
         <v>18</v>
       </c>
       <c r="G822" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -26924,7 +26924,7 @@
         <v>18</v>
       </c>
       <c r="G823" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -26950,7 +26950,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G824" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -26976,7 +26976,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G825" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -27002,7 +27002,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G826" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -27028,7 +27028,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G827" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -27054,7 +27054,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G828" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -27080,7 +27080,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G829" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -27106,7 +27106,7 @@
         <v>18.8600006103516</v>
       </c>
       <c r="G830" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -27132,7 +27132,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G831" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -27158,7 +27158,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G832" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -27184,7 +27184,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G833" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -27210,7 +27210,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G834" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -27236,7 +27236,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G835" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -27262,7 +27262,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G836" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -27288,7 +27288,7 @@
         <v>18</v>
       </c>
       <c r="G837" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -27314,7 +27314,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G838" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -27340,7 +27340,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G839" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -27366,7 +27366,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G840" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -27392,7 +27392,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G841" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -27418,7 +27418,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G842" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -27444,7 +27444,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G843" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -27470,7 +27470,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G844" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -27496,7 +27496,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G845" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -27522,7 +27522,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G846" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -27548,7 +27548,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G847" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -27574,7 +27574,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G848" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -27600,7 +27600,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G849" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -27626,7 +27626,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G850" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -27652,7 +27652,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G851" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -27678,7 +27678,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G852" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -27704,7 +27704,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G853" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -27730,7 +27730,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G854" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -27756,7 +27756,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G855" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -27782,7 +27782,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G856" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -27808,7 +27808,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G857" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -27834,7 +27834,7 @@
         <v>17.5</v>
       </c>
       <c r="G858" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -27860,7 +27860,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G859" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -27886,7 +27886,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G860" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -27912,7 +27912,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G861" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -27938,7 +27938,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G862" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -27964,7 +27964,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G863" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -27990,7 +27990,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G864" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -28016,7 +28016,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G865" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -28042,7 +28042,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G866" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -28068,7 +28068,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G867" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -28094,7 +28094,7 @@
         <v>17.1200008392334</v>
       </c>
       <c r="G868" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -28120,7 +28120,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G869" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -28146,7 +28146,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G870" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -28172,7 +28172,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G871" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -28198,7 +28198,7 @@
         <v>16.5</v>
       </c>
       <c r="G872" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -28224,7 +28224,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G873" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -28250,7 +28250,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G874" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -28276,7 +28276,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G875" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -28302,7 +28302,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G876" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -28328,7 +28328,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G877" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -28354,7 +28354,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G878" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -28380,7 +28380,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G879" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -28406,7 +28406,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G880" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -28432,7 +28432,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G881" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -28458,7 +28458,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G882" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -28484,7 +28484,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G883" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -28510,7 +28510,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G884" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -28536,7 +28536,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G885" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -28562,7 +28562,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G886" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -28588,7 +28588,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G887" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -28614,7 +28614,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G888" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -28640,7 +28640,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G889" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -28666,7 +28666,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G890" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -28692,7 +28692,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G891" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -28718,7 +28718,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G892" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -28744,7 +28744,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G893" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -28770,7 +28770,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G894" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -28796,7 +28796,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G895" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -28822,7 +28822,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G896" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -28848,7 +28848,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G897" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -28874,7 +28874,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G898" t="s">
-        <v>592</v>
+        <v>403</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -28952,7 +28952,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G901" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -29004,7 +29004,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G903" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -29134,7 +29134,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G908" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -29160,7 +29160,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G909" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -29212,7 +29212,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G911" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -29238,7 +29238,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G912" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -29290,7 +29290,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G914" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -29680,7 +29680,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G929" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -29732,7 +29732,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G931" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -29784,7 +29784,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G933" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -30070,7 +30070,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G944" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -30122,7 +30122,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G946" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -30226,7 +30226,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G950" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -30252,7 +30252,7 @@
         <v>16.5</v>
       </c>
       <c r="G951" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -30304,7 +30304,7 @@
         <v>16.5</v>
       </c>
       <c r="G953" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -30330,7 +30330,7 @@
         <v>16.5</v>
       </c>
       <c r="G954" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -30434,7 +30434,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G958" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -30486,7 +30486,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G960" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -30590,7 +30590,7 @@
         <v>16.5</v>
       </c>
       <c r="G964" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -30616,7 +30616,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G965" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -30694,7 +30694,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G968" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -30798,7 +30798,7 @@
         <v>17.5</v>
       </c>
       <c r="G972" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -30928,7 +30928,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G977" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -33164,7 +33164,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G1063" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -33606,7 +33606,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1080" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -33788,7 +33788,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G1087" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -33944,7 +33944,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G1093" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -34048,7 +34048,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G1097" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -34178,7 +34178,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G1102" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -34204,7 +34204,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1103" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -34256,7 +34256,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G1105" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -34542,7 +34542,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G1116" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -34568,7 +34568,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1117" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -71600,7 +71600,7 @@
     </row>
     <row r="2542">
       <c r="A2542" s="1" t="n">
-        <v>46024.6910185185</v>
+        <v>46024.3333333333</v>
       </c>
       <c r="B2542" t="n">
         <v>54507</v>
@@ -71609,7 +71609,7 @@
         <v>35</v>
       </c>
       <c r="D2542" t="n">
-        <v>34</v>
+        <v>33.9000015258789</v>
       </c>
       <c r="E2542" t="n">
         <v>35</v>
@@ -71621,6 +71621,32 @@
         <v>1727</v>
       </c>
       <c r="H2542" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2543">
+      <c r="A2543" s="1" t="n">
+        <v>46027.6909722222</v>
+      </c>
+      <c r="B2543" t="n">
+        <v>105244</v>
+      </c>
+      <c r="C2543" t="n">
+        <v>34.8499984741211</v>
+      </c>
+      <c r="D2543" t="n">
+        <v>34.1500015258789</v>
+      </c>
+      <c r="E2543" t="n">
+        <v>34.3499984741211</v>
+      </c>
+      <c r="F2543" t="n">
+        <v>34.6500015258789</v>
+      </c>
+      <c r="G2543" t="s">
+        <v>1726</v>
+      </c>
+      <c r="H2543" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MOL.MI.xlsx
+++ b/data/MOL.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1732" uniqueCount="1732">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1733" uniqueCount="1733">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,58 +38,58 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">6.850661277771</t>
+    <t xml:space="preserve">6.85066080093384</t>
   </si>
   <si>
     <t xml:space="preserve">MOL.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75772571563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66036558151245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77100276947021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63823890686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72674751281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81525754928589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54972791671753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31960201263428</t>
+    <t xml:space="preserve">6.75772619247437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66036462783813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77100324630737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63823795318604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72674798965454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81525707244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54972887039185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31960248947144</t>
   </si>
   <si>
     <t xml:space="preserve">6.09832811355591</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35058116912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23994398117065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5585789680481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46121883392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89475536346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52317476272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65594053268433</t>
+    <t xml:space="preserve">6.35058164596558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2399435043335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55857944488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46121835708618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8947548866272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52317523956299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65594005584717</t>
   </si>
   <si>
     <t xml:space="preserve">6.76215171813965</t>
@@ -98,148 +98,148 @@
     <t xml:space="preserve">6.66479158401489</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69134330749512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68249273300171</t>
+    <t xml:space="preserve">6.69134378433228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68249368667603</t>
   </si>
   <si>
     <t xml:space="preserve">6.01866960525513</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89918041229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28419876098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0629243850708</t>
+    <t xml:space="preserve">5.89918088912964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28419828414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06292486190796</t>
   </si>
   <si>
     <t xml:space="preserve">6.25322008132935</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39926147460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34173011779785</t>
+    <t xml:space="preserve">6.39926195144653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34172916412354</t>
   </si>
   <si>
     <t xml:space="preserve">6.50989866256714</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33287954330444</t>
+    <t xml:space="preserve">6.33287906646729</t>
   </si>
   <si>
     <t xml:space="preserve">6.42581510543823</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39040994644165</t>
+    <t xml:space="preserve">6.39041137695312</t>
   </si>
   <si>
     <t xml:space="preserve">6.30632591247559</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40811109542847</t>
+    <t xml:space="preserve">6.40811204910278</t>
   </si>
   <si>
     <t xml:space="preserve">6.35500621795654</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63381242752075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43466472625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22666788101196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24436902999878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27534770965576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26649570465088</t>
+    <t xml:space="preserve">6.63381147384644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4346661567688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2266674041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24436855316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27534818649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2664966583252</t>
   </si>
   <si>
     <t xml:space="preserve">6.62938690185547</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43909120559692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41253757476807</t>
+    <t xml:space="preserve">6.43909168243408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41253805160522</t>
   </si>
   <si>
     <t xml:space="preserve">6.45236730575562</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4567928314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36828231811523</t>
+    <t xml:space="preserve">6.45679235458374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36828279495239</t>
   </si>
   <si>
     <t xml:space="preserve">6.19568872451782</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06734895706177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28862476348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20454025268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29305028915405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24879503250122</t>
+    <t xml:space="preserve">6.06734991073608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28862380981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20453977584839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29304981231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24879455566406</t>
   </si>
   <si>
     <t xml:space="preserve">6.22224235534668</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25764560699463</t>
+    <t xml:space="preserve">6.25764608383179</t>
   </si>
   <si>
     <t xml:space="preserve">6.15585899353027</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19126272201538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58955812454224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47891998291016</t>
+    <t xml:space="preserve">6.1912636756897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58955764770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47892045974731</t>
   </si>
   <si>
     <t xml:space="preserve">6.49662256240845</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42138910293579</t>
+    <t xml:space="preserve">6.42138862609863</t>
   </si>
   <si>
     <t xml:space="preserve">6.63348913192749</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45273971557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54311418533325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44370269775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50696420669556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55667114257812</t>
+    <t xml:space="preserve">6.45274066925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54311513900757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44370317459106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50696468353271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55667066574097</t>
   </si>
   <si>
     <t xml:space="preserve">6.36688470840454</t>
@@ -248,31 +248,31 @@
     <t xml:space="preserve">6.61993265151978</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69223403930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59733963012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6831955909729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70578956604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7509765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8503885269165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94528150558472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98594999313354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10343647003174</t>
+    <t xml:space="preserve">6.69223308563232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59734010696411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68319511413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70578908920288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75097560882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85038805007935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9452805519104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9859504699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1034369468689</t>
   </si>
   <si>
     <t xml:space="preserve">7.25255393981934</t>
@@ -281,64 +281,64 @@
     <t xml:space="preserve">7.32033634185791</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45589637756348</t>
+    <t xml:space="preserve">7.45589685440063</t>
   </si>
   <si>
     <t xml:space="preserve">7.30226039886475</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37907934188843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25707387924194</t>
+    <t xml:space="preserve">7.37907886505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25707292556763</t>
   </si>
   <si>
     <t xml:space="preserve">7.22996091842651</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22544288635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19833040237427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09439849853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13958597183228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00402545928955</t>
+    <t xml:space="preserve">7.22544240951538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19832992553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09439897537231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13958692550659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00402450561523</t>
   </si>
   <si>
     <t xml:space="preserve">7.08084297180176</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95883750915527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84135103225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11699295043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16669940948486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31129741668701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32485389709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99950647354126</t>
+    <t xml:space="preserve">6.95883798599243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84135055541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11699342727661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16669845581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31129932403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32485342025757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9995059967041</t>
   </si>
   <si>
     <t xml:space="preserve">6.73290157318115</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08988094329834</t>
+    <t xml:space="preserve">7.08988046646118</t>
   </si>
   <si>
     <t xml:space="preserve">7.18477392196655</t>
@@ -347,25 +347,25 @@
     <t xml:space="preserve">6.85942602157593</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67867660522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49792814254761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57022666931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57926464080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41659116744995</t>
+    <t xml:space="preserve">6.67867708206177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49792766571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57022762298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57926511764526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41659021377563</t>
   </si>
   <si>
     <t xml:space="preserve">6.74645805358887</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65156316757202</t>
+    <t xml:space="preserve">6.65156412124634</t>
   </si>
   <si>
     <t xml:space="preserve">6.55215215682983</t>
@@ -374,13 +374,13 @@
     <t xml:space="preserve">6.46177816390991</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75549459457397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56570911407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7780876159668</t>
+    <t xml:space="preserve">6.75549507141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56570768356323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77808856964111</t>
   </si>
   <si>
     <t xml:space="preserve">6.71030807495117</t>
@@ -389,85 +389,85 @@
     <t xml:space="preserve">6.48888969421387</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53859567642212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66060161590576</t>
+    <t xml:space="preserve">6.53859615325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6606011390686</t>
   </si>
   <si>
     <t xml:space="preserve">6.68771409988403</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76001310348511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87750101089478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70127058029175</t>
+    <t xml:space="preserve">6.76001405715942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87750053405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70127010345459</t>
   </si>
   <si>
     <t xml:space="preserve">6.78712606430054</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79616355895996</t>
+    <t xml:space="preserve">6.7961630821228</t>
   </si>
   <si>
     <t xml:space="preserve">6.81423807144165</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81875705718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82327556610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80520105361938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92268800735474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90461301803589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86846303939819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98143148422241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17573690414429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01306247711182</t>
+    <t xml:space="preserve">6.81875658035278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82327604293823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80520153045654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92268753051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90461254119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86846256256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98143100738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17573595046997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01306200027466</t>
   </si>
   <si>
     <t xml:space="preserve">6.97691202163696</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64252662658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69675159454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88653755187988</t>
+    <t xml:space="preserve">6.64252614974976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69675207138062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88653802871704</t>
   </si>
   <si>
     <t xml:space="preserve">6.931725025177</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02209949493408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99046850204468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19381189346313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05824947357178</t>
+    <t xml:space="preserve">7.02209997177124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99046945571899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19381141662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05824899673462</t>
   </si>
   <si>
     <t xml:space="preserve">7.04921245574951</t>
@@ -476,109 +476,109 @@
     <t xml:space="preserve">7.0672869682312</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14862394332886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08536195755005</t>
+    <t xml:space="preserve">7.14862442016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08536243438721</t>
   </si>
   <si>
     <t xml:space="preserve">7.06276798248291</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15766143798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21188640594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38359832763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22092342376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24803686141968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18929243087769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35648679733276</t>
+    <t xml:space="preserve">7.15766191482544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21188688278198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38359689712524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22092390060425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24803590774536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18929290771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35648584365845</t>
   </si>
   <si>
     <t xml:space="preserve">7.37004137039185</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88201904296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03565549850464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18025588989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91365051269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5191593170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47849082946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50108432769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41070985794067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27514839172363</t>
+    <t xml:space="preserve">6.88201856613159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03565645217896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18025541305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91365003585815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51915979385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47849035263062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50108575820923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41070890426636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27514886856079</t>
   </si>
   <si>
     <t xml:space="preserve">7.60953330993652</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66375827789307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72702169418335</t>
+    <t xml:space="preserve">7.66375923156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72702074050903</t>
   </si>
   <si>
     <t xml:space="preserve">7.68183374404907</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67731428146362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63664674758911</t>
+    <t xml:space="preserve">7.67731475830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63664627075195</t>
   </si>
   <si>
     <t xml:space="preserve">7.77220916748047</t>
   </si>
   <si>
-    <t xml:space="preserve">7.971031665802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34156799316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41386699676514</t>
+    <t xml:space="preserve">7.97103214263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34156703948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41386795043945</t>
   </si>
   <si>
     <t xml:space="preserve">8.45001792907715</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57653999328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37771987915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40934944152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35964202880859</t>
+    <t xml:space="preserve">8.57654285430908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37771797180176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40934753417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35964298248291</t>
   </si>
   <si>
     <t xml:space="preserve">8.22408103942871</t>
@@ -587,13 +587,13 @@
     <t xml:space="preserve">8.24215602874756</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33704853057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32801246643066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32349300384521</t>
+    <t xml:space="preserve">8.33705043792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32801055908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32349395751953</t>
   </si>
   <si>
     <t xml:space="preserve">8.36416149139404</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">8.37319946289062</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46809196472168</t>
+    <t xml:space="preserve">8.46809101104736</t>
   </si>
   <si>
     <t xml:space="preserve">8.30541801452637</t>
@@ -611,13 +611,13 @@
     <t xml:space="preserve">8.30089950561523</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09755611419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26926803588867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20600605010986</t>
+    <t xml:space="preserve">8.09755516052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26926708221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20600509643555</t>
   </si>
   <si>
     <t xml:space="preserve">8.0749626159668</t>
@@ -626,10 +626,10 @@
     <t xml:space="preserve">8.11111259460449</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2828254699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29637908935547</t>
+    <t xml:space="preserve">8.28282356262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29638290405273</t>
   </si>
   <si>
     <t xml:space="preserve">8.40483093261719</t>
@@ -638,16 +638,16 @@
     <t xml:space="preserve">8.48164844512939</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4229040145874</t>
+    <t xml:space="preserve">8.42290496826172</t>
   </si>
   <si>
     <t xml:space="preserve">8.22859954833984</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2737865447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02977752685547</t>
+    <t xml:space="preserve">8.27378559112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02977466583252</t>
   </si>
   <si>
     <t xml:space="preserve">8.13370609283447</t>
@@ -656,10 +656,10 @@
     <t xml:space="preserve">8.27830600738525</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43194103240967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69402694702148</t>
+    <t xml:space="preserve">8.4319429397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69402885437012</t>
   </si>
   <si>
     <t xml:space="preserve">9.57969951629639</t>
@@ -668,100 +668,100 @@
     <t xml:space="preserve">9.25434970855713</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21820068359375</t>
+    <t xml:space="preserve">9.21820163726807</t>
   </si>
   <si>
     <t xml:space="preserve">9.01937580108643</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16397571563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2001256942749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20916366577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22723770141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94707679748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03745174407959</t>
+    <t xml:space="preserve">9.16397762298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20012664794922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2091646194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22723865509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94707870483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03745269775391</t>
   </si>
   <si>
     <t xml:space="preserve">9.1278247833252</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35376453399658</t>
+    <t xml:space="preserve">9.35376262664795</t>
   </si>
   <si>
     <t xml:space="preserve">9.55258560180664</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47124767303467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80563449859619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89600944519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2123212814331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94119739532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4472932815552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8449430465698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8087930679321</t>
+    <t xml:space="preserve">9.4712495803833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80563545227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89600849151611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2123203277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94119644165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4472951889038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8449411392212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8087911605835</t>
   </si>
   <si>
     <t xml:space="preserve">10.9082040786743</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9353170394897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7364912033081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.709379196167</t>
+    <t xml:space="preserve">10.9353151321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7364921569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7093820571899</t>
   </si>
   <si>
     <t xml:space="preserve">10.7545671463013</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4764337539673</t>
+    <t xml:space="preserve">10.476432800293</t>
   </si>
   <si>
     <t xml:space="preserve">10.2261095046997</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0128726959229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3837194442749</t>
+    <t xml:space="preserve">10.0128736495972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3837213516235</t>
   </si>
   <si>
     <t xml:space="preserve">10.4300756454468</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2817363739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4022636413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5135164260864</t>
+    <t xml:space="preserve">10.2817354202271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4022617340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5135173797607</t>
   </si>
   <si>
     <t xml:space="preserve">10.4949741363525</t>
@@ -770,22 +770,22 @@
     <t xml:space="preserve">10.5413303375244</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7452964782715</t>
+    <t xml:space="preserve">10.7452955245972</t>
   </si>
   <si>
     <t xml:space="preserve">11.0790586471558</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7743968963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5889739990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2181262969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3015651702881</t>
+    <t xml:space="preserve">11.7743949890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5889730453491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2181253433228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3015670776367</t>
   </si>
   <si>
     <t xml:space="preserve">11.0976009368896</t>
@@ -803,70 +803,70 @@
     <t xml:space="preserve">10.7545680999756</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7360248565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.986346244812</t>
+    <t xml:space="preserve">10.7360239028931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9863481521606</t>
   </si>
   <si>
     <t xml:space="preserve">10.8658208847046</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5691442489624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1254148483276</t>
+    <t xml:space="preserve">10.5691432952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1254138946533</t>
   </si>
   <si>
     <t xml:space="preserve">11.0605163574219</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4869899749756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0697870254517</t>
+    <t xml:space="preserve">11.4869909286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0697860717773</t>
   </si>
   <si>
     <t xml:space="preserve">10.9399900436401</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4499063491821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4035511016846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7094993591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0988893508911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3213958740234</t>
+    <t xml:space="preserve">11.4499053955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4035501480103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7094984054565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0988874435425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3213968276978</t>
   </si>
   <si>
     <t xml:space="preserve">11.8949222564697</t>
   </si>
   <si>
-    <t xml:space="preserve">12.516092300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5253620147705</t>
+    <t xml:space="preserve">12.5160903930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5253629684448</t>
   </si>
   <si>
     <t xml:space="preserve">12.6737003326416</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7478713989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5346336364746</t>
+    <t xml:space="preserve">12.7478704452515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5346345901489</t>
   </si>
   <si>
     <t xml:space="preserve">12.7942266464233</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7293291091919</t>
+    <t xml:space="preserve">12.7293281555176</t>
   </si>
   <si>
     <t xml:space="preserve">12.5439052581787</t>
@@ -875,16 +875,16 @@
     <t xml:space="preserve">12.5809888839722</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5624465942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4697351455688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4975481033325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4882774353027</t>
+    <t xml:space="preserve">12.5624485015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4697360992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4975490570068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4882783889771</t>
   </si>
   <si>
     <t xml:space="preserve">12.6829719543457</t>
@@ -899,43 +899,43 @@
     <t xml:space="preserve">12.1823301315308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3955659866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4233798980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2935819625854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.367751121521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8856506347656</t>
+    <t xml:space="preserve">12.395565032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.423378944397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2935829162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3677530288696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8856525421143</t>
   </si>
   <si>
     <t xml:space="preserve">12.28431224823</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1730585098267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0525321960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.95055103302</t>
+    <t xml:space="preserve">12.1730575561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0525312423706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9505491256714</t>
   </si>
   <si>
     <t xml:space="preserve">12.312123298645</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2657690048218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9412775039673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9598197937012</t>
+    <t xml:space="preserve">12.2657709121704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9412784576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9598217010498</t>
   </si>
   <si>
     <t xml:space="preserve">12.3306684494019</t>
@@ -944,40 +944,40 @@
     <t xml:space="preserve">12.4419212341309</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3492078781128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3770236968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1545143127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2472276687622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3399381637573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4511947631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.200870513916</t>
+    <t xml:space="preserve">12.3492088317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3770227432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1545152664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2472267150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3399391174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4511938095093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2008714675903</t>
   </si>
   <si>
     <t xml:space="preserve">12.4326496124268</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3028545379639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2564992904663</t>
+    <t xml:space="preserve">12.3028554916382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.256498336792</t>
   </si>
   <si>
     <t xml:space="preserve">12.0618047714233</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0247192382812</t>
+    <t xml:space="preserve">12.0247201919556</t>
   </si>
   <si>
     <t xml:space="preserve">11.440634727478</t>
@@ -989,115 +989,115 @@
     <t xml:space="preserve">11.7929391860962</t>
   </si>
   <si>
-    <t xml:space="preserve">11.663143157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6816854476929</t>
+    <t xml:space="preserve">11.6631422042847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6816864013672</t>
   </si>
   <si>
     <t xml:space="preserve">11.7465839385986</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9227352142334</t>
+    <t xml:space="preserve">11.922737121582</t>
   </si>
   <si>
     <t xml:space="preserve">11.8207530975342</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8671083450317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7373142242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2286834716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1915998458862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7651262283325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7187690734863</t>
+    <t xml:space="preserve">11.8671092987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7373113632202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2286853790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1916007995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7651252746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.718770980835</t>
   </si>
   <si>
     <t xml:space="preserve">11.1903123855591</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2922945022583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1625003814697</t>
+    <t xml:space="preserve">11.2922964096069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1624994277954</t>
   </si>
   <si>
     <t xml:space="preserve">11.5426177978516</t>
   </si>
   <si>
-    <t xml:space="preserve">11.468448638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5982446670532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5797023773193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4962615966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6724147796631</t>
+    <t xml:space="preserve">11.4684467315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5982437133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.579701423645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4962596893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6724128723145</t>
   </si>
   <si>
     <t xml:space="preserve">11.857837677002</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1452445983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0061750411987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9134645462036</t>
+    <t xml:space="preserve">12.1452436447144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.006175994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9134654998779</t>
   </si>
   <si>
     <t xml:space="preserve">12.9240226745605</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9253101348877</t>
+    <t xml:space="preserve">13.9253091812134</t>
   </si>
   <si>
     <t xml:space="preserve">14.1107349395752</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0921926498413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9438533782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9994792938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.629919052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9067668914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6286325454712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2034454345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0180225372314</t>
+    <t xml:space="preserve">14.0921907424927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9438524246216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9994802474976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6299200057983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9067678451538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6286315917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.203444480896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0180234909058</t>
   </si>
   <si>
     <t xml:space="preserve">13.7028026580811</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3888702392578</t>
+    <t xml:space="preserve">14.3888692855835</t>
   </si>
   <si>
     <t xml:space="preserve">14.518666267395</t>
@@ -1109,16 +1109,16 @@
     <t xml:space="preserve">14.4815807342529</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1849040985107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8326005935669</t>
+    <t xml:space="preserve">14.1849031448364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8325986862183</t>
   </si>
   <si>
     <t xml:space="preserve">12.9981927871704</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7756853103638</t>
+    <t xml:space="preserve">12.7756834030151</t>
   </si>
   <si>
     <t xml:space="preserve">13.3690385818481</t>
@@ -1127,34 +1127,34 @@
     <t xml:space="preserve">13.0352773666382</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7385997772217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9796485900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5173788070679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3134126663208</t>
+    <t xml:space="preserve">12.7385988235474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9796495437622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5173778533936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3134117126465</t>
   </si>
   <si>
     <t xml:space="preserve">12.6644306182861</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1081609725952</t>
+    <t xml:space="preserve">12.1081600189209</t>
   </si>
   <si>
     <t xml:space="preserve">12.0154466629028</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8300247192383</t>
+    <t xml:space="preserve">11.830023765564</t>
   </si>
   <si>
     <t xml:space="preserve">12.5902605056763</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7200574874878</t>
+    <t xml:space="preserve">12.7200565338135</t>
   </si>
   <si>
     <t xml:space="preserve">12.6088037490845</t>
@@ -1163,79 +1163,79 @@
     <t xml:space="preserve">12.1637868881226</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0339889526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0710754394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.607515335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4604635238647</t>
+    <t xml:space="preserve">12.0339879989624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0710735321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6075172424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4604644775391</t>
   </si>
   <si>
     <t xml:space="preserve">11.8114805221558</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8485660552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2379570007324</t>
+    <t xml:space="preserve">11.8485670089722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2379541397095</t>
   </si>
   <si>
     <t xml:space="preserve">12.3862943649292</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3504962921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5359210968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7213439941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2590732574463</t>
+    <t xml:space="preserve">13.3504953384399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5359230041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7213449478149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2590742111206</t>
   </si>
   <si>
     <t xml:space="preserve">14.908055305481</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7782592773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7411727905273</t>
+    <t xml:space="preserve">14.7782583236694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.741174697876</t>
   </si>
   <si>
     <t xml:space="preserve">14.7968015670776</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0235710144043</t>
+    <t xml:space="preserve">15.0235719680786</t>
   </si>
   <si>
     <t xml:space="preserve">15.684986114502</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4015235900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2314462661743</t>
+    <t xml:space="preserve">15.4015226364136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2314443588257</t>
   </si>
   <si>
     <t xml:space="preserve">15.080265045166</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1180591583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1747522354126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3070373535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1353855133057</t>
+    <t xml:space="preserve">15.1180601119995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.174750328064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.307035446167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1353845596313</t>
   </si>
   <si>
     <t xml:space="preserve">13.8141269683838</t>
@@ -1247,25 +1247,25 @@
     <t xml:space="preserve">13.6062526702881</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6818428039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0771207809448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9448385238647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1149158477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.888144493103</t>
+    <t xml:space="preserve">13.6818437576294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0771217346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9448394775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.114917755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.888147354126</t>
   </si>
   <si>
     <t xml:space="preserve">12.0944471359253</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5479879379272</t>
+    <t xml:space="preserve">12.5479898452759</t>
   </si>
   <si>
     <t xml:space="preserve">13.0015325546265</t>
@@ -1277,22 +1277,22 @@
     <t xml:space="preserve">12.6991691589355</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7558641433716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8692483901978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3401174545288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.736964225769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7180681228638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7747602462769</t>
+    <t xml:space="preserve">12.7558622360229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8692493438721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3401155471802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7369651794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7180671691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7747611999512</t>
   </si>
   <si>
     <t xml:space="preserve">12.2645254135132</t>
@@ -1304,7 +1304,7 @@
     <t xml:space="preserve">13.7763319015503</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9653081893921</t>
+    <t xml:space="preserve">13.9653072357178</t>
   </si>
   <si>
     <t xml:space="preserve">13.8708190917969</t>
@@ -1313,19 +1313,19 @@
     <t xml:space="preserve">14.0786924362183</t>
   </si>
   <si>
-    <t xml:space="preserve">13.625150680542</t>
+    <t xml:space="preserve">13.6251516342163</t>
   </si>
   <si>
     <t xml:space="preserve">13.5873565673828</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4172792434692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4550724029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4361763000488</t>
+    <t xml:space="preserve">13.4172782897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4550733566284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4361753463745</t>
   </si>
   <si>
     <t xml:space="preserve">13.247200012207</t>
@@ -1340,31 +1340,31 @@
     <t xml:space="preserve">13.473970413208</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2094039916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3605861663818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5668878555298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5101938247681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2834234237671</t>
+    <t xml:space="preserve">13.2094049453735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3605852127075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5668869018555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5101928710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2834243774414</t>
   </si>
   <si>
     <t xml:space="preserve">12.680272102356</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0393266677856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9826345443726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8125562667847</t>
+    <t xml:space="preserve">13.03932762146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9826335906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8125553131104</t>
   </si>
   <si>
     <t xml:space="preserve">12.9637365341187</t>
@@ -1373,7 +1373,7 @@
     <t xml:space="preserve">13.7952299118042</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1164884567261</t>
+    <t xml:space="preserve">14.1164875030518</t>
   </si>
   <si>
     <t xml:space="preserve">14.2676687240601</t>
@@ -1382,34 +1382,34 @@
     <t xml:space="preserve">14.3054647445679</t>
   </si>
   <si>
-    <t xml:space="preserve">14.059796333313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7007417678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4928674697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7574348449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.549560546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1731796264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9290828704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4960107803345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2692394256592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1558570861816</t>
+    <t xml:space="preserve">14.0597953796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.700740814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4928693771362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.757435798645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5495615005493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1731805801392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.929084777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4960098266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2692403793335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.155855178833</t>
   </si>
   <si>
     <t xml:space="preserve">16.5353775024414</t>
@@ -1418,10 +1418,10 @@
     <t xml:space="preserve">16.7054557800293</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9133281707764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6298656463623</t>
+    <t xml:space="preserve">16.9133319854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6298675537109</t>
   </si>
   <si>
     <t xml:space="preserve">16.2330188751221</t>
@@ -1430,58 +1430,58 @@
     <t xml:space="preserve">15.9117555618286</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5904970169067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5149078369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.004674911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2125473022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3810548782349</t>
+    <t xml:space="preserve">15.5904989242554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5149087905884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0046730041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2125492095947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3810558319092</t>
   </si>
   <si>
     <t xml:space="preserve">14.6078252792358</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4377479553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6456212997437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2487707138062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1920785903931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8897171020508</t>
+    <t xml:space="preserve">14.4377460479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.645622253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2487716674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1920795440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8897180557251</t>
   </si>
   <si>
     <t xml:space="preserve">13.5306625366211</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8519229888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0220012664795</t>
+    <t xml:space="preserve">13.8519220352173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0220003128052</t>
   </si>
   <si>
     <t xml:space="preserve">14.8723907470703</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4755420684814</t>
+    <t xml:space="preserve">14.4755411148071</t>
   </si>
   <si>
     <t xml:space="preserve">14.418848991394</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5527038574219</t>
+    <t xml:space="preserve">15.5527057647705</t>
   </si>
   <si>
     <t xml:space="preserve">14.9668788909912</t>
@@ -1493,103 +1493,103 @@
     <t xml:space="preserve">16.0629386901855</t>
   </si>
   <si>
-    <t xml:space="preserve">16.251916885376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.044038772583</t>
+    <t xml:space="preserve">16.2519130706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0440406799316</t>
   </si>
   <si>
     <t xml:space="preserve">15.8739624023438</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4582176208496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0251426696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.346399307251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1007347106934</t>
+    <t xml:space="preserve">15.4582166671753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0251407623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3464012145996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.100736618042</t>
   </si>
   <si>
     <t xml:space="preserve">16.3275051116943</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6471929550171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7983722686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9306564331055</t>
+    <t xml:space="preserve">15.6471910476685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7983713150024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9306554794312</t>
   </si>
   <si>
     <t xml:space="preserve">15.0613670349121</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8550662994385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4771108627319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7401084899902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9101858139038</t>
+    <t xml:space="preserve">15.8550653457642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4771137237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7401075363159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9101867675781</t>
   </si>
   <si>
     <t xml:space="preserve">14.5511322021484</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8156986236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9857769012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5338048934937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7416791915894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0424709320068</t>
+    <t xml:space="preserve">14.8156995773315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9857778549194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5338087081909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.741678237915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0424680709839</t>
   </si>
   <si>
     <t xml:space="preserve">15.4204216003418</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7605762481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6282949447632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8928575515747</t>
+    <t xml:space="preserve">15.7605781555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6282968521118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8928594589233</t>
   </si>
   <si>
     <t xml:space="preserve">15.9684505462646</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0062484741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9873476028442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6093950271606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6834144592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6267223358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8534936904907</t>
+    <t xml:space="preserve">16.0062465667725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9873466491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6093988418579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6834163665771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6267213821411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.853494644165</t>
   </si>
   <si>
     <t xml:space="preserve">15.1936502456665</t>
@@ -1598,64 +1598,64 @@
     <t xml:space="preserve">15.0991621017456</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2881364822388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1952209472656</t>
+    <t xml:space="preserve">15.2881383895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.195219039917</t>
   </si>
   <si>
     <t xml:space="preserve">17.0078163146973</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2345905303955</t>
+    <t xml:space="preserve">17.2345886230469</t>
   </si>
   <si>
     <t xml:space="preserve">17.2534866333008</t>
   </si>
   <si>
-    <t xml:space="preserve">17.29128074646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1023044586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0645084381104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0471839904785</t>
+    <t xml:space="preserve">17.2912788391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1023063659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.064510345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0471820831299</t>
   </si>
   <si>
     <t xml:space="preserve">17.4046669006348</t>
   </si>
   <si>
-    <t xml:space="preserve">17.347972869873</t>
+    <t xml:space="preserve">17.3479709625244</t>
   </si>
   <si>
     <t xml:space="preserve">17.366870880127</t>
   </si>
   <si>
-    <t xml:space="preserve">17.499153137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0456104278564</t>
+    <t xml:space="preserve">17.4991550445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0456142425537</t>
   </si>
   <si>
     <t xml:space="preserve">17.3857688903809</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4424610137939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8582077026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8204135894775</t>
+    <t xml:space="preserve">17.4424629211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8582096099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8204116821289</t>
   </si>
   <si>
     <t xml:space="preserve">17.5558471679688</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3290786743164</t>
+    <t xml:space="preserve">17.3290767669678</t>
   </si>
   <si>
     <t xml:space="preserve">17.140100479126</t>
@@ -1664,16 +1664,16 @@
     <t xml:space="preserve">16.5731735229492</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5920677185059</t>
+    <t xml:space="preserve">16.5920696258545</t>
   </si>
   <si>
     <t xml:space="preserve">16.2897071838379</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8566360473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1574268341064</t>
+    <t xml:space="preserve">16.8566398620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1574249267578</t>
   </si>
   <si>
     <t xml:space="preserve">16.5805950164795</t>
@@ -1691,13 +1691,13 @@
     <t xml:space="preserve">16.2343673706055</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0035457611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9843130111694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6767749786377</t>
+    <t xml:space="preserve">16.0035438537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9843101501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6767730712891</t>
   </si>
   <si>
     <t xml:space="preserve">16.8114166259766</t>
@@ -1706,88 +1706,88 @@
     <t xml:space="preserve">16.8306522369385</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7537136077881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6383018493652</t>
+    <t xml:space="preserve">16.7537117004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6382999420166</t>
   </si>
   <si>
     <t xml:space="preserve">16.4267158508301</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5228939056396</t>
+    <t xml:space="preserve">16.522891998291</t>
   </si>
   <si>
     <t xml:space="preserve">15.945839881897</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4651870727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9650745391846</t>
+    <t xml:space="preserve">16.4651889801025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9650774002075</t>
   </si>
   <si>
     <t xml:space="preserve">16.0227813720703</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8688983917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7342557907104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6573171615601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4264965057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3687896728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3110857009888</t>
+    <t xml:space="preserve">15.8689012527466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7342567443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6573181152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.426495552063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3687906265259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3110837936401</t>
   </si>
   <si>
     <t xml:space="preserve">14.9840898513794</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1956748962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2341461181641</t>
+    <t xml:space="preserve">15.1956739425659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2341451644897</t>
   </si>
   <si>
     <t xml:space="preserve">15.1379690170288</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0994987487793</t>
+    <t xml:space="preserve">15.0994997024536</t>
   </si>
   <si>
     <t xml:space="preserve">15.003324508667</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1187353134155</t>
+    <t xml:space="preserve">15.1187343597412</t>
   </si>
   <si>
     <t xml:space="preserve">15.253378868103</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0610294342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8686800003052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8494443893433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7147998809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4457302093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.176438331604</t>
+    <t xml:space="preserve">15.0610284805298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8686790466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8494434356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7147989273071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4457292556763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1764402389526</t>
   </si>
   <si>
     <t xml:space="preserve">14.8302087783813</t>
@@ -1808,7 +1808,7 @@
     <t xml:space="preserve">14.9071493148804</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0225582122803</t>
+    <t xml:space="preserve">15.0225591659546</t>
   </si>
   <si>
     <t xml:space="preserve">14.8109741210938</t>
@@ -1817,103 +1817,103 @@
     <t xml:space="preserve">14.8879137039185</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5416831970215</t>
+    <t xml:space="preserve">14.5416822433472</t>
   </si>
   <si>
     <t xml:space="preserve">14.580153465271</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5993881225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5032138824463</t>
+    <t xml:space="preserve">14.5993900299072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5032119750977</t>
   </si>
   <si>
     <t xml:space="preserve">14.6378593444824</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6186237335205</t>
+    <t xml:space="preserve">14.6186227798462</t>
   </si>
   <si>
     <t xml:space="preserve">14.4647445678711</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4455080032349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.65709400177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.926383972168</t>
+    <t xml:space="preserve">14.4455089569092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6570930480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9263830184937</t>
   </si>
   <si>
     <t xml:space="preserve">14.5609188079834</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3495559692383</t>
+    <t xml:space="preserve">15.349555015564</t>
   </si>
   <si>
     <t xml:space="preserve">15.3880252838135</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6765508651733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.522668838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7150211334229</t>
+    <t xml:space="preserve">15.676549911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5226697921753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7150192260742</t>
   </si>
   <si>
     <t xml:space="preserve">15.7919597625732</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1574249267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7727251052856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8111944198608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9073715209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6380815505981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6188468933105</t>
+    <t xml:space="preserve">16.1574230194092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7727241516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8111972808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9073734283447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6380786895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6188449859619</t>
   </si>
   <si>
     <t xml:space="preserve">15.8496646881104</t>
   </si>
   <si>
-    <t xml:space="preserve">15.580376625061</t>
+    <t xml:space="preserve">15.5803756713867</t>
   </si>
   <si>
     <t xml:space="preserve">15.5034351348877</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8304290771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9266052246094</t>
+    <t xml:space="preserve">15.8304309844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9266061782837</t>
   </si>
   <si>
     <t xml:space="preserve">16.1189556121826</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1576461791992</t>
+    <t xml:space="preserve">17.1576480865479</t>
   </si>
   <si>
     <t xml:space="preserve">17.0037689208984</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9460639953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.888355255127</t>
+    <t xml:space="preserve">16.9460620880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8883533477783</t>
   </si>
   <si>
     <t xml:space="preserve">16.9845333099365</t>
@@ -1925,7 +1925,7 @@
     <t xml:space="preserve">17.2730560302734</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2732772827148</t>
+    <t xml:space="preserve">18.2732810974121</t>
   </si>
   <si>
     <t xml:space="preserve">18.1771030426025</t>
@@ -1934,16 +1934,16 @@
     <t xml:space="preserve">17.6000537872314</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6577587127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1001625061035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9847564697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1193962097168</t>
+    <t xml:space="preserve">17.6577568054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1001644134521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9847545623779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1193981170654</t>
   </si>
   <si>
     <t xml:space="preserve">17.9655170440674</t>
@@ -1952,55 +1952,55 @@
     <t xml:space="preserve">17.9462833404541</t>
   </si>
   <si>
-    <t xml:space="preserve">18.061695098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9270477294922</t>
+    <t xml:space="preserve">18.0616931915283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9270496368408</t>
   </si>
   <si>
     <t xml:space="preserve">18.3117504119873</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7541561126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1003856658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0234470367432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5425701141357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9657421112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9080371856689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4273834228516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.812084197998</t>
+    <t xml:space="preserve">18.7541542053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1003875732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0234451293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5425720214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9657382965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9080333709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4273815155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8120822906494</t>
   </si>
   <si>
     <t xml:space="preserve">19.5235557556152</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6678199768066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2831172943115</t>
+    <t xml:space="preserve">19.6678218841553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2831192016602</t>
   </si>
   <si>
     <t xml:space="preserve">18.8503303527832</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6197338104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7159061431885</t>
+    <t xml:space="preserve">19.6197319030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7159099578857</t>
   </si>
   <si>
     <t xml:space="preserve">19.7639942169189</t>
@@ -2012,7 +2012,7 @@
     <t xml:space="preserve">19.5716438293457</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1967811584473</t>
+    <t xml:space="preserve">20.1967849731445</t>
   </si>
   <si>
     <t xml:space="preserve">20.2448692321777</t>
@@ -2021,16 +2021,16 @@
     <t xml:space="preserve">22.2164611816406</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1585350036621</t>
+    <t xml:space="preserve">21.1585330963135</t>
   </si>
   <si>
     <t xml:space="preserve">21.1104469299316</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8219203948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6295700073242</t>
+    <t xml:space="preserve">20.8219223022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6295719146729</t>
   </si>
   <si>
     <t xml:space="preserve">21.0142726898193</t>
@@ -2039,10 +2039,10 @@
     <t xml:space="preserve">20.7257442474365</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6776599884033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9563465118408</t>
+    <t xml:space="preserve">20.6776561737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9563446044922</t>
   </si>
   <si>
     <t xml:space="preserve">20.2929573059082</t>
@@ -2051,13 +2051,13 @@
     <t xml:space="preserve">20.004430770874</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8601684570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0811500549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.773832321167</t>
+    <t xml:space="preserve">19.8601703643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0811519622803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7738342285156</t>
   </si>
   <si>
     <t xml:space="preserve">20.9180965423584</t>
@@ -2066,7 +2066,7 @@
     <t xml:space="preserve">20.5814838409424</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2547073364258</t>
+    <t xml:space="preserve">21.2547130584717</t>
   </si>
   <si>
     <t xml:space="preserve">21.3989715576172</t>
@@ -2078,16 +2078,16 @@
     <t xml:space="preserve">21.6394100189209</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4470596313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8317623138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0525245666504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1006050109863</t>
+    <t xml:space="preserve">21.447057723999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8317604064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0525207519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.100606918335</t>
   </si>
   <si>
     <t xml:space="preserve">18.7349185943604</t>
@@ -2096,76 +2096,76 @@
     <t xml:space="preserve">18.1963386535645</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6192874908447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3113040924072</t>
+    <t xml:space="preserve">17.6192893981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3113059997559</t>
   </si>
   <si>
     <t xml:space="preserve">16.1958961486816</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4839792251587</t>
+    <t xml:space="preserve">14.4839782714844</t>
   </si>
   <si>
     <t xml:space="preserve">14.4262733459473</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4642992019653</t>
+    <t xml:space="preserve">12.4643001556396</t>
   </si>
   <si>
     <t xml:space="preserve">12.0218944549561</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1373052597046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6951208114624</t>
+    <t xml:space="preserve">12.1373043060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6951198577881</t>
   </si>
   <si>
     <t xml:space="preserve">12.9067058563232</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9834251403809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.310640335083</t>
+    <t xml:space="preserve">11.9834241867065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.310643196106</t>
   </si>
   <si>
     <t xml:space="preserve">13.5606966018677</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0223369598389</t>
+    <t xml:space="preserve">14.0223379135132</t>
   </si>
   <si>
     <t xml:space="preserve">14.1954526901245</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2916269302368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1185131072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.734034538269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0992784500122</t>
+    <t xml:space="preserve">14.2916278839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1185121536255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7340335845947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0992774963379</t>
   </si>
   <si>
     <t xml:space="preserve">15.4072599411011</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8691215515137</t>
+    <t xml:space="preserve">16.8691234588623</t>
   </si>
   <si>
     <t xml:space="preserve">16.1766605377197</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2151336669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4649658203125</t>
+    <t xml:space="preserve">16.2151298522949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4649648666382</t>
   </si>
   <si>
     <t xml:space="preserve">16.0612525939941</t>
@@ -2183,28 +2183,28 @@
     <t xml:space="preserve">17.215353012085</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7152423858643</t>
+    <t xml:space="preserve">16.7152404785156</t>
   </si>
   <si>
     <t xml:space="preserve">16.9268264770508</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0614700317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2540416717529</t>
+    <t xml:space="preserve">17.0614719390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2540435791016</t>
   </si>
   <si>
     <t xml:space="preserve">18.638744354248</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0774517059326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7677745819092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4580974578857</t>
+    <t xml:space="preserve">18.0774536132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7677764892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4580993652344</t>
   </si>
   <si>
     <t xml:space="preserve">17.4387435913086</t>
@@ -2213,31 +2213,31 @@
     <t xml:space="preserve">17.2064838409424</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9548721313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4193897247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6129360198975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1677742004395</t>
+    <t xml:space="preserve">16.954870223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4193859100342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6129379272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1677761077881</t>
   </si>
   <si>
     <t xml:space="preserve">17.651647567749</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4968090057373</t>
+    <t xml:space="preserve">17.4968070983887</t>
   </si>
   <si>
     <t xml:space="preserve">17.7290668487549</t>
   </si>
   <si>
-    <t xml:space="preserve">18.290355682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9419746398926</t>
+    <t xml:space="preserve">18.2903575897217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9419708251953</t>
   </si>
   <si>
     <t xml:space="preserve">18.0580978393555</t>
@@ -2246,31 +2246,31 @@
     <t xml:space="preserve">18.3871307373047</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4064884185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9032611846924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2322902679443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2516498565674</t>
+    <t xml:space="preserve">18.4064865112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9032573699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2322940826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2516479492188</t>
   </si>
   <si>
     <t xml:space="preserve">18.5806827545166</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4451942443848</t>
+    <t xml:space="preserve">18.445198059082</t>
   </si>
   <si>
     <t xml:space="preserve">18.1161632537842</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0387439727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8322925567627</t>
+    <t xml:space="preserve">18.038745880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8322944641113</t>
   </si>
   <si>
     <t xml:space="preserve">18.7742290496826</t>
@@ -2285,13 +2285,13 @@
     <t xml:space="preserve">19.0451984405518</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5968132019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3548755645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9484233856201</t>
+    <t xml:space="preserve">19.5968112945557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3548736572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9484252929688</t>
   </si>
   <si>
     <t xml:space="preserve">19.1032619476318</t>
@@ -2300,28 +2300,28 @@
     <t xml:space="preserve">18.4645500183105</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6581020355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5000381469727</t>
+    <t xml:space="preserve">18.6581001281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.500036239624</t>
   </si>
   <si>
     <t xml:space="preserve">19.6451988220215</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0806846618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3226184844971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6129398345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5645542144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0484275817871</t>
+    <t xml:space="preserve">20.0806827545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3226203918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.612943649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5645561218262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0484294891357</t>
   </si>
   <si>
     <t xml:space="preserve">21.2903633117676</t>
@@ -2333,13 +2333,13 @@
     <t xml:space="preserve">21.1935901641846</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5806865692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8710117340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.532299041748</t>
+    <t xml:space="preserve">21.5806884765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8710098266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5323009490967</t>
   </si>
   <si>
     <t xml:space="preserve">21.3387489318848</t>
@@ -2348,10 +2348,10 @@
     <t xml:space="preserve">21.7742347717285</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4516563415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9355278015137</t>
+    <t xml:space="preserve">22.4516582489014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9355297088623</t>
   </si>
   <si>
     <t xml:space="preserve">22.7903652191162</t>
@@ -2360,37 +2360,37 @@
     <t xml:space="preserve">23.3226261138916</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4194030761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0968227386475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7258529663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4839172363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0484352111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7581100463867</t>
+    <t xml:space="preserve">23.4194011688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0968189239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.72585105896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4839191436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.048433303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7581081390381</t>
   </si>
   <si>
     <t xml:space="preserve">23.95166015625</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6613349914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7419776916504</t>
+    <t xml:space="preserve">23.6613368988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.741979598999</t>
   </si>
   <si>
     <t xml:space="preserve">23.0323028564453</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4677867889404</t>
+    <t xml:space="preserve">23.4677886962891</t>
   </si>
   <si>
     <t xml:space="preserve">23.0806903839111</t>
@@ -2399,52 +2399,52 @@
     <t xml:space="preserve">22.8871402740479</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5484275817871</t>
+    <t xml:space="preserve">22.5484313964844</t>
   </si>
   <si>
     <t xml:space="preserve">21.8226222991943</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0645561218262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2419757843018</t>
+    <t xml:space="preserve">22.0645599365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2419776916504</t>
   </si>
   <si>
     <t xml:space="preserve">21.6290740966797</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4677791595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3871364593506</t>
+    <t xml:space="preserve">20.4677829742432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3871383666992</t>
   </si>
   <si>
     <t xml:space="preserve">21.0968170166016</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4839115142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2097206115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9677867889404</t>
+    <t xml:space="preserve">21.4839134216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2097225189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9677848815918</t>
   </si>
   <si>
     <t xml:space="preserve">20.9516544342041</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1129474639893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3548831939697</t>
+    <t xml:space="preserve">22.1129455566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3548812866211</t>
   </si>
   <si>
     <t xml:space="preserve">21.919397354126</t>
   </si>
   <si>
-    <t xml:space="preserve">22.838752746582</t>
+    <t xml:space="preserve">22.8387546539307</t>
   </si>
   <si>
     <t xml:space="preserve">22.6452045440674</t>
@@ -2459,73 +2459,73 @@
     <t xml:space="preserve">24.241979598999</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7419834136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1774711608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0000495910645</t>
+    <t xml:space="preserve">25.7419853210449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1774673461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0000514984131</t>
   </si>
   <si>
     <t xml:space="preserve">26.661340713501</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6129550933838</t>
+    <t xml:space="preserve">26.6129531860352</t>
   </si>
   <si>
     <t xml:space="preserve">26.3710193634033</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6774749755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6452178955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.903284072876</t>
+    <t xml:space="preserve">27.6774711608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6452159881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9032821655273</t>
   </si>
   <si>
     <t xml:space="preserve">28.9355392456055</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7581233978271</t>
+    <t xml:space="preserve">29.7581214904785</t>
   </si>
   <si>
     <t xml:space="preserve">30.3871536254883</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9194145202637</t>
+    <t xml:space="preserve">30.9194164276123</t>
   </si>
   <si>
     <t xml:space="preserve">31.7419948577881</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0323181152344</t>
+    <t xml:space="preserve">32.0323143005371</t>
   </si>
   <si>
     <t xml:space="preserve">31.5484485626221</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0807113647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2581233978271</t>
+    <t xml:space="preserve">32.0807075500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2581253051758</t>
   </si>
   <si>
     <t xml:space="preserve">32.1774787902832</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3226470947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2903900146484</t>
+    <t xml:space="preserve">32.3226432800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2903861999512</t>
   </si>
   <si>
     <t xml:space="preserve">33.1936111450195</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8065185546875</t>
+    <t xml:space="preserve">32.8065147399902</t>
   </si>
   <si>
     <t xml:space="preserve">33.4839363098145</t>
@@ -2537,13 +2537,13 @@
     <t xml:space="preserve">34.1129722595215</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7420043945312</t>
+    <t xml:space="preserve">34.742000579834</t>
   </si>
   <si>
     <t xml:space="preserve">34.5968399047852</t>
   </si>
   <si>
-    <t xml:space="preserve">35.371036529541</t>
+    <t xml:space="preserve">35.3710403442383</t>
   </si>
   <si>
     <t xml:space="preserve">35.4678115844727</t>
@@ -2558,10 +2558,10 @@
     <t xml:space="preserve">36.1936225891113</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3065147399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.564582824707</t>
+    <t xml:space="preserve">34.3065223693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5645790100098</t>
   </si>
   <si>
     <t xml:space="preserve">32.6613540649414</t>
@@ -2570,40 +2570,40 @@
     <t xml:space="preserve">32.758129119873</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7097396850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9355411529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3387660980225</t>
+    <t xml:space="preserve">32.7097434997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9355430603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3387699127197</t>
   </si>
   <si>
     <t xml:space="preserve">30.8226413726807</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5807037353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4839286804199</t>
+    <t xml:space="preserve">30.5807056427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4839305877686</t>
   </si>
   <si>
     <t xml:space="preserve">31.112964630127</t>
   </si>
   <si>
-    <t xml:space="preserve">33.435546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8710327148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2742614746094</t>
+    <t xml:space="preserve">33.4355506896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8710289001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2742652893066</t>
   </si>
   <si>
     <t xml:space="preserve">35.6613616943359</t>
   </si>
   <si>
-    <t xml:space="preserve">35.7097511291504</t>
+    <t xml:space="preserve">35.7097434997559</t>
   </si>
   <si>
     <t xml:space="preserve">37.2581367492676</t>
@@ -2615,7 +2615,7 @@
     <t xml:space="preserve">36.9678115844727</t>
   </si>
   <si>
-    <t xml:space="preserve">35.9516868591309</t>
+    <t xml:space="preserve">35.9516830444336</t>
   </si>
   <si>
     <t xml:space="preserve">36.4355545043945</t>
@@ -2624,7 +2624,7 @@
     <t xml:space="preserve">35.0807151794434</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9839363098145</t>
+    <t xml:space="preserve">34.9839401245117</t>
   </si>
   <si>
     <t xml:space="preserve">36.677490234375</t>
@@ -2633,10 +2633,10 @@
     <t xml:space="preserve">37.064582824707</t>
   </si>
   <si>
-    <t xml:space="preserve">37.6452369689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.0323333740234</t>
+    <t xml:space="preserve">37.6452331542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.0323295593262</t>
   </si>
   <si>
     <t xml:space="preserve">38.6129760742188</t>
@@ -2645,52 +2645,52 @@
     <t xml:space="preserve">38.7581367492676</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8226623535156</t>
+    <t xml:space="preserve">39.8226585388184</t>
   </si>
   <si>
     <t xml:space="preserve">39.6774940490723</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5645942687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.7097511291504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6291084289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4516868591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.1613693237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4355583190918</t>
+    <t xml:space="preserve">38.5645904541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.7097473144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6291046142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4516906738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.1613655090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4355621337891</t>
   </si>
   <si>
     <t xml:space="preserve">40.2581405639648</t>
   </si>
   <si>
-    <t xml:space="preserve">44.0807304382324</t>
+    <t xml:space="preserve">44.0807266235352</t>
   </si>
   <si>
     <t xml:space="preserve">41.9033088684082</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0645980834961</t>
+    <t xml:space="preserve">40.0645942687988</t>
   </si>
   <si>
     <t xml:space="preserve">41.1774978637695</t>
   </si>
   <si>
-    <t xml:space="preserve">41.8549194335938</t>
+    <t xml:space="preserve">41.8549156188965</t>
   </si>
   <si>
     <t xml:space="preserve">42.3387908935547</t>
   </si>
   <si>
-    <t xml:space="preserve">42.0484657287598</t>
+    <t xml:space="preserve">42.048469543457</t>
   </si>
   <si>
     <t xml:space="preserve">42.6291122436523</t>
@@ -2702,22 +2702,22 @@
     <t xml:space="preserve">42.3871803283691</t>
   </si>
   <si>
-    <t xml:space="preserve">43.5000839233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.1291122436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.7097663879395</t>
+    <t xml:space="preserve">43.5000877380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.1291198730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.7097625732422</t>
   </si>
   <si>
     <t xml:space="preserve">44.7581520080566</t>
   </si>
   <si>
-    <t xml:space="preserve">45.6775054931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.4194412231445</t>
+    <t xml:space="preserve">45.6775093078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.4194450378418</t>
   </si>
   <si>
     <t xml:space="preserve">45.0000877380371</t>
@@ -2726,7 +2726,7 @@
     <t xml:space="preserve">46.0162200927734</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4839553833008</t>
+    <t xml:space="preserve">45.483959197998</t>
   </si>
   <si>
     <t xml:space="preserve">44.9516983032227</t>
@@ -2735,43 +2735,43 @@
     <t xml:space="preserve">46.2581520080566</t>
   </si>
   <si>
-    <t xml:space="preserve">45.1452484130859</t>
+    <t xml:space="preserve">45.1452522277832</t>
   </si>
   <si>
     <t xml:space="preserve">44.6129875183105</t>
   </si>
   <si>
-    <t xml:space="preserve">44.5162200927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.274284362793</t>
+    <t xml:space="preserve">44.5162162780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2742767333984</t>
   </si>
   <si>
     <t xml:space="preserve">43.838794708252</t>
   </si>
   <si>
-    <t xml:space="preserve">43.1613731384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.3065299987793</t>
+    <t xml:space="preserve">43.161376953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.3065338134766</t>
   </si>
   <si>
     <t xml:space="preserve">43.2581481933594</t>
   </si>
   <si>
-    <t xml:space="preserve">42.8710479736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.0645980834961</t>
+    <t xml:space="preserve">42.8710517883301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.0646018981934</t>
   </si>
   <si>
     <t xml:space="preserve">44.0323448181152</t>
   </si>
   <si>
-    <t xml:space="preserve">43.4033088684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4355697631836</t>
+    <t xml:space="preserve">43.4033050537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4355621337891</t>
   </si>
   <si>
     <t xml:space="preserve">41.8992881774902</t>
@@ -2783,13 +2783,13 @@
     <t xml:space="preserve">39.799446105957</t>
   </si>
   <si>
-    <t xml:space="preserve">39.4576034545898</t>
+    <t xml:space="preserve">39.4576110839844</t>
   </si>
   <si>
     <t xml:space="preserve">40.0924415588379</t>
   </si>
   <si>
-    <t xml:space="preserve">40.8737831115723</t>
+    <t xml:space="preserve">40.873779296875</t>
   </si>
   <si>
     <t xml:space="preserve">39.9947738647461</t>
@@ -2804,7 +2804,7 @@
     <t xml:space="preserve">40.190113067627</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8971099853516</t>
+    <t xml:space="preserve">39.8971061706543</t>
   </si>
   <si>
     <t xml:space="preserve">39.6529388427734</t>
@@ -2819,22 +2819,22 @@
     <t xml:space="preserve">39.2622680664062</t>
   </si>
   <si>
-    <t xml:space="preserve">40.2877807617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9459457397461</t>
+    <t xml:space="preserve">40.2877731323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9459419250488</t>
   </si>
   <si>
     <t xml:space="preserve">37.8949279785156</t>
   </si>
   <si>
-    <t xml:space="preserve">36.7229156494141</t>
+    <t xml:space="preserve">36.7229194641113</t>
   </si>
   <si>
     <t xml:space="preserve">37.6019248962402</t>
   </si>
   <si>
-    <t xml:space="preserve">38.090259552002</t>
+    <t xml:space="preserve">38.0902633666992</t>
   </si>
   <si>
     <t xml:space="preserve">39.5552711486816</t>
@@ -2843,13 +2843,13 @@
     <t xml:space="preserve">41.7039566040039</t>
   </si>
   <si>
-    <t xml:space="preserve">42.0946197509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.459789276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0691146850586</t>
+    <t xml:space="preserve">42.0946235656738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4597854614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0691184997559</t>
   </si>
   <si>
     <t xml:space="preserve">40.3854446411133</t>
@@ -2858,7 +2858,7 @@
     <t xml:space="preserve">40.4342803955078</t>
   </si>
   <si>
-    <t xml:space="preserve">42.1922950744629</t>
+    <t xml:space="preserve">42.1922912597656</t>
   </si>
   <si>
     <t xml:space="preserve">42.0457916259766</t>
@@ -2870,19 +2870,19 @@
     <t xml:space="preserve">41.4109535217285</t>
   </si>
   <si>
-    <t xml:space="preserve">42.7294578552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3664817810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4153137207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.196647644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.8569946289062</t>
+    <t xml:space="preserve">42.7294616699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3664779663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4153099060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1966514587402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.8569984436035</t>
   </si>
   <si>
     <t xml:space="preserve">47.31982421875</t>
@@ -2897,7 +2897,7 @@
     <t xml:space="preserve">48.5895004272461</t>
   </si>
   <si>
-    <t xml:space="preserve">48.8336715698242</t>
+    <t xml:space="preserve">48.833667755127</t>
   </si>
   <si>
     <t xml:space="preserve">48.1988296508789</t>
@@ -2906,7 +2906,7 @@
     <t xml:space="preserve">49.7126770019531</t>
   </si>
   <si>
-    <t xml:space="preserve">49.9080123901367</t>
+    <t xml:space="preserve">49.9080085754395</t>
   </si>
   <si>
     <t xml:space="preserve">49.8103446960449</t>
@@ -2921,28 +2921,28 @@
     <t xml:space="preserve">51.3730201721191</t>
   </si>
   <si>
-    <t xml:space="preserve">50.2986793518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.5916786193848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4940185546875</t>
+    <t xml:space="preserve">50.2986831665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.591682434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4940147399902</t>
   </si>
   <si>
     <t xml:space="preserve">51.2753524780273</t>
   </si>
   <si>
-    <t xml:space="preserve">50.2010154724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.7870178222656</t>
+    <t xml:space="preserve">50.2010116577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.7870140075684</t>
   </si>
   <si>
     <t xml:space="preserve">50.9823532104492</t>
   </si>
   <si>
-    <t xml:space="preserve">51.8613548278809</t>
+    <t xml:space="preserve">51.8613586425781</t>
   </si>
   <si>
     <t xml:space="preserve">51.9590263366699</t>
@@ -2954,28 +2954,28 @@
     <t xml:space="preserve">45.2688140869141</t>
   </si>
   <si>
-    <t xml:space="preserve">44.5363082885742</t>
+    <t xml:space="preserve">44.536304473877</t>
   </si>
   <si>
     <t xml:space="preserve">43.5107955932617</t>
   </si>
   <si>
-    <t xml:space="preserve">44.2433013916016</t>
+    <t xml:space="preserve">44.2433052062988</t>
   </si>
   <si>
     <t xml:space="preserve">44.2921371459961</t>
   </si>
   <si>
-    <t xml:space="preserve">44.9269790649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.047966003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8037948608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.4386444091797</t>
+    <t xml:space="preserve">44.9269752502441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.0479698181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8037986755371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.4386405944824</t>
   </si>
   <si>
     <t xml:space="preserve">43.9503021240234</t>
@@ -2984,13 +2984,13 @@
     <t xml:space="preserve">44.1944694519043</t>
   </si>
   <si>
-    <t xml:space="preserve">41.2156219482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.9714508056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.7527885437012</t>
+    <t xml:space="preserve">41.2156181335449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.9714469909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.7527923583984</t>
   </si>
   <si>
     <t xml:space="preserve">42.2899589538574</t>
@@ -2999,7 +2999,7 @@
     <t xml:space="preserve">43.0712928771973</t>
   </si>
   <si>
-    <t xml:space="preserve">43.2666282653809</t>
+    <t xml:space="preserve">43.2666320800781</t>
   </si>
   <si>
     <t xml:space="preserve">43.7061347961426</t>
@@ -3008,16 +3008,16 @@
     <t xml:space="preserve">44.3409729003906</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4641456604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.0989875793457</t>
+    <t xml:space="preserve">45.4641494750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.0989837646484</t>
   </si>
   <si>
     <t xml:space="preserve">45.659481048584</t>
   </si>
   <si>
-    <t xml:space="preserve">45.7571487426758</t>
+    <t xml:space="preserve">45.7571411132812</t>
   </si>
   <si>
     <t xml:space="preserve">42.7782974243164</t>
@@ -3032,7 +3032,7 @@
     <t xml:space="preserve">43.1201324462891</t>
   </si>
   <si>
-    <t xml:space="preserve">42.4364585876465</t>
+    <t xml:space="preserve">42.4364624023438</t>
   </si>
   <si>
     <t xml:space="preserve">41.508617401123</t>
@@ -3041,7 +3041,7 @@
     <t xml:space="preserve">41.0202827453613</t>
   </si>
   <si>
-    <t xml:space="preserve">38.8715972900391</t>
+    <t xml:space="preserve">38.8716011047363</t>
   </si>
   <si>
     <t xml:space="preserve">38.2367668151855</t>
@@ -3059,7 +3059,7 @@
     <t xml:space="preserve">41.8504524230957</t>
   </si>
   <si>
-    <t xml:space="preserve">41.1179504394531</t>
+    <t xml:space="preserve">41.1179466247559</t>
   </si>
   <si>
     <t xml:space="preserve">40.8249473571777</t>
@@ -3074,19 +3074,19 @@
     <t xml:space="preserve">42.485294342041</t>
   </si>
   <si>
-    <t xml:space="preserve">42.9736251831055</t>
+    <t xml:space="preserve">42.9736289978027</t>
   </si>
   <si>
     <t xml:space="preserve">41.8016204833984</t>
   </si>
   <si>
-    <t xml:space="preserve">41.362117767334</t>
+    <t xml:space="preserve">41.3621215820312</t>
   </si>
   <si>
     <t xml:space="preserve">40.2389450073242</t>
   </si>
   <si>
-    <t xml:space="preserve">40.6296157836914</t>
+    <t xml:space="preserve">40.6296119689941</t>
   </si>
   <si>
     <t xml:space="preserve">42.8759651184082</t>
@@ -3095,13 +3095,13 @@
     <t xml:space="preserve">43.4619674682617</t>
   </si>
   <si>
-    <t xml:space="preserve">43.9991340637207</t>
+    <t xml:space="preserve">43.999137878418</t>
   </si>
   <si>
     <t xml:space="preserve">40.9226188659668</t>
   </si>
   <si>
-    <t xml:space="preserve">39.1157646179199</t>
+    <t xml:space="preserve">39.1157684326172</t>
   </si>
   <si>
     <t xml:space="preserve">42.5829582214355</t>
@@ -3113,10 +3113,10 @@
     <t xml:space="preserve">38.5785980224609</t>
   </si>
   <si>
-    <t xml:space="preserve">36.4299163818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6274299621582</t>
+    <t xml:space="preserve">36.4299125671387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6274337768555</t>
   </si>
   <si>
     <t xml:space="preserve">37.1135902404785</t>
@@ -3125,7 +3125,7 @@
     <t xml:space="preserve">35.7950820922852</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7207336425781</t>
+    <t xml:space="preserve">34.7207374572754</t>
   </si>
   <si>
     <t xml:space="preserve">35.5997467041016</t>
@@ -3134,10 +3134,10 @@
     <t xml:space="preserve">36.527587890625</t>
   </si>
   <si>
-    <t xml:space="preserve">36.6252517700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.0880851745605</t>
+    <t xml:space="preserve">36.6252555847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.0880813598633</t>
   </si>
   <si>
     <t xml:space="preserve">36.1369132995605</t>
@@ -3158,13 +3158,13 @@
     <t xml:space="preserve">33.9393997192383</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1325607299805</t>
+    <t xml:space="preserve">32.1325569152832</t>
   </si>
   <si>
     <t xml:space="preserve">31.4977169036865</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6442203521729</t>
+    <t xml:space="preserve">31.6442184448242</t>
   </si>
   <si>
     <t xml:space="preserve">33.0115623474121</t>
@@ -3173,10 +3173,10 @@
     <t xml:space="preserve">32.3767280578613</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4510650634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7695693969727</t>
+    <t xml:space="preserve">33.4510612487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7695732116699</t>
   </si>
   <si>
     <t xml:space="preserve">34.5742416381836</t>
@@ -3209,7 +3209,7 @@
     <t xml:space="preserve">31.4488849639893</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6697273254395</t>
+    <t xml:space="preserve">32.6697235107422</t>
   </si>
   <si>
     <t xml:space="preserve">32.767391204834</t>
@@ -3218,13 +3218,13 @@
     <t xml:space="preserve">31.2144813537598</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0191478729248</t>
+    <t xml:space="preserve">31.0191459655762</t>
   </si>
   <si>
     <t xml:space="preserve">30.9019451141357</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6518077850342</t>
+    <t xml:space="preserve">29.6518058776855</t>
   </si>
   <si>
     <t xml:space="preserve">30.4722099304199</t>
@@ -3233,10 +3233,10 @@
     <t xml:space="preserve">32.2302207946777</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0739517211914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9372215270996</t>
+    <t xml:space="preserve">32.0739555358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.937219619751</t>
   </si>
   <si>
     <t xml:space="preserve">31.3316841125488</t>
@@ -3248,22 +3248,22 @@
     <t xml:space="preserve">31.3902816772461</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6637516021729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8862056732178</t>
+    <t xml:space="preserve">31.6637496948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8862037658691</t>
   </si>
   <si>
     <t xml:space="preserve">29.9643402099609</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3821277618408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4993305206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2025356292725</t>
+    <t xml:space="preserve">28.3821296691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4993324279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2025337219238</t>
   </si>
   <si>
     <t xml:space="preserve">28.8704662322998</t>
@@ -3284,7 +3284,7 @@
     <t xml:space="preserve">27.0147857666016</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3235263824463</t>
+    <t xml:space="preserve">28.3235282897949</t>
   </si>
   <si>
     <t xml:space="preserve">28.5969982147217</t>
@@ -3293,7 +3293,7 @@
     <t xml:space="preserve">28.2258625030518</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5579299926758</t>
+    <t xml:space="preserve">28.5579280853271</t>
   </si>
   <si>
     <t xml:space="preserve">28.1816463470459</t>
@@ -3305,31 +3305,31 @@
     <t xml:space="preserve">26.5972957611084</t>
   </si>
   <si>
-    <t xml:space="preserve">26.676513671875</t>
+    <t xml:space="preserve">26.6765117645264</t>
   </si>
   <si>
     <t xml:space="preserve">26.8745555877686</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5281009674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4784698486328</t>
+    <t xml:space="preserve">27.5280990600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4784679412842</t>
   </si>
   <si>
     <t xml:space="preserve">26.7359256744385</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2508392333984</t>
+    <t xml:space="preserve">27.2508411407471</t>
   </si>
   <si>
     <t xml:space="preserve">28.0628204345703</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3994960784912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3202781677246</t>
+    <t xml:space="preserve">28.3994941711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.320276260376</t>
   </si>
   <si>
     <t xml:space="preserve">27.765754699707</t>
@@ -3341,7 +3341,7 @@
     <t xml:space="preserve">28.4193000793457</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0134296417236</t>
+    <t xml:space="preserve">29.013427734375</t>
   </si>
   <si>
     <t xml:space="preserve">29.1124515533447</t>
@@ -3353,7 +3353,7 @@
     <t xml:space="preserve">29.1322574615479</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9933815002441</t>
+    <t xml:space="preserve">26.9933834075928</t>
   </si>
   <si>
     <t xml:space="preserve">24.9931392669678</t>
@@ -3368,19 +3368,19 @@
     <t xml:space="preserve">24.4584217071533</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4288368225098</t>
+    <t xml:space="preserve">25.4288349151611</t>
   </si>
   <si>
     <t xml:space="preserve">25.6070766448975</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4684429168701</t>
+    <t xml:space="preserve">25.4684448242188</t>
   </si>
   <si>
     <t xml:space="preserve">24.8148994445801</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2902050018311</t>
+    <t xml:space="preserve">25.2902069091797</t>
   </si>
   <si>
     <t xml:space="preserve">25.3694229125977</t>
@@ -3404,7 +3404,7 @@
     <t xml:space="preserve">23.547420501709</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2009620666504</t>
+    <t xml:space="preserve">24.200963973999</t>
   </si>
   <si>
     <t xml:space="preserve">23.6068325042725</t>
@@ -3428,13 +3428,13 @@
     <t xml:space="preserve">22.9532890319824</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4188098907471</t>
+    <t xml:space="preserve">24.4188117980957</t>
   </si>
   <si>
     <t xml:space="preserve">23.7058544158936</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7356834411621</t>
+    <t xml:space="preserve">24.7356815338135</t>
   </si>
   <si>
     <t xml:space="preserve">24.597053527832</t>
@@ -3449,7 +3449,7 @@
     <t xml:space="preserve">25.8249244689941</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0823822021484</t>
+    <t xml:space="preserve">26.0823802947998</t>
   </si>
   <si>
     <t xml:space="preserve">26.1615982055664</t>
@@ -3458,31 +3458,31 @@
     <t xml:space="preserve">25.3892269134521</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1317691802979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5674667358398</t>
+    <t xml:space="preserve">25.1317672729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5674648284912</t>
   </si>
   <si>
     <t xml:space="preserve">26.0427722930908</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1417922973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8843364715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4882488250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5178356170654</t>
+    <t xml:space="preserve">26.1417942047119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.884334564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4882469177246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5178337097168</t>
   </si>
   <si>
     <t xml:space="preserve">24.0227241516113</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2207679748535</t>
+    <t xml:space="preserve">24.2207660675049</t>
   </si>
   <si>
     <t xml:space="preserve">24.1217479705811</t>
@@ -3497,22 +3497,22 @@
     <t xml:space="preserve">24.2603778839111</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3593978881836</t>
+    <t xml:space="preserve">24.3593997955322</t>
   </si>
   <si>
     <t xml:space="preserve">23.626636505127</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4980278015137</t>
+    <t xml:space="preserve">24.4980297088623</t>
   </si>
   <si>
     <t xml:space="preserve">23.8642902374268</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9435081481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7850723266602</t>
+    <t xml:space="preserve">23.9435062408447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7850704193115</t>
   </si>
   <si>
     <t xml:space="preserve">24.8743133544922</t>
@@ -3524,7 +3524,7 @@
     <t xml:space="preserve">24.2999877929688</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7652645111084</t>
+    <t xml:space="preserve">23.765266418457</t>
   </si>
   <si>
     <t xml:space="preserve">22.8344593048096</t>
@@ -3533,7 +3533,7 @@
     <t xml:space="preserve">22.5571994781494</t>
   </si>
   <si>
-    <t xml:space="preserve">22.715633392334</t>
+    <t xml:space="preserve">22.7156352996826</t>
   </si>
   <si>
     <t xml:space="preserve">22.0422859191895</t>
@@ -3542,7 +3542,7 @@
     <t xml:space="preserve">21.071870803833</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1212577819824</t>
+    <t xml:space="preserve">20.1212596893311</t>
   </si>
   <si>
     <t xml:space="preserve">19.8638019561768</t>
@@ -3551,7 +3551,7 @@
     <t xml:space="preserve">20.0618476867676</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2696685791016</t>
+    <t xml:space="preserve">19.2696704864502</t>
   </si>
   <si>
     <t xml:space="preserve">19.8836078643799</t>
@@ -3566,7 +3566,7 @@
     <t xml:space="preserve">20.9926528930664</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2501106262207</t>
+    <t xml:space="preserve">21.2501087188721</t>
   </si>
   <si>
     <t xml:space="preserve">21.2897186279297</t>
@@ -3578,19 +3578,19 @@
     <t xml:space="preserve">20.8540210723877</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3887424468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6065883636475</t>
+    <t xml:space="preserve">21.3887405395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6065902709961</t>
   </si>
   <si>
     <t xml:space="preserve">22.0026760101318</t>
   </si>
   <si>
-    <t xml:space="preserve">22.200719833374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6660003662109</t>
+    <t xml:space="preserve">22.2007217407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6660022735596</t>
   </si>
   <si>
     <t xml:space="preserve">21.5075664520264</t>
@@ -3605,7 +3605,7 @@
     <t xml:space="preserve">22.1809158325195</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4383735656738</t>
+    <t xml:space="preserve">22.4383716583252</t>
   </si>
   <si>
     <t xml:space="preserve">21.7848281860352</t>
@@ -3623,7 +3623,7 @@
     <t xml:space="preserve">23.6662445068359</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1415500640869</t>
+    <t xml:space="preserve">24.1415481567383</t>
   </si>
   <si>
     <t xml:space="preserve">25.7457065582275</t>
@@ -3632,22 +3632,22 @@
     <t xml:space="preserve">27.0329895019531</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6369018554688</t>
+    <t xml:space="preserve">26.6369037628174</t>
   </si>
   <si>
     <t xml:space="preserve">26.5576858520508</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9831123352051</t>
+    <t xml:space="preserve">23.9831142425537</t>
   </si>
   <si>
     <t xml:space="preserve">25.0525531768799</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2505950927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2012062072754</t>
+    <t xml:space="preserve">25.2505970001221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.201208114624</t>
   </si>
   <si>
     <t xml:space="preserve">26.4190540313721</t>
@@ -3674,10 +3674,10 @@
     <t xml:space="preserve">22.9730930328369</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7950954437256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2704029083252</t>
+    <t xml:space="preserve">24.7950973510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2704010009766</t>
   </si>
   <si>
     <t xml:space="preserve">26.1219882965088</t>
@@ -3686,7 +3686,7 @@
     <t xml:space="preserve">26.0625743865967</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7853164672852</t>
+    <t xml:space="preserve">25.7853145599365</t>
   </si>
   <si>
     <t xml:space="preserve">26.2606220245361</t>
@@ -3698,7 +3698,7 @@
     <t xml:space="preserve">26.795337677002</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0232105255127</t>
+    <t xml:space="preserve">28.0232086181641</t>
   </si>
   <si>
     <t xml:space="preserve">27.5875148773193</t>
@@ -3716,16 +3716,16 @@
     <t xml:space="preserve">28.2212543487549</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5777339935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.280668258667</t>
+    <t xml:space="preserve">28.5777320861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2806701660156</t>
   </si>
   <si>
     <t xml:space="preserve">28.8153858184814</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8747997283936</t>
+    <t xml:space="preserve">28.8747978210449</t>
   </si>
   <si>
     <t xml:space="preserve">28.7163639068604</t>
@@ -3761,7 +3761,7 @@
     <t xml:space="preserve">29.5877571105957</t>
   </si>
   <si>
-    <t xml:space="preserve">29.33030128479</t>
+    <t xml:space="preserve">29.3303031921387</t>
   </si>
   <si>
     <t xml:space="preserve">29.4491271972656</t>
@@ -3782,13 +3782,13 @@
     <t xml:space="preserve">27.805362701416</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3004703521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4787120819092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0430145263672</t>
+    <t xml:space="preserve">28.3004722595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4787139892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0430164337158</t>
   </si>
   <si>
     <t xml:space="preserve">27.6469268798828</t>
@@ -3809,10 +3809,10 @@
     <t xml:space="preserve">24.4782257080078</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3097667694092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3789615631104</t>
+    <t xml:space="preserve">23.3097686767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3789596557617</t>
   </si>
   <si>
     <t xml:space="preserve">24.280179977417</t>
@@ -3821,13 +3821,13 @@
     <t xml:space="preserve">24.5574417114258</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8347053527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0921611785889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8447265625</t>
+    <t xml:space="preserve">24.8347034454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0921630859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8447284698486</t>
   </si>
   <si>
     <t xml:space="preserve">26.3893489837646</t>
@@ -3851,7 +3851,7 @@
     <t xml:space="preserve">27.77565574646</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6766357421875</t>
+    <t xml:space="preserve">27.6766338348389</t>
   </si>
   <si>
     <t xml:space="preserve">27.4290790557861</t>
@@ -3860,19 +3860,19 @@
     <t xml:space="preserve">27.1815242767334</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9339694976807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3795680999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8844566345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7261447906494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9834823608398</t>
+    <t xml:space="preserve">26.9339714050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.379566192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8844585418701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7261428833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9834804534912</t>
   </si>
   <si>
     <t xml:space="preserve">27.330057144165</t>
@@ -3884,7 +3884,7 @@
     <t xml:space="preserve">27.9241886138916</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4688110351562</t>
+    <t xml:space="preserve">28.4688091278076</t>
   </si>
   <si>
     <t xml:space="preserve">29.5085391998291</t>
@@ -3899,13 +3899,13 @@
     <t xml:space="preserve">30.944356918335</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0831146240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6375122070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1821327209473</t>
+    <t xml:space="preserve">32.0831108093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6375141143799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1821365356445</t>
   </si>
   <si>
     <t xml:space="preserve">32.9247970581055</t>
@@ -3914,7 +3914,7 @@
     <t xml:space="preserve">32.4296875</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2316398620605</t>
+    <t xml:space="preserve">32.2316436767578</t>
   </si>
   <si>
     <t xml:space="preserve">31.9840888977051</t>
@@ -3923,10 +3923,10 @@
     <t xml:space="preserve">31.1919136047363</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3404445648193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.795825958252</t>
+    <t xml:space="preserve">31.340446472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7958240509033</t>
   </si>
   <si>
     <t xml:space="preserve">30.6472949981689</t>
@@ -3938,7 +3938,7 @@
     <t xml:space="preserve">30.3997383117676</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2512054443359</t>
+    <t xml:space="preserve">30.2512035369873</t>
   </si>
   <si>
     <t xml:space="preserve">30.5977802276611</t>
@@ -5208,6 +5208,9 @@
   </si>
   <si>
     <t xml:space="preserve">36.0499992370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.4500007629395</t>
   </si>
 </sst>
 </file>
@@ -71794,7 +71797,7 @@
     </row>
     <row r="2549">
       <c r="A2549" s="1" t="n">
-        <v>46035.6913078704</v>
+        <v>46035.3333333333</v>
       </c>
       <c r="B2549" t="n">
         <v>91361</v>
@@ -71815,6 +71818,32 @@
         <v>1731</v>
       </c>
       <c r="H2549" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2550">
+      <c r="A2550" s="1" t="n">
+        <v>46036.6916550926</v>
+      </c>
+      <c r="B2550" t="n">
+        <v>98836</v>
+      </c>
+      <c r="C2550" t="n">
+        <v>37.6500015258789</v>
+      </c>
+      <c r="D2550" t="n">
+        <v>36.25</v>
+      </c>
+      <c r="E2550" t="n">
+        <v>36.2999992370605</v>
+      </c>
+      <c r="F2550" t="n">
+        <v>37.4500007629395</v>
+      </c>
+      <c r="G2550" t="s">
+        <v>1732</v>
+      </c>
+      <c r="H2550" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MOL.MI.xlsx
+++ b/data/MOL.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1737" uniqueCount="1737">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1738" uniqueCount="1738">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">6.850661277771</t>
+    <t xml:space="preserve">6.85066175460815</t>
   </si>
   <si>
     <t xml:space="preserve">MOL.MI</t>
@@ -47,22 +47,22 @@
     <t xml:space="preserve">6.75772619247437</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66036605834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77100324630737</t>
+    <t xml:space="preserve">6.66036558151245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77100276947021</t>
   </si>
   <si>
     <t xml:space="preserve">6.63823843002319</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72674751281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81525802612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54972791671753</t>
+    <t xml:space="preserve">6.72674798965454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81525754928589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54972839355469</t>
   </si>
   <si>
     <t xml:space="preserve">6.31960296630859</t>
@@ -77,322 +77,322 @@
     <t xml:space="preserve">6.23994398117065</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5585789680481</t>
+    <t xml:space="preserve">6.55857849121094</t>
   </si>
   <si>
     <t xml:space="preserve">6.46121835708618</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89475536346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52317523956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65593957901001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76215124130249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66479063034058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69134426116943</t>
+    <t xml:space="preserve">5.89475584030151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52317476272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65594053268433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76215076446533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66479158401489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69134330749512</t>
   </si>
   <si>
     <t xml:space="preserve">6.68249320983887</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01867008209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89918041229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28419876098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06292390823364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2532205581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39926147460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34173059463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5098991394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33287954330444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42581415176392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39041042327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30632638931274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40811204910278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3550066947937</t>
+    <t xml:space="preserve">6.01866912841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89918088912964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28419780731201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0629243850708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25322008132935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39926099777222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34173011779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50989818572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33287858963013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42581510543823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39041137695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30632543563843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40811252593994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35500574111938</t>
   </si>
   <si>
     <t xml:space="preserve">6.63381195068359</t>
   </si>
   <si>
+    <t xml:space="preserve">6.43466472625732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22666692733765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24436902999878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27534770965576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26649618148804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62938690185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43909120559692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41253757476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45236682891846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4567928314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36828374862671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19568824768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06734943389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28862476348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20453977584839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29304933547974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24879503250122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22224235534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25764560699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15585851669312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19126462936401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58955764770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47892045974731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49662256240845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42138910293579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63348960876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45273971557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54311466217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44370317459106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50696468353271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55667209625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36688423156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61993312835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69223308563232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59733963012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6831955909729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70578861236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75097608566284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85038805007935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94528150558472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98595094680786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1034369468689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25255489349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32033634185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45589733123779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30225992202759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37907934188843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25707387924194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22996044158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22544193267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19832992553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09439897537231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13958644866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00402498245239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08084297180176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95883750915527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84135150909424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11699295043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16669893264771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31129837036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32485389709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9995059967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73290157318115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08988046646118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18477344512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85942602157593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67867708206177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49792814254761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57022666931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57926511764526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41659021377563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74645757675171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65156507492065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55215263366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46177816390991</t>
+  </si>
+  <si>
     <t xml:space="preserve">6.43466520309448</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22666692733765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24436902999878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2753472328186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2664966583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62938690185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43909025192261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41253709793091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45236825942993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4567928314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36828279495239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19568824768066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06734895706177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28862380981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20453977584839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29304933547974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24879455566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22224283218384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25764608383179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15585994720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19126319885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58955717086792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47892045974731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49662208557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42138910293579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63348913192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45274066925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54311466217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44370269775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50696516036987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55667114257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36688423156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61993312835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69223213195801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59733963012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68319606781006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70578908920288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75097560882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85038805007935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94528102874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9859504699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10343742370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25255441665649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32033538818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45589780807495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30226135253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37907886505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25707244873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22996091842651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22544240951538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19832992553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09439897537231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13958644866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00402498245239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08084392547607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95883798599243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84135103225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11699247360229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16669893264771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31129837036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32485389709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9995059967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73290157318115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08987998962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18477344512939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85942554473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67867660522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49792766571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57022714614868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57926464080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41659021377563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74645757675171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65156412124634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55215215682983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46177816390991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43466472625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75549507141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56570863723755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77808904647827</t>
+    <t xml:space="preserve">6.75549459457397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56570816040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77808856964111</t>
   </si>
   <si>
     <t xml:space="preserve">6.71030759811401</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48889017105103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53859567642212</t>
+    <t xml:space="preserve">6.48888921737671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53859615325928</t>
   </si>
   <si>
     <t xml:space="preserve">6.66060161590576</t>
@@ -401,34 +401,34 @@
     <t xml:space="preserve">6.68771409988403</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76001405715942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87750101089478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70127010345459</t>
+    <t xml:space="preserve">6.76001358032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87750053405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70127058029175</t>
   </si>
   <si>
     <t xml:space="preserve">6.78712606430054</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7961630821228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81423807144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81875705718994</t>
+    <t xml:space="preserve">6.79616403579712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81423854827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8187575340271</t>
   </si>
   <si>
     <t xml:space="preserve">6.82327604293823</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80520009994507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92268705368042</t>
+    <t xml:space="preserve">6.80520105361938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92268753051758</t>
   </si>
   <si>
     <t xml:space="preserve">6.90461254119873</t>
@@ -437,28 +437,28 @@
     <t xml:space="preserve">6.86846303939819</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98143148422241</t>
+    <t xml:space="preserve">6.98143100738525</t>
   </si>
   <si>
     <t xml:space="preserve">7.17573642730713</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01306247711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97691249847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64252710342407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6967511177063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88653802871704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93172550201416</t>
+    <t xml:space="preserve">7.01306295394897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97691202163696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64252662658691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69675064086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88653755187988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.931725025177</t>
   </si>
   <si>
     <t xml:space="preserve">7.02209949493408</t>
@@ -470,88 +470,88 @@
     <t xml:space="preserve">7.19381141662598</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05824995040894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04921245574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06728744506836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1486234664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08536195755005</t>
+    <t xml:space="preserve">7.05824851989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04921197891235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06728792190552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14862394332886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08536243438721</t>
   </si>
   <si>
     <t xml:space="preserve">7.06276845932007</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15766191482544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21188640594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38359689712524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22092390060425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24803686141968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18929290771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35648632049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37004232406616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88201904296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0356559753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18025541305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91365051269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51915979385376</t>
+    <t xml:space="preserve">7.15766143798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21188592910767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38359785079956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22092342376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24803638458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18929243087769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35648536682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.370041847229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88201856613159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03565549850464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18025493621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91365098953247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51916027069092</t>
   </si>
   <si>
     <t xml:space="preserve">7.47849082946777</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50108528137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41070985794067</t>
+    <t xml:space="preserve">7.50108480453491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41070938110352</t>
   </si>
   <si>
     <t xml:space="preserve">7.27514839172363</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60953521728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66375827789307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72702121734619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68183326721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67731618881226</t>
+    <t xml:space="preserve">7.60953426361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66375732421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72702169418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68183469772339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67731475830078</t>
   </si>
   <si>
     <t xml:space="preserve">7.63664674758911</t>
@@ -563,28 +563,28 @@
     <t xml:space="preserve">7.97103214263916</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34156799316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41386699676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45001697540283</t>
+    <t xml:space="preserve">8.34156703948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41386795043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45001792907715</t>
   </si>
   <si>
     <t xml:space="preserve">8.57654094696045</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37771701812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.409348487854</t>
+    <t xml:space="preserve">8.37771606445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40934944152832</t>
   </si>
   <si>
     <t xml:space="preserve">8.35964298248291</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22408199310303</t>
+    <t xml:space="preserve">8.22408008575439</t>
   </si>
   <si>
     <t xml:space="preserve">8.24215602874756</t>
@@ -599,37 +599,37 @@
     <t xml:space="preserve">8.32349300384521</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36416149139404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37319946289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46809101104736</t>
+    <t xml:space="preserve">8.36416053771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37319755554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.468092918396</t>
   </si>
   <si>
     <t xml:space="preserve">8.30541801452637</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30089855194092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09755516052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26926708221436</t>
+    <t xml:space="preserve">8.30089950561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09755706787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26926898956299</t>
   </si>
   <si>
     <t xml:space="preserve">8.20600605010986</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07496166229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11111259460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2828254699707</t>
+    <t xml:space="preserve">8.07496356964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11111354827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28282451629639</t>
   </si>
   <si>
     <t xml:space="preserve">8.2963809967041</t>
@@ -638,25 +638,25 @@
     <t xml:space="preserve">8.40482997894287</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48164939880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4229040145874</t>
+    <t xml:space="preserve">8.48164749145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42290592193604</t>
   </si>
   <si>
     <t xml:space="preserve">8.22859954833984</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27378845214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02977657318115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13370513916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27830505371094</t>
+    <t xml:space="preserve">8.2737865447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02977561950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13370609283447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27830600738525</t>
   </si>
   <si>
     <t xml:space="preserve">8.4319429397583</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">8.69402885437012</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5797004699707</t>
+    <t xml:space="preserve">9.57969760894775</t>
   </si>
   <si>
     <t xml:space="preserve">9.25434970855713</t>
@@ -674,46 +674,46 @@
     <t xml:space="preserve">9.21820068359375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01937484741211</t>
+    <t xml:space="preserve">9.01937675476074</t>
   </si>
   <si>
     <t xml:space="preserve">9.16397571563721</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20012664794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20916271209717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22723865509033</t>
+    <t xml:space="preserve">9.20012474060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20916175842285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22723770141602</t>
   </si>
   <si>
     <t xml:space="preserve">8.94707679748535</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03745079040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12782573699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35376358032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55258655548096</t>
+    <t xml:space="preserve">9.03745174407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12782669067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35376071929932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55258369445801</t>
   </si>
   <si>
     <t xml:space="preserve">9.47124767303467</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80563545227051</t>
+    <t xml:space="preserve">9.80563449859619</t>
   </si>
   <si>
     <t xml:space="preserve">9.89600849151611</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2123193740845</t>
+    <t xml:space="preserve">10.2123212814331</t>
   </si>
   <si>
     <t xml:space="preserve">9.94119548797607</t>
@@ -722,19 +722,19 @@
     <t xml:space="preserve">10.4472942352295</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8449411392212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8087930679321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9082040786743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9353160858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7364921569824</t>
+    <t xml:space="preserve">10.8449420928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8087911605835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.908203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9353151321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7364931106567</t>
   </si>
   <si>
     <t xml:space="preserve">10.7093801498413</t>
@@ -743,76 +743,76 @@
     <t xml:space="preserve">10.7545671463013</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4764308929443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2261095046997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0128717422485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3837184906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4300756454468</t>
+    <t xml:space="preserve">10.4764318466187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.226110458374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0128736495972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3837203979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4300765991211</t>
   </si>
   <si>
     <t xml:space="preserve">10.2817373275757</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4022617340088</t>
+    <t xml:space="preserve">10.4022626876831</t>
   </si>
   <si>
     <t xml:space="preserve">10.5135164260864</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4949731826782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5413284301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7452974319458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0790586471558</t>
+    <t xml:space="preserve">10.4949741363525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5413303375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7452964782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0790576934814</t>
   </si>
   <si>
     <t xml:space="preserve">11.7743968963623</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5889739990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2181262969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3015661239624</t>
+    <t xml:space="preserve">11.5889749526978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2181253433228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3015651702881</t>
   </si>
   <si>
     <t xml:space="preserve">11.0976009368896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1439561843872</t>
+    <t xml:space="preserve">11.1439571380615</t>
   </si>
   <si>
     <t xml:space="preserve">11.0327024459839</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8287372589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7360248565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9863471984863</t>
+    <t xml:space="preserve">10.8287363052368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7360258102417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.986346244812</t>
   </si>
   <si>
     <t xml:space="preserve">10.8658218383789</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5691442489624</t>
+    <t xml:space="preserve">10.5691432952881</t>
   </si>
   <si>
     <t xml:space="preserve">11.1254138946533</t>
@@ -821,7 +821,7 @@
     <t xml:space="preserve">11.0605163574219</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4869899749756</t>
+    <t xml:space="preserve">11.4869909286499</t>
   </si>
   <si>
     <t xml:space="preserve">11.069787979126</t>
@@ -830,91 +830,91 @@
     <t xml:space="preserve">10.9399909973145</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4499063491821</t>
+    <t xml:space="preserve">11.4499053955078</t>
   </si>
   <si>
     <t xml:space="preserve">11.4035491943359</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7095003128052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0988903045654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3213968276978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8949203491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5160903930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5253620147705</t>
+    <t xml:space="preserve">11.7094993591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0988893508911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3213977813721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.894923210144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5160913467407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5253629684448</t>
   </si>
   <si>
     <t xml:space="preserve">12.6737003326416</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7478713989258</t>
+    <t xml:space="preserve">12.7478723526001</t>
   </si>
   <si>
     <t xml:space="preserve">12.5346345901489</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7942266464233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7293281555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5439033508301</t>
+    <t xml:space="preserve">12.7942276000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7293272018433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5439052581787</t>
   </si>
   <si>
     <t xml:space="preserve">12.5809888839722</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5624465942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4697351455688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4975481033325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4882783889771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.68297290802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6273460388184</t>
+    <t xml:space="preserve">12.5624475479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4697341918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4975490570068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4882793426514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6829719543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.627345085144</t>
   </si>
   <si>
     <t xml:space="preserve">12.5531759262085</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1823282241821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3955659866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4233779907227</t>
+    <t xml:space="preserve">12.1823291778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.395565032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.423378944397</t>
   </si>
   <si>
     <t xml:space="preserve">12.2935838699341</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3677530288696</t>
+    <t xml:space="preserve">12.367751121521</t>
   </si>
   <si>
     <t xml:space="preserve">11.8856506347656</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2843112945557</t>
+    <t xml:space="preserve">12.2843132019043</t>
   </si>
   <si>
     <t xml:space="preserve">12.1730575561523</t>
@@ -923,22 +923,22 @@
     <t xml:space="preserve">12.0525321960449</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9505500793457</t>
+    <t xml:space="preserve">11.9505491256714</t>
   </si>
   <si>
     <t xml:space="preserve">12.3121252059937</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2657699584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.941276550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9598197937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3306674957275</t>
+    <t xml:space="preserve">12.2657690048218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9412775039673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9598188400269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3306684494019</t>
   </si>
   <si>
     <t xml:space="preserve">12.4419221878052</t>
@@ -950,31 +950,31 @@
     <t xml:space="preserve">12.3770236968994</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1545143127441</t>
+    <t xml:space="preserve">12.1545133590698</t>
   </si>
   <si>
     <t xml:space="preserve">12.2472267150879</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3399391174316</t>
+    <t xml:space="preserve">12.339940071106</t>
   </si>
   <si>
     <t xml:space="preserve">12.451192855835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2008695602417</t>
+    <t xml:space="preserve">12.200870513916</t>
   </si>
   <si>
     <t xml:space="preserve">12.4326505661011</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3028554916382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2564992904663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.061803817749</t>
+    <t xml:space="preserve">12.3028545379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.256498336792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0618028640747</t>
   </si>
   <si>
     <t xml:space="preserve">12.0247192382812</t>
@@ -989,223 +989,223 @@
     <t xml:space="preserve">11.7929401397705</t>
   </si>
   <si>
-    <t xml:space="preserve">11.663143157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6816844940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7465829849243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9227342605591</t>
+    <t xml:space="preserve">11.6631422042847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6816854476929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7465839385986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9227352142334</t>
   </si>
   <si>
     <t xml:space="preserve">11.8207530975342</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8671102523804</t>
+    <t xml:space="preserve">11.8671083450317</t>
   </si>
   <si>
     <t xml:space="preserve">11.7373123168945</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2286834716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1915979385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7651243209839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7187690734863</t>
+    <t xml:space="preserve">12.228684425354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1915988922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7651252746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7187700271606</t>
   </si>
   <si>
     <t xml:space="preserve">11.1903123855591</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2922954559326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1624984741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5426177978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.468448638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5982456207275</t>
+    <t xml:space="preserve">11.2922964096069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1624994277954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5426168441772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4684467315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5982446670532</t>
   </si>
   <si>
     <t xml:space="preserve">11.5797023773193</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4962615966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6724138259888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8578386306763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.145245552063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0061769485474</t>
+    <t xml:space="preserve">11.496262550354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6724128723145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.857837677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1452445983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.006175994873</t>
   </si>
   <si>
     <t xml:space="preserve">11.9134645462036</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9240236282349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9253101348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1107349395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.092191696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9438514709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9994802474976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6299200057983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9067687988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6286334991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.203444480896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0180225372314</t>
+    <t xml:space="preserve">12.9240226745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.925311088562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1107339859009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0921907424927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9438524246216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9994792938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6299180984497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9067678451538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6286315917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2034454345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0180215835571</t>
   </si>
   <si>
     <t xml:space="preserve">13.7028017044067</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3888692855835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5186653137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.574294090271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4815816879272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1849040985107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8325996398926</t>
+    <t xml:space="preserve">14.3888702392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.518666267395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5742931365967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4815797805786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1849031448364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8325977325439</t>
   </si>
   <si>
     <t xml:space="preserve">12.9981927871704</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7756843566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3690395355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0352792739868</t>
+    <t xml:space="preserve">12.7756853103638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3690385818481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0352773666382</t>
   </si>
   <si>
     <t xml:space="preserve">12.7385988235474</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9796495437622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5173807144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3134126663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6644287109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1081609725952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0154476165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8300256729126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5902605056763</t>
+    <t xml:space="preserve">12.9796514511108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5173788070679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3134117126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6644296646118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1081590652466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0154485702515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.830023765564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5902614593506</t>
   </si>
   <si>
     <t xml:space="preserve">12.7200565338135</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6088047027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1637859344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0339879989624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0710744857788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.607515335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4604644775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8114814758301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8485660552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2379550933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3862934112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3504972457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5359210968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7213439941406</t>
+    <t xml:space="preserve">12.6088027954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1637868881226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0339889526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0710754394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6075143814087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4604635238647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8114824295044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8485670089722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2379560470581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3862953186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3504962921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5359201431274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7213459014893</t>
   </si>
   <si>
     <t xml:space="preserve">14.2590732574463</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9080543518066</t>
+    <t xml:space="preserve">14.908055305481</t>
   </si>
   <si>
     <t xml:space="preserve">14.7782592773438</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7411727905273</t>
+    <t xml:space="preserve">14.7411737442017</t>
   </si>
   <si>
     <t xml:space="preserve">14.7968015670776</t>
@@ -1214,43 +1214,43 @@
     <t xml:space="preserve">15.0235710144043</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6849880218506</t>
+    <t xml:space="preserve">15.6849851608276</t>
   </si>
   <si>
     <t xml:space="preserve">15.4015235900879</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2314453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.080265045166</t>
+    <t xml:space="preserve">15.2314462661743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0802640914917</t>
   </si>
   <si>
     <t xml:space="preserve">15.1180591583252</t>
   </si>
   <si>
-    <t xml:space="preserve">15.174750328064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.307035446167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.13538646698</t>
+    <t xml:space="preserve">15.1747531890869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3070363998413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1353855133057</t>
   </si>
   <si>
     <t xml:space="preserve">13.8141269683838</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2660980224609</t>
+    <t xml:space="preserve">13.2660970687866</t>
   </si>
   <si>
     <t xml:space="preserve">13.6062536239624</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6818437576294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0771217346191</t>
+    <t xml:space="preserve">13.6818428039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0771207809448</t>
   </si>
   <si>
     <t xml:space="preserve">12.9448385238647</t>
@@ -1259,34 +1259,34 @@
     <t xml:space="preserve">13.114917755127</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8881454467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0944490432739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5479898452759</t>
+    <t xml:space="preserve">12.8881483078003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0944471359253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5479879379272</t>
   </si>
   <si>
     <t xml:space="preserve">13.0015316009521</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6235790252686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6991701126099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7558622360229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8692493438721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3401174545288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.736964225769</t>
+    <t xml:space="preserve">12.6235809326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6991691589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7558631896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8692483901978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3401165008545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7369651794434</t>
   </si>
   <si>
     <t xml:space="preserve">12.7180681228638</t>
@@ -1295,34 +1295,34 @@
     <t xml:space="preserve">12.7747611999512</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2645244598389</t>
+    <t xml:space="preserve">12.2645254135132</t>
   </si>
   <si>
     <t xml:space="preserve">13.7385358810425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7763338088989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9653072357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8708190917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0786933898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6251516342163</t>
+    <t xml:space="preserve">13.7763319015503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9653091430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8708181381226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0786924362183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6251497268677</t>
   </si>
   <si>
     <t xml:space="preserve">13.5873565673828</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4172773361206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4550714492798</t>
+    <t xml:space="preserve">13.4172782897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4550733566284</t>
   </si>
   <si>
     <t xml:space="preserve">13.4361753463745</t>
@@ -1331,7 +1331,7 @@
     <t xml:space="preserve">13.247200012207</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1338129043579</t>
+    <t xml:space="preserve">13.1338138580322</t>
   </si>
   <si>
     <t xml:space="preserve">13.3227910995483</t>
@@ -1340,13 +1340,13 @@
     <t xml:space="preserve">13.473970413208</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2094030380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3605861663818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5668869018555</t>
+    <t xml:space="preserve">13.2094039916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3605852127075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5668878555298</t>
   </si>
   <si>
     <t xml:space="preserve">12.5101947784424</t>
@@ -1358,55 +1358,55 @@
     <t xml:space="preserve">12.6802730560303</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0393266677856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9826335906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8125562667847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9637355804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7952299118042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1164875030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2676696777344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3054647445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.059796333313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.700740814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4928684234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7574348449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.549560546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1731815338135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9290838241577</t>
+    <t xml:space="preserve">13.0393257141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9826326370239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8125553131104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9637365341187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7952289581299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1164884567261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2676687240601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3054656982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0597953796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7007427215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4928693771362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.757435798645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5495624542236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1731805801392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.929084777832</t>
   </si>
   <si>
     <t xml:space="preserve">15.4960098266602</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2692413330078</t>
+    <t xml:space="preserve">15.2692384719849</t>
   </si>
   <si>
     <t xml:space="preserve">15.1558561325073</t>
@@ -1418,31 +1418,31 @@
     <t xml:space="preserve">16.7054557800293</t>
   </si>
   <si>
-    <t xml:space="preserve">16.913330078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6298637390137</t>
+    <t xml:space="preserve">16.9133319854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6298675537109</t>
   </si>
   <si>
     <t xml:space="preserve">16.2330169677734</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9117603302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5904998779297</t>
+    <t xml:space="preserve">15.9117565155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5904989242554</t>
   </si>
   <si>
     <t xml:space="preserve">15.5149097442627</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0046739578247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2125473022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3810548782349</t>
+    <t xml:space="preserve">15.004674911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2125482559204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3810539245605</t>
   </si>
   <si>
     <t xml:space="preserve">14.6078262329102</t>
@@ -1457,22 +1457,22 @@
     <t xml:space="preserve">14.2487707138062</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1920785903931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8897180557251</t>
+    <t xml:space="preserve">14.1920795440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8897171020508</t>
   </si>
   <si>
     <t xml:space="preserve">13.5306634902954</t>
   </si>
   <si>
-    <t xml:space="preserve">13.851921081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0220012664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8723917007446</t>
+    <t xml:space="preserve">13.8519229888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0219993591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.872389793396</t>
   </si>
   <si>
     <t xml:space="preserve">14.4755411148071</t>
@@ -1481,49 +1481,49 @@
     <t xml:space="preserve">14.4188499450684</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5527019500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9668798446655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0818347930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0629367828369</t>
+    <t xml:space="preserve">15.5527038574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9668788909912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0818367004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0629405975342</t>
   </si>
   <si>
     <t xml:space="preserve">16.2519149780273</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0440406799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8739624023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4582138061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0251426696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3464031219482</t>
+    <t xml:space="preserve">16.0440425872803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8739614486694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4582166671753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0251407623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.346399307251</t>
   </si>
   <si>
     <t xml:space="preserve">16.1007347106934</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3275051116943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6471900939941</t>
+    <t xml:space="preserve">16.3275032043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6471929550171</t>
   </si>
   <si>
     <t xml:space="preserve">15.7983713150024</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9306564331055</t>
+    <t xml:space="preserve">15.9306583404541</t>
   </si>
   <si>
     <t xml:space="preserve">15.0613670349121</t>
@@ -1532,7 +1532,7 @@
     <t xml:space="preserve">15.8550672531128</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4771118164062</t>
+    <t xml:space="preserve">15.4771108627319</t>
   </si>
   <si>
     <t xml:space="preserve">14.7401084899902</t>
@@ -1553,31 +1553,31 @@
     <t xml:space="preserve">15.5338077545166</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7416763305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0424690246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4204206466675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7605772018433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6282968521118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8928594589233</t>
+    <t xml:space="preserve">15.7416791915894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0424699783325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4204187393188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7605781555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6282939910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.892858505249</t>
   </si>
   <si>
     <t xml:space="preserve">15.9684505462646</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0062465667725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9873476028442</t>
+    <t xml:space="preserve">16.0062446594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9873456954956</t>
   </si>
   <si>
     <t xml:space="preserve">15.6093978881836</t>
@@ -1589,13 +1589,13 @@
     <t xml:space="preserve">14.6267223358154</t>
   </si>
   <si>
-    <t xml:space="preserve">14.853494644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1936492919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0991621017456</t>
+    <t xml:space="preserve">14.8534936904907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1936502456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0991611480713</t>
   </si>
   <si>
     <t xml:space="preserve">15.2881383895874</t>
@@ -1610,10 +1610,10 @@
     <t xml:space="preserve">17.2345886230469</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2534847259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2912788391113</t>
+    <t xml:space="preserve">17.2534866333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2912826538086</t>
   </si>
   <si>
     <t xml:space="preserve">17.1023063659668</t>
@@ -1622,31 +1622,31 @@
     <t xml:space="preserve">17.0645084381104</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0471858978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4046669006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3479747772217</t>
+    <t xml:space="preserve">18.0471839904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4046649932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3479766845703</t>
   </si>
   <si>
     <t xml:space="preserve">17.366870880127</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4991569519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0456123352051</t>
+    <t xml:space="preserve">17.4991550445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0456142425537</t>
   </si>
   <si>
     <t xml:space="preserve">17.3857688903809</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4424610137939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8582096099854</t>
+    <t xml:space="preserve">17.4424591064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8582057952881</t>
   </si>
   <si>
     <t xml:space="preserve">17.8204154968262</t>
@@ -1655,10 +1655,10 @@
     <t xml:space="preserve">17.5558471679688</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3290748596191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.140100479126</t>
+    <t xml:space="preserve">17.3290767669678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1400985717773</t>
   </si>
   <si>
     <t xml:space="preserve">16.5731735229492</t>
@@ -1667,7 +1667,7 @@
     <t xml:space="preserve">16.5920715332031</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2897071838379</t>
+    <t xml:space="preserve">16.2897052764893</t>
   </si>
   <si>
     <t xml:space="preserve">16.8566379547119</t>
@@ -1676,7 +1676,7 @@
     <t xml:space="preserve">16.1574268341064</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5805969238281</t>
+    <t xml:space="preserve">16.5805950164795</t>
   </si>
   <si>
     <t xml:space="preserve">16.5421276092529</t>
@@ -1691,13 +1691,13 @@
     <t xml:space="preserve">16.2343654632568</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0035438537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9843101501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6767711639404</t>
+    <t xml:space="preserve">16.0035457611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9843111038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6767749786377</t>
   </si>
   <si>
     <t xml:space="preserve">16.8114166259766</t>
@@ -1718,43 +1718,43 @@
     <t xml:space="preserve">16.522891998291</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9458417892456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4651870727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9650774002075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0227794647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8689012527466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7342538833618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6573162078857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4264965057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3687887191772</t>
+    <t xml:space="preserve">15.945839881897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4651889801025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9650745391846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0227813720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8689002990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7342557907104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6573143005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4264945983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3687896728516</t>
   </si>
   <si>
     <t xml:space="preserve">15.3110847473145</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9840888977051</t>
+    <t xml:space="preserve">14.9840898513794</t>
   </si>
   <si>
     <t xml:space="preserve">15.1956748962402</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2341461181641</t>
+    <t xml:space="preserve">15.2341451644897</t>
   </si>
   <si>
     <t xml:space="preserve">15.1379690170288</t>
@@ -1766,28 +1766,28 @@
     <t xml:space="preserve">15.003324508667</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1187343597412</t>
+    <t xml:space="preserve">15.1187353134155</t>
   </si>
   <si>
     <t xml:space="preserve">15.2533798217773</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0610303878784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8686790466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8494443893433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7147998809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.445728302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1764392852783</t>
+    <t xml:space="preserve">15.0610294342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8686809539795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8494424819946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7147989273071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4457311630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.176438331604</t>
   </si>
   <si>
     <t xml:space="preserve">14.8302097320557</t>
@@ -1796,31 +1796,31 @@
     <t xml:space="preserve">14.9648542404175</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1572046279907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7917385101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7532691955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9071483612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0225601196289</t>
+    <t xml:space="preserve">15.1572036743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7917394638062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7532682418823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9071493148804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0225582122803</t>
   </si>
   <si>
     <t xml:space="preserve">14.8109741210938</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8879127502441</t>
+    <t xml:space="preserve">14.8879146575928</t>
   </si>
   <si>
     <t xml:space="preserve">14.5416831970215</t>
   </si>
   <si>
-    <t xml:space="preserve">14.580153465271</t>
+    <t xml:space="preserve">14.5801525115967</t>
   </si>
   <si>
     <t xml:space="preserve">14.5993890762329</t>
@@ -1832,13 +1832,13 @@
     <t xml:space="preserve">14.6378593444824</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6186237335205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4647426605225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4455080032349</t>
+    <t xml:space="preserve">14.6186227798462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4647445678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4455089569092</t>
   </si>
   <si>
     <t xml:space="preserve">14.65709400177</t>
@@ -1847,97 +1847,97 @@
     <t xml:space="preserve">14.9263849258423</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5609188079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.349555015564</t>
+    <t xml:space="preserve">14.5609197616577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3495559692383</t>
   </si>
   <si>
     <t xml:space="preserve">15.3880243301392</t>
   </si>
   <si>
-    <t xml:space="preserve">15.676549911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5226707458496</t>
+    <t xml:space="preserve">15.6765508651733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5226697921753</t>
   </si>
   <si>
     <t xml:space="preserve">15.7150211334229</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7919607162476</t>
+    <t xml:space="preserve">15.7919626235962</t>
   </si>
   <si>
     <t xml:space="preserve">16.1574249267578</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7727251052856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8111972808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9073724746704</t>
+    <t xml:space="preserve">15.7727241516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8111963272095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9073705673218</t>
   </si>
   <si>
     <t xml:space="preserve">15.6380805969238</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6188449859619</t>
+    <t xml:space="preserve">15.6188459396362</t>
   </si>
   <si>
     <t xml:space="preserve">15.849666595459</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5803756713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5034351348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8304281234741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9266042709351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1189556121826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1576480865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0037670135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.94606590271</t>
+    <t xml:space="preserve">15.580376625061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.503436088562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8304300308228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.926607131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1189594268799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1576461791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0037689208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9460639953613</t>
   </si>
   <si>
     <t xml:space="preserve">16.8883590698242</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9845314025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.119176864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2730560302734</t>
+    <t xml:space="preserve">16.9845333099365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1191749572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2730579376221</t>
   </si>
   <si>
     <t xml:space="preserve">18.2732791900635</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1771049499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6000518798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6577625274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1001644134521</t>
+    <t xml:space="preserve">18.1771011352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6000556945801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6577606201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1001663208008</t>
   </si>
   <si>
     <t xml:space="preserve">17.9847545623779</t>
@@ -1946,25 +1946,25 @@
     <t xml:space="preserve">18.1193981170654</t>
   </si>
   <si>
-    <t xml:space="preserve">17.965518951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9462852478027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0616931915283</t>
+    <t xml:space="preserve">17.9655170440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9462833404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0616970062256</t>
   </si>
   <si>
     <t xml:space="preserve">17.9270477294922</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3117504119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7541561126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1003875732422</t>
+    <t xml:space="preserve">18.3117523193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7541580200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1003856658936</t>
   </si>
   <si>
     <t xml:space="preserve">19.0234470367432</t>
@@ -1973,7 +1973,7 @@
     <t xml:space="preserve">18.5425720214844</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9657382965088</t>
+    <t xml:space="preserve">18.9657421112061</t>
   </si>
   <si>
     <t xml:space="preserve">18.9080352783203</t>
@@ -1982,7 +1982,7 @@
     <t xml:space="preserve">19.4273834228516</t>
   </si>
   <si>
-    <t xml:space="preserve">19.812084197998</t>
+    <t xml:space="preserve">19.8120822906494</t>
   </si>
   <si>
     <t xml:space="preserve">19.5235557556152</t>
@@ -1991,13 +1991,13 @@
     <t xml:space="preserve">19.6678199768066</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2831153869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8503322601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6197319030762</t>
+    <t xml:space="preserve">19.2831172943115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8503284454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6197338104248</t>
   </si>
   <si>
     <t xml:space="preserve">19.7159061431885</t>
@@ -2006,22 +2006,22 @@
     <t xml:space="preserve">19.7639942169189</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3312072753906</t>
+    <t xml:space="preserve">19.331205368042</t>
   </si>
   <si>
     <t xml:space="preserve">19.5716457366943</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1967830657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2448711395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2164630889893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1585350036621</t>
+    <t xml:space="preserve">20.1967811584473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2448692321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2164611816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1585311889648</t>
   </si>
   <si>
     <t xml:space="preserve">21.1104469299316</t>
@@ -2036,10 +2036,10 @@
     <t xml:space="preserve">21.0142726898193</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7257423400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6776561737061</t>
+    <t xml:space="preserve">20.7257461547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6776599884033</t>
   </si>
   <si>
     <t xml:space="preserve">19.9563465118408</t>
@@ -2048,10 +2048,10 @@
     <t xml:space="preserve">20.2929592132568</t>
   </si>
   <si>
-    <t xml:space="preserve">20.004430770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8601703643799</t>
+    <t xml:space="preserve">20.0044326782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8601722717285</t>
   </si>
   <si>
     <t xml:space="preserve">19.0811500549316</t>
@@ -2060,58 +2060,58 @@
     <t xml:space="preserve">20.7738342285156</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9180946350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5814838409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2547092437744</t>
+    <t xml:space="preserve">20.918098449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5814819335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2547073364258</t>
   </si>
   <si>
     <t xml:space="preserve">21.3989715576172</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2066192626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6394081115723</t>
+    <t xml:space="preserve">21.2066211700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6394119262695</t>
   </si>
   <si>
     <t xml:space="preserve">21.4470596313477</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8317604064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0525207519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1006107330322</t>
+    <t xml:space="preserve">21.8317623138428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0525188446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.100606918335</t>
   </si>
   <si>
     <t xml:space="preserve">18.734920501709</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1963405609131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6192893981934</t>
+    <t xml:space="preserve">18.1963424682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6192874908447</t>
   </si>
   <si>
     <t xml:space="preserve">16.3113040924072</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1958980560303</t>
+    <t xml:space="preserve">16.1958961486816</t>
   </si>
   <si>
     <t xml:space="preserve">14.4839782714844</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4262742996216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4642992019653</t>
+    <t xml:space="preserve">14.4262733459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.464301109314</t>
   </si>
   <si>
     <t xml:space="preserve">12.0218954086304</t>
@@ -2120,64 +2120,64 @@
     <t xml:space="preserve">12.1373043060303</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6951198577881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9067058563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9834232330322</t>
+    <t xml:space="preserve">12.6951217651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9067068099976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9834251403809</t>
   </si>
   <si>
     <t xml:space="preserve">13.3106412887573</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5606966018677</t>
+    <t xml:space="preserve">13.560697555542</t>
   </si>
   <si>
     <t xml:space="preserve">14.0223379135132</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1954526901245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2916269302368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1185131072998</t>
+    <t xml:space="preserve">14.1954536437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2916278839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1185121536255</t>
   </si>
   <si>
     <t xml:space="preserve">14.7340335845947</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0992774963379</t>
+    <t xml:space="preserve">14.0992784500122</t>
   </si>
   <si>
     <t xml:space="preserve">15.4072599411011</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8691253662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1766605377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2151317596436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4649648666382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0612545013428</t>
+    <t xml:space="preserve">16.8691215515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1766586303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2151336669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4649658203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0612506866455</t>
   </si>
   <si>
     <t xml:space="preserve">16.1381931304932</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0420150756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5998306274414</t>
+    <t xml:space="preserve">16.0420169830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.59983253479</t>
   </si>
   <si>
     <t xml:space="preserve">17.215353012085</t>
@@ -2189,43 +2189,43 @@
     <t xml:space="preserve">16.9268283843994</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0614700317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2540454864502</t>
+    <t xml:space="preserve">17.0614719390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2540416717529</t>
   </si>
   <si>
     <t xml:space="preserve">18.638744354248</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0774517059326</t>
+    <t xml:space="preserve">18.0774536132812</t>
   </si>
   <si>
     <t xml:space="preserve">17.7677764892578</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4580974578857</t>
+    <t xml:space="preserve">17.4580993652344</t>
   </si>
   <si>
     <t xml:space="preserve">17.4387435913086</t>
   </si>
   <si>
-    <t xml:space="preserve">17.206485748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.954870223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4193916320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6129360198975</t>
+    <t xml:space="preserve">17.2064876556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9548721313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4193878173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6129379272461</t>
   </si>
   <si>
     <t xml:space="preserve">17.1677742004395</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6516494750977</t>
+    <t xml:space="preserve">17.651647567749</t>
   </si>
   <si>
     <t xml:space="preserve">17.4968070983887</t>
@@ -2234,19 +2234,19 @@
     <t xml:space="preserve">17.7290668487549</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2903575897217</t>
+    <t xml:space="preserve">18.290355682373</t>
   </si>
   <si>
     <t xml:space="preserve">17.9419708251953</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0580997467041</t>
+    <t xml:space="preserve">18.0580978393555</t>
   </si>
   <si>
     <t xml:space="preserve">18.3871307373047</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4064865112305</t>
+    <t xml:space="preserve">18.4064884185791</t>
   </si>
   <si>
     <t xml:space="preserve">17.9032611846924</t>
@@ -2255,7 +2255,7 @@
     <t xml:space="preserve">18.2322940826416</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2516460418701</t>
+    <t xml:space="preserve">18.2516498565674</t>
   </si>
   <si>
     <t xml:space="preserve">18.580680847168</t>
@@ -2267,19 +2267,19 @@
     <t xml:space="preserve">18.1161632537842</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0387439727783</t>
+    <t xml:space="preserve">18.038745880127</t>
   </si>
   <si>
     <t xml:space="preserve">18.8322925567627</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7742290496826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6774559020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9097156524658</t>
+    <t xml:space="preserve">18.7742309570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.677453994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9097137451172</t>
   </si>
   <si>
     <t xml:space="preserve">19.0451984405518</t>
@@ -2291,31 +2291,31 @@
     <t xml:space="preserve">19.3548755645752</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9484233856201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1032657623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4645500183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6581020355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.500036239624</t>
+    <t xml:space="preserve">18.9484214782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1032619476318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4645519256592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6581039428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5000381469727</t>
   </si>
   <si>
     <t xml:space="preserve">19.6451988220215</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0806827545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3226203918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6129417419434</t>
+    <t xml:space="preserve">20.0806846618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3226222991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6129398345947</t>
   </si>
   <si>
     <t xml:space="preserve">20.5645561218262</t>
@@ -2324,7 +2324,7 @@
     <t xml:space="preserve">21.0484275817871</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2903633117676</t>
+    <t xml:space="preserve">21.2903614044189</t>
   </si>
   <si>
     <t xml:space="preserve">21.7258472442627</t>
@@ -2333,7 +2333,7 @@
     <t xml:space="preserve">21.1935901641846</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5806846618652</t>
+    <t xml:space="preserve">21.5806865692139</t>
   </si>
   <si>
     <t xml:space="preserve">21.8710117340088</t>
@@ -2342,16 +2342,16 @@
     <t xml:space="preserve">21.532299041748</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3387508392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7742347717285</t>
+    <t xml:space="preserve">21.3387489318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7742366790771</t>
   </si>
   <si>
     <t xml:space="preserve">22.4516563415527</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9355297088623</t>
+    <t xml:space="preserve">22.9355278015137</t>
   </si>
   <si>
     <t xml:space="preserve">22.7903652191162</t>
@@ -2360,16 +2360,16 @@
     <t xml:space="preserve">23.3226261138916</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4193992614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0968189239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7258529663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4839153289795</t>
+    <t xml:space="preserve">23.4194011688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0968227386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7258548736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4839172363281</t>
   </si>
   <si>
     <t xml:space="preserve">24.048433303833</t>
@@ -2387,7 +2387,7 @@
     <t xml:space="preserve">22.741979598999</t>
   </si>
   <si>
-    <t xml:space="preserve">23.032299041748</t>
+    <t xml:space="preserve">23.0323009490967</t>
   </si>
   <si>
     <t xml:space="preserve">23.4677867889404</t>
@@ -2399,34 +2399,34 @@
     <t xml:space="preserve">22.8871402740479</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5484313964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8226203918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0645599365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2419776916504</t>
+    <t xml:space="preserve">22.5484294891357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8226222991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0645580291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2419757843018</t>
   </si>
   <si>
     <t xml:space="preserve">21.6290740966797</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4677791595459</t>
+    <t xml:space="preserve">20.4677810668945</t>
   </si>
   <si>
     <t xml:space="preserve">21.3871383666992</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0968132019043</t>
+    <t xml:space="preserve">21.0968151092529</t>
   </si>
   <si>
     <t xml:space="preserve">21.4839134216309</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2097187042236</t>
+    <t xml:space="preserve">22.2097225189209</t>
   </si>
   <si>
     <t xml:space="preserve">21.9677867889404</t>
@@ -2435,13 +2435,13 @@
     <t xml:space="preserve">20.9516525268555</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1129493713379</t>
+    <t xml:space="preserve">22.1129455566406</t>
   </si>
   <si>
     <t xml:space="preserve">22.3548812866211</t>
   </si>
   <si>
-    <t xml:space="preserve">21.919397354126</t>
+    <t xml:space="preserve">21.9193954467773</t>
   </si>
   <si>
     <t xml:space="preserve">22.838752746582</t>
@@ -2450,19 +2450,19 @@
     <t xml:space="preserve">22.645206451416</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4355316162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3387565612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2419815063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7419872283936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1774673461914</t>
+    <t xml:space="preserve">24.4355297088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3387546539307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.241979598999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7419853210449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1774711608887</t>
   </si>
   <si>
     <t xml:space="preserve">27.0000514984131</t>
@@ -2474,16 +2474,16 @@
     <t xml:space="preserve">26.6129550933838</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3710174560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6774711608887</t>
+    <t xml:space="preserve">26.3710193634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6774730682373</t>
   </si>
   <si>
     <t xml:space="preserve">28.6452159881592</t>
   </si>
   <si>
-    <t xml:space="preserve">29.903284072876</t>
+    <t xml:space="preserve">29.9032821655273</t>
   </si>
   <si>
     <t xml:space="preserve">28.9355392456055</t>
@@ -2492,37 +2492,37 @@
     <t xml:space="preserve">29.7581233978271</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3871555328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9194145202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7419986724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0323143005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5484447479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0807075500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2581214904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1774826049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3226432800293</t>
+    <t xml:space="preserve">30.3871536254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.919412612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7419948577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0323181152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5484466552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0807113647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2581253051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1774787902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.322639465332</t>
   </si>
   <si>
     <t xml:space="preserve">33.2903861999512</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1936149597168</t>
+    <t xml:space="preserve">33.1936111450195</t>
   </si>
   <si>
     <t xml:space="preserve">32.8065147399902</t>
@@ -2534,16 +2534,16 @@
     <t xml:space="preserve">33.7258720397949</t>
   </si>
   <si>
-    <t xml:space="preserve">34.1129684448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7420043945312</t>
+    <t xml:space="preserve">34.1129722595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7420082092285</t>
   </si>
   <si>
     <t xml:space="preserve">34.5968437194824</t>
   </si>
   <si>
-    <t xml:space="preserve">35.3710327148438</t>
+    <t xml:space="preserve">35.371036529541</t>
   </si>
   <si>
     <t xml:space="preserve">35.4678115844727</t>
@@ -2558,52 +2558,52 @@
     <t xml:space="preserve">36.1936225891113</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3065223693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.564582824707</t>
+    <t xml:space="preserve">34.3065185546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5645790100098</t>
   </si>
   <si>
     <t xml:space="preserve">32.6613540649414</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7581253051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7097434997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9355430603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3387680053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.822639465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5807056427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4839305877686</t>
+    <t xml:space="preserve">32.758129119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7097396850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9355411529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3387660980225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8226413726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5807037353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4839324951172</t>
   </si>
   <si>
     <t xml:space="preserve">31.112964630127</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4355506896973</t>
+    <t xml:space="preserve">33.435546875</t>
   </si>
   <si>
     <t xml:space="preserve">33.8710327148438</t>
   </si>
   <si>
-    <t xml:space="preserve">35.2742576599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6613578796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7097473144531</t>
+    <t xml:space="preserve">35.2742614746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6613616943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7097434997559</t>
   </si>
   <si>
     <t xml:space="preserve">37.2581367492676</t>
@@ -2612,13 +2612,13 @@
     <t xml:space="preserve">37.0162010192871</t>
   </si>
   <si>
-    <t xml:space="preserve">36.9678153991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9516868591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4355583190918</t>
+    <t xml:space="preserve">36.9678115844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9516792297363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4355545043945</t>
   </si>
   <si>
     <t xml:space="preserve">35.0807113647461</t>
@@ -2630,25 +2630,25 @@
     <t xml:space="preserve">36.677490234375</t>
   </si>
   <si>
-    <t xml:space="preserve">37.0645904541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6452331542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.0323333740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.612979888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.7581367492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8226585388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6774940490723</t>
+    <t xml:space="preserve">37.0645866394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6452369689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.0323295593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6129760742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.7581405639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8226623535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.677490234375</t>
   </si>
   <si>
     <t xml:space="preserve">38.5645904541016</t>
@@ -2660,16 +2660,16 @@
     <t xml:space="preserve">39.6291122436523</t>
   </si>
   <si>
-    <t xml:space="preserve">40.4516944885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.1613655090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4355621337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2581405639648</t>
+    <t xml:space="preserve">40.4516906738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.1613693237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4355583190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2581443786621</t>
   </si>
   <si>
     <t xml:space="preserve">44.0807304382324</t>
@@ -2684,40 +2684,40 @@
     <t xml:space="preserve">41.1774978637695</t>
   </si>
   <si>
-    <t xml:space="preserve">41.854923248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.338794708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.0484657287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.6291160583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.6129837036133</t>
+    <t xml:space="preserve">41.8549194335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.3387908935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.048469543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.6291122436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.612979888916</t>
   </si>
   <si>
     <t xml:space="preserve">42.3871803283691</t>
   </si>
   <si>
-    <t xml:space="preserve">43.5000839233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.1291198730469</t>
+    <t xml:space="preserve">43.5000801086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.1291160583496</t>
   </si>
   <si>
     <t xml:space="preserve">44.7097625732422</t>
   </si>
   <si>
-    <t xml:space="preserve">44.7581520080566</t>
+    <t xml:space="preserve">44.7581481933594</t>
   </si>
   <si>
     <t xml:space="preserve">45.6775054931641</t>
   </si>
   <si>
-    <t xml:space="preserve">44.4194374084473</t>
+    <t xml:space="preserve">44.4194450378418</t>
   </si>
   <si>
     <t xml:space="preserve">45.0000839233398</t>
@@ -2747,19 +2747,19 @@
     <t xml:space="preserve">44.2742805480957</t>
   </si>
   <si>
-    <t xml:space="preserve">43.838794708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.1613693237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.3065299987793</t>
+    <t xml:space="preserve">43.8387908935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.1613731384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.3065338134766</t>
   </si>
   <si>
     <t xml:space="preserve">43.2581481933594</t>
   </si>
   <si>
-    <t xml:space="preserve">42.8710517883301</t>
+    <t xml:space="preserve">42.8710479736328</t>
   </si>
   <si>
     <t xml:space="preserve">43.0645980834961</t>
@@ -2783,7 +2783,7 @@
     <t xml:space="preserve">39.7994422912598</t>
   </si>
   <si>
-    <t xml:space="preserve">39.4576110839844</t>
+    <t xml:space="preserve">39.4576072692871</t>
   </si>
   <si>
     <t xml:space="preserve">40.0924415588379</t>
@@ -2792,16 +2792,16 @@
     <t xml:space="preserve">40.8737831115723</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9947776794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.7761116027832</t>
+    <t xml:space="preserve">39.9947814941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.7761154174805</t>
   </si>
   <si>
     <t xml:space="preserve">40.6784477233887</t>
   </si>
   <si>
-    <t xml:space="preserve">40.190113067627</t>
+    <t xml:space="preserve">40.1901168823242</t>
   </si>
   <si>
     <t xml:space="preserve">39.8971061706543</t>
@@ -2810,7 +2810,7 @@
     <t xml:space="preserve">39.6529388427734</t>
   </si>
   <si>
-    <t xml:space="preserve">39.6041069030762</t>
+    <t xml:space="preserve">39.6041030883789</t>
   </si>
   <si>
     <t xml:space="preserve">39.7506103515625</t>
@@ -2837,7 +2837,7 @@
     <t xml:space="preserve">38.0902633666992</t>
   </si>
   <si>
-    <t xml:space="preserve">39.5552749633789</t>
+    <t xml:space="preserve">39.5552711486816</t>
   </si>
   <si>
     <t xml:space="preserve">41.7039527893066</t>
@@ -2849,19 +2849,19 @@
     <t xml:space="preserve">41.459789276123</t>
   </si>
   <si>
-    <t xml:space="preserve">41.0691108703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.385440826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4342765808105</t>
+    <t xml:space="preserve">41.0691146850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.3854446411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4342803955078</t>
   </si>
   <si>
     <t xml:space="preserve">42.1922912597656</t>
   </si>
   <si>
-    <t xml:space="preserve">42.0457878112793</t>
+    <t xml:space="preserve">42.0457916259766</t>
   </si>
   <si>
     <t xml:space="preserve">41.9481201171875</t>
@@ -2870,13 +2870,13 @@
     <t xml:space="preserve">41.4109535217285</t>
   </si>
   <si>
-    <t xml:space="preserve">42.7294654846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3664779663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4153099060059</t>
+    <t xml:space="preserve">42.7294616699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3664817810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4153137207031</t>
   </si>
   <si>
     <t xml:space="preserve">46.1966514587402</t>
@@ -2885,13 +2885,13 @@
     <t xml:space="preserve">47.8569946289062</t>
   </si>
   <si>
-    <t xml:space="preserve">47.3198280334473</t>
+    <t xml:space="preserve">47.31982421875</t>
   </si>
   <si>
     <t xml:space="preserve">47.8081665039062</t>
   </si>
   <si>
-    <t xml:space="preserve">48.5406684875488</t>
+    <t xml:space="preserve">48.5406646728516</t>
   </si>
   <si>
     <t xml:space="preserve">48.5895004272461</t>
@@ -2903,28 +2903,28 @@
     <t xml:space="preserve">48.1988296508789</t>
   </si>
   <si>
-    <t xml:space="preserve">49.7126770019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.9080085754395</t>
+    <t xml:space="preserve">49.7126808166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.9080123901367</t>
   </si>
   <si>
     <t xml:space="preserve">49.8103446960449</t>
   </si>
   <si>
-    <t xml:space="preserve">50.0056762695312</t>
+    <t xml:space="preserve">50.0056800842285</t>
   </si>
   <si>
     <t xml:space="preserve">50.6893501281738</t>
   </si>
   <si>
-    <t xml:space="preserve">51.3730163574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.2986755371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.5916862487793</t>
+    <t xml:space="preserve">51.3730201721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.2986793518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.591682434082</t>
   </si>
   <si>
     <t xml:space="preserve">50.4940147399902</t>
@@ -2945,13 +2945,13 @@
     <t xml:space="preserve">51.8613548278809</t>
   </si>
   <si>
-    <t xml:space="preserve">51.9590301513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.8846855163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2688102722168</t>
+    <t xml:space="preserve">51.9590263366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.8846817016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.2688140869141</t>
   </si>
   <si>
     <t xml:space="preserve">44.5363082885742</t>
@@ -2960,10 +2960,10 @@
     <t xml:space="preserve">43.5107955932617</t>
   </si>
   <si>
-    <t xml:space="preserve">44.2433052062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.2921371459961</t>
+    <t xml:space="preserve">44.2433013916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2921333312988</t>
   </si>
   <si>
     <t xml:space="preserve">44.9269752502441</t>
@@ -2975,7 +2975,7 @@
     <t xml:space="preserve">43.8038024902344</t>
   </si>
   <si>
-    <t xml:space="preserve">44.4386405944824</t>
+    <t xml:space="preserve">44.4386444091797</t>
   </si>
   <si>
     <t xml:space="preserve">43.9503021240234</t>
@@ -3008,43 +3008,43 @@
     <t xml:space="preserve">44.3409767150879</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4641456604004</t>
+    <t xml:space="preserve">45.4641494750977</t>
   </si>
   <si>
     <t xml:space="preserve">46.0989837646484</t>
   </si>
   <si>
-    <t xml:space="preserve">45.659481048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.7571487426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.7782974243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2644500732422</t>
+    <t xml:space="preserve">45.6594848632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.7571449279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.7782936096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2644538879395</t>
   </si>
   <si>
     <t xml:space="preserve">42.6806259155273</t>
   </si>
   <si>
-    <t xml:space="preserve">43.1201362609863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.3387908935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4364585876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.5086212158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0202827453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8715972900391</t>
+    <t xml:space="preserve">43.1201324462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.3387870788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4364624023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.508617401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0202865600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8716011047363</t>
   </si>
   <si>
     <t xml:space="preserve">38.2367668151855</t>
@@ -3056,46 +3056,46 @@
     <t xml:space="preserve">39.8482780456543</t>
   </si>
   <si>
-    <t xml:space="preserve">40.5319442749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8504524230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1179504394531</t>
+    <t xml:space="preserve">40.5319480895996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.850456237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1179466247559</t>
   </si>
   <si>
     <t xml:space="preserve">40.824951171875</t>
   </si>
   <si>
-    <t xml:space="preserve">41.6551208496094</t>
+    <t xml:space="preserve">41.6551246643066</t>
   </si>
   <si>
     <t xml:space="preserve">41.6062850952148</t>
   </si>
   <si>
-    <t xml:space="preserve">42.485294342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9736289978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8016166687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.3621215820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.238941192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.6296119689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.8759651184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.4619636535645</t>
+    <t xml:space="preserve">42.4852905273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.9736251831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8016204833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.362117767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2389450073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.6296157836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.8759613037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.4619674682617</t>
   </si>
   <si>
     <t xml:space="preserve">43.999137878418</t>
@@ -3119,7 +3119,7 @@
     <t xml:space="preserve">36.4299163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">38.6274299621582</t>
+    <t xml:space="preserve">38.6274337768555</t>
   </si>
   <si>
     <t xml:space="preserve">37.1135864257812</t>
@@ -3131,13 +3131,13 @@
     <t xml:space="preserve">34.7207374572754</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5997428894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.5275917053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6252517700195</t>
+    <t xml:space="preserve">35.5997467041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.527587890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6252555847168</t>
   </si>
   <si>
     <t xml:space="preserve">36.0880813598633</t>
@@ -3146,16 +3146,16 @@
     <t xml:space="preserve">36.1369171142578</t>
   </si>
   <si>
-    <t xml:space="preserve">35.4532432556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5254020690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3810806274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3555755615234</t>
+    <t xml:space="preserve">35.4532470703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5253982543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3810844421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3555793762207</t>
   </si>
   <si>
     <t xml:space="preserve">33.9393997192383</t>
@@ -3167,22 +3167,22 @@
     <t xml:space="preserve">31.4977188110352</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6442222595215</t>
+    <t xml:space="preserve">31.6442203521729</t>
   </si>
   <si>
     <t xml:space="preserve">33.0115623474121</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3767242431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4510612487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7695732116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5742416381836</t>
+    <t xml:space="preserve">32.3767280578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4510650634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7695693969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5742378234863</t>
   </si>
   <si>
     <t xml:space="preserve">35.3067474365234</t>
@@ -3209,16 +3209,16 @@
     <t xml:space="preserve">32.6208915710449</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4488849639893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6697235107422</t>
+    <t xml:space="preserve">31.4488830566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6697273254395</t>
   </si>
   <si>
     <t xml:space="preserve">32.767391204834</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2144813537598</t>
+    <t xml:space="preserve">31.2144794464111</t>
   </si>
   <si>
     <t xml:space="preserve">31.0191459655762</t>
@@ -3230,34 +3230,34 @@
     <t xml:space="preserve">29.6518058776855</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4722118377686</t>
+    <t xml:space="preserve">30.4722099304199</t>
   </si>
   <si>
     <t xml:space="preserve">32.2302207946777</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0739517211914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9372234344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3316860198975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1716194152832</t>
+    <t xml:space="preserve">32.0739555358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9372215270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3316841125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1716232299805</t>
   </si>
   <si>
     <t xml:space="preserve">31.3902835845947</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6637477874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8862056732178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9643383026123</t>
+    <t xml:space="preserve">31.6637516021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8862075805664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9643402099609</t>
   </si>
   <si>
     <t xml:space="preserve">28.3821277618408</t>
@@ -3266,16 +3266,16 @@
     <t xml:space="preserve">28.4993286132812</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2025337219238</t>
+    <t xml:space="preserve">29.2025356292725</t>
   </si>
   <si>
     <t xml:space="preserve">28.8704662322998</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9290676116943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.085334777832</t>
+    <t xml:space="preserve">28.9290657043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0853328704834</t>
   </si>
   <si>
     <t xml:space="preserve">28.3039951324463</t>
@@ -3290,13 +3290,13 @@
     <t xml:space="preserve">28.3235301971436</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5969982147217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2258605957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5579299926758</t>
+    <t xml:space="preserve">28.596996307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2258625030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5579280853271</t>
   </si>
   <si>
     <t xml:space="preserve">28.1816463470459</t>
@@ -3305,22 +3305,22 @@
     <t xml:space="preserve">26.8943614959717</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5972957611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6765117645264</t>
+    <t xml:space="preserve">26.5972938537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.676513671875</t>
   </si>
   <si>
     <t xml:space="preserve">26.8745555877686</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5280990600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4784679412842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7359237670898</t>
+    <t xml:space="preserve">27.5281009674072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4784698486328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7359256744385</t>
   </si>
   <si>
     <t xml:space="preserve">27.2508392333984</t>
@@ -3329,19 +3329,19 @@
     <t xml:space="preserve">28.0628204345703</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3994941711426</t>
+    <t xml:space="preserve">28.3994960784912</t>
   </si>
   <si>
     <t xml:space="preserve">28.320276260376</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7657527923584</t>
+    <t xml:space="preserve">27.765754699707</t>
   </si>
   <si>
     <t xml:space="preserve">27.9439926147461</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4193000793457</t>
+    <t xml:space="preserve">28.4192981719971</t>
   </si>
   <si>
     <t xml:space="preserve">29.0134296417236</t>
@@ -3362,13 +3362,13 @@
     <t xml:space="preserve">24.9931392669678</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0129451751709</t>
+    <t xml:space="preserve">25.0129432678223</t>
   </si>
   <si>
     <t xml:space="preserve">25.6466846466064</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4584217071533</t>
+    <t xml:space="preserve">24.4584197998047</t>
   </si>
   <si>
     <t xml:space="preserve">25.4288368225098</t>
@@ -3380,7 +3380,7 @@
     <t xml:space="preserve">25.4684429168701</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8148994445801</t>
+    <t xml:space="preserve">24.8148975372314</t>
   </si>
   <si>
     <t xml:space="preserve">25.2902050018311</t>
@@ -3401,7 +3401,7 @@
     <t xml:space="preserve">23.8444843292236</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0523090362549</t>
+    <t xml:space="preserve">23.0523109436035</t>
   </si>
   <si>
     <t xml:space="preserve">23.5474185943604</t>
@@ -3413,19 +3413,19 @@
     <t xml:space="preserve">23.6068325042725</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1909408569336</t>
+    <t xml:space="preserve">23.190938949585</t>
   </si>
   <si>
     <t xml:space="preserve">22.9136772155762</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4185676574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5669822692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8146572113037</t>
+    <t xml:space="preserve">22.4185695648193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5669803619385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8146591186523</t>
   </si>
   <si>
     <t xml:space="preserve">22.9532890319824</t>
@@ -3440,13 +3440,13 @@
     <t xml:space="preserve">24.7356834411621</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5970497131348</t>
+    <t xml:space="preserve">24.5970516204834</t>
   </si>
   <si>
     <t xml:space="preserve">25.1911849975586</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9239444732666</t>
+    <t xml:space="preserve">25.9239463806152</t>
   </si>
   <si>
     <t xml:space="preserve">25.8249244689941</t>
@@ -3458,7 +3458,7 @@
     <t xml:space="preserve">26.1615982055664</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3892250061035</t>
+    <t xml:space="preserve">25.3892269134521</t>
   </si>
   <si>
     <t xml:space="preserve">25.1317691802979</t>
@@ -3467,10 +3467,10 @@
     <t xml:space="preserve">25.5674667358398</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0427703857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1417922973633</t>
+    <t xml:space="preserve">26.0427722930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1417942047119</t>
   </si>
   <si>
     <t xml:space="preserve">25.8843364715576</t>
@@ -3488,7 +3488,7 @@
     <t xml:space="preserve">24.2207679748535</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1217460632324</t>
+    <t xml:space="preserve">24.1217479705811</t>
   </si>
   <si>
     <t xml:space="preserve">23.6860504150391</t>
@@ -3506,7 +3506,7 @@
     <t xml:space="preserve">23.626636505127</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4980297088623</t>
+    <t xml:space="preserve">24.4980278015137</t>
   </si>
   <si>
     <t xml:space="preserve">23.8642902374268</t>
@@ -3515,19 +3515,19 @@
     <t xml:space="preserve">23.9435081481934</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7850704193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8743133544922</t>
+    <t xml:space="preserve">23.7850723266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8743152618408</t>
   </si>
   <si>
     <t xml:space="preserve">24.9535312652588</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2999858856201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7652683258057</t>
+    <t xml:space="preserve">24.2999877929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.765266418457</t>
   </si>
   <si>
     <t xml:space="preserve">22.8344612121582</t>
@@ -3536,7 +3536,7 @@
     <t xml:space="preserve">22.5571994781494</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7156372070312</t>
+    <t xml:space="preserve">22.7156352996826</t>
   </si>
   <si>
     <t xml:space="preserve">22.0422859191895</t>
@@ -3554,10 +3554,10 @@
     <t xml:space="preserve">20.0618476867676</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2696704864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8836059570312</t>
+    <t xml:space="preserve">19.2696685791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8836078643799</t>
   </si>
   <si>
     <t xml:space="preserve">20.2400875091553</t>
@@ -3581,7 +3581,7 @@
     <t xml:space="preserve">20.8540210723877</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3887424468994</t>
+    <t xml:space="preserve">21.3887405395508</t>
   </si>
   <si>
     <t xml:space="preserve">21.6065883636475</t>
@@ -3590,7 +3590,7 @@
     <t xml:space="preserve">22.0026741027832</t>
   </si>
   <si>
-    <t xml:space="preserve">22.200719833374</t>
+    <t xml:space="preserve">22.2007217407227</t>
   </si>
   <si>
     <t xml:space="preserve">21.6660003662109</t>
@@ -3599,16 +3599,16 @@
     <t xml:space="preserve">21.5075664520264</t>
   </si>
   <si>
-    <t xml:space="preserve">22.676025390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3195476531982</t>
+    <t xml:space="preserve">22.6760234832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3195457458496</t>
   </si>
   <si>
     <t xml:space="preserve">22.1809158325195</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4383735656738</t>
+    <t xml:space="preserve">22.4383716583252</t>
   </si>
   <si>
     <t xml:space="preserve">21.7848262786865</t>
@@ -3632,22 +3632,22 @@
     <t xml:space="preserve">25.7457065582275</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0329914093018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6369037628174</t>
+    <t xml:space="preserve">27.0329895019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6369018554688</t>
   </si>
   <si>
     <t xml:space="preserve">26.5576858520508</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9831161499023</t>
+    <t xml:space="preserve">23.9831142425537</t>
   </si>
   <si>
     <t xml:space="preserve">25.0525512695312</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2505970001221</t>
+    <t xml:space="preserve">25.2505950927734</t>
   </si>
   <si>
     <t xml:space="preserve">26.2012062072754</t>
@@ -3656,7 +3656,7 @@
     <t xml:space="preserve">26.4190540313721</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6963157653809</t>
+    <t xml:space="preserve">26.6963176727295</t>
   </si>
   <si>
     <t xml:space="preserve">26.7161197662354</t>
@@ -3674,25 +3674,25 @@
     <t xml:space="preserve">23.8246803283691</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9730930328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7950973510742</t>
+    <t xml:space="preserve">22.9730911254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7950954437256</t>
   </si>
   <si>
     <t xml:space="preserve">25.2704010009766</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1219902038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0625762939453</t>
+    <t xml:space="preserve">26.1219882965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0625743865967</t>
   </si>
   <si>
     <t xml:space="preserve">25.7853164672852</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2606201171875</t>
+    <t xml:space="preserve">26.2606220245361</t>
   </si>
   <si>
     <t xml:space="preserve">27.0725994110107</t>
@@ -3710,7 +3710,7 @@
     <t xml:space="preserve">27.4884929656982</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6965618133545</t>
+    <t xml:space="preserve">28.6965599060059</t>
   </si>
   <si>
     <t xml:space="preserve">28.7757759094238</t>
@@ -3719,10 +3719,10 @@
     <t xml:space="preserve">28.2212543487549</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5777339935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2806663513184</t>
+    <t xml:space="preserve">28.5777359008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.280668258667</t>
   </si>
   <si>
     <t xml:space="preserve">28.8153877258301</t>
@@ -3737,7 +3737,7 @@
     <t xml:space="preserve">28.6569519042969</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9540176391602</t>
+    <t xml:space="preserve">28.9540157318115</t>
   </si>
   <si>
     <t xml:space="preserve">28.8549938201904</t>
@@ -3746,7 +3746,7 @@
     <t xml:space="preserve">28.9738216400146</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7955799102783</t>
+    <t xml:space="preserve">28.795581817627</t>
   </si>
   <si>
     <t xml:space="preserve">30.280912399292</t>
@@ -3761,7 +3761,7 @@
     <t xml:space="preserve">29.7065830230713</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5877552032471</t>
+    <t xml:space="preserve">29.5877571105957</t>
   </si>
   <si>
     <t xml:space="preserve">29.33030128479</t>
@@ -3788,7 +3788,7 @@
     <t xml:space="preserve">28.3004722595215</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4787139892578</t>
+    <t xml:space="preserve">28.4787120819092</t>
   </si>
   <si>
     <t xml:space="preserve">28.0430145263672</t>
@@ -3800,7 +3800,7 @@
     <t xml:space="preserve">27.7063407897949</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0131874084473</t>
+    <t xml:space="preserve">27.0131893157959</t>
   </si>
   <si>
     <t xml:space="preserve">26.7755355834961</t>
@@ -3818,22 +3818,22 @@
     <t xml:space="preserve">22.3789615631104</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2801837921143</t>
+    <t xml:space="preserve">24.2801818847656</t>
   </si>
   <si>
     <t xml:space="preserve">24.5574436187744</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8347015380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0921611785889</t>
+    <t xml:space="preserve">24.8347034454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0921630859375</t>
   </si>
   <si>
     <t xml:space="preserve">25.8447284698486</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3893489837646</t>
+    <t xml:space="preserve">26.389347076416</t>
   </si>
   <si>
     <t xml:space="preserve">27.0825023651123</t>
@@ -3848,7 +3848,7 @@
     <t xml:space="preserve">27.4785900115967</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0727214813232</t>
+    <t xml:space="preserve">28.0727233886719</t>
   </si>
   <si>
     <t xml:space="preserve">27.7756538391113</t>
@@ -3857,10 +3857,10 @@
     <t xml:space="preserve">27.6766357421875</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4290809631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.181526184082</t>
+    <t xml:space="preserve">27.4290790557861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1815242767334</t>
   </si>
   <si>
     <t xml:space="preserve">26.9339694976807</t>
@@ -3869,13 +3869,13 @@
     <t xml:space="preserve">27.3795680999756</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8844604492188</t>
+    <t xml:space="preserve">26.8844585418701</t>
   </si>
   <si>
     <t xml:space="preserve">27.7261447906494</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9834785461426</t>
+    <t xml:space="preserve">26.9834804534912</t>
   </si>
   <si>
     <t xml:space="preserve">27.330057144165</t>
@@ -3890,7 +3890,7 @@
     <t xml:space="preserve">28.4688110351562</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5085411071777</t>
+    <t xml:space="preserve">29.5085391998291</t>
   </si>
   <si>
     <t xml:space="preserve">30.5482711791992</t>
@@ -3905,7 +3905,7 @@
     <t xml:space="preserve">32.0831146240234</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6375141143799</t>
+    <t xml:space="preserve">31.6375122070312</t>
   </si>
   <si>
     <t xml:space="preserve">32.1821327209473</t>
@@ -3914,25 +3914,25 @@
     <t xml:space="preserve">32.9247970581055</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2316436767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9840850830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1919136047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.340446472168</t>
+    <t xml:space="preserve">32.4296913146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2316398620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9840888977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.191915512085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3404445648193</t>
   </si>
   <si>
     <t xml:space="preserve">30.795825958252</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6472930908203</t>
+    <t xml:space="preserve">30.6472949981689</t>
   </si>
   <si>
     <t xml:space="preserve">30.2016944885254</t>
@@ -3944,7 +3944,7 @@
     <t xml:space="preserve">30.2512035369873</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5977821350098</t>
+    <t xml:space="preserve">30.5977802276611</t>
   </si>
   <si>
     <t xml:space="preserve">30.4492492675781</t>
@@ -5223,6 +5223,9 @@
   </si>
   <si>
     <t xml:space="preserve">36.7000007629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2999992370605</t>
   </si>
 </sst>
 </file>
@@ -71991,7 +71994,7 @@
     </row>
     <row r="2556">
       <c r="A2556" s="1" t="n">
-        <v>46044.6911921296</v>
+        <v>46044.3333333333</v>
       </c>
       <c r="B2556" t="n">
         <v>42584</v>
@@ -72012,6 +72015,32 @@
         <v>1736</v>
       </c>
       <c r="H2556" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2557">
+      <c r="A2557" s="1" t="n">
+        <v>46045.6909837963</v>
+      </c>
+      <c r="B2557" t="n">
+        <v>33383</v>
+      </c>
+      <c r="C2557" t="n">
+        <v>37.2000007629395</v>
+      </c>
+      <c r="D2557" t="n">
+        <v>36.1500015258789</v>
+      </c>
+      <c r="E2557" t="n">
+        <v>37.2000007629395</v>
+      </c>
+      <c r="F2557" t="n">
+        <v>36.2999992370605</v>
+      </c>
+      <c r="G2557" t="s">
+        <v>1737</v>
+      </c>
+      <c r="H2557" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MOL.MI.xlsx
+++ b/data/MOL.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1749" uniqueCount="1749">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1750" uniqueCount="1750">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">6.850661277771</t>
+    <t xml:space="preserve">6.85066080093384</t>
   </si>
   <si>
     <t xml:space="preserve">MOL.MI</t>
@@ -47,19 +47,19 @@
     <t xml:space="preserve">6.75772666931152</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66036510467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77100276947021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63823795318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7267484664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81525754928589</t>
+    <t xml:space="preserve">6.66036558151245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77100324630737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63823843002319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72674798965454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81525707244873</t>
   </si>
   <si>
     <t xml:space="preserve">6.54972839355469</t>
@@ -68,10 +68,10 @@
     <t xml:space="preserve">6.31960296630859</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09832859039307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35058116912842</t>
+    <t xml:space="preserve">6.09832811355591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35058069229126</t>
   </si>
   <si>
     <t xml:space="preserve">6.2399435043335</t>
@@ -80,16 +80,16 @@
     <t xml:space="preserve">6.5585789680481</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46121883392334</t>
+    <t xml:space="preserve">6.46121835708618</t>
   </si>
   <si>
     <t xml:space="preserve">5.89475536346436</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52317523956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65594005584717</t>
+    <t xml:space="preserve">6.5231761932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65594053268433</t>
   </si>
   <si>
     <t xml:space="preserve">6.76215171813965</t>
@@ -98,16 +98,16 @@
     <t xml:space="preserve">6.66479158401489</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69134378433228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68249273300171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01866865158081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89918041229248</t>
+    <t xml:space="preserve">6.69134330749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68249320983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01866960525513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89918088912964</t>
   </si>
   <si>
     <t xml:space="preserve">6.28419876098633</t>
@@ -116,112 +116,112 @@
     <t xml:space="preserve">6.0629243850708</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2532205581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39926195144653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34172964096069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5098991394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3328800201416</t>
+    <t xml:space="preserve">6.25322008132935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39926099777222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34173059463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50989866256714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33287954330444</t>
   </si>
   <si>
     <t xml:space="preserve">6.42581462860107</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39041042327881</t>
+    <t xml:space="preserve">6.39041090011597</t>
   </si>
   <si>
     <t xml:space="preserve">6.30632591247559</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40811204910278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3550066947937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63381290435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43466472625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22666692733765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24436902999878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27534770965576</t>
+    <t xml:space="preserve">6.40811157226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35500621795654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63381195068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43466520309448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22666645050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24436950683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27534818649292</t>
   </si>
   <si>
     <t xml:space="preserve">6.2664966583252</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62938594818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43909120559692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41253757476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45236778259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45679330825806</t>
+    <t xml:space="preserve">6.62938642501831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43909072875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41253805160522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45236730575562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4567928314209</t>
   </si>
   <si>
     <t xml:space="preserve">6.36828279495239</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19568824768066</t>
+    <t xml:space="preserve">6.19568920135498</t>
   </si>
   <si>
     <t xml:space="preserve">6.06734943389893</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28862476348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20453977584839</t>
+    <t xml:space="preserve">6.28862428665161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20453929901123</t>
   </si>
   <si>
     <t xml:space="preserve">6.29304933547974</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2487940788269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22224187850952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25764513015747</t>
+    <t xml:space="preserve">6.24879455566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22224140167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25764656066895</t>
   </si>
   <si>
     <t xml:space="preserve">6.15585947036743</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19126319885254</t>
+    <t xml:space="preserve">6.19126272201538</t>
   </si>
   <si>
     <t xml:space="preserve">6.58955812454224</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47892045974731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49662208557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42138862609863</t>
+    <t xml:space="preserve">6.47892189025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49662113189697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42138910293579</t>
   </si>
   <si>
     <t xml:space="preserve">6.63348913192749</t>
@@ -230,37 +230,37 @@
     <t xml:space="preserve">6.45274019241333</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54311513900757</t>
+    <t xml:space="preserve">6.54311466217041</t>
   </si>
   <si>
     <t xml:space="preserve">6.44370269775391</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50696516036987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55667066574097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36688470840454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61993265151978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69223260879517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59733963012695</t>
+    <t xml:space="preserve">6.50696468353271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55667114257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36688423156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61993312835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69223308563232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59733915328979</t>
   </si>
   <si>
     <t xml:space="preserve">6.6831955909729</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70578908920288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75097560882568</t>
+    <t xml:space="preserve">6.70578956604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75097608566284</t>
   </si>
   <si>
     <t xml:space="preserve">6.85038757324219</t>
@@ -272,43 +272,43 @@
     <t xml:space="preserve">6.98594951629639</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1034369468689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25255346298218</t>
+    <t xml:space="preserve">7.10343647003174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25255441665649</t>
   </si>
   <si>
     <t xml:space="preserve">7.32033586502075</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45589780807495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30226182937622</t>
+    <t xml:space="preserve">7.45589733123779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3022608757019</t>
   </si>
   <si>
     <t xml:space="preserve">7.37907886505127</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25707292556763</t>
+    <t xml:space="preserve">7.25707340240479</t>
   </si>
   <si>
     <t xml:space="preserve">7.22996139526367</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22544288635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19832992553711</t>
+    <t xml:space="preserve">7.22544193267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19833040237427</t>
   </si>
   <si>
     <t xml:space="preserve">7.09439945220947</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13958692550659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00402450561523</t>
+    <t xml:space="preserve">7.13958597183228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00402498245239</t>
   </si>
   <si>
     <t xml:space="preserve">7.08084297180176</t>
@@ -317,16 +317,16 @@
     <t xml:space="preserve">6.95883798599243</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84135103225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11699295043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16669893264771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31129837036133</t>
+    <t xml:space="preserve">6.84135055541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11699342727661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16669940948486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31129884719849</t>
   </si>
   <si>
     <t xml:space="preserve">7.32485437393188</t>
@@ -335,58 +335,58 @@
     <t xml:space="preserve">6.99950647354126</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73290157318115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08988046646118</t>
+    <t xml:space="preserve">6.73290061950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08988094329834</t>
   </si>
   <si>
     <t xml:space="preserve">7.18477344512939</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85942554473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67867708206177</t>
+    <t xml:space="preserve">6.85942602157593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67867660522461</t>
   </si>
   <si>
     <t xml:space="preserve">6.49792814254761</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57022619247437</t>
+    <t xml:space="preserve">6.57022714614868</t>
   </si>
   <si>
     <t xml:space="preserve">6.57926464080811</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41659021377563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74645757675171</t>
+    <t xml:space="preserve">6.41659069061279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74645805358887</t>
   </si>
   <si>
     <t xml:space="preserve">6.6515645980835</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55215215682983</t>
+    <t xml:space="preserve">6.55215263366699</t>
   </si>
   <si>
     <t xml:space="preserve">6.46177864074707</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75549507141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56570863723755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77808904647827</t>
+    <t xml:space="preserve">6.75549459457397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56570816040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77808856964111</t>
   </si>
   <si>
     <t xml:space="preserve">6.71030807495117</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48889017105103</t>
+    <t xml:space="preserve">6.48888969421387</t>
   </si>
   <si>
     <t xml:space="preserve">6.53859615325928</t>
@@ -395,25 +395,25 @@
     <t xml:space="preserve">6.66060161590576</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68771409988403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76001310348511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87750053405762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70127010345459</t>
+    <t xml:space="preserve">6.68771362304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76001358032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87750101089478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70127105712891</t>
   </si>
   <si>
     <t xml:space="preserve">6.78712606430054</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79616355895996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81423807144165</t>
+    <t xml:space="preserve">6.7961630821228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81423759460449</t>
   </si>
   <si>
     <t xml:space="preserve">6.8187575340271</t>
@@ -422,7 +422,7 @@
     <t xml:space="preserve">6.82327604293823</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80520057678223</t>
+    <t xml:space="preserve">6.80520153045654</t>
   </si>
   <si>
     <t xml:space="preserve">6.92268800735474</t>
@@ -434,28 +434,28 @@
     <t xml:space="preserve">6.86846256256104</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98143148422241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17573595046997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01306295394897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97691297531128</t>
+    <t xml:space="preserve">6.98143100738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17573738098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01306343078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97691202163696</t>
   </si>
   <si>
     <t xml:space="preserve">6.64252710342407</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69675064086914</t>
+    <t xml:space="preserve">6.6967511177063</t>
   </si>
   <si>
     <t xml:space="preserve">6.88653802871704</t>
   </si>
   <si>
-    <t xml:space="preserve">6.931725025177</t>
+    <t xml:space="preserve">6.93172550201416</t>
   </si>
   <si>
     <t xml:space="preserve">7.02209997177124</t>
@@ -464,16 +464,16 @@
     <t xml:space="preserve">6.99046897888184</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19381189346313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05824995040894</t>
+    <t xml:space="preserve">7.19381141662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05824899673462</t>
   </si>
   <si>
     <t xml:space="preserve">7.04921245574951</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0672869682312</t>
+    <t xml:space="preserve">7.06728744506836</t>
   </si>
   <si>
     <t xml:space="preserve">7.14862442016602</t>
@@ -482,34 +482,34 @@
     <t xml:space="preserve">7.08536243438721</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06276893615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15766143798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21188688278198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38359785079956</t>
+    <t xml:space="preserve">7.06276798248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15766191482544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21188592910767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38359832763672</t>
   </si>
   <si>
     <t xml:space="preserve">7.22092342376709</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24803638458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18929290771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35648584365845</t>
+    <t xml:space="preserve">7.24803686141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18929195404053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35648536682129</t>
   </si>
   <si>
     <t xml:space="preserve">7.37004137039185</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88201904296875</t>
+    <t xml:space="preserve">6.88201951980591</t>
   </si>
   <si>
     <t xml:space="preserve">7.0356559753418</t>
@@ -524,58 +524,58 @@
     <t xml:space="preserve">7.5191593170166</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47849035263062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50108575820923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41070985794067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27514743804932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60953521728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66375780105591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72702074050903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68183469772339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67731666564941</t>
+    <t xml:space="preserve">7.47849082946777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50108432769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41071081161499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27514886856079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60953330993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66375827789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72702264785767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68183374404907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67731428146362</t>
   </si>
   <si>
     <t xml:space="preserve">7.63664579391479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77220821380615</t>
+    <t xml:space="preserve">7.77220773696899</t>
   </si>
   <si>
     <t xml:space="preserve">7.971031665802</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34156799316406</t>
+    <t xml:space="preserve">8.34156703948975</t>
   </si>
   <si>
     <t xml:space="preserve">8.41386795043945</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45001792907715</t>
+    <t xml:space="preserve">8.45001697540283</t>
   </si>
   <si>
     <t xml:space="preserve">8.57654094696045</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37771606445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40934944152832</t>
+    <t xml:space="preserve">8.37771797180176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40935039520264</t>
   </si>
   <si>
     <t xml:space="preserve">8.35964298248291</t>
@@ -587,67 +587,67 @@
     <t xml:space="preserve">8.24215507507324</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33705043792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32801246643066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32349395751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36416244506836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37319850921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.468092918396</t>
+    <t xml:space="preserve">8.33704853057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32801151275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3234920501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36416053771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37319755554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46809101104736</t>
   </si>
   <si>
     <t xml:space="preserve">8.30541801452637</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30089950561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09755611419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26926612854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20600509643555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0749626159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11111164093018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28282451629639</t>
+    <t xml:space="preserve">8.30090045928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09755706787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26926803588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20600605010986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07496356964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11111259460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28282260894775</t>
   </si>
   <si>
     <t xml:space="preserve">8.2963809967041</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40483093261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48164939880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4229040145874</t>
+    <t xml:space="preserve">8.40482997894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48164844512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42290592193604</t>
   </si>
   <si>
     <t xml:space="preserve">8.22859954833984</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27378749847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02977657318115</t>
+    <t xml:space="preserve">8.27378559112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02977466583252</t>
   </si>
   <si>
     <t xml:space="preserve">8.13370704650879</t>
@@ -656,13 +656,13 @@
     <t xml:space="preserve">8.27830505371094</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43194389343262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69402885437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57969951629639</t>
+    <t xml:space="preserve">8.43194103240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6940279006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57969760894775</t>
   </si>
   <si>
     <t xml:space="preserve">9.25435066223145</t>
@@ -671,7 +671,7 @@
     <t xml:space="preserve">9.21820068359375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01937580108643</t>
+    <t xml:space="preserve">9.01937675476074</t>
   </si>
   <si>
     <t xml:space="preserve">9.16397571563721</t>
@@ -680,7 +680,7 @@
     <t xml:space="preserve">9.20012664794922</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20916271209717</t>
+    <t xml:space="preserve">9.20916175842285</t>
   </si>
   <si>
     <t xml:space="preserve">9.22723865509033</t>
@@ -692,40 +692,40 @@
     <t xml:space="preserve">9.03744983673096</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12782573699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35376262664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55258655548096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47124862670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80563449859619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89600849151611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2123193740845</t>
+    <t xml:space="preserve">9.12782669067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35376167297363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55258560180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47124671936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80563640594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89601039886475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2123203277588</t>
   </si>
   <si>
     <t xml:space="preserve">9.94119644165039</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4472942352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8449411392212</t>
+    <t xml:space="preserve">10.4472951889038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8449420928955</t>
   </si>
   <si>
     <t xml:space="preserve">10.8087921142578</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9082040786743</t>
+    <t xml:space="preserve">10.9082050323486</t>
   </si>
   <si>
     <t xml:space="preserve">10.9353170394897</t>
@@ -734,13 +734,13 @@
     <t xml:space="preserve">10.7364931106567</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7093811035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.754566192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4764308929443</t>
+    <t xml:space="preserve">10.7093801498413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7545671463013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.476432800293</t>
   </si>
   <si>
     <t xml:space="preserve">10.2261095046997</t>
@@ -749,58 +749,58 @@
     <t xml:space="preserve">10.0128726959229</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3837194442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4300746917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2817363739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4022626876831</t>
+    <t xml:space="preserve">10.3837203979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4300756454468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2817373275757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4022607803345</t>
   </si>
   <si>
     <t xml:space="preserve">10.5135164260864</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4949731826782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5413293838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7452974319458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0790586471558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7743978500366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5889739990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2181272506714</t>
+    <t xml:space="preserve">10.4949750900269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5413312911987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7452945709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0790576934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7743968963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5889720916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2181253433228</t>
   </si>
   <si>
     <t xml:space="preserve">11.3015661239624</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0976009368896</t>
+    <t xml:space="preserve">11.097601890564</t>
   </si>
   <si>
     <t xml:space="preserve">11.1439561843872</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0327014923096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8287372589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7545671463013</t>
+    <t xml:space="preserve">11.0327024459839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8287363052368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7545690536499</t>
   </si>
   <si>
     <t xml:space="preserve">10.7360248565674</t>
@@ -818,7 +818,7 @@
     <t xml:space="preserve">11.1254138946533</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0605163574219</t>
+    <t xml:space="preserve">11.0605154037476</t>
   </si>
   <si>
     <t xml:space="preserve">11.4869909286499</t>
@@ -827,10 +827,10 @@
     <t xml:space="preserve">11.0697870254517</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9399919509888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4499073028564</t>
+    <t xml:space="preserve">10.9399909973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4499063491821</t>
   </si>
   <si>
     <t xml:space="preserve">11.4035491943359</t>
@@ -839,94 +839,94 @@
     <t xml:space="preserve">11.7094993591309</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0988883972168</t>
+    <t xml:space="preserve">12.0988874435425</t>
   </si>
   <si>
     <t xml:space="preserve">12.3213968276978</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8949213027954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5160903930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5253629684448</t>
+    <t xml:space="preserve">11.894923210144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5160913467407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5253610610962</t>
   </si>
   <si>
     <t xml:space="preserve">12.6737012863159</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7478713989258</t>
+    <t xml:space="preserve">12.7478704452515</t>
   </si>
   <si>
     <t xml:space="preserve">12.5346345901489</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7942266464233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7293281555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5439043045044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5809907913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5624465942383</t>
+    <t xml:space="preserve">12.794225692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7293272018433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5439052581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5809879302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5624485015869</t>
   </si>
   <si>
     <t xml:space="preserve">12.4697351455688</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4975490570068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4882793426514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6829719543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6273441314697</t>
+    <t xml:space="preserve">12.4975481033325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4882783889771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6829710006714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.627345085144</t>
   </si>
   <si>
     <t xml:space="preserve">12.5531768798828</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1823282241821</t>
+    <t xml:space="preserve">12.1823291778564</t>
   </si>
   <si>
     <t xml:space="preserve">12.3955659866333</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4233779907227</t>
+    <t xml:space="preserve">12.423378944397</t>
   </si>
   <si>
     <t xml:space="preserve">12.2935838699341</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3677520751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8856506347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2843112945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.173056602478</t>
+    <t xml:space="preserve">12.367751121521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8856496810913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.28431224823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1730575561523</t>
   </si>
   <si>
     <t xml:space="preserve">12.0525331497192</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9505491256714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.312126159668</t>
+    <t xml:space="preserve">11.9505500793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3121252059937</t>
   </si>
   <si>
     <t xml:space="preserve">12.2657690048218</t>
@@ -935,10 +935,10 @@
     <t xml:space="preserve">11.9412775039673</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9598207473755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3306665420532</t>
+    <t xml:space="preserve">11.9598197937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3306684494019</t>
   </si>
   <si>
     <t xml:space="preserve">12.4419221878052</t>
@@ -947,100 +947,100 @@
     <t xml:space="preserve">12.3492097854614</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3770227432251</t>
+    <t xml:space="preserve">12.3770246505737</t>
   </si>
   <si>
     <t xml:space="preserve">12.1545143127441</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2472276687622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3399381637573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4511919021606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2008714675903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4326505661011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3028554916382</t>
+    <t xml:space="preserve">12.2472257614136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3399391174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4511938095093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.200870513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4326496124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3028535842896</t>
   </si>
   <si>
     <t xml:space="preserve">12.2564992904663</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0618019104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0247201919556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4406328201294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6353302001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7929382324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.663143157959</t>
+    <t xml:space="preserve">12.061803817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0247173309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4406337738037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6353311538696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7929401397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6631412506104</t>
   </si>
   <si>
     <t xml:space="preserve">11.6816844940186</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7465848922729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9227352142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8207530975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8671092987061</t>
+    <t xml:space="preserve">11.7465839385986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9227342605591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8207521438599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8671083450317</t>
   </si>
   <si>
     <t xml:space="preserve">11.7373123168945</t>
   </si>
   <si>
-    <t xml:space="preserve">12.228684425354</t>
+    <t xml:space="preserve">12.2286853790283</t>
   </si>
   <si>
     <t xml:space="preserve">12.1915998458862</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7651252746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.718770980835</t>
+    <t xml:space="preserve">11.7651243209839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7187690734863</t>
   </si>
   <si>
     <t xml:space="preserve">11.1903133392334</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2922945022583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1624994277954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5426177978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4684495925903</t>
+    <t xml:space="preserve">11.2922954559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1624984741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5426168441772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4684476852417</t>
   </si>
   <si>
     <t xml:space="preserve">11.5982446670532</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5797023773193</t>
+    <t xml:space="preserve">11.579701423645</t>
   </si>
   <si>
     <t xml:space="preserve">11.4962615966797</t>
@@ -1052,79 +1052,79 @@
     <t xml:space="preserve">11.857837677002</t>
   </si>
   <si>
-    <t xml:space="preserve">12.145245552063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.006175994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9134645462036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9240226745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9253120422363</t>
+    <t xml:space="preserve">12.1452436447144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0061769485474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9134654998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9240236282349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.925311088562</t>
   </si>
   <si>
     <t xml:space="preserve">14.1107339859009</t>
   </si>
   <si>
-    <t xml:space="preserve">14.092191696167</t>
+    <t xml:space="preserve">14.0921907424927</t>
   </si>
   <si>
     <t xml:space="preserve">13.9438524246216</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9994802474976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6299180984497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9067687988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6286334991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2034463882446</t>
+    <t xml:space="preserve">13.9994812011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6299200057983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9067678451538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6286325454712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2034454345703</t>
   </si>
   <si>
     <t xml:space="preserve">14.0180215835571</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7028017044067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3888711929321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5186653137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5742921829224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4815816879272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1849040985107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8325986862183</t>
+    <t xml:space="preserve">13.7028026580811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3888702392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5186643600464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5742931365967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4815807342529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1849050521851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8325977325439</t>
   </si>
   <si>
     <t xml:space="preserve">12.9981927871704</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7756843566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3690404891968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0352783203125</t>
+    <t xml:space="preserve">12.7756834030151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3690395355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0352773666382</t>
   </si>
   <si>
     <t xml:space="preserve">12.7385988235474</t>
@@ -1133,52 +1133,52 @@
     <t xml:space="preserve">12.9796504974365</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5173797607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3134126663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6644287109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1081600189209</t>
+    <t xml:space="preserve">13.5173778533936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3134117126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6644306182861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1081590652466</t>
   </si>
   <si>
     <t xml:space="preserve">12.0154476165771</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8300247192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5902614593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7200555801392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6088027954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1637859344482</t>
+    <t xml:space="preserve">11.830023765564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5902605056763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7200574874878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6088037490845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1637868881226</t>
   </si>
   <si>
     <t xml:space="preserve">12.033989906311</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0710735321045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.607515335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4604635238647</t>
+    <t xml:space="preserve">12.0710763931274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6075162887573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4604625701904</t>
   </si>
   <si>
     <t xml:space="preserve">11.8114805221558</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8485651016235</t>
+    <t xml:space="preserve">11.8485670089722</t>
   </si>
   <si>
     <t xml:space="preserve">12.2379550933838</t>
@@ -1187,97 +1187,97 @@
     <t xml:space="preserve">12.3862953186035</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3504962921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5359220504761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7213449478149</t>
+    <t xml:space="preserve">13.3504972457886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5359201431274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7213439941406</t>
   </si>
   <si>
     <t xml:space="preserve">14.2590732574463</t>
   </si>
   <si>
-    <t xml:space="preserve">14.908055305481</t>
+    <t xml:space="preserve">14.9080562591553</t>
   </si>
   <si>
     <t xml:space="preserve">14.7782592773438</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7411727905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.796802520752</t>
+    <t xml:space="preserve">14.741171836853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7968006134033</t>
   </si>
   <si>
     <t xml:space="preserve">15.0235710144043</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6849880218506</t>
+    <t xml:space="preserve">15.6849870681763</t>
   </si>
   <si>
     <t xml:space="preserve">15.4015216827393</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2314453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0802659988403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1180591583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1747512817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.307035446167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1353845596313</t>
+    <t xml:space="preserve">15.2314462661743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0802640914917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1180601119995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1747531890869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3070363998413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.13538646698</t>
   </si>
   <si>
     <t xml:space="preserve">13.8141269683838</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2660980224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6062536239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6818447113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0771217346191</t>
+    <t xml:space="preserve">13.2660961151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6062517166138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6818437576294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0771207809448</t>
   </si>
   <si>
     <t xml:space="preserve">12.9448385238647</t>
   </si>
   <si>
-    <t xml:space="preserve">13.114917755127</t>
+    <t xml:space="preserve">13.1149168014526</t>
   </si>
   <si>
     <t xml:space="preserve">12.8881454467773</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0944480895996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5479898452759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0015306472778</t>
+    <t xml:space="preserve">12.0944471359253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5479888916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0015316009521</t>
   </si>
   <si>
     <t xml:space="preserve">12.6235799789429</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6991701126099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7558622360229</t>
+    <t xml:space="preserve">12.6991691589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7558612823486</t>
   </si>
   <si>
     <t xml:space="preserve">12.8692474365234</t>
@@ -1289,13 +1289,13 @@
     <t xml:space="preserve">12.7369651794434</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7180671691895</t>
+    <t xml:space="preserve">12.7180681228638</t>
   </si>
   <si>
     <t xml:space="preserve">12.7747611999512</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2645254135132</t>
+    <t xml:space="preserve">12.2645263671875</t>
   </si>
   <si>
     <t xml:space="preserve">13.7385358810425</t>
@@ -1304,70 +1304,70 @@
     <t xml:space="preserve">13.7763328552246</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9653072357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8708200454712</t>
+    <t xml:space="preserve">13.9653081893921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8708190917969</t>
   </si>
   <si>
     <t xml:space="preserve">14.0786933898926</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6251516342163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5873575210571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4172773361206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4550714492798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4361753463745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2472009658813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1338148117065</t>
+    <t xml:space="preserve">13.625150680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5873565673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4172782897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4550733566284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4361763000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2471990585327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1338119506836</t>
   </si>
   <si>
     <t xml:space="preserve">13.322790145874</t>
   </si>
   <si>
-    <t xml:space="preserve">13.473970413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2094030380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3605861663818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5668869018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5101938247681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2834243774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6802730560303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.03932762146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9826335906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8125553131104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.96373462677</t>
+    <t xml:space="preserve">13.4739713668823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2094049453735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3605842590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5668888092041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5101947784424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2834234237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6802740097046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0393266677856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9826326370239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.812557220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9637365341187</t>
   </si>
   <si>
     <t xml:space="preserve">13.7952299118042</t>
@@ -1376,7 +1376,7 @@
     <t xml:space="preserve">14.1164865493774</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2676696777344</t>
+    <t xml:space="preserve">14.2676687240601</t>
   </si>
   <si>
     <t xml:space="preserve">14.3054637908936</t>
@@ -1385,118 +1385,118 @@
     <t xml:space="preserve">14.0597953796387</t>
   </si>
   <si>
-    <t xml:space="preserve">13.700740814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4928693771362</t>
+    <t xml:space="preserve">13.7007417678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4928674697876</t>
   </si>
   <si>
     <t xml:space="preserve">13.7574338912964</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5495595932007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1731824874878</t>
+    <t xml:space="preserve">13.5495615005493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1731805801392</t>
   </si>
   <si>
     <t xml:space="preserve">14.9290838241577</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4960098266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2692413330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.155855178833</t>
+    <t xml:space="preserve">15.4960117340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2692384719849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1558561325073</t>
   </si>
   <si>
     <t xml:space="preserve">16.5353755950928</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7054576873779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9133281707764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6298656463623</t>
+    <t xml:space="preserve">16.7054557800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.913330078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6298675537109</t>
   </si>
   <si>
     <t xml:space="preserve">16.2330169677734</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9117603302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5904998779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.514910697937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0046730041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2125463485718</t>
+    <t xml:space="preserve">15.9117565155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5904979705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5149078369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0046739578247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2125482559204</t>
   </si>
   <si>
     <t xml:space="preserve">14.3810548782349</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6078243255615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4377460479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6456203460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2487697601318</t>
+    <t xml:space="preserve">14.6078252792358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4377470016479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6456184387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2487707138062</t>
   </si>
   <si>
     <t xml:space="preserve">14.1920795440674</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8897180557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5306634902954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.851921081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0220003128052</t>
+    <t xml:space="preserve">13.8897171020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5306644439697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8519229888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0220012664795</t>
   </si>
   <si>
     <t xml:space="preserve">14.8723907470703</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4755420684814</t>
+    <t xml:space="preserve">14.4755411148071</t>
   </si>
   <si>
     <t xml:space="preserve">14.4188499450684</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5527019500732</t>
+    <t xml:space="preserve">15.5527009963989</t>
   </si>
   <si>
     <t xml:space="preserve">14.9668798446655</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0818367004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0629405975342</t>
+    <t xml:space="preserve">16.0818347930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0629386901855</t>
   </si>
   <si>
     <t xml:space="preserve">16.2519149780273</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0440425872803</t>
+    <t xml:space="preserve">16.0440406799316</t>
   </si>
   <si>
     <t xml:space="preserve">15.8739624023438</t>
@@ -1505,31 +1505,31 @@
     <t xml:space="preserve">15.4582147598267</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0251407623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3464012145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.100736618042</t>
+    <t xml:space="preserve">16.0251426696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3464031219482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1007347106934</t>
   </si>
   <si>
     <t xml:space="preserve">16.3275051116943</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6471900939941</t>
+    <t xml:space="preserve">15.6471910476685</t>
   </si>
   <si>
     <t xml:space="preserve">15.7983713150024</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9306554794312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0613679885864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8550691604614</t>
+    <t xml:space="preserve">15.9306583404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0613660812378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8550672531128</t>
   </si>
   <si>
     <t xml:space="preserve">15.4771127700806</t>
@@ -1538,7 +1538,7 @@
     <t xml:space="preserve">14.7401094436646</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9101848602295</t>
+    <t xml:space="preserve">14.9101867675781</t>
   </si>
   <si>
     <t xml:space="preserve">14.5511322021484</t>
@@ -1550,22 +1550,22 @@
     <t xml:space="preserve">14.9857769012451</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5338087081909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.741678237915</t>
+    <t xml:space="preserve">15.5338077545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7416801452637</t>
   </si>
   <si>
     <t xml:space="preserve">15.0424699783325</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4204196929932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7605772018433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6282958984375</t>
+    <t xml:space="preserve">15.4204216003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7605781555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6282968521118</t>
   </si>
   <si>
     <t xml:space="preserve">15.8928594589233</t>
@@ -1574,76 +1574,76 @@
     <t xml:space="preserve">15.9684505462646</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0062465667725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9873476028442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6093969345093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6834154129028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6267213821411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8534936904907</t>
+    <t xml:space="preserve">16.0062446594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9873495101929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6093978881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6834163665771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6267232894897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.853494644165</t>
   </si>
   <si>
     <t xml:space="preserve">15.1936502456665</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0991611480713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2881393432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.195219039917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0078182220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2345867156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2534847259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2912788391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1023063659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.064510345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0471839904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4046669006348</t>
+    <t xml:space="preserve">15.0991621017456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2881383895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1952228546143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0078201293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2345905303955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2534866333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2912769317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1023044586182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0645084381104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0471858978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4046649932861</t>
   </si>
   <si>
     <t xml:space="preserve">17.347972869873</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3668689727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4991550445557</t>
+    <t xml:space="preserve">17.3668727874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4991569519043</t>
   </si>
   <si>
     <t xml:space="preserve">17.0456123352051</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3857707977295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4424610137939</t>
+    <t xml:space="preserve">17.3857688903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4424629211426</t>
   </si>
   <si>
     <t xml:space="preserve">17.8582077026367</t>
@@ -1652,7 +1652,7 @@
     <t xml:space="preserve">17.8204135894775</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5558471679688</t>
+    <t xml:space="preserve">17.5558490753174</t>
   </si>
   <si>
     <t xml:space="preserve">17.3290748596191</t>
@@ -1661,52 +1661,52 @@
     <t xml:space="preserve">17.140100479126</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5731735229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5920715332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2897090911865</t>
+    <t xml:space="preserve">16.5731716156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5920696258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2897109985352</t>
   </si>
   <si>
     <t xml:space="preserve">16.8566360473633</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1574268341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5805950164795</t>
+    <t xml:space="preserve">16.1574287414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5805988311768</t>
   </si>
   <si>
     <t xml:space="preserve">16.5421276092529</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3882484436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.445951461792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2343635559082</t>
+    <t xml:space="preserve">16.3882465362549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4459533691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2343654632568</t>
   </si>
   <si>
     <t xml:space="preserve">16.0035457611084</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9843111038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6767711639404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8114166259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8306503295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7537136077881</t>
+    <t xml:space="preserve">15.9843120574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6767730712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8114185333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8306522369385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7537117004395</t>
   </si>
   <si>
     <t xml:space="preserve">16.6383018493652</t>
@@ -1718,46 +1718,46 @@
     <t xml:space="preserve">16.522891998291</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9458408355713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4651870727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9650774002075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0227794647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8689012527466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7342548370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6573162078857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.426495552063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3687887191772</t>
+    <t xml:space="preserve">15.9458417892456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4651889801025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9650754928589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0227813720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8688993453979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7342538833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6573152542114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4264974594116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3687896728516</t>
   </si>
   <si>
     <t xml:space="preserve">15.3110857009888</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9840888977051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1956748962402</t>
+    <t xml:space="preserve">14.9840898513794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1956758499146</t>
   </si>
   <si>
     <t xml:space="preserve">15.2341451644897</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1379699707031</t>
+    <t xml:space="preserve">15.1379690170288</t>
   </si>
   <si>
     <t xml:space="preserve">15.0994997024536</t>
@@ -1769,55 +1769,52 @@
     <t xml:space="preserve">15.1187343597412</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2533798217773</t>
+    <t xml:space="preserve">15.2533807754517</t>
   </si>
   <si>
     <t xml:space="preserve">15.0610294342041</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8686780929565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8494443893433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7147998809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4457292556763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.176438331604</t>
+    <t xml:space="preserve">14.8686800003052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8494434356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7147989273071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4457311630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1764392852783</t>
   </si>
   <si>
     <t xml:space="preserve">14.8302097320557</t>
   </si>
   <si>
-    <t xml:space="preserve">15.080265045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9648542404175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1572046279907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7917385101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7532691955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9071493148804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0225601196289</t>
+    <t xml:space="preserve">14.9648532867432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1572036743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7917394638062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7532682418823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9071474075317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0225582122803</t>
   </si>
   <si>
     <t xml:space="preserve">14.8109741210938</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8879127502441</t>
+    <t xml:space="preserve">14.8879146575928</t>
   </si>
   <si>
     <t xml:space="preserve">14.5416841506958</t>
@@ -1826,28 +1823,28 @@
     <t xml:space="preserve">14.580153465271</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5993881225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5032119750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6378593444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6186237335205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4647436141968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4455089569092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6570930480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9263858795166</t>
+    <t xml:space="preserve">14.5993890762329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.503212928772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6378583908081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6186227798462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4647426605225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4455099105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.65709400177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9263849258423</t>
   </si>
   <si>
     <t xml:space="preserve">14.5609188079834</t>
@@ -1862,34 +1859,37 @@
     <t xml:space="preserve">15.6765489578247</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5226707458496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7150192260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7919616699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7727251052856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8111982345581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9073715209961</t>
+    <t xml:space="preserve">15.522668838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7150201797485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7919597625732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1574249267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7727270126343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8111972808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9073724746704</t>
   </si>
   <si>
     <t xml:space="preserve">15.6380805969238</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6188449859619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8496656417847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5803756713867</t>
+    <t xml:space="preserve">15.6188430786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8496646881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5803775787354</t>
   </si>
   <si>
     <t xml:space="preserve">15.5034351348877</t>
@@ -1898,10 +1898,10 @@
     <t xml:space="preserve">15.8304281234741</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9266052246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.118953704834</t>
+    <t xml:space="preserve">15.9266061782837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1189575195312</t>
   </si>
   <si>
     <t xml:space="preserve">17.1576480865479</t>
@@ -1913,10 +1913,10 @@
     <t xml:space="preserve">16.9460639953613</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8883590698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9845314025879</t>
+    <t xml:space="preserve">16.8883571624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9845333099365</t>
   </si>
   <si>
     <t xml:space="preserve">17.119176864624</t>
@@ -1925,10 +1925,10 @@
     <t xml:space="preserve">17.2730560302734</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2732810974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1771030426025</t>
+    <t xml:space="preserve">18.2732791900635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1771049499512</t>
   </si>
   <si>
     <t xml:space="preserve">17.6000518798828</t>
@@ -1937,82 +1937,82 @@
     <t xml:space="preserve">17.6577606201172</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1001663208008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9847545623779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1193981170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.965518951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9462871551514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0616912841797</t>
+    <t xml:space="preserve">18.1001625061035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9847583770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1194000244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9655170440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9462852478027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0616931915283</t>
   </si>
   <si>
     <t xml:space="preserve">17.9270496368408</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3117504119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7541561126709</t>
+    <t xml:space="preserve">18.3117542266846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7541542053223</t>
   </si>
   <si>
     <t xml:space="preserve">19.1003875732422</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0234451293945</t>
+    <t xml:space="preserve">19.0234470367432</t>
   </si>
   <si>
     <t xml:space="preserve">18.5425720214844</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9657382965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9080352783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4273815155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8120822906494</t>
+    <t xml:space="preserve">18.9657402038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9080333709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4273853302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8120803833008</t>
   </si>
   <si>
     <t xml:space="preserve">19.5235557556152</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6678218841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2831192016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8503303527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6197319030762</t>
+    <t xml:space="preserve">19.6678199768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2831153869629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8503284454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6197338104248</t>
   </si>
   <si>
     <t xml:space="preserve">19.7159080505371</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7639942169189</t>
+    <t xml:space="preserve">19.7639923095703</t>
   </si>
   <si>
     <t xml:space="preserve">19.3312072753906</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5716438293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1967830657959</t>
+    <t xml:space="preserve">19.5716457366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1967811584473</t>
   </si>
   <si>
     <t xml:space="preserve">20.2448711395264</t>
@@ -2021,28 +2021,28 @@
     <t xml:space="preserve">22.2164611816406</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1585330963135</t>
+    <t xml:space="preserve">21.1585350036621</t>
   </si>
   <si>
     <t xml:space="preserve">21.1104469299316</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8219203948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6295719146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0142726898193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7257442474365</t>
+    <t xml:space="preserve">20.8219184875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6295738220215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0142707824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7257461547852</t>
   </si>
   <si>
     <t xml:space="preserve">20.6776580810547</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9563465118408</t>
+    <t xml:space="preserve">19.9563446044922</t>
   </si>
   <si>
     <t xml:space="preserve">20.2929592132568</t>
@@ -2054,61 +2054,61 @@
     <t xml:space="preserve">19.8601703643799</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0811500549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.773832321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9180946350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5814819335938</t>
+    <t xml:space="preserve">19.0811519622803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7738342285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9180965423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5814800262451</t>
   </si>
   <si>
     <t xml:space="preserve">21.2547092437744</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3989734649658</t>
+    <t xml:space="preserve">21.3989715576172</t>
   </si>
   <si>
     <t xml:space="preserve">21.2066211700439</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6394100189209</t>
+    <t xml:space="preserve">21.6394081115723</t>
   </si>
   <si>
     <t xml:space="preserve">21.4470596313477</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8317604064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0525226593018</t>
+    <t xml:space="preserve">21.8317623138428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0525188446045</t>
   </si>
   <si>
     <t xml:space="preserve">20.1006088256836</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7349185943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1963405609131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6192855834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3113040924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1958980560303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4839782714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4262742996216</t>
+    <t xml:space="preserve">18.734920501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1963386535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6192893981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3113059997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1958961486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4839792251587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4262733459473</t>
   </si>
   <si>
     <t xml:space="preserve">12.4643001556396</t>
@@ -2117,7 +2117,7 @@
     <t xml:space="preserve">12.0218954086304</t>
   </si>
   <si>
-    <t xml:space="preserve">12.137303352356</t>
+    <t xml:space="preserve">12.1373052597046</t>
   </si>
   <si>
     <t xml:space="preserve">12.6951198577881</t>
@@ -2126,85 +2126,85 @@
     <t xml:space="preserve">12.9067068099976</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9834241867065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3106412887573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5606966018677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0223398208618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1954517364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2916269302368</t>
+    <t xml:space="preserve">11.9834251403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.310640335083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.560697555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0223379135132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1954526901245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2916278839111</t>
   </si>
   <si>
     <t xml:space="preserve">14.1185131072998</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7340335845947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0992774963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4072599411011</t>
+    <t xml:space="preserve">14.7340326309204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0992784500122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4072589874268</t>
   </si>
   <si>
     <t xml:space="preserve">16.8691234588623</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1766605377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2151317596436</t>
+    <t xml:space="preserve">16.1766624450684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2151336669922</t>
   </si>
   <si>
     <t xml:space="preserve">15.4649648666382</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0612525939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1381931304932</t>
+    <t xml:space="preserve">16.0612506866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1381950378418</t>
   </si>
   <si>
     <t xml:space="preserve">16.0420169830322</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5998344421387</t>
+    <t xml:space="preserve">16.5998306274414</t>
   </si>
   <si>
     <t xml:space="preserve">17.215353012085</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7152423858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9268283843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0614700317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2540435791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6387424468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0774536132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7677783966064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4580993652344</t>
+    <t xml:space="preserve">16.7152404785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.926830291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0614719390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2540454864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.638744354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0774517059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7677764892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4580974578857</t>
   </si>
   <si>
     <t xml:space="preserve">17.4387435913086</t>
@@ -2216,22 +2216,22 @@
     <t xml:space="preserve">16.954870223999</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4193897247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6129379272461</t>
+    <t xml:space="preserve">17.4193916320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6129360198975</t>
   </si>
   <si>
     <t xml:space="preserve">17.1677742004395</t>
   </si>
   <si>
-    <t xml:space="preserve">17.651647567749</t>
+    <t xml:space="preserve">17.6516494750977</t>
   </si>
   <si>
     <t xml:space="preserve">17.4968070983887</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7290649414062</t>
+    <t xml:space="preserve">17.7290668487549</t>
   </si>
   <si>
     <t xml:space="preserve">18.2903575897217</t>
@@ -2246,7 +2246,7 @@
     <t xml:space="preserve">18.3871307373047</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4064846038818</t>
+    <t xml:space="preserve">18.4064865112305</t>
   </si>
   <si>
     <t xml:space="preserve">17.9032611846924</t>
@@ -2255,49 +2255,49 @@
     <t xml:space="preserve">18.2322940826416</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2516479492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5806827545166</t>
+    <t xml:space="preserve">18.2516460418701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.580680847168</t>
   </si>
   <si>
     <t xml:space="preserve">18.4451961517334</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1161613464355</t>
+    <t xml:space="preserve">18.1161632537842</t>
   </si>
   <si>
     <t xml:space="preserve">18.0387439727783</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8322944641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7742309570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.677453994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9097137451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0452003479004</t>
+    <t xml:space="preserve">18.8322925567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7742290496826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6774559020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9097156524658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0451984405518</t>
   </si>
   <si>
     <t xml:space="preserve">19.5968132019043</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3548774719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9484214782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1032638549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4645519256592</t>
+    <t xml:space="preserve">19.3548755645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9484233856201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1032657623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4645500183105</t>
   </si>
   <si>
     <t xml:space="preserve">18.6581020355225</t>
@@ -2309,7 +2309,7 @@
     <t xml:space="preserve">19.6451988220215</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0806846618652</t>
+    <t xml:space="preserve">20.0806827545166</t>
   </si>
   <si>
     <t xml:space="preserve">20.3226203918457</t>
@@ -2318,25 +2318,25 @@
     <t xml:space="preserve">20.6129417419434</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5645542144775</t>
+    <t xml:space="preserve">20.5645561218262</t>
   </si>
   <si>
     <t xml:space="preserve">21.0484275817871</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2903614044189</t>
+    <t xml:space="preserve">21.2903633117676</t>
   </si>
   <si>
     <t xml:space="preserve">21.7258472442627</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1935882568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5806865692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8710098266602</t>
+    <t xml:space="preserve">21.1935901641846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5806846618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8710117340088</t>
   </si>
   <si>
     <t xml:space="preserve">21.532299041748</t>
@@ -2357,19 +2357,19 @@
     <t xml:space="preserve">22.7903652191162</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3226280212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4194011688232</t>
+    <t xml:space="preserve">23.3226261138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4193992614746</t>
   </si>
   <si>
     <t xml:space="preserve">24.0968189239502</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7258548736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4839172363281</t>
+    <t xml:space="preserve">24.7258529663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4839153289795</t>
   </si>
   <si>
     <t xml:space="preserve">24.048433303833</t>
@@ -2378,7 +2378,7 @@
     <t xml:space="preserve">23.7581100463867</t>
   </si>
   <si>
-    <t xml:space="preserve">23.95166015625</t>
+    <t xml:space="preserve">23.9516582489014</t>
   </si>
   <si>
     <t xml:space="preserve">23.6613368988037</t>
@@ -2387,10 +2387,10 @@
     <t xml:space="preserve">22.741979598999</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0323009490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4677886962891</t>
+    <t xml:space="preserve">23.032299041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4677867889404</t>
   </si>
   <si>
     <t xml:space="preserve">23.0806903839111</t>
@@ -2399,19 +2399,19 @@
     <t xml:space="preserve">22.8871402740479</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5484294891357</t>
+    <t xml:space="preserve">22.5484313964844</t>
   </si>
   <si>
     <t xml:space="preserve">21.8226203918457</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0645580291748</t>
+    <t xml:space="preserve">22.0645599365234</t>
   </si>
   <si>
     <t xml:space="preserve">21.2419776916504</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6290760040283</t>
+    <t xml:space="preserve">21.6290740966797</t>
   </si>
   <si>
     <t xml:space="preserve">20.4677791595459</t>
@@ -2420,10 +2420,10 @@
     <t xml:space="preserve">21.3871383666992</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0968151092529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4839115142822</t>
+    <t xml:space="preserve">21.0968132019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4839134216309</t>
   </si>
   <si>
     <t xml:space="preserve">22.2097187042236</t>
@@ -2435,7 +2435,7 @@
     <t xml:space="preserve">20.9516525268555</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1129474639893</t>
+    <t xml:space="preserve">22.1129493713379</t>
   </si>
   <si>
     <t xml:space="preserve">22.3548812866211</t>
@@ -2456,13 +2456,13 @@
     <t xml:space="preserve">24.3387565612793</t>
   </si>
   <si>
-    <t xml:space="preserve">24.241979598999</t>
+    <t xml:space="preserve">24.2419815063477</t>
   </si>
   <si>
     <t xml:space="preserve">25.7419872283936</t>
   </si>
   <si>
-    <t xml:space="preserve">26.17746925354</t>
+    <t xml:space="preserve">26.1774673461914</t>
   </si>
   <si>
     <t xml:space="preserve">27.0000514984131</t>
@@ -2477,7 +2477,7 @@
     <t xml:space="preserve">26.3710174560547</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6774730682373</t>
+    <t xml:space="preserve">27.6774711608887</t>
   </si>
   <si>
     <t xml:space="preserve">28.6452159881592</t>
@@ -2495,28 +2495,28 @@
     <t xml:space="preserve">30.3871555328369</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9194164276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7419948577881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0323181152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5484466552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0807113647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2581195831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1774787902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.322639465332</t>
+    <t xml:space="preserve">30.9194145202637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7419986724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0323143005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5484447479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0807075500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2581214904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1774826049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3226432800293</t>
   </si>
   <si>
     <t xml:space="preserve">33.2903861999512</t>
@@ -2531,19 +2531,19 @@
     <t xml:space="preserve">33.4839363098145</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7258682250977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1129722595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.742000579834</t>
+    <t xml:space="preserve">33.7258720397949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1129684448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7420043945312</t>
   </si>
   <si>
     <t xml:space="preserve">34.5968437194824</t>
   </si>
   <si>
-    <t xml:space="preserve">35.371036529541</t>
+    <t xml:space="preserve">35.3710327148438</t>
   </si>
   <si>
     <t xml:space="preserve">35.4678115844727</t>
@@ -2552,13 +2552,13 @@
     <t xml:space="preserve">36.8226509094238</t>
   </si>
   <si>
-    <t xml:space="preserve">37.1613655090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.1936187744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3065185546875</t>
+    <t xml:space="preserve">37.1613616943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.1936225891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3065223693848</t>
   </si>
   <si>
     <t xml:space="preserve">32.564582824707</t>
@@ -2567,22 +2567,22 @@
     <t xml:space="preserve">32.6613540649414</t>
   </si>
   <si>
-    <t xml:space="preserve">32.758129119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7097396850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9355449676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3387699127197</t>
+    <t xml:space="preserve">32.7581253051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7097434997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9355430603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3387680053711</t>
   </si>
   <si>
     <t xml:space="preserve">30.822639465332</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5807037353516</t>
+    <t xml:space="preserve">30.5807056427002</t>
   </si>
   <si>
     <t xml:space="preserve">30.4839305877686</t>
@@ -2591,19 +2591,19 @@
     <t xml:space="preserve">31.112964630127</t>
   </si>
   <si>
-    <t xml:space="preserve">33.435546875</t>
+    <t xml:space="preserve">33.4355506896973</t>
   </si>
   <si>
     <t xml:space="preserve">33.8710327148438</t>
   </si>
   <si>
-    <t xml:space="preserve">35.2742614746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6613616943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7097434997559</t>
+    <t xml:space="preserve">35.2742576599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6613578796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7097473144531</t>
   </si>
   <si>
     <t xml:space="preserve">37.2581367492676</t>
@@ -2618,19 +2618,19 @@
     <t xml:space="preserve">35.9516868591309</t>
   </si>
   <si>
-    <t xml:space="preserve">36.4355545043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0807151794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9839401245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6774978637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.0645866394043</t>
+    <t xml:space="preserve">36.4355583190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0807113647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.983943939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.677490234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.0645904541016</t>
   </si>
   <si>
     <t xml:space="preserve">37.6452331542969</t>
@@ -2639,10 +2639,10 @@
     <t xml:space="preserve">38.0323333740234</t>
   </si>
   <si>
-    <t xml:space="preserve">38.6129837036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.7581405639648</t>
+    <t xml:space="preserve">38.612979888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.7581367492676</t>
   </si>
   <si>
     <t xml:space="preserve">39.8226585388184</t>
@@ -2651,19 +2651,19 @@
     <t xml:space="preserve">39.6774940490723</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5645942687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.7097549438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6291084289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4516906738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.1613693237305</t>
+    <t xml:space="preserve">38.5645904541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.7097511291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6291122436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4516944885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.1613655090332</t>
   </si>
   <si>
     <t xml:space="preserve">39.4355621337891</t>
@@ -2678,19 +2678,19 @@
     <t xml:space="preserve">41.9033050537109</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0645942687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1775016784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8549194335938</t>
+    <t xml:space="preserve">40.0645904541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1774978637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.854923248291</t>
   </si>
   <si>
     <t xml:space="preserve">42.338794708252</t>
   </si>
   <si>
-    <t xml:space="preserve">42.048469543457</t>
+    <t xml:space="preserve">42.0484657287598</t>
   </si>
   <si>
     <t xml:space="preserve">42.6291160583496</t>
@@ -2699,13 +2699,13 @@
     <t xml:space="preserve">41.6129837036133</t>
   </si>
   <si>
-    <t xml:space="preserve">42.3871765136719</t>
+    <t xml:space="preserve">42.3871803283691</t>
   </si>
   <si>
     <t xml:space="preserve">43.5000839233398</t>
   </si>
   <si>
-    <t xml:space="preserve">44.1291160583496</t>
+    <t xml:space="preserve">44.1291198730469</t>
   </si>
   <si>
     <t xml:space="preserve">44.7097625732422</t>
@@ -2720,7 +2720,7 @@
     <t xml:space="preserve">44.4194374084473</t>
   </si>
   <si>
-    <t xml:space="preserve">45.0000801086426</t>
+    <t xml:space="preserve">45.0000839233398</t>
   </si>
   <si>
     <t xml:space="preserve">46.0162162780762</t>
@@ -2735,13 +2735,13 @@
     <t xml:space="preserve">46.2581520080566</t>
   </si>
   <si>
-    <t xml:space="preserve">45.1452484130859</t>
+    <t xml:space="preserve">45.1452522277832</t>
   </si>
   <si>
     <t xml:space="preserve">44.6129875183105</t>
   </si>
   <si>
-    <t xml:space="preserve">44.5162162780762</t>
+    <t xml:space="preserve">44.5162124633789</t>
   </si>
   <si>
     <t xml:space="preserve">44.2742805480957</t>
@@ -2750,28 +2750,28 @@
     <t xml:space="preserve">43.838794708252</t>
   </si>
   <si>
-    <t xml:space="preserve">43.1613731384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.3065338134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.2581520080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.8710479736328</t>
+    <t xml:space="preserve">43.1613693237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.3065299987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.2581481933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.8710517883301</t>
   </si>
   <si>
     <t xml:space="preserve">43.0645980834961</t>
   </si>
   <si>
-    <t xml:space="preserve">44.032341003418</t>
+    <t xml:space="preserve">44.0323448181152</t>
   </si>
   <si>
     <t xml:space="preserve">43.4033088684082</t>
   </si>
   <si>
-    <t xml:space="preserve">42.4355583190918</t>
+    <t xml:space="preserve">42.4355621337891</t>
   </si>
   <si>
     <t xml:space="preserve">41.8992919921875</t>
@@ -2786,7 +2786,7 @@
     <t xml:space="preserve">39.4576110839844</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0924453735352</t>
+    <t xml:space="preserve">40.0924415588379</t>
   </si>
   <si>
     <t xml:space="preserve">40.8737831115723</t>
@@ -2813,7 +2813,7 @@
     <t xml:space="preserve">39.6041069030762</t>
   </si>
   <si>
-    <t xml:space="preserve">39.7506065368652</t>
+    <t xml:space="preserve">39.7506103515625</t>
   </si>
   <si>
     <t xml:space="preserve">39.2622718811035</t>
@@ -2822,7 +2822,7 @@
     <t xml:space="preserve">40.2877769470215</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9459419250488</t>
+    <t xml:space="preserve">39.9459457397461</t>
   </si>
   <si>
     <t xml:space="preserve">37.8949279785156</t>
@@ -2834,37 +2834,37 @@
     <t xml:space="preserve">37.6019248962402</t>
   </si>
   <si>
-    <t xml:space="preserve">38.090259552002</t>
+    <t xml:space="preserve">38.0902633666992</t>
   </si>
   <si>
     <t xml:space="preserve">39.5552749633789</t>
   </si>
   <si>
-    <t xml:space="preserve">41.7039566040039</t>
+    <t xml:space="preserve">41.7039527893066</t>
   </si>
   <si>
     <t xml:space="preserve">42.0946235656738</t>
   </si>
   <si>
-    <t xml:space="preserve">41.4597854614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0691146850586</t>
+    <t xml:space="preserve">41.459789276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0691108703613</t>
   </si>
   <si>
     <t xml:space="preserve">40.385440826416</t>
   </si>
   <si>
-    <t xml:space="preserve">40.4342803955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.1922950744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.0457916259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.9481239318848</t>
+    <t xml:space="preserve">40.4342765808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.1922912597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.0457878112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.9481201171875</t>
   </si>
   <si>
     <t xml:space="preserve">41.4109535217285</t>
@@ -2891,7 +2891,7 @@
     <t xml:space="preserve">47.8081665039062</t>
   </si>
   <si>
-    <t xml:space="preserve">48.5406646728516</t>
+    <t xml:space="preserve">48.5406684875488</t>
   </si>
   <si>
     <t xml:space="preserve">48.5895004272461</t>
@@ -2906,7 +2906,7 @@
     <t xml:space="preserve">49.7126770019531</t>
   </si>
   <si>
-    <t xml:space="preserve">49.9080123901367</t>
+    <t xml:space="preserve">49.9080085754395</t>
   </si>
   <si>
     <t xml:space="preserve">49.8103446960449</t>
@@ -2924,7 +2924,7 @@
     <t xml:space="preserve">50.2986755371094</t>
   </si>
   <si>
-    <t xml:space="preserve">50.591682434082</t>
+    <t xml:space="preserve">50.5916862487793</t>
   </si>
   <si>
     <t xml:space="preserve">50.4940147399902</t>
@@ -2954,7 +2954,7 @@
     <t xml:space="preserve">45.2688102722168</t>
   </si>
   <si>
-    <t xml:space="preserve">44.536304473877</t>
+    <t xml:space="preserve">44.5363082885742</t>
   </si>
   <si>
     <t xml:space="preserve">43.5107955932617</t>
@@ -2984,7 +2984,7 @@
     <t xml:space="preserve">44.1944694519043</t>
   </si>
   <si>
-    <t xml:space="preserve">41.2156181335449</t>
+    <t xml:space="preserve">41.2156219482422</t>
   </si>
   <si>
     <t xml:space="preserve">40.9714508056641</t>
@@ -3002,7 +3002,7 @@
     <t xml:space="preserve">43.2666320800781</t>
   </si>
   <si>
-    <t xml:space="preserve">43.7061347961426</t>
+    <t xml:space="preserve">43.7061309814453</t>
   </si>
   <si>
     <t xml:space="preserve">44.3409767150879</t>
@@ -3020,19 +3020,19 @@
     <t xml:space="preserve">45.7571487426758</t>
   </si>
   <si>
-    <t xml:space="preserve">42.7782936096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2644462585449</t>
+    <t xml:space="preserve">42.7782974243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2644500732422</t>
   </si>
   <si>
     <t xml:space="preserve">42.6806259155273</t>
   </si>
   <si>
-    <t xml:space="preserve">43.1201324462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.3387870788574</t>
+    <t xml:space="preserve">43.1201362609863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.3387908935547</t>
   </si>
   <si>
     <t xml:space="preserve">42.4364585876465</t>
@@ -3053,10 +3053,10 @@
     <t xml:space="preserve">39.0669364929199</t>
   </si>
   <si>
-    <t xml:space="preserve">39.848274230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5319480895996</t>
+    <t xml:space="preserve">39.8482780456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5319442749023</t>
   </si>
   <si>
     <t xml:space="preserve">41.8504524230957</t>
@@ -3065,10 +3065,10 @@
     <t xml:space="preserve">41.1179504394531</t>
   </si>
   <si>
-    <t xml:space="preserve">40.8249473571777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.6551246643066</t>
+    <t xml:space="preserve">40.824951171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.6551208496094</t>
   </si>
   <si>
     <t xml:space="preserve">41.6062850952148</t>
@@ -3077,25 +3077,25 @@
     <t xml:space="preserve">42.485294342041</t>
   </si>
   <si>
-    <t xml:space="preserve">42.9736251831055</t>
+    <t xml:space="preserve">42.9736289978027</t>
   </si>
   <si>
     <t xml:space="preserve">41.8016166687012</t>
   </si>
   <si>
-    <t xml:space="preserve">41.362117767334</t>
+    <t xml:space="preserve">41.3621215820312</t>
   </si>
   <si>
     <t xml:space="preserve">40.238941192627</t>
   </si>
   <si>
-    <t xml:space="preserve">40.6296157836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.8759613037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.4619674682617</t>
+    <t xml:space="preserve">40.6296119689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.8759651184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.4619636535645</t>
   </si>
   <si>
     <t xml:space="preserve">43.999137878418</t>
@@ -3104,16 +3104,16 @@
     <t xml:space="preserve">40.9226150512695</t>
   </si>
   <si>
-    <t xml:space="preserve">39.1157722473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5829620361328</t>
+    <t xml:space="preserve">39.1157684326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5829582214355</t>
   </si>
   <si>
     <t xml:space="preserve">42.6317939758301</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5786018371582</t>
+    <t xml:space="preserve">38.5785980224609</t>
   </si>
   <si>
     <t xml:space="preserve">36.4299163818359</t>
@@ -3134,7 +3134,7 @@
     <t xml:space="preserve">35.5997428894043</t>
   </si>
   <si>
-    <t xml:space="preserve">36.527587890625</t>
+    <t xml:space="preserve">36.5275917053223</t>
   </si>
   <si>
     <t xml:space="preserve">36.6252517700195</t>
@@ -3143,16 +3143,16 @@
     <t xml:space="preserve">36.0880813598633</t>
   </si>
   <si>
-    <t xml:space="preserve">36.1369132995605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4532470703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5253982543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3810844421387</t>
+    <t xml:space="preserve">36.1369171142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4532432556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5254020690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3810806274414</t>
   </si>
   <si>
     <t xml:space="preserve">35.3555755615234</t>
@@ -3161,10 +3161,10 @@
     <t xml:space="preserve">33.9393997192383</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1325531005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4977169036865</t>
+    <t xml:space="preserve">32.1325569152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4977188110352</t>
   </si>
   <si>
     <t xml:space="preserve">31.6442222595215</t>
@@ -3173,7 +3173,7 @@
     <t xml:space="preserve">33.0115623474121</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3767280578613</t>
+    <t xml:space="preserve">32.3767242431641</t>
   </si>
   <si>
     <t xml:space="preserve">33.4510612487793</t>
@@ -3218,7 +3218,7 @@
     <t xml:space="preserve">32.767391204834</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2144832611084</t>
+    <t xml:space="preserve">31.2144813537598</t>
   </si>
   <si>
     <t xml:space="preserve">31.0191459655762</t>
@@ -3230,16 +3230,16 @@
     <t xml:space="preserve">29.6518058776855</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4722099304199</t>
+    <t xml:space="preserve">30.4722118377686</t>
   </si>
   <si>
     <t xml:space="preserve">32.2302207946777</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0739555358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.937219619751</t>
+    <t xml:space="preserve">32.0739517211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9372234344482</t>
   </si>
   <si>
     <t xml:space="preserve">31.3316860198975</t>
@@ -3251,10 +3251,10 @@
     <t xml:space="preserve">31.3902835845947</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6637496948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8862075805664</t>
+    <t xml:space="preserve">31.6637477874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8862056732178</t>
   </si>
   <si>
     <t xml:space="preserve">29.9643383026123</t>
@@ -3269,7 +3269,7 @@
     <t xml:space="preserve">29.2025337219238</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8704681396484</t>
+    <t xml:space="preserve">28.8704662322998</t>
   </si>
   <si>
     <t xml:space="preserve">28.9290676116943</t>
@@ -3278,13 +3278,13 @@
     <t xml:space="preserve">29.085334777832</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3039970397949</t>
+    <t xml:space="preserve">28.3039951324463</t>
   </si>
   <si>
     <t xml:space="preserve">28.4211978912354</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0147876739502</t>
+    <t xml:space="preserve">27.0147857666016</t>
   </si>
   <si>
     <t xml:space="preserve">28.3235301971436</t>
@@ -5259,6 +5259,9 @@
   </si>
   <si>
     <t xml:space="preserve">31.7999992370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5499992370605</t>
   </si>
 </sst>
 </file>
@@ -28937,7 +28940,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G898" t="s">
-        <v>593</v>
+        <v>403</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -28963,7 +28966,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G899" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -28989,7 +28992,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G900" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -29041,7 +29044,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G902" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -29093,7 +29096,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G904" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -29119,7 +29122,7 @@
         <v>15.5</v>
       </c>
       <c r="G905" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -29145,7 +29148,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G906" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -29171,7 +29174,7 @@
         <v>15.5</v>
       </c>
       <c r="G907" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -29249,7 +29252,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G910" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -29327,7 +29330,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G913" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -29379,7 +29382,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G915" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -29405,7 +29408,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G916" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -29431,7 +29434,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G917" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -29457,7 +29460,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G918" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -29483,7 +29486,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G919" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -29509,7 +29512,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G920" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -29535,7 +29538,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G921" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -29561,7 +29564,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G922" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -29587,7 +29590,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G923" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -29613,7 +29616,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G924" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -29639,7 +29642,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G925" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -29665,7 +29668,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G926" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -29691,7 +29694,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G927" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -29717,7 +29720,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G928" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -29769,7 +29772,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G930" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -29821,7 +29824,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G932" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -29873,7 +29876,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G934" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -29899,7 +29902,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G935" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -29925,7 +29928,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G936" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -29951,7 +29954,7 @@
         <v>16</v>
       </c>
       <c r="G937" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -29977,7 +29980,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G938" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -30003,7 +30006,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G939" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -30029,7 +30032,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G940" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -30055,7 +30058,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G941" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -30081,7 +30084,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G942" t="s">
-        <v>553</v>
+        <v>618</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -30471,7 +30474,7 @@
         <v>16</v>
       </c>
       <c r="G957" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -30601,7 +30604,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G962" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -30731,7 +30734,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G967" t="s">
-        <v>553</v>
+        <v>618</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -33643,7 +33646,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G1079" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -33695,7 +33698,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G1081" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -33981,7 +33984,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G1092" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -34137,7 +34140,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1098" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -34215,7 +34218,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G1101" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -34371,7 +34374,7 @@
         <v>16</v>
       </c>
       <c r="G1107" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -34397,7 +34400,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1108" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -34449,7 +34452,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1110" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -34475,7 +34478,7 @@
         <v>16</v>
       </c>
       <c r="G1111" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -34579,7 +34582,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G1115" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -72443,7 +72446,7 @@
     </row>
     <row r="2572">
       <c r="A2572" s="1" t="n">
-        <v>46066.6911921296</v>
+        <v>46066.3333333333</v>
       </c>
       <c r="B2572" t="n">
         <v>149243</v>
@@ -72464,6 +72467,32 @@
         <v>1748</v>
       </c>
       <c r="H2572" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2573">
+      <c r="A2573" s="1" t="n">
+        <v>46069.6911342593</v>
+      </c>
+      <c r="B2573" t="n">
+        <v>66430</v>
+      </c>
+      <c r="C2573" t="n">
+        <v>32.0499992370605</v>
+      </c>
+      <c r="D2573" t="n">
+        <v>31.3500003814697</v>
+      </c>
+      <c r="E2573" t="n">
+        <v>31.7999992370605</v>
+      </c>
+      <c r="F2573" t="n">
+        <v>31.5499992370605</v>
+      </c>
+      <c r="G2573" t="s">
+        <v>1749</v>
+      </c>
+      <c r="H2573" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MOL.MI.xlsx
+++ b/data/MOL.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1750" uniqueCount="1750">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1751" uniqueCount="1751">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,46 +38,46 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85066080093384</t>
+    <t xml:space="preserve">6.850661277771</t>
   </si>
   <si>
     <t xml:space="preserve">MOL.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75772666931152</t>
+    <t xml:space="preserve">6.75772619247437</t>
   </si>
   <si>
     <t xml:space="preserve">6.66036558151245</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77100324630737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63823843002319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72674798965454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81525707244873</t>
+    <t xml:space="preserve">6.77100276947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63823795318604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72674751281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81525754928589</t>
   </si>
   <si>
     <t xml:space="preserve">6.54972839355469</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31960296630859</t>
+    <t xml:space="preserve">6.31960248947144</t>
   </si>
   <si>
     <t xml:space="preserve">6.09832811355591</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35058069229126</t>
+    <t xml:space="preserve">6.35058116912842</t>
   </si>
   <si>
     <t xml:space="preserve">6.2399435043335</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5585789680481</t>
+    <t xml:space="preserve">6.55857849121094</t>
   </si>
   <si>
     <t xml:space="preserve">6.46121835708618</t>
@@ -86,91 +86,91 @@
     <t xml:space="preserve">5.89475536346436</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5231761932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65594053268433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76215171813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66479158401489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69134330749512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68249320983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01866960525513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89918088912964</t>
+    <t xml:space="preserve">6.52317523956299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65593957901001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76215219497681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66479110717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69134378433228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68249273300171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01866912841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8991813659668</t>
   </si>
   <si>
     <t xml:space="preserve">6.28419876098633</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0629243850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25322008132935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39926099777222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34173059463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50989866256714</t>
+    <t xml:space="preserve">6.06292390823364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2532205581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39926147460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34173011779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5098991394043</t>
   </si>
   <si>
     <t xml:space="preserve">6.33287954330444</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42581462860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39041090011597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30632591247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40811157226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35500621795654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63381195068359</t>
+    <t xml:space="preserve">6.42581415176392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39041042327881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30632638931274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40811204910278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35500717163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63381242752075</t>
   </si>
   <si>
     <t xml:space="preserve">6.43466520309448</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22666645050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24436950683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27534818649292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2664966583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62938642501831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43909072875977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41253805160522</t>
+    <t xml:space="preserve">6.22666692733765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24436902999878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27534770965576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26649713516235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62938737869263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43909120559692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41253757476807</t>
   </si>
   <si>
     <t xml:space="preserve">6.45236730575562</t>
@@ -179,10 +179,10 @@
     <t xml:space="preserve">6.4567928314209</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36828279495239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19568920135498</t>
+    <t xml:space="preserve">6.36828327178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19568872451782</t>
   </si>
   <si>
     <t xml:space="preserve">6.06734943389893</t>
@@ -191,37 +191,37 @@
     <t xml:space="preserve">6.28862428665161</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20453929901123</t>
+    <t xml:space="preserve">6.20453977584839</t>
   </si>
   <si>
     <t xml:space="preserve">6.29304933547974</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24879455566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22224140167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25764656066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15585947036743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19126272201538</t>
+    <t xml:space="preserve">6.2487940788269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22224235534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25764608383179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15585899353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1912636756897</t>
   </si>
   <si>
     <t xml:space="preserve">6.58955812454224</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47892189025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49662113189697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42138910293579</t>
+    <t xml:space="preserve">6.47892093658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49662208557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42138957977295</t>
   </si>
   <si>
     <t xml:space="preserve">6.63348913192749</t>
@@ -233,10 +233,10 @@
     <t xml:space="preserve">6.54311466217041</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44370269775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50696468353271</t>
+    <t xml:space="preserve">6.44370222091675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50696563720703</t>
   </si>
   <si>
     <t xml:space="preserve">6.55667114257812</t>
@@ -251,34 +251,34 @@
     <t xml:space="preserve">6.69223308563232</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59733915328979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6831955909729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70578956604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75097608566284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85038757324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94528150558472</t>
+    <t xml:space="preserve">6.59733963012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68319511413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70578861236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75097513198853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8503885269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94528102874756</t>
   </si>
   <si>
     <t xml:space="preserve">6.98594951629639</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10343647003174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25255441665649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32033586502075</t>
+    <t xml:space="preserve">7.10343742370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25255393981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32033729553223</t>
   </si>
   <si>
     <t xml:space="preserve">7.45589733123779</t>
@@ -296,31 +296,31 @@
     <t xml:space="preserve">7.22996139526367</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22544193267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19833040237427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09439945220947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13958597183228</t>
+    <t xml:space="preserve">7.22544240951538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19832992553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09439897537231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13958644866943</t>
   </si>
   <si>
     <t xml:space="preserve">7.00402498245239</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08084297180176</t>
+    <t xml:space="preserve">7.08084344863892</t>
   </si>
   <si>
     <t xml:space="preserve">6.95883798599243</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84135055541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11699342727661</t>
+    <t xml:space="preserve">6.84135103225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11699295043945</t>
   </si>
   <si>
     <t xml:space="preserve">7.16669940948486</t>
@@ -329,7 +329,7 @@
     <t xml:space="preserve">7.31129884719849</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32485437393188</t>
+    <t xml:space="preserve">7.32485294342041</t>
   </si>
   <si>
     <t xml:space="preserve">6.99950647354126</t>
@@ -338,7 +338,7 @@
     <t xml:space="preserve">6.73290061950684</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08988094329834</t>
+    <t xml:space="preserve">7.08988046646118</t>
   </si>
   <si>
     <t xml:space="preserve">7.18477344512939</t>
@@ -347,28 +347,28 @@
     <t xml:space="preserve">6.85942602157593</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67867660522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49792814254761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57022714614868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57926464080811</t>
+    <t xml:space="preserve">6.67867612838745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49792718887329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57022762298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57926511764526</t>
   </si>
   <si>
     <t xml:space="preserve">6.41659069061279</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74645805358887</t>
+    <t xml:space="preserve">6.74645853042603</t>
   </si>
   <si>
     <t xml:space="preserve">6.6515645980835</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55215263366699</t>
+    <t xml:space="preserve">6.55215215682983</t>
   </si>
   <si>
     <t xml:space="preserve">6.46177864074707</t>
@@ -377,13 +377,13 @@
     <t xml:space="preserve">6.75549459457397</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56570816040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77808856964111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71030807495117</t>
+    <t xml:space="preserve">6.56570768356323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77808904647827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71030759811401</t>
   </si>
   <si>
     <t xml:space="preserve">6.48888969421387</t>
@@ -392,7 +392,7 @@
     <t xml:space="preserve">6.53859615325928</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66060161590576</t>
+    <t xml:space="preserve">6.6606011390686</t>
   </si>
   <si>
     <t xml:space="preserve">6.68771362304688</t>
@@ -401,10 +401,10 @@
     <t xml:space="preserve">6.76001358032227</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87750101089478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70127105712891</t>
+    <t xml:space="preserve">6.87750053405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70127010345459</t>
   </si>
   <si>
     <t xml:space="preserve">6.78712606430054</t>
@@ -413,67 +413,67 @@
     <t xml:space="preserve">6.7961630821228</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81423759460449</t>
+    <t xml:space="preserve">6.81423807144165</t>
   </si>
   <si>
     <t xml:space="preserve">6.8187575340271</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82327604293823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80520153045654</t>
+    <t xml:space="preserve">6.82327556610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80520105361938</t>
   </si>
   <si>
     <t xml:space="preserve">6.92268800735474</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90461254119873</t>
+    <t xml:space="preserve">6.90461301803589</t>
   </si>
   <si>
     <t xml:space="preserve">6.86846256256104</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98143100738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17573738098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01306343078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97691202163696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64252710342407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6967511177063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88653802871704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93172550201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02209997177124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99046897888184</t>
+    <t xml:space="preserve">6.98143148422241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17573642730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01306247711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97691297531128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64252662658691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69675159454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88653755187988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93172597885132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0221004486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99046850204468</t>
   </si>
   <si>
     <t xml:space="preserve">7.19381141662598</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05824899673462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04921245574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06728744506836</t>
+    <t xml:space="preserve">7.05824947357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04921197891235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0672869682312</t>
   </si>
   <si>
     <t xml:space="preserve">7.14862442016602</t>
@@ -485,70 +485,70 @@
     <t xml:space="preserve">7.06276798248291</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15766191482544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21188592910767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38359832763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22092342376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24803686141968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18929195404053</t>
+    <t xml:space="preserve">7.15766143798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21188688278198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38359785079956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22092294692993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24803638458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18929290771484</t>
   </si>
   <si>
     <t xml:space="preserve">7.35648536682129</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37004137039185</t>
+    <t xml:space="preserve">7.370041847229</t>
   </si>
   <si>
     <t xml:space="preserve">6.88201951980591</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0356559753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18025541305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91365098953247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5191593170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47849082946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50108432769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41071081161499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27514886856079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60953330993652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66375827789307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72702264785767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68183374404907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67731428146362</t>
+    <t xml:space="preserve">7.03565549850464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18025493621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91365051269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51915836334229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4784893989563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50108480453491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41070938110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27514839172363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60953426361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66375780105591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72702074050903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68183279037476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6773157119751</t>
   </si>
   <si>
     <t xml:space="preserve">7.63664579391479</t>
@@ -563,31 +563,31 @@
     <t xml:space="preserve">8.34156703948975</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41386795043945</t>
+    <t xml:space="preserve">8.41386699676514</t>
   </si>
   <si>
     <t xml:space="preserve">8.45001697540283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57654094696045</t>
+    <t xml:space="preserve">8.57654190063477</t>
   </si>
   <si>
     <t xml:space="preserve">8.37771797180176</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40935039520264</t>
+    <t xml:space="preserve">8.409348487854</t>
   </si>
   <si>
     <t xml:space="preserve">8.35964298248291</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22408199310303</t>
+    <t xml:space="preserve">8.22408103942871</t>
   </si>
   <si>
     <t xml:space="preserve">8.24215507507324</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33704853057861</t>
+    <t xml:space="preserve">8.33704948425293</t>
   </si>
   <si>
     <t xml:space="preserve">8.32801151275635</t>
@@ -596,13 +596,13 @@
     <t xml:space="preserve">8.3234920501709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36416053771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37319755554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46809101104736</t>
+    <t xml:space="preserve">8.36416149139404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37319850921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46809196472168</t>
   </si>
   <si>
     <t xml:space="preserve">8.30541801452637</t>
@@ -611,13 +611,13 @@
     <t xml:space="preserve">8.30090045928955</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09755706787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26926803588867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20600605010986</t>
+    <t xml:space="preserve">8.09755611419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26926708221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20600700378418</t>
   </si>
   <si>
     <t xml:space="preserve">8.07496356964111</t>
@@ -626,43 +626,43 @@
     <t xml:space="preserve">8.11111259460449</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28282260894775</t>
+    <t xml:space="preserve">8.28282451629639</t>
   </si>
   <si>
     <t xml:space="preserve">8.2963809967041</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40482997894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48164844512939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42290592193604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22859954833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27378559112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02977466583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13370704650879</t>
+    <t xml:space="preserve">8.40482902526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48164939880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42290496826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22860050201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2737865447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02977561950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13370609283447</t>
   </si>
   <si>
     <t xml:space="preserve">8.27830505371094</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43194103240967</t>
+    <t xml:space="preserve">8.4319429397583</t>
   </si>
   <si>
     <t xml:space="preserve">8.6940279006958</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57969760894775</t>
+    <t xml:space="preserve">9.57969856262207</t>
   </si>
   <si>
     <t xml:space="preserve">9.25435066223145</t>
@@ -671,7 +671,7 @@
     <t xml:space="preserve">9.21820068359375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01937675476074</t>
+    <t xml:space="preserve">9.01937484741211</t>
   </si>
   <si>
     <t xml:space="preserve">9.16397571563721</t>
@@ -680,22 +680,22 @@
     <t xml:space="preserve">9.20012664794922</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20916175842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22723865509033</t>
+    <t xml:space="preserve">9.20916271209717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22723770141602</t>
   </si>
   <si>
     <t xml:space="preserve">8.94707775115967</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03744983673096</t>
+    <t xml:space="preserve">9.03745079040527</t>
   </si>
   <si>
     <t xml:space="preserve">9.12782669067383</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35376167297363</t>
+    <t xml:space="preserve">9.35376262664795</t>
   </si>
   <si>
     <t xml:space="preserve">9.55258560180664</t>
@@ -704,13 +704,13 @@
     <t xml:space="preserve">9.47124671936035</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80563640594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89601039886475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2123203277588</t>
+    <t xml:space="preserve">9.80563545227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89600944519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2123212814331</t>
   </si>
   <si>
     <t xml:space="preserve">9.94119644165039</t>
@@ -722,28 +722,28 @@
     <t xml:space="preserve">10.8449420928955</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8087921142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9082050323486</t>
+    <t xml:space="preserve">10.8087930679321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9082040786743</t>
   </si>
   <si>
     <t xml:space="preserve">10.9353170394897</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7364931106567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7093801498413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7545671463013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.476432800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2261095046997</t>
+    <t xml:space="preserve">10.7364902496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7093820571899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7545680999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4764318466187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.226110458374</t>
   </si>
   <si>
     <t xml:space="preserve">10.0128726959229</t>
@@ -752,37 +752,37 @@
     <t xml:space="preserve">10.3837203979492</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4300756454468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2817373275757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4022607803345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5135164260864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4949750900269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5413312911987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7452945709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0790576934814</t>
+    <t xml:space="preserve">10.4300765991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2817363739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4022626876831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5135154724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4949731826782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5413303375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7452955245972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0790586471558</t>
   </si>
   <si>
     <t xml:space="preserve">11.7743968963623</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5889720916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2181253433228</t>
+    <t xml:space="preserve">11.5889739990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2181262969971</t>
   </si>
   <si>
     <t xml:space="preserve">11.3015661239624</t>
@@ -791,19 +791,19 @@
     <t xml:space="preserve">11.097601890564</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1439561843872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0327024459839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8287363052368</t>
+    <t xml:space="preserve">11.1439571380615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0327014923096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8287372589111</t>
   </si>
   <si>
     <t xml:space="preserve">10.7545690536499</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7360248565674</t>
+    <t xml:space="preserve">10.7360258102417</t>
   </si>
   <si>
     <t xml:space="preserve">10.9863471984863</t>
@@ -815,7 +815,7 @@
     <t xml:space="preserve">10.5691432952881</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1254138946533</t>
+    <t xml:space="preserve">11.125412940979</t>
   </si>
   <si>
     <t xml:space="preserve">11.0605154037476</t>
@@ -827,58 +827,58 @@
     <t xml:space="preserve">11.0697870254517</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9399909973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4499063491821</t>
+    <t xml:space="preserve">10.9399929046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4499053955078</t>
   </si>
   <si>
     <t xml:space="preserve">11.4035491943359</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7094993591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0988874435425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3213968276978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.894923210144</t>
+    <t xml:space="preserve">11.7094974517822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0988883972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3213958740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8949213027954</t>
   </si>
   <si>
     <t xml:space="preserve">12.5160913467407</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5253610610962</t>
+    <t xml:space="preserve">12.5253620147705</t>
   </si>
   <si>
     <t xml:space="preserve">12.6737012863159</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7478704452515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5346345901489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.794225692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7293272018433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5439052581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5809879302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5624485015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4697351455688</t>
+    <t xml:space="preserve">12.7478694915771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5346336364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7942266464233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7293281555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5439043045044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5809898376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5624475479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4697360992432</t>
   </si>
   <si>
     <t xml:space="preserve">12.4975481033325</t>
@@ -887,31 +887,31 @@
     <t xml:space="preserve">12.4882783889771</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6829710006714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.627345085144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5531768798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1823291778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3955659866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.423378944397</t>
+    <t xml:space="preserve">12.6829719543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6273460388184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5531749725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1823282241821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.395565032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4233779907227</t>
   </si>
   <si>
     <t xml:space="preserve">12.2935838699341</t>
   </si>
   <si>
-    <t xml:space="preserve">12.367751121521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8856496810913</t>
+    <t xml:space="preserve">12.3677530288696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8856515884399</t>
   </si>
   <si>
     <t xml:space="preserve">12.28431224823</t>
@@ -920,13 +920,13 @@
     <t xml:space="preserve">12.1730575561523</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0525331497192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9505500793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3121252059937</t>
+    <t xml:space="preserve">12.0525312423706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9505491256714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.312126159668</t>
   </si>
   <si>
     <t xml:space="preserve">12.2657690048218</t>
@@ -935,34 +935,34 @@
     <t xml:space="preserve">11.9412775039673</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9598197937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3306684494019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4419221878052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3492097854614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3770246505737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1545143127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2472257614136</t>
+    <t xml:space="preserve">11.9598207473755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3306674957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4419212341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3492107391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.377025604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1545133590698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2472267150879</t>
   </si>
   <si>
     <t xml:space="preserve">12.3399391174316</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4511938095093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.200870513916</t>
+    <t xml:space="preserve">12.451192855835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2008714675903</t>
   </si>
   <si>
     <t xml:space="preserve">12.4326496124268</t>
@@ -974,10 +974,10 @@
     <t xml:space="preserve">12.2564992904663</t>
   </si>
   <si>
-    <t xml:space="preserve">12.061803817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0247173309326</t>
+    <t xml:space="preserve">12.0618028640747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0247192382812</t>
   </si>
   <si>
     <t xml:space="preserve">11.4406337738037</t>
@@ -989,28 +989,28 @@
     <t xml:space="preserve">11.7929401397705</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6631412506104</t>
+    <t xml:space="preserve">11.663143157959</t>
   </si>
   <si>
     <t xml:space="preserve">11.6816844940186</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7465839385986</t>
+    <t xml:space="preserve">11.74658203125</t>
   </si>
   <si>
     <t xml:space="preserve">11.9227342605591</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8207521438599</t>
+    <t xml:space="preserve">11.8207530975342</t>
   </si>
   <si>
     <t xml:space="preserve">11.8671083450317</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7373123168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2286853790283</t>
+    <t xml:space="preserve">11.7373113632202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.228684425354</t>
   </si>
   <si>
     <t xml:space="preserve">12.1915998458862</t>
@@ -1022,13 +1022,13 @@
     <t xml:space="preserve">11.7187690734863</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1903133392334</t>
+    <t xml:space="preserve">11.1903123855591</t>
   </si>
   <si>
     <t xml:space="preserve">11.2922954559326</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1624984741211</t>
+    <t xml:space="preserve">11.1625003814697</t>
   </si>
   <si>
     <t xml:space="preserve">11.5426168441772</t>
@@ -1037,13 +1037,13 @@
     <t xml:space="preserve">11.4684476852417</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5982446670532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.579701423645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4962615966797</t>
+    <t xml:space="preserve">11.5982456207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5797033309937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4962606430054</t>
   </si>
   <si>
     <t xml:space="preserve">11.6724138259888</t>
@@ -1058,31 +1058,31 @@
     <t xml:space="preserve">12.0061769485474</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9134654998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9240236282349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.925311088562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1107339859009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0921907424927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9438524246216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9994812011719</t>
+    <t xml:space="preserve">11.9134645462036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9240217208862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9253091812134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1107349395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.092191696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9438514709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9994802474976</t>
   </si>
   <si>
     <t xml:space="preserve">14.6299200057983</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9067678451538</t>
+    <t xml:space="preserve">13.9067687988281</t>
   </si>
   <si>
     <t xml:space="preserve">13.6286325454712</t>
@@ -1091,16 +1091,16 @@
     <t xml:space="preserve">14.2034454345703</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0180215835571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7028026580811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3888702392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5186643600464</t>
+    <t xml:space="preserve">14.0180225372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7028017044067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3888692855835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.518666267395</t>
   </si>
   <si>
     <t xml:space="preserve">14.5742931365967</t>
@@ -1109,7 +1109,7 @@
     <t xml:space="preserve">14.4815807342529</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1849050521851</t>
+    <t xml:space="preserve">14.1849040985107</t>
   </si>
   <si>
     <t xml:space="preserve">13.8325977325439</t>
@@ -1124,10 +1124,10 @@
     <t xml:space="preserve">13.3690395355225</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0352773666382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7385988235474</t>
+    <t xml:space="preserve">13.0352783203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7385997772217</t>
   </si>
   <si>
     <t xml:space="preserve">12.9796504974365</t>
@@ -1136,37 +1136,37 @@
     <t xml:space="preserve">13.5173778533936</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3134117126465</t>
+    <t xml:space="preserve">13.3134126663208</t>
   </si>
   <si>
     <t xml:space="preserve">12.6644306182861</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1081590652466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0154476165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.830023765564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5902605056763</t>
+    <t xml:space="preserve">12.1081600189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0154485702515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8300247192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.590259552002</t>
   </si>
   <si>
     <t xml:space="preserve">12.7200574874878</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6088037490845</t>
+    <t xml:space="preserve">12.6088047027588</t>
   </si>
   <si>
     <t xml:space="preserve">12.1637868881226</t>
   </si>
   <si>
-    <t xml:space="preserve">12.033989906311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0710763931274</t>
+    <t xml:space="preserve">12.0339889526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0710735321045</t>
   </si>
   <si>
     <t xml:space="preserve">11.6075162887573</t>
@@ -1175,82 +1175,82 @@
     <t xml:space="preserve">12.4604625701904</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8114805221558</t>
+    <t xml:space="preserve">11.8114814758301</t>
   </si>
   <si>
     <t xml:space="preserve">11.8485670089722</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2379550933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3862953186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3504972457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5359201431274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7213439941406</t>
+    <t xml:space="preserve">12.2379560470581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3862943649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3504962921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5359210968018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7213449478149</t>
   </si>
   <si>
     <t xml:space="preserve">14.2590732574463</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9080562591553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7782592773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.741171836853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7968006134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0235710144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6849870681763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4015216827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2314462661743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0802640914917</t>
+    <t xml:space="preserve">14.908055305481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7782583236694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7411737442017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7968015670776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0235719680786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6849880218506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4015226364136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2314453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.080265045166</t>
   </si>
   <si>
     <t xml:space="preserve">15.1180601119995</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1747531890869</t>
+    <t xml:space="preserve">15.1747512817383</t>
   </si>
   <si>
     <t xml:space="preserve">15.3070363998413</t>
   </si>
   <si>
-    <t xml:space="preserve">14.13538646698</t>
+    <t xml:space="preserve">14.1353855133057</t>
   </si>
   <si>
     <t xml:space="preserve">13.8141269683838</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2660961151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6062517166138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6818437576294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0771207809448</t>
+    <t xml:space="preserve">13.2660980224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6062526702881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6818428039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0771217346191</t>
   </si>
   <si>
     <t xml:space="preserve">12.9448385238647</t>
@@ -1259,28 +1259,28 @@
     <t xml:space="preserve">13.1149168014526</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8881454467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0944471359253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5479888916016</t>
+    <t xml:space="preserve">12.8881464004517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0944480895996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5479898452759</t>
   </si>
   <si>
     <t xml:space="preserve">13.0015316009521</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6235799789429</t>
+    <t xml:space="preserve">12.6235790252686</t>
   </si>
   <si>
     <t xml:space="preserve">12.6991691589355</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7558612823486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8692474365234</t>
+    <t xml:space="preserve">12.7558631896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8692483901978</t>
   </si>
   <si>
     <t xml:space="preserve">12.3401174545288</t>
@@ -1289,22 +1289,22 @@
     <t xml:space="preserve">12.7369651794434</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7180681228638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7747611999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2645263671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7385358810425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7763328552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9653081893921</t>
+    <t xml:space="preserve">12.7180671691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7747602462769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2645244598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7385349273682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7763319015503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9653072357178</t>
   </si>
   <si>
     <t xml:space="preserve">13.8708190917969</t>
@@ -1313,7 +1313,7 @@
     <t xml:space="preserve">14.0786933898926</t>
   </si>
   <si>
-    <t xml:space="preserve">13.625150680542</t>
+    <t xml:space="preserve">13.6251516342163</t>
   </si>
   <si>
     <t xml:space="preserve">13.5873565673828</t>
@@ -1322,49 +1322,49 @@
     <t xml:space="preserve">13.4172782897949</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4550733566284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4361763000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2471990585327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1338119506836</t>
+    <t xml:space="preserve">13.4550724029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4361753463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.247200012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1338129043579</t>
   </si>
   <si>
     <t xml:space="preserve">13.322790145874</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4739713668823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2094049453735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3605842590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5668888092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5101947784424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2834234237671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6802740097046</t>
+    <t xml:space="preserve">13.473970413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2094039916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3605861663818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5668878555298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5101938247681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2834224700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.680272102356</t>
   </si>
   <si>
     <t xml:space="preserve">13.0393266677856</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9826326370239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.812557220459</t>
+    <t xml:space="preserve">12.9826345443726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8125553131104</t>
   </si>
   <si>
     <t xml:space="preserve">12.9637365341187</t>
@@ -1382,13 +1382,13 @@
     <t xml:space="preserve">14.3054637908936</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0597953796387</t>
+    <t xml:space="preserve">14.0597972869873</t>
   </si>
   <si>
     <t xml:space="preserve">13.7007417678833</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4928674697876</t>
+    <t xml:space="preserve">13.4928684234619</t>
   </si>
   <si>
     <t xml:space="preserve">13.7574338912964</t>
@@ -1397,19 +1397,19 @@
     <t xml:space="preserve">13.5495615005493</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1731805801392</t>
+    <t xml:space="preserve">14.1731815338135</t>
   </si>
   <si>
     <t xml:space="preserve">14.9290838241577</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4960117340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2692384719849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1558561325073</t>
+    <t xml:space="preserve">15.4960098266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2692394256592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.155855178833</t>
   </si>
   <si>
     <t xml:space="preserve">16.5353755950928</t>
@@ -1418,10 +1418,10 @@
     <t xml:space="preserve">16.7054557800293</t>
   </si>
   <si>
-    <t xml:space="preserve">16.913330078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6298675537109</t>
+    <t xml:space="preserve">16.9133281707764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6298637390137</t>
   </si>
   <si>
     <t xml:space="preserve">16.2330169677734</t>
@@ -1430,34 +1430,34 @@
     <t xml:space="preserve">15.9117565155029</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5904979705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5149078369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0046739578247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2125482559204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3810548782349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6078252792358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4377470016479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6456184387207</t>
+    <t xml:space="preserve">15.5904998779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5149116516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.004674911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2125473022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3810558319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6078243255615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4377479553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6456203460693</t>
   </si>
   <si>
     <t xml:space="preserve">14.2487707138062</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1920795440674</t>
+    <t xml:space="preserve">14.1920776367188</t>
   </si>
   <si>
     <t xml:space="preserve">13.8897171020508</t>
@@ -1466,10 +1466,10 @@
     <t xml:space="preserve">13.5306644439697</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8519229888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0220012664795</t>
+    <t xml:space="preserve">13.8519220352173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0220022201538</t>
   </si>
   <si>
     <t xml:space="preserve">14.8723907470703</t>
@@ -1481,7 +1481,7 @@
     <t xml:space="preserve">14.4188499450684</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5527009963989</t>
+    <t xml:space="preserve">15.5527048110962</t>
   </si>
   <si>
     <t xml:space="preserve">14.9668798446655</t>
@@ -1490,109 +1490,109 @@
     <t xml:space="preserve">16.0818347930908</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0629386901855</t>
+    <t xml:space="preserve">16.0629405975342</t>
   </si>
   <si>
     <t xml:space="preserve">16.2519149780273</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0440406799316</t>
+    <t xml:space="preserve">16.0440425872803</t>
   </si>
   <si>
     <t xml:space="preserve">15.8739624023438</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4582147598267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0251426696777</t>
+    <t xml:space="preserve">15.4582176208496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0251407623291</t>
   </si>
   <si>
     <t xml:space="preserve">16.3464031219482</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1007347106934</t>
+    <t xml:space="preserve">16.100736618042</t>
   </si>
   <si>
     <t xml:space="preserve">16.3275051116943</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6471910476685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7983713150024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9306583404541</t>
+    <t xml:space="preserve">15.6471920013428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7983703613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9306545257568</t>
   </si>
   <si>
     <t xml:space="preserve">15.0613660812378</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8550672531128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4771127700806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7401094436646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9101867675781</t>
+    <t xml:space="preserve">15.8550634384155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4771118164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7401084899902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9101858139038</t>
   </si>
   <si>
     <t xml:space="preserve">14.5511322021484</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8156986236572</t>
+    <t xml:space="preserve">14.8156995773315</t>
   </si>
   <si>
     <t xml:space="preserve">14.9857769012451</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5338077545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7416801452637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0424699783325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4204216003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7605781555176</t>
+    <t xml:space="preserve">15.5338087081909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.741681098938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0424690246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4204196929932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7605752944946</t>
   </si>
   <si>
     <t xml:space="preserve">15.6282968521118</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8928594589233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9684505462646</t>
+    <t xml:space="preserve">15.8928575515747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.968448638916</t>
   </si>
   <si>
     <t xml:space="preserve">16.0062446594238</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9873495101929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6093978881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6834163665771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6267232894897</t>
+    <t xml:space="preserve">15.9873476028442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6093969345093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6834154129028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6267213821411</t>
   </si>
   <si>
     <t xml:space="preserve">14.853494644165</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1936502456665</t>
+    <t xml:space="preserve">15.1936492919922</t>
   </si>
   <si>
     <t xml:space="preserve">15.0991621017456</t>
@@ -1601,28 +1601,28 @@
     <t xml:space="preserve">15.2881383895874</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1952228546143</t>
+    <t xml:space="preserve">16.1952209472656</t>
   </si>
   <si>
     <t xml:space="preserve">17.0078201293945</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2345905303955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2534866333008</t>
+    <t xml:space="preserve">17.2345867156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2534847259521</t>
   </si>
   <si>
     <t xml:space="preserve">17.2912769317627</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1023044586182</t>
+    <t xml:space="preserve">17.1023063659668</t>
   </si>
   <si>
     <t xml:space="preserve">17.0645084381104</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0471858978271</t>
+    <t xml:space="preserve">18.0471820831299</t>
   </si>
   <si>
     <t xml:space="preserve">17.4046649932861</t>
@@ -1631,31 +1631,31 @@
     <t xml:space="preserve">17.347972869873</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3668727874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4991569519043</t>
+    <t xml:space="preserve">17.366870880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.499153137207</t>
   </si>
   <si>
     <t xml:space="preserve">17.0456123352051</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3857688903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4424629211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8582077026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8204135894775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5558490753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3290748596191</t>
+    <t xml:space="preserve">17.3857669830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4424610137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8582096099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8204116821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5558471679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3290767669678</t>
   </si>
   <si>
     <t xml:space="preserve">17.140100479126</t>
@@ -1676,13 +1676,13 @@
     <t xml:space="preserve">16.1574287414551</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5805988311768</t>
+    <t xml:space="preserve">16.5805969238281</t>
   </si>
   <si>
     <t xml:space="preserve">16.5421276092529</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3882465362549</t>
+    <t xml:space="preserve">16.3882484436035</t>
   </si>
   <si>
     <t xml:space="preserve">16.4459533691406</t>
@@ -1691,22 +1691,22 @@
     <t xml:space="preserve">16.2343654632568</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0035457611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9843120574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6767730712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8114185333252</t>
+    <t xml:space="preserve">16.0035438537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9843101501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6767711639404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8114166259766</t>
   </si>
   <si>
     <t xml:space="preserve">16.8306522369385</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7537117004395</t>
+    <t xml:space="preserve">16.7537136077881</t>
   </si>
   <si>
     <t xml:space="preserve">16.6383018493652</t>
@@ -1715,76 +1715,76 @@
     <t xml:space="preserve">16.4267158508301</t>
   </si>
   <si>
-    <t xml:space="preserve">16.522891998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9458417892456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4651889801025</t>
+    <t xml:space="preserve">16.5228900909424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.945839881897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4651870727539</t>
   </si>
   <si>
     <t xml:space="preserve">15.9650754928589</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0227813720703</t>
+    <t xml:space="preserve">16.0227794647217</t>
   </si>
   <si>
     <t xml:space="preserve">15.8688993453979</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7342538833618</t>
+    <t xml:space="preserve">15.7342548370361</t>
   </si>
   <si>
     <t xml:space="preserve">15.6573152542114</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4264974594116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3687896728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3110857009888</t>
+    <t xml:space="preserve">15.426495552063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3687887191772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3110837936401</t>
   </si>
   <si>
     <t xml:space="preserve">14.9840898513794</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1956758499146</t>
+    <t xml:space="preserve">15.1956748962402</t>
   </si>
   <si>
     <t xml:space="preserve">15.2341451644897</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1379690170288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0994997024536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0033254623413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1187343597412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2533807754517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0610294342041</t>
+    <t xml:space="preserve">15.1379680633545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0994987487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.003324508667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1187334060669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2533798217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0610303878784</t>
   </si>
   <si>
     <t xml:space="preserve">14.8686800003052</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8494434356689</t>
+    <t xml:space="preserve">14.8494443893433</t>
   </si>
   <si>
     <t xml:space="preserve">14.7147989273071</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4457311630249</t>
+    <t xml:space="preserve">15.445728302002</t>
   </si>
   <si>
     <t xml:space="preserve">15.1764392852783</t>
@@ -1793,31 +1793,31 @@
     <t xml:space="preserve">14.8302097320557</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9648532867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1572036743164</t>
+    <t xml:space="preserve">14.9648551940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1572046279907</t>
   </si>
   <si>
     <t xml:space="preserve">14.7917394638062</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7532682418823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9071474075317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0225582122803</t>
+    <t xml:space="preserve">14.7532691955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9071483612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0225601196289</t>
   </si>
   <si>
     <t xml:space="preserve">14.8109741210938</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8879146575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5416841506958</t>
+    <t xml:space="preserve">14.8879137039185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5416831970215</t>
   </si>
   <si>
     <t xml:space="preserve">14.580153465271</t>
@@ -1826,10 +1826,10 @@
     <t xml:space="preserve">14.5993890762329</t>
   </si>
   <si>
-    <t xml:space="preserve">14.503212928772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6378583908081</t>
+    <t xml:space="preserve">14.5032138824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6378593444824</t>
   </si>
   <si>
     <t xml:space="preserve">14.6186227798462</t>
@@ -1838,43 +1838,43 @@
     <t xml:space="preserve">14.4647426605225</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4455099105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.65709400177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9263849258423</t>
+    <t xml:space="preserve">14.4455089569092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6570930480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9263858795166</t>
   </si>
   <si>
     <t xml:space="preserve">14.5609188079834</t>
   </si>
   <si>
-    <t xml:space="preserve">15.349555015564</t>
+    <t xml:space="preserve">15.3495559692383</t>
   </si>
   <si>
     <t xml:space="preserve">15.3880252838135</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6765489578247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.522668838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7150201797485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7919597625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1574249267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7727270126343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8111972808838</t>
+    <t xml:space="preserve">15.6765470504761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5226697921753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7150192260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7919616699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1574268341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7727241516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8111953735352</t>
   </si>
   <si>
     <t xml:space="preserve">15.9073724746704</t>
@@ -1883,49 +1883,49 @@
     <t xml:space="preserve">15.6380805969238</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6188430786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8496646881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5803775787354</t>
+    <t xml:space="preserve">15.6188440322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8496656417847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5803756713867</t>
   </si>
   <si>
     <t xml:space="preserve">15.5034351348877</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8304281234741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9266061782837</t>
+    <t xml:space="preserve">15.8304290771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9266042709351</t>
   </si>
   <si>
     <t xml:space="preserve">16.1189575195312</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1576480865479</t>
+    <t xml:space="preserve">17.1576499938965</t>
   </si>
   <si>
     <t xml:space="preserve">17.0037670135498</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9460639953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8883571624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9845333099365</t>
+    <t xml:space="preserve">16.94606590271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8883590698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9845314025879</t>
   </si>
   <si>
     <t xml:space="preserve">17.119176864624</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2730560302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2732791900635</t>
+    <t xml:space="preserve">17.2730579376221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2732810974121</t>
   </si>
   <si>
     <t xml:space="preserve">18.1771049499512</t>
@@ -1940,28 +1940,28 @@
     <t xml:space="preserve">18.1001625061035</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9847583770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1194000244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9655170440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9462852478027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0616931915283</t>
+    <t xml:space="preserve">17.9847545623779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1193981170654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.965518951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9462871551514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.061695098877</t>
   </si>
   <si>
     <t xml:space="preserve">17.9270496368408</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3117542266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7541542053223</t>
+    <t xml:space="preserve">18.3117504119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7541561126709</t>
   </si>
   <si>
     <t xml:space="preserve">19.1003875732422</t>
@@ -1976,16 +1976,16 @@
     <t xml:space="preserve">18.9657402038574</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9080333709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4273853302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8120803833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5235557556152</t>
+    <t xml:space="preserve">18.9080352783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4273815155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8120822906494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5235538482666</t>
   </si>
   <si>
     <t xml:space="preserve">19.6678199768066</t>
@@ -1994,64 +1994,64 @@
     <t xml:space="preserve">19.2831153869629</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8503284454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6197338104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7159080505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7639923095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3312072753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5716457366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1967811584473</t>
+    <t xml:space="preserve">18.8503322601318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6197299957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7159061431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7639942169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.331205368042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5716438293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1967830657959</t>
   </si>
   <si>
     <t xml:space="preserve">20.2448711395264</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2164611816406</t>
+    <t xml:space="preserve">22.2164630889893</t>
   </si>
   <si>
     <t xml:space="preserve">21.1585350036621</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1104469299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8219184875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6295738220215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0142707824707</t>
+    <t xml:space="preserve">21.110445022583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8219203948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6295719146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0142726898193</t>
   </si>
   <si>
     <t xml:space="preserve">20.7257461547852</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6776580810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9563446044922</t>
+    <t xml:space="preserve">20.6776599884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9563465118408</t>
   </si>
   <si>
     <t xml:space="preserve">20.2929592132568</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0044326782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8601703643799</t>
+    <t xml:space="preserve">20.004430770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8601684570312</t>
   </si>
   <si>
     <t xml:space="preserve">19.0811519622803</t>
@@ -2063,61 +2063,61 @@
     <t xml:space="preserve">20.9180965423584</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5814800262451</t>
+    <t xml:space="preserve">20.5814819335938</t>
   </si>
   <si>
     <t xml:space="preserve">21.2547092437744</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3989715576172</t>
+    <t xml:space="preserve">21.3989734649658</t>
   </si>
   <si>
     <t xml:space="preserve">21.2066211700439</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6394081115723</t>
+    <t xml:space="preserve">21.6394100189209</t>
   </si>
   <si>
     <t xml:space="preserve">21.4470596313477</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8317623138428</t>
+    <t xml:space="preserve">21.8317604064941</t>
   </si>
   <si>
     <t xml:space="preserve">20.0525188446045</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1006088256836</t>
+    <t xml:space="preserve">20.100606918335</t>
   </si>
   <si>
     <t xml:space="preserve">18.734920501709</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1963386535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6192893981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3113059997559</t>
+    <t xml:space="preserve">18.1963405609131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6192874908447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3113040924072</t>
   </si>
   <si>
     <t xml:space="preserve">16.1958961486816</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4839792251587</t>
+    <t xml:space="preserve">14.4839782714844</t>
   </si>
   <si>
     <t xml:space="preserve">14.4262733459473</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4643001556396</t>
+    <t xml:space="preserve">12.4642992019653</t>
   </si>
   <si>
     <t xml:space="preserve">12.0218954086304</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1373052597046</t>
+    <t xml:space="preserve">12.137303352356</t>
   </si>
   <si>
     <t xml:space="preserve">12.6951198577881</t>
@@ -2126,7 +2126,7 @@
     <t xml:space="preserve">12.9067068099976</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9834251403809</t>
+    <t xml:space="preserve">11.9834241867065</t>
   </si>
   <si>
     <t xml:space="preserve">13.310640335083</t>
@@ -2135,34 +2135,34 @@
     <t xml:space="preserve">13.560697555542</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0223379135132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1954526901245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2916278839111</t>
+    <t xml:space="preserve">14.0223388671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1954517364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2916269302368</t>
   </si>
   <si>
     <t xml:space="preserve">14.1185131072998</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7340326309204</t>
+    <t xml:space="preserve">14.7340335845947</t>
   </si>
   <si>
     <t xml:space="preserve">14.0992784500122</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4072589874268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8691234588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1766624450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2151336669922</t>
+    <t xml:space="preserve">15.4072608947754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8691253662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1766605377197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2151317596436</t>
   </si>
   <si>
     <t xml:space="preserve">15.4649648666382</t>
@@ -2171,22 +2171,22 @@
     <t xml:space="preserve">16.0612506866455</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1381950378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0420169830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5998306274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.215353012085</t>
+    <t xml:space="preserve">16.1381931304932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0420150756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.59983253479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2153549194336</t>
   </si>
   <si>
     <t xml:space="preserve">16.7152404785156</t>
   </si>
   <si>
-    <t xml:space="preserve">16.926830291748</t>
+    <t xml:space="preserve">16.9268283843994</t>
   </si>
   <si>
     <t xml:space="preserve">17.0614719390869</t>
@@ -2195,13 +2195,13 @@
     <t xml:space="preserve">18.2540454864502</t>
   </si>
   <si>
-    <t xml:space="preserve">18.638744354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0774517059326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7677764892578</t>
+    <t xml:space="preserve">18.6387462615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0774536132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7677783966064</t>
   </si>
   <si>
     <t xml:space="preserve">17.4580974578857</t>
@@ -2210,43 +2210,43 @@
     <t xml:space="preserve">17.4387435913086</t>
   </si>
   <si>
-    <t xml:space="preserve">17.206485748291</t>
+    <t xml:space="preserve">17.2064876556396</t>
   </si>
   <si>
     <t xml:space="preserve">16.954870223999</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4193916320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6129360198975</t>
+    <t xml:space="preserve">17.4193878173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6129379272461</t>
   </si>
   <si>
     <t xml:space="preserve">17.1677742004395</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6516494750977</t>
+    <t xml:space="preserve">17.651647567749</t>
   </si>
   <si>
     <t xml:space="preserve">17.4968070983887</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7290668487549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2903575897217</t>
+    <t xml:space="preserve">17.7290687561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.290355682373</t>
   </si>
   <si>
     <t xml:space="preserve">17.9419708251953</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0580997467041</t>
+    <t xml:space="preserve">18.0580978393555</t>
   </si>
   <si>
     <t xml:space="preserve">18.3871307373047</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4064865112305</t>
+    <t xml:space="preserve">18.4064846038818</t>
   </si>
   <si>
     <t xml:space="preserve">17.9032611846924</t>
@@ -2255,22 +2255,22 @@
     <t xml:space="preserve">18.2322940826416</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2516460418701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.580680847168</t>
+    <t xml:space="preserve">18.2516498565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5806827545166</t>
   </si>
   <si>
     <t xml:space="preserve">18.4451961517334</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1161632537842</t>
+    <t xml:space="preserve">18.1161651611328</t>
   </si>
   <si>
     <t xml:space="preserve">18.0387439727783</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8322925567627</t>
+    <t xml:space="preserve">18.8322906494141</t>
   </si>
   <si>
     <t xml:space="preserve">18.7742290496826</t>
@@ -2279,10 +2279,10 @@
     <t xml:space="preserve">18.6774559020996</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9097156524658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0451984405518</t>
+    <t xml:space="preserve">18.9097137451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0451965332031</t>
   </si>
   <si>
     <t xml:space="preserve">19.5968132019043</t>
@@ -2294,7 +2294,7 @@
     <t xml:space="preserve">18.9484233856201</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1032657623291</t>
+    <t xml:space="preserve">19.1032638549805</t>
   </si>
   <si>
     <t xml:space="preserve">18.4645500183105</t>
@@ -2303,13 +2303,13 @@
     <t xml:space="preserve">18.6581020355225</t>
   </si>
   <si>
-    <t xml:space="preserve">19.500036239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6451988220215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0806827545166</t>
+    <t xml:space="preserve">19.5000381469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6452007293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0806846618652</t>
   </si>
   <si>
     <t xml:space="preserve">20.3226203918457</t>
@@ -2324,22 +2324,22 @@
     <t xml:space="preserve">21.0484275817871</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2903633117676</t>
+    <t xml:space="preserve">21.2903614044189</t>
   </si>
   <si>
     <t xml:space="preserve">21.7258472442627</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1935901641846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5806846618652</t>
+    <t xml:space="preserve">21.1935882568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5806865692139</t>
   </si>
   <si>
     <t xml:space="preserve">21.8710117340088</t>
   </si>
   <si>
-    <t xml:space="preserve">21.532299041748</t>
+    <t xml:space="preserve">21.5323009490967</t>
   </si>
   <si>
     <t xml:space="preserve">21.3387508392334</t>
@@ -2360,25 +2360,25 @@
     <t xml:space="preserve">23.3226261138916</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4193992614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0968189239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7258529663086</t>
+    <t xml:space="preserve">23.4194011688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0968208312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7258548736572</t>
   </si>
   <si>
     <t xml:space="preserve">24.4839153289795</t>
   </si>
   <si>
-    <t xml:space="preserve">24.048433303833</t>
+    <t xml:space="preserve">24.0484313964844</t>
   </si>
   <si>
     <t xml:space="preserve">23.7581100463867</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9516582489014</t>
+    <t xml:space="preserve">23.95166015625</t>
   </si>
   <si>
     <t xml:space="preserve">23.6613368988037</t>
@@ -2387,10 +2387,10 @@
     <t xml:space="preserve">22.741979598999</t>
   </si>
   <si>
-    <t xml:space="preserve">23.032299041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4677867889404</t>
+    <t xml:space="preserve">23.0323009490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4677886962891</t>
   </si>
   <si>
     <t xml:space="preserve">23.0806903839111</t>
@@ -2399,16 +2399,16 @@
     <t xml:space="preserve">22.8871402740479</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5484313964844</t>
+    <t xml:space="preserve">22.5484294891357</t>
   </si>
   <si>
     <t xml:space="preserve">21.8226203918457</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0645599365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2419776916504</t>
+    <t xml:space="preserve">22.0645580291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2419757843018</t>
   </si>
   <si>
     <t xml:space="preserve">21.6290740966797</t>
@@ -2420,28 +2420,28 @@
     <t xml:space="preserve">21.3871383666992</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0968132019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4839134216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2097187042236</t>
+    <t xml:space="preserve">21.0968151092529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4839153289795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2097206115723</t>
   </si>
   <si>
     <t xml:space="preserve">21.9677867889404</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9516525268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1129493713379</t>
+    <t xml:space="preserve">20.9516544342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1129474639893</t>
   </si>
   <si>
     <t xml:space="preserve">22.3548812866211</t>
   </si>
   <si>
-    <t xml:space="preserve">21.919397354126</t>
+    <t xml:space="preserve">21.9193954467773</t>
   </si>
   <si>
     <t xml:space="preserve">22.838752746582</t>
@@ -2450,7 +2450,7 @@
     <t xml:space="preserve">22.645206451416</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4355316162109</t>
+    <t xml:space="preserve">24.4355297088623</t>
   </si>
   <si>
     <t xml:space="preserve">24.3387565612793</t>
@@ -2459,10 +2459,10 @@
     <t xml:space="preserve">24.2419815063477</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7419872283936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1774673461914</t>
+    <t xml:space="preserve">25.7419853210449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.17746925354</t>
   </si>
   <si>
     <t xml:space="preserve">27.0000514984131</t>
@@ -2471,28 +2471,28 @@
     <t xml:space="preserve">26.661340713501</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6129550933838</t>
+    <t xml:space="preserve">26.6129570007324</t>
   </si>
   <si>
     <t xml:space="preserve">26.3710174560547</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6774711608887</t>
+    <t xml:space="preserve">27.6774730682373</t>
   </si>
   <si>
     <t xml:space="preserve">28.6452159881592</t>
   </si>
   <si>
-    <t xml:space="preserve">29.903284072876</t>
+    <t xml:space="preserve">29.9032821655273</t>
   </si>
   <si>
     <t xml:space="preserve">28.9355392456055</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7581233978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3871555328369</t>
+    <t xml:space="preserve">29.7581214904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3871536254883</t>
   </si>
   <si>
     <t xml:space="preserve">30.9194145202637</t>
@@ -2501,16 +2501,16 @@
     <t xml:space="preserve">31.7419986724854</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0323143005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5484447479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0807075500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2581214904785</t>
+    <t xml:space="preserve">32.0323181152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5484485626221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0807113647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2581253051758</t>
   </si>
   <si>
     <t xml:space="preserve">32.1774826049805</t>
@@ -2522,19 +2522,19 @@
     <t xml:space="preserve">33.2903861999512</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1936149597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8065147399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4839363098145</t>
+    <t xml:space="preserve">33.1936111450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.806510925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4839324951172</t>
   </si>
   <si>
     <t xml:space="preserve">33.7258720397949</t>
   </si>
   <si>
-    <t xml:space="preserve">34.1129684448242</t>
+    <t xml:space="preserve">34.1129722595215</t>
   </si>
   <si>
     <t xml:space="preserve">34.7420043945312</t>
@@ -2546,22 +2546,22 @@
     <t xml:space="preserve">35.3710327148438</t>
   </si>
   <si>
-    <t xml:space="preserve">35.4678115844727</t>
+    <t xml:space="preserve">35.4678077697754</t>
   </si>
   <si>
     <t xml:space="preserve">36.8226509094238</t>
   </si>
   <si>
-    <t xml:space="preserve">37.1613616943359</t>
+    <t xml:space="preserve">37.1613655090332</t>
   </si>
   <si>
     <t xml:space="preserve">36.1936225891113</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3065223693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.564582824707</t>
+    <t xml:space="preserve">34.3065185546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5645790100098</t>
   </si>
   <si>
     <t xml:space="preserve">32.6613540649414</t>
@@ -2573,7 +2573,7 @@
     <t xml:space="preserve">32.7097434997559</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9355430603027</t>
+    <t xml:space="preserve">31.9355392456055</t>
   </si>
   <si>
     <t xml:space="preserve">30.3387680053711</t>
@@ -2585,13 +2585,13 @@
     <t xml:space="preserve">30.5807056427002</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4839305877686</t>
+    <t xml:space="preserve">30.4839324951172</t>
   </si>
   <si>
     <t xml:space="preserve">31.112964630127</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4355506896973</t>
+    <t xml:space="preserve">33.435546875</t>
   </si>
   <si>
     <t xml:space="preserve">33.8710327148438</t>
@@ -2600,10 +2600,10 @@
     <t xml:space="preserve">35.2742576599121</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6613578796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7097473144531</t>
+    <t xml:space="preserve">35.6613616943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7097434997559</t>
   </si>
   <si>
     <t xml:space="preserve">37.2581367492676</t>
@@ -2612,13 +2612,13 @@
     <t xml:space="preserve">37.0162010192871</t>
   </si>
   <si>
-    <t xml:space="preserve">36.9678153991699</t>
+    <t xml:space="preserve">36.9678115844727</t>
   </si>
   <si>
     <t xml:space="preserve">35.9516868591309</t>
   </si>
   <si>
-    <t xml:space="preserve">36.4355583190918</t>
+    <t xml:space="preserve">36.4355545043945</t>
   </si>
   <si>
     <t xml:space="preserve">35.0807113647461</t>
@@ -2636,19 +2636,19 @@
     <t xml:space="preserve">37.6452331542969</t>
   </si>
   <si>
-    <t xml:space="preserve">38.0323333740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.612979888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.7581367492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8226585388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6774940490723</t>
+    <t xml:space="preserve">38.0323295593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6129760742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.7581405639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8226623535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.677490234375</t>
   </si>
   <si>
     <t xml:space="preserve">38.5645904541016</t>
@@ -2657,79 +2657,79 @@
     <t xml:space="preserve">38.7097511291504</t>
   </si>
   <si>
-    <t xml:space="preserve">39.6291122436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4516944885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.1613655090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4355621337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2581405639648</t>
+    <t xml:space="preserve">39.6291160583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4516906738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.1613693237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4355583190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2581443786621</t>
   </si>
   <si>
     <t xml:space="preserve">44.0807304382324</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9033050537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.0645904541016</t>
+    <t xml:space="preserve">41.9033088684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.0645942687988</t>
   </si>
   <si>
     <t xml:space="preserve">41.1774978637695</t>
   </si>
   <si>
-    <t xml:space="preserve">41.854923248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.338794708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.0484657287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.6291160583496</t>
+    <t xml:space="preserve">41.8549194335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.3387908935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.048469543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.6291122436523</t>
   </si>
   <si>
     <t xml:space="preserve">41.6129837036133</t>
   </si>
   <si>
-    <t xml:space="preserve">42.3871803283691</t>
+    <t xml:space="preserve">42.3871765136719</t>
   </si>
   <si>
     <t xml:space="preserve">43.5000839233398</t>
   </si>
   <si>
-    <t xml:space="preserve">44.1291198730469</t>
+    <t xml:space="preserve">44.1291160583496</t>
   </si>
   <si>
     <t xml:space="preserve">44.7097625732422</t>
   </si>
   <si>
-    <t xml:space="preserve">44.7581520080566</t>
+    <t xml:space="preserve">44.7581481933594</t>
   </si>
   <si>
     <t xml:space="preserve">45.6775054931641</t>
   </si>
   <si>
-    <t xml:space="preserve">44.4194374084473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.0000839233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.0162162780762</t>
+    <t xml:space="preserve">44.4194412231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.0000877380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.0162200927734</t>
   </si>
   <si>
     <t xml:space="preserve">45.483959197998</t>
   </si>
   <si>
-    <t xml:space="preserve">44.9516983032227</t>
+    <t xml:space="preserve">44.9517021179199</t>
   </si>
   <si>
     <t xml:space="preserve">46.2581520080566</t>
@@ -2744,16 +2744,16 @@
     <t xml:space="preserve">44.5162124633789</t>
   </si>
   <si>
-    <t xml:space="preserve">44.2742805480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.838794708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.1613693237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.3065299987793</t>
+    <t xml:space="preserve">44.2742767333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8387908935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.1613731384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.3065338134766</t>
   </si>
   <si>
     <t xml:space="preserve">43.2581481933594</t>
@@ -2762,10 +2762,10 @@
     <t xml:space="preserve">42.8710517883301</t>
   </si>
   <si>
-    <t xml:space="preserve">43.0645980834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.0323448181152</t>
+    <t xml:space="preserve">43.0646018981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.0323486328125</t>
   </si>
   <si>
     <t xml:space="preserve">43.4033088684082</t>
@@ -2777,43 +2777,43 @@
     <t xml:space="preserve">41.8992919921875</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0436096191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.7994422912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4576110839844</t>
+    <t xml:space="preserve">40.0436058044434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.7994384765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4576072692871</t>
   </si>
   <si>
     <t xml:space="preserve">40.0924415588379</t>
   </si>
   <si>
-    <t xml:space="preserve">40.8737831115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9947776794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.7761116027832</t>
+    <t xml:space="preserve">40.873779296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9947814941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.7761154174805</t>
   </si>
   <si>
     <t xml:space="preserve">40.6784477233887</t>
   </si>
   <si>
-    <t xml:space="preserve">40.190113067627</t>
+    <t xml:space="preserve">40.1901168823242</t>
   </si>
   <si>
     <t xml:space="preserve">39.8971061706543</t>
   </si>
   <si>
-    <t xml:space="preserve">39.6529388427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6041069030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.7506103515625</t>
+    <t xml:space="preserve">39.6529426574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6041030883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.7506065368652</t>
   </si>
   <si>
     <t xml:space="preserve">39.2622718811035</t>
@@ -2822,7 +2822,7 @@
     <t xml:space="preserve">40.2877769470215</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9459457397461</t>
+    <t xml:space="preserve">39.9459419250488</t>
   </si>
   <si>
     <t xml:space="preserve">37.8949279785156</t>
@@ -2846,22 +2846,22 @@
     <t xml:space="preserve">42.0946235656738</t>
   </si>
   <si>
-    <t xml:space="preserve">41.459789276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0691108703613</t>
+    <t xml:space="preserve">41.4597854614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0691146850586</t>
   </si>
   <si>
     <t xml:space="preserve">40.385440826416</t>
   </si>
   <si>
-    <t xml:space="preserve">40.4342765808105</t>
+    <t xml:space="preserve">40.4342803955078</t>
   </si>
   <si>
     <t xml:space="preserve">42.1922912597656</t>
   </si>
   <si>
-    <t xml:space="preserve">42.0457878112793</t>
+    <t xml:space="preserve">42.0457916259766</t>
   </si>
   <si>
     <t xml:space="preserve">41.9481201171875</t>
@@ -2870,13 +2870,13 @@
     <t xml:space="preserve">41.4109535217285</t>
   </si>
   <si>
-    <t xml:space="preserve">42.7294654846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3664779663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4153099060059</t>
+    <t xml:space="preserve">42.7294616699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3664817810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4153137207031</t>
   </si>
   <si>
     <t xml:space="preserve">46.1966514587402</t>
@@ -2885,16 +2885,16 @@
     <t xml:space="preserve">47.8569946289062</t>
   </si>
   <si>
-    <t xml:space="preserve">47.3198280334473</t>
+    <t xml:space="preserve">47.31982421875</t>
   </si>
   <si>
     <t xml:space="preserve">47.8081665039062</t>
   </si>
   <si>
-    <t xml:space="preserve">48.5406684875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.5895004272461</t>
+    <t xml:space="preserve">48.5406646728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.5895042419434</t>
   </si>
   <si>
     <t xml:space="preserve">48.8336715698242</t>
@@ -2903,28 +2903,28 @@
     <t xml:space="preserve">48.1988296508789</t>
   </si>
   <si>
-    <t xml:space="preserve">49.7126770019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.9080085754395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.8103446960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0056762695312</t>
+    <t xml:space="preserve">49.7126808166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.9080123901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.8103408813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0056800842285</t>
   </si>
   <si>
     <t xml:space="preserve">50.6893501281738</t>
   </si>
   <si>
-    <t xml:space="preserve">51.3730163574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.2986755371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.5916862487793</t>
+    <t xml:space="preserve">51.3730201721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.2986793518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.591682434082</t>
   </si>
   <si>
     <t xml:space="preserve">50.4940147399902</t>
@@ -2945,22 +2945,22 @@
     <t xml:space="preserve">51.8613548278809</t>
   </si>
   <si>
-    <t xml:space="preserve">51.9590301513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.8846855163574</t>
+    <t xml:space="preserve">51.9590263366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.8846817016602</t>
   </si>
   <si>
     <t xml:space="preserve">45.2688102722168</t>
   </si>
   <si>
-    <t xml:space="preserve">44.5363082885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.5107955932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.2433052062988</t>
+    <t xml:space="preserve">44.536304473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.510799407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2433013916016</t>
   </si>
   <si>
     <t xml:space="preserve">44.2921371459961</t>
@@ -2975,7 +2975,7 @@
     <t xml:space="preserve">43.8038024902344</t>
   </si>
   <si>
-    <t xml:space="preserve">44.4386405944824</t>
+    <t xml:space="preserve">44.4386444091797</t>
   </si>
   <si>
     <t xml:space="preserve">43.9503021240234</t>
@@ -2993,7 +2993,7 @@
     <t xml:space="preserve">41.7527885437012</t>
   </si>
   <si>
-    <t xml:space="preserve">42.2899551391602</t>
+    <t xml:space="preserve">42.2899589538574</t>
   </si>
   <si>
     <t xml:space="preserve">43.0712966918945</t>
@@ -3002,7 +3002,7 @@
     <t xml:space="preserve">43.2666320800781</t>
   </si>
   <si>
-    <t xml:space="preserve">43.7061309814453</t>
+    <t xml:space="preserve">43.7061347961426</t>
   </si>
   <si>
     <t xml:space="preserve">44.3409767150879</t>
@@ -3014,13 +3014,13 @@
     <t xml:space="preserve">46.0989837646484</t>
   </si>
   <si>
-    <t xml:space="preserve">45.659481048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.7571487426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.7782974243164</t>
+    <t xml:space="preserve">45.6594848632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.7571449279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.7782936096191</t>
   </si>
   <si>
     <t xml:space="preserve">41.2644500732422</t>
@@ -3029,13 +3029,13 @@
     <t xml:space="preserve">42.6806259155273</t>
   </si>
   <si>
-    <t xml:space="preserve">43.1201362609863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.3387908935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4364585876465</t>
+    <t xml:space="preserve">43.1201324462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.3387870788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4364624023438</t>
   </si>
   <si>
     <t xml:space="preserve">41.5086212158203</t>
@@ -3053,22 +3053,22 @@
     <t xml:space="preserve">39.0669364929199</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8482780456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5319442749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8504524230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1179504394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.824951171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.6551208496094</t>
+    <t xml:space="preserve">39.848274230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5319480895996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.850456237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1179466247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.8249473571777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.6551246643066</t>
   </si>
   <si>
     <t xml:space="preserve">41.6062850952148</t>
@@ -3077,55 +3077,55 @@
     <t xml:space="preserve">42.485294342041</t>
   </si>
   <si>
-    <t xml:space="preserve">42.9736289978027</t>
+    <t xml:space="preserve">42.9736251831055</t>
   </si>
   <si>
     <t xml:space="preserve">41.8016166687012</t>
   </si>
   <si>
-    <t xml:space="preserve">41.3621215820312</t>
+    <t xml:space="preserve">41.362117767334</t>
   </si>
   <si>
     <t xml:space="preserve">40.238941192627</t>
   </si>
   <si>
-    <t xml:space="preserve">40.6296119689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.8759651184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.4619636535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.999137878418</t>
+    <t xml:space="preserve">40.6296157836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.8759613037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.4619674682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.9991416931152</t>
   </si>
   <si>
     <t xml:space="preserve">40.9226150512695</t>
   </si>
   <si>
-    <t xml:space="preserve">39.1157684326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5829582214355</t>
+    <t xml:space="preserve">39.1157722473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5829620361328</t>
   </si>
   <si>
     <t xml:space="preserve">42.6317939758301</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5785980224609</t>
+    <t xml:space="preserve">38.5786018371582</t>
   </si>
   <si>
     <t xml:space="preserve">36.4299163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">38.6274299621582</t>
+    <t xml:space="preserve">38.6274337768555</t>
   </si>
   <si>
     <t xml:space="preserve">37.1135864257812</t>
   </si>
   <si>
-    <t xml:space="preserve">35.7950820922852</t>
+    <t xml:space="preserve">35.7950782775879</t>
   </si>
   <si>
     <t xml:space="preserve">34.7207374572754</t>
@@ -3134,10 +3134,10 @@
     <t xml:space="preserve">35.5997428894043</t>
   </si>
   <si>
-    <t xml:space="preserve">36.5275917053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6252517700195</t>
+    <t xml:space="preserve">36.527587890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6252555847168</t>
   </si>
   <si>
     <t xml:space="preserve">36.0880813598633</t>
@@ -3149,13 +3149,13 @@
     <t xml:space="preserve">35.4532432556152</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5254020690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3810806274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3555755615234</t>
+    <t xml:space="preserve">34.5253982543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3810844421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3555793762207</t>
   </si>
   <si>
     <t xml:space="preserve">33.9393997192383</t>
@@ -3173,10 +3173,10 @@
     <t xml:space="preserve">33.0115623474121</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3767242431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4510612487793</t>
+    <t xml:space="preserve">32.3767280578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4510650634766</t>
   </si>
   <si>
     <t xml:space="preserve">34.7695732116699</t>
@@ -3209,7 +3209,7 @@
     <t xml:space="preserve">32.6208915710449</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4488849639893</t>
+    <t xml:space="preserve">31.4488830566406</t>
   </si>
   <si>
     <t xml:space="preserve">32.6697235107422</t>
@@ -3230,16 +3230,16 @@
     <t xml:space="preserve">29.6518058776855</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4722118377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2302207946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0739517211914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9372234344482</t>
+    <t xml:space="preserve">30.4722099304199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2302169799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0739555358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.937219619751</t>
   </si>
   <si>
     <t xml:space="preserve">31.3316860198975</t>
@@ -3251,10 +3251,10 @@
     <t xml:space="preserve">31.3902835845947</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6637477874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8862056732178</t>
+    <t xml:space="preserve">31.6637496948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8862075805664</t>
   </si>
   <si>
     <t xml:space="preserve">29.9643383026123</t>
@@ -3269,7 +3269,7 @@
     <t xml:space="preserve">29.2025337219238</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8704662322998</t>
+    <t xml:space="preserve">28.8704681396484</t>
   </si>
   <si>
     <t xml:space="preserve">28.9290676116943</t>
@@ -3290,13 +3290,13 @@
     <t xml:space="preserve">28.3235301971436</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5969982147217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2258605957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5579299926758</t>
+    <t xml:space="preserve">28.596996307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2258625030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5579280853271</t>
   </si>
   <si>
     <t xml:space="preserve">28.1816463470459</t>
@@ -3305,22 +3305,22 @@
     <t xml:space="preserve">26.8943614959717</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5972957611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6765117645264</t>
+    <t xml:space="preserve">26.5972938537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.676513671875</t>
   </si>
   <si>
     <t xml:space="preserve">26.8745555877686</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5280990600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4784679412842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7359237670898</t>
+    <t xml:space="preserve">27.5281009674072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4784698486328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7359256744385</t>
   </si>
   <si>
     <t xml:space="preserve">27.2508392333984</t>
@@ -3329,19 +3329,19 @@
     <t xml:space="preserve">28.0628204345703</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3994941711426</t>
+    <t xml:space="preserve">28.3994960784912</t>
   </si>
   <si>
     <t xml:space="preserve">28.320276260376</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7657527923584</t>
+    <t xml:space="preserve">27.765754699707</t>
   </si>
   <si>
     <t xml:space="preserve">27.9439926147461</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4193000793457</t>
+    <t xml:space="preserve">28.4192981719971</t>
   </si>
   <si>
     <t xml:space="preserve">29.0134296417236</t>
@@ -3362,13 +3362,13 @@
     <t xml:space="preserve">24.9931392669678</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0129451751709</t>
+    <t xml:space="preserve">25.0129432678223</t>
   </si>
   <si>
     <t xml:space="preserve">25.6466846466064</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4584217071533</t>
+    <t xml:space="preserve">24.4584197998047</t>
   </si>
   <si>
     <t xml:space="preserve">25.4288368225098</t>
@@ -3380,7 +3380,7 @@
     <t xml:space="preserve">25.4684429168701</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8148994445801</t>
+    <t xml:space="preserve">24.8148975372314</t>
   </si>
   <si>
     <t xml:space="preserve">25.2902050018311</t>
@@ -3401,7 +3401,7 @@
     <t xml:space="preserve">23.8444843292236</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0523090362549</t>
+    <t xml:space="preserve">23.0523109436035</t>
   </si>
   <si>
     <t xml:space="preserve">23.5474185943604</t>
@@ -3413,19 +3413,19 @@
     <t xml:space="preserve">23.6068325042725</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1909408569336</t>
+    <t xml:space="preserve">23.190938949585</t>
   </si>
   <si>
     <t xml:space="preserve">22.9136772155762</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4185676574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5669822692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8146572113037</t>
+    <t xml:space="preserve">22.4185695648193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5669803619385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8146591186523</t>
   </si>
   <si>
     <t xml:space="preserve">22.9532890319824</t>
@@ -3440,13 +3440,13 @@
     <t xml:space="preserve">24.7356834411621</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5970497131348</t>
+    <t xml:space="preserve">24.5970516204834</t>
   </si>
   <si>
     <t xml:space="preserve">25.1911849975586</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9239444732666</t>
+    <t xml:space="preserve">25.9239463806152</t>
   </si>
   <si>
     <t xml:space="preserve">25.8249244689941</t>
@@ -3458,7 +3458,7 @@
     <t xml:space="preserve">26.1615982055664</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3892250061035</t>
+    <t xml:space="preserve">25.3892269134521</t>
   </si>
   <si>
     <t xml:space="preserve">25.1317691802979</t>
@@ -3467,10 +3467,10 @@
     <t xml:space="preserve">25.5674667358398</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0427703857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1417922973633</t>
+    <t xml:space="preserve">26.0427722930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1417942047119</t>
   </si>
   <si>
     <t xml:space="preserve">25.8843364715576</t>
@@ -3488,7 +3488,7 @@
     <t xml:space="preserve">24.2207679748535</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1217460632324</t>
+    <t xml:space="preserve">24.1217479705811</t>
   </si>
   <si>
     <t xml:space="preserve">23.6860504150391</t>
@@ -3506,7 +3506,7 @@
     <t xml:space="preserve">23.626636505127</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4980297088623</t>
+    <t xml:space="preserve">24.4980278015137</t>
   </si>
   <si>
     <t xml:space="preserve">23.8642902374268</t>
@@ -3515,19 +3515,19 @@
     <t xml:space="preserve">23.9435081481934</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7850704193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8743133544922</t>
+    <t xml:space="preserve">23.7850723266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8743152618408</t>
   </si>
   <si>
     <t xml:space="preserve">24.9535312652588</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2999858856201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7652683258057</t>
+    <t xml:space="preserve">24.2999877929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.765266418457</t>
   </si>
   <si>
     <t xml:space="preserve">22.8344612121582</t>
@@ -3536,7 +3536,7 @@
     <t xml:space="preserve">22.5571994781494</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7156372070312</t>
+    <t xml:space="preserve">22.7156352996826</t>
   </si>
   <si>
     <t xml:space="preserve">22.0422859191895</t>
@@ -3554,10 +3554,10 @@
     <t xml:space="preserve">20.0618476867676</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2696704864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8836059570312</t>
+    <t xml:space="preserve">19.2696685791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8836078643799</t>
   </si>
   <si>
     <t xml:space="preserve">20.2400875091553</t>
@@ -3581,7 +3581,7 @@
     <t xml:space="preserve">20.8540210723877</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3887424468994</t>
+    <t xml:space="preserve">21.3887405395508</t>
   </si>
   <si>
     <t xml:space="preserve">21.6065883636475</t>
@@ -3590,7 +3590,7 @@
     <t xml:space="preserve">22.0026741027832</t>
   </si>
   <si>
-    <t xml:space="preserve">22.200719833374</t>
+    <t xml:space="preserve">22.2007217407227</t>
   </si>
   <si>
     <t xml:space="preserve">21.6660003662109</t>
@@ -3599,16 +3599,16 @@
     <t xml:space="preserve">21.5075664520264</t>
   </si>
   <si>
-    <t xml:space="preserve">22.676025390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3195476531982</t>
+    <t xml:space="preserve">22.6760234832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3195457458496</t>
   </si>
   <si>
     <t xml:space="preserve">22.1809158325195</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4383735656738</t>
+    <t xml:space="preserve">22.4383716583252</t>
   </si>
   <si>
     <t xml:space="preserve">21.7848262786865</t>
@@ -3632,22 +3632,22 @@
     <t xml:space="preserve">25.7457065582275</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0329914093018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6369037628174</t>
+    <t xml:space="preserve">27.0329895019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6369018554688</t>
   </si>
   <si>
     <t xml:space="preserve">26.5576858520508</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9831161499023</t>
+    <t xml:space="preserve">23.9831142425537</t>
   </si>
   <si>
     <t xml:space="preserve">25.0525512695312</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2505970001221</t>
+    <t xml:space="preserve">25.2505950927734</t>
   </si>
   <si>
     <t xml:space="preserve">26.2012062072754</t>
@@ -3656,7 +3656,7 @@
     <t xml:space="preserve">26.4190540313721</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6963157653809</t>
+    <t xml:space="preserve">26.6963176727295</t>
   </si>
   <si>
     <t xml:space="preserve">26.7161197662354</t>
@@ -3674,25 +3674,25 @@
     <t xml:space="preserve">23.8246803283691</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9730930328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7950973510742</t>
+    <t xml:space="preserve">22.9730911254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7950954437256</t>
   </si>
   <si>
     <t xml:space="preserve">25.2704010009766</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1219902038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0625762939453</t>
+    <t xml:space="preserve">26.1219882965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0625743865967</t>
   </si>
   <si>
     <t xml:space="preserve">25.7853164672852</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2606201171875</t>
+    <t xml:space="preserve">26.2606220245361</t>
   </si>
   <si>
     <t xml:space="preserve">27.0725994110107</t>
@@ -3710,7 +3710,7 @@
     <t xml:space="preserve">27.4884929656982</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6965618133545</t>
+    <t xml:space="preserve">28.6965599060059</t>
   </si>
   <si>
     <t xml:space="preserve">28.7757759094238</t>
@@ -3719,10 +3719,10 @@
     <t xml:space="preserve">28.2212543487549</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5777339935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2806663513184</t>
+    <t xml:space="preserve">28.5777359008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.280668258667</t>
   </si>
   <si>
     <t xml:space="preserve">28.8153877258301</t>
@@ -3737,7 +3737,7 @@
     <t xml:space="preserve">28.6569519042969</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9540176391602</t>
+    <t xml:space="preserve">28.9540157318115</t>
   </si>
   <si>
     <t xml:space="preserve">28.8549938201904</t>
@@ -3746,7 +3746,7 @@
     <t xml:space="preserve">28.9738216400146</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7955799102783</t>
+    <t xml:space="preserve">28.795581817627</t>
   </si>
   <si>
     <t xml:space="preserve">30.280912399292</t>
@@ -3761,7 +3761,7 @@
     <t xml:space="preserve">29.7065830230713</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5877552032471</t>
+    <t xml:space="preserve">29.5877571105957</t>
   </si>
   <si>
     <t xml:space="preserve">29.33030128479</t>
@@ -3788,7 +3788,7 @@
     <t xml:space="preserve">28.3004722595215</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4787139892578</t>
+    <t xml:space="preserve">28.4787120819092</t>
   </si>
   <si>
     <t xml:space="preserve">28.0430145263672</t>
@@ -3800,7 +3800,7 @@
     <t xml:space="preserve">27.7063407897949</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0131874084473</t>
+    <t xml:space="preserve">27.0131893157959</t>
   </si>
   <si>
     <t xml:space="preserve">26.7755355834961</t>
@@ -3818,22 +3818,22 @@
     <t xml:space="preserve">22.3789615631104</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2801837921143</t>
+    <t xml:space="preserve">24.2801818847656</t>
   </si>
   <si>
     <t xml:space="preserve">24.5574436187744</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8347015380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0921611785889</t>
+    <t xml:space="preserve">24.8347034454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0921630859375</t>
   </si>
   <si>
     <t xml:space="preserve">25.8447284698486</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3893489837646</t>
+    <t xml:space="preserve">26.389347076416</t>
   </si>
   <si>
     <t xml:space="preserve">27.0825023651123</t>
@@ -3848,7 +3848,7 @@
     <t xml:space="preserve">27.4785900115967</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0727214813232</t>
+    <t xml:space="preserve">28.0727233886719</t>
   </si>
   <si>
     <t xml:space="preserve">27.7756538391113</t>
@@ -3857,10 +3857,10 @@
     <t xml:space="preserve">27.6766357421875</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4290809631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.181526184082</t>
+    <t xml:space="preserve">27.4290790557861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1815242767334</t>
   </si>
   <si>
     <t xml:space="preserve">26.9339694976807</t>
@@ -3869,13 +3869,13 @@
     <t xml:space="preserve">27.3795680999756</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8844604492188</t>
+    <t xml:space="preserve">26.8844585418701</t>
   </si>
   <si>
     <t xml:space="preserve">27.7261447906494</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9834785461426</t>
+    <t xml:space="preserve">26.9834804534912</t>
   </si>
   <si>
     <t xml:space="preserve">27.330057144165</t>
@@ -3890,7 +3890,7 @@
     <t xml:space="preserve">28.4688110351562</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5085411071777</t>
+    <t xml:space="preserve">29.5085391998291</t>
   </si>
   <si>
     <t xml:space="preserve">30.5482711791992</t>
@@ -3905,7 +3905,7 @@
     <t xml:space="preserve">32.0831146240234</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6375141143799</t>
+    <t xml:space="preserve">31.6375122070312</t>
   </si>
   <si>
     <t xml:space="preserve">32.1821327209473</t>
@@ -3914,25 +3914,25 @@
     <t xml:space="preserve">32.9247970581055</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2316436767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9840850830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1919136047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.340446472168</t>
+    <t xml:space="preserve">32.4296913146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2316398620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9840888977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.191915512085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3404445648193</t>
   </si>
   <si>
     <t xml:space="preserve">30.795825958252</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6472930908203</t>
+    <t xml:space="preserve">30.6472949981689</t>
   </si>
   <si>
     <t xml:space="preserve">30.2016944885254</t>
@@ -3944,7 +3944,7 @@
     <t xml:space="preserve">30.2512035369873</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5977821350098</t>
+    <t xml:space="preserve">30.5977802276611</t>
   </si>
   <si>
     <t xml:space="preserve">30.4492492675781</t>
@@ -5262,6 +5262,9 @@
   </si>
   <si>
     <t xml:space="preserve">31.5499992370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2999992370605</t>
   </si>
 </sst>
 </file>
@@ -72472,7 +72475,7 @@
     </row>
     <row r="2573">
       <c r="A2573" s="1" t="n">
-        <v>46069.6911342593</v>
+        <v>46069.3333333333</v>
       </c>
       <c r="B2573" t="n">
         <v>66430</v>
@@ -72493,6 +72496,32 @@
         <v>1749</v>
       </c>
       <c r="H2573" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2574">
+      <c r="A2574" s="1" t="n">
+        <v>46070.6912731481</v>
+      </c>
+      <c r="B2574" t="n">
+        <v>56105</v>
+      </c>
+      <c r="C2574" t="n">
+        <v>32.7000007629395</v>
+      </c>
+      <c r="D2574" t="n">
+        <v>31.3500003814697</v>
+      </c>
+      <c r="E2574" t="n">
+        <v>32</v>
+      </c>
+      <c r="F2574" t="n">
+        <v>32.2999992370605</v>
+      </c>
+      <c r="G2574" t="s">
+        <v>1750</v>
+      </c>
+      <c r="H2574" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MOL.MI.xlsx
+++ b/data/MOL.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1758" uniqueCount="1758">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1759" uniqueCount="1759">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85066032409668</t>
+    <t xml:space="preserve">6.850661277771</t>
   </si>
   <si>
     <t xml:space="preserve">MOL.MI</t>
@@ -47,16 +47,16 @@
     <t xml:space="preserve">6.75772666931152</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66036558151245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77100229263306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63823747634888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72674751281738</t>
+    <t xml:space="preserve">6.66036510467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7710018157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63823843002319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72674798965454</t>
   </si>
   <si>
     <t xml:space="preserve">6.81525754928589</t>
@@ -65,70 +65,70 @@
     <t xml:space="preserve">6.54972791671753</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31960248947144</t>
+    <t xml:space="preserve">6.31960296630859</t>
   </si>
   <si>
     <t xml:space="preserve">6.09832763671875</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35058069229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2399435043335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5585789680481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46121835708618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89475440979004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52317571640015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65593957901001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76215124130249</t>
+    <t xml:space="preserve">6.35058116912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23994398117065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55857944488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46121883392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89475536346436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52317476272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65594005584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76215171813965</t>
   </si>
   <si>
     <t xml:space="preserve">6.66479110717773</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69134473800659</t>
+    <t xml:space="preserve">6.69134426116943</t>
   </si>
   <si>
     <t xml:space="preserve">6.68249320983887</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01866912841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89918041229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28419923782349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06292343139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25322103500366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39926099777222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34172964096069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50989818572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33287858963013</t>
+    <t xml:space="preserve">6.01866960525513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89918088912964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28419876098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0629243850708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25322008132935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39926147460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34173011779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50989866256714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33287906646729</t>
   </si>
   <si>
     <t xml:space="preserve">6.42581415176392</t>
@@ -149,82 +149,82 @@
     <t xml:space="preserve">6.63381242752075</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43466472625732</t>
+    <t xml:space="preserve">6.43466567993164</t>
   </si>
   <si>
     <t xml:space="preserve">6.22666692733765</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24436950683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27534818649292</t>
+    <t xml:space="preserve">6.24436902999878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2753472328186</t>
   </si>
   <si>
     <t xml:space="preserve">6.26649713516235</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62938737869263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43909025192261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41253709793091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45236778259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45679235458374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36828327178955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19568872451782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06734991073608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28862428665161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20453977584839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29304933547974</t>
+    <t xml:space="preserve">6.62938642501831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43909072875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41253757476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45236730575562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45679330825806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36828279495239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19568920135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06734943389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28862476348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20454025268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29304981231689</t>
   </si>
   <si>
     <t xml:space="preserve">6.24879455566406</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22224235534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25764608383179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15585851669312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19126272201538</t>
+    <t xml:space="preserve">6.22224140167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25764465332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15585947036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19126319885254</t>
   </si>
   <si>
     <t xml:space="preserve">6.58955812454224</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47892045974731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49662303924561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42138910293579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63349008560181</t>
+    <t xml:space="preserve">6.47892093658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49662160873413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42138862609863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63348865509033</t>
   </si>
   <si>
     <t xml:space="preserve">6.45274066925049</t>
@@ -239,16 +239,16 @@
     <t xml:space="preserve">6.50696468353271</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55667114257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36688423156738</t>
+    <t xml:space="preserve">6.55667066574097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3668851852417</t>
   </si>
   <si>
     <t xml:space="preserve">6.61993312835693</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69223308563232</t>
+    <t xml:space="preserve">6.69223356246948</t>
   </si>
   <si>
     <t xml:space="preserve">6.59734010696411</t>
@@ -266,10 +266,10 @@
     <t xml:space="preserve">6.8503885269165</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94528150558472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98594999313354</t>
+    <t xml:space="preserve">6.94528102874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9859504699707</t>
   </si>
   <si>
     <t xml:space="preserve">7.1034369468689</t>
@@ -278,34 +278,34 @@
     <t xml:space="preserve">7.25255441665649</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32033634185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45589685440063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30226135253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37907934188843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25707387924194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22996091842651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22544193267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19832992553711</t>
+    <t xml:space="preserve">7.32033538818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45589780807495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3022608757019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37907886505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25707292556763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22996139526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22544288635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19833040237427</t>
   </si>
   <si>
     <t xml:space="preserve">7.09439945220947</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13958644866943</t>
+    <t xml:space="preserve">7.13958692550659</t>
   </si>
   <si>
     <t xml:space="preserve">7.00402498245239</t>
@@ -314,46 +314,46 @@
     <t xml:space="preserve">7.08084344863892</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95883798599243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84135150909424</t>
+    <t xml:space="preserve">6.95883750915527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84135055541992</t>
   </si>
   <si>
     <t xml:space="preserve">7.11699342727661</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16669893264771</t>
+    <t xml:space="preserve">7.16669845581055</t>
   </si>
   <si>
     <t xml:space="preserve">7.31129884719849</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32485389709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99950551986694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73290109634399</t>
+    <t xml:space="preserve">7.32485437393188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9995059967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73290157318115</t>
   </si>
   <si>
     <t xml:space="preserve">7.08988046646118</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18477344512939</t>
+    <t xml:space="preserve">7.18477439880371</t>
   </si>
   <si>
     <t xml:space="preserve">6.85942554473877</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67867660522461</t>
+    <t xml:space="preserve">6.67867708206177</t>
   </si>
   <si>
     <t xml:space="preserve">6.49792766571045</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57022714614868</t>
+    <t xml:space="preserve">6.57022762298584</t>
   </si>
   <si>
     <t xml:space="preserve">6.57926511764526</t>
@@ -365,79 +365,79 @@
     <t xml:space="preserve">6.74645709991455</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65156364440918</t>
+    <t xml:space="preserve">6.6515645980835</t>
   </si>
   <si>
     <t xml:space="preserve">6.55215215682983</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46177816390991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75549459457397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56570863723755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77808809280396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71030759811401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48889017105103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53859567642212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66060209274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68771457672119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76001358032227</t>
+    <t xml:space="preserve">6.46177768707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75549507141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56570911407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77808904647827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71030807495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48888969421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53859663009644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6606011390686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68771362304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76001405715942</t>
   </si>
   <si>
     <t xml:space="preserve">6.87750101089478</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70127010345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7871265411377</t>
+    <t xml:space="preserve">6.70126962661743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78712606430054</t>
   </si>
   <si>
     <t xml:space="preserve">6.79616355895996</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81423854827881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81875801086426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82327556610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80520153045654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92268848419189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90461254119873</t>
+    <t xml:space="preserve">6.81423759460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81875705718994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82327604293823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80520105361938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92268800735474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90461301803589</t>
   </si>
   <si>
     <t xml:space="preserve">6.86846303939819</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98143100738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17573738098145</t>
+    <t xml:space="preserve">6.98143148422241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17573642730713</t>
   </si>
   <si>
     <t xml:space="preserve">7.01306247711182</t>
@@ -446,10 +446,10 @@
     <t xml:space="preserve">6.97691202163696</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64252614974976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6967511177063</t>
+    <t xml:space="preserve">6.64252662658691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69675159454346</t>
   </si>
   <si>
     <t xml:space="preserve">6.88653755187988</t>
@@ -464,145 +464,145 @@
     <t xml:space="preserve">6.99046850204468</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19381141662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05824995040894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04921293258667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06728744506836</t>
+    <t xml:space="preserve">7.19381093978882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05824899673462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04921197891235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0672869682312</t>
   </si>
   <si>
     <t xml:space="preserve">7.14862394332886</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08536243438721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06276845932007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15766143798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21188545227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38359832763672</t>
+    <t xml:space="preserve">7.08536195755005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06276798248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15766191482544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21188688278198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3835973739624</t>
   </si>
   <si>
     <t xml:space="preserve">7.22092342376709</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24803638458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18929243087769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35648488998413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37004137039185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88201951980591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03565645217896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18025493621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91365003585815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51915979385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47849082946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50108575820923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41070938110352</t>
+    <t xml:space="preserve">7.24803590774536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18929290771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35648584365845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37004089355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88201856613159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03565549850464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1802544593811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.913649559021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51915884017944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47848987579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50108480453491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41070985794067</t>
   </si>
   <si>
     <t xml:space="preserve">7.27514839172363</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60953378677368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66375827789307</t>
+    <t xml:space="preserve">7.60953330993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66375970840454</t>
   </si>
   <si>
     <t xml:space="preserve">7.72702169418335</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6818323135376</t>
+    <t xml:space="preserve">7.68183279037476</t>
   </si>
   <si>
     <t xml:space="preserve">7.67731380462646</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63664627075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77220773696899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.971031665802</t>
+    <t xml:space="preserve">7.63664722442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77220821380615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97103118896484</t>
   </si>
   <si>
     <t xml:space="preserve">8.34156703948975</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41386795043945</t>
+    <t xml:space="preserve">8.41386699676514</t>
   </si>
   <si>
     <t xml:space="preserve">8.45001792907715</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57654094696045</t>
+    <t xml:space="preserve">8.57654190063477</t>
   </si>
   <si>
     <t xml:space="preserve">8.37771797180176</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40935039520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35964298248291</t>
+    <t xml:space="preserve">8.40934944152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35964107513428</t>
   </si>
   <si>
     <t xml:space="preserve">8.22408103942871</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24215602874756</t>
+    <t xml:space="preserve">8.24215698242188</t>
   </si>
   <si>
     <t xml:space="preserve">8.33704853057861</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32801246643066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3234920501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36416149139404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37319755554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46809196472168</t>
+    <t xml:space="preserve">8.32801151275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32349300384521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36416244506836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37319946289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.468092918396</t>
   </si>
   <si>
     <t xml:space="preserve">8.30541706085205</t>
@@ -614,25 +614,25 @@
     <t xml:space="preserve">8.09755611419678</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26926898956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20600414276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07496356964111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11111259460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28282642364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2963809967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40482902526855</t>
+    <t xml:space="preserve">8.26926803588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20600509643555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07496452331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11111164093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2828254699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29638195037842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40482997894287</t>
   </si>
   <si>
     <t xml:space="preserve">8.48164844512939</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">8.02977561950684</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13370704650879</t>
+    <t xml:space="preserve">8.13370609283447</t>
   </si>
   <si>
     <t xml:space="preserve">8.27830600738525</t>
@@ -662,43 +662,43 @@
     <t xml:space="preserve">8.6940279006958</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57969856262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25435161590576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21820068359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01937580108643</t>
+    <t xml:space="preserve">9.57969951629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25435066223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21820163726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01937675476074</t>
   </si>
   <si>
     <t xml:space="preserve">9.16397666931152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20012664794922</t>
+    <t xml:space="preserve">9.2001256942749</t>
   </si>
   <si>
     <t xml:space="preserve">9.20916366577148</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22723865509033</t>
+    <t xml:space="preserve">9.22723770141602</t>
   </si>
   <si>
     <t xml:space="preserve">8.94707679748535</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03745079040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12782669067383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35376262664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55258464813232</t>
+    <t xml:space="preserve">9.03744983673096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12782573699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35376358032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55258560180664</t>
   </si>
   <si>
     <t xml:space="preserve">9.47124767303467</t>
@@ -713,19 +713,19 @@
     <t xml:space="preserve">10.2123203277588</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94119548797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4472951889038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8449411392212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8087921142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.908203125</t>
+    <t xml:space="preserve">9.94119644165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4472942352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8449401855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8087930679321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9082040786743</t>
   </si>
   <si>
     <t xml:space="preserve">10.9353170394897</t>
@@ -734,10 +734,10 @@
     <t xml:space="preserve">10.7364912033081</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7093811035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.754566192627</t>
+    <t xml:space="preserve">10.7093801498413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7545671463013</t>
   </si>
   <si>
     <t xml:space="preserve">10.4764318466187</t>
@@ -746,19 +746,19 @@
     <t xml:space="preserve">10.2261095046997</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0128736495972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3837203979492</t>
+    <t xml:space="preserve">10.0128726959229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3837194442749</t>
   </si>
   <si>
     <t xml:space="preserve">10.4300746917725</t>
   </si>
   <si>
-    <t xml:space="preserve">10.28173828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4022617340088</t>
+    <t xml:space="preserve">10.2817373275757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4022626876831</t>
   </si>
   <si>
     <t xml:space="preserve">10.5135164260864</t>
@@ -767,13 +767,13 @@
     <t xml:space="preserve">10.4949741363525</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5413312911987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7452964782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0790576934814</t>
+    <t xml:space="preserve">10.5413303375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7452955245972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0790596008301</t>
   </si>
   <si>
     <t xml:space="preserve">11.7743968963623</t>
@@ -782,34 +782,34 @@
     <t xml:space="preserve">11.5889730453491</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2181272506714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3015670776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.097601890564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1439571380615</t>
+    <t xml:space="preserve">11.2181262969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3015661239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0976009368896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1439580917358</t>
   </si>
   <si>
     <t xml:space="preserve">11.0327024459839</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8287372589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7545671463013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7360258102417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9863481521606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8658218383789</t>
+    <t xml:space="preserve">10.8287353515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7545680999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7360248565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9863471984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8658208847046</t>
   </si>
   <si>
     <t xml:space="preserve">10.5691432952881</t>
@@ -818,70 +818,70 @@
     <t xml:space="preserve">11.1254138946533</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0605163574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4869899749756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0697870254517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9399909973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4499063491821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4035482406616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7094993591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0988893508911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3213958740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.894923210144</t>
+    <t xml:space="preserve">11.0605154037476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4869909286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.069785118103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9399919509888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4499053955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4035501480103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7094974517822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0988864898682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3213987350464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8949222564697</t>
   </si>
   <si>
     <t xml:space="preserve">12.5160903930664</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5253620147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6737003326416</t>
+    <t xml:space="preserve">12.5253629684448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6737012863159</t>
   </si>
   <si>
     <t xml:space="preserve">12.7478704452515</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5346336364746</t>
+    <t xml:space="preserve">12.5346345901489</t>
   </si>
   <si>
     <t xml:space="preserve">12.794225692749</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7293281555176</t>
+    <t xml:space="preserve">12.7293291091919</t>
   </si>
   <si>
     <t xml:space="preserve">12.5439043045044</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5809888839722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5624475479126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4697351455688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4975471496582</t>
+    <t xml:space="preserve">12.5809898376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5624465942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4697360992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4975490570068</t>
   </si>
   <si>
     <t xml:space="preserve">12.4882774353027</t>
@@ -890,10 +890,10 @@
     <t xml:space="preserve">12.6829719543457</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6273460388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5531759262085</t>
+    <t xml:space="preserve">12.627345085144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5531768798828</t>
   </si>
   <si>
     <t xml:space="preserve">12.1823291778564</t>
@@ -905,46 +905,46 @@
     <t xml:space="preserve">12.4233798980713</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2935819625854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3677530288696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8856496810913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.28431224823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1730585098267</t>
+    <t xml:space="preserve">12.2935829162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3677520751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8856506347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2843112945557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.173056602478</t>
   </si>
   <si>
     <t xml:space="preserve">12.0525321960449</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9505500793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3121252059937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2657690048218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9412794113159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9598197937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3306674957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4419212341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3492097854614</t>
+    <t xml:space="preserve">11.9505491256714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.312123298645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2657699584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9412775039673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9598207473755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3306684494019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4419221878052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3492107391357</t>
   </si>
   <si>
     <t xml:space="preserve">12.3770246505737</t>
@@ -953,7 +953,7 @@
     <t xml:space="preserve">12.1545143127441</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2472267150879</t>
+    <t xml:space="preserve">12.2472276687622</t>
   </si>
   <si>
     <t xml:space="preserve">12.3399381637573</t>
@@ -965,31 +965,31 @@
     <t xml:space="preserve">12.200870513916</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4326505661011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3028545379639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2564992904663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0618028640747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0247182846069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4406356811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.635329246521</t>
+    <t xml:space="preserve">12.4326515197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3028535842896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.256498336792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.061803817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0247201919556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.440634727478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6353282928467</t>
   </si>
   <si>
     <t xml:space="preserve">11.7929391860962</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6631441116333</t>
+    <t xml:space="preserve">11.6631422042847</t>
   </si>
   <si>
     <t xml:space="preserve">11.6816854476929</t>
@@ -1004,22 +1004,22 @@
     <t xml:space="preserve">11.8207530975342</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8671083450317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7373113632202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.228684425354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1915998458862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7651252746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.718770980835</t>
+    <t xml:space="preserve">11.8671073913574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7373123168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2286853790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1915988922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7651243209839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7187700271606</t>
   </si>
   <si>
     <t xml:space="preserve">11.1903123855591</t>
@@ -1031,16 +1031,16 @@
     <t xml:space="preserve">11.1624984741211</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5426187515259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4684476852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5982446670532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.579701423645</t>
+    <t xml:space="preserve">11.5426168441772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4684467315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5982437133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5797023773193</t>
   </si>
   <si>
     <t xml:space="preserve">11.4962615966797</t>
@@ -1067,16 +1067,16 @@
     <t xml:space="preserve">13.9253101348877</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1107339859009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0921926498413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9438533782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9994802474976</t>
+    <t xml:space="preserve">14.1107349395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.092191696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9438524246216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9994812011719</t>
   </si>
   <si>
     <t xml:space="preserve">14.6299200057983</t>
@@ -1088,13 +1088,13 @@
     <t xml:space="preserve">13.6286325454712</t>
   </si>
   <si>
-    <t xml:space="preserve">14.203444480896</t>
+    <t xml:space="preserve">14.2034463882446</t>
   </si>
   <si>
     <t xml:space="preserve">14.0180225372314</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7028017044067</t>
+    <t xml:space="preserve">13.7028026580811</t>
   </si>
   <si>
     <t xml:space="preserve">14.3888692855835</t>
@@ -1103,64 +1103,64 @@
     <t xml:space="preserve">14.518666267395</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5742921829224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4815797805786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1849040985107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8325977325439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9981908798218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7756824493408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3690395355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0352773666382</t>
+    <t xml:space="preserve">14.5742931365967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4815807342529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1849012374878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8325986862183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9981927871704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7756834030151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3690404891968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0352764129639</t>
   </si>
   <si>
     <t xml:space="preserve">12.7385988235474</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9796504974365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5173768997192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3134126663208</t>
+    <t xml:space="preserve">12.9796495437622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5173778533936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3134117126465</t>
   </si>
   <si>
     <t xml:space="preserve">12.6644306182861</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1081600189209</t>
+    <t xml:space="preserve">12.1081590652466</t>
   </si>
   <si>
     <t xml:space="preserve">12.0154476165771</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8300247192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.590259552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7200574874878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6088047027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1637868881226</t>
+    <t xml:space="preserve">11.830023765564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5902614593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7200565338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6088037490845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1637859344482</t>
   </si>
   <si>
     <t xml:space="preserve">12.033989906311</t>
@@ -1169,31 +1169,31 @@
     <t xml:space="preserve">12.0710744857788</t>
   </si>
   <si>
-    <t xml:space="preserve">11.607515335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4604644775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8114814758301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8485660552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2379550933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3862953186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3504981994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5359210968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7213449478149</t>
+    <t xml:space="preserve">11.6075172424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4604625701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8114805221558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8485670089722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2379560470581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3862943649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3504962921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5359220504761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7213430404663</t>
   </si>
   <si>
     <t xml:space="preserve">14.2590732574463</t>
@@ -1208,58 +1208,58 @@
     <t xml:space="preserve">14.741174697876</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7968015670776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0235729217529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6849870681763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4015216827393</t>
+    <t xml:space="preserve">14.796802520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0235719680786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6849889755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4015235900879</t>
   </si>
   <si>
     <t xml:space="preserve">15.2314462661743</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0802631378174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1180601119995</t>
+    <t xml:space="preserve">15.080265045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1180610656738</t>
   </si>
   <si>
     <t xml:space="preserve">15.1747512817383</t>
   </si>
   <si>
-    <t xml:space="preserve">15.307035446167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.13538646698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8141269683838</t>
+    <t xml:space="preserve">15.3070344924927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1353855133057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8141260147095</t>
   </si>
   <si>
     <t xml:space="preserve">13.2660970687866</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6062545776367</t>
+    <t xml:space="preserve">13.6062517166138</t>
   </si>
   <si>
     <t xml:space="preserve">13.6818428039551</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0771217346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9448394775391</t>
+    <t xml:space="preserve">13.0771207809448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9448385238647</t>
   </si>
   <si>
     <t xml:space="preserve">13.1149168014526</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8881454467773</t>
+    <t xml:space="preserve">12.8881464004517</t>
   </si>
   <si>
     <t xml:space="preserve">12.0944471359253</t>
@@ -1271,19 +1271,19 @@
     <t xml:space="preserve">13.0015316009521</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6235809326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6991701126099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7558612823486</t>
+    <t xml:space="preserve">12.6235799789429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6991691589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7558631896973</t>
   </si>
   <si>
     <t xml:space="preserve">12.8692483901978</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3401174545288</t>
+    <t xml:space="preserve">12.3401155471802</t>
   </si>
   <si>
     <t xml:space="preserve">12.7369651794434</t>
@@ -1292,7 +1292,7 @@
     <t xml:space="preserve">12.7180681228638</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7747602462769</t>
+    <t xml:space="preserve">12.7747621536255</t>
   </si>
   <si>
     <t xml:space="preserve">12.2645254135132</t>
@@ -1301,19 +1301,19 @@
     <t xml:space="preserve">13.7385368347168</t>
   </si>
   <si>
-    <t xml:space="preserve">13.776330947876</t>
+    <t xml:space="preserve">13.7763319015503</t>
   </si>
   <si>
     <t xml:space="preserve">13.9653072357178</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8708200454712</t>
+    <t xml:space="preserve">13.8708181381226</t>
   </si>
   <si>
     <t xml:space="preserve">14.0786924362183</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6251516342163</t>
+    <t xml:space="preserve">13.6251525878906</t>
   </si>
   <si>
     <t xml:space="preserve">13.5873565673828</t>
@@ -1322,13 +1322,13 @@
     <t xml:space="preserve">13.4172782897949</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4550724029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4361763000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2471990585327</t>
+    <t xml:space="preserve">13.4550733566284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4361753463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.247200012207</t>
   </si>
   <si>
     <t xml:space="preserve">13.1338138580322</t>
@@ -1340,19 +1340,19 @@
     <t xml:space="preserve">13.473970413208</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2094039916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3605861663818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5668869018555</t>
+    <t xml:space="preserve">13.2094049453735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3605852127075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5668878555298</t>
   </si>
   <si>
     <t xml:space="preserve">12.5101938247681</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2834234237671</t>
+    <t xml:space="preserve">12.2834243774414</t>
   </si>
   <si>
     <t xml:space="preserve">12.6802730560303</t>
@@ -1364,10 +1364,10 @@
     <t xml:space="preserve">12.9826335906982</t>
   </si>
   <si>
-    <t xml:space="preserve">12.812557220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9637365341187</t>
+    <t xml:space="preserve">12.8125553131104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.96373462677</t>
   </si>
   <si>
     <t xml:space="preserve">13.7952299118042</t>
@@ -1376,37 +1376,37 @@
     <t xml:space="preserve">14.1164875030518</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2676687240601</t>
+    <t xml:space="preserve">14.2676696777344</t>
   </si>
   <si>
     <t xml:space="preserve">14.3054637908936</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0597953796387</t>
+    <t xml:space="preserve">14.059796333313</t>
   </si>
   <si>
     <t xml:space="preserve">13.700740814209</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4928665161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7574338912964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.549560546875</t>
+    <t xml:space="preserve">13.4928684234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7574348449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5495595932007</t>
   </si>
   <si>
     <t xml:space="preserve">14.1731815338135</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9290838241577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4960088729858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2692394256592</t>
+    <t xml:space="preserve">14.929084777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4960098266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2692422866821</t>
   </si>
   <si>
     <t xml:space="preserve">15.155855178833</t>
@@ -1418,19 +1418,19 @@
     <t xml:space="preserve">16.7054557800293</t>
   </si>
   <si>
-    <t xml:space="preserve">16.913330078125</t>
+    <t xml:space="preserve">16.9133319854736</t>
   </si>
   <si>
     <t xml:space="preserve">16.6298656463623</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2330150604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9117565155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5904979705811</t>
+    <t xml:space="preserve">16.2330169677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9117574691772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5904989242554</t>
   </si>
   <si>
     <t xml:space="preserve">15.5149078369141</t>
@@ -1445,7 +1445,7 @@
     <t xml:space="preserve">14.3810558319092</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6078252792358</t>
+    <t xml:space="preserve">14.6078262329102</t>
   </si>
   <si>
     <t xml:space="preserve">14.4377470016479</t>
@@ -1454,16 +1454,16 @@
     <t xml:space="preserve">14.6456212997437</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2487716674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1920795440674</t>
+    <t xml:space="preserve">14.2487707138062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1920785903931</t>
   </si>
   <si>
     <t xml:space="preserve">13.8897171020508</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5306634902954</t>
+    <t xml:space="preserve">13.5306625366211</t>
   </si>
   <si>
     <t xml:space="preserve">13.8519220352173</t>
@@ -1472,19 +1472,19 @@
     <t xml:space="preserve">14.0219993591309</t>
   </si>
   <si>
-    <t xml:space="preserve">14.872389793396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4755401611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4188499450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5527000427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9668788909912</t>
+    <t xml:space="preserve">14.8723907470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4755430221558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.418848991394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5527029037476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9668798446655</t>
   </si>
   <si>
     <t xml:space="preserve">16.0818367004395</t>
@@ -1493,46 +1493,46 @@
     <t xml:space="preserve">16.0629386901855</t>
   </si>
   <si>
-    <t xml:space="preserve">16.251916885376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0440368652344</t>
+    <t xml:space="preserve">16.2519149780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0440425872803</t>
   </si>
   <si>
     <t xml:space="preserve">15.8739624023438</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4582185745239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0251426696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3464031219482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1007347106934</t>
+    <t xml:space="preserve">15.4582166671753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0251445770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3464012145996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1007385253906</t>
   </si>
   <si>
     <t xml:space="preserve">16.327507019043</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6471929550171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7983713150024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9306583404541</t>
+    <t xml:space="preserve">15.6471920013428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7983741760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9306545257568</t>
   </si>
   <si>
     <t xml:space="preserve">15.0613670349121</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8550653457642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4771118164062</t>
+    <t xml:space="preserve">15.8550672531128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4771127700806</t>
   </si>
   <si>
     <t xml:space="preserve">14.7401084899902</t>
@@ -1541,55 +1541,55 @@
     <t xml:space="preserve">14.9101867675781</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5511322021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8156986236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9857769012451</t>
+    <t xml:space="preserve">14.5511331558228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8156995773315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9857759475708</t>
   </si>
   <si>
     <t xml:space="preserve">15.533805847168</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7416801452637</t>
+    <t xml:space="preserve">15.7416791915894</t>
   </si>
   <si>
     <t xml:space="preserve">15.0424690246582</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4204196929932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7605772018433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6282949447632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8928594589233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9684505462646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0062427520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9873456954956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6093988418579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6834144592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6267232894897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.853494644165</t>
+    <t xml:space="preserve">15.4204225540161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7605762481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6282968521118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8928604125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9684524536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0062465667725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9873466491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6093969345093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6834173202515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6267223358154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8534936904907</t>
   </si>
   <si>
     <t xml:space="preserve">15.1936502456665</t>
@@ -1598,100 +1598,100 @@
     <t xml:space="preserve">15.0991621017456</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2881374359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1952228546143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0078182220459</t>
+    <t xml:space="preserve">15.2881393432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.195219039917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0078144073486</t>
   </si>
   <si>
     <t xml:space="preserve">17.2345886230469</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2534866333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2912769317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1023063659668</t>
+    <t xml:space="preserve">17.2534847259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2912788391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1023044586182</t>
   </si>
   <si>
     <t xml:space="preserve">17.064510345459</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0471858978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4046669006348</t>
+    <t xml:space="preserve">18.0471820831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4046649932861</t>
   </si>
   <si>
     <t xml:space="preserve">17.347972869873</t>
   </si>
   <si>
-    <t xml:space="preserve">17.366870880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4991550445557</t>
+    <t xml:space="preserve">17.3668689727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4991569519043</t>
   </si>
   <si>
     <t xml:space="preserve">17.0456123352051</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3857669830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4424591064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8582057952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8204154968262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5558490753174</t>
+    <t xml:space="preserve">17.3857707977295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4424610137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8582077026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8204116821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5558471679688</t>
   </si>
   <si>
     <t xml:space="preserve">17.3290767669678</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1401023864746</t>
+    <t xml:space="preserve">17.140100479126</t>
   </si>
   <si>
     <t xml:space="preserve">16.5731735229492</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5920715332031</t>
+    <t xml:space="preserve">16.5920696258545</t>
   </si>
   <si>
     <t xml:space="preserve">16.2897090911865</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8566341400146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1574287414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5805988311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5421257019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3882465362549</t>
+    <t xml:space="preserve">16.8566398620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1574268341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5805950164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5421276092529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3882503509521</t>
   </si>
   <si>
     <t xml:space="preserve">16.4459533691406</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2343673706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0035457611084</t>
+    <t xml:space="preserve">16.2343654632568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0035438537598</t>
   </si>
   <si>
     <t xml:space="preserve">15.9843101501465</t>
@@ -1700,58 +1700,58 @@
     <t xml:space="preserve">16.6767711639404</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8114166259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8306522369385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7537136077881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.638298034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4267158508301</t>
+    <t xml:space="preserve">16.8114185333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8306503295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7537117004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6382999420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4267139434814</t>
   </si>
   <si>
     <t xml:space="preserve">16.522891998291</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9458417892456</t>
+    <t xml:space="preserve">15.945839881897</t>
   </si>
   <si>
     <t xml:space="preserve">16.4651870727539</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9650754928589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0227794647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8688993453979</t>
+    <t xml:space="preserve">15.9650774002075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0227813720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8689012527466</t>
   </si>
   <si>
     <t xml:space="preserve">15.7342567443848</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6573162078857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4264965057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3687906265259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3110857009888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9840898513794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1956739425659</t>
+    <t xml:space="preserve">15.6573171615601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.426495552063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3687896728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3110847473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9840888977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1956748962402</t>
   </si>
   <si>
     <t xml:space="preserve">15.2341451644897</t>
@@ -1760,7 +1760,7 @@
     <t xml:space="preserve">15.1379690170288</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0994997024536</t>
+    <t xml:space="preserve">15.0994987487793</t>
   </si>
   <si>
     <t xml:space="preserve">15.003324508667</t>
@@ -1769,40 +1769,40 @@
     <t xml:space="preserve">15.1187343597412</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2533798217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0610303878784</t>
+    <t xml:space="preserve">15.2533779144287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0610294342041</t>
   </si>
   <si>
     <t xml:space="preserve">14.8686800003052</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8494424819946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7147998809814</t>
+    <t xml:space="preserve">14.8494434356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7147970199585</t>
   </si>
   <si>
     <t xml:space="preserve">15.4457292556763</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1764392852783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8302097320557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9648542404175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1572036743164</t>
+    <t xml:space="preserve">15.1764402389526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8302087783813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9648551940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1572046279907</t>
   </si>
   <si>
     <t xml:space="preserve">14.7917394638062</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7532691955566</t>
+    <t xml:space="preserve">14.753270149231</t>
   </si>
   <si>
     <t xml:space="preserve">14.9071493148804</t>
@@ -1817,43 +1817,43 @@
     <t xml:space="preserve">14.8879137039185</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5416831970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5801525115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5993900299072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5032138824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6378583908081</t>
+    <t xml:space="preserve">14.5416841506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.580153465271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5993890762329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5032119750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6378593444824</t>
   </si>
   <si>
     <t xml:space="preserve">14.6186237335205</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4647426605225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4455089569092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.65709400177</t>
+    <t xml:space="preserve">14.4647445678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4455080032349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6570930480957</t>
   </si>
   <si>
     <t xml:space="preserve">14.926383972168</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5609188079834</t>
+    <t xml:space="preserve">14.5609178543091</t>
   </si>
   <si>
     <t xml:space="preserve">15.349555015564</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3880252838135</t>
+    <t xml:space="preserve">15.3880262374878</t>
   </si>
   <si>
     <t xml:space="preserve">15.676549911499</t>
@@ -1862,34 +1862,34 @@
     <t xml:space="preserve">15.522668838501</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7150201797485</t>
+    <t xml:space="preserve">15.7150192260742</t>
   </si>
   <si>
     <t xml:space="preserve">15.7919597625732</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1574268341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7727270126343</t>
+    <t xml:space="preserve">16.1574249267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7727241516113</t>
   </si>
   <si>
     <t xml:space="preserve">15.8111953735352</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9073724746704</t>
+    <t xml:space="preserve">15.9073734283447</t>
   </si>
   <si>
     <t xml:space="preserve">15.6380786895752</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6188449859619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.849663734436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.580376625061</t>
+    <t xml:space="preserve">15.6188459396362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8496646881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5803747177124</t>
   </si>
   <si>
     <t xml:space="preserve">15.503436088562</t>
@@ -1904,22 +1904,22 @@
     <t xml:space="preserve">16.1189575195312</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1576461791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0037651062012</t>
+    <t xml:space="preserve">17.1576499938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0037670135498</t>
   </si>
   <si>
     <t xml:space="preserve">16.9460639953613</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8883590698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9845314025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1191787719727</t>
+    <t xml:space="preserve">16.888355255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9845333099365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1191749572754</t>
   </si>
   <si>
     <t xml:space="preserve">17.2730579376221</t>
@@ -1931,10 +1931,10 @@
     <t xml:space="preserve">18.1771030426025</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6000518798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6577606201172</t>
+    <t xml:space="preserve">17.6000537872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6577587127686</t>
   </si>
   <si>
     <t xml:space="preserve">18.1001644134521</t>
@@ -1943,34 +1943,34 @@
     <t xml:space="preserve">17.9847564697266</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1194000244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.965518951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9462852478027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0616931915283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9270496368408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3117523193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7541561126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1003856658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0234470367432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5425720214844</t>
+    <t xml:space="preserve">18.1193981170654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9655170440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9462814331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.061695098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9270515441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3117504119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7541542053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1003875732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0234451293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5425701141357</t>
   </si>
   <si>
     <t xml:space="preserve">18.9657402038574</t>
@@ -1979,13 +1979,13 @@
     <t xml:space="preserve">18.9080352783203</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4273834228516</t>
+    <t xml:space="preserve">19.4273815155029</t>
   </si>
   <si>
     <t xml:space="preserve">19.8120803833008</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5235557556152</t>
+    <t xml:space="preserve">19.5235576629639</t>
   </si>
   <si>
     <t xml:space="preserve">19.6678199768066</t>
@@ -2000,124 +2000,124 @@
     <t xml:space="preserve">19.6197319030762</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7159061431885</t>
+    <t xml:space="preserve">19.7159080505371</t>
   </si>
   <si>
     <t xml:space="preserve">19.7639942169189</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3312072753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5716438293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1967830657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2448673248291</t>
+    <t xml:space="preserve">19.331205368042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5716457366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1967849731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2448692321777</t>
   </si>
   <si>
     <t xml:space="preserve">22.2164611816406</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1585350036621</t>
+    <t xml:space="preserve">21.1585330963135</t>
   </si>
   <si>
     <t xml:space="preserve">21.1104469299316</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8219184875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6295738220215</t>
+    <t xml:space="preserve">20.8219223022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6295719146729</t>
   </si>
   <si>
     <t xml:space="preserve">21.0142726898193</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7257461547852</t>
+    <t xml:space="preserve">20.7257442474365</t>
   </si>
   <si>
     <t xml:space="preserve">20.6776580810547</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9563484191895</t>
+    <t xml:space="preserve">19.9563465118408</t>
   </si>
   <si>
     <t xml:space="preserve">20.2929573059082</t>
   </si>
   <si>
-    <t xml:space="preserve">20.004430770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8601703643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0811538696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.773832321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9180946350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5814838409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2547092437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3989753723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2066211700439</t>
+    <t xml:space="preserve">20.0044326782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8601684570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0811500549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7738342285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9180965423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5814819335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.254711151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3989715576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2066192626953</t>
   </si>
   <si>
     <t xml:space="preserve">21.6394081115723</t>
   </si>
   <si>
-    <t xml:space="preserve">21.447057723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8317623138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0525188446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1006088256836</t>
+    <t xml:space="preserve">21.4470596313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8317604064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0525207519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.100606918335</t>
   </si>
   <si>
     <t xml:space="preserve">18.734920501709</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1963405609131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6192874908447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3113040924072</t>
+    <t xml:space="preserve">18.1963386535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6192893981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3113059997559</t>
   </si>
   <si>
     <t xml:space="preserve">16.1958961486816</t>
   </si>
   <si>
-    <t xml:space="preserve">14.483980178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4262723922729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4643001556396</t>
+    <t xml:space="preserve">14.4839782714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4262742996216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.464301109314</t>
   </si>
   <si>
     <t xml:space="preserve">12.0218944549561</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1373043060303</t>
+    <t xml:space="preserve">12.1373052597046</t>
   </si>
   <si>
     <t xml:space="preserve">12.6951208114624</t>
@@ -2132,10 +2132,10 @@
     <t xml:space="preserve">13.3106412887573</t>
   </si>
   <si>
-    <t xml:space="preserve">13.560697555542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0223360061646</t>
+    <t xml:space="preserve">13.5606966018677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0223379135132</t>
   </si>
   <si>
     <t xml:space="preserve">14.1954526901245</t>
@@ -2144,25 +2144,25 @@
     <t xml:space="preserve">14.2916278839111</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1185140609741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7340326309204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0992774963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4072608947754</t>
+    <t xml:space="preserve">14.1185121536255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.734034538269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0992784500122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4072599411011</t>
   </si>
   <si>
     <t xml:space="preserve">16.8691234588623</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1766605377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2151336669922</t>
+    <t xml:space="preserve">16.1766624450684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2151298522949</t>
   </si>
   <si>
     <t xml:space="preserve">15.4649648666382</t>
@@ -2171,22 +2171,22 @@
     <t xml:space="preserve">16.0612506866455</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1381950378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0420169830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5998306274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.215353012085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7152404785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9268283843994</t>
+    <t xml:space="preserve">16.1381931304932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0420150756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.59983253479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2153549194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7152423858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9268264770508</t>
   </si>
   <si>
     <t xml:space="preserve">17.0614719390869</t>
@@ -2195,7 +2195,7 @@
     <t xml:space="preserve">18.2540454864502</t>
   </si>
   <si>
-    <t xml:space="preserve">18.638744354248</t>
+    <t xml:space="preserve">18.6387424468994</t>
   </si>
   <si>
     <t xml:space="preserve">18.0774536132812</t>
@@ -2207,22 +2207,22 @@
     <t xml:space="preserve">17.4580993652344</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4387454986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.206485748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9548721313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4193897247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6129360198975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1677742004395</t>
+    <t xml:space="preserve">17.4387435913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2064838409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.954870223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4193859100342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6129379272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1677761077881</t>
   </si>
   <si>
     <t xml:space="preserve">17.651647567749</t>
@@ -2237,19 +2237,19 @@
     <t xml:space="preserve">18.2903575897217</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9419727325439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0580997467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3871326446533</t>
+    <t xml:space="preserve">17.9419708251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0580978393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3871307373047</t>
   </si>
   <si>
     <t xml:space="preserve">18.4064865112305</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9032611846924</t>
+    <t xml:space="preserve">17.9032573699951</t>
   </si>
   <si>
     <t xml:space="preserve">18.2322940826416</t>
@@ -2261,40 +2261,40 @@
     <t xml:space="preserve">18.5806827545166</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4451961517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1161651611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0387439727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8322906494141</t>
+    <t xml:space="preserve">18.445198059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1161632537842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.038745880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8322944641113</t>
   </si>
   <si>
     <t xml:space="preserve">18.7742290496826</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6774559020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9097156524658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0451965332031</t>
+    <t xml:space="preserve">18.677453994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9097137451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0451984405518</t>
   </si>
   <si>
     <t xml:space="preserve">19.5968112945557</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3548755645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9484233856201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1032638549805</t>
+    <t xml:space="preserve">19.3548736572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9484252929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1032619476318</t>
   </si>
   <si>
     <t xml:space="preserve">18.4645500183105</t>
@@ -2309,31 +2309,31 @@
     <t xml:space="preserve">19.6451988220215</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0806846618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3226222991943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6129417419434</t>
+    <t xml:space="preserve">20.0806827545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3226203918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.612943649292</t>
   </si>
   <si>
     <t xml:space="preserve">20.5645561218262</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0484256744385</t>
+    <t xml:space="preserve">21.0484294891357</t>
   </si>
   <si>
     <t xml:space="preserve">21.2903633117676</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7258472442627</t>
+    <t xml:space="preserve">21.7258491516113</t>
   </si>
   <si>
     <t xml:space="preserve">21.1935901641846</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5806846618652</t>
+    <t xml:space="preserve">21.5806884765625</t>
   </si>
   <si>
     <t xml:space="preserve">21.8710098266602</t>
@@ -2351,7 +2351,7 @@
     <t xml:space="preserve">22.4516582489014</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9355278015137</t>
+    <t xml:space="preserve">22.9355297088623</t>
   </si>
   <si>
     <t xml:space="preserve">22.7903652191162</t>
@@ -2363,22 +2363,22 @@
     <t xml:space="preserve">23.4194011688232</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0968208312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7258548736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4839172363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0484313964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7581100463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9516582489014</t>
+    <t xml:space="preserve">24.0968189239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.72585105896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4839191436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.048433303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7581081390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.95166015625</t>
   </si>
   <si>
     <t xml:space="preserve">23.6613368988037</t>
@@ -2390,7 +2390,7 @@
     <t xml:space="preserve">23.0323028564453</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4677867889404</t>
+    <t xml:space="preserve">23.4677886962891</t>
   </si>
   <si>
     <t xml:space="preserve">23.0806903839111</t>
@@ -2402,55 +2402,55 @@
     <t xml:space="preserve">22.5484313964844</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8226203918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0645618438721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2419757843018</t>
+    <t xml:space="preserve">21.8226222991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0645599365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2419776916504</t>
   </si>
   <si>
     <t xml:space="preserve">21.6290740966797</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4677810668945</t>
+    <t xml:space="preserve">20.4677829742432</t>
   </si>
   <si>
     <t xml:space="preserve">21.3871383666992</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0968151092529</t>
+    <t xml:space="preserve">21.0968170166016</t>
   </si>
   <si>
     <t xml:space="preserve">21.4839134216309</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2097206115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9677867889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9516525268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1129474639893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3548831939697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9193954467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.838752746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.645206451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4355297088623</t>
+    <t xml:space="preserve">22.2097225189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9677848815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9516544342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1129455566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3548812866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.919397354126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8387546539307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6452045440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4355316162109</t>
   </si>
   <si>
     <t xml:space="preserve">24.3387565612793</t>
@@ -2468,16 +2468,16 @@
     <t xml:space="preserve">27.0000514984131</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6613426208496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6129570007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3710155487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6774730682373</t>
+    <t xml:space="preserve">26.661340713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6129531860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3710193634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6774711608887</t>
   </si>
   <si>
     <t xml:space="preserve">28.6452159881592</t>
@@ -2486,25 +2486,25 @@
     <t xml:space="preserve">29.9032821655273</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9355411529541</t>
+    <t xml:space="preserve">28.9355392456055</t>
   </si>
   <si>
     <t xml:space="preserve">29.7581214904785</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3871555328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9194145202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7419986724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0323181152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5484466552734</t>
+    <t xml:space="preserve">30.3871536254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9194164276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7419948577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0323143005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5484485626221</t>
   </si>
   <si>
     <t xml:space="preserve">32.0807075500488</t>
@@ -2513,13 +2513,13 @@
     <t xml:space="preserve">31.2581253051758</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1774826049805</t>
+    <t xml:space="preserve">32.1774787902832</t>
   </si>
   <si>
     <t xml:space="preserve">32.3226432800293</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2903823852539</t>
+    <t xml:space="preserve">33.2903861999512</t>
   </si>
   <si>
     <t xml:space="preserve">33.1936111450195</t>
@@ -2528,25 +2528,25 @@
     <t xml:space="preserve">32.8065147399902</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4839286804199</t>
+    <t xml:space="preserve">33.4839363098145</t>
   </si>
   <si>
     <t xml:space="preserve">33.7258720397949</t>
   </si>
   <si>
-    <t xml:space="preserve">34.1129684448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7420082092285</t>
+    <t xml:space="preserve">34.1129722595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.742000579834</t>
   </si>
   <si>
     <t xml:space="preserve">34.5968399047852</t>
   </si>
   <si>
-    <t xml:space="preserve">35.3710327148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4678153991699</t>
+    <t xml:space="preserve">35.3710403442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4678115844727</t>
   </si>
   <si>
     <t xml:space="preserve">36.8226509094238</t>
@@ -2558,43 +2558,43 @@
     <t xml:space="preserve">36.1936225891113</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3065185546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.564582824707</t>
+    <t xml:space="preserve">34.3065223693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5645790100098</t>
   </si>
   <si>
     <t xml:space="preserve">32.6613540649414</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7581253051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7097396850586</t>
+    <t xml:space="preserve">32.758129119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7097434997559</t>
   </si>
   <si>
     <t xml:space="preserve">31.9355430603027</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3387660980225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.822639465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5807037353516</t>
+    <t xml:space="preserve">30.3387699127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8226413726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5807056427002</t>
   </si>
   <si>
     <t xml:space="preserve">30.4839305877686</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1129627227783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.435546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8710327148438</t>
+    <t xml:space="preserve">31.112964630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4355506896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8710289001465</t>
   </si>
   <si>
     <t xml:space="preserve">35.2742652893066</t>
@@ -2603,7 +2603,7 @@
     <t xml:space="preserve">35.6613616943359</t>
   </si>
   <si>
-    <t xml:space="preserve">35.7097473144531</t>
+    <t xml:space="preserve">35.7097434997559</t>
   </si>
   <si>
     <t xml:space="preserve">37.2581367492676</t>
@@ -2612,7 +2612,7 @@
     <t xml:space="preserve">37.0162010192871</t>
   </si>
   <si>
-    <t xml:space="preserve">36.9678153991699</t>
+    <t xml:space="preserve">36.9678115844727</t>
   </si>
   <si>
     <t xml:space="preserve">35.9516830444336</t>
@@ -2621,16 +2621,16 @@
     <t xml:space="preserve">36.4355545043945</t>
   </si>
   <si>
-    <t xml:space="preserve">35.0807113647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.983943939209</t>
+    <t xml:space="preserve">35.0807151794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9839401245117</t>
   </si>
   <si>
     <t xml:space="preserve">36.677490234375</t>
   </si>
   <si>
-    <t xml:space="preserve">37.0645904541016</t>
+    <t xml:space="preserve">37.064582824707</t>
   </si>
   <si>
     <t xml:space="preserve">37.6452331542969</t>
@@ -2651,43 +2651,43 @@
     <t xml:space="preserve">39.6774940490723</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5645866394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.7097511291504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6291122436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4516944885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.1613693237305</t>
+    <t xml:space="preserve">38.5645904541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.7097473144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6291046142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4516906738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.1613655090332</t>
   </si>
   <si>
     <t xml:space="preserve">39.4355621337891</t>
   </si>
   <si>
-    <t xml:space="preserve">40.2581443786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.0807304382324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.9033050537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.0645980834961</t>
+    <t xml:space="preserve">40.2581405639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.0807266235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.9033088684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.0645942687988</t>
   </si>
   <si>
     <t xml:space="preserve">41.1774978637695</t>
   </si>
   <si>
-    <t xml:space="preserve">41.854923248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.3387870788574</t>
+    <t xml:space="preserve">41.8549156188965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.3387908935547</t>
   </si>
   <si>
     <t xml:space="preserve">42.048469543457</t>
@@ -2702,37 +2702,37 @@
     <t xml:space="preserve">42.3871803283691</t>
   </si>
   <si>
-    <t xml:space="preserve">43.5000801086426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.1291236877441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.7097663879395</t>
+    <t xml:space="preserve">43.5000877380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.1291198730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.7097625732422</t>
   </si>
   <si>
     <t xml:space="preserve">44.7581520080566</t>
   </si>
   <si>
-    <t xml:space="preserve">45.6775054931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.4194412231445</t>
+    <t xml:space="preserve">45.6775093078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.4194450378418</t>
   </si>
   <si>
     <t xml:space="preserve">45.0000877380371</t>
   </si>
   <si>
-    <t xml:space="preserve">46.0162162780762</t>
+    <t xml:space="preserve">46.0162200927734</t>
   </si>
   <si>
     <t xml:space="preserve">45.483959197998</t>
   </si>
   <si>
-    <t xml:space="preserve">44.9517021179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.2581558227539</t>
+    <t xml:space="preserve">44.9516983032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.2581520080566</t>
   </si>
   <si>
     <t xml:space="preserve">45.1452522277832</t>
@@ -2747,13 +2747,13 @@
     <t xml:space="preserve">44.2742767333984</t>
   </si>
   <si>
-    <t xml:space="preserve">43.8387908935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.1613693237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.3065299987793</t>
+    <t xml:space="preserve">43.838794708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.161376953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.3065338134766</t>
   </si>
   <si>
     <t xml:space="preserve">43.2581481933594</t>
@@ -2768,43 +2768,43 @@
     <t xml:space="preserve">44.0323448181152</t>
   </si>
   <si>
-    <t xml:space="preserve">43.4033088684082</t>
+    <t xml:space="preserve">43.4033050537109</t>
   </si>
   <si>
     <t xml:space="preserve">42.4355621337891</t>
   </si>
   <si>
-    <t xml:space="preserve">41.8992919921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.0436096191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.7994422912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4576072692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.0924453735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.8737831115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9947776794434</t>
+    <t xml:space="preserve">41.8992881774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.0436134338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.799446105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4576110839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.0924415588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.873779296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9947738647461</t>
   </si>
   <si>
     <t xml:space="preserve">40.7761154174805</t>
   </si>
   <si>
-    <t xml:space="preserve">40.6784515380859</t>
+    <t xml:space="preserve">40.6784477233887</t>
   </si>
   <si>
     <t xml:space="preserve">40.190113067627</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8971099853516</t>
+    <t xml:space="preserve">39.8971061706543</t>
   </si>
   <si>
     <t xml:space="preserve">39.6529388427734</t>
@@ -2816,13 +2816,13 @@
     <t xml:space="preserve">39.7506103515625</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2622718811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2877807617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9459457397461</t>
+    <t xml:space="preserve">39.2622680664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2877731323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9459419250488</t>
   </si>
   <si>
     <t xml:space="preserve">37.8949279785156</t>
@@ -2849,13 +2849,13 @@
     <t xml:space="preserve">41.4597854614258</t>
   </si>
   <si>
-    <t xml:space="preserve">41.0691146850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.385440826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4342842102051</t>
+    <t xml:space="preserve">41.0691184997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.3854446411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4342803955078</t>
   </si>
   <si>
     <t xml:space="preserve">42.1922912597656</t>
@@ -2864,25 +2864,25 @@
     <t xml:space="preserve">42.0457916259766</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9481201171875</t>
+    <t xml:space="preserve">41.9481239318848</t>
   </si>
   <si>
     <t xml:space="preserve">41.4109535217285</t>
   </si>
   <si>
-    <t xml:space="preserve">42.7294578552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3664817810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4153137207031</t>
+    <t xml:space="preserve">42.7294616699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3664779663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4153099060059</t>
   </si>
   <si>
     <t xml:space="preserve">46.1966514587402</t>
   </si>
   <si>
-    <t xml:space="preserve">47.8569946289062</t>
+    <t xml:space="preserve">47.8569984436035</t>
   </si>
   <si>
     <t xml:space="preserve">47.31982421875</t>
@@ -2891,40 +2891,40 @@
     <t xml:space="preserve">47.808162689209</t>
   </si>
   <si>
-    <t xml:space="preserve">48.5406646728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.5894966125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.8336715698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.1988258361816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.7126808166504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.9080123901367</t>
+    <t xml:space="preserve">48.5406684875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.5895004272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.833667755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.1988296508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.7126770019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.9080085754395</t>
   </si>
   <si>
     <t xml:space="preserve">49.8103446960449</t>
   </si>
   <si>
-    <t xml:space="preserve">50.0056800842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.6893501281738</t>
+    <t xml:space="preserve">50.0056762695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.6893539428711</t>
   </si>
   <si>
     <t xml:space="preserve">51.3730201721191</t>
   </si>
   <si>
-    <t xml:space="preserve">50.2986793518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.5916862487793</t>
+    <t xml:space="preserve">50.2986831665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.591682434082</t>
   </si>
   <si>
     <t xml:space="preserve">50.4940147399902</t>
@@ -2933,16 +2933,16 @@
     <t xml:space="preserve">51.2753524780273</t>
   </si>
   <si>
-    <t xml:space="preserve">50.2010154724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.7870216369629</t>
+    <t xml:space="preserve">50.2010116577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.7870140075684</t>
   </si>
   <si>
     <t xml:space="preserve">50.9823532104492</t>
   </si>
   <si>
-    <t xml:space="preserve">51.8613548278809</t>
+    <t xml:space="preserve">51.8613586425781</t>
   </si>
   <si>
     <t xml:space="preserve">51.9590263366699</t>
@@ -2951,28 +2951,28 @@
     <t xml:space="preserve">50.8846817016602</t>
   </si>
   <si>
-    <t xml:space="preserve">45.2688102722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.5363121032715</t>
+    <t xml:space="preserve">45.2688140869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.536304473877</t>
   </si>
   <si>
     <t xml:space="preserve">43.5107955932617</t>
   </si>
   <si>
-    <t xml:space="preserve">44.2433013916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.2921333312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.9269790649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.047966003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8038024902344</t>
+    <t xml:space="preserve">44.2433052062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2921371459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.9269752502441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.0479698181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8037986755371</t>
   </si>
   <si>
     <t xml:space="preserve">44.4386405944824</t>
@@ -2984,16 +2984,16 @@
     <t xml:space="preserve">44.1944694519043</t>
   </si>
   <si>
-    <t xml:space="preserve">41.2156219482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.9714508056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.7527885437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.2899551391602</t>
+    <t xml:space="preserve">41.2156181335449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.9714469909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.7527923583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.2899589538574</t>
   </si>
   <si>
     <t xml:space="preserve">43.0712928771973</t>
@@ -3002,13 +3002,13 @@
     <t xml:space="preserve">43.2666320800781</t>
   </si>
   <si>
-    <t xml:space="preserve">43.7061309814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.3409767150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4641456604004</t>
+    <t xml:space="preserve">43.7061347961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.3409729003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4641494750977</t>
   </si>
   <si>
     <t xml:space="preserve">46.0989837646484</t>
@@ -3017,7 +3017,7 @@
     <t xml:space="preserve">45.659481048584</t>
   </si>
   <si>
-    <t xml:space="preserve">45.7571449279785</t>
+    <t xml:space="preserve">45.7571411132812</t>
   </si>
   <si>
     <t xml:space="preserve">42.7782974243164</t>
@@ -3035,34 +3035,34 @@
     <t xml:space="preserve">42.4364624023438</t>
   </si>
   <si>
-    <t xml:space="preserve">41.5086212158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0202865600586</t>
+    <t xml:space="preserve">41.508617401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0202827453613</t>
   </si>
   <si>
     <t xml:space="preserve">38.8716011047363</t>
   </si>
   <si>
-    <t xml:space="preserve">38.2367630004883</t>
+    <t xml:space="preserve">38.2367668151855</t>
   </si>
   <si>
     <t xml:space="preserve">39.0669364929199</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8482780456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5319480895996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.850456237793</t>
+    <t xml:space="preserve">39.848274230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5319442749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8504524230957</t>
   </si>
   <si>
     <t xml:space="preserve">41.1179466247559</t>
   </si>
   <si>
-    <t xml:space="preserve">40.824951171875</t>
+    <t xml:space="preserve">40.8249473571777</t>
   </si>
   <si>
     <t xml:space="preserve">41.6551208496094</t>
@@ -3071,7 +3071,7 @@
     <t xml:space="preserve">41.6062850952148</t>
   </si>
   <si>
-    <t xml:space="preserve">42.4852905273438</t>
+    <t xml:space="preserve">42.485294342041</t>
   </si>
   <si>
     <t xml:space="preserve">42.9736289978027</t>
@@ -3080,16 +3080,16 @@
     <t xml:space="preserve">41.8016204833984</t>
   </si>
   <si>
-    <t xml:space="preserve">41.362117767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2389488220215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.6296157836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.8759613037109</t>
+    <t xml:space="preserve">41.3621215820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2389450073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.6296119689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.8759651184082</t>
   </si>
   <si>
     <t xml:space="preserve">43.4619674682617</t>
@@ -3098,22 +3098,22 @@
     <t xml:space="preserve">43.999137878418</t>
   </si>
   <si>
-    <t xml:space="preserve">40.9226150512695</t>
+    <t xml:space="preserve">40.9226188659668</t>
   </si>
   <si>
     <t xml:space="preserve">39.1157684326172</t>
   </si>
   <si>
-    <t xml:space="preserve">42.5829620361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.6317939758301</t>
+    <t xml:space="preserve">42.5829582214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.6317977905273</t>
   </si>
   <si>
     <t xml:space="preserve">38.5785980224609</t>
   </si>
   <si>
-    <t xml:space="preserve">36.4299163818359</t>
+    <t xml:space="preserve">36.4299125671387</t>
   </si>
   <si>
     <t xml:space="preserve">38.6274337768555</t>
@@ -3122,28 +3122,28 @@
     <t xml:space="preserve">37.1135902404785</t>
   </si>
   <si>
-    <t xml:space="preserve">35.7950859069824</t>
+    <t xml:space="preserve">35.7950820922852</t>
   </si>
   <si>
     <t xml:space="preserve">34.7207374572754</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5997505187988</t>
+    <t xml:space="preserve">35.5997467041016</t>
   </si>
   <si>
     <t xml:space="preserve">36.527587890625</t>
   </si>
   <si>
-    <t xml:space="preserve">36.6252517700195</t>
+    <t xml:space="preserve">36.6252555847168</t>
   </si>
   <si>
     <t xml:space="preserve">36.0880813598633</t>
   </si>
   <si>
-    <t xml:space="preserve">36.1369171142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4532470703125</t>
+    <t xml:space="preserve">36.1369132995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4532432556152</t>
   </si>
   <si>
     <t xml:space="preserve">34.5254020690918</t>
@@ -3152,7 +3152,7 @@
     <t xml:space="preserve">36.3810844421387</t>
   </si>
   <si>
-    <t xml:space="preserve">35.3555755615234</t>
+    <t xml:space="preserve">35.3555793762207</t>
   </si>
   <si>
     <t xml:space="preserve">33.9393997192383</t>
@@ -3161,37 +3161,37 @@
     <t xml:space="preserve">32.1325569152832</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4977188110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6442222595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0115585327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3767242431641</t>
+    <t xml:space="preserve">31.4977169036865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6442184448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0115623474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3767280578613</t>
   </si>
   <si>
     <t xml:space="preserve">33.4510612487793</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7695693969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5742378234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3067474365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0348892211914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4000492095947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5975608825684</t>
+    <t xml:space="preserve">34.7695732116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5742416381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3067436218262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0348854064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4000511169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5975646972656</t>
   </si>
   <si>
     <t xml:space="preserve">32.9627265930176</t>
@@ -3200,7 +3200,7 @@
     <t xml:space="preserve">32.5232238769531</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4255561828613</t>
+    <t xml:space="preserve">32.4255599975586</t>
   </si>
   <si>
     <t xml:space="preserve">32.6208915710449</t>
@@ -3209,13 +3209,13 @@
     <t xml:space="preserve">31.4488849639893</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6697273254395</t>
+    <t xml:space="preserve">32.6697235107422</t>
   </si>
   <si>
     <t xml:space="preserve">32.767391204834</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2144794464111</t>
+    <t xml:space="preserve">31.2144813537598</t>
   </si>
   <si>
     <t xml:space="preserve">31.0191459655762</t>
@@ -3227,49 +3227,49 @@
     <t xml:space="preserve">29.6518058776855</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4722118377686</t>
+    <t xml:space="preserve">30.4722099304199</t>
   </si>
   <si>
     <t xml:space="preserve">32.2302207946777</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0739593505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9372215270996</t>
+    <t xml:space="preserve">32.0739555358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.937219619751</t>
   </si>
   <si>
     <t xml:space="preserve">31.3316841125488</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1716194152832</t>
+    <t xml:space="preserve">32.1716232299805</t>
   </si>
   <si>
     <t xml:space="preserve">31.3902816772461</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6637516021729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8862075805664</t>
+    <t xml:space="preserve">31.6637496948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8862037658691</t>
   </si>
   <si>
     <t xml:space="preserve">29.9643402099609</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3821277618408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4993305206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2025356292725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8704643249512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9290657043457</t>
+    <t xml:space="preserve">28.3821296691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4993324279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2025337219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8704662322998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9290676116943</t>
   </si>
   <si>
     <t xml:space="preserve">29.085334777832</t>
@@ -3278,22 +3278,22 @@
     <t xml:space="preserve">28.3039951324463</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4211978912354</t>
+    <t xml:space="preserve">28.4211959838867</t>
   </si>
   <si>
     <t xml:space="preserve">27.0147857666016</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3235301971436</t>
+    <t xml:space="preserve">28.3235282897949</t>
   </si>
   <si>
     <t xml:space="preserve">28.5969982147217</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2258605957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5579299926758</t>
+    <t xml:space="preserve">28.2258625030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5579280853271</t>
   </si>
   <si>
     <t xml:space="preserve">28.1816463470459</t>
@@ -3302,31 +3302,31 @@
     <t xml:space="preserve">26.8943614959717</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5972938537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.676513671875</t>
+    <t xml:space="preserve">26.5972957611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6765117645264</t>
   </si>
   <si>
     <t xml:space="preserve">26.8745555877686</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5281009674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4784698486328</t>
+    <t xml:space="preserve">27.5280990600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4784679412842</t>
   </si>
   <si>
     <t xml:space="preserve">26.7359256744385</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2508392333984</t>
+    <t xml:space="preserve">27.2508411407471</t>
   </si>
   <si>
     <t xml:space="preserve">28.0628204345703</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3994960784912</t>
+    <t xml:space="preserve">28.3994941711426</t>
   </si>
   <si>
     <t xml:space="preserve">28.320276260376</t>
@@ -3338,10 +3338,10 @@
     <t xml:space="preserve">27.9439926147461</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4192981719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0134296417236</t>
+    <t xml:space="preserve">28.4193000793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.013427734375</t>
   </si>
   <si>
     <t xml:space="preserve">29.1124515533447</t>
@@ -3350,7 +3350,7 @@
     <t xml:space="preserve">29.5481491088867</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1322555541992</t>
+    <t xml:space="preserve">29.1322574615479</t>
   </si>
   <si>
     <t xml:space="preserve">26.9933834075928</t>
@@ -3365,22 +3365,22 @@
     <t xml:space="preserve">25.6466846466064</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4584197998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4288368225098</t>
+    <t xml:space="preserve">24.4584217071533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4288349151611</t>
   </si>
   <si>
     <t xml:space="preserve">25.6070766448975</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4684429168701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8148975372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2902050018311</t>
+    <t xml:space="preserve">25.4684448242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8148994445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2902069091797</t>
   </si>
   <si>
     <t xml:space="preserve">25.3694229125977</t>
@@ -3398,10 +3398,10 @@
     <t xml:space="preserve">23.8444843292236</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0523109436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5474185943604</t>
+    <t xml:space="preserve">23.0523090362549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.547420501709</t>
   </si>
   <si>
     <t xml:space="preserve">24.200963973999</t>
@@ -3410,13 +3410,13 @@
     <t xml:space="preserve">23.6068325042725</t>
   </si>
   <si>
-    <t xml:space="preserve">23.190938949585</t>
+    <t xml:space="preserve">23.1909408569336</t>
   </si>
   <si>
     <t xml:space="preserve">22.9136772155762</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4185695648193</t>
+    <t xml:space="preserve">22.4185676574707</t>
   </si>
   <si>
     <t xml:space="preserve">21.5669803619385</t>
@@ -3434,16 +3434,16 @@
     <t xml:space="preserve">23.7058544158936</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7356834411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5970516204834</t>
+    <t xml:space="preserve">24.7356815338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.597053527832</t>
   </si>
   <si>
     <t xml:space="preserve">25.1911849975586</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9239463806152</t>
+    <t xml:space="preserve">25.9239444732666</t>
   </si>
   <si>
     <t xml:space="preserve">25.8249244689941</t>
@@ -3458,10 +3458,10 @@
     <t xml:space="preserve">25.3892269134521</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1317691802979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5674667358398</t>
+    <t xml:space="preserve">25.1317672729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5674648284912</t>
   </si>
   <si>
     <t xml:space="preserve">26.0427722930908</t>
@@ -3470,19 +3470,19 @@
     <t xml:space="preserve">26.1417942047119</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8843364715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4882488250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5178356170654</t>
+    <t xml:space="preserve">25.884334564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4882469177246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5178337097168</t>
   </si>
   <si>
     <t xml:space="preserve">24.0227241516113</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2207679748535</t>
+    <t xml:space="preserve">24.2207660675049</t>
   </si>
   <si>
     <t xml:space="preserve">24.1217479705811</t>
@@ -3494,28 +3494,28 @@
     <t xml:space="preserve">24.3197898864746</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2603759765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3593978881836</t>
+    <t xml:space="preserve">24.2603778839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3593997955322</t>
   </si>
   <si>
     <t xml:space="preserve">23.626636505127</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4980278015137</t>
+    <t xml:space="preserve">24.4980297088623</t>
   </si>
   <si>
     <t xml:space="preserve">23.8642902374268</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9435081481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7850723266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8743152618408</t>
+    <t xml:space="preserve">23.9435062408447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7850704193115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8743133544922</t>
   </si>
   <si>
     <t xml:space="preserve">24.9535312652588</t>
@@ -3527,7 +3527,7 @@
     <t xml:space="preserve">23.765266418457</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8344612121582</t>
+    <t xml:space="preserve">22.8344593048096</t>
   </si>
   <si>
     <t xml:space="preserve">22.5571994781494</t>
@@ -3551,7 +3551,7 @@
     <t xml:space="preserve">20.0618476867676</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2696685791016</t>
+    <t xml:space="preserve">19.2696704864502</t>
   </si>
   <si>
     <t xml:space="preserve">19.8836078643799</t>
@@ -3560,7 +3560,7 @@
     <t xml:space="preserve">20.2400875091553</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4481544494629</t>
+    <t xml:space="preserve">21.4481525421143</t>
   </si>
   <si>
     <t xml:space="preserve">20.9926528930664</t>
@@ -3581,25 +3581,25 @@
     <t xml:space="preserve">21.3887405395508</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6065883636475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0026741027832</t>
+    <t xml:space="preserve">21.6065902709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0026760101318</t>
   </si>
   <si>
     <t xml:space="preserve">22.2007217407227</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6660003662109</t>
+    <t xml:space="preserve">21.6660022735596</t>
   </si>
   <si>
     <t xml:space="preserve">21.5075664520264</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6760234832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3195457458496</t>
+    <t xml:space="preserve">22.676025390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3195476531982</t>
   </si>
   <si>
     <t xml:space="preserve">22.1809158325195</t>
@@ -3608,7 +3608,7 @@
     <t xml:space="preserve">22.4383716583252</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7848262786865</t>
+    <t xml:space="preserve">21.7848281860352</t>
   </si>
   <si>
     <t xml:space="preserve">22.0620899200439</t>
@@ -3632,7 +3632,7 @@
     <t xml:space="preserve">27.0329895019531</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6369018554688</t>
+    <t xml:space="preserve">26.6369037628174</t>
   </si>
   <si>
     <t xml:space="preserve">26.5576858520508</t>
@@ -3641,13 +3641,13 @@
     <t xml:space="preserve">23.9831142425537</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0525512695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2505950927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2012062072754</t>
+    <t xml:space="preserve">25.0525531768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2505970001221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.201208114624</t>
   </si>
   <si>
     <t xml:space="preserve">26.4190540313721</t>
@@ -3671,10 +3671,10 @@
     <t xml:space="preserve">23.8246803283691</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9730911254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7950954437256</t>
+    <t xml:space="preserve">22.9730930328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7950973510742</t>
   </si>
   <si>
     <t xml:space="preserve">25.2704010009766</t>
@@ -3686,7 +3686,7 @@
     <t xml:space="preserve">26.0625743865967</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7853164672852</t>
+    <t xml:space="preserve">25.7853145599365</t>
   </si>
   <si>
     <t xml:space="preserve">26.2606220245361</t>
@@ -3695,40 +3695,40 @@
     <t xml:space="preserve">27.0725994110107</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7953395843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0232105255127</t>
+    <t xml:space="preserve">26.795337677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0232086181641</t>
   </si>
   <si>
     <t xml:space="preserve">27.5875148773193</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4884929656982</t>
+    <t xml:space="preserve">27.4884948730469</t>
   </si>
   <si>
     <t xml:space="preserve">28.6965599060059</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7757759094238</t>
+    <t xml:space="preserve">28.7757778167725</t>
   </si>
   <si>
     <t xml:space="preserve">28.2212543487549</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5777359008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.280668258667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8153877258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8747997283936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.716365814209</t>
+    <t xml:space="preserve">28.5777320861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2806701660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8153858184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8747978210449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7163639068604</t>
   </si>
   <si>
     <t xml:space="preserve">28.6569519042969</t>
@@ -3737,7 +3737,7 @@
     <t xml:space="preserve">28.9540157318115</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8549938201904</t>
+    <t xml:space="preserve">28.8549957275391</t>
   </si>
   <si>
     <t xml:space="preserve">28.9738216400146</t>
@@ -3749,19 +3749,19 @@
     <t xml:space="preserve">30.280912399292</t>
   </si>
   <si>
-    <t xml:space="preserve">29.924430847168</t>
+    <t xml:space="preserve">29.9244327545166</t>
   </si>
   <si>
     <t xml:space="preserve">29.9838466644287</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7065830230713</t>
+    <t xml:space="preserve">29.7065849304199</t>
   </si>
   <si>
     <t xml:space="preserve">29.5877571105957</t>
   </si>
   <si>
-    <t xml:space="preserve">29.33030128479</t>
+    <t xml:space="preserve">29.3303031921387</t>
   </si>
   <si>
     <t xml:space="preserve">29.4491271972656</t>
@@ -3773,7 +3773,7 @@
     <t xml:space="preserve">29.2510833740234</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9342136383057</t>
+    <t xml:space="preserve">28.934211730957</t>
   </si>
   <si>
     <t xml:space="preserve">28.2608642578125</t>
@@ -3785,10 +3785,10 @@
     <t xml:space="preserve">28.3004722595215</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4787120819092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0430145263672</t>
+    <t xml:space="preserve">28.4787139892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0430164337158</t>
   </si>
   <si>
     <t xml:space="preserve">27.6469268798828</t>
@@ -3797,7 +3797,7 @@
     <t xml:space="preserve">27.7063407897949</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0131893157959</t>
+    <t xml:space="preserve">27.0131874084473</t>
   </si>
   <si>
     <t xml:space="preserve">26.7755355834961</t>
@@ -3806,19 +3806,19 @@
     <t xml:space="preserve">25.6664886474609</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4782238006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3097667694092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3789615631104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2801818847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5574436187744</t>
+    <t xml:space="preserve">24.4782257080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3097686767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3789596557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.280179977417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5574417114258</t>
   </si>
   <si>
     <t xml:space="preserve">24.8347034454346</t>
@@ -3830,13 +3830,13 @@
     <t xml:space="preserve">25.8447284698486</t>
   </si>
   <si>
-    <t xml:space="preserve">26.389347076416</t>
+    <t xml:space="preserve">26.3893489837646</t>
   </si>
   <si>
     <t xml:space="preserve">27.0825023651123</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8349475860596</t>
+    <t xml:space="preserve">26.8349494934082</t>
   </si>
   <si>
     <t xml:space="preserve">27.2805442810059</t>
@@ -3845,13 +3845,13 @@
     <t xml:space="preserve">27.4785900115967</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0727233886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7756538391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6766357421875</t>
+    <t xml:space="preserve">28.0727214813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.77565574646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6766338348389</t>
   </si>
   <si>
     <t xml:space="preserve">27.4290790557861</t>
@@ -3860,16 +3860,16 @@
     <t xml:space="preserve">27.1815242767334</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9339694976807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3795680999756</t>
+    <t xml:space="preserve">26.9339714050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.379566192627</t>
   </si>
   <si>
     <t xml:space="preserve">26.8844585418701</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7261447906494</t>
+    <t xml:space="preserve">27.7261428833008</t>
   </si>
   <si>
     <t xml:space="preserve">26.9834804534912</t>
@@ -3881,10 +3881,10 @@
     <t xml:space="preserve">27.6271228790283</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9241905212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4688110351562</t>
+    <t xml:space="preserve">27.9241886138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4688091278076</t>
   </si>
   <si>
     <t xml:space="preserve">29.5085391998291</t>
@@ -3893,40 +3893,40 @@
     <t xml:space="preserve">30.5482711791992</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3007164001465</t>
+    <t xml:space="preserve">30.3007144927979</t>
   </si>
   <si>
     <t xml:space="preserve">30.944356918335</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0831146240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6375122070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1821327209473</t>
+    <t xml:space="preserve">32.0831108093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6375141143799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1821365356445</t>
   </si>
   <si>
     <t xml:space="preserve">32.9247970581055</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4296913146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2316398620605</t>
+    <t xml:space="preserve">32.4296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2316436767578</t>
   </si>
   <si>
     <t xml:space="preserve">31.9840888977051</t>
   </si>
   <si>
-    <t xml:space="preserve">31.191915512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3404445648193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.795825958252</t>
+    <t xml:space="preserve">31.1919136047363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.340446472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7958240509033</t>
   </si>
   <si>
     <t xml:space="preserve">30.6472949981689</t>
@@ -3944,7 +3944,7 @@
     <t xml:space="preserve">30.5977802276611</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4492492675781</t>
+    <t xml:space="preserve">30.4492473602295</t>
   </si>
   <si>
     <t xml:space="preserve">29.9219970703125</t>
@@ -3953,13 +3953,13 @@
     <t xml:space="preserve">29.6237697601318</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8225860595703</t>
+    <t xml:space="preserve">29.8225879669189</t>
   </si>
   <si>
     <t xml:space="preserve">29.6734752655029</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4687423706055</t>
+    <t xml:space="preserve">30.4687442779541</t>
   </si>
   <si>
     <t xml:space="preserve">30.717264175415</t>
@@ -3971,10 +3971,10 @@
     <t xml:space="preserve">30.3196315765381</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1148986816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3137187957764</t>
+    <t xml:space="preserve">31.1149005889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3137168884277</t>
   </si>
   <si>
     <t xml:space="preserve">31.5125350952148</t>
@@ -3983,13 +3983,13 @@
     <t xml:space="preserve">31.1646041870117</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4131259918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0592842102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7551460266113</t>
+    <t xml:space="preserve">31.4131278991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0592803955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7551422119141</t>
   </si>
   <si>
     <t xml:space="preserve">31.8107604980469</t>
@@ -4001,7 +4001,7 @@
     <t xml:space="preserve">32.3575057983398</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8166732788086</t>
+    <t xml:space="preserve">30.8166751861572</t>
   </si>
   <si>
     <t xml:space="preserve">30.7669715881348</t>
@@ -4013,28 +4013,28 @@
     <t xml:space="preserve">28.0829372406006</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9894428253174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6912174224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.398904800415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3551120758057</t>
+    <t xml:space="preserve">26.9894409179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6912155151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3989028930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3551139831543</t>
   </si>
   <si>
     <t xml:space="preserve">24.8024520874023</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6533393859863</t>
+    <t xml:space="preserve">24.6533374786377</t>
   </si>
   <si>
     <t xml:space="preserve">24.4545211791992</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6036357879639</t>
+    <t xml:space="preserve">24.6036338806152</t>
   </si>
   <si>
     <t xml:space="preserve">24.4048175811768</t>
@@ -4055,13 +4055,13 @@
     <t xml:space="preserve">25.6971302032471</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9456520080566</t>
+    <t xml:space="preserve">25.945650100708</t>
   </si>
   <si>
     <t xml:space="preserve">25.2000865936279</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7030429840088</t>
+    <t xml:space="preserve">24.7030448913574</t>
   </si>
   <si>
     <t xml:space="preserve">25.647424697876</t>
@@ -4073,19 +4073,19 @@
     <t xml:space="preserve">26.8403282165527</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2935810089111</t>
+    <t xml:space="preserve">26.2935829162598</t>
   </si>
   <si>
     <t xml:space="preserve">25.7965393066406</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2994976043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5539302825928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7527484893799</t>
+    <t xml:space="preserve">25.2994956970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5539321899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7527465820312</t>
   </si>
   <si>
     <t xml:space="preserve">24.1065921783447</t>
@@ -4094,7 +4094,7 @@
     <t xml:space="preserve">24.5042266845703</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1562957763672</t>
+    <t xml:space="preserve">24.1562938690186</t>
   </si>
   <si>
     <t xml:space="preserve">25.3491992950439</t>
@@ -4106,16 +4106,16 @@
     <t xml:space="preserve">25.8462429046631</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5421047210693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4923973083496</t>
+    <t xml:space="preserve">26.5421028137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4923992156982</t>
   </si>
   <si>
     <t xml:space="preserve">26.4426956176758</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9397373199463</t>
+    <t xml:space="preserve">26.9397392272949</t>
   </si>
   <si>
     <t xml:space="preserve">27.6355972290039</t>
@@ -4136,7 +4136,7 @@
     <t xml:space="preserve">29.7231788635254</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6296844482422</t>
+    <t xml:space="preserve">28.6296825408936</t>
   </si>
   <si>
     <t xml:space="preserve">29.7728843688965</t>
@@ -4160,19 +4160,19 @@
     <t xml:space="preserve">27.7847118377686</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0332336425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1823463439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3752498626709</t>
+    <t xml:space="preserve">28.0332317352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1823444366455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3752479553223</t>
   </si>
   <si>
     <t xml:space="preserve">29.2261352539062</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5681533813477</t>
+    <t xml:space="preserve">30.568151473999</t>
   </si>
   <si>
     <t xml:space="preserve">31.5622386932373</t>
@@ -4202,7 +4202,7 @@
     <t xml:space="preserve">31.3634204864502</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9101676940918</t>
+    <t xml:space="preserve">31.9101657867432</t>
   </si>
   <si>
     <t xml:space="preserve">31.7610569000244</t>
@@ -4229,10 +4229,10 @@
     <t xml:space="preserve">30.6675624847412</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2640132904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3693332672119</t>
+    <t xml:space="preserve">31.2640151977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3693351745605</t>
   </si>
   <si>
     <t xml:space="preserve">30.6178569793701</t>
@@ -4241,13 +4241,13 @@
     <t xml:space="preserve">33.5504112243652</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6936149597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8486328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7989349365234</t>
+    <t xml:space="preserve">34.6936111450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8486366271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7989311218262</t>
   </si>
   <si>
     <t xml:space="preserve">34.1468620300293</t>
@@ -4262,16 +4262,16 @@
     <t xml:space="preserve">33.3018913269043</t>
   </si>
   <si>
-    <t xml:space="preserve">32.606029510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9042549133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5563278198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8048439025879</t>
+    <t xml:space="preserve">32.6060256958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9042510986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.556324005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8048477172852</t>
   </si>
   <si>
     <t xml:space="preserve">34.4947929382324</t>
@@ -4289,7 +4289,7 @@
     <t xml:space="preserve">37.1788291931152</t>
   </si>
   <si>
-    <t xml:space="preserve">36.781192779541</t>
+    <t xml:space="preserve">36.7811889648438</t>
   </si>
   <si>
     <t xml:space="preserve">36.3835563659668</t>
@@ -4301,10 +4301,10 @@
     <t xml:space="preserve">37.2285308837891</t>
   </si>
   <si>
-    <t xml:space="preserve">36.8805961608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.4711380004883</t>
+    <t xml:space="preserve">36.8805999755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.4711418151855</t>
   </si>
   <si>
     <t xml:space="preserve">37.9740943908691</t>
@@ -4316,16 +4316,16 @@
     <t xml:space="preserve">35.8368072509766</t>
   </si>
   <si>
-    <t xml:space="preserve">36.1350364685059</t>
+    <t xml:space="preserve">36.1350326538086</t>
   </si>
   <si>
     <t xml:space="preserve">34.7930183410645</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1409454345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4391746520996</t>
+    <t xml:space="preserve">35.1409492492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4391784667969</t>
   </si>
   <si>
     <t xml:space="preserve">34.2462730407715</t>
@@ -4334,13 +4334,13 @@
     <t xml:space="preserve">35.0415420532227</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6995239257812</t>
+    <t xml:space="preserve">33.6995277404785</t>
   </si>
   <si>
     <t xml:space="preserve">34.1965675354004</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6439056396484</t>
+    <t xml:space="preserve">34.6439018249512</t>
   </si>
   <si>
     <t xml:space="preserve">35.0912437438965</t>
@@ -4349,7 +4349,7 @@
     <t xml:space="preserve">34.5444984436035</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0474548339844</t>
+    <t xml:space="preserve">34.0474510192871</t>
   </si>
   <si>
     <t xml:space="preserve">34.8924293518066</t>
@@ -4358,13 +4358,13 @@
     <t xml:space="preserve">34.9421310424805</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7433128356934</t>
+    <t xml:space="preserve">34.7433166503906</t>
   </si>
   <si>
     <t xml:space="preserve">35.3894691467285</t>
   </si>
   <si>
-    <t xml:space="preserve">36.3338508605957</t>
+    <t xml:space="preserve">36.333854675293</t>
   </si>
   <si>
     <t xml:space="preserve">36.0853309631348</t>
@@ -4376,10 +4376,10 @@
     <t xml:space="preserve">37.7255744934082</t>
   </si>
   <si>
-    <t xml:space="preserve">38.620246887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5705490112305</t>
+    <t xml:space="preserve">38.6202507019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.5705451965332</t>
   </si>
   <si>
     <t xml:space="preserve">36.7314872741699</t>
@@ -4391,7 +4391,7 @@
     <t xml:space="preserve">37.327938079834</t>
   </si>
   <si>
-    <t xml:space="preserve">36.6817817687988</t>
+    <t xml:space="preserve">36.6817855834961</t>
   </si>
   <si>
     <t xml:space="preserve">36.9800109863281</t>
@@ -4409,7 +4409,7 @@
     <t xml:space="preserve">33.9480476379395</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3456802368164</t>
+    <t xml:space="preserve">34.3456764221191</t>
   </si>
   <si>
     <t xml:space="preserve">34.0971565246582</t>
@@ -4418,7 +4418,7 @@
     <t xml:space="preserve">35.2900619506836</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1906547546387</t>
+    <t xml:space="preserve">35.1906585693359</t>
   </si>
   <si>
     <t xml:space="preserve">33.8983383178711</t>
@@ -5286,6 +5286,9 @@
   </si>
   <si>
     <t xml:space="preserve">32.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5</t>
   </si>
 </sst>
 </file>
@@ -72782,7 +72785,7 @@
     </row>
     <row r="2584">
       <c r="A2584" s="1" t="n">
-        <v>46084.691087963</v>
+        <v>46084.3333333333</v>
       </c>
       <c r="B2584" t="n">
         <v>30897</v>
@@ -72803,6 +72806,32 @@
         <v>1753</v>
       </c>
       <c r="H2584" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2585">
+      <c r="A2585" s="1" t="n">
+        <v>46085.6909837963</v>
+      </c>
+      <c r="B2585" t="n">
+        <v>15848</v>
+      </c>
+      <c r="C2585" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="D2585" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="E2585" t="n">
+        <v>32.6500015258789</v>
+      </c>
+      <c r="F2585" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="G2585" t="s">
+        <v>1758</v>
+      </c>
+      <c r="H2585" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MOL.MI.xlsx
+++ b/data/MOL.MI.xlsx
@@ -44,58 +44,58 @@
     <t xml:space="preserve">MOL.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75772619247437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66036510467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77100324630737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63823795318604</t>
+    <t xml:space="preserve">6.75772666931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66036558151245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77100276947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63823843002319</t>
   </si>
   <si>
     <t xml:space="preserve">6.72674751281738</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81525754928589</t>
+    <t xml:space="preserve">6.81525802612305</t>
   </si>
   <si>
     <t xml:space="preserve">6.54972791671753</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31960248947144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09832763671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35058164596558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23994445800781</t>
+    <t xml:space="preserve">6.31960201263428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09832811355591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35058069229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2399435043335</t>
   </si>
   <si>
     <t xml:space="preserve">6.5585789680481</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46121835708618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8947548866272</t>
+    <t xml:space="preserve">6.4612193107605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89475536346436</t>
   </si>
   <si>
     <t xml:space="preserve">6.52317523956299</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65594053268433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76215219497681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66479063034058</t>
+    <t xml:space="preserve">6.65594005584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76215171813965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66479110717773</t>
   </si>
   <si>
     <t xml:space="preserve">6.69134378433228</t>
@@ -104,34 +104,34 @@
     <t xml:space="preserve">6.68249273300171</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01866960525513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89917945861816</t>
+    <t xml:space="preserve">6.01867008209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89918088912964</t>
   </si>
   <si>
     <t xml:space="preserve">6.28419828414917</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06292390823364</t>
+    <t xml:space="preserve">6.06292343139648</t>
   </si>
   <si>
     <t xml:space="preserve">6.25321960449219</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39926195144653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34172916412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5098991394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33287858963013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42581462860107</t>
+    <t xml:space="preserve">6.39926099777222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34172964096069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50989866256714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33287906646729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42581367492676</t>
   </si>
   <si>
     <t xml:space="preserve">6.39041042327881</t>
@@ -146,34 +146,34 @@
     <t xml:space="preserve">6.3550066947937</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63381242752075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43466520309448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2266674041748</t>
+    <t xml:space="preserve">6.63381195068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43466567993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22666645050049</t>
   </si>
   <si>
     <t xml:space="preserve">6.24436855316162</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27534866333008</t>
+    <t xml:space="preserve">6.27534770965576</t>
   </si>
   <si>
     <t xml:space="preserve">6.2664966583252</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62938594818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43909120559692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41253757476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45236730575562</t>
+    <t xml:space="preserve">6.62938690185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43909072875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41253709793091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45236825942993</t>
   </si>
   <si>
     <t xml:space="preserve">6.4567928314209</t>
@@ -182,16 +182,16 @@
     <t xml:space="preserve">6.36828279495239</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19568872451782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06735038757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28862428665161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20453977584839</t>
+    <t xml:space="preserve">6.19568824768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06734991073608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28862380981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20454025268555</t>
   </si>
   <si>
     <t xml:space="preserve">6.29304933547974</t>
@@ -203,25 +203,25 @@
     <t xml:space="preserve">6.22224187850952</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25764560699463</t>
+    <t xml:space="preserve">6.25764608383179</t>
   </si>
   <si>
     <t xml:space="preserve">6.15585947036743</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1912636756897</t>
+    <t xml:space="preserve">6.19126272201538</t>
   </si>
   <si>
     <t xml:space="preserve">6.58955812454224</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47892045974731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49662303924561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42138910293579</t>
+    <t xml:space="preserve">6.47892093658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49662256240845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42138862609863</t>
   </si>
   <si>
     <t xml:space="preserve">6.63348960876465</t>
@@ -233,13 +233,13 @@
     <t xml:space="preserve">6.54311466217041</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44370222091675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50696420669556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55667161941528</t>
+    <t xml:space="preserve">6.44370269775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50696516036987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55667066574097</t>
   </si>
   <si>
     <t xml:space="preserve">6.36688423156738</t>
@@ -248,25 +248,25 @@
     <t xml:space="preserve">6.61993217468262</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69223308563232</t>
+    <t xml:space="preserve">6.69223260879517</t>
   </si>
   <si>
     <t xml:space="preserve">6.59734010696411</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68319511413574</t>
+    <t xml:space="preserve">6.6831955909729</t>
   </si>
   <si>
     <t xml:space="preserve">6.70578908920288</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7509765625</t>
+    <t xml:space="preserve">6.75097560882568</t>
   </si>
   <si>
     <t xml:space="preserve">6.85038805007935</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94528150558472</t>
+    <t xml:space="preserve">6.94528102874756</t>
   </si>
   <si>
     <t xml:space="preserve">6.98594999313354</t>
@@ -275,31 +275,31 @@
     <t xml:space="preserve">7.10343742370605</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25255441665649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32033586502075</t>
+    <t xml:space="preserve">7.25255393981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32033634185791</t>
   </si>
   <si>
     <t xml:space="preserve">7.45589780807495</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30226039886475</t>
+    <t xml:space="preserve">7.3022608757019</t>
   </si>
   <si>
     <t xml:space="preserve">7.37907886505127</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25707340240479</t>
+    <t xml:space="preserve">7.25707292556763</t>
   </si>
   <si>
     <t xml:space="preserve">7.22996139526367</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22544288635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19833040237427</t>
+    <t xml:space="preserve">7.22544240951538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19832992553711</t>
   </si>
   <si>
     <t xml:space="preserve">7.09439897537231</t>
@@ -308,61 +308,61 @@
     <t xml:space="preserve">7.13958692550659</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00402498245239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08084297180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95883798599243</t>
+    <t xml:space="preserve">7.00402450561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08084392547607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95883750915527</t>
   </si>
   <si>
     <t xml:space="preserve">6.84135103225708</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11699342727661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16669845581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31129837036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32485437393188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99950551986694</t>
+    <t xml:space="preserve">7.11699295043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16669893264771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31129884719849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32485342025757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9995059967041</t>
   </si>
   <si>
     <t xml:space="preserve">6.73290109634399</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08988094329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18477439880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85942602157593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67867660522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49792814254761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57022762298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57926368713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41659021377563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74645805358887</t>
+    <t xml:space="preserve">7.08988046646118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18477344512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85942649841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67867612838745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49792718887329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57022714614868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57926511764526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41658973693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74645709991455</t>
   </si>
   <si>
     <t xml:space="preserve">6.65156507492065</t>
@@ -374,22 +374,19 @@
     <t xml:space="preserve">6.46177768707275</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43466567993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75549459457397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56570768356323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77808856964111</t>
+    <t xml:space="preserve">6.75549507141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56570816040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77808904647827</t>
   </si>
   <si>
     <t xml:space="preserve">6.71030807495117</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48889064788818</t>
+    <t xml:space="preserve">6.48888969421387</t>
   </si>
   <si>
     <t xml:space="preserve">6.53859615325928</t>
@@ -404,10 +401,10 @@
     <t xml:space="preserve">6.76001358032227</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87750101089478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70126962661743</t>
+    <t xml:space="preserve">6.87750053405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70127058029175</t>
   </si>
   <si>
     <t xml:space="preserve">6.7871265411377</t>
@@ -416,25 +413,25 @@
     <t xml:space="preserve">6.7961630821228</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81423759460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81875705718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82327556610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80520153045654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92268753051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90461349487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86846256256104</t>
+    <t xml:space="preserve">6.81423807144165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81875658035278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82327604293823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80520105361938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92268657684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90461301803589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86846303939819</t>
   </si>
   <si>
     <t xml:space="preserve">6.98143148422241</t>
@@ -443,34 +440,34 @@
     <t xml:space="preserve">7.17573595046997</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0130615234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97691202163696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64252710342407</t>
+    <t xml:space="preserve">7.01306247711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97691249847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64252662658691</t>
   </si>
   <si>
     <t xml:space="preserve">6.6967511177063</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88653755187988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.931725025177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02209997177124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99046945571899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19381141662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05824947357178</t>
+    <t xml:space="preserve">6.88653707504272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93172550201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02209949493408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99046802520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19381093978882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05824899673462</t>
   </si>
   <si>
     <t xml:space="preserve">7.04921197891235</t>
@@ -482,34 +479,34 @@
     <t xml:space="preserve">7.14862394332886</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08536195755005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06276845932007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15766143798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21188640594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38359785079956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22092342376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24803590774536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18929243087769</t>
+    <t xml:space="preserve">7.08536291122437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06276798248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15766191482544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21188688278198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38359880447388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22092294692993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24803686141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18929290771484</t>
   </si>
   <si>
     <t xml:space="preserve">7.35648584365845</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37004089355469</t>
+    <t xml:space="preserve">7.370041847229</t>
   </si>
   <si>
     <t xml:space="preserve">6.88201856613159</t>
@@ -521,22 +518,22 @@
     <t xml:space="preserve">7.18025541305542</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91365003585815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5191593170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47849082946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50108575820923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41070938110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27514791488647</t>
+    <t xml:space="preserve">6.91365098953247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51915836334229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47848987579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50108480453491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41070890426636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27514839172363</t>
   </si>
   <si>
     <t xml:space="preserve">7.60953426361084</t>
@@ -545,46 +542,46 @@
     <t xml:space="preserve">7.66375780105591</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72702074050903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68183374404907</t>
+    <t xml:space="preserve">7.72702169418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68183469772339</t>
   </si>
   <si>
     <t xml:space="preserve">7.67731523513794</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63664627075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77220916748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97103261947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34156608581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41386890411377</t>
+    <t xml:space="preserve">7.63664674758911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77220821380615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97103214263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34156799316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41386699676514</t>
   </si>
   <si>
     <t xml:space="preserve">8.45001792907715</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57653999328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37771892547607</t>
+    <t xml:space="preserve">8.57654190063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37771701812744</t>
   </si>
   <si>
     <t xml:space="preserve">8.409348487854</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35964107513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22408199310303</t>
+    <t xml:space="preserve">8.35964202880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22408103942871</t>
   </si>
   <si>
     <t xml:space="preserve">8.24215602874756</t>
@@ -599,34 +596,34 @@
     <t xml:space="preserve">8.32349300384521</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36416149139404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37319755554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46809196472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30541706085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30089855194092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09755611419678</t>
+    <t xml:space="preserve">8.36416244506836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37320041656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46809101104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30541801452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30090045928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09755516052246</t>
   </si>
   <si>
     <t xml:space="preserve">8.26926708221436</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20600509643555</t>
+    <t xml:space="preserve">8.20600700378418</t>
   </si>
   <si>
     <t xml:space="preserve">8.0749626159668</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11111259460449</t>
+    <t xml:space="preserve">8.11111354827881</t>
   </si>
   <si>
     <t xml:space="preserve">8.28282451629639</t>
@@ -635,25 +632,25 @@
     <t xml:space="preserve">8.2963809967041</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40483093261719</t>
+    <t xml:space="preserve">8.40482997894287</t>
   </si>
   <si>
     <t xml:space="preserve">8.48164749145508</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4229040145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22859954833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2737865447998</t>
+    <t xml:space="preserve">8.42290496826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22860050201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27378749847412</t>
   </si>
   <si>
     <t xml:space="preserve">8.02977561950684</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13370609283447</t>
+    <t xml:space="preserve">8.13370704650879</t>
   </si>
   <si>
     <t xml:space="preserve">8.27830505371094</t>
@@ -665,22 +662,22 @@
     <t xml:space="preserve">8.6940279006958</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57969951629639</t>
+    <t xml:space="preserve">9.57969856262207</t>
   </si>
   <si>
     <t xml:space="preserve">9.25435066223145</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21820068359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01937580108643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16397666931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20012664794922</t>
+    <t xml:space="preserve">9.21819972991943</t>
+  </si>